--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2050" uniqueCount="2050">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2051" uniqueCount="2051">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,64 +44,64 @@
     <t xml:space="preserve">AMP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3910927772522</t>
+    <t xml:space="preserve">7.39109182357788</t>
   </si>
   <si>
     <t xml:space="preserve">7.31191825866699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36780500411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15357112884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96262311935425</t>
+    <t xml:space="preserve">7.36780548095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15357065200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96262264251709</t>
   </si>
   <si>
     <t xml:space="preserve">7.21877288818359</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27931785583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16288566589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0324821472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08836984634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1954870223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9859094619751</t>
+    <t xml:space="preserve">7.2793173789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1628851890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03248262405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08836936950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19548654556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98590898513794</t>
   </si>
   <si>
     <t xml:space="preserve">7.13494205474854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34451913833618</t>
+    <t xml:space="preserve">7.34451961517334</t>
   </si>
   <si>
     <t xml:space="preserve">7.23740196228027</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35383415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14891338348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18151426315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40972185134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28397464752197</t>
+    <t xml:space="preserve">7.35383462905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1489143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18151473999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40972137451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28397512435913</t>
   </si>
   <si>
     <t xml:space="preserve">7.13959932327271</t>
@@ -110,67 +110,67 @@
     <t xml:space="preserve">7.05111122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84619092941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51086664199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45497941970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5900411605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33389139175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2919750213623</t>
+    <t xml:space="preserve">6.84619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51086759567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45497989654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59004163742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33389234542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29197549819946</t>
   </si>
   <si>
     <t xml:space="preserve">6.42237949371338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61798477172852</t>
+    <t xml:space="preserve">6.61798572540283</t>
   </si>
   <si>
     <t xml:space="preserve">6.88344955444336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71113014221191</t>
+    <t xml:space="preserve">6.71113061904907</t>
   </si>
   <si>
     <t xml:space="preserve">6.8368763923645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70181560516357</t>
+    <t xml:space="preserve">6.70181608200073</t>
   </si>
   <si>
     <t xml:space="preserve">6.6272988319397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9952244758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89276456832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80427503585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79961824417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84153413772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65989971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63195610046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79496049880981</t>
+    <t xml:space="preserve">6.99522399902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8927640914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80427598953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7996187210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84153366088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65990018844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63195705413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79496192932129</t>
   </si>
   <si>
     <t xml:space="preserve">6.78564691543579</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">7.00919580459595</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11165618896484</t>
+    <t xml:space="preserve">7.111656665802</t>
   </si>
   <si>
     <t xml:space="preserve">7.08371210098267</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2094578742981</t>
+    <t xml:space="preserve">7.20945882797241</t>
   </si>
   <si>
     <t xml:space="preserve">7.10699844360352</t>
@@ -203,40 +203,40 @@
     <t xml:space="preserve">7.09768438339233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17220020294189</t>
+    <t xml:space="preserve">7.17219972610474</t>
   </si>
   <si>
     <t xml:space="preserve">6.93467950820923</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91605043411255</t>
+    <t xml:space="preserve">6.91604995727539</t>
   </si>
   <si>
     <t xml:space="preserve">7.00453805923462</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27000331878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32588958740234</t>
+    <t xml:space="preserve">7.27000284194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3258900642395</t>
   </si>
   <si>
     <t xml:space="preserve">7.22808790206909</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50286674499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41437864303589</t>
+    <t xml:space="preserve">7.50286769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41437911987305</t>
   </si>
   <si>
     <t xml:space="preserve">7.48423767089844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57738304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55409574508667</t>
+    <t xml:space="preserve">7.57738351821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55409717559814</t>
   </si>
   <si>
     <t xml:space="preserve">7.73107290267944</t>
@@ -245,28 +245,28 @@
     <t xml:space="preserve">7.60066938400269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64258527755737</t>
+    <t xml:space="preserve">7.64258480072021</t>
   </si>
   <si>
     <t xml:space="preserve">7.70313024520874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73573064804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88476324081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88942241668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8707914352417</t>
+    <t xml:space="preserve">7.73573112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88476276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88942050933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87079095840454</t>
   </si>
   <si>
     <t xml:space="preserve">7.78695964813232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94530630111694</t>
+    <t xml:space="preserve">7.9453067779541</t>
   </si>
   <si>
     <t xml:space="preserve">7.88010549545288</t>
@@ -281,19 +281,19 @@
     <t xml:space="preserve">8.09717178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10653305053711</t>
+    <t xml:space="preserve">8.10653209686279</t>
   </si>
   <si>
     <t xml:space="preserve">8.05036735534668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17205905914307</t>
+    <t xml:space="preserve">8.17205810546875</t>
   </si>
   <si>
     <t xml:space="preserve">8.21418190002441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23758506774902</t>
+    <t xml:space="preserve">8.23758602142334</t>
   </si>
   <si>
     <t xml:space="preserve">8.22354412078857</t>
@@ -308,73 +308,73 @@
     <t xml:space="preserve">8.08313083648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14397525787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01292419433594</t>
+    <t xml:space="preserve">8.14397621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01292514801025</t>
   </si>
   <si>
     <t xml:space="preserve">7.91463327407837</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8210244178772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64316892623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62912607192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65253019332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55891942977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63848829269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98952293395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9473991394043</t>
+    <t xml:space="preserve">7.82102537155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6431679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62912654876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6525297164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55892086029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63848781585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98952054977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94739818572998</t>
   </si>
   <si>
     <t xml:space="preserve">8.05972766876221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67593145370483</t>
+    <t xml:space="preserve">7.67593193054199</t>
   </si>
   <si>
     <t xml:space="preserve">7.71337461471558</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72273635864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87250947952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92867755889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89123153686523</t>
+    <t xml:space="preserve">7.72273588180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87250995635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92867565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89123201370239</t>
   </si>
   <si>
     <t xml:space="preserve">7.81166505813599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71805572509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88187074661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96143960952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91931486129761</t>
+    <t xml:space="preserve">7.71805620193481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88187122344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96143913269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91931533813477</t>
   </si>
   <si>
     <t xml:space="preserve">7.90995407104492</t>
@@ -383,25 +383,25 @@
     <t xml:space="preserve">8.05504703521729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18141841888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16737747192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19546031951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19077968597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30779266357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36395740509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34991550445557</t>
+    <t xml:space="preserve">8.18142032623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16737842559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19546127319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19078159332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3077917098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36395645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34991455078125</t>
   </si>
   <si>
     <t xml:space="preserve">8.33119487762451</t>
@@ -413,40 +413,40 @@
     <t xml:space="preserve">8.15333652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28906917572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36863613128662</t>
+    <t xml:space="preserve">8.28907012939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36863708496094</t>
   </si>
   <si>
     <t xml:space="preserve">8.50905132293701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60733985900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51373291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.635422706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75711345672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65414428710938</t>
+    <t xml:space="preserve">8.60733890533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51373100280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63542461395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75711441040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65414524078369</t>
   </si>
   <si>
     <t xml:space="preserve">8.78519725799561</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80860042572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92092895507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84604358673096</t>
+    <t xml:space="preserve">8.80859756469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92092990875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84604263305664</t>
   </si>
   <si>
     <t xml:space="preserve">8.81796073913574</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">8.74775409698486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75243377685547</t>
+    <t xml:space="preserve">8.75243473052979</t>
   </si>
   <si>
     <t xml:space="preserve">8.82264137268066</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">8.761794090271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65882587432861</t>
+    <t xml:space="preserve">8.6588249206543</t>
   </si>
   <si>
     <t xml:space="preserve">8.59329986572266</t>
@@ -482,31 +482,31 @@
     <t xml:space="preserve">8.56053638458252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4856481552124</t>
+    <t xml:space="preserve">8.48565006256104</t>
   </si>
   <si>
     <t xml:space="preserve">8.54181385040283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53245258331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66818714141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49969005584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61670112609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49500942230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5558557510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61202049255371</t>
+    <t xml:space="preserve">8.5324535369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66818618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49969100952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61670017242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49501037597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55585479736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61202144622803</t>
   </si>
   <si>
     <t xml:space="preserve">8.46692752838135</t>
@@ -515,13 +515,13 @@
     <t xml:space="preserve">8.52777290344238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56521701812744</t>
+    <t xml:space="preserve">8.56521606445312</t>
   </si>
   <si>
     <t xml:space="preserve">8.69158840179443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08006381988525</t>
+    <t xml:space="preserve">9.08006477355957</t>
   </si>
   <si>
     <t xml:space="preserve">9.24856185913086</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">9.07070255279541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01454067230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89284706115723</t>
+    <t xml:space="preserve">9.01453971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89284801483154</t>
   </si>
   <si>
     <t xml:space="preserve">8.93965244293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81328105926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50437164306641</t>
+    <t xml:space="preserve">8.81328010559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50436973571777</t>
   </si>
   <si>
     <t xml:space="preserve">8.42480278015137</t>
@@ -551,79 +551,79 @@
     <t xml:space="preserve">8.40140151977539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39671993255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58393955230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34523582458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46224594116211</t>
+    <t xml:space="preserve">8.39671897888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58393859863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34523487091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46224689483643</t>
   </si>
   <si>
     <t xml:space="preserve">8.3826789855957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47160720825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98645687103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09878730773926</t>
+    <t xml:space="preserve">8.47160625457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98645496368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09878826141357</t>
   </si>
   <si>
     <t xml:space="preserve">9.0613431930542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51841354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16269779205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31247234344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4419093132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98483991622925</t>
+    <t xml:space="preserve">8.51841163635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16269874572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31247138977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44190883636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98484182357788</t>
   </si>
   <si>
     <t xml:space="preserve">7.95675992965698</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38735961914062</t>
+    <t xml:space="preserve">8.38735771179199</t>
   </si>
   <si>
     <t xml:space="preserve">8.41076183319092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44820499420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4809684753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37331676483154</t>
+    <t xml:space="preserve">8.44820594787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48096942901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37331867218018</t>
   </si>
   <si>
     <t xml:space="preserve">8.2329044342041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18609809875488</t>
+    <t xml:space="preserve">8.18610095977783</t>
   </si>
   <si>
     <t xml:space="preserve">8.37799835205078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57925701141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64946556091309</t>
+    <t xml:space="preserve">8.57925796508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64946365356445</t>
   </si>
   <si>
     <t xml:space="preserve">8.72435092926025</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">8.74307346343994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7103099822998</t>
+    <t xml:space="preserve">8.71031093597412</t>
   </si>
   <si>
     <t xml:space="preserve">9.15495204925537</t>
@@ -647,31 +647,31 @@
     <t xml:space="preserve">9.14091205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26728248596191</t>
+    <t xml:space="preserve">9.26728343963623</t>
   </si>
   <si>
     <t xml:space="preserve">9.33749103546143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40769577026367</t>
+    <t xml:space="preserve">9.40769672393799</t>
   </si>
   <si>
     <t xml:space="preserve">9.37961578369141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29536628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36089324951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44513988494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48258399963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4357795715332</t>
+    <t xml:space="preserve">9.29536533355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36089134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44514083862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48258495330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43577861785889</t>
   </si>
   <si>
     <t xml:space="preserve">9.3562126159668</t>
@@ -689,22 +689,22 @@
     <t xml:space="preserve">9.4638614654541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81021595001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95999050140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82893657684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91318607330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64171886444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70724678039551</t>
+    <t xml:space="preserve">9.81021499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95998859405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82893753051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91318416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64171981811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70724391937256</t>
   </si>
   <si>
     <t xml:space="preserve">9.71660614013672</t>
@@ -716,67 +716,67 @@
     <t xml:space="preserve">9.79149341583252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0255165100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0067930221558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1846504211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2408151626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2595386505127</t>
+    <t xml:space="preserve">10.0255155563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0067939758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1846513748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.240816116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2595367431641</t>
   </si>
   <si>
     <t xml:space="preserve">10.4280347824097</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4748373031616</t>
+    <t xml:space="preserve">10.4748382568359</t>
   </si>
   <si>
     <t xml:space="preserve">10.3625078201294</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3344259262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5778093338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5122804641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5029201507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8118305206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8867177963257</t>
+    <t xml:space="preserve">10.3344249725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5778074264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5122814178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5029220581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8118314743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8867168426514</t>
   </si>
   <si>
     <t xml:space="preserve">10.7182207107544</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6526947021484</t>
+    <t xml:space="preserve">10.6526956558228</t>
   </si>
   <si>
     <t xml:space="preserve">10.6433334350586</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6246128082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7088613510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8960790634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8399133682251</t>
+    <t xml:space="preserve">10.6246118545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7088603973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8960771560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8399143218994</t>
   </si>
   <si>
     <t xml:space="preserve">10.9335222244263</t>
@@ -788,10 +788,10 @@
     <t xml:space="preserve">11.1301021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0926580429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2517919540405</t>
+    <t xml:space="preserve">11.092658996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2517929077148</t>
   </si>
   <si>
     <t xml:space="preserve">10.9616050720215</t>
@@ -803,25 +803,25 @@
     <t xml:space="preserve">11.1675443649292</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1488237380981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1862659454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2798748016357</t>
+    <t xml:space="preserve">11.1488218307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1862649917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2798757553101</t>
   </si>
   <si>
     <t xml:space="preserve">11.4296503067017</t>
   </si>
   <si>
-    <t xml:space="preserve">11.410927772522</t>
+    <t xml:space="preserve">11.4109268188477</t>
   </si>
   <si>
     <t xml:space="preserve">11.4577322006226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5801248550415</t>
+    <t xml:space="preserve">11.5801239013672</t>
   </si>
   <si>
     <t xml:space="preserve">11.8249073028564</t>
@@ -836,43 +836,43 @@
     <t xml:space="preserve">11.9190540313721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9284677505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9378833770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9661273956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602760314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0979347229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0226182937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2109098434448</t>
+    <t xml:space="preserve">11.9284687042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9378843307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9661283493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0602750778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0979337692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0226163864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2109117507935</t>
   </si>
   <si>
     <t xml:space="preserve">12.1826658248901</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2391557693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9096384048462</t>
+    <t xml:space="preserve">12.2391567230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9096393585205</t>
   </si>
   <si>
     <t xml:space="preserve">12.1450071334839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4859771728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2976808547974</t>
+    <t xml:space="preserve">11.4859762191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2976818084717</t>
   </si>
   <si>
     <t xml:space="preserve">11.6930999755859</t>
@@ -881,58 +881,58 @@
     <t xml:space="preserve">11.7307596206665</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7684173583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7590045928955</t>
+    <t xml:space="preserve">11.7684183120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7590036392212</t>
   </si>
   <si>
     <t xml:space="preserve">11.6271982192993</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5707092285156</t>
+    <t xml:space="preserve">11.5707101821899</t>
   </si>
   <si>
     <t xml:space="preserve">11.5236349105835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4671468734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3729982376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0811433792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8834342956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6951360702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5633325576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6104068756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7422113418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.911678314209</t>
+    <t xml:space="preserve">11.4671459197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3730001449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0811424255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8834323883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6951370239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5633335113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.610405921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7422122955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9116764068604</t>
   </si>
   <si>
     <t xml:space="preserve">10.9022626876831</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9493379592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1376314163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3541707992554</t>
+    <t xml:space="preserve">10.9493360519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1376304626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3541698455811</t>
   </si>
   <si>
     <t xml:space="preserve">11.3824138641357</t>
@@ -941,13 +941,13 @@
     <t xml:space="preserve">11.3447561264038</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4106578826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2694387435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5048055648804</t>
+    <t xml:space="preserve">11.4106588363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.269437789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5048046112061</t>
   </si>
   <si>
     <t xml:space="preserve">11.4294881820679</t>
@@ -959,28 +959,28 @@
     <t xml:space="preserve">11.2788524627686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2506074905396</t>
+    <t xml:space="preserve">11.2506065368652</t>
   </si>
   <si>
     <t xml:space="preserve">11.1093864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0340690612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9210920333862</t>
+    <t xml:space="preserve">11.0340700149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9210910797119</t>
   </si>
   <si>
     <t xml:space="preserve">10.6668939590454</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8363599777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7892866134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1941194534302</t>
+    <t xml:space="preserve">10.8363590240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.78928565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1941213607788</t>
   </si>
   <si>
     <t xml:space="preserve">11.1658754348755</t>
@@ -989,10 +989,10 @@
     <t xml:space="preserve">11.0717277526855</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1282157897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3165102005005</t>
+    <t xml:space="preserve">11.1282167434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3165121078491</t>
   </si>
   <si>
     <t xml:space="preserve">11.3259248733521</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">11.241192817688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0623140335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0905570983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1752901077271</t>
+    <t xml:space="preserve">11.062313079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0905561447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1752891540527</t>
   </si>
   <si>
     <t xml:space="preserve">11.4389019012451</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">11.984956741333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0132007598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9567136764526</t>
+    <t xml:space="preserve">12.0132026672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.956711769104</t>
   </si>
   <si>
     <t xml:space="preserve">12.0508604049683</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">12.0791044235229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9755430221558</t>
+    <t xml:space="preserve">11.9755420684814</t>
   </si>
   <si>
     <t xml:space="preserve">11.834321975708</t>
@@ -1046,46 +1046,46 @@
     <t xml:space="preserve">12.2203254699707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1544237136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1073484420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4839382171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5215978622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.643988609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7852096557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8134546279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8322849273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8040399551392</t>
+    <t xml:space="preserve">12.1544218063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1073474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4839372634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5215969085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6439895629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7852087020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8134536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8322830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8040409088135</t>
   </si>
   <si>
     <t xml:space="preserve">12.1920804977417</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7872467041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8531513214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0320320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1732521057129</t>
+    <t xml:space="preserve">11.7872495651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8531503677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0320310592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1732530593872</t>
   </si>
   <si>
     <t xml:space="preserve">12.2768135070801</t>
@@ -1097,73 +1097,73 @@
     <t xml:space="preserve">11.4483165740967</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5612955093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4012432098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6742706298828</t>
+    <t xml:space="preserve">11.5612936019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4012441635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6742715835571</t>
   </si>
   <si>
     <t xml:space="preserve">11.7778329849243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0885190963745</t>
+    <t xml:space="preserve">12.0885200500488</t>
   </si>
   <si>
     <t xml:space="preserve">12.0696887969971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2014951705933</t>
+    <t xml:space="preserve">12.2014970779419</t>
   </si>
   <si>
     <t xml:space="preserve">12.135594367981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3615465164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3333034515381</t>
+    <t xml:space="preserve">12.3615455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3333015441895</t>
   </si>
   <si>
     <t xml:space="preserve">12.1638374328613</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7401742935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1261787414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5404262542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5498418807983</t>
+    <t xml:space="preserve">11.7401733398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1261777877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5404253005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.549840927124</t>
   </si>
   <si>
     <t xml:space="preserve">12.5027675628662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6345748901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1335554122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1241407394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.086480140686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9546747207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4254121780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4630708694458</t>
+    <t xml:space="preserve">12.6345729827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1335535049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1241397857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0864791870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9546766281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4254112243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4630718231201</t>
   </si>
   <si>
     <t xml:space="preserve">13.5383882522583</t>
@@ -1172,22 +1172,22 @@
     <t xml:space="preserve">13.5572175979614</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6042928695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5101451873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2559461593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4724855422974</t>
+    <t xml:space="preserve">13.6042909622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5101442337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2559471130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.472484588623</t>
   </si>
   <si>
     <t xml:space="preserve">13.3030195236206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9735040664673</t>
+    <t xml:space="preserve">12.9735050201416</t>
   </si>
   <si>
     <t xml:space="preserve">12.615743637085</t>
@@ -1208,40 +1208,40 @@
     <t xml:space="preserve">12.8228693008423</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8793563842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.851113319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5969142913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2862272262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2579851150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7287225723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0394067764282</t>
+    <t xml:space="preserve">12.8793573379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8511123657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5969152450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2862281799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.257984161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7287216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0394096374512</t>
   </si>
   <si>
     <t xml:space="preserve">13.0958948135376</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2653608322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4065828323364</t>
+    <t xml:space="preserve">13.2653617858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4065818786621</t>
   </si>
   <si>
     <t xml:space="preserve">13.3312644958496</t>
   </si>
   <si>
-    <t xml:space="preserve">13.321849822998</t>
+    <t xml:space="preserve">13.3218488693237</t>
   </si>
   <si>
     <t xml:space="preserve">13.1617984771729</t>
@@ -1250,16 +1250,16 @@
     <t xml:space="preserve">13.3406791687012</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2465314865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8887701034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8605270385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2936038970947</t>
+    <t xml:space="preserve">13.2465333938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8887710571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8605279922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.293604850769</t>
   </si>
   <si>
     <t xml:space="preserve">13.566632270813</t>
@@ -1268,43 +1268,43 @@
     <t xml:space="preserve">13.6419506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3124341964722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7925844192505</t>
+    <t xml:space="preserve">13.3124351501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7925872802734</t>
   </si>
   <si>
     <t xml:space="preserve">13.9997110366821</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1409330368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3951301574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3009834289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5645942687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6022529602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6869859695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9129400253296</t>
+    <t xml:space="preserve">14.1409311294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3951292037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3009815216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5645952224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6022539138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6869869232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9129390716553</t>
   </si>
   <si>
     <t xml:space="preserve">14.8564510345459</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1106491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.969428062439</t>
+    <t xml:space="preserve">15.1106472015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9694271087646</t>
   </si>
   <si>
     <t xml:space="preserve">14.9976720809937</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">15.0353317260742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.903525352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8941106796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7152318954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5928382873535</t>
+    <t xml:space="preserve">14.9035243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8941097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7152299880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5928392410278</t>
   </si>
   <si>
     <t xml:space="preserve">15.1671380996704</t>
@@ -1331,22 +1331,22 @@
     <t xml:space="preserve">15.2706995010376</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2424564361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2518711090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4401655197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3930931091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5531435012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6567039489746</t>
+    <t xml:space="preserve">15.2424554824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2518720626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4401636123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3930921554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5531425476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6567058563232</t>
   </si>
   <si>
     <t xml:space="preserve">15.4213342666626</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">15.0165004730225</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3460168838501</t>
+    <t xml:space="preserve">15.3460159301758</t>
   </si>
   <si>
     <t xml:space="preserve">14.818528175354</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">14.3444862365723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6099491119385</t>
+    <t xml:space="preserve">14.6099500656128</t>
   </si>
   <si>
     <t xml:space="preserve">14.7332000732422</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">14.8754119873047</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9273300170898</t>
+    <t xml:space="preserve">13.9273290634155</t>
   </si>
   <si>
     <t xml:space="preserve">14.4013710021973</t>
@@ -1391,13 +1391,13 @@
     <t xml:space="preserve">15.1882801055908</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4916667938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1173992156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4587078094482</t>
+    <t xml:space="preserve">15.4916658401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1174030303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4587116241455</t>
   </si>
   <si>
     <t xml:space="preserve">16.1553249359131</t>
@@ -1409,19 +1409,19 @@
     <t xml:space="preserve">16.202730178833</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2122116088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3259792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1079177856445</t>
+    <t xml:space="preserve">16.2122077941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3259773254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1079216003418</t>
   </si>
   <si>
     <t xml:space="preserve">16.069995880127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.525074005127</t>
+    <t xml:space="preserve">16.5250778198242</t>
   </si>
   <si>
     <t xml:space="preserve">16.7241725921631</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">16.6672897338867</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5724811553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3070163726807</t>
+    <t xml:space="preserve">16.5724792480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3070182800293</t>
   </si>
   <si>
     <t xml:space="preserve">16.2596111297607</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">16.6767673492432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8379421234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8853454589844</t>
+    <t xml:space="preserve">16.8379440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.885347366333</t>
   </si>
   <si>
     <t xml:space="preserve">17.0465221405029</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9232711791992</t>
+    <t xml:space="preserve">16.9232692718506</t>
   </si>
   <si>
     <t xml:space="preserve">16.771577835083</t>
@@ -1460,25 +1460,25 @@
     <t xml:space="preserve">16.3733825683594</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4492282867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2216892242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4018249511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5535182952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3639011383057</t>
+    <t xml:space="preserve">16.4492301940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2216911315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4018230438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5535163879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3639049530029</t>
   </si>
   <si>
     <t xml:space="preserve">16.5155944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1034069061279</t>
+    <t xml:space="preserve">17.1034088134766</t>
   </si>
   <si>
     <t xml:space="preserve">17.5395221710205</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">18.0799331665039</t>
   </si>
   <si>
-    <t xml:space="preserve">18.16526222229</t>
+    <t xml:space="preserve">18.1652584075928</t>
   </si>
   <si>
     <t xml:space="preserve">18.715145111084</t>
@@ -1505,34 +1505,34 @@
     <t xml:space="preserve">18.4117584228516</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2505874633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0704517364502</t>
+    <t xml:space="preserve">18.2505855560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0704498291016</t>
   </si>
   <si>
     <t xml:space="preserve">17.8618717193604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6343307495117</t>
+    <t xml:space="preserve">17.634334564209</t>
   </si>
   <si>
     <t xml:space="preserve">17.7860260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7575836181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2979888916016</t>
+    <t xml:space="preserve">17.7575798034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2979869842529</t>
   </si>
   <si>
     <t xml:space="preserve">18.3738346099854</t>
   </si>
   <si>
-    <t xml:space="preserve">18.203182220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0325260162354</t>
+    <t xml:space="preserve">18.2031803131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.032527923584</t>
   </si>
   <si>
     <t xml:space="preserve">18.1083736419678</t>
@@ -1541,22 +1541,22 @@
     <t xml:space="preserve">18.2126617431641</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0609683990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9377174377441</t>
+    <t xml:space="preserve">18.0609664916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9377193450928</t>
   </si>
   <si>
     <t xml:space="preserve">18.0040836334229</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5774478912354</t>
+    <t xml:space="preserve">17.577449798584</t>
   </si>
   <si>
     <t xml:space="preserve">18.3927974700928</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8334274291992</t>
+    <t xml:space="preserve">17.8334293365479</t>
   </si>
   <si>
     <t xml:space="preserve">18.0135650634766</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">18.7435874938965</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3408813476562</t>
+    <t xml:space="preserve">19.3408794403076</t>
   </si>
   <si>
     <t xml:space="preserve">19.41672706604</t>
@@ -1574,43 +1574,43 @@
     <t xml:space="preserve">19.3788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1891860961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0564556121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7246246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4496841430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5255298614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.772029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9616508483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6867027282715</t>
+    <t xml:space="preserve">19.18918800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0564575195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7246265411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4496803283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5255317687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7720317840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9616470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6867046356201</t>
   </si>
   <si>
     <t xml:space="preserve">18.1462955474854</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5065689086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0420074462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3025054931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5629978179932</t>
+    <t xml:space="preserve">18.5065670013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0420093536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3025035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5629959106445</t>
   </si>
   <si>
     <t xml:space="preserve">15.4537420272827</t>
@@ -1619,82 +1619,82 @@
     <t xml:space="preserve">15.5864744186401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6718006134033</t>
+    <t xml:space="preserve">15.6718044281006</t>
   </si>
   <si>
     <t xml:space="preserve">15.0081443786621</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4252996444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4632244110107</t>
+    <t xml:space="preserve">15.4253005981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4632234573364</t>
   </si>
   <si>
     <t xml:space="preserve">15.8045330047607</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7286863327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9512596130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0745096206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9986639022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9797019958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0176258087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8469686508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6573524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7047567367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6763143539429</t>
+    <t xml:space="preserve">15.7286853790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9512586593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0745086669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9986619949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9797029495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0176248550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8469696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6573534011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7047576904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6763153076172</t>
   </si>
   <si>
     <t xml:space="preserve">14.6478719711304</t>
   </si>
   <si>
-    <t xml:space="preserve">14.932297706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0555477142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7900848388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8135585784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.728232383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1309413909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0835380554199</t>
+    <t xml:space="preserve">14.9322986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0555486679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7900857925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8135595321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7282333374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1309423446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0835371017456</t>
   </si>
   <si>
     <t xml:space="preserve">13.3869228363037</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2636709213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3964042663574</t>
+    <t xml:space="preserve">13.263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3964033126831</t>
   </si>
   <si>
     <t xml:space="preserve">13.6523857116699</t>
@@ -1715,43 +1715,43 @@
     <t xml:space="preserve">14.4961795806885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2212362289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1643505096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3065624237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3350048065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7945985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7377119064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5955018997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7566747665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8988876342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9462919235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4203338623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7756376266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7232656478882</t>
+    <t xml:space="preserve">14.2212352752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1643495559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3065633773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3350057601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7945995330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7377138137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5955009460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7566757202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.898886680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9462938308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4203329086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7756366729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7232646942139</t>
   </si>
   <si>
     <t xml:space="preserve">13.320556640625</t>
@@ -1760,70 +1760,70 @@
     <t xml:space="preserve">13.1878252029419</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7471942901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0695428848267</t>
+    <t xml:space="preserve">13.7471933364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.069543838501</t>
   </si>
   <si>
     <t xml:space="preserve">14.8374891281128</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2546443939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8848924636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0839900970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1787986755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1503562927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3115320205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3589353561401</t>
+    <t xml:space="preserve">15.2546453475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8848934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0839910507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1787996292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1503582000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3115301132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3589372634888</t>
   </si>
   <si>
     <t xml:space="preserve">15.2925682067871</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1408767700195</t>
+    <t xml:space="preserve">15.1408758163452</t>
   </si>
   <si>
     <t xml:space="preserve">15.0271062850952</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9228172302246</t>
+    <t xml:space="preserve">14.922815322876</t>
   </si>
   <si>
     <t xml:space="preserve">14.8280086517334</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8659324645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.941780090332</t>
+    <t xml:space="preserve">14.8659315109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9417781829834</t>
   </si>
   <si>
     <t xml:space="preserve">15.6149158477783</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7097253799438</t>
+    <t xml:space="preserve">15.7097225189209</t>
   </si>
   <si>
     <t xml:space="preserve">15.0650291442871</t>
   </si>
   <si>
-    <t xml:space="preserve">15.216721534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5485515594482</t>
+    <t xml:space="preserve">15.2167205810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5485506057739</t>
   </si>
   <si>
     <t xml:space="preserve">15.4347820281982</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">15.396858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7806043624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9038543701172</t>
+    <t xml:space="preserve">14.7806053161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9038553237915</t>
   </si>
   <si>
     <t xml:space="preserve">15.2262029647827</t>
@@ -1844,34 +1844,34 @@
     <t xml:space="preserve">15.1977605819702</t>
   </si>
   <si>
-    <t xml:space="preserve">15.444260597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3684148788452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5106287002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7381677627563</t>
+    <t xml:space="preserve">15.4442625045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3684139251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.510630607605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7381687164307</t>
   </si>
   <si>
     <t xml:space="preserve">16.4302673339844</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9657068252563</t>
+    <t xml:space="preserve">15.965705871582</t>
   </si>
   <si>
     <t xml:space="preserve">15.2641267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">15.785572052002</t>
+    <t xml:space="preserve">15.7855701446533</t>
   </si>
   <si>
     <t xml:space="preserve">16.6862506866455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8474235534668</t>
+    <t xml:space="preserve">16.8474254608154</t>
   </si>
   <si>
     <t xml:space="preserve">16.4966335296631</t>
@@ -1880,13 +1880,13 @@
     <t xml:space="preserve">16.1932468414307</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2311725616455</t>
+    <t xml:space="preserve">16.2311706542969</t>
   </si>
   <si>
     <t xml:space="preserve">16.7526149749756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4207859039307</t>
+    <t xml:space="preserve">16.4207878112793</t>
   </si>
   <si>
     <t xml:space="preserve">16.8094997406006</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">16.8948287963867</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8663864135742</t>
+    <t xml:space="preserve">16.8663845062256</t>
   </si>
   <si>
     <t xml:space="preserve">16.2501316070557</t>
@@ -1907,19 +1907,19 @@
     <t xml:space="preserve">15.8993425369263</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8898620605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9277830123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8519353866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3544216156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.240650177002</t>
+    <t xml:space="preserve">15.8898611068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9277839660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8519382476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3544235229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2406482696533</t>
   </si>
   <si>
     <t xml:space="preserve">15.9183044433594</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">17.283540725708</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8239459991455</t>
+    <t xml:space="preserve">17.8239498138428</t>
   </si>
   <si>
     <t xml:space="preserve">18.6677417755127</t>
@@ -1949,13 +1949,13 @@
     <t xml:space="preserve">18.5743827819824</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8704280853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5962142944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5007152557373</t>
+    <t xml:space="preserve">18.8704261779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.596212387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5007133483887</t>
   </si>
   <si>
     <t xml:space="preserve">18.9277248382568</t>
@@ -1964,52 +1964,52 @@
     <t xml:space="preserve">18.9468250274658</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9850254058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5934810638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7080783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9659252166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0327739715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2333183288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.386116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0900707244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1951236724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.118724822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.252420425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9018058776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1501045227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2646980285645</t>
+    <t xml:space="preserve">18.9850234985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5934791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7080821990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9659271240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0327758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2333164215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3861179351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0900726318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1951198577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1187229156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2524223327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9018077850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1501026153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2646999359131</t>
   </si>
   <si>
     <t xml:space="preserve">20.589391708374</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5511951446533</t>
+    <t xml:space="preserve">20.5511932373047</t>
   </si>
   <si>
     <t xml:space="preserve">20.7994899749756</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">19.9591045379639</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8445091247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4816150665283</t>
+    <t xml:space="preserve">19.8445110321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4816131591797</t>
   </si>
   <si>
     <t xml:space="preserve">19.3097171783447</t>
@@ -2030,10 +2030,10 @@
     <t xml:space="preserve">19.6344108581543</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6726131439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0928077697754</t>
+    <t xml:space="preserve">19.6726112365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0928039550781</t>
   </si>
   <si>
     <t xml:space="preserve">19.9400062561035</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">19.5580139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">19.729907989502</t>
+    <t xml:space="preserve">19.7299098968506</t>
   </si>
   <si>
     <t xml:space="preserve">20.3028984069824</t>
@@ -2054,13 +2054,13 @@
     <t xml:space="preserve">20.2837982177734</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2265014648438</t>
+    <t xml:space="preserve">20.2264995574951</t>
   </si>
   <si>
     <t xml:space="preserve">20.7039890289307</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6848907470703</t>
+    <t xml:space="preserve">20.6848888397217</t>
   </si>
   <si>
     <t xml:space="preserve">20.4174957275391</t>
@@ -2072,10 +2072,10 @@
     <t xml:space="preserve">20.1310024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1882972717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2769813537598</t>
+    <t xml:space="preserve">20.1883010864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2769794464111</t>
   </si>
   <si>
     <t xml:space="preserve">21.1814804077148</t>
@@ -2108,19 +2108,19 @@
     <t xml:space="preserve">21.2960777282715</t>
   </si>
   <si>
-    <t xml:space="preserve">21.849967956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4802551269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5566520690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5184555053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0982608795166</t>
+    <t xml:space="preserve">21.8499660491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4802589416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5566558837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5184535980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0982627868652</t>
   </si>
   <si>
     <t xml:space="preserve">22.2510585784912</t>
@@ -2132,13 +2132,13 @@
     <t xml:space="preserve">21.9454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3083610534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5948543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.747652053833</t>
+    <t xml:space="preserve">22.3083629608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5948524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7476501464844</t>
   </si>
   <si>
     <t xml:space="preserve">22.8049488067627</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">21.3533802032471</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4747943878174</t>
+    <t xml:space="preserve">20.474796295166</t>
   </si>
   <si>
     <t xml:space="preserve">20.455696105957</t>
@@ -2168,52 +2168,52 @@
     <t xml:space="preserve">20.8758869171143</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0859813690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7353687286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.506175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2196807861328</t>
+    <t xml:space="preserve">21.0859851837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7353706359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5061740875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2196788787842</t>
   </si>
   <si>
     <t xml:space="preserve">21.3724765777588</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6016731262207</t>
+    <t xml:space="preserve">21.6016750335693</t>
   </si>
   <si>
     <t xml:space="preserve">21.678071975708</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4870758056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5825710296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.646692276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6084938049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.493896484375</t>
+    <t xml:space="preserve">21.4870777130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5825729370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6466941833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.608491897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4938945770264</t>
   </si>
   <si>
     <t xml:space="preserve">20.8567867279053</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3792991638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8949871063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9331855773926</t>
+    <t xml:space="preserve">20.3792972564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8949851989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9331874847412</t>
   </si>
   <si>
     <t xml:space="preserve">20.3219985961914</t>
@@ -2222,7 +2222,7 @@
     <t xml:space="preserve">20.3410968780518</t>
   </si>
   <si>
-    <t xml:space="preserve">21.830867767334</t>
+    <t xml:space="preserve">21.8308696746826</t>
   </si>
   <si>
     <t xml:space="preserve">22.0218658447266</t>
@@ -2234,10 +2234,10 @@
     <t xml:space="preserve">22.6521511077881</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0150470733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4543342590332</t>
+    <t xml:space="preserve">23.0150451660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4543380737305</t>
   </si>
   <si>
     <t xml:space="preserve">23.7217330932617</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">23.5689353942871</t>
   </si>
   <si>
-    <t xml:space="preserve">24.084623336792</t>
+    <t xml:space="preserve">24.0846214294434</t>
   </si>
   <si>
     <t xml:space="preserve">23.7981300354004</t>
@@ -2258,40 +2258,40 @@
     <t xml:space="preserve">23.8745269775391</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9700260162354</t>
+    <t xml:space="preserve">23.970027923584</t>
   </si>
   <si>
     <t xml:space="preserve">24.3711185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8677082061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0969066619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3642978668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3329162597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.982307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.287899017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9250049591064</t>
+    <t xml:space="preserve">24.8677101135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.09690284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3642997741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3329181671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9823055267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2879009246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9250068664551</t>
   </si>
   <si>
     <t xml:space="preserve">25.0205059051514</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6194133758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9441089630127</t>
+    <t xml:space="preserve">24.6194152832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9441108703613</t>
   </si>
   <si>
     <t xml:space="preserve">24.8295097351074</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">24.4475173950195</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5430164337158</t>
+    <t xml:space="preserve">24.5430183410645</t>
   </si>
   <si>
     <t xml:space="preserve">24.3520164489746</t>
@@ -2321,19 +2321,19 @@
     <t xml:space="preserve">24.5621147155762</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5812129974365</t>
+    <t xml:space="preserve">24.5812149047852</t>
   </si>
   <si>
     <t xml:space="preserve">24.6958122253418</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3069972991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3451995849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8486080169678</t>
+    <t xml:space="preserve">25.306999206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3451976776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8486099243164</t>
   </si>
   <si>
     <t xml:space="preserve">25.0014057159424</t>
@@ -2342,10 +2342,10 @@
     <t xml:space="preserve">25.2115039825439</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7653884887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6125946044922</t>
+    <t xml:space="preserve">25.7653903961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6125926971436</t>
   </si>
   <si>
     <t xml:space="preserve">25.5552959442139</t>
@@ -2354,19 +2354,19 @@
     <t xml:space="preserve">25.154203414917</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8226890563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7722110748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5239162445068</t>
+    <t xml:space="preserve">25.8226909637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7722091674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5239143371582</t>
   </si>
   <si>
     <t xml:space="preserve">24.9059066772461</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6698932647705</t>
+    <t xml:space="preserve">25.6698913574219</t>
   </si>
   <si>
     <t xml:space="preserve">26.2237815856934</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">27.1405620574951</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2169609069824</t>
+    <t xml:space="preserve">27.2169628143311</t>
   </si>
   <si>
     <t xml:space="preserve">27.5225563049316</t>
@@ -2402,25 +2402,25 @@
     <t xml:space="preserve">28.2865428924561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8854503631592</t>
+    <t xml:space="preserve">27.8854484558105</t>
   </si>
   <si>
     <t xml:space="preserve">25.9754867553711</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2306022644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6003150939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6071319580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4666156768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4352359771729</t>
+    <t xml:space="preserve">25.2306041717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6003131866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6071300506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4666175842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4352378845215</t>
   </si>
   <si>
     <t xml:space="preserve">19.8254089355469</t>
@@ -2429,19 +2429,19 @@
     <t xml:space="preserve">19.3479175567627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5852909088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3233585357666</t>
+    <t xml:space="preserve">15.5852899551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.323356628418</t>
   </si>
   <si>
     <t xml:space="preserve">15.7285394668579</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1200790405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.903169631958</t>
+    <t xml:space="preserve">16.120080947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9031677246094</t>
   </si>
   <si>
     <t xml:space="preserve">17.523904800415</t>
@@ -2450,25 +2450,25 @@
     <t xml:space="preserve">17.7435493469238</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1350898742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8322277069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1446437835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.221040725708</t>
+    <t xml:space="preserve">18.1350917816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8322296142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1446418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2210388183594</t>
   </si>
   <si>
     <t xml:space="preserve">18.1159896850586</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8772449493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3806552886963</t>
+    <t xml:space="preserve">17.8772468566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3806571960449</t>
   </si>
   <si>
     <t xml:space="preserve">17.4093055725098</t>
@@ -2477,22 +2477,22 @@
     <t xml:space="preserve">16.8076686859131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6480522155762</t>
+    <t xml:space="preserve">17.6480503082275</t>
   </si>
   <si>
     <t xml:space="preserve">18.7844791412354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4311351776123</t>
+    <t xml:space="preserve">18.4311370849609</t>
   </si>
   <si>
     <t xml:space="preserve">18.4454593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7653770446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9536418914795</t>
+    <t xml:space="preserve">18.7653789520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9536437988281</t>
   </si>
   <si>
     <t xml:space="preserve">20.8663387298584</t>
@@ -2507,64 +2507,64 @@
     <t xml:space="preserve">20.0068550109863</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2455997467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9877529144287</t>
+    <t xml:space="preserve">20.2456016540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9877548217773</t>
   </si>
   <si>
     <t xml:space="preserve">19.9686546325684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7681102752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6753406524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7640209197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3820247650146</t>
+    <t xml:space="preserve">19.7681083679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6753387451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7640228271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3820266723633</t>
   </si>
   <si>
     <t xml:space="preserve">22.3370056152344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7926712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0191345214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4297771453857</t>
+    <t xml:space="preserve">21.792667388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0191383361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4297752380371</t>
   </si>
   <si>
     <t xml:space="preserve">21.8595161437988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9522876739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9932174682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6589698791504</t>
+    <t xml:space="preserve">20.9522857666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9932155609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6589736938477</t>
   </si>
   <si>
     <t xml:space="preserve">23.0341453552246</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1391925811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2797088623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5020885467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8267784118652</t>
+    <t xml:space="preserve">23.1391906738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2797107696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5020866394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8267803192139</t>
   </si>
   <si>
     <t xml:space="preserve">23.5211849212646</t>
@@ -2573,22 +2573,22 @@
     <t xml:space="preserve">23.8458786010742</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8172302246094</t>
+    <t xml:space="preserve">23.8172283172607</t>
   </si>
   <si>
     <t xml:space="preserve">23.3588371276855</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6903514862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6330528259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8881664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0696144104004</t>
+    <t xml:space="preserve">22.6903495788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6330547332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8881702423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0696125030518</t>
   </si>
   <si>
     <t xml:space="preserve">22.6999015808105</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">23.3015403747559</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6808032989502</t>
+    <t xml:space="preserve">22.6808013916016</t>
   </si>
   <si>
     <t xml:space="preserve">22.7094497680664</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">23.4638862609863</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4229564666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4611587524414</t>
+    <t xml:space="preserve">22.4229545593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4611549377441</t>
   </si>
   <si>
     <t xml:space="preserve">22.6426029205322</t>
@@ -2624,13 +2624,13 @@
     <t xml:space="preserve">22.7380981445312</t>
   </si>
   <si>
-    <t xml:space="preserve">23.272891998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2442417144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5402851104736</t>
+    <t xml:space="preserve">23.2728900909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2442398071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.540283203125</t>
   </si>
   <si>
     <t xml:space="preserve">23.7408313751221</t>
@@ -2639,16 +2639,16 @@
     <t xml:space="preserve">23.8363285064697</t>
   </si>
   <si>
-    <t xml:space="preserve">23.71217918396</t>
+    <t xml:space="preserve">23.7121810913086</t>
   </si>
   <si>
     <t xml:space="preserve">23.7599296569824</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1610221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3233680725098</t>
+    <t xml:space="preserve">24.1610202789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3233699798584</t>
   </si>
   <si>
     <t xml:space="preserve">24.7340106964111</t>
@@ -2666,13 +2666,13 @@
     <t xml:space="preserve">24.7531108856201</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1351013183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5580234527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5102787017822</t>
+    <t xml:space="preserve">25.1351051330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5580253601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5102767944336</t>
   </si>
   <si>
     <t xml:space="preserve">27.6467056274414</t>
@@ -2681,13 +2681,13 @@
     <t xml:space="preserve">28.2292404174805</t>
   </si>
   <si>
-    <t xml:space="preserve">27.503454208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5894031524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1596641540527</t>
+    <t xml:space="preserve">27.5034561157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5894050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1596622467041</t>
   </si>
   <si>
     <t xml:space="preserve">27.5512065887451</t>
@@ -2696,31 +2696,31 @@
     <t xml:space="preserve">27.0164165496826</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0355167388916</t>
+    <t xml:space="preserve">27.035514831543</t>
   </si>
   <si>
     <t xml:space="preserve">27.3793087005615</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2265129089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.054615020752</t>
+    <t xml:space="preserve">27.2265148162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0546169281006</t>
   </si>
   <si>
     <t xml:space="preserve">27.2838096618652</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5675754547119</t>
+    <t xml:space="preserve">26.5675735473633</t>
   </si>
   <si>
     <t xml:space="preserve">27.0450668334961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.710823059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5007247924805</t>
+    <t xml:space="preserve">26.7108211517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5007266998291</t>
   </si>
   <si>
     <t xml:space="preserve">26.4529781341553</t>
@@ -2729,16 +2729,16 @@
     <t xml:space="preserve">26.6630725860596</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5389270782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2619800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4625263214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5989532470703</t>
+    <t xml:space="preserve">26.5389251708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2619781494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4625244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5989570617676</t>
   </si>
   <si>
     <t xml:space="preserve">26.6726245880127</t>
@@ -2756,7 +2756,7 @@
     <t xml:space="preserve">28.1814918518066</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3533897399902</t>
+    <t xml:space="preserve">28.3533916473389</t>
   </si>
   <si>
     <t xml:space="preserve">28.5061874389648</t>
@@ -2771,25 +2771,25 @@
     <t xml:space="preserve">28.6971817016602</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5798530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.65625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4748058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6849040985107</t>
+    <t xml:space="preserve">27.57985496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6562519073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4748077392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6849021911621</t>
   </si>
   <si>
     <t xml:space="preserve">29.3847694396973</t>
   </si>
   <si>
-    <t xml:space="preserve">29.967306137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.174674987793</t>
+    <t xml:space="preserve">29.9673080444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1746711730957</t>
   </si>
   <si>
     <t xml:space="preserve">29.4802684783936</t>
@@ -2798,13 +2798,13 @@
     <t xml:space="preserve">29.8336124420166</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0246047973633</t>
+    <t xml:space="preserve">30.0246067047119</t>
   </si>
   <si>
     <t xml:space="preserve">29.1651248931885</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3274688720703</t>
+    <t xml:space="preserve">29.3274707794189</t>
   </si>
   <si>
     <t xml:space="preserve">29.8049583435059</t>
@@ -2822,52 +2822,52 @@
     <t xml:space="preserve">30.5402946472168</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9222888946533</t>
+    <t xml:space="preserve">30.922290802002</t>
   </si>
   <si>
     <t xml:space="preserve">30.7408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9318408966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7217407226562</t>
+    <t xml:space="preserve">30.9318389892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7217426300049</t>
   </si>
   <si>
     <t xml:space="preserve">30.6835422515869</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8172416687012</t>
+    <t xml:space="preserve">30.8172397613525</t>
   </si>
   <si>
     <t xml:space="preserve">30.4829959869385</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5593967437744</t>
+    <t xml:space="preserve">30.5593948364258</t>
   </si>
   <si>
     <t xml:space="preserve">28.7258319854736</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2128715515137</t>
+    <t xml:space="preserve">29.2128734588623</t>
   </si>
   <si>
     <t xml:space="preserve">30.9031887054443</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9918689727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.899097442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6535377502441</t>
+    <t xml:space="preserve">31.9918651580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8991012573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6535339355469</t>
   </si>
   <si>
     <t xml:space="preserve">33.309741973877</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4693603515625</t>
+    <t xml:space="preserve">32.4693565368652</t>
   </si>
   <si>
     <t xml:space="preserve">33.3288421630859</t>
@@ -2876,19 +2876,19 @@
     <t xml:space="preserve">33.558032989502</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1310234069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4338874816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4461708068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8158836364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9304809570312</t>
+    <t xml:space="preserve">34.1310272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4338836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8158798217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.930477142334</t>
   </si>
   <si>
     <t xml:space="preserve">32.6603584289551</t>
@@ -2903,25 +2903,25 @@
     <t xml:space="preserve">31.5143737792969</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6098728179932</t>
+    <t xml:space="preserve">31.6098747253418</t>
   </si>
   <si>
     <t xml:space="preserve">31.9727668762207</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7367515563965</t>
+    <t xml:space="preserve">32.7367553710938</t>
   </si>
   <si>
     <t xml:space="preserve">32.0587158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2565326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8840923309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0177879333496</t>
+    <t xml:space="preserve">31.2565307617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.884090423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.017786026001</t>
   </si>
   <si>
     <t xml:space="preserve">31.1323833465576</t>
@@ -2939,25 +2939,25 @@
     <t xml:space="preserve">32.0969161987305</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3615798950195</t>
+    <t xml:space="preserve">31.3615818023682</t>
   </si>
   <si>
     <t xml:space="preserve">32.1542091369629</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9441223144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4216156005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6958179473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2115097045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7435741424561</t>
+    <t xml:space="preserve">31.9441204071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4216117858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.695821762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2115135192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7435722351074</t>
   </si>
   <si>
     <t xml:space="preserve">32.2783584594727</t>
@@ -2966,25 +2966,25 @@
     <t xml:space="preserve">32.5075569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4120597839355</t>
+    <t xml:space="preserve">32.412052154541</t>
   </si>
   <si>
     <t xml:space="preserve">32.0491676330566</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5334777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2087841033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3165626525879</t>
+    <t xml:space="preserve">31.5334758758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2087821960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3165588378906</t>
   </si>
   <si>
     <t xml:space="preserve">32.1637649536133</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1064643859863</t>
+    <t xml:space="preserve">32.1064682006836</t>
   </si>
   <si>
     <t xml:space="preserve">32.3834114074707</t>
@@ -2996,13 +2996,13 @@
     <t xml:space="preserve">32.650806427002</t>
   </si>
   <si>
-    <t xml:space="preserve">32.803596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5839538574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3547592163086</t>
+    <t xml:space="preserve">32.8036003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5839500427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3547630310059</t>
   </si>
   <si>
     <t xml:space="preserve">32.0682678222656</t>
@@ -3014,10 +3014,10 @@
     <t xml:space="preserve">32.5648536682129</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3261070251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9250164031982</t>
+    <t xml:space="preserve">32.3261108398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9250202178955</t>
   </si>
   <si>
     <t xml:space="preserve">33.0423469543457</t>
@@ -3029,58 +3029,58 @@
     <t xml:space="preserve">34.5989646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4843711853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.942756652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8854598999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.000057220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.80224609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5539436340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3342971801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2551727294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9018325805664</t>
+    <t xml:space="preserve">34.4843673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9427604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8854560852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0000610351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8022422790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5539474487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.334300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2551765441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9018287658691</t>
   </si>
   <si>
     <t xml:space="preserve">33.3670387268066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3192901611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7817707061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8104228973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4598083496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7081031799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9768562316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4898166656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6876335144043</t>
+    <t xml:space="preserve">33.3192939758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7817687988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8104248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4598121643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7080993652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9768581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4898147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6876373291016</t>
   </si>
   <si>
     <t xml:space="preserve">29.0027770996094</t>
@@ -3095,13 +3095,13 @@
     <t xml:space="preserve">31.4761734008789</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5211963653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.731294631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1228332519531</t>
+    <t xml:space="preserve">30.5211982727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7312927246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1228351593018</t>
   </si>
   <si>
     <t xml:space="preserve">30.5498447418213</t>
@@ -3110,115 +3110,115 @@
     <t xml:space="preserve">29.5375671386719</t>
   </si>
   <si>
-    <t xml:space="preserve">30.148754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6671752929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4065990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7694931030273</t>
+    <t xml:space="preserve">30.1487560272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6671733856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4066009521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.769495010376</t>
   </si>
   <si>
     <t xml:space="preserve">30.6644439697266</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3111019134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9413890838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2756290435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9604873657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5812244415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3424758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5007438659668</t>
+    <t xml:space="preserve">30.3111000061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9413871765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2756309509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.960485458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.581226348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3424816131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5007362365723</t>
   </si>
   <si>
     <t xml:space="preserve">32.9373016357422</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8731842041016</t>
+    <t xml:space="preserve">33.8731803894043</t>
   </si>
   <si>
     <t xml:space="preserve">33.6344375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">33.624885559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1787757873535</t>
+    <t xml:space="preserve">33.6248817443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1787719726562</t>
   </si>
   <si>
     <t xml:space="preserve">34.2169761657715</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9905090332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8281631469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3029174804688</t>
+    <t xml:space="preserve">34.9905052185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8281669616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3029136657715</t>
   </si>
   <si>
     <t xml:space="preserve">33.1091918945312</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5484886169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.806339263916</t>
+    <t xml:space="preserve">33.5484924316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8063354492188</t>
   </si>
   <si>
     <t xml:space="preserve">33.2333450317383</t>
   </si>
   <si>
-    <t xml:space="preserve">34.092830657959</t>
+    <t xml:space="preserve">34.0928268432617</t>
   </si>
   <si>
     <t xml:space="preserve">33.5771369934082</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2688140869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9059238433838</t>
+    <t xml:space="preserve">32.2688102722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9059200286865</t>
   </si>
   <si>
     <t xml:space="preserve">31.8868179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0873603820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.946849822998</t>
+    <t xml:space="preserve">32.0873680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9468460083008</t>
   </si>
   <si>
     <t xml:space="preserve">33.1378440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7995109558105</t>
+    <t xml:space="preserve">34.7995071411133</t>
   </si>
   <si>
     <t xml:space="preserve">35.885196685791</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6538162231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9620590209961</t>
+    <t xml:space="preserve">36.6538238525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9620552062988</t>
   </si>
   <si>
     <t xml:space="preserve">36.769115447998</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">37.018913269043</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6818580627441</t>
+    <t xml:space="preserve">37.6818542480469</t>
   </si>
   <si>
     <t xml:space="preserve">38.2391090393066</t>
@@ -3248,19 +3248,19 @@
     <t xml:space="preserve">37.8836212158203</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0181312561035</t>
+    <t xml:space="preserve">38.0181274414062</t>
   </si>
   <si>
     <t xml:space="preserve">39.2479286193848</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6138153076172</t>
+    <t xml:space="preserve">38.6138114929199</t>
   </si>
   <si>
     <t xml:space="preserve">38.6426391601562</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3440055847168</t>
+    <t xml:space="preserve">39.3440093994141</t>
   </si>
   <si>
     <t xml:space="preserve">38.5946006774902</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">38.7195014953613</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6042098999023</t>
+    <t xml:space="preserve">38.6042060852051</t>
   </si>
   <si>
     <t xml:space="preserve">39.6130294799805</t>
@@ -3281,25 +3281,25 @@
     <t xml:space="preserve">39.6514587402344</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7475357055664</t>
+    <t xml:space="preserve">39.7475395202637</t>
   </si>
   <si>
     <t xml:space="preserve">40.4969482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0069465637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8051834106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9685134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6034240722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7571487426758</t>
+    <t xml:space="preserve">40.0069427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8051872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9685173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6034202575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7571449279785</t>
   </si>
   <si>
     <t xml:space="preserve">39.9973411560059</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">36.5769577026367</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5665626525879</t>
+    <t xml:space="preserve">37.5665588378906</t>
   </si>
   <si>
     <t xml:space="preserve">37.5569534301758</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">38.3736190795898</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9789085388184</t>
+    <t xml:space="preserve">38.9789123535156</t>
   </si>
   <si>
     <t xml:space="preserve">39.1614570617676</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">38.4793014526367</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4496955871582</t>
+    <t xml:space="preserve">39.4496994018555</t>
   </si>
   <si>
     <t xml:space="preserve">39.1806755065918</t>
@@ -3344,70 +3344,70 @@
     <t xml:space="preserve">38.7675399780273</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0453758239746</t>
+    <t xml:space="preserve">40.0453796386719</t>
   </si>
   <si>
     <t xml:space="preserve">40.6410636901855</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7275314331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3528251647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7083168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2567520141602</t>
+    <t xml:space="preserve">40.7275352478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3528289794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7083129882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2567558288574</t>
   </si>
   <si>
     <t xml:space="preserve">40.333610534668</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2663536071777</t>
+    <t xml:space="preserve">40.266357421875</t>
   </si>
   <si>
     <t xml:space="preserve">40.4489059448242</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0157623291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1406669616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3424339294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2271423339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2367477416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5634117126465</t>
+    <t xml:space="preserve">41.0157661437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1406707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3424301147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2271385192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2367515563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5634155273438</t>
   </si>
   <si>
     <t xml:space="preserve">42.0822372436523</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0814476013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2455673217773</t>
+    <t xml:space="preserve">43.0814514160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2455711364746</t>
   </si>
   <si>
     <t xml:space="preserve">42.0341987609863</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7651824951172</t>
+    <t xml:space="preserve">41.7651786804199</t>
   </si>
   <si>
     <t xml:space="preserve">41.9669418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">42.466552734375</t>
+    <t xml:space="preserve">42.4665489196777</t>
   </si>
   <si>
     <t xml:space="preserve">42.5434112548828</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">42.9853706359863</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3896903991699</t>
+    <t xml:space="preserve">42.3896865844727</t>
   </si>
   <si>
     <t xml:space="preserve">42.8988990783691</t>
@@ -3428,10 +3428,10 @@
     <t xml:space="preserve">42.0245895385742</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9765472412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.534595489502</t>
+    <t xml:space="preserve">41.9765510559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5345916748047</t>
   </si>
   <si>
     <t xml:space="preserve">41.4577331542969</t>
@@ -3440,13 +3440,13 @@
     <t xml:space="preserve">39.7187156677246</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0061645507812</t>
+    <t xml:space="preserve">41.006160736084</t>
   </si>
   <si>
     <t xml:space="preserve">40.0165596008301</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8332252502441</t>
+    <t xml:space="preserve">40.8332214355469</t>
   </si>
   <si>
     <t xml:space="preserve">41.0638084411621</t>
@@ -3455,19 +3455,19 @@
     <t xml:space="preserve">43.0718383789062</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1679153442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3112525939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2159614562988</t>
+    <t xml:space="preserve">43.1679191589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3112487792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2159576416016</t>
   </si>
   <si>
     <t xml:space="preserve">41.9477272033691</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7859687805176</t>
+    <t xml:space="preserve">39.7859649658203</t>
   </si>
   <si>
     <t xml:space="preserve">40.2759628295898</t>
@@ -3476,7 +3476,7 @@
     <t xml:space="preserve">39.5842056274414</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1902809143066</t>
+    <t xml:space="preserve">39.1902847290039</t>
   </si>
   <si>
     <t xml:space="preserve">39.5169525146484</t>
@@ -3491,10 +3491,10 @@
     <t xml:space="preserve">39.0077362060547</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0653800964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9108695983887</t>
+    <t xml:space="preserve">39.0653839111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9108657836914</t>
   </si>
   <si>
     <t xml:space="preserve">40.2087097167969</t>
@@ -3509,7 +3509,7 @@
     <t xml:space="preserve">42.7932167053223</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5730247497559</t>
+    <t xml:space="preserve">41.5730209350586</t>
   </si>
   <si>
     <t xml:space="preserve">41.169490814209</t>
@@ -3524,37 +3524,37 @@
     <t xml:space="preserve">42.3800811767578</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3992958068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.004581451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9653663635254</t>
+    <t xml:space="preserve">42.3992919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0045852661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9653625488281</t>
   </si>
   <si>
     <t xml:space="preserve">43.8596839904785</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7147750854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2632141113281</t>
+    <t xml:space="preserve">44.7147789001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2632102966309</t>
   </si>
   <si>
     <t xml:space="preserve">43.7251739501953</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0037956237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.20556640625</t>
+    <t xml:space="preserve">44.0037994384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2055625915527</t>
   </si>
   <si>
     <t xml:space="preserve">43.436939239502</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2551765441895</t>
+    <t xml:space="preserve">42.2551803588867</t>
   </si>
   <si>
     <t xml:space="preserve">42.8604698181152</t>
@@ -3563,40 +3563,40 @@
     <t xml:space="preserve">42.8028221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6794967651367</t>
+    <t xml:space="preserve">40.6794929504395</t>
   </si>
   <si>
     <t xml:space="preserve">41.6018409729004</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5449905395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0830192565918</t>
+    <t xml:space="preserve">40.5449829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0830230712891</t>
   </si>
   <si>
     <t xml:space="preserve">41.4289016723633</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4193000793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1318511962891</t>
+    <t xml:space="preserve">41.4192962646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1318473815918</t>
   </si>
   <si>
     <t xml:space="preserve">40.1606712341309</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2655715942383</t>
+    <t xml:space="preserve">41.2655754089355</t>
   </si>
   <si>
     <t xml:space="preserve">40.1798858642578</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1414527893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3143920898438</t>
+    <t xml:space="preserve">40.1414566040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3143997192383</t>
   </si>
   <si>
     <t xml:space="preserve">41.0926322937012</t>
@@ -3614,10 +3614,10 @@
     <t xml:space="preserve">42.3704681396484</t>
   </si>
   <si>
-    <t xml:space="preserve">42.562629699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.533016204834</t>
+    <t xml:space="preserve">42.5626258850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5330200195312</t>
   </si>
   <si>
     <t xml:space="preserve">43.6579170227051</t>
@@ -3629,16 +3629,16 @@
     <t xml:space="preserve">45.0702667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3681144714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5890922546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8108520507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8885040283203</t>
+    <t xml:space="preserve">45.3681106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5890884399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8108558654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8885078430176</t>
   </si>
   <si>
     <t xml:space="preserve">44.0518341064453</t>
@@ -3650,10 +3650,10 @@
     <t xml:space="preserve">41.8708648681641</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0261611938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2671432495117</t>
+    <t xml:space="preserve">40.0261650085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.267147064209</t>
   </si>
   <si>
     <t xml:space="preserve">38.9308700561523</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">38.383228302002</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1814613342285</t>
+    <t xml:space="preserve">38.1814651489258</t>
   </si>
   <si>
     <t xml:space="preserve">37.2014656066895</t>
@@ -3671,13 +3671,13 @@
     <t xml:space="preserve">35.7795104980469</t>
   </si>
   <si>
-    <t xml:space="preserve">34.520881652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.001277923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0397109985352</t>
+    <t xml:space="preserve">34.5208854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0012702941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0397071838379</t>
   </si>
   <si>
     <t xml:space="preserve">34.4632377624512</t>
@@ -3689,19 +3689,19 @@
     <t xml:space="preserve">36.7018585205078</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8644065856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5585250854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.885986328125</t>
+    <t xml:space="preserve">37.8644027709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5585289001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8859825134277</t>
   </si>
   <si>
     <t xml:space="preserve">34.6553916931152</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7138252258301</t>
+    <t xml:space="preserve">33.7138290405273</t>
   </si>
   <si>
     <t xml:space="preserve">35.116569519043</t>
@@ -3710,13 +3710,13 @@
     <t xml:space="preserve">34.7706871032715</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9636344909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3775596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7418594360352</t>
+    <t xml:space="preserve">33.9636306762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.377555847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7418632507324</t>
   </si>
   <si>
     <t xml:space="preserve">34.2710800170898</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">34.280689239502</t>
   </si>
   <si>
-    <t xml:space="preserve">34.146183013916</t>
+    <t xml:space="preserve">34.1461791992188</t>
   </si>
   <si>
     <t xml:space="preserve">33.7714767456055</t>
@@ -3734,13 +3734,13 @@
     <t xml:space="preserve">33.8291206359863</t>
   </si>
   <si>
-    <t xml:space="preserve">34.568920135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2510757446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9332389831543</t>
+    <t xml:space="preserve">34.5689239501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2510795593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.933235168457</t>
   </si>
   <si>
     <t xml:space="preserve">36.9420547485352</t>
@@ -3749,16 +3749,16 @@
     <t xml:space="preserve">36.4712677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4520530700684</t>
+    <t xml:space="preserve">36.4520568847656</t>
   </si>
   <si>
     <t xml:space="preserve">36.1253852844238</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7802963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.588924407959</t>
+    <t xml:space="preserve">34.7802925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5889282226562</t>
   </si>
   <si>
     <t xml:space="preserve">35.6449966430664</t>
@@ -3767,10 +3767,10 @@
     <t xml:space="preserve">33.7042236328125</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4344100952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1357803344727</t>
+    <t xml:space="preserve">34.4344139099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1357841491699</t>
   </si>
   <si>
     <t xml:space="preserve">34.9244117736816</t>
@@ -3788,28 +3788,28 @@
     <t xml:space="preserve">35.5200996398926</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0973510742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7602920532227</t>
+    <t xml:space="preserve">35.0973472595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7602958679199</t>
   </si>
   <si>
     <t xml:space="preserve">36.211856842041</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5081329345703</t>
+    <t xml:space="preserve">38.508129119873</t>
   </si>
   <si>
     <t xml:space="preserve">39.0173416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9500885009766</t>
+    <t xml:space="preserve">38.9500923156738</t>
   </si>
   <si>
     <t xml:space="preserve">40.2375373840332</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2943916320801</t>
+    <t xml:space="preserve">41.2943954467773</t>
   </si>
   <si>
     <t xml:space="preserve">40.890869140625</t>
@@ -3824,34 +3824,34 @@
     <t xml:space="preserve">38.6330299377441</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4208679199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2191047668457</t>
+    <t xml:space="preserve">39.4208717346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.219108581543</t>
   </si>
   <si>
     <t xml:space="preserve">38.6234245300293</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9797019958496</t>
+    <t xml:space="preserve">37.9796981811523</t>
   </si>
   <si>
     <t xml:space="preserve">36.8075485229492</t>
   </si>
   <si>
-    <t xml:space="preserve">36.644214630127</t>
+    <t xml:space="preserve">36.6442108154297</t>
   </si>
   <si>
     <t xml:space="preserve">36.3367652893066</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4528427124023</t>
+    <t xml:space="preserve">35.4528388977051</t>
   </si>
   <si>
     <t xml:space="preserve">36.2502899169922</t>
   </si>
   <si>
-    <t xml:space="preserve">36.721076965332</t>
+    <t xml:space="preserve">36.7210731506348</t>
   </si>
   <si>
     <t xml:space="preserve">36.1349983215332</t>
@@ -3860,13 +3860,13 @@
     <t xml:space="preserve">35.7218589782715</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3183288574219</t>
+    <t xml:space="preserve">35.3183326721191</t>
   </si>
   <si>
     <t xml:space="preserve">34.0693168640137</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2726593017578</t>
+    <t xml:space="preserve">32.2726554870605</t>
   </si>
   <si>
     <t xml:space="preserve">32.9836349487305</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">32.9740257263184</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0524616241455</t>
+    <t xml:space="preserve">31.0524635314941</t>
   </si>
   <si>
     <t xml:space="preserve">32.9067687988281</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">32.9163780212402</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9644165039062</t>
+    <t xml:space="preserve">32.9644203186035</t>
   </si>
   <si>
     <t xml:space="preserve">31.2734413146973</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">30.3414840698242</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6777572631836</t>
+    <t xml:space="preserve">30.6777591705322</t>
   </si>
   <si>
     <t xml:space="preserve">31.2105293273926</t>
@@ -6162,6 +6162,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.8900003433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2250003814697</t>
   </si>
 </sst>
 </file>
@@ -71162,7 +71165,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6494560185</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>1235588</v>
@@ -71183,6 +71186,32 @@
         <v>2049</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6516550926</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>2941738</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>14.7299995422363</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>14.1599998474121</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>14.6899995803833</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>14.2250003814697</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>2050</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33520555496216</t>
+    <t xml:space="preserve">7.335205078125</t>
   </si>
   <si>
     <t xml:space="preserve">AMP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39109182357788</t>
+    <t xml:space="preserve">7.39109230041504</t>
   </si>
   <si>
     <t xml:space="preserve">7.31191825866699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36780500411987</t>
+    <t xml:space="preserve">7.36780548095703</t>
   </si>
   <si>
     <t xml:space="preserve">7.15357160568237</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96262264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21877336502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27931785583496</t>
+    <t xml:space="preserve">6.96262311935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21877384185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27931833267212</t>
   </si>
   <si>
     <t xml:space="preserve">7.16288566589355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03248262405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08836984634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19548559188843</t>
+    <t xml:space="preserve">7.03248167037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08836936950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19548654556274</t>
   </si>
   <si>
     <t xml:space="preserve">6.98590993881226</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13494157791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3445200920105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23740243911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35383319854736</t>
+    <t xml:space="preserve">7.13494205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34451961517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23740196228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35383462905884</t>
   </si>
   <si>
     <t xml:space="preserve">7.14891386032104</t>
@@ -98,115 +98,115 @@
     <t xml:space="preserve">7.18151473999023</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40972089767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28397560119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13959980010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05111074447632</t>
+    <t xml:space="preserve">7.40972137451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28397512435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13959932327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05111169815063</t>
   </si>
   <si>
     <t xml:space="preserve">6.84619140625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51086711883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45498037338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59004163742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33389139175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29197597503662</t>
+    <t xml:space="preserve">6.51086759567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45497989654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59004068374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33389186859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29197549819946</t>
   </si>
   <si>
     <t xml:space="preserve">6.42237997055054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61798572540283</t>
+    <t xml:space="preserve">6.61798524856567</t>
   </si>
   <si>
     <t xml:space="preserve">6.8834490776062</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71113014221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83687734603882</t>
+    <t xml:space="preserve">6.71113109588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83687686920166</t>
   </si>
   <si>
     <t xml:space="preserve">6.70181560516357</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6272988319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99522495269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89276456832886</t>
+    <t xml:space="preserve">6.62729930877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9952244758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8927640914917</t>
   </si>
   <si>
     <t xml:space="preserve">6.80427551269531</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7996187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84153461456299</t>
+    <t xml:space="preserve">6.79961824417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84153366088867</t>
   </si>
   <si>
     <t xml:space="preserve">6.65989971160889</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63195657730103</t>
+    <t xml:space="preserve">6.63195705413818</t>
   </si>
   <si>
     <t xml:space="preserve">6.79496145248413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78564643859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86016273498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00919580459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11165618896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08371210098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20945882797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10699892044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04179668426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24206018447876</t>
+    <t xml:space="preserve">6.78564739227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86016321182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00919532775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11165571212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08371162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20945835113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10699844360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04179716110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2420597076416</t>
   </si>
   <si>
     <t xml:space="preserve">7.09768342971802</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17220020294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93467950820923</t>
+    <t xml:space="preserve">7.17219972610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93467903137207</t>
   </si>
   <si>
     <t xml:space="preserve">6.91604995727539</t>
@@ -221,55 +221,55 @@
     <t xml:space="preserve">7.3258900642395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22808790206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50286722183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41437816619873</t>
+    <t xml:space="preserve">7.22808837890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50286769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41437911987305</t>
   </si>
   <si>
     <t xml:space="preserve">7.48423767089844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57738351821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55409622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73107385635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60066890716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64258432388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70312976837158</t>
+    <t xml:space="preserve">7.57738399505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55409574508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73107242584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60066986083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64258480072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7031307220459</t>
   </si>
   <si>
     <t xml:space="preserve">7.73573064804077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88476276397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88942241668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8707914352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78695964813232</t>
+    <t xml:space="preserve">7.88476228713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88941955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87079000473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7869610786438</t>
   </si>
   <si>
     <t xml:space="preserve">7.94530725479126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88010597229004</t>
+    <t xml:space="preserve">7.88010549545288</t>
   </si>
   <si>
     <t xml:space="preserve">8.08968353271484</t>
@@ -284,13 +284,13 @@
     <t xml:space="preserve">8.10653400421143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05036735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17205715179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21418285369873</t>
+    <t xml:space="preserve">8.050368309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17205905914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21418190002441</t>
   </si>
   <si>
     <t xml:space="preserve">8.23758602142334</t>
@@ -299,34 +299,34 @@
     <t xml:space="preserve">8.22354412078857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15801906585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07844924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08313179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14397525787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01292514801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91463375091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82102537155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64316892623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62912559509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65253019332886</t>
+    <t xml:space="preserve">8.15801811218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07845020294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08313083648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14397621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01292419433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91463565826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82102584838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6431679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62912750244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65252923965454</t>
   </si>
   <si>
     <t xml:space="preserve">7.55892038345337</t>
@@ -335,37 +335,37 @@
     <t xml:space="preserve">7.63848781585693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9895224571228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94739818572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05972671508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67593240737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71337461471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72273588180542</t>
+    <t xml:space="preserve">7.98952007293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94739723205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05972576141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67593193054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71337556838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72273540496826</t>
   </si>
   <si>
     <t xml:space="preserve">7.87251043319702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92867708206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89123153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81166505813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71805667877197</t>
+    <t xml:space="preserve">7.92867660522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89123249053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81166553497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71805620193481</t>
   </si>
   <si>
     <t xml:space="preserve">7.88187074661255</t>
@@ -374,91 +374,91 @@
     <t xml:space="preserve">7.96143913269043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91931438446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90995359420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05504703521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18141841888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16737937927246</t>
+    <t xml:space="preserve">7.91931581497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90995407104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0550479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18142127990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16737747192383</t>
   </si>
   <si>
     <t xml:space="preserve">8.19546127319336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19077968597412</t>
+    <t xml:space="preserve">8.19078063964844</t>
   </si>
   <si>
     <t xml:space="preserve">8.3077917098999</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36395835876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34991550445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3311939239502</t>
+    <t xml:space="preserve">8.36395645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34991455078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33119297027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.29375076293945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15333557128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28907108306885</t>
+    <t xml:space="preserve">8.1533374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28906917572021</t>
   </si>
   <si>
     <t xml:space="preserve">8.36863708496094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50905227661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60733985900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51373195648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63542461395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75711345672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65414524078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78519725799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80860042572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92093181610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84604358673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81796169281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74775409698486</t>
+    <t xml:space="preserve">8.5090503692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60734081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51373386383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.635422706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75711441040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65414333343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78519821166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80859851837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92092990875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84604263305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81796073913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74775505065918</t>
   </si>
   <si>
     <t xml:space="preserve">8.75243473052979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82264137268066</t>
+    <t xml:space="preserve">8.82264232635498</t>
   </si>
   <si>
     <t xml:space="preserve">8.7337121963501</t>
@@ -467,13 +467,13 @@
     <t xml:space="preserve">8.77115440368652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76179313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6588249206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59329891204834</t>
+    <t xml:space="preserve">8.76179504394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65882587432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59329986572266</t>
   </si>
   <si>
     <t xml:space="preserve">8.57457733154297</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">8.56053733825684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48564720153809</t>
+    <t xml:space="preserve">8.4856481552124</t>
   </si>
   <si>
     <t xml:space="preserve">8.54181480407715</t>
@@ -491,34 +491,34 @@
     <t xml:space="preserve">8.53245258331299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66818523406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49969005584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61670207977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49500846862793</t>
+    <t xml:space="preserve">8.66818714141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49968910217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61670112609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49501037597656</t>
   </si>
   <si>
     <t xml:space="preserve">8.5558557510376</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61202049255371</t>
+    <t xml:space="preserve">8.61202144622803</t>
   </si>
   <si>
     <t xml:space="preserve">8.46692657470703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52777290344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56521701812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69158840179443</t>
+    <t xml:space="preserve">8.52777194976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56521606445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6915864944458</t>
   </si>
   <si>
     <t xml:space="preserve">9.08006572723389</t>
@@ -530,13 +530,13 @@
     <t xml:space="preserve">9.07070350646973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01453971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89284896850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93965148925781</t>
+    <t xml:space="preserve">9.01453876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89284706115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93965244293213</t>
   </si>
   <si>
     <t xml:space="preserve">8.81328010559082</t>
@@ -548,43 +548,43 @@
     <t xml:space="preserve">8.42480278015137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40140056610107</t>
+    <t xml:space="preserve">8.40139865875244</t>
   </si>
   <si>
     <t xml:space="preserve">8.39672088623047</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58393859863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34523487091064</t>
+    <t xml:space="preserve">8.5839376449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34523582458496</t>
   </si>
   <si>
     <t xml:space="preserve">8.46224689483643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3826789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47160816192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98645782470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09878826141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0613431930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51841259002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16269683837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31247329711914</t>
+    <t xml:space="preserve">8.38267803192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47160720825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98645687103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09878635406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06134414672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51841163635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16269779205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31247138977051</t>
   </si>
   <si>
     <t xml:space="preserve">7.44190883636475</t>
@@ -593,34 +593,34 @@
     <t xml:space="preserve">7.98484086990356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95675849914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38735961914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41075992584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44820404052734</t>
+    <t xml:space="preserve">7.95675802230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38735866546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41076183319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44820499420166</t>
   </si>
   <si>
     <t xml:space="preserve">8.48096942901611</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37331771850586</t>
+    <t xml:space="preserve">8.37331867218018</t>
   </si>
   <si>
     <t xml:space="preserve">8.23290538787842</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18610095977783</t>
+    <t xml:space="preserve">8.18610000610352</t>
   </si>
   <si>
     <t xml:space="preserve">8.37800025939941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57925796508789</t>
+    <t xml:space="preserve">8.57925701141357</t>
   </si>
   <si>
     <t xml:space="preserve">8.64946460723877</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">8.72435092926025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67286777496338</t>
+    <t xml:space="preserve">8.67286586761475</t>
   </si>
   <si>
     <t xml:space="preserve">8.74307250976562</t>
@@ -638,19 +638,19 @@
     <t xml:space="preserve">8.7103099822998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15495204925537</t>
+    <t xml:space="preserve">9.15495300292969</t>
   </si>
   <si>
     <t xml:space="preserve">8.96773433685303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14091300964355</t>
+    <t xml:space="preserve">9.14091110229492</t>
   </si>
   <si>
     <t xml:space="preserve">9.26728343963623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33749103546143</t>
+    <t xml:space="preserve">9.33749008178711</t>
   </si>
   <si>
     <t xml:space="preserve">9.40769672393799</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">9.37961578369141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29536724090576</t>
+    <t xml:space="preserve">9.29536628723145</t>
   </si>
   <si>
     <t xml:space="preserve">9.36089324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44513988494873</t>
+    <t xml:space="preserve">9.44514179229736</t>
   </si>
   <si>
     <t xml:space="preserve">9.48258495330811</t>
@@ -674,34 +674,34 @@
     <t xml:space="preserve">9.43577861785889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35621166229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11282730102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1081485748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15963459014893</t>
+    <t xml:space="preserve">9.35621070861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11282825469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10814762115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15963268280029</t>
   </si>
   <si>
     <t xml:space="preserve">9.46386241912842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81021499633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95998954772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82893657684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91318511962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6417179107666</t>
+    <t xml:space="preserve">9.81021404266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95998859405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82893753051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91318416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64171981811523</t>
   </si>
   <si>
     <t xml:space="preserve">9.70724487304688</t>
@@ -716,40 +716,40 @@
     <t xml:space="preserve">9.79149341583252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0255155563354</t>
+    <t xml:space="preserve">10.0255174636841</t>
   </si>
   <si>
     <t xml:space="preserve">10.0067949295044</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1846504211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2408170700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.259539604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4280338287354</t>
+    <t xml:space="preserve">10.1846494674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2408151626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2595376968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4280347824097</t>
   </si>
   <si>
     <t xml:space="preserve">10.4748373031616</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3625078201294</t>
+    <t xml:space="preserve">10.3625068664551</t>
   </si>
   <si>
     <t xml:space="preserve">10.3344249725342</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5778093338013</t>
+    <t xml:space="preserve">10.577808380127</t>
   </si>
   <si>
     <t xml:space="preserve">10.5122814178467</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5029211044312</t>
+    <t xml:space="preserve">10.5029220581055</t>
   </si>
   <si>
     <t xml:space="preserve">10.8118314743042</t>
@@ -761,22 +761,22 @@
     <t xml:space="preserve">10.7182216644287</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6526947021484</t>
+    <t xml:space="preserve">10.6526956558228</t>
   </si>
   <si>
     <t xml:space="preserve">10.6433343887329</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6246118545532</t>
+    <t xml:space="preserve">10.6246128082275</t>
   </si>
   <si>
     <t xml:space="preserve">10.7088603973389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8960790634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8399143218994</t>
+    <t xml:space="preserve">10.8960781097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8399124145508</t>
   </si>
   <si>
     <t xml:space="preserve">10.9335222244263</t>
@@ -785,13 +785,13 @@
     <t xml:space="preserve">10.9990482330322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1301002502441</t>
+    <t xml:space="preserve">11.1301012039185</t>
   </si>
   <si>
     <t xml:space="preserve">11.0926580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2517938613892</t>
+    <t xml:space="preserve">11.2517919540405</t>
   </si>
   <si>
     <t xml:space="preserve">10.9616041183472</t>
@@ -800,49 +800,49 @@
     <t xml:space="preserve">11.2049884796143</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1675453186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1488227844238</t>
+    <t xml:space="preserve">11.1675462722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1488218307495</t>
   </si>
   <si>
     <t xml:space="preserve">11.1862668991089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2798757553101</t>
+    <t xml:space="preserve">11.2798767089844</t>
   </si>
   <si>
     <t xml:space="preserve">11.4296493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4109268188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4577322006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5801229476929</t>
+    <t xml:space="preserve">11.410927772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4577331542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5801239013672</t>
   </si>
   <si>
     <t xml:space="preserve">11.8249073028564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8625650405884</t>
+    <t xml:space="preserve">11.862566947937</t>
   </si>
   <si>
     <t xml:space="preserve">11.9472970962524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9190540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9284696578979</t>
+    <t xml:space="preserve">11.9190530776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9284687042236</t>
   </si>
   <si>
     <t xml:space="preserve">11.9378833770752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9661283493042</t>
+    <t xml:space="preserve">11.9661273956299</t>
   </si>
   <si>
     <t xml:space="preserve">12.0602760314941</t>
@@ -851,55 +851,55 @@
     <t xml:space="preserve">12.0979347229004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0226163864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2109098434448</t>
+    <t xml:space="preserve">12.0226173400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2109107971191</t>
   </si>
   <si>
     <t xml:space="preserve">12.1826658248901</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2391557693481</t>
+    <t xml:space="preserve">12.2391567230225</t>
   </si>
   <si>
     <t xml:space="preserve">11.9096393585205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1450090408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4859752655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2976818084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6930999755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7307605743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7684183120728</t>
+    <t xml:space="preserve">12.1450080871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4859762191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.297682762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6931009292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7307596206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7684192657471</t>
   </si>
   <si>
     <t xml:space="preserve">11.7590026855469</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6271982192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.570707321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5236339569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4671478271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3730001449585</t>
+    <t xml:space="preserve">11.627197265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5707092285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5236349105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4671468734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3729991912842</t>
   </si>
   <si>
     <t xml:space="preserve">11.0811424255371</t>
@@ -908,25 +908,25 @@
     <t xml:space="preserve">10.88343334198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6951389312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5633316040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6104068756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7422122955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9116764068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9022626876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9493379592896</t>
+    <t xml:space="preserve">10.6951379776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5633335113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.610405921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7422113418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9116773605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9022617340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9493370056152</t>
   </si>
   <si>
     <t xml:space="preserve">11.1376314163208</t>
@@ -935,13 +935,13 @@
     <t xml:space="preserve">11.3541698455811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3824148178101</t>
+    <t xml:space="preserve">11.3824138641357</t>
   </si>
   <si>
     <t xml:space="preserve">11.3447551727295</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4106578826904</t>
+    <t xml:space="preserve">11.4106588363647</t>
   </si>
   <si>
     <t xml:space="preserve">11.269437789917</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">11.4294881820679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3353395462036</t>
+    <t xml:space="preserve">11.3353404998779</t>
   </si>
   <si>
     <t xml:space="preserve">11.2788515090942</t>
@@ -962,19 +962,19 @@
     <t xml:space="preserve">11.2506074905396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1093864440918</t>
+    <t xml:space="preserve">11.1093873977661</t>
   </si>
   <si>
     <t xml:space="preserve">11.0340690612793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9210929870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6668949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8363609313965</t>
+    <t xml:space="preserve">10.9210920333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6668939590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8363599777222</t>
   </si>
   <si>
     <t xml:space="preserve">10.78928565979</t>
@@ -986,31 +986,31 @@
     <t xml:space="preserve">11.1658754348755</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0717277526855</t>
+    <t xml:space="preserve">11.0717267990112</t>
   </si>
   <si>
     <t xml:space="preserve">11.1282167434692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3165111541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3259248733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2411918640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0623121261597</t>
+    <t xml:space="preserve">11.3165121078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3259258270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.241192817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.062313079834</t>
   </si>
   <si>
     <t xml:space="preserve">11.0905561447144</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1752891540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4389019012451</t>
+    <t xml:space="preserve">11.1752901077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4389028549194</t>
   </si>
   <si>
     <t xml:space="preserve">11.7213449478149</t>
@@ -1019,64 +1019,64 @@
     <t xml:space="preserve">11.8154916763306</t>
   </si>
   <si>
-    <t xml:space="preserve">11.984956741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.013201713562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9567136764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0508613586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0414438247681</t>
+    <t xml:space="preserve">11.9849576950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0132007598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9567127227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0508623123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0414457321167</t>
   </si>
   <si>
     <t xml:space="preserve">12.0791053771973</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9755439758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8343200683594</t>
+    <t xml:space="preserve">11.9755430221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.834321975708</t>
   </si>
   <si>
     <t xml:space="preserve">12.2203245162964</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1544246673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.107349395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4839382171631</t>
+    <t xml:space="preserve">12.1544208526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1073484420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4839372634888</t>
   </si>
   <si>
     <t xml:space="preserve">12.5215978622437</t>
   </si>
   <si>
-    <t xml:space="preserve">12.643988609314</t>
+    <t xml:space="preserve">12.6439905166626</t>
   </si>
   <si>
     <t xml:space="preserve">12.7852096557617</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8134536743164</t>
+    <t xml:space="preserve">12.8134527206421</t>
   </si>
   <si>
     <t xml:space="preserve">12.8322830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8040399551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.192081451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7872476577759</t>
+    <t xml:space="preserve">12.8040409088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1920804977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7872495651245</t>
   </si>
   <si>
     <t xml:space="preserve">11.8531503677368</t>
@@ -1088,64 +1088,64 @@
     <t xml:space="preserve">12.1732530593872</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2768144607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9002256393433</t>
+    <t xml:space="preserve">12.2768135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9002246856689</t>
   </si>
   <si>
     <t xml:space="preserve">11.448317527771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5612936019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4012441635132</t>
+    <t xml:space="preserve">11.5612945556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4012422561646</t>
   </si>
   <si>
     <t xml:space="preserve">11.6742706298828</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7778339385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0885181427002</t>
+    <t xml:space="preserve">11.7778329849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0885190963745</t>
   </si>
   <si>
     <t xml:space="preserve">12.0696897506714</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2014970779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1355905532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3615465164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3333024978638</t>
+    <t xml:space="preserve">12.2014961242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1355934143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3615474700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3333044052124</t>
   </si>
   <si>
     <t xml:space="preserve">12.1638374328613</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7401733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1261777877808</t>
+    <t xml:space="preserve">11.7401742935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1261787414551</t>
   </si>
   <si>
     <t xml:space="preserve">12.5404262542725</t>
   </si>
   <si>
-    <t xml:space="preserve">12.549840927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5027675628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6345729827881</t>
+    <t xml:space="preserve">12.5498418807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5027666091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6345739364624</t>
   </si>
   <si>
     <t xml:space="preserve">13.1335544586182</t>
@@ -1157,22 +1157,22 @@
     <t xml:space="preserve">13.0864810943604</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9546766281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4254121780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4630718231201</t>
+    <t xml:space="preserve">12.9546747207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4254112243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4630708694458</t>
   </si>
   <si>
     <t xml:space="preserve">13.5383882522583</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5572175979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6042909622192</t>
+    <t xml:space="preserve">13.5572185516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6042919158936</t>
   </si>
   <si>
     <t xml:space="preserve">13.5101442337036</t>
@@ -1181,28 +1181,28 @@
     <t xml:space="preserve">13.2559471130371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.472487449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3030214309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9735040664673</t>
+    <t xml:space="preserve">13.4724855422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3030204772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.973503112793</t>
   </si>
   <si>
     <t xml:space="preserve">12.6157445907593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4086208343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3803749084473</t>
+    <t xml:space="preserve">12.4086198806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3803758621216</t>
   </si>
   <si>
     <t xml:space="preserve">12.4651079177856</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5121812820435</t>
+    <t xml:space="preserve">12.5121822357178</t>
   </si>
   <si>
     <t xml:space="preserve">12.822868347168</t>
@@ -1214,43 +1214,43 @@
     <t xml:space="preserve">12.8511123657227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5969152450562</t>
+    <t xml:space="preserve">12.5969142913818</t>
   </si>
   <si>
     <t xml:space="preserve">12.2862281799316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.257984161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7287216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0394086837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0958967208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.26535987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4065818786621</t>
+    <t xml:space="preserve">12.2579851150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7287225723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0394077301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0958948135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2653608322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4065828323364</t>
   </si>
   <si>
     <t xml:space="preserve">13.3312644958496</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3218488693237</t>
+    <t xml:space="preserve">13.321849822998</t>
   </si>
   <si>
     <t xml:space="preserve">13.1617975234985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3406782150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2465305328369</t>
+    <t xml:space="preserve">13.3406791687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2465314865112</t>
   </si>
   <si>
     <t xml:space="preserve">12.8887701034546</t>
@@ -1262,22 +1262,22 @@
     <t xml:space="preserve">13.2936058044434</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5666332244873</t>
+    <t xml:space="preserve">13.566632270813</t>
   </si>
   <si>
     <t xml:space="preserve">13.6419496536255</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3124341964722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7925863265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9997100830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1409320831299</t>
+    <t xml:space="preserve">13.3124351501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7925853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9997110366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1409311294556</t>
   </si>
   <si>
     <t xml:space="preserve">14.3951282501221</t>
@@ -1286,19 +1286,19 @@
     <t xml:space="preserve">14.3009815216064</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5645933151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6022548675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6869859695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.912938117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8564510345459</t>
+    <t xml:space="preserve">14.5645952224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6022539138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6869869232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9129400253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8564500808716</t>
   </si>
   <si>
     <t xml:space="preserve">15.1106481552124</t>
@@ -1319,58 +1319,58 @@
     <t xml:space="preserve">14.8941097259521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7152299880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5928392410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1671380996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2706995010376</t>
+    <t xml:space="preserve">14.7152309417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5928382873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.167140007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2706985473633</t>
   </si>
   <si>
     <t xml:space="preserve">15.2424554824829</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2518701553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4401636123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3930912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5531425476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6567010879517</t>
+    <t xml:space="preserve">15.2518720626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.44016456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3930902481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5531415939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.656702041626</t>
   </si>
   <si>
     <t xml:space="preserve">15.4213352203369</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0165023803711</t>
+    <t xml:space="preserve">15.0165014266968</t>
   </si>
   <si>
     <t xml:space="preserve">15.3460168838501</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8185272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6668338775635</t>
+    <t xml:space="preserve">14.818528175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6668348312378</t>
   </si>
   <si>
     <t xml:space="preserve">14.3444871902466</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6099510192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7332000732422</t>
+    <t xml:space="preserve">14.6099500656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7331991195679</t>
   </si>
   <si>
     <t xml:space="preserve">14.875412940979</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">15.1882801055908</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4916648864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1174011230469</t>
+    <t xml:space="preserve">15.4916658401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1173992156982</t>
   </si>
   <si>
     <t xml:space="preserve">16.4587116241455</t>
@@ -1406,19 +1406,19 @@
     <t xml:space="preserve">16.1648025512695</t>
   </si>
   <si>
-    <t xml:space="preserve">16.202730178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2122097015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3259792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1079216003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0699977874756</t>
+    <t xml:space="preserve">16.2027282714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2122077941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3259773254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1079196929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0699996948242</t>
   </si>
   <si>
     <t xml:space="preserve">16.525074005127</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">16.6672878265381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5724811553955</t>
+    <t xml:space="preserve">16.5724792480469</t>
   </si>
   <si>
     <t xml:space="preserve">16.3070182800293</t>
@@ -1439,28 +1439,28 @@
     <t xml:space="preserve">16.2596111297607</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6767711639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8379421234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8853454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0465183258057</t>
+    <t xml:space="preserve">16.6767692565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8379402160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.885347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0465202331543</t>
   </si>
   <si>
     <t xml:space="preserve">16.9232692718506</t>
   </si>
   <si>
-    <t xml:space="preserve">16.771577835083</t>
+    <t xml:space="preserve">16.7715759277344</t>
   </si>
   <si>
     <t xml:space="preserve">16.3733825683594</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4492282867432</t>
+    <t xml:space="preserve">16.4492301940918</t>
   </si>
   <si>
     <t xml:space="preserve">16.2216892242432</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">16.4018249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5535182952881</t>
+    <t xml:space="preserve">16.5535163879395</t>
   </si>
   <si>
     <t xml:space="preserve">16.3639030456543</t>
@@ -1484,13 +1484,13 @@
     <t xml:space="preserve">17.5395240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9472007751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4447135925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0799293518066</t>
+    <t xml:space="preserve">17.9471988677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4447154998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0799312591553</t>
   </si>
   <si>
     <t xml:space="preserve">18.1652584075928</t>
@@ -1499,13 +1499,13 @@
     <t xml:space="preserve">18.7151470184326</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1368160247803</t>
+    <t xml:space="preserve">18.1368141174316</t>
   </si>
   <si>
     <t xml:space="preserve">18.4117584228516</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2505836486816</t>
+    <t xml:space="preserve">18.2505855560303</t>
   </si>
   <si>
     <t xml:space="preserve">18.0704498291016</t>
@@ -1517,19 +1517,19 @@
     <t xml:space="preserve">17.6343326568604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7860260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7575836181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2979907989502</t>
+    <t xml:space="preserve">17.7860240936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7575817108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2979888916016</t>
   </si>
   <si>
     <t xml:space="preserve">18.3738346099854</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2031841278076</t>
+    <t xml:space="preserve">18.203182220459</t>
   </si>
   <si>
     <t xml:space="preserve">18.0325260162354</t>
@@ -1538,28 +1538,28 @@
     <t xml:space="preserve">18.1083755493164</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2126617431641</t>
+    <t xml:space="preserve">18.2126598358154</t>
   </si>
   <si>
     <t xml:space="preserve">18.0609664916992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9377193450928</t>
+    <t xml:space="preserve">17.9377174377441</t>
   </si>
   <si>
     <t xml:space="preserve">18.0040855407715</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5774478912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3927974700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8334312438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0135631561279</t>
+    <t xml:space="preserve">17.577449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3927993774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8334293365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0135650634766</t>
   </si>
   <si>
     <t xml:space="preserve">18.7435894012451</t>
@@ -1571,55 +1571,55 @@
     <t xml:space="preserve">19.41672706604</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3788051605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1891860961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0564556121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7246284484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4496841430664</t>
+    <t xml:space="preserve">19.3788070678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.18918800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0564594268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7246265411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4496803283691</t>
   </si>
   <si>
     <t xml:space="preserve">18.5255298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.772029876709</t>
+    <t xml:space="preserve">18.7720317840576</t>
   </si>
   <si>
     <t xml:space="preserve">18.9616470336914</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6867008209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.146297454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5065670013428</t>
+    <t xml:space="preserve">18.6867027282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1462955474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5065689086914</t>
   </si>
   <si>
     <t xml:space="preserve">18.0420074462891</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3025016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5629997253418</t>
+    <t xml:space="preserve">17.3025035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5629978179932</t>
   </si>
   <si>
     <t xml:space="preserve">15.4537420272827</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5864744186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6718015670776</t>
+    <t xml:space="preserve">15.5864763259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6718034744263</t>
   </si>
   <si>
     <t xml:space="preserve">15.0081443786621</t>
@@ -1628,16 +1628,16 @@
     <t xml:space="preserve">15.4252986907959</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4632244110107</t>
+    <t xml:space="preserve">15.4632234573364</t>
   </si>
   <si>
     <t xml:space="preserve">15.8045339584351</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7286863327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9512596130371</t>
+    <t xml:space="preserve">15.7286853790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9512586593628</t>
   </si>
   <si>
     <t xml:space="preserve">15.0745096206665</t>
@@ -1646,67 +1646,67 @@
     <t xml:space="preserve">14.9986629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9797029495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0176239013672</t>
+    <t xml:space="preserve">14.9797019958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0176248550415</t>
   </si>
   <si>
     <t xml:space="preserve">14.8469696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6573543548584</t>
+    <t xml:space="preserve">14.6573534011841</t>
   </si>
   <si>
     <t xml:space="preserve">14.704758644104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6763153076172</t>
+    <t xml:space="preserve">14.6763143539429</t>
   </si>
   <si>
     <t xml:space="preserve">14.6478729248047</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9322986602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0555477142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7900848388672</t>
+    <t xml:space="preserve">14.932297706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0555486679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7900857925415</t>
   </si>
   <si>
     <t xml:space="preserve">13.8135595321655</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7282314300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1309423446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0835371017456</t>
+    <t xml:space="preserve">13.728232383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1309413909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0835380554199</t>
   </si>
   <si>
     <t xml:space="preserve">13.386923789978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2636709213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3964052200317</t>
+    <t xml:space="preserve">13.263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3964042663574</t>
   </si>
   <si>
     <t xml:space="preserve">13.6523866653442</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4912118911743</t>
+    <t xml:space="preserve">13.4912128448486</t>
   </si>
   <si>
     <t xml:space="preserve">13.2257490158081</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8704462051392</t>
+    <t xml:space="preserve">13.8704452514648</t>
   </si>
   <si>
     <t xml:space="preserve">14.0126571655273</t>
@@ -1718,85 +1718,85 @@
     <t xml:space="preserve">14.2212352752686</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1643505096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3065633773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3350067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7945985794067</t>
+    <t xml:space="preserve">14.1643495559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3065643310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3350057601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7945995330811</t>
   </si>
   <si>
     <t xml:space="preserve">13.7377128601074</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5955009460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7566757202148</t>
+    <t xml:space="preserve">13.5954999923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7566766738892</t>
   </si>
   <si>
     <t xml:space="preserve">13.898886680603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9462938308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4203338623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7756366729736</t>
+    <t xml:space="preserve">13.9462919235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4203319549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7756376266479</t>
   </si>
   <si>
     <t xml:space="preserve">12.7232656478882</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3205575942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1878261566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7471952438354</t>
+    <t xml:space="preserve">13.320556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1878252029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7471942901611</t>
   </si>
   <si>
     <t xml:space="preserve">14.0695428848267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8374872207642</t>
+    <t xml:space="preserve">14.8374881744385</t>
   </si>
   <si>
     <t xml:space="preserve">15.2546463012695</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8848943710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0839900970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1788005828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1503562927246</t>
+    <t xml:space="preserve">14.8848934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0839910507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1787996292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1503553390503</t>
   </si>
   <si>
     <t xml:space="preserve">15.3115301132202</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3589344024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2925682067871</t>
+    <t xml:space="preserve">15.3589363098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2925691604614</t>
   </si>
   <si>
     <t xml:space="preserve">15.1408748626709</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0271062850952</t>
+    <t xml:space="preserve">15.0271053314209</t>
   </si>
   <si>
     <t xml:space="preserve">14.9228162765503</t>
@@ -1811,10 +1811,10 @@
     <t xml:space="preserve">14.9417791366577</t>
   </si>
   <si>
-    <t xml:space="preserve">15.614914894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7097253799438</t>
+    <t xml:space="preserve">15.6149168014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7097234725952</t>
   </si>
   <si>
     <t xml:space="preserve">15.0650291442871</t>
@@ -1826,16 +1826,16 @@
     <t xml:space="preserve">15.5485506057739</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4347829818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3968563079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7806043624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9038562774658</t>
+    <t xml:space="preserve">15.4347820281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3968572616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7806053161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9038553237915</t>
   </si>
   <si>
     <t xml:space="preserve">15.2262029647827</t>
@@ -1844,25 +1844,25 @@
     <t xml:space="preserve">15.1977624893188</t>
   </si>
   <si>
-    <t xml:space="preserve">15.444263458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3684139251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.510627746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.738166809082</t>
+    <t xml:space="preserve">15.4442625045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3684158325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5106287002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7381677627563</t>
   </si>
   <si>
     <t xml:space="preserve">16.4302654266357</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9657077789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2641267776489</t>
+    <t xml:space="preserve">15.9657096862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2641277313232</t>
   </si>
   <si>
     <t xml:space="preserve">15.7855710983276</t>
@@ -1871,28 +1871,28 @@
     <t xml:space="preserve">16.6862487792969</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8474254608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4966316223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.193244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2311725616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7526149749756</t>
+    <t xml:space="preserve">16.8474235534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4966335296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1932487487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2311706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7526168823242</t>
   </si>
   <si>
     <t xml:space="preserve">16.4207878112793</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8095016479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7336540222168</t>
+    <t xml:space="preserve">16.8094997406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7336559295654</t>
   </si>
   <si>
     <t xml:space="preserve">16.8948287963867</t>
@@ -1910,40 +1910,40 @@
     <t xml:space="preserve">15.8898601531982</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9277820587158</t>
+    <t xml:space="preserve">15.9277839660645</t>
   </si>
   <si>
     <t xml:space="preserve">15.851936340332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.354419708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.240650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9183034896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5016021728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6627750396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0894107818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3119850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2835426330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8239459991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6677436828613</t>
+    <t xml:space="preserve">16.3544216156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2406482696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9183053970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5016002655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6627712249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0894145965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3119831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.283540725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8239479064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6677417755127</t>
   </si>
   <si>
     <t xml:space="preserve">18.5743827819824</t>
@@ -1952,19 +1952,19 @@
     <t xml:space="preserve">18.8704280853271</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5962104797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5007133483887</t>
+    <t xml:space="preserve">19.596212387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5007152557373</t>
   </si>
   <si>
     <t xml:space="preserve">18.9277267456055</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9468250274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9850234985352</t>
+    <t xml:space="preserve">18.9468231201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9850215911865</t>
   </si>
   <si>
     <t xml:space="preserve">18.5934829711914</t>
@@ -1979,16 +1979,16 @@
     <t xml:space="preserve">19.0327739715576</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2333202362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.386116027832</t>
+    <t xml:space="preserve">19.2333221435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3861179351807</t>
   </si>
   <si>
     <t xml:space="preserve">19.0900726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1951217651367</t>
+    <t xml:space="preserve">19.1951236724854</t>
   </si>
   <si>
     <t xml:space="preserve">19.1187229156494</t>
@@ -2015,52 +2015,52 @@
     <t xml:space="preserve">20.799488067627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9591064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8445072174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4816150665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3097152709961</t>
+    <t xml:space="preserve">19.9591045379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8445091247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4816131591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3097171783447</t>
   </si>
   <si>
     <t xml:space="preserve">19.6344127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6726112365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0928020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9400043487549</t>
+    <t xml:space="preserve">19.6726131439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0928039550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9400062561035</t>
   </si>
   <si>
     <t xml:space="preserve">19.6535110473633</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5580139160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7299098968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3029003143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2837963104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2265014648438</t>
+    <t xml:space="preserve">19.558012008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.729907989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3029022216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2837982177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2264995574951</t>
   </si>
   <si>
     <t xml:space="preserve">20.7039890289307</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6848907470703</t>
+    <t xml:space="preserve">20.6848926544189</t>
   </si>
   <si>
     <t xml:space="preserve">20.4174976348877</t>
@@ -2075,7 +2075,7 @@
     <t xml:space="preserve">20.1882991790771</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2769794464111</t>
+    <t xml:space="preserve">21.2769813537598</t>
   </si>
   <si>
     <t xml:space="preserve">21.1814823150635</t>
@@ -2093,13 +2093,13 @@
     <t xml:space="preserve">20.9904842376709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1050834655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1623802185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2578811645508</t>
+    <t xml:space="preserve">21.1050815582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1623821258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2578792572021</t>
   </si>
   <si>
     <t xml:space="preserve">21.0286846160889</t>
@@ -2114,10 +2114,10 @@
     <t xml:space="preserve">22.4802570343018</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5566558837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5184574127197</t>
+    <t xml:space="preserve">22.5566539764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5184555053711</t>
   </si>
   <si>
     <t xml:space="preserve">22.0982608795166</t>
@@ -2129,34 +2129,34 @@
     <t xml:space="preserve">21.9645671844482</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9454650878906</t>
+    <t xml:space="preserve">21.9454669952393</t>
   </si>
   <si>
     <t xml:space="preserve">22.3083610534668</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5948543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7476501464844</t>
+    <t xml:space="preserve">22.5948524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7476482391357</t>
   </si>
   <si>
     <t xml:space="preserve">22.8049488067627</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0600662231445</t>
+    <t xml:space="preserve">22.0600643157959</t>
   </si>
   <si>
     <t xml:space="preserve">22.2319602966309</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3533782958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4747982025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.455696105957</t>
+    <t xml:space="preserve">21.3533802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4747943878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4556980133057</t>
   </si>
   <si>
     <t xml:space="preserve">21.1241836547852</t>
@@ -2183,10 +2183,10 @@
     <t xml:space="preserve">21.3724765777588</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6016750335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6780700683594</t>
+    <t xml:space="preserve">21.6016731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.678071975708</t>
   </si>
   <si>
     <t xml:space="preserve">21.4870738983154</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">20.646692276001</t>
   </si>
   <si>
-    <t xml:space="preserve">20.608491897583</t>
+    <t xml:space="preserve">20.6084938049316</t>
   </si>
   <si>
     <t xml:space="preserve">20.4938945770264</t>
@@ -2207,40 +2207,40 @@
     <t xml:space="preserve">20.8567886352539</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3792953491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.894983291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9331855773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3219985961914</t>
+    <t xml:space="preserve">20.3792972564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8949851989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9331836700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3219966888428</t>
   </si>
   <si>
     <t xml:space="preserve">20.3410968780518</t>
   </si>
   <si>
-    <t xml:space="preserve">21.830867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0218658447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5375556945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6521530151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0150451660156</t>
+    <t xml:space="preserve">21.8308696746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0218639373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5375576019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6521511077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0150470733643</t>
   </si>
   <si>
     <t xml:space="preserve">23.4543361663818</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7217311859131</t>
+    <t xml:space="preserve">23.7217330932617</t>
   </si>
   <si>
     <t xml:space="preserve">23.9127292633057</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">23.5689334869385</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0846214294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7981300354004</t>
+    <t xml:space="preserve">24.084623336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.798131942749</t>
   </si>
   <si>
     <t xml:space="preserve">23.8745288848877</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">24.3711204528809</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8677082061768</t>
+    <t xml:space="preserve">24.8677101135254</t>
   </si>
   <si>
     <t xml:space="preserve">25.0969047546387</t>
@@ -2285,10 +2285,10 @@
     <t xml:space="preserve">24.9250087738037</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0205059051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6194114685059</t>
+    <t xml:space="preserve">25.0205097198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6194133758545</t>
   </si>
   <si>
     <t xml:space="preserve">24.9441070556641</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">24.8295078277588</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6385135650635</t>
+    <t xml:space="preserve">24.6385116577148</t>
   </si>
   <si>
     <t xml:space="preserve">24.4475154876709</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">24.5430164337158</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3520183563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6576156616211</t>
+    <t xml:space="preserve">24.3520202636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6576137542725</t>
   </si>
   <si>
     <t xml:space="preserve">24.6767120361328</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">25.3070011138916</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3452014923096</t>
+    <t xml:space="preserve">25.3451995849609</t>
   </si>
   <si>
     <t xml:space="preserve">24.8486099243164</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">25.7653923034668</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6125907897949</t>
+    <t xml:space="preserve">25.6125926971436</t>
   </si>
   <si>
     <t xml:space="preserve">25.5552940368652</t>
@@ -2360,10 +2360,10 @@
     <t xml:space="preserve">24.7722091674805</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5239143371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9059085845947</t>
+    <t xml:space="preserve">24.5239162445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9059066772461</t>
   </si>
   <si>
     <t xml:space="preserve">25.6698913574219</t>
@@ -2372,22 +2372,22 @@
     <t xml:space="preserve">26.2237815856934</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2810821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3956775665283</t>
+    <t xml:space="preserve">26.281078338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3956756591797</t>
   </si>
   <si>
     <t xml:space="preserve">27.1405639648438</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2169609069824</t>
+    <t xml:space="preserve">27.2169628143311</t>
   </si>
   <si>
     <t xml:space="preserve">27.5225563049316</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6944522857666</t>
+    <t xml:space="preserve">27.694450378418</t>
   </si>
   <si>
     <t xml:space="preserve">27.8281497955322</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">28.783130645752</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2865409851074</t>
+    <t xml:space="preserve">28.2865390777588</t>
   </si>
   <si>
     <t xml:space="preserve">27.8854503631592</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">24.6003150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6071338653564</t>
+    <t xml:space="preserve">23.6071319580078</t>
   </si>
   <si>
     <t xml:space="preserve">24.4666175842285</t>
@@ -2423,28 +2423,28 @@
     <t xml:space="preserve">23.4352359771729</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8254070281982</t>
+    <t xml:space="preserve">19.8254089355469</t>
   </si>
   <si>
     <t xml:space="preserve">19.3479194641113</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5852918624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.323356628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7285385131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1200790405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9031658172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5239028930664</t>
+    <t xml:space="preserve">15.5852909088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3233547210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7285394668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.120080947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9031677246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.523904800415</t>
   </si>
   <si>
     <t xml:space="preserve">17.7435493469238</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">18.1350917816162</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8322296142578</t>
+    <t xml:space="preserve">18.8322277069092</t>
   </si>
   <si>
     <t xml:space="preserve">18.1446399688721</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">18.1159896850586</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8772468566895</t>
+    <t xml:space="preserve">17.8772430419922</t>
   </si>
   <si>
     <t xml:space="preserve">17.3806591033936</t>
@@ -2477,34 +2477,34 @@
     <t xml:space="preserve">16.8076667785645</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6480484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7844772338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4311351776123</t>
+    <t xml:space="preserve">17.6480503082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7844791412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4311332702637</t>
   </si>
   <si>
     <t xml:space="preserve">18.4454612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7653770446777</t>
+    <t xml:space="preserve">18.7653789520264</t>
   </si>
   <si>
     <t xml:space="preserve">17.9536437988281</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8663368225098</t>
+    <t xml:space="preserve">20.8663387298584</t>
   </si>
   <si>
     <t xml:space="preserve">19.2715187072754</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8465557098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0068550109863</t>
+    <t xml:space="preserve">18.8465538024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0068531036377</t>
   </si>
   <si>
     <t xml:space="preserve">20.2455997467041</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">22.3370094299316</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7926692962646</t>
+    <t xml:space="preserve">21.7926712036133</t>
   </si>
   <si>
     <t xml:space="preserve">21.0191345214844</t>
@@ -2543,25 +2543,25 @@
     <t xml:space="preserve">21.8595161437988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9522876739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9932174682617</t>
+    <t xml:space="preserve">20.9522857666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9932155609131</t>
   </si>
   <si>
     <t xml:space="preserve">21.658971786499</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0341453552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1391925811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2797088623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5020847320557</t>
+    <t xml:space="preserve">23.0341472625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1391906738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2797107696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5020866394043</t>
   </si>
   <si>
     <t xml:space="preserve">23.8267803192139</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">23.8172302246094</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3588390350342</t>
+    <t xml:space="preserve">23.3588371276855</t>
   </si>
   <si>
     <t xml:space="preserve">22.6903514862061</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">22.0696144104004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6998996734619</t>
+    <t xml:space="preserve">22.6999015808105</t>
   </si>
   <si>
     <t xml:space="preserve">22.9386463165283</t>
@@ -2609,16 +2609,16 @@
     <t xml:space="preserve">23.1487426757812</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4638843536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4229545593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4611549377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6426029205322</t>
+    <t xml:space="preserve">23.4638862609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4229583740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4611568450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6426010131836</t>
   </si>
   <si>
     <t xml:space="preserve">22.7381000518799</t>
@@ -2627,55 +2627,55 @@
     <t xml:space="preserve">23.272891998291</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2442417144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5402851104736</t>
+    <t xml:space="preserve">23.2442398071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.540283203125</t>
   </si>
   <si>
     <t xml:space="preserve">23.7408313751221</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8363265991211</t>
+    <t xml:space="preserve">23.8363285064697</t>
   </si>
   <si>
     <t xml:space="preserve">23.7121810913086</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7599296569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1610221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3233699798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7340106964111</t>
+    <t xml:space="preserve">23.7599315643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1610202789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3233680725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7340087890625</t>
   </si>
   <si>
     <t xml:space="preserve">25.2783508300781</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0682563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0587024688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7531127929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1351013183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5580253601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.510274887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6467018127441</t>
+    <t xml:space="preserve">25.0682544708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0587043762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7531108856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.135103225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5580234527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5102767944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6467037200928</t>
   </si>
   <si>
     <t xml:space="preserve">28.2292404174805</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">27.0355129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3793087005615</t>
+    <t xml:space="preserve">27.3793106079102</t>
   </si>
   <si>
     <t xml:space="preserve">27.2265110015869</t>
@@ -2720,16 +2720,16 @@
     <t xml:space="preserve">26.7108211517334</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5007266998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4529800415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6630725860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5389251708984</t>
+    <t xml:space="preserve">26.5007286071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4529781341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6630744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5389270782471</t>
   </si>
   <si>
     <t xml:space="preserve">26.2619800567627</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">26.4625282287598</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5989532470703</t>
+    <t xml:space="preserve">27.5989551544189</t>
   </si>
   <si>
     <t xml:space="preserve">26.6726226806641</t>
@@ -2762,16 +2762,16 @@
     <t xml:space="preserve">28.5061874389648</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9932270050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7926807403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6971836090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.57985496521</t>
+    <t xml:space="preserve">28.9932250976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7926826477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6971817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5798530578613</t>
   </si>
   <si>
     <t xml:space="preserve">27.6562519073486</t>
@@ -2780,10 +2780,10 @@
     <t xml:space="preserve">27.4748058319092</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6849021911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3847675323486</t>
+    <t xml:space="preserve">27.6849040985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3847694396973</t>
   </si>
   <si>
     <t xml:space="preserve">29.967306137085</t>
@@ -2792,13 +2792,13 @@
     <t xml:space="preserve">29.1746711730957</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4802684783936</t>
+    <t xml:space="preserve">29.4802665710449</t>
   </si>
   <si>
     <t xml:space="preserve">29.8336124420166</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0246086120605</t>
+    <t xml:space="preserve">30.0246067047119</t>
   </si>
   <si>
     <t xml:space="preserve">29.1651248931885</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">30.9891376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7503910064697</t>
+    <t xml:space="preserve">30.7503929138184</t>
   </si>
   <si>
     <t xml:space="preserve">30.5402965545654</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">30.6835441589355</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8172416687012</t>
+    <t xml:space="preserve">30.8172397613525</t>
   </si>
   <si>
     <t xml:space="preserve">30.4829998016357</t>
@@ -2864,13 +2864,13 @@
     <t xml:space="preserve">33.6535377502441</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3097381591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4693641662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3288421630859</t>
+    <t xml:space="preserve">33.309741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4693603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3288383483887</t>
   </si>
   <si>
     <t xml:space="preserve">33.5580368041992</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">34.1310272216797</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4338912963867</t>
+    <t xml:space="preserve">33.4338874816895</t>
   </si>
   <si>
     <t xml:space="preserve">34.4461708068848</t>
@@ -2903,16 +2903,16 @@
     <t xml:space="preserve">31.5143756866455</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6098766326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9727687835693</t>
+    <t xml:space="preserve">31.6098728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9727649688721</t>
   </si>
   <si>
     <t xml:space="preserve">32.7367515563965</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0587158203125</t>
+    <t xml:space="preserve">32.0587196350098</t>
   </si>
   <si>
     <t xml:space="preserve">31.256534576416</t>
@@ -2927,37 +2927,37 @@
     <t xml:space="preserve">31.1323833465576</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8745422363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0846385955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6194286346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0969123840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3615798950195</t>
+    <t xml:space="preserve">30.8745403289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0846366882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6194248199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0969161987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3615818023682</t>
   </si>
   <si>
     <t xml:space="preserve">32.1542129516602</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9441204071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4216117858887</t>
+    <t xml:space="preserve">31.9441165924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4216079711914</t>
   </si>
   <si>
     <t xml:space="preserve">31.6958236694336</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2115097045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7435722351074</t>
+    <t xml:space="preserve">32.2115135192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7435760498047</t>
   </si>
   <si>
     <t xml:space="preserve">32.2783584594727</t>
@@ -2966,16 +2966,16 @@
     <t xml:space="preserve">32.5075569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4120597839355</t>
+    <t xml:space="preserve">32.4120559692383</t>
   </si>
   <si>
     <t xml:space="preserve">32.0491638183594</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5334777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2087802886963</t>
+    <t xml:space="preserve">31.5334739685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2087841033936</t>
   </si>
   <si>
     <t xml:space="preserve">32.3165626525879</t>
@@ -2984,13 +2984,13 @@
     <t xml:space="preserve">32.163761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1064605712891</t>
+    <t xml:space="preserve">32.1064643859863</t>
   </si>
   <si>
     <t xml:space="preserve">32.3834114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6221504211426</t>
+    <t xml:space="preserve">32.6221542358398</t>
   </si>
   <si>
     <t xml:space="preserve">32.6508026123047</t>
@@ -3002,19 +3002,19 @@
     <t xml:space="preserve">32.5839576721191</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3547668457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0682640075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0396156311035</t>
+    <t xml:space="preserve">32.3547630310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0682678222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0396194458008</t>
   </si>
   <si>
     <t xml:space="preserve">32.5648536682129</t>
   </si>
   <si>
-    <t xml:space="preserve">32.326114654541</t>
+    <t xml:space="preserve">32.3261108398438</t>
   </si>
   <si>
     <t xml:space="preserve">31.9250202178955</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">33.7967834472656</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5989685058594</t>
+    <t xml:space="preserve">34.5989608764648</t>
   </si>
   <si>
     <t xml:space="preserve">34.4843711853027</t>
@@ -3041,13 +3041,13 @@
     <t xml:space="preserve">35.0000610351562</t>
   </si>
   <si>
-    <t xml:space="preserve">35.80224609375</t>
+    <t xml:space="preserve">35.8022422790527</t>
   </si>
   <si>
     <t xml:space="preserve">35.5539474487305</t>
   </si>
   <si>
-    <t xml:space="preserve">35.334300994873</t>
+    <t xml:space="preserve">35.3343048095703</t>
   </si>
   <si>
     <t xml:space="preserve">34.2551727294922</t>
@@ -3059,19 +3059,19 @@
     <t xml:space="preserve">33.3670387268066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3192863464355</t>
+    <t xml:space="preserve">33.3192901611328</t>
   </si>
   <si>
     <t xml:space="preserve">31.781774520874</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8104248046875</t>
+    <t xml:space="preserve">31.8104209899902</t>
   </si>
   <si>
     <t xml:space="preserve">32.4598083496094</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7081031799316</t>
+    <t xml:space="preserve">32.7080993652344</t>
   </si>
   <si>
     <t xml:space="preserve">29.9768581390381</t>
@@ -3083,10 +3083,10 @@
     <t xml:space="preserve">28.6876335144043</t>
   </si>
   <si>
-    <t xml:space="preserve">29.002779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3874988555908</t>
+    <t xml:space="preserve">29.0027770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3875007629395</t>
   </si>
   <si>
     <t xml:space="preserve">30.6453456878662</t>
@@ -3095,19 +3095,19 @@
     <t xml:space="preserve">31.4761772155762</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5211963653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.731294631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1228370666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5498466491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5375652313232</t>
+    <t xml:space="preserve">30.5211944580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7312927246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1228313446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5498447418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5375671386719</t>
   </si>
   <si>
     <t xml:space="preserve">30.1487522125244</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">31.6671752929688</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4065971374512</t>
+    <t xml:space="preserve">30.4065990447998</t>
   </si>
   <si>
     <t xml:space="preserve">30.7694931030273</t>
@@ -3125,13 +3125,13 @@
     <t xml:space="preserve">30.6644439697266</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3111000061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9413890838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2756328582764</t>
+    <t xml:space="preserve">30.3111019134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9413928985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2756290435791</t>
   </si>
   <si>
     <t xml:space="preserve">30.9604835510254</t>
@@ -3146,31 +3146,31 @@
     <t xml:space="preserve">33.5007400512695</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9372978210449</t>
+    <t xml:space="preserve">32.9373016357422</t>
   </si>
   <si>
     <t xml:space="preserve">33.8731803894043</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6344375610352</t>
+    <t xml:space="preserve">33.6344337463379</t>
   </si>
   <si>
     <t xml:space="preserve">33.624885559082</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1787757873535</t>
+    <t xml:space="preserve">34.1787796020508</t>
   </si>
   <si>
     <t xml:space="preserve">34.2169761657715</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9905052185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8281631469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3029174804688</t>
+    <t xml:space="preserve">34.9905090332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8281669616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.302921295166</t>
   </si>
   <si>
     <t xml:space="preserve">33.1091918945312</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">33.5484924316406</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8063316345215</t>
+    <t xml:space="preserve">33.8063354492188</t>
   </si>
   <si>
     <t xml:space="preserve">33.233341217041</t>
@@ -3191,22 +3191,22 @@
     <t xml:space="preserve">33.5771408081055</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2688102722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9059143066406</t>
+    <t xml:space="preserve">32.2688140869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9059181213379</t>
   </si>
   <si>
     <t xml:space="preserve">31.8868179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0873641967773</t>
+    <t xml:space="preserve">32.0873680114746</t>
   </si>
   <si>
     <t xml:space="preserve">32.946849822998</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1378440856934</t>
+    <t xml:space="preserve">33.1378479003906</t>
   </si>
   <si>
     <t xml:space="preserve">34.7995109558105</t>
@@ -3215,10 +3215,10 @@
     <t xml:space="preserve">35.8851928710938</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6538162231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9620552062988</t>
+    <t xml:space="preserve">36.6538200378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9620590209961</t>
   </si>
   <si>
     <t xml:space="preserve">36.769115447998</t>
@@ -3227,22 +3227,22 @@
     <t xml:space="preserve">37.0765647888184</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4224472045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1245994567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0189170837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6818542480469</t>
+    <t xml:space="preserve">37.4224433898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1246032714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.018913269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6818580627441</t>
   </si>
   <si>
     <t xml:space="preserve">38.2391090393066</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7683258056641</t>
+    <t xml:space="preserve">37.7683296203613</t>
   </si>
   <si>
     <t xml:space="preserve">37.8836212158203</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">39.2479286193848</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6138153076172</t>
+    <t xml:space="preserve">38.6138114929199</t>
   </si>
   <si>
     <t xml:space="preserve">38.6426391601562</t>
@@ -3263,19 +3263,19 @@
     <t xml:space="preserve">39.3440093994141</t>
   </si>
   <si>
-    <t xml:space="preserve">38.594596862793</t>
+    <t xml:space="preserve">38.5946006774902</t>
   </si>
   <si>
     <t xml:space="preserve">38.7963638305664</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7194976806641</t>
+    <t xml:space="preserve">38.7195014953613</t>
   </si>
   <si>
     <t xml:space="preserve">38.6042060852051</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6130256652832</t>
+    <t xml:space="preserve">39.6130294799805</t>
   </si>
   <si>
     <t xml:space="preserve">39.6514587402344</t>
@@ -3284,31 +3284,31 @@
     <t xml:space="preserve">39.7475357055664</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4969482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.006950378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8051834106445</t>
+    <t xml:space="preserve">40.4969520568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0069427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8051795959473</t>
   </si>
   <si>
     <t xml:space="preserve">39.9685173034668</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6034202575684</t>
+    <t xml:space="preserve">39.6034240722656</t>
   </si>
   <si>
     <t xml:space="preserve">39.7571449279785</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9973449707031</t>
+    <t xml:space="preserve">39.9973411560059</t>
   </si>
   <si>
     <t xml:space="preserve">39.0749893188477</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5769538879395</t>
+    <t xml:space="preserve">36.5769577026367</t>
   </si>
   <si>
     <t xml:space="preserve">37.5665588378906</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">37.556957244873</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3736152648926</t>
+    <t xml:space="preserve">38.3736190795898</t>
   </si>
   <si>
     <t xml:space="preserve">38.9789161682129</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">39.1614608764648</t>
   </si>
   <si>
-    <t xml:space="preserve">38.479305267334</t>
+    <t xml:space="preserve">38.4793014526367</t>
   </si>
   <si>
     <t xml:space="preserve">39.4496955871582</t>
@@ -3335,13 +3335,13 @@
     <t xml:space="preserve">39.1806755065918</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8540077209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.430477142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7675361633301</t>
+    <t xml:space="preserve">38.8540115356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4304809570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7675323486328</t>
   </si>
   <si>
     <t xml:space="preserve">40.0453796386719</t>
@@ -3359,13 +3359,13 @@
     <t xml:space="preserve">40.7083168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2567558288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3336181640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.266357421875</t>
+    <t xml:space="preserve">40.2567520141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3336143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2663536071777</t>
   </si>
   <si>
     <t xml:space="preserve">40.4489059448242</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">41.1406707763672</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3424301147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2271461486816</t>
+    <t xml:space="preserve">41.3424339294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2271385192871</t>
   </si>
   <si>
     <t xml:space="preserve">41.2367477416992</t>
@@ -3395,10 +3395,10 @@
     <t xml:space="preserve">43.0814476013184</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2455749511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0341949462891</t>
+    <t xml:space="preserve">42.2455711364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0341987609863</t>
   </si>
   <si>
     <t xml:space="preserve">41.7651786804199</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">41.9669418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">42.466552734375</t>
+    <t xml:space="preserve">42.4665489196777</t>
   </si>
   <si>
     <t xml:space="preserve">42.5434074401855</t>
@@ -3416,22 +3416,22 @@
     <t xml:space="preserve">42.6683120727539</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9853706359863</t>
+    <t xml:space="preserve">42.9853744506836</t>
   </si>
   <si>
     <t xml:space="preserve">42.3896865844727</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8988990783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0245895385742</t>
+    <t xml:space="preserve">42.8989028930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0245933532715</t>
   </si>
   <si>
     <t xml:space="preserve">41.9765472412109</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5345916748047</t>
+    <t xml:space="preserve">41.5345878601074</t>
   </si>
   <si>
     <t xml:space="preserve">41.4577293395996</t>
@@ -3440,25 +3440,25 @@
     <t xml:space="preserve">39.7187118530273</t>
   </si>
   <si>
-    <t xml:space="preserve">41.006160736084</t>
+    <t xml:space="preserve">41.0061645507812</t>
   </si>
   <si>
     <t xml:space="preserve">40.0165596008301</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8332176208496</t>
+    <t xml:space="preserve">40.8332214355469</t>
   </si>
   <si>
     <t xml:space="preserve">41.0638084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0718383789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1679229736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3112487792969</t>
+    <t xml:space="preserve">43.0718421936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1679191589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3112449645996</t>
   </si>
   <si>
     <t xml:space="preserve">43.2159576416016</t>
@@ -3467,13 +3467,13 @@
     <t xml:space="preserve">41.9477272033691</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7859649658203</t>
+    <t xml:space="preserve">39.7859725952148</t>
   </si>
   <si>
     <t xml:space="preserve">40.2759666442871</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5842056274414</t>
+    <t xml:space="preserve">39.5842094421387</t>
   </si>
   <si>
     <t xml:space="preserve">39.1902847290039</t>
@@ -3488,22 +3488,22 @@
     <t xml:space="preserve">40.10302734375</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0077323913574</t>
+    <t xml:space="preserve">39.0077362060547</t>
   </si>
   <si>
     <t xml:space="preserve">39.0653800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9108695983887</t>
+    <t xml:space="preserve">39.9108734130859</t>
   </si>
   <si>
     <t xml:space="preserve">40.2087097167969</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2463569641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6210594177246</t>
+    <t xml:space="preserve">41.2463531494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6210632324219</t>
   </si>
   <si>
     <t xml:space="preserve">42.7932167053223</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">42.9469413757324</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3800773620605</t>
+    <t xml:space="preserve">42.3800811767578</t>
   </si>
   <si>
     <t xml:space="preserve">42.3992919921875</t>
@@ -3548,19 +3548,19 @@
     <t xml:space="preserve">44.0037994384766</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2055587768555</t>
+    <t xml:space="preserve">44.2055625915527</t>
   </si>
   <si>
     <t xml:space="preserve">43.4369354248047</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2551803588867</t>
+    <t xml:space="preserve">42.2551765441895</t>
   </si>
   <si>
     <t xml:space="preserve">42.8604698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8028221130371</t>
+    <t xml:space="preserve">42.8028182983398</t>
   </si>
   <si>
     <t xml:space="preserve">40.6794967651367</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">40.1318511962891</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1606750488281</t>
+    <t xml:space="preserve">40.1606712341309</t>
   </si>
   <si>
     <t xml:space="preserve">41.2655715942383</t>
@@ -3602,37 +3602,37 @@
     <t xml:space="preserve">41.0926322937012</t>
   </si>
   <si>
-    <t xml:space="preserve">41.986156463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5057678222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3512573242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3704681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5626220703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5330200195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6579170227051</t>
+    <t xml:space="preserve">41.9861602783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5057640075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.351261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3704719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5626258850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.533016204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6579132080078</t>
   </si>
   <si>
     <t xml:space="preserve">44.4169387817383</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0702667236328</t>
+    <t xml:space="preserve">45.0702705383301</t>
   </si>
   <si>
     <t xml:space="preserve">45.368106842041</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5890922546387</t>
+    <t xml:space="preserve">45.5890884399414</t>
   </si>
   <si>
     <t xml:space="preserve">44.8108558654785</t>
@@ -3647,25 +3647,25 @@
     <t xml:space="preserve">42.5914535522461</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8708610534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0261650085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2671432495117</t>
+    <t xml:space="preserve">41.8708648681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0261611938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.267147064209</t>
   </si>
   <si>
     <t xml:space="preserve">38.9308738708496</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3832244873047</t>
+    <t xml:space="preserve">38.383228302002</t>
   </si>
   <si>
     <t xml:space="preserve">38.1814651489258</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2014694213867</t>
+    <t xml:space="preserve">37.2014656066895</t>
   </si>
   <si>
     <t xml:space="preserve">35.7795104980469</t>
@@ -3677,7 +3677,7 @@
     <t xml:space="preserve">35.001277923584</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0397071838379</t>
+    <t xml:space="preserve">35.0397109985352</t>
   </si>
   <si>
     <t xml:space="preserve">34.4632339477539</t>
@@ -3689,25 +3689,25 @@
     <t xml:space="preserve">36.7018623352051</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8644065856934</t>
+    <t xml:space="preserve">37.8644027709961</t>
   </si>
   <si>
     <t xml:space="preserve">35.5585250854492</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8859825134277</t>
+    <t xml:space="preserve">34.8859786987305</t>
   </si>
   <si>
     <t xml:space="preserve">34.6553955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7138290405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1165733337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7706909179688</t>
+    <t xml:space="preserve">33.7138252258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.116569519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7706871032715</t>
   </si>
   <si>
     <t xml:space="preserve">33.9636306762695</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">34.280689239502</t>
   </si>
   <si>
-    <t xml:space="preserve">34.146183013916</t>
+    <t xml:space="preserve">34.1461791992188</t>
   </si>
   <si>
     <t xml:space="preserve">33.7714767456055</t>
@@ -3734,19 +3734,19 @@
     <t xml:space="preserve">33.8291206359863</t>
   </si>
   <si>
-    <t xml:space="preserve">34.568920135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2510757446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.933235168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9420547485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4712677001953</t>
+    <t xml:space="preserve">34.5689239501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2510795593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9332389831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9420509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4712715148926</t>
   </si>
   <si>
     <t xml:space="preserve">36.4520530700684</t>
@@ -3755,10 +3755,10 @@
     <t xml:space="preserve">36.1253852844238</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7803001403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5889282226562</t>
+    <t xml:space="preserve">34.7802925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5889205932617</t>
   </si>
   <si>
     <t xml:space="preserve">35.6450004577637</t>
@@ -3767,16 +3767,16 @@
     <t xml:space="preserve">33.7042236328125</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4344139099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1357879638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9244155883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2695045471191</t>
+    <t xml:space="preserve">34.4344177246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1357841491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9244117736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2695083618164</t>
   </si>
   <si>
     <t xml:space="preserve">36.3175468444824</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">35.7602920532227</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2118606567383</t>
+    <t xml:space="preserve">36.2118644714355</t>
   </si>
   <si>
     <t xml:space="preserve">38.508129119873</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">39.0173454284668</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9500923156738</t>
+    <t xml:space="preserve">38.9500885009766</t>
   </si>
   <si>
     <t xml:space="preserve">40.2375373840332</t>
@@ -3812,7 +3812,7 @@
     <t xml:space="preserve">41.2943954467773</t>
   </si>
   <si>
-    <t xml:space="preserve">40.890869140625</t>
+    <t xml:space="preserve">40.8908653259277</t>
   </si>
   <si>
     <t xml:space="preserve">40.6891021728516</t>
@@ -3830,10 +3830,10 @@
     <t xml:space="preserve">39.219108581543</t>
   </si>
   <si>
-    <t xml:space="preserve">38.623420715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9797019958496</t>
+    <t xml:space="preserve">38.6234245300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9796981811523</t>
   </si>
   <si>
     <t xml:space="preserve">36.8075485229492</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">36.6442108154297</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3367652893066</t>
+    <t xml:space="preserve">36.3367614746094</t>
   </si>
   <si>
     <t xml:space="preserve">35.4528427124023</t>
@@ -3854,10 +3854,10 @@
     <t xml:space="preserve">36.721076965332</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1349983215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7218627929688</t>
+    <t xml:space="preserve">36.1350021362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7218589782715</t>
   </si>
   <si>
     <t xml:space="preserve">35.3183326721191</t>
@@ -3866,10 +3866,10 @@
     <t xml:space="preserve">34.0693168640137</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2726516723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9836349487305</t>
+    <t xml:space="preserve">32.2726554870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9836387634277</t>
   </si>
   <si>
     <t xml:space="preserve">32.9740257263184</t>
@@ -3878,19 +3878,19 @@
     <t xml:space="preserve">31.0524635314941</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9067726135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9163780212402</t>
+    <t xml:space="preserve">32.9067687988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.916374206543</t>
   </si>
   <si>
     <t xml:space="preserve">32.9644203186035</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2734451293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3414840698242</t>
+    <t xml:space="preserve">31.2734432220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3414859771729</t>
   </si>
   <si>
     <t xml:space="preserve">30.6777591705322</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">30.9489860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2492733001709</t>
+    <t xml:space="preserve">31.2492713928223</t>
   </si>
   <si>
     <t xml:space="preserve">31.3558235168457</t>
@@ -3917,7 +3917,7 @@
     <t xml:space="preserve">31.0555400848389</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1934242248535</t>
+    <t xml:space="preserve">30.1934223175049</t>
   </si>
   <si>
     <t xml:space="preserve">30.0965557098389</t>
@@ -3929,28 +3929,28 @@
     <t xml:space="preserve">30.3484115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4646530151367</t>
+    <t xml:space="preserve">30.4646511077881</t>
   </si>
   <si>
     <t xml:space="preserve">29.7865810394287</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2948322296143</t>
+    <t xml:space="preserve">28.2948303222656</t>
   </si>
   <si>
     <t xml:space="preserve">26.2606258392334</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5438137054443</t>
+    <t xml:space="preserve">25.5438117980957</t>
   </si>
   <si>
     <t xml:space="preserve">26.3090591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3985118865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4760036468506</t>
+    <t xml:space="preserve">25.398509979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.476001739502</t>
   </si>
   <si>
     <t xml:space="preserve">25.4663181304932</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">28.3335781097412</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4378604888916</t>
+    <t xml:space="preserve">29.4378623962402</t>
   </si>
   <si>
     <t xml:space="preserve">29.9900035858154</t>
@@ -4004,13 +4004,13 @@
     <t xml:space="preserve">28.2173366546631</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7523784637451</t>
+    <t xml:space="preserve">27.7523765563965</t>
   </si>
   <si>
     <t xml:space="preserve">28.3238925933838</t>
   </si>
   <si>
-    <t xml:space="preserve">28.924467086792</t>
+    <t xml:space="preserve">28.9244689941406</t>
   </si>
   <si>
     <t xml:space="preserve">28.8469734191895</t>
@@ -4019,13 +4019,13 @@
     <t xml:space="preserve">29.6994037628174</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1837368011475</t>
+    <t xml:space="preserve">30.1837387084961</t>
   </si>
   <si>
     <t xml:space="preserve">29.6412811279297</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4766082763672</t>
+    <t xml:space="preserve">29.4766063690186</t>
   </si>
   <si>
     <t xml:space="preserve">30.358097076416</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">31.2008399963379</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4236354827881</t>
+    <t xml:space="preserve">31.4236335754395</t>
   </si>
   <si>
     <t xml:space="preserve">29.970630645752</t>
@@ -4046,16 +4046,16 @@
     <t xml:space="preserve">30.8714923858643</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0942859649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4281749725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7381477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9922752380371</t>
+    <t xml:space="preserve">31.0942840576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4281730651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7381496429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9922733306885</t>
   </si>
   <si>
     <t xml:space="preserve">29.4572353363037</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">28.1979656219482</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8879909515381</t>
+    <t xml:space="preserve">27.8879928588867</t>
   </si>
   <si>
     <t xml:space="preserve">27.8104953765869</t>
@@ -4079,7 +4079,7 @@
     <t xml:space="preserve">26.8030815124512</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7740211486816</t>
+    <t xml:space="preserve">26.774019241333</t>
   </si>
   <si>
     <t xml:space="preserve">26.8612003326416</t>
@@ -4094,13 +4094,13 @@
     <t xml:space="preserve">24.962610244751</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2338371276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6816959381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0885372161865</t>
+    <t xml:space="preserve">25.2338352203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6816940307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0885353088379</t>
   </si>
   <si>
     <t xml:space="preserve">25.0497894287109</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">25.10791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2144622802734</t>
+    <t xml:space="preserve">25.2144641876221</t>
   </si>
   <si>
     <t xml:space="preserve">24.5073337554932</t>
@@ -4124,7 +4124,7 @@
     <t xml:space="preserve">24.2554817199707</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1779861450195</t>
+    <t xml:space="preserve">24.1779880523682</t>
   </si>
   <si>
     <t xml:space="preserve">23.8970737457275</t>
@@ -4136,13 +4136,13 @@
     <t xml:space="preserve">23.8292675018311</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0908069610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.013313293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1973609924316</t>
+    <t xml:space="preserve">24.0908088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0133152008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.197359085083</t>
   </si>
   <si>
     <t xml:space="preserve">24.8463687896729</t>
@@ -4151,13 +4151,13 @@
     <t xml:space="preserve">25.8053512573242</t>
   </si>
   <si>
-    <t xml:space="preserve">25.291955947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0572071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5728702545166</t>
+    <t xml:space="preserve">25.2919578552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0572052001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.572868347168</t>
   </si>
   <si>
     <t xml:space="preserve">26.7159004211426</t>
@@ -4175,13 +4175,13 @@
     <t xml:space="preserve">25.3307037353516</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6235733032227</t>
+    <t xml:space="preserve">24.6235752105713</t>
   </si>
   <si>
     <t xml:space="preserve">23.8389530181885</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9187183380127</t>
+    <t xml:space="preserve">22.9187164306641</t>
   </si>
   <si>
     <t xml:space="preserve">23.916446685791</t>
@@ -4190,7 +4190,7 @@
     <t xml:space="preserve">24.4395275115967</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3500785827637</t>
+    <t xml:space="preserve">25.350076675415</t>
   </si>
   <si>
     <t xml:space="preserve">24.8366813659668</t>
@@ -4226,10 +4226,10 @@
     <t xml:space="preserve">23.3643054962158</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4007816314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8150386810303</t>
+    <t xml:space="preserve">24.4007835388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8150367736816</t>
   </si>
   <si>
     <t xml:space="preserve">25.7278575897217</t>
@@ -4247,10 +4247,10 @@
     <t xml:space="preserve">27.7426891326904</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7062149047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.764331817627</t>
+    <t xml:space="preserve">26.7062129974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7643337249756</t>
   </si>
   <si>
     <t xml:space="preserve">26.5221672058105</t>
@@ -4259,16 +4259,16 @@
     <t xml:space="preserve">26.3187465667725</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8321399688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8805732727051</t>
+    <t xml:space="preserve">26.8321418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8805751800537</t>
   </si>
   <si>
     <t xml:space="preserve">27.0065002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1421146392822</t>
+    <t xml:space="preserve">27.1421165466309</t>
   </si>
   <si>
     <t xml:space="preserve">26.0087738037109</t>
@@ -4283,13 +4283,13 @@
     <t xml:space="preserve">26.9483833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1540718078613</t>
+    <t xml:space="preserve">26.15407371521</t>
   </si>
   <si>
     <t xml:space="preserve">26.6771545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6965274810791</t>
+    <t xml:space="preserve">26.6965255737305</t>
   </si>
   <si>
     <t xml:space="preserve">27.0936813354492</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">27.6651954650879</t>
   </si>
   <si>
-    <t xml:space="preserve">27.975170135498</t>
+    <t xml:space="preserve">27.9751682281494</t>
   </si>
   <si>
     <t xml:space="preserve">26.444673538208</t>
@@ -4325,37 +4325,37 @@
     <t xml:space="preserve">25.9700260162354</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6287212371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8708896636963</t>
+    <t xml:space="preserve">26.628719329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8708877563477</t>
   </si>
   <si>
     <t xml:space="preserve">26.1443843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2509384155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9677562713623</t>
+    <t xml:space="preserve">26.250940322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9677543640137</t>
   </si>
   <si>
     <t xml:space="preserve">25.9797115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1056385040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5996608734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.63840675354</t>
+    <t xml:space="preserve">26.105640411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5996589660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6384086608887</t>
   </si>
   <si>
     <t xml:space="preserve">26.2412528991699</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6019306182861</t>
+    <t xml:space="preserve">25.6019325256348</t>
   </si>
   <si>
     <t xml:space="preserve">24.9044876098633</t>
@@ -4370,16 +4370,16 @@
     <t xml:space="preserve">24.9916687011719</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9335498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7398147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4782733917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6070785522461</t>
+    <t xml:space="preserve">24.9335479736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7398166656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4782752990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6070766448975</t>
   </si>
   <si>
     <t xml:space="preserve">26.9290065765381</t>
@@ -4388,7 +4388,7 @@
     <t xml:space="preserve">27.1227416992188</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7666053771973</t>
+    <t xml:space="preserve">25.7666034698486</t>
   </si>
   <si>
     <t xml:space="preserve">26.483419418335</t>
@@ -4397,19 +4397,19 @@
     <t xml:space="preserve">27.2777290344238</t>
   </si>
   <si>
-    <t xml:space="preserve">26.541540145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2025051116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6190319061279</t>
+    <t xml:space="preserve">26.5415420532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.202507019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6190338134766</t>
   </si>
   <si>
     <t xml:space="preserve">26.5027942657471</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3358497619629</t>
+    <t xml:space="preserve">27.3358478546143</t>
   </si>
   <si>
     <t xml:space="preserve">29.1763210296631</t>
@@ -4427,10 +4427,10 @@
     <t xml:space="preserve">28.2367095947266</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1107845306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0310211181641</t>
+    <t xml:space="preserve">28.1107864379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0310192108154</t>
   </si>
   <si>
     <t xml:space="preserve">28.4304447174072</t>
@@ -4439,16 +4439,16 @@
     <t xml:space="preserve">28.8954067230225</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1860084533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6606559753418</t>
+    <t xml:space="preserve">29.1860065460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6606578826904</t>
   </si>
   <si>
     <t xml:space="preserve">30.6583862304688</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9392986297607</t>
+    <t xml:space="preserve">30.9393005371094</t>
   </si>
   <si>
     <t xml:space="preserve">30.8327445983887</t>
@@ -4460,10 +4460,10 @@
     <t xml:space="preserve">31.4817543029785</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6173667907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5689353942871</t>
+    <t xml:space="preserve">31.6173648834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5689315795898</t>
   </si>
   <si>
     <t xml:space="preserve">32.1404495239258</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">31.6754875183105</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2783336639404</t>
+    <t xml:space="preserve">31.2783355712891</t>
   </si>
   <si>
     <t xml:space="preserve">31.9176559448242</t>
@@ -4481,7 +4481,7 @@
     <t xml:space="preserve">31.9854621887207</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7820415496826</t>
+    <t xml:space="preserve">31.7820453643799</t>
   </si>
   <si>
     <t xml:space="preserve">32.3729286193848</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">32.3341865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7313423156738</t>
+    <t xml:space="preserve">32.7313385009766</t>
   </si>
   <si>
     <t xml:space="preserve">32.2373161315918</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">34.3780746459961</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7678146362305</t>
+    <t xml:space="preserve">33.7678184509277</t>
   </si>
   <si>
     <t xml:space="preserve">34.7655410766602</t>
@@ -4517,13 +4517,13 @@
     <t xml:space="preserve">34.7267951965332</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3296432495117</t>
+    <t xml:space="preserve">34.3296394348145</t>
   </si>
   <si>
     <t xml:space="preserve">34.2134017944336</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6686782836914</t>
+    <t xml:space="preserve">34.6686744689941</t>
   </si>
   <si>
     <t xml:space="preserve">34.8817825317383</t>
@@ -4544,16 +4544,16 @@
     <t xml:space="preserve">33.1478691101074</t>
   </si>
   <si>
-    <t xml:space="preserve">33.167407989502</t>
+    <t xml:space="preserve">33.1674041748047</t>
   </si>
   <si>
     <t xml:space="preserve">32.297924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0536842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4577445983887</t>
+    <t xml:space="preserve">32.0536880493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4577465057373</t>
   </si>
   <si>
     <t xml:space="preserve">32.2393035888672</t>
@@ -4565,22 +4565,22 @@
     <t xml:space="preserve">32.1513786315918</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5359020233154</t>
+    <t xml:space="preserve">31.5359001159668</t>
   </si>
   <si>
     <t xml:space="preserve">31.6238231658936</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6789321899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9489631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2908935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0466537475586</t>
+    <t xml:space="preserve">32.6789283752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9489669799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2908973693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0466575622559</t>
   </si>
   <si>
     <t xml:space="preserve">34.1638946533203</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">34.6816749572754</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4179000854492</t>
+    <t xml:space="preserve">34.417896270752</t>
   </si>
   <si>
     <t xml:space="preserve">34.2225074768066</t>
@@ -4604,7 +4604,7 @@
     <t xml:space="preserve">33.7438049316406</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6656455993652</t>
+    <t xml:space="preserve">33.6656494140625</t>
   </si>
   <si>
     <t xml:space="preserve">33.216251373291</t>
@@ -4625,10 +4625,10 @@
     <t xml:space="preserve">32.4835395812988</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9853000640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.887601852417</t>
+    <t xml:space="preserve">31.9852981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8875999450684</t>
   </si>
   <si>
     <t xml:space="preserve">30.0997867584229</t>
@@ -4655,19 +4655,19 @@
     <t xml:space="preserve">31.1451206207275</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0474262237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3440246582031</t>
+    <t xml:space="preserve">31.0474281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3440227508545</t>
   </si>
   <si>
     <t xml:space="preserve">30.2560977935791</t>
   </si>
   <si>
-    <t xml:space="preserve">30.363561630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.451488494873</t>
+    <t xml:space="preserve">30.3635635375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4514865875244</t>
   </si>
   <si>
     <t xml:space="preserve">30.9204235076904</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">30.8520374298096</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7152652740479</t>
+    <t xml:space="preserve">30.7152633666992</t>
   </si>
   <si>
     <t xml:space="preserve">30.0802478790283</t>
@@ -4700,16 +4700,16 @@
     <t xml:space="preserve">29.2009925842285</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6406192779541</t>
+    <t xml:space="preserve">29.6406211853027</t>
   </si>
   <si>
     <t xml:space="preserve">29.3182277679443</t>
   </si>
   <si>
-    <t xml:space="preserve">29.415922164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0739898681641</t>
+    <t xml:space="preserve">29.4159240722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0739917755127</t>
   </si>
   <si>
     <t xml:space="preserve">28.5562057495117</t>
@@ -4721,7 +4721,7 @@
     <t xml:space="preserve">29.0935287475586</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2889194488525</t>
+    <t xml:space="preserve">29.2889175415039</t>
   </si>
   <si>
     <t xml:space="preserve">29.1814556121826</t>
@@ -4733,10 +4733,10 @@
     <t xml:space="preserve">29.7578544616699</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5722332000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3475360870361</t>
+    <t xml:space="preserve">29.5722351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3475379943848</t>
   </si>
   <si>
     <t xml:space="preserve">28.800443649292</t>
@@ -4760,19 +4760,19 @@
     <t xml:space="preserve">28.2240447998047</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3217391967773</t>
+    <t xml:space="preserve">28.321741104126</t>
   </si>
   <si>
     <t xml:space="preserve">28.5952854156494</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3119716644287</t>
+    <t xml:space="preserve">28.3119697570801</t>
   </si>
   <si>
     <t xml:space="preserve">27.9309597015381</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0677337646484</t>
+    <t xml:space="preserve">28.0677318572998</t>
   </si>
   <si>
     <t xml:space="preserve">29.650390625</t>
@@ -4814,13 +4814,13 @@
     <t xml:space="preserve">26.6706962585449</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5143852233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0028591156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1005554199219</t>
+    <t xml:space="preserve">26.51438331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.002857208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1005535125732</t>
   </si>
   <si>
     <t xml:space="preserve">27.4620246887207</t>
@@ -4829,7 +4829,7 @@
     <t xml:space="preserve">26.709774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2799186706543</t>
+    <t xml:space="preserve">26.2799167633057</t>
   </si>
   <si>
     <t xml:space="preserve">26.4557685852051</t>
@@ -4838,13 +4838,13 @@
     <t xml:space="preserve">26.6120796203613</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4362297058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6511573791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6609287261963</t>
+    <t xml:space="preserve">26.4362277984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.651159286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6609268188477</t>
   </si>
   <si>
     <t xml:space="preserve">26.2213001251221</t>
@@ -4853,31 +4853,31 @@
     <t xml:space="preserve">25.1661968231201</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7949562072754</t>
+    <t xml:space="preserve">24.7949542999268</t>
   </si>
   <si>
     <t xml:space="preserve">26.0259094238281</t>
   </si>
   <si>
-    <t xml:space="preserve">25.889139175415</t>
+    <t xml:space="preserve">25.8891372680664</t>
   </si>
   <si>
     <t xml:space="preserve">26.8953952789307</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0614757537842</t>
+    <t xml:space="preserve">27.0614776611328</t>
   </si>
   <si>
     <t xml:space="preserve">27.1200923919678</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9344730377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9149322509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.475305557251</t>
+    <t xml:space="preserve">26.9344711303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9149341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4753074645996</t>
   </si>
   <si>
     <t xml:space="preserve">26.3385334014893</t>
@@ -4886,13 +4886,13 @@
     <t xml:space="preserve">27.5890274047852</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7683906555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3776111602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8856258392334</t>
+    <t xml:space="preserve">26.7683925628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.377613067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8856239318848</t>
   </si>
   <si>
     <t xml:space="preserve">27.5206432342529</t>
@@ -4907,25 +4907,25 @@
     <t xml:space="preserve">27.6085662841797</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7648773193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9505004882812</t>
+    <t xml:space="preserve">27.7648792266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9504985809326</t>
   </si>
   <si>
     <t xml:space="preserve">27.5499515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8723449707031</t>
+    <t xml:space="preserve">27.8723430633545</t>
   </si>
   <si>
     <t xml:space="preserve">27.3154811859131</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0517082214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9735527038574</t>
+    <t xml:space="preserve">27.0517063140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9735507965088</t>
   </si>
   <si>
     <t xml:space="preserve">28.0775032043457</t>
@@ -4958,7 +4958,7 @@
     <t xml:space="preserve">30.6175689697266</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5296440124512</t>
+    <t xml:space="preserve">30.5296421051025</t>
   </si>
   <si>
     <t xml:space="preserve">29.796932220459</t>
@@ -4970,7 +4970,7 @@
     <t xml:space="preserve">30.8715763092041</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6761856079102</t>
+    <t xml:space="preserve">30.6761837005615</t>
   </si>
   <si>
     <t xml:space="preserve">30.8911151885986</t>
@@ -4997,7 +4997,7 @@
     <t xml:space="preserve">29.1912231445312</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1619167327881</t>
+    <t xml:space="preserve">29.1619148254395</t>
   </si>
   <si>
     <t xml:space="preserve">29.9337043762207</t>
@@ -5015,10 +5015,10 @@
     <t xml:space="preserve">29.0544509887695</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4612560272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.510103225708</t>
+    <t xml:space="preserve">30.4612579345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5101051330566</t>
   </si>
   <si>
     <t xml:space="preserve">30.7738800048828</t>
@@ -5030,13 +5030,13 @@
     <t xml:space="preserve">30.1584033966064</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4221801757812</t>
+    <t xml:space="preserve">30.4221782684326</t>
   </si>
   <si>
     <t xml:space="preserve">30.8813457489014</t>
   </si>
   <si>
-    <t xml:space="preserve">31.125581741333</t>
+    <t xml:space="preserve">31.1255836486816</t>
   </si>
   <si>
     <t xml:space="preserve">30.744571685791</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">30.2658672332764</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0439147949219</t>
+    <t xml:space="preserve">32.0439109802246</t>
   </si>
   <si>
     <t xml:space="preserve">32.893856048584</t>
@@ -5078,7 +5078,7 @@
     <t xml:space="preserve">32.2002258300781</t>
   </si>
   <si>
-    <t xml:space="preserve">33.030632019043</t>
+    <t xml:space="preserve">33.0306358337402</t>
   </si>
   <si>
     <t xml:space="preserve">32.8547821044922</t>
@@ -5090,7 +5090,7 @@
     <t xml:space="preserve">31.6433639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9888095855713</t>
+    <t xml:space="preserve">30.9888076782227</t>
   </si>
   <si>
     <t xml:space="preserve">31.2916622161865</t>
@@ -5099,16 +5099,16 @@
     <t xml:space="preserve">31.1158142089844</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3858489990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2357940673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2650985717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0208625793457</t>
+    <t xml:space="preserve">32.3858451843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2357902526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2651023864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0208587646484</t>
   </si>
   <si>
     <t xml:space="preserve">32.4933090209961</t>
@@ -5123,7 +5123,7 @@
     <t xml:space="preserve">31.1646614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7605991363525</t>
+    <t xml:space="preserve">31.7605953216553</t>
   </si>
   <si>
     <t xml:space="preserve">30.1290950775146</t>
@@ -5132,10 +5132,10 @@
     <t xml:space="preserve">30.4026412963867</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1193237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8422679901123</t>
+    <t xml:space="preserve">30.1193256378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8422660827637</t>
   </si>
   <si>
     <t xml:space="preserve">31.2818927764893</t>
@@ -5147,16 +5147,16 @@
     <t xml:space="preserve">30.3049449920654</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7836494445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.705493927002</t>
+    <t xml:space="preserve">30.7836513519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7054958343506</t>
   </si>
   <si>
     <t xml:space="preserve">30.8227272033691</t>
   </si>
   <si>
-    <t xml:space="preserve">33.069709777832</t>
+    <t xml:space="preserve">33.0697059631348</t>
   </si>
   <si>
     <t xml:space="preserve">32.591007232666</t>
@@ -5180,7 +5180,7 @@
     <t xml:space="preserve">33.5972595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5679512023926</t>
+    <t xml:space="preserve">33.5679550170898</t>
   </si>
   <si>
     <t xml:space="preserve">34.0310287475586</t>
@@ -71275,7 +71275,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6493171296</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>1705414</v>
@@ -71296,6 +71296,32 @@
         <v>2052</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6494907407</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>2268182</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>15.210000038147</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>14.585000038147</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>14.7700004577637</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>15.1549997329712</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>2023</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="2059">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2060" uniqueCount="2060">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">7.39109230041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31191873550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36780500411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15357160568237</t>
+    <t xml:space="preserve">7.31191825866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36780548095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15357065200806</t>
   </si>
   <si>
     <t xml:space="preserve">6.96262264251709</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">7.16288614273071</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03248119354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08836936950684</t>
+    <t xml:space="preserve">7.0324821472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08836984634399</t>
   </si>
   <si>
     <t xml:space="preserve">7.19548654556274</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">7.34451961517334</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23740196228027</t>
+    <t xml:space="preserve">7.23740291595459</t>
   </si>
   <si>
     <t xml:space="preserve">7.35383367538452</t>
@@ -95,19 +95,19 @@
     <t xml:space="preserve">7.1489143371582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18151426315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40972137451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28397560119629</t>
+    <t xml:space="preserve">7.18151473999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40972089767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28397464752197</t>
   </si>
   <si>
     <t xml:space="preserve">7.13959932327271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05111169815063</t>
+    <t xml:space="preserve">7.05111122131348</t>
   </si>
   <si>
     <t xml:space="preserve">6.84619140625</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">6.51086759567261</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45498037338257</t>
+    <t xml:space="preserve">6.45497989654541</t>
   </si>
   <si>
     <t xml:space="preserve">6.5900411605835</t>
@@ -131,31 +131,31 @@
     <t xml:space="preserve">6.42237949371338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61798477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8834490776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71113014221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83687686920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70181560516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62729930877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99522542953491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8927640914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80427503585815</t>
+    <t xml:space="preserve">6.61798524856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88344955444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71112966537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83687734603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70181608200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62729978561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99522399902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89276313781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80427551269531</t>
   </si>
   <si>
     <t xml:space="preserve">6.79961824417114</t>
@@ -164,34 +164,34 @@
     <t xml:space="preserve">6.84153366088867</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6599006652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63195705413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79496097564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78564691543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86016273498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00919532775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11165571212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08371162414551</t>
+    <t xml:space="preserve">6.65989971160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63195610046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79496145248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78564596176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86016321182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00919580459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.111656665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08371210098267</t>
   </si>
   <si>
     <t xml:space="preserve">7.20945835113525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10699892044067</t>
+    <t xml:space="preserve">7.10699844360352</t>
   </si>
   <si>
     <t xml:space="preserve">7.04179668426514</t>
@@ -200,79 +200,79 @@
     <t xml:space="preserve">7.24205923080444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09768390655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17219972610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93467950820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91605043411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00453805923462</t>
+    <t xml:space="preserve">7.09768342971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17220020294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93467998504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91604995727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00453901290894</t>
   </si>
   <si>
     <t xml:space="preserve">7.27000284194946</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32588958740234</t>
+    <t xml:space="preserve">7.32589101791382</t>
   </si>
   <si>
     <t xml:space="preserve">7.22808742523193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50286722183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41437864303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4842381477356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57738399505615</t>
+    <t xml:space="preserve">7.50286674499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41437911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48423767089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57738351821899</t>
   </si>
   <si>
     <t xml:space="preserve">7.55409574508667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73107290267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60066843032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64258480072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70312976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73572969436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88476276397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88942050933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87079095840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78696060180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94530820846558</t>
+    <t xml:space="preserve">7.7310733795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60066986083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64258527755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7031307220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73573064804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88476181030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88942241668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87078952789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78695821762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94530725479126</t>
   </si>
   <si>
     <t xml:space="preserve">7.88010549545288</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08968353271484</t>
+    <t xml:space="preserve">8.08968257904053</t>
   </si>
   <si>
     <t xml:space="preserve">8.01760387420654</t>
@@ -281,61 +281,61 @@
     <t xml:space="preserve">8.09717178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10653305053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.050368309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17205905914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21418190002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23758506774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22354412078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1580171585083</t>
+    <t xml:space="preserve">8.10653400421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05036735534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21418285369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23758602142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22354507446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15801811218262</t>
   </si>
   <si>
     <t xml:space="preserve">8.07845020294189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08313179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14397525787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0129222869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91463470458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82102489471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64316844940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62912702560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6525297164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55892038345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63848876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98952102661133</t>
+    <t xml:space="preserve">8.0831298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14397621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01292514801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91463422775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82102537155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64316940307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62912607192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65253019332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55891990661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63848924636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98952341079712</t>
   </si>
   <si>
     <t xml:space="preserve">7.94739723205566</t>
@@ -344,49 +344,49 @@
     <t xml:space="preserve">8.05972766876221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67593097686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71337556838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72273683547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87250995635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92867565155029</t>
+    <t xml:space="preserve">7.67593145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71337461471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72273778915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87251043319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92867708206177</t>
   </si>
   <si>
     <t xml:space="preserve">7.89123249053955</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81166505813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71805572509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88187170028687</t>
+    <t xml:space="preserve">7.81166458129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71805477142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88186931610107</t>
   </si>
   <si>
     <t xml:space="preserve">7.96143913269043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91931390762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90995407104492</t>
+    <t xml:space="preserve">7.91931295394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90995311737061</t>
   </si>
   <si>
     <t xml:space="preserve">8.0550479888916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18142032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16737842559814</t>
+    <t xml:space="preserve">8.18141937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16737747192383</t>
   </si>
   <si>
     <t xml:space="preserve">8.19546222686768</t>
@@ -398,73 +398,73 @@
     <t xml:space="preserve">8.30779075622559</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36395740509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34991645812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3311939239502</t>
+    <t xml:space="preserve">8.36395835876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3499174118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33119297027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.29374980926514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1533374786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2890682220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36863803863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5090503692627</t>
+    <t xml:space="preserve">8.15333652496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28907012939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36863708496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50905132293701</t>
   </si>
   <si>
     <t xml:space="preserve">8.60733985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51373291015625</t>
+    <t xml:space="preserve">8.51373195648193</t>
   </si>
   <si>
     <t xml:space="preserve">8.63542366027832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75711441040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65414428710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78519725799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80859851837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92093086242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84604167938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81796073913574</t>
+    <t xml:space="preserve">8.75711345672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65414524078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78519535064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8085994720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92092990875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84604358673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81796169281006</t>
   </si>
   <si>
     <t xml:space="preserve">8.74775505065918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75243377685547</t>
+    <t xml:space="preserve">8.75243473052979</t>
   </si>
   <si>
     <t xml:space="preserve">8.82264041900635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73371124267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77115631103516</t>
+    <t xml:space="preserve">8.7337121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77115440368652</t>
   </si>
   <si>
     <t xml:space="preserve">8.76179504394531</t>
@@ -473,37 +473,37 @@
     <t xml:space="preserve">8.65882587432861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59329891204834</t>
+    <t xml:space="preserve">8.59329986572266</t>
   </si>
   <si>
     <t xml:space="preserve">8.57457637786865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5605354309082</t>
+    <t xml:space="preserve">8.56053733825684</t>
   </si>
   <si>
     <t xml:space="preserve">8.4856481552124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54181480407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5324535369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66818714141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49969005584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61670112609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49500942230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5558557510376</t>
+    <t xml:space="preserve">8.54181575775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53245258331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66818523406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49968910217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61670017242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49500846862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55585765838623</t>
   </si>
   <si>
     <t xml:space="preserve">8.61202144622803</t>
@@ -512,10 +512,10 @@
     <t xml:space="preserve">8.46692752838135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52777194976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56521511077881</t>
+    <t xml:space="preserve">8.52777290344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56521606445312</t>
   </si>
   <si>
     <t xml:space="preserve">8.69158840179443</t>
@@ -527,37 +527,37 @@
     <t xml:space="preserve">9.24856185913086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07070446014404</t>
+    <t xml:space="preserve">9.07070350646973</t>
   </si>
   <si>
     <t xml:space="preserve">9.01453876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89284801483154</t>
+    <t xml:space="preserve">8.89284896850586</t>
   </si>
   <si>
     <t xml:space="preserve">8.93965244293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81328010559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50436973571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42480278015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40140056610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39672088623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58393859863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34523582458496</t>
+    <t xml:space="preserve">8.81328201293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50437164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42480182647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40140151977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39671993255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58393955230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34523391723633</t>
   </si>
   <si>
     <t xml:space="preserve">8.46224594116211</t>
@@ -566,55 +566,55 @@
     <t xml:space="preserve">8.3826789855957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47160816192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98645782470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09878540039062</t>
+    <t xml:space="preserve">8.47160720825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98645687103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09878826141357</t>
   </si>
   <si>
     <t xml:space="preserve">9.06134414672852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51841259002686</t>
+    <t xml:space="preserve">8.51841354370117</t>
   </si>
   <si>
     <t xml:space="preserve">8.16269779205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31247234344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4419093132019</t>
+    <t xml:space="preserve">8.31247329711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44190883636475</t>
   </si>
   <si>
     <t xml:space="preserve">7.98484086990356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95675802230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38735961914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41076183319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44820499420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48096752166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37331771850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2329044342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18610000610352</t>
+    <t xml:space="preserve">7.95675849914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38736057281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41075992584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44820404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48096942901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37331676483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23290634155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18610095977783</t>
   </si>
   <si>
     <t xml:space="preserve">8.37799835205078</t>
@@ -629,16 +629,16 @@
     <t xml:space="preserve">8.72435188293457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67286586761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74307346343994</t>
+    <t xml:space="preserve">8.67286682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74307250976562</t>
   </si>
   <si>
     <t xml:space="preserve">8.71031093597412</t>
   </si>
   <si>
-    <t xml:space="preserve">9.154953956604</t>
+    <t xml:space="preserve">9.15495109558105</t>
   </si>
   <si>
     <t xml:space="preserve">8.96773529052734</t>
@@ -647,52 +647,52 @@
     <t xml:space="preserve">9.14091205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26728439331055</t>
+    <t xml:space="preserve">9.26728343963623</t>
   </si>
   <si>
     <t xml:space="preserve">9.33749008178711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40769577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37961387634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29536533355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36089134216309</t>
+    <t xml:space="preserve">9.4076976776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37961578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29536628723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36089038848877</t>
   </si>
   <si>
     <t xml:space="preserve">9.44514179229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48258399963379</t>
+    <t xml:space="preserve">9.48258495330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.43578052520752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35621070861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11282920837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10814762115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15963268280029</t>
+    <t xml:space="preserve">9.35621166229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11282825469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1081485748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15963363647461</t>
   </si>
   <si>
     <t xml:space="preserve">9.4638614654541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81021404266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95998954772949</t>
+    <t xml:space="preserve">9.81021499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95999050140381</t>
   </si>
   <si>
     <t xml:space="preserve">9.82893657684326</t>
@@ -704,10 +704,10 @@
     <t xml:space="preserve">9.64171886444092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70724487304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71660804748535</t>
+    <t xml:space="preserve">9.70724582672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71660709381104</t>
   </si>
   <si>
     <t xml:space="preserve">9.66043949127197</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">9.79149341583252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0255165100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0067949295044</t>
+    <t xml:space="preserve">10.0255146026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0067939758301</t>
   </si>
   <si>
     <t xml:space="preserve">10.1846504211426</t>
@@ -731,10 +731,10 @@
     <t xml:space="preserve">10.2595386505127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4280347824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4748363494873</t>
+    <t xml:space="preserve">10.4280338287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4748373031616</t>
   </si>
   <si>
     <t xml:space="preserve">10.3625078201294</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">10.3344259262085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5778074264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5122814178467</t>
+    <t xml:space="preserve">10.577808380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.512282371521</t>
   </si>
   <si>
     <t xml:space="preserve">10.5029211044312</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">10.8118314743042</t>
   </si>
   <si>
-    <t xml:space="preserve">10.88671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7182216644287</t>
+    <t xml:space="preserve">10.8867177963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7182207107544</t>
   </si>
   <si>
     <t xml:space="preserve">10.6526947021484</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">10.6433343887329</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6246128082275</t>
+    <t xml:space="preserve">10.6246137619019</t>
   </si>
   <si>
     <t xml:space="preserve">10.7088603973389</t>
@@ -776,25 +776,25 @@
     <t xml:space="preserve">10.8960790634155</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8399133682251</t>
+    <t xml:space="preserve">10.8399143218994</t>
   </si>
   <si>
     <t xml:space="preserve">10.9335231781006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9990491867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1301012039185</t>
+    <t xml:space="preserve">10.9990482330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1301021575928</t>
   </si>
   <si>
     <t xml:space="preserve">11.0926580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2517919540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9616031646729</t>
+    <t xml:space="preserve">11.2517929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9616050720215</t>
   </si>
   <si>
     <t xml:space="preserve">11.2049884796143</t>
@@ -806,49 +806,49 @@
     <t xml:space="preserve">11.1488227844238</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862668991089</t>
+    <t xml:space="preserve">11.1862659454346</t>
   </si>
   <si>
     <t xml:space="preserve">11.2798757553101</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4296493530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4109258651733</t>
+    <t xml:space="preserve">11.4296503067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.410927772522</t>
   </si>
   <si>
     <t xml:space="preserve">11.4577322006226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5801239013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8249073028564</t>
+    <t xml:space="preserve">11.5801248550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8249092102051</t>
   </si>
   <si>
     <t xml:space="preserve">11.8625659942627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9472980499268</t>
+    <t xml:space="preserve">11.9472970962524</t>
   </si>
   <si>
     <t xml:space="preserve">11.9190540313721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9284696578979</t>
+    <t xml:space="preserve">11.9284687042236</t>
   </si>
   <si>
     <t xml:space="preserve">11.9378833770752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9661283493042</t>
+    <t xml:space="preserve">11.9661273956299</t>
   </si>
   <si>
     <t xml:space="preserve">12.0602750778198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0979337692261</t>
+    <t xml:space="preserve">12.0979347229004</t>
   </si>
   <si>
     <t xml:space="preserve">12.0226173400879</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">12.1826658248901</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2391557693481</t>
+    <t xml:space="preserve">12.2391548156738</t>
   </si>
   <si>
     <t xml:space="preserve">11.9096384048462</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1450080871582</t>
+    <t xml:space="preserve">12.1450071334839</t>
   </si>
   <si>
     <t xml:space="preserve">11.4859762191772</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">11.6930999755859</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7307605743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7684192657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7590036392212</t>
+    <t xml:space="preserve">11.7307596206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7684183120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7590026855469</t>
   </si>
   <si>
     <t xml:space="preserve">11.627197265625</t>
@@ -893,73 +893,73 @@
     <t xml:space="preserve">11.5707082748413</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5236349105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4671468734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3729982376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0811424255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8834352493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6951389312744</t>
+    <t xml:space="preserve">11.5236358642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4671478271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3729991912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0811443328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8834323883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6951360702515</t>
   </si>
   <si>
     <t xml:space="preserve">10.5633325576782</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6104068756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7422103881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.911678314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9022626876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9493370056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1376314163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3541688919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3824129104614</t>
+    <t xml:space="preserve">10.610405921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7422132492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9116764068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9022636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9493360519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1376304626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3541707992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3824148178101</t>
   </si>
   <si>
     <t xml:space="preserve">11.3447551727295</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4106597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.269437789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.504807472229</t>
+    <t xml:space="preserve">11.4106588363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2694368362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5048055648804</t>
   </si>
   <si>
     <t xml:space="preserve">11.4294881820679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3353395462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2788524627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2506074905396</t>
+    <t xml:space="preserve">11.3353404998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2788515090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2506084442139</t>
   </si>
   <si>
     <t xml:space="preserve">11.1093873977661</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">11.0340690612793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9210929870605</t>
+    <t xml:space="preserve">10.9210920333862</t>
   </si>
   <si>
     <t xml:space="preserve">10.6668949127197</t>
@@ -980,37 +980,37 @@
     <t xml:space="preserve">10.78928565979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1941204071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1658754348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0717287063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1282167434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3165121078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3259248733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2411918640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0623121261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0905561447144</t>
+    <t xml:space="preserve">11.1941194534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1658744812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0717277526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1282148361206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3165111541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3259258270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.241192817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0623111724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0905570983887</t>
   </si>
   <si>
     <t xml:space="preserve">11.1752910614014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4389028549194</t>
+    <t xml:space="preserve">11.4389009475708</t>
   </si>
   <si>
     <t xml:space="preserve">11.7213449478149</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">11.984956741333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0132007598877</t>
+    <t xml:space="preserve">12.013201713562</t>
   </si>
   <si>
     <t xml:space="preserve">11.9567136764526</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">12.0508613586426</t>
   </si>
   <si>
-    <t xml:space="preserve">12.041446685791</t>
+    <t xml:space="preserve">12.0414457321167</t>
   </si>
   <si>
     <t xml:space="preserve">12.0791044235229</t>
@@ -1040,58 +1040,58 @@
     <t xml:space="preserve">11.9755430221558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.834321975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2203245162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1544218063354</t>
+    <t xml:space="preserve">11.8343210220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.220326423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1544227600098</t>
   </si>
   <si>
     <t xml:space="preserve">12.1073484420776</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4839382171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5215978622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6439895629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.785210609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8134536743164</t>
+    <t xml:space="preserve">12.4839372634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5215969085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.643988609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7852087020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8134527206421</t>
   </si>
   <si>
     <t xml:space="preserve">12.8322830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8040399551392</t>
+    <t xml:space="preserve">12.8040409088135</t>
   </si>
   <si>
     <t xml:space="preserve">12.1920804977417</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7872476577759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8531503677368</t>
+    <t xml:space="preserve">11.7872486114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8531513214111</t>
   </si>
   <si>
     <t xml:space="preserve">12.0320310592651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1732530593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2768125534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9002237319946</t>
+    <t xml:space="preserve">12.1732521057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2768144607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9002256393433</t>
   </si>
   <si>
     <t xml:space="preserve">11.448317527771</t>
@@ -1100,40 +1100,40 @@
     <t xml:space="preserve">11.5612936019897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4012432098389</t>
+    <t xml:space="preserve">11.4012441635132</t>
   </si>
   <si>
     <t xml:space="preserve">11.6742706298828</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7778339385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0885190963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0696897506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2014961242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.135594367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3615484237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3333034515381</t>
+    <t xml:space="preserve">11.7778329849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0885200500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0696887969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2014970779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1355934143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3615465164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3333024978638</t>
   </si>
   <si>
     <t xml:space="preserve">12.1638374328613</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7401762008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1261777877808</t>
+    <t xml:space="preserve">11.7401733398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1261787414551</t>
   </si>
   <si>
     <t xml:space="preserve">12.5404253005981</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">12.549840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5027666091919</t>
+    <t xml:space="preserve">12.5027675628662</t>
   </si>
   <si>
     <t xml:space="preserve">12.6345739364624</t>
@@ -1151,64 +1151,64 @@
     <t xml:space="preserve">13.1335544586182</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1241407394409</t>
+    <t xml:space="preserve">13.1241388320923</t>
   </si>
   <si>
     <t xml:space="preserve">13.0864810943604</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9546747207642</t>
+    <t xml:space="preserve">12.9546766281128</t>
   </si>
   <si>
     <t xml:space="preserve">13.4254112243652</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4630708694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5383892059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5572175979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6042909622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5101432800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2559471130371</t>
+    <t xml:space="preserve">13.4630699157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5383882522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5572166442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6042919158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5101451873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2559461593628</t>
   </si>
   <si>
     <t xml:space="preserve">13.4724855422974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3030195236206</t>
+    <t xml:space="preserve">13.3030214309692</t>
   </si>
   <si>
     <t xml:space="preserve">12.973503112793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.615743637085</t>
+    <t xml:space="preserve">12.6157426834106</t>
   </si>
   <si>
     <t xml:space="preserve">12.4086198806763</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3803758621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4651079177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5121822357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8228693008423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8793563842773</t>
+    <t xml:space="preserve">12.3803749084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.46510887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5121831893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.822868347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8793592453003</t>
   </si>
   <si>
     <t xml:space="preserve">12.8511123657227</t>
@@ -1223,43 +1223,43 @@
     <t xml:space="preserve">12.2579851150513</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7287216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0394086837769</t>
+    <t xml:space="preserve">12.728723526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0394067764282</t>
   </si>
   <si>
     <t xml:space="preserve">13.0958957672119</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2653608322144</t>
+    <t xml:space="preserve">13.26535987854</t>
   </si>
   <si>
     <t xml:space="preserve">13.4065818786621</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3312644958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3218507766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1617975234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3406801223755</t>
+    <t xml:space="preserve">13.3312635421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.321849822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1617984771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3406791687012</t>
   </si>
   <si>
     <t xml:space="preserve">13.2465324401855</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8887720108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8605279922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2936038970947</t>
+    <t xml:space="preserve">12.8887710571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8605260848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.293604850769</t>
   </si>
   <si>
     <t xml:space="preserve">13.566632270813</t>
@@ -1268,16 +1268,16 @@
     <t xml:space="preserve">13.6419506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3124361038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7925844192505</t>
+    <t xml:space="preserve">13.3124351501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7925853729248</t>
   </si>
   <si>
     <t xml:space="preserve">13.9997110366821</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1409320831299</t>
+    <t xml:space="preserve">14.1409311294556</t>
   </si>
   <si>
     <t xml:space="preserve">14.3951292037964</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">14.6869859695435</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9129400253296</t>
+    <t xml:space="preserve">14.9129390716553</t>
   </si>
   <si>
     <t xml:space="preserve">14.8564510345459</t>
@@ -1304,79 +1304,79 @@
     <t xml:space="preserve">15.1106472015381</t>
   </si>
   <si>
-    <t xml:space="preserve">14.969428062439</t>
+    <t xml:space="preserve">14.9694271087646</t>
   </si>
   <si>
     <t xml:space="preserve">14.997673034668</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0353317260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9035234451294</t>
+    <t xml:space="preserve">15.0353307723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.903525352478</t>
   </si>
   <si>
     <t xml:space="preserve">14.8941097259521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7152299880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5928392410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1671371459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2706985473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2424564361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2518711090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4401636123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3930921554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5531406402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6567039489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4213352203369</t>
+    <t xml:space="preserve">14.7152309417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5928382873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1671380996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2706995010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2424545288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2518720626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.44016456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3930902481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5531425476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6567029953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4213342666626</t>
   </si>
   <si>
     <t xml:space="preserve">15.0165014266968</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3460168838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8185272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6668348312378</t>
+    <t xml:space="preserve">15.3460178375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.818528175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6668357849121</t>
   </si>
   <si>
     <t xml:space="preserve">14.3444862365723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6099491119385</t>
+    <t xml:space="preserve">14.6099500656128</t>
   </si>
   <si>
     <t xml:space="preserve">14.7332000732422</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8754119873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9273281097412</t>
+    <t xml:space="preserve">14.875412940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9273290634155</t>
   </si>
   <si>
     <t xml:space="preserve">14.4013710021973</t>
@@ -1394,58 +1394,58 @@
     <t xml:space="preserve">15.4916658401489</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1173992156982</t>
+    <t xml:space="preserve">16.1174011230469</t>
   </si>
   <si>
     <t xml:space="preserve">16.4587097167969</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1553249359131</t>
+    <t xml:space="preserve">16.1553230285645</t>
   </si>
   <si>
     <t xml:space="preserve">16.1648044586182</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2027263641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2122077941895</t>
+    <t xml:space="preserve">16.2027282714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2122097015381</t>
   </si>
   <si>
     <t xml:space="preserve">16.3259792327881</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1079196929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.069995880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.525074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7241706848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6672859191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5724811553955</t>
+    <t xml:space="preserve">16.1079177856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0699996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5250759124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7241744995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6672878265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5724792480469</t>
   </si>
   <si>
     <t xml:space="preserve">16.3070182800293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596092224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6767692565918</t>
+    <t xml:space="preserve">16.2596130371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6767711639404</t>
   </si>
   <si>
     <t xml:space="preserve">16.8379421234131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.885347366333</t>
+    <t xml:space="preserve">16.8853454589844</t>
   </si>
   <si>
     <t xml:space="preserve">17.0465202331543</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">16.771577835083</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3733863830566</t>
+    <t xml:space="preserve">16.3733825683594</t>
   </si>
   <si>
     <t xml:space="preserve">16.4492282867432</t>
@@ -1466,31 +1466,31 @@
     <t xml:space="preserve">16.2216892242432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4018249511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5535182952881</t>
+    <t xml:space="preserve">16.4018230438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5535163879395</t>
   </si>
   <si>
     <t xml:space="preserve">16.3639030456543</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5155963897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1034069061279</t>
+    <t xml:space="preserve">16.5155944824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1034088134766</t>
   </si>
   <si>
     <t xml:space="preserve">17.5395240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9471988677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4447154998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0799312591553</t>
+    <t xml:space="preserve">17.9472007751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4447135925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0799331665039</t>
   </si>
   <si>
     <t xml:space="preserve">18.1652584075928</t>
@@ -1502,10 +1502,10 @@
     <t xml:space="preserve">18.1368160247803</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4117603302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2505836486816</t>
+    <t xml:space="preserve">18.4117584228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2505874633789</t>
   </si>
   <si>
     <t xml:space="preserve">18.0704498291016</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">17.7575817108154</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2979907989502</t>
+    <t xml:space="preserve">18.2979869842529</t>
   </si>
   <si>
     <t xml:space="preserve">18.3738346099854</t>
@@ -1532,22 +1532,22 @@
     <t xml:space="preserve">18.2031841278076</t>
   </si>
   <si>
-    <t xml:space="preserve">18.032527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1083736419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2126617431641</t>
+    <t xml:space="preserve">18.0325260162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1083755493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2126579284668</t>
   </si>
   <si>
     <t xml:space="preserve">18.0609683990479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9377174377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0040836334229</t>
+    <t xml:space="preserve">17.9377193450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0040855407715</t>
   </si>
   <si>
     <t xml:space="preserve">17.577449798584</t>
@@ -1559,10 +1559,10 @@
     <t xml:space="preserve">17.8334293365479</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0135669708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7435894012451</t>
+    <t xml:space="preserve">18.0135650634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7435874938965</t>
   </si>
   <si>
     <t xml:space="preserve">19.3408813476562</t>
@@ -1571,58 +1571,58 @@
     <t xml:space="preserve">19.41672706604</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3788051605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.18918800354</t>
+    <t xml:space="preserve">19.3788032531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1891860961914</t>
   </si>
   <si>
     <t xml:space="preserve">19.0564556121826</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7246265411377</t>
+    <t xml:space="preserve">18.7246246337891</t>
   </si>
   <si>
     <t xml:space="preserve">18.4496822357178</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5255298614502</t>
+    <t xml:space="preserve">18.5255279541016</t>
   </si>
   <si>
     <t xml:space="preserve">18.772029876709</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9616451263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6867027282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.146297454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5065670013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0420093536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3025054931641</t>
+    <t xml:space="preserve">18.96164894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6867046356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1462955474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5065689086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0420074462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3025016784668</t>
   </si>
   <si>
     <t xml:space="preserve">16.5629997253418</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4537420272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5864753723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6718015670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0081424713135</t>
+    <t xml:space="preserve">15.453742980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5864763259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6718044281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0081443786621</t>
   </si>
   <si>
     <t xml:space="preserve">15.4253005981445</t>
@@ -1631,16 +1631,16 @@
     <t xml:space="preserve">15.4632225036621</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8045349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7286853790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9512596130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0745096206665</t>
+    <t xml:space="preserve">15.8045320510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7286863327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9512586593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0745086669922</t>
   </si>
   <si>
     <t xml:space="preserve">14.9986629486084</t>
@@ -1652,34 +1652,34 @@
     <t xml:space="preserve">15.0176248550415</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8469686508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6573543548584</t>
+    <t xml:space="preserve">14.8469696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6573534011841</t>
   </si>
   <si>
     <t xml:space="preserve">14.704758644104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6763143539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6478729248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9322986602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0555477142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7900848388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8135604858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.728232383728</t>
+    <t xml:space="preserve">14.6763153076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6478719711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.932297706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0555486679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7900857925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8135595321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7282333374023</t>
   </si>
   <si>
     <t xml:space="preserve">13.1309423446655</t>
@@ -1688,34 +1688,34 @@
     <t xml:space="preserve">13.0835371017456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3869218826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2636709213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3964033126831</t>
+    <t xml:space="preserve">13.386923789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3964042663574</t>
   </si>
   <si>
     <t xml:space="preserve">13.6523857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2257490158081</t>
+    <t xml:space="preserve">13.4912128448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2257480621338</t>
   </si>
   <si>
     <t xml:space="preserve">13.8704452514648</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0126581192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4961795806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2212352752686</t>
+    <t xml:space="preserve">14.012656211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4961786270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2212362289429</t>
   </si>
   <si>
     <t xml:space="preserve">14.1643495559692</t>
@@ -1727,10 +1727,10 @@
     <t xml:space="preserve">14.3350057601929</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7945985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7377138137817</t>
+    <t xml:space="preserve">13.7945995330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7377128601074</t>
   </si>
   <si>
     <t xml:space="preserve">13.5955009460449</t>
@@ -1742,31 +1742,31 @@
     <t xml:space="preserve">13.898886680603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9462919235229</t>
+    <t xml:space="preserve">13.9462928771973</t>
   </si>
   <si>
     <t xml:space="preserve">14.4203329086304</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7756376266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7232656478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3205575942993</t>
+    <t xml:space="preserve">13.7756357192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7232666015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.320556640625</t>
   </si>
   <si>
     <t xml:space="preserve">13.1878261566162</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7471952438354</t>
+    <t xml:space="preserve">13.7471942901611</t>
   </si>
   <si>
     <t xml:space="preserve">14.0695428848267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8374891281128</t>
+    <t xml:space="preserve">14.8374872207642</t>
   </si>
   <si>
     <t xml:space="preserve">15.2546453475952</t>
@@ -1775,43 +1775,43 @@
     <t xml:space="preserve">14.8848934173584</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0839910507202</t>
+    <t xml:space="preserve">15.0839900970459</t>
   </si>
   <si>
     <t xml:space="preserve">15.1787996292114</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1503562927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3115301132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3589353561401</t>
+    <t xml:space="preserve">15.1503553390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3115310668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3589363098145</t>
   </si>
   <si>
     <t xml:space="preserve">15.2925682067871</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1408758163452</t>
+    <t xml:space="preserve">15.1408748626709</t>
   </si>
   <si>
     <t xml:space="preserve">15.0271062850952</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9228172302246</t>
+    <t xml:space="preserve">14.9228162765503</t>
   </si>
   <si>
     <t xml:space="preserve">14.8280086517334</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8659334182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9417781829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6149158477783</t>
+    <t xml:space="preserve">14.8659324645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9417791366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6149168014526</t>
   </si>
   <si>
     <t xml:space="preserve">15.7097234725952</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">15.0650291442871</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2167205810547</t>
+    <t xml:space="preserve">15.216721534729</t>
   </si>
   <si>
     <t xml:space="preserve">15.5485496520996</t>
@@ -1829,16 +1829,16 @@
     <t xml:space="preserve">15.4347810745239</t>
   </si>
   <si>
-    <t xml:space="preserve">15.396858215332</t>
+    <t xml:space="preserve">15.3968572616577</t>
   </si>
   <si>
     <t xml:space="preserve">14.7806034088135</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9038562774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2262020111084</t>
+    <t xml:space="preserve">14.9038553237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.226203918457</t>
   </si>
   <si>
     <t xml:space="preserve">15.1977615356445</t>
@@ -1850,13 +1850,13 @@
     <t xml:space="preserve">15.3684158325195</t>
   </si>
   <si>
-    <t xml:space="preserve">15.510627746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7381658554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.430269241333</t>
+    <t xml:space="preserve">15.5106296539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7381677627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4302673339844</t>
   </si>
   <si>
     <t xml:space="preserve">15.9657077789307</t>
@@ -1868,25 +1868,25 @@
     <t xml:space="preserve">15.785572052002</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6862506866455</t>
+    <t xml:space="preserve">16.6862487792969</t>
   </si>
   <si>
     <t xml:space="preserve">16.8474235534668</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4966335296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.193244934082</t>
+    <t xml:space="preserve">16.4966354370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1932487487793</t>
   </si>
   <si>
     <t xml:space="preserve">16.2311687469482</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7526149749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4207859039307</t>
+    <t xml:space="preserve">16.7526168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4207878112793</t>
   </si>
   <si>
     <t xml:space="preserve">16.8095016479492</t>
@@ -1898,13 +1898,13 @@
     <t xml:space="preserve">16.8948287963867</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8663883209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.250129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8993425369263</t>
+    <t xml:space="preserve">16.8663864135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2501316070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8993444442749</t>
   </si>
   <si>
     <t xml:space="preserve">15.8898620605469</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">15.9277820587158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.851936340332</t>
+    <t xml:space="preserve">15.8519372940063</t>
   </si>
   <si>
     <t xml:space="preserve">16.3544216156006</t>
@@ -1925,10 +1925,10 @@
     <t xml:space="preserve">15.9183034896851</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5016021728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6627750396729</t>
+    <t xml:space="preserve">17.5016002655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6627731323242</t>
   </si>
   <si>
     <t xml:space="preserve">18.089412689209</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">17.8239498138428</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6677436828613</t>
+    <t xml:space="preserve">18.6677417755127</t>
   </si>
   <si>
     <t xml:space="preserve">18.5743808746338</t>
@@ -6189,6 +6189,9 @@
   </si>
   <si>
     <t xml:space="preserve">15.335000038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9899997711182</t>
   </si>
 </sst>
 </file>
@@ -71475,7 +71478,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.693587963</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>1155328</v>
@@ -71496,6 +71499,32 @@
         <v>2058</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6930671296</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>1506172</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>15.3649997711182</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>14.9750003814697</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>15.2700004577637</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>14.9899997711182</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>2059</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2060" uniqueCount="2060">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="2061">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.335205078125</t>
+    <t xml:space="preserve">7.33520460128784</t>
   </si>
   <si>
     <t xml:space="preserve">AMP.MI</t>
@@ -47,67 +47,67 @@
     <t xml:space="preserve">7.39109230041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31191825866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36780548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15357065200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96262264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21877336502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27931785583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16288614273071</t>
+    <t xml:space="preserve">7.31191921234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36780595779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15357160568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96262311935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21877288818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2793173789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16288566589355</t>
   </si>
   <si>
     <t xml:space="preserve">7.0324821472168</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08836984634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19548654556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98590993881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13494205474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34451961517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23740291595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35383367538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1489143371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18151473999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40972089767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28397464752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13959932327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05111122131348</t>
+    <t xml:space="preserve">7.08836936950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19548749923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9859094619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13494157791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34451913833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23740243911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35383415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14891386032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18151521682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40972185134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28397560119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13960027694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05111169815063</t>
   </si>
   <si>
     <t xml:space="preserve">6.84619140625</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">6.51086759567261</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45497989654541</t>
+    <t xml:space="preserve">6.45498037338257</t>
   </si>
   <si>
     <t xml:space="preserve">6.5900411605835</t>
@@ -131,67 +131,67 @@
     <t xml:space="preserve">6.42237949371338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61798524856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88344955444336</t>
+    <t xml:space="preserve">6.61798429489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88344860076904</t>
   </si>
   <si>
     <t xml:space="preserve">6.71112966537476</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83687734603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70181608200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62729978561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99522399902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89276313781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80427551269531</t>
+    <t xml:space="preserve">6.83687686920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70181560516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6272988319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99522495269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8927640914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80427598953247</t>
   </si>
   <si>
     <t xml:space="preserve">6.79961824417114</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84153366088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65989971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63195610046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79496145248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78564596176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86016321182251</t>
+    <t xml:space="preserve">6.84153318405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6599006652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63195657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79496097564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78564643859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86016273498535</t>
   </si>
   <si>
     <t xml:space="preserve">7.00919580459595</t>
   </si>
   <si>
-    <t xml:space="preserve">7.111656665802</t>
+    <t xml:space="preserve">7.11165571212769</t>
   </si>
   <si>
     <t xml:space="preserve">7.08371210098267</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20945835113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10699844360352</t>
+    <t xml:space="preserve">7.20945882797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10699892044067</t>
   </si>
   <si>
     <t xml:space="preserve">7.04179668426514</t>
@@ -200,22 +200,22 @@
     <t xml:space="preserve">7.24205923080444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09768342971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17220020294189</t>
+    <t xml:space="preserve">7.09768390655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17219972610474</t>
   </si>
   <si>
     <t xml:space="preserve">6.93467998504639</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91604995727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00453901290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27000284194946</t>
+    <t xml:space="preserve">6.91604948043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00453805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27000331878662</t>
   </si>
   <si>
     <t xml:space="preserve">7.32589101791382</t>
@@ -224,187 +224,187 @@
     <t xml:space="preserve">7.22808742523193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50286674499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41437911987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48423767089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57738351821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55409574508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7310733795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60066986083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64258527755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7031307220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73573064804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88476181030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88942241668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87078952789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78695821762085</t>
+    <t xml:space="preserve">7.50286722183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41437864303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4842381477356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57738304138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55409717559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73107290267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60066938400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64258480072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70312881469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73572969436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88476276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88942050933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87079191207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78695964813232</t>
   </si>
   <si>
     <t xml:space="preserve">7.94530725479126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88010549545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08968257904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01760387420654</t>
+    <t xml:space="preserve">7.8801064491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08968544006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01760482788086</t>
   </si>
   <si>
     <t xml:space="preserve">8.09717178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10653400421143</t>
+    <t xml:space="preserve">8.10653114318848</t>
   </si>
   <si>
     <t xml:space="preserve">8.05036735534668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17205810546875</t>
+    <t xml:space="preserve">8.17205905914307</t>
   </si>
   <si>
     <t xml:space="preserve">8.21418285369873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23758602142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22354507446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15801811218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07845020294189</t>
+    <t xml:space="preserve">8.23758697509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22354316711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15801620483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07844924926758</t>
   </si>
   <si>
     <t xml:space="preserve">8.0831298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14397621154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01292514801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91463422775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82102537155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64316940307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62912607192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65253019332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55891990661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63848924636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98952341079712</t>
+    <t xml:space="preserve">8.14397716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01292324066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91463375091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82102489471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64316892623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62912797927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65252923965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55892038345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63848829269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98952054977417</t>
   </si>
   <si>
     <t xml:space="preserve">7.94739723205566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05972766876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67593145370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71337461471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72273778915405</t>
+    <t xml:space="preserve">8.05972862243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67593193054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71337509155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72273635864258</t>
   </si>
   <si>
     <t xml:space="preserve">7.87251043319702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92867708206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89123249053955</t>
+    <t xml:space="preserve">7.92867565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89123153686523</t>
   </si>
   <si>
     <t xml:space="preserve">7.81166458129883</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71805477142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88186931610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96143913269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91931295394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90995311737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0550479888916</t>
+    <t xml:space="preserve">7.7180552482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88187170028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96143960952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91931581497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90995454788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05504703521729</t>
   </si>
   <si>
     <t xml:space="preserve">8.18141937255859</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16737747192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19546222686768</t>
+    <t xml:space="preserve">8.16737937927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19546127319336</t>
   </si>
   <si>
     <t xml:space="preserve">8.19078063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30779075622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36395835876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3499174118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33119297027588</t>
+    <t xml:space="preserve">8.30779266357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36395740509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34991645812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3311939239502</t>
   </si>
   <si>
     <t xml:space="preserve">8.29374980926514</t>
@@ -413,34 +413,34 @@
     <t xml:space="preserve">8.15333652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28907012939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36863708496094</t>
+    <t xml:space="preserve">8.28906917572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36863803863525</t>
   </si>
   <si>
     <t xml:space="preserve">8.50905132293701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60733985900879</t>
+    <t xml:space="preserve">8.60734081268311</t>
   </si>
   <si>
     <t xml:space="preserve">8.51373195648193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63542366027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75711345672607</t>
+    <t xml:space="preserve">8.63542461395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75711441040039</t>
   </si>
   <si>
     <t xml:space="preserve">8.65414524078369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78519535064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8085994720459</t>
+    <t xml:space="preserve">8.78519821166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80860042572021</t>
   </si>
   <si>
     <t xml:space="preserve">8.92092990875244</t>
@@ -449,22 +449,22 @@
     <t xml:space="preserve">8.84604358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81796169281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74775505065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75243473052979</t>
+    <t xml:space="preserve">8.81796073913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74775409698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75243377685547</t>
   </si>
   <si>
     <t xml:space="preserve">8.82264041900635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7337121963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77115440368652</t>
+    <t xml:space="preserve">8.73371315002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77115631103516</t>
   </si>
   <si>
     <t xml:space="preserve">8.76179504394531</t>
@@ -473,19 +473,19 @@
     <t xml:space="preserve">8.65882587432861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59329986572266</t>
+    <t xml:space="preserve">8.59329891204834</t>
   </si>
   <si>
     <t xml:space="preserve">8.57457637786865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56053733825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4856481552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54181575775146</t>
+    <t xml:space="preserve">8.56053638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48564910888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54181480407715</t>
   </si>
   <si>
     <t xml:space="preserve">8.53245258331299</t>
@@ -494,19 +494,19 @@
     <t xml:space="preserve">8.66818523406982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49968910217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61670017242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49500846862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55585765838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61202144622803</t>
+    <t xml:space="preserve">8.49969005584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61670112609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49500942230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5558557510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61202239990234</t>
   </si>
   <si>
     <t xml:space="preserve">8.46692752838135</t>
@@ -515,40 +515,40 @@
     <t xml:space="preserve">8.52777290344238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56521606445312</t>
+    <t xml:space="preserve">8.56521797180176</t>
   </si>
   <si>
     <t xml:space="preserve">8.69158840179443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08006572723389</t>
+    <t xml:space="preserve">9.08006477355957</t>
   </si>
   <si>
     <t xml:space="preserve">9.24856185913086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07070350646973</t>
+    <t xml:space="preserve">9.07070541381836</t>
   </si>
   <si>
     <t xml:space="preserve">9.01453876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89284896850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93965244293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81328201293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50437164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42480182647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40140151977539</t>
+    <t xml:space="preserve">8.89284801483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93965148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81328010559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50437068939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42480278015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40140056610107</t>
   </si>
   <si>
     <t xml:space="preserve">8.39671993255615</t>
@@ -557,34 +557,34 @@
     <t xml:space="preserve">8.58393955230713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34523391723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46224594116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3826789855957</t>
+    <t xml:space="preserve">8.34523582458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46224689483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38267803192139</t>
   </si>
   <si>
     <t xml:space="preserve">8.47160720825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98645687103271</t>
+    <t xml:space="preserve">8.9864559173584</t>
   </si>
   <si>
     <t xml:space="preserve">9.09878826141357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06134414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51841354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16269779205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31247329711914</t>
+    <t xml:space="preserve">9.0613431930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51841259002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16269874572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31247138977051</t>
   </si>
   <si>
     <t xml:space="preserve">7.44190883636475</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">7.98484086990356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95675849914551</t>
+    <t xml:space="preserve">7.95675897598267</t>
   </si>
   <si>
     <t xml:space="preserve">8.38736057281494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41075992584229</t>
+    <t xml:space="preserve">8.41076183319092</t>
   </si>
   <si>
     <t xml:space="preserve">8.44820404052734</t>
@@ -608,40 +608,40 @@
     <t xml:space="preserve">8.48096942901611</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37331676483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23290634155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18610095977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37799835205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57925701141357</t>
+    <t xml:space="preserve">8.37331867218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2329044342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18610000610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3779993057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57925891876221</t>
   </si>
   <si>
     <t xml:space="preserve">8.64946460723877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72435188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67286682128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74307250976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71031093597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15495109558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96773529052734</t>
+    <t xml:space="preserve">8.72435092926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67286777496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74307346343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7103099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15495300292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96773433685303</t>
   </si>
   <si>
     <t xml:space="preserve">9.14091205596924</t>
@@ -653,28 +653,28 @@
     <t xml:space="preserve">9.33749008178711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4076976776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37961578369141</t>
+    <t xml:space="preserve">9.40769577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37961483001709</t>
   </si>
   <si>
     <t xml:space="preserve">9.29536628723145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36089038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44514179229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48258495330811</t>
+    <t xml:space="preserve">9.3608922958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44514083862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48258399963379</t>
   </si>
   <si>
     <t xml:space="preserve">9.43578052520752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35621166229248</t>
+    <t xml:space="preserve">9.35621070861816</t>
   </si>
   <si>
     <t xml:space="preserve">9.11282825469971</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">9.15963363647461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4638614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81021499633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95999050140381</t>
+    <t xml:space="preserve">9.46386432647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81021404266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95998954772949</t>
   </si>
   <si>
     <t xml:space="preserve">9.82893657684326</t>
@@ -701,22 +701,22 @@
     <t xml:space="preserve">9.91318416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64171886444092</t>
+    <t xml:space="preserve">9.64171981811523</t>
   </si>
   <si>
     <t xml:space="preserve">9.70724582672119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71660709381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66043949127197</t>
+    <t xml:space="preserve">9.71660614013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66044139862061</t>
   </si>
   <si>
     <t xml:space="preserve">9.79149341583252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0255146026611</t>
+    <t xml:space="preserve">10.0255155563354</t>
   </si>
   <si>
     <t xml:space="preserve">10.0067939758301</t>
@@ -725,67 +725,67 @@
     <t xml:space="preserve">10.1846504211426</t>
   </si>
   <si>
-    <t xml:space="preserve">10.240816116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2595386505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4280338287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4748373031616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3625078201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3344259262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.577808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.512282371521</t>
+    <t xml:space="preserve">10.2408151626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2595367431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4280347824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4748382568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3625068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3344249725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5778093338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5122814178467</t>
   </si>
   <si>
     <t xml:space="preserve">10.5029211044312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8118314743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8867177963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7182207107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6526947021484</t>
+    <t xml:space="preserve">10.8118305206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8867158889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7182216644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6526956558228</t>
   </si>
   <si>
     <t xml:space="preserve">10.6433343887329</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6246137619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7088603973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8960790634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8399143218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9335231781006</t>
+    <t xml:space="preserve">10.6246118545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7088594436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8960800170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8399124145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.933521270752</t>
   </si>
   <si>
     <t xml:space="preserve">10.9990482330322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1301021575928</t>
+    <t xml:space="preserve">11.1301002502441</t>
   </si>
   <si>
     <t xml:space="preserve">11.0926580429077</t>
@@ -794,82 +794,82 @@
     <t xml:space="preserve">11.2517929077148</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9616050720215</t>
+    <t xml:space="preserve">10.9616041183472</t>
   </si>
   <si>
     <t xml:space="preserve">11.2049884796143</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1675453186035</t>
+    <t xml:space="preserve">11.1675443649292</t>
   </si>
   <si>
     <t xml:space="preserve">11.1488227844238</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862659454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2798757553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4296503067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.410927772522</t>
+    <t xml:space="preserve">11.1862678527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2798738479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4296493530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4109287261963</t>
   </si>
   <si>
     <t xml:space="preserve">11.4577322006226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5801248550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8249092102051</t>
+    <t xml:space="preserve">11.5801239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8249073028564</t>
   </si>
   <si>
     <t xml:space="preserve">11.8625659942627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9472970962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9190540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9284687042236</t>
+    <t xml:space="preserve">11.9472990036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9190530776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9284677505493</t>
   </si>
   <si>
     <t xml:space="preserve">11.9378833770752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9661273956299</t>
+    <t xml:space="preserve">11.9661283493042</t>
   </si>
   <si>
     <t xml:space="preserve">12.0602750778198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0979347229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0226173400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2109107971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1826658248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2391548156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9096384048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1450071334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4859762191772</t>
+    <t xml:space="preserve">12.0979337692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0226154327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2109117507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1826648712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2391557693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9096393585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1450080871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4859752655029</t>
   </si>
   <si>
     <t xml:space="preserve">11.2976818084717</t>
@@ -878,19 +878,19 @@
     <t xml:space="preserve">11.6930999755859</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7307596206665</t>
+    <t xml:space="preserve">11.7307605743408</t>
   </si>
   <si>
     <t xml:space="preserve">11.7684183120728</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7590026855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.627197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5707082748413</t>
+    <t xml:space="preserve">11.7590036392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6271963119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5707092285156</t>
   </si>
   <si>
     <t xml:space="preserve">11.5236358642578</t>
@@ -899,37 +899,37 @@
     <t xml:space="preserve">11.4671478271484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3729991912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0811443328857</t>
+    <t xml:space="preserve">11.3730001449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0811424255371</t>
   </si>
   <si>
     <t xml:space="preserve">10.8834323883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6951360702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5633325576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.610405921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7422132492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9116764068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9022636413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9493360519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1376304626465</t>
+    <t xml:space="preserve">10.6951389312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5633316040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6104068756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7422122955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.911675453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9022617340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9493370056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1376314163208</t>
   </si>
   <si>
     <t xml:space="preserve">11.3541707992554</t>
@@ -938,10 +938,10 @@
     <t xml:space="preserve">11.3824148178101</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3447551727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4106588363647</t>
+    <t xml:space="preserve">11.3447542190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4106578826904</t>
   </si>
   <si>
     <t xml:space="preserve">11.2694368362427</t>
@@ -950,25 +950,25 @@
     <t xml:space="preserve">11.5048055648804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4294881820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3353404998779</t>
+    <t xml:space="preserve">11.4294862747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3353395462036</t>
   </si>
   <si>
     <t xml:space="preserve">11.2788515090942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2506084442139</t>
+    <t xml:space="preserve">11.2506074905396</t>
   </si>
   <si>
     <t xml:space="preserve">11.1093873977661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0340690612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9210920333862</t>
+    <t xml:space="preserve">11.0340700149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9210910797119</t>
   </si>
   <si>
     <t xml:space="preserve">10.6668949127197</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">10.8363590240479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.78928565979</t>
+    <t xml:space="preserve">10.7892866134644</t>
   </si>
   <si>
     <t xml:space="preserve">11.1941194534302</t>
@@ -986,16 +986,16 @@
     <t xml:space="preserve">11.1658744812012</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0717277526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1282148361206</t>
+    <t xml:space="preserve">11.0717267990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1282157897949</t>
   </si>
   <si>
     <t xml:space="preserve">11.3165111541748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3259258270264</t>
+    <t xml:space="preserve">11.3259248733521</t>
   </si>
   <si>
     <t xml:space="preserve">11.241192817688</t>
@@ -1004,16 +1004,16 @@
     <t xml:space="preserve">11.0623111724854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0905570983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1752910614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4389009475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7213449478149</t>
+    <t xml:space="preserve">11.0905561447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1752901077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4389028549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7213459014893</t>
   </si>
   <si>
     <t xml:space="preserve">11.8154916763306</t>
@@ -1022,40 +1022,40 @@
     <t xml:space="preserve">11.984956741333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.013201713562</t>
+    <t xml:space="preserve">12.0132007598877</t>
   </si>
   <si>
     <t xml:space="preserve">11.9567136764526</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0508613586426</t>
+    <t xml:space="preserve">12.0508604049683</t>
   </si>
   <si>
     <t xml:space="preserve">12.0414457321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0791044235229</t>
+    <t xml:space="preserve">12.0791053771973</t>
   </si>
   <si>
     <t xml:space="preserve">11.9755430221558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8343210220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.220326423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1544227600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1073484420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4839372634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5215969085693</t>
+    <t xml:space="preserve">11.8343200683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2203254699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1544237136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1073474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4839391708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.521595954895</t>
   </si>
   <si>
     <t xml:space="preserve">12.643988609314</t>
@@ -1064,130 +1064,130 @@
     <t xml:space="preserve">12.7852087020874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8134527206421</t>
+    <t xml:space="preserve">12.8134536743164</t>
   </si>
   <si>
     <t xml:space="preserve">12.8322830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8040409088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1920804977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7872486114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8531513214111</t>
+    <t xml:space="preserve">12.8040399551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1920795440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7872495651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8531503677368</t>
   </si>
   <si>
     <t xml:space="preserve">12.0320310592651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1732521057129</t>
+    <t xml:space="preserve">12.1732511520386</t>
   </si>
   <si>
     <t xml:space="preserve">12.2768144607544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9002256393433</t>
+    <t xml:space="preserve">11.9002246856689</t>
   </si>
   <si>
     <t xml:space="preserve">11.448317527771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5612936019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4012441635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6742706298828</t>
+    <t xml:space="preserve">11.5612945556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4012432098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6742696762085</t>
   </si>
   <si>
     <t xml:space="preserve">11.7778329849243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0885200500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0696887969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2014970779419</t>
+    <t xml:space="preserve">12.0885190963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0696897506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2014961242676</t>
   </si>
   <si>
     <t xml:space="preserve">12.1355934143066</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3615465164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3333024978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1638374328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7401733398438</t>
+    <t xml:space="preserve">12.3615455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3333034515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.163836479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7401752471924</t>
   </si>
   <si>
     <t xml:space="preserve">12.1261787414551</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5404253005981</t>
+    <t xml:space="preserve">12.5404262542725</t>
   </si>
   <si>
     <t xml:space="preserve">12.549840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5027675628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6345739364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1335544586182</t>
+    <t xml:space="preserve">12.5027685165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6345748901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1335554122925</t>
   </si>
   <si>
     <t xml:space="preserve">13.1241388320923</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0864810943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9546766281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4254112243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4630699157715</t>
+    <t xml:space="preserve">13.086480140686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9546737670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4254121780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4630708694458</t>
   </si>
   <si>
     <t xml:space="preserve">13.5383882522583</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5572166442871</t>
+    <t xml:space="preserve">13.5572175979614</t>
   </si>
   <si>
     <t xml:space="preserve">13.6042919158936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5101451873779</t>
+    <t xml:space="preserve">13.5101442337036</t>
   </si>
   <si>
     <t xml:space="preserve">13.2559461593628</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4724855422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3030214309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.973503112793</t>
+    <t xml:space="preserve">13.472484588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3030195236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9735040664673</t>
   </si>
   <si>
     <t xml:space="preserve">12.6157426834106</t>
@@ -1196,34 +1196,34 @@
     <t xml:space="preserve">12.4086198806763</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3803749084473</t>
+    <t xml:space="preserve">12.3803758621216</t>
   </si>
   <si>
     <t xml:space="preserve">12.46510887146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5121831893921</t>
+    <t xml:space="preserve">12.5121841430664</t>
   </si>
   <si>
     <t xml:space="preserve">12.822868347168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8793592453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8511123657227</t>
+    <t xml:space="preserve">12.8793573379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.851113319397</t>
   </si>
   <si>
     <t xml:space="preserve">12.5969152450562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2862281799316</t>
+    <t xml:space="preserve">12.286229133606</t>
   </si>
   <si>
     <t xml:space="preserve">12.2579851150513</t>
   </si>
   <si>
-    <t xml:space="preserve">12.728723526001</t>
+    <t xml:space="preserve">12.7287216186523</t>
   </si>
   <si>
     <t xml:space="preserve">13.0394067764282</t>
@@ -1232,16 +1232,16 @@
     <t xml:space="preserve">13.0958957672119</t>
   </si>
   <si>
-    <t xml:space="preserve">13.26535987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4065818786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3312635421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.321849822998</t>
+    <t xml:space="preserve">13.2653608322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4065828323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3312644958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3218488693237</t>
   </si>
   <si>
     <t xml:space="preserve">13.1617984771729</t>
@@ -1256,43 +1256,43 @@
     <t xml:space="preserve">12.8887710571289</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8605260848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.293604850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.566632270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6419506072998</t>
+    <t xml:space="preserve">12.8605279922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2936038970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5666332244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6419496536255</t>
   </si>
   <si>
     <t xml:space="preserve">13.3124351501465</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7925853729248</t>
+    <t xml:space="preserve">13.7925872802734</t>
   </si>
   <si>
     <t xml:space="preserve">13.9997110366821</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1409311294556</t>
+    <t xml:space="preserve">14.1409320831299</t>
   </si>
   <si>
     <t xml:space="preserve">14.3951292037964</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3009815216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5645952224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6022539138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6869859695435</t>
+    <t xml:space="preserve">14.3009824752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5645942687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6022529602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6869869232178</t>
   </si>
   <si>
     <t xml:space="preserve">14.9129390716553</t>
@@ -1301,37 +1301,37 @@
     <t xml:space="preserve">14.8564510345459</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1106472015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9694271087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.997673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0353307723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.903525352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8941097259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7152309417725</t>
+    <t xml:space="preserve">15.1106481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.969428062439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9976720809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0353317260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9035243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8941106796265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7152290344238</t>
   </si>
   <si>
     <t xml:space="preserve">14.5928382873535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1671380996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2706995010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2424545288086</t>
+    <t xml:space="preserve">15.1671371459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2707004547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2424564361572</t>
   </si>
   <si>
     <t xml:space="preserve">15.2518720626831</t>
@@ -1340,10 +1340,10 @@
     <t xml:space="preserve">15.44016456604</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3930902481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5531425476074</t>
+    <t xml:space="preserve">15.3930912017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5531415939331</t>
   </si>
   <si>
     <t xml:space="preserve">15.6567029953003</t>
@@ -1358,25 +1358,25 @@
     <t xml:space="preserve">15.3460178375244</t>
   </si>
   <si>
-    <t xml:space="preserve">14.818528175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6668357849121</t>
+    <t xml:space="preserve">14.8185272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6668338775635</t>
   </si>
   <si>
     <t xml:space="preserve">14.3444862365723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6099500656128</t>
+    <t xml:space="preserve">14.6099491119385</t>
   </si>
   <si>
     <t xml:space="preserve">14.7332000732422</t>
   </si>
   <si>
-    <t xml:space="preserve">14.875412940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9273290634155</t>
+    <t xml:space="preserve">14.8754119873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9273300170898</t>
   </si>
   <si>
     <t xml:space="preserve">14.4013710021973</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">16.4587097167969</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1553230285645</t>
+    <t xml:space="preserve">16.1553249359131</t>
   </si>
   <si>
     <t xml:space="preserve">16.1648044586182</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">16.2027282714844</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2122097015381</t>
+    <t xml:space="preserve">16.2122058868408</t>
   </si>
   <si>
     <t xml:space="preserve">16.3259792327881</t>
@@ -1418,16 +1418,16 @@
     <t xml:space="preserve">16.1079177856445</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0699996948242</t>
+    <t xml:space="preserve">16.069995880127</t>
   </si>
   <si>
     <t xml:space="preserve">16.5250759124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7241744995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6672878265381</t>
+    <t xml:space="preserve">16.7241725921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6672916412354</t>
   </si>
   <si>
     <t xml:space="preserve">16.5724792480469</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">16.3070182800293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596130371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6767711639404</t>
+    <t xml:space="preserve">16.2596111297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6767692565918</t>
   </si>
   <si>
     <t xml:space="preserve">16.8379421234131</t>
@@ -1448,19 +1448,19 @@
     <t xml:space="preserve">16.8853454589844</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0465202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9232711791992</t>
+    <t xml:space="preserve">17.0465221405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9232730865479</t>
   </si>
   <si>
     <t xml:space="preserve">16.771577835083</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3733825683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4492282867432</t>
+    <t xml:space="preserve">16.373384475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4492301940918</t>
   </si>
   <si>
     <t xml:space="preserve">16.2216892242432</t>
@@ -1478,79 +1478,79 @@
     <t xml:space="preserve">16.5155944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1034088134766</t>
+    <t xml:space="preserve">17.1034069061279</t>
   </si>
   <si>
     <t xml:space="preserve">17.5395240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9472007751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4447135925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0799331665039</t>
+    <t xml:space="preserve">17.9471988677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4447154998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0799293518066</t>
   </si>
   <si>
     <t xml:space="preserve">18.1652584075928</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7151470184326</t>
+    <t xml:space="preserve">18.715145111084</t>
   </si>
   <si>
     <t xml:space="preserve">18.1368160247803</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4117584228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2505874633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0704498291016</t>
+    <t xml:space="preserve">18.4117603302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2505855560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0704536437988</t>
   </si>
   <si>
     <t xml:space="preserve">17.8618717193604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.634334564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7860240936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7575817108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2979869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3738346099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2031841278076</t>
+    <t xml:space="preserve">17.6343307495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7860260009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7575836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2979888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.373836517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.203182220459</t>
   </si>
   <si>
     <t xml:space="preserve">18.0325260162354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1083755493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2126579284668</t>
+    <t xml:space="preserve">18.1083736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2126636505127</t>
   </si>
   <si>
     <t xml:space="preserve">18.0609683990479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9377193450928</t>
+    <t xml:space="preserve">17.9377174377441</t>
   </si>
   <si>
     <t xml:space="preserve">18.0040855407715</t>
   </si>
   <si>
-    <t xml:space="preserve">17.577449798584</t>
+    <t xml:space="preserve">17.5774459838867</t>
   </si>
   <si>
     <t xml:space="preserve">18.3927974700928</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">18.0135650634766</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7435874938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3408813476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.41672706604</t>
+    <t xml:space="preserve">18.7435894012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3408794403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4167251586914</t>
   </si>
   <si>
     <t xml:space="preserve">19.3788032531738</t>
@@ -1583,22 +1583,22 @@
     <t xml:space="preserve">18.7246246337891</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4496822357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5255279541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.772029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.96164894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6867046356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1462955474854</t>
+    <t xml:space="preserve">18.4496841430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5255298614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7720317840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9616470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6867008209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.146297454834</t>
   </si>
   <si>
     <t xml:space="preserve">18.5065689086914</t>
@@ -1607,25 +1607,25 @@
     <t xml:space="preserve">18.0420074462891</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3025016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5629997253418</t>
+    <t xml:space="preserve">17.3025054931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5629978179932</t>
   </si>
   <si>
     <t xml:space="preserve">15.453742980957</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5864763259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6718044281006</t>
+    <t xml:space="preserve">15.5864753723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6718015670776</t>
   </si>
   <si>
     <t xml:space="preserve">15.0081443786621</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4253005981445</t>
+    <t xml:space="preserve">15.4252996444702</t>
   </si>
   <si>
     <t xml:space="preserve">15.4632225036621</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">14.9512586593628</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0745086669922</t>
+    <t xml:space="preserve">15.0745096206665</t>
   </si>
   <si>
     <t xml:space="preserve">14.9986629486084</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">14.9797010421753</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0176248550415</t>
+    <t xml:space="preserve">15.0176258087158</t>
   </si>
   <si>
     <t xml:space="preserve">14.8469696044922</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">14.6573534011841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.704758644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6763153076172</t>
+    <t xml:space="preserve">14.7047576904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6763143539429</t>
   </si>
   <si>
     <t xml:space="preserve">14.6478719711304</t>
@@ -1676,58 +1676,58 @@
     <t xml:space="preserve">14.7900857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8135595321655</t>
+    <t xml:space="preserve">13.8135604858398</t>
   </si>
   <si>
     <t xml:space="preserve">13.7282333374023</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1309423446655</t>
+    <t xml:space="preserve">13.1309404373169</t>
   </si>
   <si>
     <t xml:space="preserve">13.0835371017456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.386923789978</t>
+    <t xml:space="preserve">13.3869228363037</t>
   </si>
   <si>
     <t xml:space="preserve">13.263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3964042663574</t>
+    <t xml:space="preserve">13.3964023590088</t>
   </si>
   <si>
     <t xml:space="preserve">13.6523857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4912128448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2257480621338</t>
+    <t xml:space="preserve">13.4912118911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2257490158081</t>
   </si>
   <si>
     <t xml:space="preserve">13.8704452514648</t>
   </si>
   <si>
-    <t xml:space="preserve">14.012656211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4961786270142</t>
+    <t xml:space="preserve">14.0126571655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4961805343628</t>
   </si>
   <si>
     <t xml:space="preserve">14.2212362289429</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1643495559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3065643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3350057601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7945995330811</t>
+    <t xml:space="preserve">14.1643505096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3065624237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3350048065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7945985794067</t>
   </si>
   <si>
     <t xml:space="preserve">13.7377128601074</t>
@@ -1736,22 +1736,22 @@
     <t xml:space="preserve">13.5955009460449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7566766738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.898886680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9462928771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4203329086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7756357192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7232666015625</t>
+    <t xml:space="preserve">13.7566747665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8988876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9462909698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4203338623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7756366729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7232656478882</t>
   </si>
   <si>
     <t xml:space="preserve">13.320556640625</t>
@@ -1763,85 +1763,85 @@
     <t xml:space="preserve">13.7471942901611</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0695428848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8374872207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2546453475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8848934173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0839900970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1787996292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1503553390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3115310668945</t>
+    <t xml:space="preserve">14.069543838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8374891281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2546443939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8848924636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0839910507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1787986755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1503562927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3115291595459</t>
   </si>
   <si>
     <t xml:space="preserve">15.3589363098145</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2925682067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1408748626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0271062850952</t>
+    <t xml:space="preserve">15.2925672531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1408758163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0271053314209</t>
   </si>
   <si>
     <t xml:space="preserve">14.9228162765503</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8280086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8659324645996</t>
+    <t xml:space="preserve">14.8280076980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8659315109253</t>
   </si>
   <si>
     <t xml:space="preserve">14.9417791366577</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6149168014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7097234725952</t>
+    <t xml:space="preserve">15.614914894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7097253799438</t>
   </si>
   <si>
     <t xml:space="preserve">15.0650291442871</t>
   </si>
   <si>
-    <t xml:space="preserve">15.216721534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5485496520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4347810745239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3968572616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7806034088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9038553237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.226203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1977615356445</t>
+    <t xml:space="preserve">15.2167205810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5485506057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4347820281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3968563079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7806043624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9038543701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2262020111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1977605819702</t>
   </si>
   <si>
     <t xml:space="preserve">15.4442625045776</t>
@@ -1850,10 +1850,10 @@
     <t xml:space="preserve">15.3684158325195</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5106296539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7381677627563</t>
+    <t xml:space="preserve">15.510627746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.738166809082</t>
   </si>
   <si>
     <t xml:space="preserve">16.4302673339844</t>
@@ -1865,37 +1865,37 @@
     <t xml:space="preserve">15.2641267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">15.785572052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6862487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8474235534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4966354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1932487487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2311687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7526168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4207878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8095016479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7336540222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8948287963867</t>
+    <t xml:space="preserve">15.7855701446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6862525939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8474216461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4966316223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1932468414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2311725616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7526149749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4207859039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.809497833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7336559295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8948268890381</t>
   </si>
   <si>
     <t xml:space="preserve">16.8663864135742</t>
@@ -1904,40 +1904,40 @@
     <t xml:space="preserve">16.2501316070557</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8993444442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8898620605469</t>
+    <t xml:space="preserve">15.8993434906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8898601531982</t>
   </si>
   <si>
     <t xml:space="preserve">15.9277820587158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8519372940063</t>
+    <t xml:space="preserve">15.8519382476807</t>
   </si>
   <si>
     <t xml:space="preserve">16.3544216156006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.240650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9183034896851</t>
+    <t xml:space="preserve">16.2406520843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9183044433594</t>
   </si>
   <si>
     <t xml:space="preserve">17.5016002655029</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6627731323242</t>
+    <t xml:space="preserve">17.6627750396729</t>
   </si>
   <si>
     <t xml:space="preserve">18.089412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3119812011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2835426330566</t>
+    <t xml:space="preserve">17.3119831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.283540725708</t>
   </si>
   <si>
     <t xml:space="preserve">17.8239498138428</t>
@@ -1946,22 +1946,22 @@
     <t xml:space="preserve">18.6677417755127</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5743808746338</t>
+    <t xml:space="preserve">18.5743846893311</t>
   </si>
   <si>
     <t xml:space="preserve">18.8704280853271</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5962104797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5007133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9277248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9468250274658</t>
+    <t xml:space="preserve">19.5962142944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5007152557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9277286529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9468269348145</t>
   </si>
   <si>
     <t xml:space="preserve">18.9850234985352</t>
@@ -1970,25 +1970,25 @@
     <t xml:space="preserve">18.5934810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">18.708080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9659252166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.032772064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2333202362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.386116027832</t>
+    <t xml:space="preserve">18.7080783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9659271240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0327739715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2333183288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3861179351807</t>
   </si>
   <si>
     <t xml:space="preserve">19.0900726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1951217651367</t>
+    <t xml:space="preserve">19.1951198577881</t>
   </si>
   <si>
     <t xml:space="preserve">19.1187210083008</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">19.9018077850342</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1501026153564</t>
+    <t xml:space="preserve">20.1501007080078</t>
   </si>
   <si>
     <t xml:space="preserve">20.2646980285645</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5893936157227</t>
+    <t xml:space="preserve">20.589391708374</t>
   </si>
   <si>
     <t xml:space="preserve">20.5511951446533</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">19.9591064453125</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8445091247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4816150665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3097171783447</t>
+    <t xml:space="preserve">19.8445072174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.481616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3097190856934</t>
   </si>
   <si>
     <t xml:space="preserve">19.6344108581543</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">19.6726112365723</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0928039550781</t>
+    <t xml:space="preserve">20.0928020477295</t>
   </si>
   <si>
     <t xml:space="preserve">19.9400062561035</t>
@@ -2042,13 +2042,13 @@
     <t xml:space="preserve">19.6535129547119</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5580139160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.729907989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3028984069824</t>
+    <t xml:space="preserve">19.558012008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7299098968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3028964996338</t>
   </si>
   <si>
     <t xml:space="preserve">20.2837982177734</t>
@@ -2057,52 +2057,52 @@
     <t xml:space="preserve">20.2264995574951</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7039890289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6848907470703</t>
+    <t xml:space="preserve">20.7039909362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6848926544189</t>
   </si>
   <si>
     <t xml:space="preserve">20.4174957275391</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0355014801025</t>
+    <t xml:space="preserve">20.0355052947998</t>
   </si>
   <si>
     <t xml:space="preserve">20.1310024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1882991790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2769813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1814823150635</t>
+    <t xml:space="preserve">20.1883010864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2769794464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1814804077148</t>
   </si>
   <si>
     <t xml:space="preserve">20.436595916748</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0164031982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5702934265137</t>
+    <t xml:space="preserve">20.0164051055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5702953338623</t>
   </si>
   <si>
     <t xml:space="preserve">20.9904861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1050815582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1623821258545</t>
+    <t xml:space="preserve">21.1050834655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1623802185059</t>
   </si>
   <si>
     <t xml:space="preserve">21.2578792572021</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0286865234375</t>
+    <t xml:space="preserve">21.0286846160889</t>
   </si>
   <si>
     <t xml:space="preserve">21.2960777282715</t>
@@ -2111,58 +2111,58 @@
     <t xml:space="preserve">21.8499660491943</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4802570343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5566558837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5184555053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0982608795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2510604858398</t>
+    <t xml:space="preserve">22.4802551269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5566539764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5184574127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0982646942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2510585784912</t>
   </si>
   <si>
     <t xml:space="preserve">21.9645652770996</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9454650878906</t>
+    <t xml:space="preserve">21.9454669952393</t>
   </si>
   <si>
     <t xml:space="preserve">22.3083591461182</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5948524475098</t>
+    <t xml:space="preserve">22.594856262207</t>
   </si>
   <si>
     <t xml:space="preserve">22.7476501464844</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8049488067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0600662231445</t>
+    <t xml:space="preserve">22.8049468994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0600643157959</t>
   </si>
   <si>
     <t xml:space="preserve">22.2319602966309</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3533763885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4747943878174</t>
+    <t xml:space="preserve">21.3533782958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.474796295166</t>
   </si>
   <si>
     <t xml:space="preserve">20.455696105957</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1241817474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.780387878418</t>
+    <t xml:space="preserve">21.1241836547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7803897857666</t>
   </si>
   <si>
     <t xml:space="preserve">20.8758869171143</t>
@@ -2174,19 +2174,19 @@
     <t xml:space="preserve">21.7353706359863</t>
   </si>
   <si>
-    <t xml:space="preserve">21.506175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2196788787842</t>
+    <t xml:space="preserve">21.5061740875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2196807861328</t>
   </si>
   <si>
     <t xml:space="preserve">21.3724765777588</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6016750335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.678071975708</t>
+    <t xml:space="preserve">21.6016731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6780700683594</t>
   </si>
   <si>
     <t xml:space="preserve">21.4870758056641</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">21.5825748443604</t>
   </si>
   <si>
-    <t xml:space="preserve">20.646692276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.608491897583</t>
+    <t xml:space="preserve">20.6466903686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6084938049316</t>
   </si>
   <si>
     <t xml:space="preserve">20.4938945770264</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">20.8567867279053</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3792972564697</t>
+    <t xml:space="preserve">20.3792953491211</t>
   </si>
   <si>
     <t xml:space="preserve">20.8949871063232</t>
@@ -2216,25 +2216,25 @@
     <t xml:space="preserve">20.9331874847412</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3219985961914</t>
+    <t xml:space="preserve">20.3219966888428</t>
   </si>
   <si>
     <t xml:space="preserve">20.3410987854004</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8308696746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0218677520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5375537872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6521511077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0150451660156</t>
+    <t xml:space="preserve">21.8308658599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0218639373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5375576019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6521530151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.015043258667</t>
   </si>
   <si>
     <t xml:space="preserve">23.4543361663818</t>
@@ -2243,10 +2243,10 @@
     <t xml:space="preserve">23.7217311859131</t>
   </si>
   <si>
-    <t xml:space="preserve">23.912727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5689334869385</t>
+    <t xml:space="preserve">23.9127292633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5689353942871</t>
   </si>
   <si>
     <t xml:space="preserve">24.084623336792</t>
@@ -2255,10 +2255,10 @@
     <t xml:space="preserve">23.7981300354004</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8745288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9700260162354</t>
+    <t xml:space="preserve">23.8745269775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9700241088867</t>
   </si>
   <si>
     <t xml:space="preserve">24.3711185455322</t>
@@ -2273,31 +2273,31 @@
     <t xml:space="preserve">25.3642978668213</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3329200744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9823055267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.287899017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9250087738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6194152832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9441089630127</t>
+    <t xml:space="preserve">24.3329181671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.982307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2879009246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9250068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0205059051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6194114685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9441070556641</t>
   </si>
   <si>
     <t xml:space="preserve">24.8295097351074</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6385116577148</t>
+    <t xml:space="preserve">24.6385135650635</t>
   </si>
   <si>
     <t xml:space="preserve">24.4475173950195</t>
@@ -2309,43 +2309,43 @@
     <t xml:space="preserve">24.3520183563232</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6576118469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6767120361328</t>
+    <t xml:space="preserve">24.6576156616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6767139434814</t>
   </si>
   <si>
     <t xml:space="preserve">24.4857158660889</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5621147155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5812129974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6958141326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.306999206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3452014923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8486099243164</t>
+    <t xml:space="preserve">24.5621128082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5812149047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6958122253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3070011138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3451995849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8486080169678</t>
   </si>
   <si>
     <t xml:space="preserve">25.0014057159424</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2115020751953</t>
+    <t xml:space="preserve">25.2115039825439</t>
   </si>
   <si>
     <t xml:space="preserve">25.7653903961182</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6125926971436</t>
+    <t xml:space="preserve">25.6125946044922</t>
   </si>
   <si>
     <t xml:space="preserve">25.5552959442139</t>
@@ -2354,13 +2354,13 @@
     <t xml:space="preserve">25.1542015075684</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8226909637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7722091674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5239162445068</t>
+    <t xml:space="preserve">25.8226890563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7722110748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5239143371582</t>
   </si>
   <si>
     <t xml:space="preserve">24.9059066772461</t>
@@ -2369,13 +2369,13 @@
     <t xml:space="preserve">25.6698913574219</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2237815856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2810802459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3956775665283</t>
+    <t xml:space="preserve">26.223783493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2810840606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.395679473877</t>
   </si>
   <si>
     <t xml:space="preserve">27.1405639648438</t>
@@ -2387,22 +2387,22 @@
     <t xml:space="preserve">27.5225563049316</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6944541931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8281497955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1910438537598</t>
+    <t xml:space="preserve">27.6944522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8281517028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1910419464111</t>
   </si>
   <si>
     <t xml:space="preserve">28.783130645752</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2865409851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8854503631592</t>
+    <t xml:space="preserve">28.2865390777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8854522705078</t>
   </si>
   <si>
     <t xml:space="preserve">25.9754867553711</t>
@@ -2414,28 +2414,28 @@
     <t xml:space="preserve">24.6003131866455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6071319580078</t>
+    <t xml:space="preserve">23.6071338653564</t>
   </si>
   <si>
     <t xml:space="preserve">24.4666175842285</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4352359771729</t>
+    <t xml:space="preserve">23.4352340698242</t>
   </si>
   <si>
     <t xml:space="preserve">19.8254089355469</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3479175567627</t>
+    <t xml:space="preserve">19.3479156494141</t>
   </si>
   <si>
     <t xml:space="preserve">15.5852918624878</t>
   </si>
   <si>
-    <t xml:space="preserve">17.323356628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7285385131836</t>
+    <t xml:space="preserve">17.3233604431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7285375595093</t>
   </si>
   <si>
     <t xml:space="preserve">16.1200790405273</t>
@@ -2444,28 +2444,28 @@
     <t xml:space="preserve">16.9031658172607</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5239028930664</t>
+    <t xml:space="preserve">17.523904800415</t>
   </si>
   <si>
     <t xml:space="preserve">17.7435493469238</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1350917816162</t>
+    <t xml:space="preserve">18.1350898742676</t>
   </si>
   <si>
     <t xml:space="preserve">18.8322277069092</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1446437835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.221040725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1159915924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8772449493408</t>
+    <t xml:space="preserve">18.1446399688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2210388183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1159896850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8772468566895</t>
   </si>
   <si>
     <t xml:space="preserve">17.3806571960449</t>
@@ -2483,55 +2483,55 @@
     <t xml:space="preserve">18.7844791412354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4311351776123</t>
+    <t xml:space="preserve">18.4311370849609</t>
   </si>
   <si>
     <t xml:space="preserve">18.4454612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7653770446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9536457061768</t>
+    <t xml:space="preserve">18.7653789520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9536437988281</t>
   </si>
   <si>
     <t xml:space="preserve">20.8663387298584</t>
   </si>
   <si>
-    <t xml:space="preserve">19.271520614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8465538024902</t>
+    <t xml:space="preserve">19.2715187072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8465557098389</t>
   </si>
   <si>
     <t xml:space="preserve">20.0068550109863</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2455978393555</t>
+    <t xml:space="preserve">20.2455997467041</t>
   </si>
   <si>
     <t xml:space="preserve">19.987756729126</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9686546325684</t>
+    <t xml:space="preserve">19.968656539917</t>
   </si>
   <si>
     <t xml:space="preserve">19.7681083679199</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6753425598145</t>
+    <t xml:space="preserve">20.6753406524658</t>
   </si>
   <si>
     <t xml:space="preserve">21.7640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3820247650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3370094299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.792667388916</t>
+    <t xml:space="preserve">21.3820266723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.337007522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7926692962646</t>
   </si>
   <si>
     <t xml:space="preserve">21.0191345214844</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">21.8595161437988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9522895812988</t>
+    <t xml:space="preserve">20.9522857666016</t>
   </si>
   <si>
     <t xml:space="preserve">21.9932155609131</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">21.658971786499</t>
   </si>
   <si>
-    <t xml:space="preserve">23.034143447876</t>
+    <t xml:space="preserve">23.0341453552246</t>
   </si>
   <si>
     <t xml:space="preserve">23.1391925811768</t>
@@ -2564,40 +2564,40 @@
     <t xml:space="preserve">23.5020847320557</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8267803192139</t>
+    <t xml:space="preserve">23.8267784118652</t>
   </si>
   <si>
     <t xml:space="preserve">23.521183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8458766937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.817232131958</t>
+    <t xml:space="preserve">23.8458786010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8172283172607</t>
   </si>
   <si>
     <t xml:space="preserve">23.3588390350342</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6903533935547</t>
+    <t xml:space="preserve">22.6903514862061</t>
   </si>
   <si>
     <t xml:space="preserve">22.6330528259277</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8881683349609</t>
+    <t xml:space="preserve">21.8881664276123</t>
   </si>
   <si>
     <t xml:space="preserve">22.0696144104004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6998996734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.938648223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3015365600586</t>
+    <t xml:space="preserve">22.6999034881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9386463165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3015384674072</t>
   </si>
   <si>
     <t xml:space="preserve">22.6808032989502</t>
@@ -2606,16 +2606,16 @@
     <t xml:space="preserve">22.7094535827637</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1487445831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4638862609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4229545593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4611568450928</t>
+    <t xml:space="preserve">23.1487426757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4638843536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4229564666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4611549377441</t>
   </si>
   <si>
     <t xml:space="preserve">22.6426010131836</t>
@@ -2624,10 +2624,10 @@
     <t xml:space="preserve">22.7381000518799</t>
   </si>
   <si>
-    <t xml:space="preserve">23.272891998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2442398071289</t>
+    <t xml:space="preserve">23.2728900909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2442417144775</t>
   </si>
   <si>
     <t xml:space="preserve">23.5402851104736</t>
@@ -2636,22 +2636,22 @@
     <t xml:space="preserve">23.7408313751221</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8363285064697</t>
+    <t xml:space="preserve">23.8363265991211</t>
   </si>
   <si>
     <t xml:space="preserve">23.7121810913086</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7599315643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1610202789307</t>
+    <t xml:space="preserve">23.7599296569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1610221862793</t>
   </si>
   <si>
     <t xml:space="preserve">24.3233699798584</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7340087890625</t>
+    <t xml:space="preserve">24.7340106964111</t>
   </si>
   <si>
     <t xml:space="preserve">25.2783489227295</t>
@@ -2660,16 +2660,16 @@
     <t xml:space="preserve">25.0682544708252</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0587043762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7531108856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.135103225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5580272674561</t>
+    <t xml:space="preserve">25.0587024688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7531127929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1351013183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5580253601074</t>
   </si>
   <si>
     <t xml:space="preserve">26.5102767944336</t>
@@ -2681,34 +2681,34 @@
     <t xml:space="preserve">28.2292423248291</t>
   </si>
   <si>
-    <t xml:space="preserve">27.503454208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5894050598145</t>
+    <t xml:space="preserve">27.5034561157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5894031524658</t>
   </si>
   <si>
     <t xml:space="preserve">27.1596641540527</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5512065887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0164184570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.035514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3793087005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2265129089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0546169281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2838115692139</t>
+    <t xml:space="preserve">27.5512046813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0164165496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0355129241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3793067932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2265110015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.054615020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2838134765625</t>
   </si>
   <si>
     <t xml:space="preserve">26.5675754547119</t>
@@ -2720,25 +2720,25 @@
     <t xml:space="preserve">26.7108211517334</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5007266998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4529800415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6630725860596</t>
+    <t xml:space="preserve">26.5007247924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4529781341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6630706787109</t>
   </si>
   <si>
     <t xml:space="preserve">26.5389270782471</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2619800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4625282287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5989532470703</t>
+    <t xml:space="preserve">26.2619819641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4625263214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5989551544189</t>
   </si>
   <si>
     <t xml:space="preserve">26.6726226806641</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">27.388858795166</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4461574554443</t>
+    <t xml:space="preserve">27.446159362793</t>
   </si>
   <si>
     <t xml:space="preserve">28.1814937591553</t>
@@ -2759,22 +2759,22 @@
     <t xml:space="preserve">28.3533916473389</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5061855316162</t>
+    <t xml:space="preserve">28.5061874389648</t>
   </si>
   <si>
     <t xml:space="preserve">28.9932270050049</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7926807403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6971817016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.57985496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6562538146973</t>
+    <t xml:space="preserve">28.7926788330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6971836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5798530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6562519073486</t>
   </si>
   <si>
     <t xml:space="preserve">27.4748077392578</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">29.3847694396973</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9673042297363</t>
+    <t xml:space="preserve">29.9673099517822</t>
   </si>
   <si>
     <t xml:space="preserve">29.1746711730957</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">29.4802684783936</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8336124420166</t>
+    <t xml:space="preserve">29.833610534668</t>
   </si>
   <si>
     <t xml:space="preserve">30.0246086120605</t>
@@ -2804,10 +2804,10 @@
     <t xml:space="preserve">29.1651210784912</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3274707794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8049621582031</t>
+    <t xml:space="preserve">29.3274669647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8049602508545</t>
   </si>
   <si>
     <t xml:space="preserve">30.4734477996826</t>
@@ -2816,19 +2816,19 @@
     <t xml:space="preserve">30.9891376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7503929138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5402965545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.922290802002</t>
+    <t xml:space="preserve">30.7503910064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5402984619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9222869873047</t>
   </si>
   <si>
     <t xml:space="preserve">30.7408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9318370819092</t>
+    <t xml:space="preserve">30.9318351745605</t>
   </si>
   <si>
     <t xml:space="preserve">30.7217407226562</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">30.6835460662842</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8172416687012</t>
+    <t xml:space="preserve">30.8172397613525</t>
   </si>
   <si>
     <t xml:space="preserve">30.4829998016357</t>
@@ -2855,22 +2855,22 @@
     <t xml:space="preserve">30.9031887054443</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9918689727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8991012573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6535415649414</t>
+    <t xml:space="preserve">31.9918670654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.899097442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6535377502441</t>
   </si>
   <si>
     <t xml:space="preserve">33.309741973877</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4693565368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3288421630859</t>
+    <t xml:space="preserve">32.4693603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3288383483887</t>
   </si>
   <si>
     <t xml:space="preserve">33.5580368041992</t>
@@ -2879,19 +2879,19 @@
     <t xml:space="preserve">34.1310272216797</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4338874816895</t>
+    <t xml:space="preserve">33.4338912963867</t>
   </si>
   <si>
     <t xml:space="preserve">34.4461708068848</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8158798217773</t>
+    <t xml:space="preserve">33.8158836364746</t>
   </si>
   <si>
     <t xml:space="preserve">33.930477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6603546142578</t>
+    <t xml:space="preserve">32.6603507995605</t>
   </si>
   <si>
     <t xml:space="preserve">32.6699028015137</t>
@@ -2903,79 +2903,79 @@
     <t xml:space="preserve">31.5143775939941</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6098747253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9727687835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7367477416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0587196350098</t>
+    <t xml:space="preserve">31.6098728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9727668762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7367553710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0587120056152</t>
   </si>
   <si>
     <t xml:space="preserve">31.2565307617188</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8840866088867</t>
+    <t xml:space="preserve">30.884090423584</t>
   </si>
   <si>
     <t xml:space="preserve">31.0177879333496</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1323852539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8745403289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0846366882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6194248199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0969123840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3615818023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1542129516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9441204071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4216079711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6958198547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2115135192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7435760498047</t>
+    <t xml:space="preserve">31.1323871612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8745422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0846347808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6194267272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0969161987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3615798950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1542091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9441184997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4216156005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.695821762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2115097045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7435722351074</t>
   </si>
   <si>
     <t xml:space="preserve">32.2783622741699</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5075569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4120559692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0491714477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5334720611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2087821960449</t>
+    <t xml:space="preserve">32.5075607299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4120597839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0491676330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5334777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2087802886963</t>
   </si>
   <si>
     <t xml:space="preserve">32.3165626525879</t>
@@ -2984,25 +2984,25 @@
     <t xml:space="preserve">32.1637649536133</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1064682006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3834075927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6221504211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6508026123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.803596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5839538574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3547630310059</t>
+    <t xml:space="preserve">32.1064643859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3834114074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6221542358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.650806427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8036003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5839576721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3547592163086</t>
   </si>
   <si>
     <t xml:space="preserve">32.0682640075684</t>
@@ -3020,7 +3020,7 @@
     <t xml:space="preserve">31.9250202178955</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0423469543457</t>
+    <t xml:space="preserve">33.0423431396484</t>
   </si>
   <si>
     <t xml:space="preserve">33.7967834472656</t>
@@ -3029,13 +3029,13 @@
     <t xml:space="preserve">34.5989646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4843673706055</t>
+    <t xml:space="preserve">34.4843711853027</t>
   </si>
   <si>
     <t xml:space="preserve">34.942756652832</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8854560852051</t>
+    <t xml:space="preserve">34.8854598999023</t>
   </si>
   <si>
     <t xml:space="preserve">35.000057220459</t>
@@ -3044,13 +3044,13 @@
     <t xml:space="preserve">35.8022422790527</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5539474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.334300994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2551765441895</t>
+    <t xml:space="preserve">35.5539512634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3343048095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2551689147949</t>
   </si>
   <si>
     <t xml:space="preserve">33.9018287658691</t>
@@ -3062,37 +3062,37 @@
     <t xml:space="preserve">33.3192901611328</t>
   </si>
   <si>
-    <t xml:space="preserve">31.781774520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8104209899902</t>
+    <t xml:space="preserve">31.7817707061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8104228973389</t>
   </si>
   <si>
     <t xml:space="preserve">32.4598121643066</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7081069946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9768581390381</t>
+    <t xml:space="preserve">32.7081031799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9768562316895</t>
   </si>
   <si>
     <t xml:space="preserve">29.4898166656494</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6876354217529</t>
+    <t xml:space="preserve">28.6876335144043</t>
   </si>
   <si>
     <t xml:space="preserve">29.0027770996094</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3875007629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6453437805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4761753082275</t>
+    <t xml:space="preserve">30.3874988555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6453456878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4761772155762</t>
   </si>
   <si>
     <t xml:space="preserve">30.5211963653564</t>
@@ -3101,58 +3101,58 @@
     <t xml:space="preserve">30.7312927246094</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1228351593018</t>
+    <t xml:space="preserve">31.1228370666504</t>
   </si>
   <si>
     <t xml:space="preserve">30.5498466491699</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5375671386719</t>
+    <t xml:space="preserve">29.5375652313232</t>
   </si>
   <si>
     <t xml:space="preserve">30.148754119873</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6671714782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4065990447998</t>
+    <t xml:space="preserve">31.6671752929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4065971374512</t>
   </si>
   <si>
     <t xml:space="preserve">30.7694911956787</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6644458770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3111000061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9413909912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.275634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9604892730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5812225341797</t>
+    <t xml:space="preserve">30.6644439697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3111019134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9413890838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2756328582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.960485458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5812282562256</t>
   </si>
   <si>
     <t xml:space="preserve">31.3424816131592</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5007400512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9373016357422</t>
+    <t xml:space="preserve">33.5007362365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9372978210449</t>
   </si>
   <si>
     <t xml:space="preserve">33.8731803894043</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6344337463379</t>
+    <t xml:space="preserve">33.6344375610352</t>
   </si>
   <si>
     <t xml:space="preserve">33.624885559082</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">34.1787796020508</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2169761657715</t>
+    <t xml:space="preserve">34.2169723510742</t>
   </si>
   <si>
     <t xml:space="preserve">34.9905090332031</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">34.8281631469727</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3029251098633</t>
+    <t xml:space="preserve">34.302921295166</t>
   </si>
   <si>
     <t xml:space="preserve">33.1091957092285</t>
@@ -3182,22 +3182,22 @@
     <t xml:space="preserve">33.8063316345215</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2333450317383</t>
+    <t xml:space="preserve">33.233341217041</t>
   </si>
   <si>
     <t xml:space="preserve">34.0928268432617</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5771331787109</t>
+    <t xml:space="preserve">33.5771408081055</t>
   </si>
   <si>
     <t xml:space="preserve">32.2688140869141</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9059219360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8868217468262</t>
+    <t xml:space="preserve">31.9059162139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8868179321289</t>
   </si>
   <si>
     <t xml:space="preserve">32.0873641967773</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">37.4224433898926</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1246032714844</t>
+    <t xml:space="preserve">37.1245994567871</t>
   </si>
   <si>
     <t xml:space="preserve">37.018913269043</t>
@@ -3239,7 +3239,7 @@
     <t xml:space="preserve">37.6818580627441</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2391128540039</t>
+    <t xml:space="preserve">38.2391090393066</t>
   </si>
   <si>
     <t xml:space="preserve">37.7683258056641</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">38.6138153076172</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6426391601562</t>
+    <t xml:space="preserve">38.642635345459</t>
   </si>
   <si>
     <t xml:space="preserve">39.3440093994141</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">40.4969482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0069465637207</t>
+    <t xml:space="preserve">40.006950378418</t>
   </si>
   <si>
     <t xml:space="preserve">39.8051795959473</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">39.6034240722656</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7571487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9973411560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0749893188477</t>
+    <t xml:space="preserve">39.7571449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9973449707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0749931335449</t>
   </si>
   <si>
     <t xml:space="preserve">36.5769538879395</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">39.4304809570312</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7675399780273</t>
+    <t xml:space="preserve">38.7675361633301</t>
   </si>
   <si>
     <t xml:space="preserve">40.0453796386719</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">41.3424339294434</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2271423339844</t>
+    <t xml:space="preserve">41.2271461486816</t>
   </si>
   <si>
     <t xml:space="preserve">41.2367477416992</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">43.0814476013184</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2455673217773</t>
+    <t xml:space="preserve">42.2455711364746</t>
   </si>
   <si>
     <t xml:space="preserve">42.0341949462891</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">42.6683120727539</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9853744506836</t>
+    <t xml:space="preserve">42.9853706359863</t>
   </si>
   <si>
     <t xml:space="preserve">42.3896903991699</t>
@@ -3431,25 +3431,25 @@
     <t xml:space="preserve">41.9765472412109</t>
   </si>
   <si>
-    <t xml:space="preserve">41.534595489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4577293395996</t>
+    <t xml:space="preserve">41.5345916748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4577331542969</t>
   </si>
   <si>
     <t xml:space="preserve">39.7187118530273</t>
   </si>
   <si>
-    <t xml:space="preserve">41.006160736084</t>
+    <t xml:space="preserve">41.0061569213867</t>
   </si>
   <si>
     <t xml:space="preserve">40.0165596008301</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8332214355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0638046264648</t>
+    <t xml:space="preserve">40.8332176208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0638084411621</t>
   </si>
   <si>
     <t xml:space="preserve">43.0718421936035</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">43.2159576416016</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9477272033691</t>
+    <t xml:space="preserve">41.9477233886719</t>
   </si>
   <si>
     <t xml:space="preserve">39.7859687805176</t>
@@ -3488,13 +3488,13 @@
     <t xml:space="preserve">40.10302734375</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0077323913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0653800964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9108734130859</t>
+    <t xml:space="preserve">39.0077362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0653839111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9108695983887</t>
   </si>
   <si>
     <t xml:space="preserve">40.2087097167969</t>
@@ -3509,10 +3509,10 @@
     <t xml:space="preserve">42.7932167053223</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5730209350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.169490814209</t>
+    <t xml:space="preserve">41.5730247497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1694946289062</t>
   </si>
   <si>
     <t xml:space="preserve">42.2263565063477</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">43.0045852661133</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9653663635254</t>
+    <t xml:space="preserve">43.9653625488281</t>
   </si>
   <si>
     <t xml:space="preserve">43.8596801757812</t>
@@ -3557,19 +3557,19 @@
     <t xml:space="preserve">42.2551765441895</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8604698181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8028221130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.679500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6018486022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5449867248535</t>
+    <t xml:space="preserve">42.860466003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8028182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6794967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6018447875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5449829101562</t>
   </si>
   <si>
     <t xml:space="preserve">41.0830230712891</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">41.4192962646484</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1318511962891</t>
+    <t xml:space="preserve">40.1318550109863</t>
   </si>
   <si>
     <t xml:space="preserve">40.1606750488281</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">41.2655715942383</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1798858642578</t>
+    <t xml:space="preserve">40.1798896789551</t>
   </si>
   <si>
     <t xml:space="preserve">40.1414566040039</t>
@@ -3611,10 +3611,10 @@
     <t xml:space="preserve">42.3512573242188</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3704681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5626220703125</t>
+    <t xml:space="preserve">42.3704719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5626258850098</t>
   </si>
   <si>
     <t xml:space="preserve">43.5330200195312</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">43.6579170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">44.416934967041</t>
+    <t xml:space="preserve">44.4169387817383</t>
   </si>
   <si>
     <t xml:space="preserve">45.0702667236328</t>
@@ -3635,10 +3635,10 @@
     <t xml:space="preserve">45.5890884399414</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8108520507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8885040283203</t>
+    <t xml:space="preserve">44.8108558654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8885078430176</t>
   </si>
   <si>
     <t xml:space="preserve">44.0518379211426</t>
@@ -3668,10 +3668,10 @@
     <t xml:space="preserve">37.2014656066895</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7795066833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5208854675293</t>
+    <t xml:space="preserve">35.7795104980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.520881652832</t>
   </si>
   <si>
     <t xml:space="preserve">35.001277923584</t>
@@ -3680,19 +3680,19 @@
     <t xml:space="preserve">35.0397071838379</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4632377624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0581321716309</t>
+    <t xml:space="preserve">34.4632339477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0581359863281</t>
   </si>
   <si>
     <t xml:space="preserve">36.7018585205078</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8644027709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5585250854492</t>
+    <t xml:space="preserve">37.8644065856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.558521270752</t>
   </si>
   <si>
     <t xml:space="preserve">34.8859825134277</t>
@@ -3713,16 +3713,16 @@
     <t xml:space="preserve">33.9636306762695</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3775596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7418632507324</t>
+    <t xml:space="preserve">33.377555847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7418670654297</t>
   </si>
   <si>
     <t xml:space="preserve">34.2710800170898</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2806854248047</t>
+    <t xml:space="preserve">34.280689239502</t>
   </si>
   <si>
     <t xml:space="preserve">34.146183013916</t>
@@ -3740,10 +3740,10 @@
     <t xml:space="preserve">35.2510757446289</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9332313537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9420509338379</t>
+    <t xml:space="preserve">35.933235168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9420547485352</t>
   </si>
   <si>
     <t xml:space="preserve">36.4712715148926</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">36.4520530700684</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1253852844238</t>
+    <t xml:space="preserve">36.1253890991211</t>
   </si>
   <si>
     <t xml:space="preserve">34.7802963256836</t>
@@ -3764,19 +3764,19 @@
     <t xml:space="preserve">35.6449966430664</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7042236328125</t>
+    <t xml:space="preserve">33.7042198181152</t>
   </si>
   <si>
     <t xml:space="preserve">34.4344139099121</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1357841491699</t>
+    <t xml:space="preserve">35.1357879638672</t>
   </si>
   <si>
     <t xml:space="preserve">34.9244117736816</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2695083618164</t>
+    <t xml:space="preserve">36.2695045471191</t>
   </si>
   <si>
     <t xml:space="preserve">36.3175468444824</t>
@@ -3788,7 +3788,7 @@
     <t xml:space="preserve">35.5200958251953</t>
   </si>
   <si>
-    <t xml:space="preserve">35.097354888916</t>
+    <t xml:space="preserve">35.0973510742188</t>
   </si>
   <si>
     <t xml:space="preserve">35.7602958679199</t>
@@ -3800,10 +3800,10 @@
     <t xml:space="preserve">38.5081329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0173416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9500846862793</t>
+    <t xml:space="preserve">39.0173454284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9500885009766</t>
   </si>
   <si>
     <t xml:space="preserve">40.2375373840332</t>
@@ -3812,7 +3812,7 @@
     <t xml:space="preserve">41.2943954467773</t>
   </si>
   <si>
-    <t xml:space="preserve">40.890869140625</t>
+    <t xml:space="preserve">40.8908653259277</t>
   </si>
   <si>
     <t xml:space="preserve">40.6891021728516</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">39.8340072631836</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6330299377441</t>
+    <t xml:space="preserve">38.6330261230469</t>
   </si>
   <si>
     <t xml:space="preserve">39.4208717346191</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">39.219108581543</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6234169006348</t>
+    <t xml:space="preserve">38.623420715332</t>
   </si>
   <si>
     <t xml:space="preserve">37.9797019958496</t>
@@ -3842,13 +3842,13 @@
     <t xml:space="preserve">36.6442108154297</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3367652893066</t>
+    <t xml:space="preserve">36.3367614746094</t>
   </si>
   <si>
     <t xml:space="preserve">35.4528427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2502861022949</t>
+    <t xml:space="preserve">36.2502899169922</t>
   </si>
   <si>
     <t xml:space="preserve">36.7210731506348</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">36.1350021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7218589782715</t>
+    <t xml:space="preserve">35.7218627929688</t>
   </si>
   <si>
     <t xml:space="preserve">35.3183326721191</t>
@@ -3866,7 +3866,7 @@
     <t xml:space="preserve">34.0693168640137</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2726554870605</t>
+    <t xml:space="preserve">32.2726516723633</t>
   </si>
   <si>
     <t xml:space="preserve">32.9836387634277</t>
@@ -6192,6 +6192,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.9899997711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7200002670288</t>
   </si>
 </sst>
 </file>
@@ -71504,7 +71507,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6930671296</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>1506172</v>
@@ -71525,6 +71528,32 @@
         <v>2059</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6940046296</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>4674551</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>15.0749998092651</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>14.0299997329712</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>14.4750003814697</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>14.7200002670288</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>2060</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33520460128784</t>
+    <t xml:space="preserve">7.335205078125</t>
   </si>
   <si>
     <t xml:space="preserve">AMP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39109230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31191921234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36780595779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15357160568237</t>
+    <t xml:space="preserve">7.39109325408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31191873550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36780548095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15357112884521</t>
   </si>
   <si>
     <t xml:space="preserve">6.96262311935425</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21877288818359</t>
+    <t xml:space="preserve">7.21877241134644</t>
   </si>
   <si>
     <t xml:space="preserve">7.2793173789978</t>
@@ -71,145 +71,145 @@
     <t xml:space="preserve">7.0324821472168</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08836936950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19548749923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9859094619751</t>
+    <t xml:space="preserve">7.08836889266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1954870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98590993881226</t>
   </si>
   <si>
     <t xml:space="preserve">7.13494157791138</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34451913833618</t>
+    <t xml:space="preserve">7.34451961517334</t>
   </si>
   <si>
     <t xml:space="preserve">7.23740243911743</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35383415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14891386032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18151521682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40972185134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28397560119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13960027694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05111169815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84619140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51086759567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45498037338257</t>
+    <t xml:space="preserve">7.35383367538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14891338348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18151473999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40972137451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28397512435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13959932327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05111122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84619188308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51086711883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45497989654541</t>
   </si>
   <si>
     <t xml:space="preserve">6.5900411605835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33389186859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29197597503662</t>
+    <t xml:space="preserve">6.33389043807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29197549819946</t>
   </si>
   <si>
     <t xml:space="preserve">6.42237949371338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61798429489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88344860076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71112966537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83687686920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70181560516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6272988319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99522495269775</t>
+    <t xml:space="preserve">6.61798524856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88344955444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71113014221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83687734603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70181608200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62729978561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99522399902344</t>
   </si>
   <si>
     <t xml:space="preserve">6.8927640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80427598953247</t>
+    <t xml:space="preserve">6.80427551269531</t>
   </si>
   <si>
     <t xml:space="preserve">6.79961824417114</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84153318405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6599006652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63195657730103</t>
+    <t xml:space="preserve">6.84153366088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65990018844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63195705413818</t>
   </si>
   <si>
     <t xml:space="preserve">6.79496097564697</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78564643859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86016273498535</t>
+    <t xml:space="preserve">6.78564596176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86016321182251</t>
   </si>
   <si>
     <t xml:space="preserve">7.00919580459595</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11165571212769</t>
+    <t xml:space="preserve">7.111656665802</t>
   </si>
   <si>
     <t xml:space="preserve">7.08371210098267</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20945882797241</t>
+    <t xml:space="preserve">7.2094578742981</t>
   </si>
   <si>
     <t xml:space="preserve">7.10699892044067</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04179668426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24205923080444</t>
+    <t xml:space="preserve">7.04179620742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24206018447876</t>
   </si>
   <si>
     <t xml:space="preserve">7.09768390655518</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17219972610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93467998504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91604948043823</t>
+    <t xml:space="preserve">7.17220020294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93467903137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91605043411255</t>
   </si>
   <si>
     <t xml:space="preserve">7.00453805923462</t>
@@ -221,190 +221,190 @@
     <t xml:space="preserve">7.32589101791382</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22808742523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50286722183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41437864303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4842381477356</t>
+    <t xml:space="preserve">7.22808790206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50286674499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41437911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48423767089844</t>
   </si>
   <si>
     <t xml:space="preserve">7.57738304138184</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55409717559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73107290267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60066938400269</t>
+    <t xml:space="preserve">7.55409574508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73107385635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60066986083984</t>
   </si>
   <si>
     <t xml:space="preserve">7.64258480072021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70312881469727</t>
+    <t xml:space="preserve">7.70313024520874</t>
   </si>
   <si>
     <t xml:space="preserve">7.73572969436646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88476276397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88942050933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87079191207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78695964813232</t>
+    <t xml:space="preserve">7.88476228713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88942193984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8707914352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78696060180664</t>
   </si>
   <si>
     <t xml:space="preserve">7.94530725479126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8801064491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08968544006348</t>
+    <t xml:space="preserve">7.88010549545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08968257904053</t>
   </si>
   <si>
     <t xml:space="preserve">8.01760482788086</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09717178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10653114318848</t>
+    <t xml:space="preserve">8.09717082977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10653209686279</t>
   </si>
   <si>
     <t xml:space="preserve">8.05036735534668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17205905914307</t>
+    <t xml:space="preserve">8.17205715179443</t>
   </si>
   <si>
     <t xml:space="preserve">8.21418285369873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23758697509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22354316711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15801620483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07844924926758</t>
+    <t xml:space="preserve">8.23758602142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22354412078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15801811218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07844829559326</t>
   </si>
   <si>
     <t xml:space="preserve">8.0831298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14397716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01292324066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91463375091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82102489471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64316892623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62912797927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65252923965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55892038345337</t>
+    <t xml:space="preserve">8.14397621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01292419433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91463422775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8210244178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64316940307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62912654876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6525297164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55891990661621</t>
   </si>
   <si>
     <t xml:space="preserve">7.63848829269409</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98952054977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94739723205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05972862243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67593193054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71337509155273</t>
+    <t xml:space="preserve">7.98952102661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94739866256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05972766876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67593097686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71337604522705</t>
   </si>
   <si>
     <t xml:space="preserve">7.72273635864258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87251043319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92867565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89123153686523</t>
+    <t xml:space="preserve">7.87250900268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92867708206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89123106002808</t>
   </si>
   <si>
     <t xml:space="preserve">7.81166458129883</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7180552482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88187170028687</t>
+    <t xml:space="preserve">7.71805572509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88187122344971</t>
   </si>
   <si>
     <t xml:space="preserve">7.96143960952759</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91931581497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90995454788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05504703521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18141937255859</t>
+    <t xml:space="preserve">7.91931438446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90995407104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05504608154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18142032623291</t>
   </si>
   <si>
     <t xml:space="preserve">8.16737937927246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19546127319336</t>
+    <t xml:space="preserve">8.19546031951904</t>
   </si>
   <si>
     <t xml:space="preserve">8.19078063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30779266357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36395740509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34991645812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3311939239502</t>
+    <t xml:space="preserve">8.3077917098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36395645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34991550445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33119297027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.29374980926514</t>
@@ -416,16 +416,16 @@
     <t xml:space="preserve">8.28906917572021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36863803863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50905132293701</t>
+    <t xml:space="preserve">8.36863708496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50905227661133</t>
   </si>
   <si>
     <t xml:space="preserve">8.60734081268311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51373195648193</t>
+    <t xml:space="preserve">8.51373291015625</t>
   </si>
   <si>
     <t xml:space="preserve">8.63542461395264</t>
@@ -437,37 +437,37 @@
     <t xml:space="preserve">8.65414524078369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78519821166992</t>
+    <t xml:space="preserve">8.78519725799561</t>
   </si>
   <si>
     <t xml:space="preserve">8.80860042572021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92092990875244</t>
+    <t xml:space="preserve">8.92093086242676</t>
   </si>
   <si>
     <t xml:space="preserve">8.84604358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81796073913574</t>
+    <t xml:space="preserve">8.81796169281006</t>
   </si>
   <si>
     <t xml:space="preserve">8.74775409698486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75243377685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82264041900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73371315002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77115631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76179504394531</t>
+    <t xml:space="preserve">8.75243473052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82264137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7337121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77115535736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76179599761963</t>
   </si>
   <si>
     <t xml:space="preserve">8.65882587432861</t>
@@ -476,28 +476,28 @@
     <t xml:space="preserve">8.59329891204834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57457637786865</t>
+    <t xml:space="preserve">8.57457733154297</t>
   </si>
   <si>
     <t xml:space="preserve">8.56053638458252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48564910888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54181480407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53245258331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66818523406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49969005584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61670112609863</t>
+    <t xml:space="preserve">8.48564720153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54181575775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5324535369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66818714141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49969100952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61670017242432</t>
   </si>
   <si>
     <t xml:space="preserve">8.49500942230225</t>
@@ -506,28 +506,28 @@
     <t xml:space="preserve">8.5558557510376</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61202239990234</t>
+    <t xml:space="preserve">8.61202144622803</t>
   </si>
   <si>
     <t xml:space="preserve">8.46692752838135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52777290344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56521797180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69158840179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08006477355957</t>
+    <t xml:space="preserve">8.5277738571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56521701812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69158935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0800666809082</t>
   </si>
   <si>
     <t xml:space="preserve">9.24856185913086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07070541381836</t>
+    <t xml:space="preserve">9.07070350646973</t>
   </si>
   <si>
     <t xml:space="preserve">9.01453876495361</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">8.89284801483154</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93965148925781</t>
+    <t xml:space="preserve">8.93965244293213</t>
   </si>
   <si>
     <t xml:space="preserve">8.81328010559082</t>
@@ -545,82 +545,82 @@
     <t xml:space="preserve">8.50437068939209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42480278015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40140056610107</t>
+    <t xml:space="preserve">8.42480373382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40140151977539</t>
   </si>
   <si>
     <t xml:space="preserve">8.39671993255615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58393955230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34523582458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46224689483643</t>
+    <t xml:space="preserve">8.58393859863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34523487091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46224594116211</t>
   </si>
   <si>
     <t xml:space="preserve">8.38267803192139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47160720825195</t>
+    <t xml:space="preserve">8.47160816192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.9864559173584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09878826141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0613431930542</t>
+    <t xml:space="preserve">9.09878730773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06134414672852</t>
   </si>
   <si>
     <t xml:space="preserve">8.51841259002686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16269874572754</t>
+    <t xml:space="preserve">8.16269779205322</t>
   </si>
   <si>
     <t xml:space="preserve">8.31247138977051</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44190883636475</t>
+    <t xml:space="preserve">7.4419093132019</t>
   </si>
   <si>
     <t xml:space="preserve">7.98484086990356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95675897598267</t>
+    <t xml:space="preserve">7.95675849914551</t>
   </si>
   <si>
     <t xml:space="preserve">8.38736057281494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41076183319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44820404052734</t>
+    <t xml:space="preserve">8.41076278686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44820499420166</t>
   </si>
   <si>
     <t xml:space="preserve">8.48096942901611</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37331867218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2329044342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18610000610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3779993057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57925891876221</t>
+    <t xml:space="preserve">8.37331676483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23290538787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1860990524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37799835205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57925796508789</t>
   </si>
   <si>
     <t xml:space="preserve">8.64946460723877</t>
@@ -635,31 +635,31 @@
     <t xml:space="preserve">8.74307346343994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7103099822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15495300292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96773433685303</t>
+    <t xml:space="preserve">8.71031093597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15495204925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96773529052734</t>
   </si>
   <si>
     <t xml:space="preserve">9.14091205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26728343963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33749008178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40769577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37961483001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29536628723145</t>
+    <t xml:space="preserve">9.26728248596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33748912811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40769672393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37961673736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29536533355713</t>
   </si>
   <si>
     <t xml:space="preserve">9.3608922958374</t>
@@ -671,31 +671,31 @@
     <t xml:space="preserve">9.48258399963379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43578052520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35621070861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11282825469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1081485748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15963363647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46386432647705</t>
+    <t xml:space="preserve">9.4357795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35621166229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11283016204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10814762115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15963459014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4638614654541</t>
   </si>
   <si>
     <t xml:space="preserve">9.81021404266357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95998954772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82893657684326</t>
+    <t xml:space="preserve">9.95999145507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82893562316895</t>
   </si>
   <si>
     <t xml:space="preserve">9.91318416595459</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">9.70724582672119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71660614013672</t>
+    <t xml:space="preserve">9.7166051864624</t>
   </si>
   <si>
     <t xml:space="preserve">9.66044139862061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79149341583252</t>
+    <t xml:space="preserve">9.7914924621582</t>
   </si>
   <si>
     <t xml:space="preserve">10.0255155563354</t>
@@ -722,25 +722,25 @@
     <t xml:space="preserve">10.0067939758301</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1846504211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2408151626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2595367431641</t>
+    <t xml:space="preserve">10.1846513748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.240816116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2595386505127</t>
   </si>
   <si>
     <t xml:space="preserve">10.4280347824097</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4748382568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3625068664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3344249725342</t>
+    <t xml:space="preserve">10.4748373031616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3625078201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3344259262085</t>
   </si>
   <si>
     <t xml:space="preserve">10.5778093338013</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">10.8118305206299</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8867158889771</t>
+    <t xml:space="preserve">10.8867177963257</t>
   </si>
   <si>
     <t xml:space="preserve">10.7182216644287</t>
@@ -764,37 +764,37 @@
     <t xml:space="preserve">10.6526956558228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6433343887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6246118545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7088594436646</t>
+    <t xml:space="preserve">10.6433353424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6246137619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7088603973389</t>
   </si>
   <si>
     <t xml:space="preserve">10.8960800170898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8399124145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.933521270752</t>
+    <t xml:space="preserve">10.8399143218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9335222244263</t>
   </si>
   <si>
     <t xml:space="preserve">10.9990482330322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1301002502441</t>
+    <t xml:space="preserve">11.1301012039185</t>
   </si>
   <si>
     <t xml:space="preserve">11.0926580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2517929077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9616041183472</t>
+    <t xml:space="preserve">11.2517919540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9616050720215</t>
   </si>
   <si>
     <t xml:space="preserve">11.2049884796143</t>
@@ -806,67 +806,67 @@
     <t xml:space="preserve">11.1488227844238</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862678527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2798738479614</t>
+    <t xml:space="preserve">11.1862668991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2798757553101</t>
   </si>
   <si>
     <t xml:space="preserve">11.4296493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4109287261963</t>
+    <t xml:space="preserve">11.4109258651733</t>
   </si>
   <si>
     <t xml:space="preserve">11.4577322006226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5801239013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8249073028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8625659942627</t>
+    <t xml:space="preserve">11.5801229476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8249082565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8625640869141</t>
   </si>
   <si>
     <t xml:space="preserve">11.9472990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9190530776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9284677505493</t>
+    <t xml:space="preserve">11.9190540313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9284687042236</t>
   </si>
   <si>
     <t xml:space="preserve">11.9378833770752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9661283493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602750778198</t>
+    <t xml:space="preserve">11.9661264419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0602760314941</t>
   </si>
   <si>
     <t xml:space="preserve">12.0979337692261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0226154327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2109117507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1826648712158</t>
+    <t xml:space="preserve">12.0226144790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2109107971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1826658248901</t>
   </si>
   <si>
     <t xml:space="preserve">12.2391557693481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9096393585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1450080871582</t>
+    <t xml:space="preserve">11.9096403121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1450071334839</t>
   </si>
   <si>
     <t xml:space="preserve">11.4859752655029</t>
@@ -878,40 +878,40 @@
     <t xml:space="preserve">11.6930999755859</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7307605743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7684183120728</t>
+    <t xml:space="preserve">11.7307596206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7684192657471</t>
   </si>
   <si>
     <t xml:space="preserve">11.7590036392212</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6271963119507</t>
+    <t xml:space="preserve">11.627197265625</t>
   </si>
   <si>
     <t xml:space="preserve">11.5707092285156</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5236358642578</t>
+    <t xml:space="preserve">11.5236349105835</t>
   </si>
   <si>
     <t xml:space="preserve">11.4671478271484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3730001449585</t>
+    <t xml:space="preserve">11.3729991912842</t>
   </si>
   <si>
     <t xml:space="preserve">11.0811424255371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834323883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6951389312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5633316040039</t>
+    <t xml:space="preserve">10.8834342956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6951379776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5633325576782</t>
   </si>
   <si>
     <t xml:space="preserve">10.6104068756104</t>
@@ -920,55 +920,55 @@
     <t xml:space="preserve">10.7422122955322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.911675453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9022617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9493370056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1376314163208</t>
+    <t xml:space="preserve">10.9116773605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9022626876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9493350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1376304626465</t>
   </si>
   <si>
     <t xml:space="preserve">11.3541707992554</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3824148178101</t>
+    <t xml:space="preserve">11.3824138641357</t>
   </si>
   <si>
     <t xml:space="preserve">11.3447542190552</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4106578826904</t>
+    <t xml:space="preserve">11.4106588363647</t>
   </si>
   <si>
     <t xml:space="preserve">11.2694368362427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5048055648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4294862747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3353395462036</t>
+    <t xml:space="preserve">11.5048065185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4294881820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3353404998779</t>
   </si>
   <si>
     <t xml:space="preserve">11.2788515090942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2506074905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1093873977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0340700149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9210910797119</t>
+    <t xml:space="preserve">11.2506084442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1093864440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.034068107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9210920333862</t>
   </si>
   <si>
     <t xml:space="preserve">10.6668949127197</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">10.8363590240479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7892866134644</t>
+    <t xml:space="preserve">10.78928565979</t>
   </si>
   <si>
     <t xml:space="preserve">11.1941194534302</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1658744812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0717267990112</t>
+    <t xml:space="preserve">11.1658754348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0717277526855</t>
   </si>
   <si>
     <t xml:space="preserve">11.1282157897949</t>
@@ -995,25 +995,25 @@
     <t xml:space="preserve">11.3165111541748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3259248733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.241192817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0623111724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0905561447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1752901077271</t>
+    <t xml:space="preserve">11.3259258270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2411909103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0623140335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.090558052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1752910614014</t>
   </si>
   <si>
     <t xml:space="preserve">11.4389028549194</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7213459014893</t>
+    <t xml:space="preserve">11.7213449478149</t>
   </si>
   <si>
     <t xml:space="preserve">11.8154916763306</t>
@@ -1025,19 +1025,19 @@
     <t xml:space="preserve">12.0132007598877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9567136764526</t>
+    <t xml:space="preserve">11.9567127227783</t>
   </si>
   <si>
     <t xml:space="preserve">12.0508604049683</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0414457321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0791053771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9755430221558</t>
+    <t xml:space="preserve">12.0414447784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0791063308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9755439758301</t>
   </si>
   <si>
     <t xml:space="preserve">11.8343200683594</t>
@@ -1046,25 +1046,25 @@
     <t xml:space="preserve">12.2203254699707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1544237136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1073474884033</t>
+    <t xml:space="preserve">12.1544227600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1073484420776</t>
   </si>
   <si>
     <t xml:space="preserve">12.4839391708374</t>
   </si>
   <si>
-    <t xml:space="preserve">12.521595954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.643988609314</t>
+    <t xml:space="preserve">12.5215969085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6439876556396</t>
   </si>
   <si>
     <t xml:space="preserve">12.7852087020874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8134536743164</t>
+    <t xml:space="preserve">12.8134546279907</t>
   </si>
   <si>
     <t xml:space="preserve">12.8322830200195</t>
@@ -1073,10 +1073,10 @@
     <t xml:space="preserve">12.8040399551392</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1920795440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7872495651245</t>
+    <t xml:space="preserve">12.1920804977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7872486114502</t>
   </si>
   <si>
     <t xml:space="preserve">11.8531503677368</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">12.0320310592651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1732511520386</t>
+    <t xml:space="preserve">12.1732521057129</t>
   </si>
   <si>
     <t xml:space="preserve">12.2768144607544</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">11.9002246856689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.448317527771</t>
+    <t xml:space="preserve">11.4483156204224</t>
   </si>
   <si>
     <t xml:space="preserve">11.5612945556641</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">11.6742696762085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7778329849243</t>
+    <t xml:space="preserve">11.77783203125</t>
   </si>
   <si>
     <t xml:space="preserve">12.0885190963745</t>
@@ -1121,43 +1121,43 @@
     <t xml:space="preserve">12.1355934143066</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3615455627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3333034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.163836479187</t>
+    <t xml:space="preserve">12.3615465164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3333024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1638374328613</t>
   </si>
   <si>
     <t xml:space="preserve">11.7401752471924</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1261787414551</t>
+    <t xml:space="preserve">12.1261777877808</t>
   </si>
   <si>
     <t xml:space="preserve">12.5404262542725</t>
   </si>
   <si>
-    <t xml:space="preserve">12.549840927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5027685165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6345748901367</t>
+    <t xml:space="preserve">12.5498418807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5027675628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6345729827881</t>
   </si>
   <si>
     <t xml:space="preserve">13.1335554122925</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1241388320923</t>
+    <t xml:space="preserve">13.1241407394409</t>
   </si>
   <si>
     <t xml:space="preserve">13.086480140686</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9546737670898</t>
+    <t xml:space="preserve">12.9546747207642</t>
   </si>
   <si>
     <t xml:space="preserve">13.4254121780396</t>
@@ -1166,19 +1166,19 @@
     <t xml:space="preserve">13.4630708694458</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5383882522583</t>
+    <t xml:space="preserve">13.5383892059326</t>
   </si>
   <si>
     <t xml:space="preserve">13.5572175979614</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6042919158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5101442337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2559461593628</t>
+    <t xml:space="preserve">13.6042928695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5101432800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2559471130371</t>
   </si>
   <si>
     <t xml:space="preserve">13.472484588623</t>
@@ -1190,16 +1190,16 @@
     <t xml:space="preserve">12.9735040664673</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6157426834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4086198806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3803758621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.46510887146</t>
+    <t xml:space="preserve">12.615743637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4086208343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3803768157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4651079177856</t>
   </si>
   <si>
     <t xml:space="preserve">12.5121841430664</t>
@@ -1208,34 +1208,34 @@
     <t xml:space="preserve">12.822868347168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8793573379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.851113319397</t>
+    <t xml:space="preserve">12.8793563842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8511123657227</t>
   </si>
   <si>
     <t xml:space="preserve">12.5969152450562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.286229133606</t>
+    <t xml:space="preserve">12.2862281799316</t>
   </si>
   <si>
     <t xml:space="preserve">12.2579851150513</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7287216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0394067764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0958957672119</t>
+    <t xml:space="preserve">12.728720664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0394058227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0958967208862</t>
   </si>
   <si>
     <t xml:space="preserve">13.2653608322144</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4065828323364</t>
+    <t xml:space="preserve">13.4065818786621</t>
   </si>
   <si>
     <t xml:space="preserve">13.3312644958496</t>
@@ -1250,112 +1250,112 @@
     <t xml:space="preserve">13.3406791687012</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2465324401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8887710571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8605279922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2936038970947</t>
+    <t xml:space="preserve">13.2465314865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8887720108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8605289459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.293604850769</t>
   </si>
   <si>
     <t xml:space="preserve">13.5666332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6419496536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3124351501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7925872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9997110366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1409320831299</t>
+    <t xml:space="preserve">13.6419506072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3124361038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7925863265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9997100830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1409330368042</t>
   </si>
   <si>
     <t xml:space="preserve">14.3951292037964</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3009824752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5645942687988</t>
+    <t xml:space="preserve">14.3009834289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5645933151245</t>
   </si>
   <si>
     <t xml:space="preserve">14.6022529602051</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6869869232178</t>
+    <t xml:space="preserve">14.6869859695435</t>
   </si>
   <si>
     <t xml:space="preserve">14.9129390716553</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8564510345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1106481552124</t>
+    <t xml:space="preserve">14.8564491271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1106491088867</t>
   </si>
   <si>
     <t xml:space="preserve">14.969428062439</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9976720809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0353317260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9035243988037</t>
+    <t xml:space="preserve">14.997673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0353298187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9035263061523</t>
   </si>
   <si>
     <t xml:space="preserve">14.8941106796265</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7152290344238</t>
+    <t xml:space="preserve">14.7152299880981</t>
   </si>
   <si>
     <t xml:space="preserve">14.5928382873535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1671371459961</t>
+    <t xml:space="preserve">15.1671380996704</t>
   </si>
   <si>
     <t xml:space="preserve">15.2707004547119</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2424564361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2518720626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.44016456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3930912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5531415939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6567029953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4213342666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0165014266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3460178375244</t>
+    <t xml:space="preserve">15.2424554824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2518711090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4401636123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3930902481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5531425476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6567039489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4213352203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0165004730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3460187911987</t>
   </si>
   <si>
     <t xml:space="preserve">14.8185272216797</t>
@@ -1364,7 +1364,7 @@
     <t xml:space="preserve">14.6668338775635</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3444862365723</t>
+    <t xml:space="preserve">14.3444852828979</t>
   </si>
   <si>
     <t xml:space="preserve">14.6099491119385</t>
@@ -1379,13 +1379,13 @@
     <t xml:space="preserve">13.9273300170898</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4013710021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6194305419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6289110183716</t>
+    <t xml:space="preserve">14.4013719558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6194295883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6289119720459</t>
   </si>
   <si>
     <t xml:space="preserve">15.1882801055908</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">16.1174011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4587097167969</t>
+    <t xml:space="preserve">16.4587116241455</t>
   </si>
   <si>
     <t xml:space="preserve">16.1553249359131</t>
@@ -1409,28 +1409,28 @@
     <t xml:space="preserve">16.2027282714844</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2122058868408</t>
+    <t xml:space="preserve">16.2122077941895</t>
   </si>
   <si>
     <t xml:space="preserve">16.3259792327881</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1079177856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.069995880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5250759124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7241725921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6672916412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5724792480469</t>
+    <t xml:space="preserve">16.1079196929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0699977874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.525074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7241706848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6672897338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5724773406982</t>
   </si>
   <si>
     <t xml:space="preserve">16.3070182800293</t>
@@ -1439,10 +1439,10 @@
     <t xml:space="preserve">16.2596111297607</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6767692565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8379421234131</t>
+    <t xml:space="preserve">16.6767673492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8379440307617</t>
   </si>
   <si>
     <t xml:space="preserve">16.8853454589844</t>
@@ -1451,10 +1451,10 @@
     <t xml:space="preserve">17.0465221405029</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9232730865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.771577835083</t>
+    <t xml:space="preserve">16.9232711791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7715797424316</t>
   </si>
   <si>
     <t xml:space="preserve">16.373384475708</t>
@@ -1466,13 +1466,13 @@
     <t xml:space="preserve">16.2216892242432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4018230438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5535163879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3639030456543</t>
+    <t xml:space="preserve">16.4018249511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5535182952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3639011383057</t>
   </si>
   <si>
     <t xml:space="preserve">16.5155944824219</t>
@@ -1481,19 +1481,19 @@
     <t xml:space="preserve">17.1034069061279</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5395240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9471988677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4447154998779</t>
+    <t xml:space="preserve">17.5395259857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9472007751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4447135925293</t>
   </si>
   <si>
     <t xml:space="preserve">18.0799293518066</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1652584075928</t>
+    <t xml:space="preserve">18.1652565002441</t>
   </si>
   <si>
     <t xml:space="preserve">18.715145111084</t>
@@ -1502,13 +1502,13 @@
     <t xml:space="preserve">18.1368160247803</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4117603302002</t>
+    <t xml:space="preserve">18.4117584228516</t>
   </si>
   <si>
     <t xml:space="preserve">18.2505855560303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0704536437988</t>
+    <t xml:space="preserve">18.0704517364502</t>
   </si>
   <si>
     <t xml:space="preserve">17.8618717193604</t>
@@ -1520,22 +1520,22 @@
     <t xml:space="preserve">17.7860260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7575836181641</t>
+    <t xml:space="preserve">17.7575817108154</t>
   </si>
   <si>
     <t xml:space="preserve">18.2979888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.373836517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.203182220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0325260162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1083736419678</t>
+    <t xml:space="preserve">18.3738384246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2031841278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.032527923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1083698272705</t>
   </si>
   <si>
     <t xml:space="preserve">18.2126636505127</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">18.0609683990479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9377174377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0040855407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5774459838867</t>
+    <t xml:space="preserve">17.9377155303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0040836334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5774478912354</t>
   </si>
   <si>
     <t xml:space="preserve">18.3927974700928</t>
@@ -1568,13 +1568,13 @@
     <t xml:space="preserve">19.3408794403076</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4167251586914</t>
+    <t xml:space="preserve">19.41672706604</t>
   </si>
   <si>
     <t xml:space="preserve">19.3788032531738</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1891860961914</t>
+    <t xml:space="preserve">19.1891841888428</t>
   </si>
   <si>
     <t xml:space="preserve">19.0564556121826</t>
@@ -1583,43 +1583,43 @@
     <t xml:space="preserve">18.7246246337891</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4496841430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5255298614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7720317840576</t>
+    <t xml:space="preserve">18.449686050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5255279541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.772029876709</t>
   </si>
   <si>
     <t xml:space="preserve">18.9616470336914</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6867008209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.146297454834</t>
+    <t xml:space="preserve">18.6867027282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1462955474854</t>
   </si>
   <si>
     <t xml:space="preserve">18.5065689086914</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0420074462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3025054931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5629978179932</t>
+    <t xml:space="preserve">18.0420093536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3025035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5629959106445</t>
   </si>
   <si>
     <t xml:space="preserve">15.453742980957</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5864753723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6718015670776</t>
+    <t xml:space="preserve">15.5864763259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.671802520752</t>
   </si>
   <si>
     <t xml:space="preserve">15.0081443786621</t>
@@ -1628,19 +1628,19 @@
     <t xml:space="preserve">15.4252996444702</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4632225036621</t>
+    <t xml:space="preserve">15.4632234573364</t>
   </si>
   <si>
     <t xml:space="preserve">15.8045320510864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7286863327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9512586593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0745096206665</t>
+    <t xml:space="preserve">15.7286853790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9512596130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0745105743408</t>
   </si>
   <si>
     <t xml:space="preserve">14.9986629486084</t>
@@ -1649,34 +1649,34 @@
     <t xml:space="preserve">14.9797010421753</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0176258087158</t>
+    <t xml:space="preserve">15.0176248550415</t>
   </si>
   <si>
     <t xml:space="preserve">14.8469696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6573534011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7047576904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6763143539429</t>
+    <t xml:space="preserve">14.6573543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7047567367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6763153076172</t>
   </si>
   <si>
     <t xml:space="preserve">14.6478719711304</t>
   </si>
   <si>
-    <t xml:space="preserve">14.932297706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0555486679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7900857925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8135604858398</t>
+    <t xml:space="preserve">14.9322967529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0555477142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7900848388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8135614395142</t>
   </si>
   <si>
     <t xml:space="preserve">13.7282333374023</t>
@@ -1685,22 +1685,22 @@
     <t xml:space="preserve">13.1309404373169</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0835371017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3869228363037</t>
+    <t xml:space="preserve">13.0835361480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3869218826294</t>
   </si>
   <si>
     <t xml:space="preserve">13.263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3964023590088</t>
+    <t xml:space="preserve">13.3964033126831</t>
   </si>
   <si>
     <t xml:space="preserve">13.6523857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4912118911743</t>
+    <t xml:space="preserve">13.4912128448486</t>
   </si>
   <si>
     <t xml:space="preserve">13.2257490158081</t>
@@ -1709,13 +1709,13 @@
     <t xml:space="preserve">13.8704452514648</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0126571655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4961805343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2212362289429</t>
+    <t xml:space="preserve">14.012656211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4961795806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2212352752686</t>
   </si>
   <si>
     <t xml:space="preserve">14.1643505096436</t>
@@ -1736,7 +1736,7 @@
     <t xml:space="preserve">13.5955009460449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7566747665405</t>
+    <t xml:space="preserve">13.7566757202148</t>
   </si>
   <si>
     <t xml:space="preserve">13.8988876342773</t>
@@ -1745,13 +1745,13 @@
     <t xml:space="preserve">13.9462909698486</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4203338623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7756366729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7232656478882</t>
+    <t xml:space="preserve">14.4203329086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7756357192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7232646942139</t>
   </si>
   <si>
     <t xml:space="preserve">13.320556640625</t>
@@ -1760,22 +1760,22 @@
     <t xml:space="preserve">13.1878261566162</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7471942901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.069543838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8374891281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2546443939209</t>
+    <t xml:space="preserve">13.7471933364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0695428848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8374910354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2546463012695</t>
   </si>
   <si>
     <t xml:space="preserve">14.8848924636841</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0839910507202</t>
+    <t xml:space="preserve">15.0839900970459</t>
   </si>
   <si>
     <t xml:space="preserve">15.1787986755371</t>
@@ -1784,28 +1784,28 @@
     <t xml:space="preserve">15.1503562927246</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3115291595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3589363098145</t>
+    <t xml:space="preserve">15.3115301132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3589353561401</t>
   </si>
   <si>
     <t xml:space="preserve">15.2925672531128</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1408758163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0271053314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9228162765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8280076980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8659315109253</t>
+    <t xml:space="preserve">15.1408748626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0271062850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9228172302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8280086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8659324645996</t>
   </si>
   <si>
     <t xml:space="preserve">14.9417791366577</t>
@@ -1814,40 +1814,40 @@
     <t xml:space="preserve">15.614914894104</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7097253799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0650291442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2167205810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5485506057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4347820281982</t>
+    <t xml:space="preserve">15.7097272872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0650281906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.216721534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5485496520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4347829818726</t>
   </si>
   <si>
     <t xml:space="preserve">15.3968563079834</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7806043624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9038543701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2262020111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1977605819702</t>
+    <t xml:space="preserve">14.7806034088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9038553237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2262029647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1977615356445</t>
   </si>
   <si>
     <t xml:space="preserve">15.4442625045776</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3684158325195</t>
+    <t xml:space="preserve">15.3684148788452</t>
   </si>
   <si>
     <t xml:space="preserve">15.510627746582</t>
@@ -1856,10 +1856,10 @@
     <t xml:space="preserve">15.738166809082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4302673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9657077789307</t>
+    <t xml:space="preserve">16.430269241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9657068252563</t>
   </si>
   <si>
     <t xml:space="preserve">15.2641267776489</t>
@@ -1868,10 +1868,10 @@
     <t xml:space="preserve">15.7855701446533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6862525939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8474216461182</t>
+    <t xml:space="preserve">16.6862506866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8474254608154</t>
   </si>
   <si>
     <t xml:space="preserve">16.4966316223145</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">16.1932468414307</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2311725616455</t>
+    <t xml:space="preserve">16.2311706542969</t>
   </si>
   <si>
     <t xml:space="preserve">16.7526149749756</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">16.809497833252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7336559295654</t>
+    <t xml:space="preserve">16.7336521148682</t>
   </si>
   <si>
     <t xml:space="preserve">16.8948268890381</t>
@@ -1904,28 +1904,28 @@
     <t xml:space="preserve">16.2501316070557</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8993434906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8898601531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9277820587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8519382476807</t>
+    <t xml:space="preserve">15.899341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8898611068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9277839660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.851936340332</t>
   </si>
   <si>
     <t xml:space="preserve">16.3544216156006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2406520843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9183044433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5016002655029</t>
+    <t xml:space="preserve">16.2406539916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9183053970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5016021728516</t>
   </si>
   <si>
     <t xml:space="preserve">17.6627750396729</t>
@@ -1943,10 +1943,10 @@
     <t xml:space="preserve">17.8239498138428</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6677417755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5743846893311</t>
+    <t xml:space="preserve">18.6677436828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5743827819824</t>
   </si>
   <si>
     <t xml:space="preserve">18.8704280853271</t>
@@ -1955,10 +1955,10 @@
     <t xml:space="preserve">19.5962142944336</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5007152557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9277286529541</t>
+    <t xml:space="preserve">19.50071144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9277248382568</t>
   </si>
   <si>
     <t xml:space="preserve">18.9468269348145</t>
@@ -1973,43 +1973,43 @@
     <t xml:space="preserve">18.7080783843994</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9659271240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0327739715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2333183288574</t>
+    <t xml:space="preserve">18.9659252166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0327758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2333202362061</t>
   </si>
   <si>
     <t xml:space="preserve">19.3861179351807</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0900726318359</t>
+    <t xml:space="preserve">19.0900707244873</t>
   </si>
   <si>
     <t xml:space="preserve">19.1951198577881</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1187210083008</t>
+    <t xml:space="preserve">19.1187229156494</t>
   </si>
   <si>
     <t xml:space="preserve">19.252420425415</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9018077850342</t>
+    <t xml:space="preserve">19.9018058776855</t>
   </si>
   <si>
     <t xml:space="preserve">20.1501007080078</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2646980285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.589391708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5511951446533</t>
+    <t xml:space="preserve">20.2647018432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5893936157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5511932373047</t>
   </si>
   <si>
     <t xml:space="preserve">20.799488067627</t>
@@ -2018,28 +2018,28 @@
     <t xml:space="preserve">19.9591064453125</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8445072174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.481616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3097190856934</t>
+    <t xml:space="preserve">19.8445091247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4816131591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3097171783447</t>
   </si>
   <si>
     <t xml:space="preserve">19.6344108581543</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6726112365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0928020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9400062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6535129547119</t>
+    <t xml:space="preserve">19.6726131439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0928058624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9400043487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6535110473633</t>
   </si>
   <si>
     <t xml:space="preserve">19.558012008667</t>
@@ -2051,10 +2051,10 @@
     <t xml:space="preserve">20.3028964996338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2837982177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2264995574951</t>
+    <t xml:space="preserve">20.2838001251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2264976501465</t>
   </si>
   <si>
     <t xml:space="preserve">20.7039909362793</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">20.6848926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4174957275391</t>
+    <t xml:space="preserve">20.4174976348877</t>
   </si>
   <si>
     <t xml:space="preserve">20.0355052947998</t>
@@ -2075,7 +2075,7 @@
     <t xml:space="preserve">20.1883010864258</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2769794464111</t>
+    <t xml:space="preserve">21.2769813537598</t>
   </si>
   <si>
     <t xml:space="preserve">21.1814804077148</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">20.0164051055908</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5702953338623</t>
+    <t xml:space="preserve">20.5702934265137</t>
   </si>
   <si>
     <t xml:space="preserve">20.9904861450195</t>
@@ -2096,55 +2096,55 @@
     <t xml:space="preserve">21.1050834655762</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1623802185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2578792572021</t>
+    <t xml:space="preserve">21.1623821258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2578811645508</t>
   </si>
   <si>
     <t xml:space="preserve">21.0286846160889</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2960777282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8499660491943</t>
+    <t xml:space="preserve">21.2960796356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.849967956543</t>
   </si>
   <si>
     <t xml:space="preserve">22.4802551269531</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5566539764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5184574127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0982646942139</t>
+    <t xml:space="preserve">22.5566558837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5184555053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0982627868652</t>
   </si>
   <si>
     <t xml:space="preserve">22.2510585784912</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9645652770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9454669952393</t>
+    <t xml:space="preserve">21.9645671844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9454650878906</t>
   </si>
   <si>
     <t xml:space="preserve">22.3083591461182</t>
   </si>
   <si>
-    <t xml:space="preserve">22.594856262207</t>
+    <t xml:space="preserve">22.5948543548584</t>
   </si>
   <si>
     <t xml:space="preserve">22.7476501464844</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8049468994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0600643157959</t>
+    <t xml:space="preserve">22.8049488067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0600624084473</t>
   </si>
   <si>
     <t xml:space="preserve">22.2319602966309</t>
@@ -2153,10 +2153,10 @@
     <t xml:space="preserve">21.3533782958984</t>
   </si>
   <si>
-    <t xml:space="preserve">20.474796295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.455696105957</t>
+    <t xml:space="preserve">20.4747943878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4556941986084</t>
   </si>
   <si>
     <t xml:space="preserve">21.1241836547852</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">20.8758869171143</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0859851837158</t>
+    <t xml:space="preserve">21.0859813690186</t>
   </si>
   <si>
     <t xml:space="preserve">21.7353706359863</t>
@@ -2186,13 +2186,13 @@
     <t xml:space="preserve">21.6016731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6780700683594</t>
+    <t xml:space="preserve">21.6780738830566</t>
   </si>
   <si>
     <t xml:space="preserve">21.4870758056641</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5825748443604</t>
+    <t xml:space="preserve">21.5825729370117</t>
   </si>
   <si>
     <t xml:space="preserve">20.6466903686523</t>
@@ -2204,37 +2204,37 @@
     <t xml:space="preserve">20.4938945770264</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8567867279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3792953491211</t>
+    <t xml:space="preserve">20.8567886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3792972564697</t>
   </si>
   <si>
     <t xml:space="preserve">20.8949871063232</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9331874847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3219966888428</t>
+    <t xml:space="preserve">20.9331855773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3219985961914</t>
   </si>
   <si>
     <t xml:space="preserve">20.3410987854004</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8308658599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0218639373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5375576019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6521530151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.015043258667</t>
+    <t xml:space="preserve">21.830867767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0218658447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5375556945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6521511077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0150451660156</t>
   </si>
   <si>
     <t xml:space="preserve">23.4543361663818</t>
@@ -2243,10 +2243,10 @@
     <t xml:space="preserve">23.7217311859131</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9127292633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5689353942871</t>
+    <t xml:space="preserve">23.912727355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5689334869385</t>
   </si>
   <si>
     <t xml:space="preserve">24.084623336792</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">23.7981300354004</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8745269775391</t>
+    <t xml:space="preserve">23.8745288848877</t>
   </si>
   <si>
     <t xml:space="preserve">23.9700241088867</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">24.8677101135254</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0969047546387</t>
+    <t xml:space="preserve">25.09690284729</t>
   </si>
   <si>
     <t xml:space="preserve">25.3642978668213</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">24.3329181671143</t>
   </si>
   <si>
-    <t xml:space="preserve">24.982307434082</t>
+    <t xml:space="preserve">24.9823055267334</t>
   </si>
   <si>
     <t xml:space="preserve">25.2879009246826</t>
@@ -2285,19 +2285,19 @@
     <t xml:space="preserve">24.9250068664551</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0205059051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6194114685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9441070556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8295097351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6385135650635</t>
+    <t xml:space="preserve">25.0205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6194133758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9441089630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8295078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6385116577148</t>
   </si>
   <si>
     <t xml:space="preserve">24.4475173950195</t>
@@ -2309,37 +2309,37 @@
     <t xml:space="preserve">24.3520183563232</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6576156616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6767139434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4857158660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5621128082275</t>
+    <t xml:space="preserve">24.6576137542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6767120361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4857139587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5621147155762</t>
   </si>
   <si>
     <t xml:space="preserve">24.5812149047852</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6958122253418</t>
+    <t xml:space="preserve">24.6958103179932</t>
   </si>
   <si>
     <t xml:space="preserve">25.3070011138916</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3451995849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8486080169678</t>
+    <t xml:space="preserve">25.3451976776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8486099243164</t>
   </si>
   <si>
     <t xml:space="preserve">25.0014057159424</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2115039825439</t>
+    <t xml:space="preserve">25.2115001678467</t>
   </si>
   <si>
     <t xml:space="preserve">25.7653903961182</t>
@@ -2351,58 +2351,58 @@
     <t xml:space="preserve">25.5552959442139</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1542015075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8226890563965</t>
+    <t xml:space="preserve">25.154203414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8226909637451</t>
   </si>
   <si>
     <t xml:space="preserve">24.7722110748291</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5239143371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9059066772461</t>
+    <t xml:space="preserve">24.5239162445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9059085845947</t>
   </si>
   <si>
     <t xml:space="preserve">25.6698913574219</t>
   </si>
   <si>
-    <t xml:space="preserve">26.223783493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2810840606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.395679473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1405639648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2169609069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5225563049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6944522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8281517028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1910419464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.783130645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2865390777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8854522705078</t>
+    <t xml:space="preserve">26.2237815856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2810802459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3956775665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1405620574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2169628143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5225582122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6944541931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8281497955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1910457611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7831325531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2865409851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8854503631592</t>
   </si>
   <si>
     <t xml:space="preserve">25.9754867553711</t>
@@ -2411,79 +2411,79 @@
     <t xml:space="preserve">25.2306003570557</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6003131866455</t>
+    <t xml:space="preserve">24.6003150939941</t>
   </si>
   <si>
     <t xml:space="preserve">23.6071338653564</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4666175842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4352340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8254089355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3479156494141</t>
+    <t xml:space="preserve">24.4666156768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4352397918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8254070281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3479175567627</t>
   </si>
   <si>
     <t xml:space="preserve">15.5852918624878</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3233604431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7285375595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1200790405273</t>
+    <t xml:space="preserve">17.323356628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7285385131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.120080947876</t>
   </si>
   <si>
     <t xml:space="preserve">16.9031658172607</t>
   </si>
   <si>
-    <t xml:space="preserve">17.523904800415</t>
+    <t xml:space="preserve">17.5239028930664</t>
   </si>
   <si>
     <t xml:space="preserve">17.7435493469238</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1350898742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8322277069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1446399688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2210388183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1159896850586</t>
+    <t xml:space="preserve">18.1350917816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8322257995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1446418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.221040725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1159915924072</t>
   </si>
   <si>
     <t xml:space="preserve">17.8772468566895</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3806571960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4093055725098</t>
+    <t xml:space="preserve">17.3806591033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4093036651611</t>
   </si>
   <si>
     <t xml:space="preserve">16.8076686859131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6480503082275</t>
+    <t xml:space="preserve">17.6480522155762</t>
   </si>
   <si>
     <t xml:space="preserve">18.7844791412354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4311370849609</t>
+    <t xml:space="preserve">18.4311351776123</t>
   </si>
   <si>
     <t xml:space="preserve">18.4454612731934</t>
@@ -2492,37 +2492,37 @@
     <t xml:space="preserve">18.7653789520264</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9536437988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8663387298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2715187072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8465557098389</t>
+    <t xml:space="preserve">17.9536457061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8663368225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.271520614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8465538024902</t>
   </si>
   <si>
     <t xml:space="preserve">20.0068550109863</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2455997467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.987756729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.968656539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7681083679199</t>
+    <t xml:space="preserve">20.2456016540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9877548217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9686546325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7681102752686</t>
   </si>
   <si>
     <t xml:space="preserve">20.6753406524658</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7640190124512</t>
+    <t xml:space="preserve">21.7640209197998</t>
   </si>
   <si>
     <t xml:space="preserve">21.3820266723633</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">21.8595161437988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9522857666016</t>
+    <t xml:space="preserve">20.9522838592529</t>
   </si>
   <si>
     <t xml:space="preserve">21.9932155609131</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">21.658971786499</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0341453552246</t>
+    <t xml:space="preserve">23.0341472625732</t>
   </si>
   <si>
     <t xml:space="preserve">23.1391925811768</t>
@@ -2561,19 +2561,19 @@
     <t xml:space="preserve">22.2797088623047</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5020847320557</t>
+    <t xml:space="preserve">23.5020866394043</t>
   </si>
   <si>
     <t xml:space="preserve">23.8267784118652</t>
   </si>
   <si>
-    <t xml:space="preserve">23.521183013916</t>
+    <t xml:space="preserve">23.5211849212646</t>
   </si>
   <si>
     <t xml:space="preserve">23.8458786010742</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8172283172607</t>
+    <t xml:space="preserve">23.8172264099121</t>
   </si>
   <si>
     <t xml:space="preserve">23.3588390350342</t>
@@ -2585,25 +2585,25 @@
     <t xml:space="preserve">22.6330528259277</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8881664276123</t>
+    <t xml:space="preserve">21.8881683349609</t>
   </si>
   <si>
     <t xml:space="preserve">22.0696144104004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6999034881592</t>
+    <t xml:space="preserve">22.6999015808105</t>
   </si>
   <si>
     <t xml:space="preserve">22.9386463165283</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3015384674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6808032989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7094535827637</t>
+    <t xml:space="preserve">23.3015403747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6808013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.709451675415</t>
   </si>
   <si>
     <t xml:space="preserve">23.1487426757812</t>
@@ -2615,31 +2615,31 @@
     <t xml:space="preserve">22.4229564666748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4611549377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6426010131836</t>
+    <t xml:space="preserve">22.4611568450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6426029205322</t>
   </si>
   <si>
     <t xml:space="preserve">22.7381000518799</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2728900909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2442417144775</t>
+    <t xml:space="preserve">23.272891998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2442378997803</t>
   </si>
   <si>
     <t xml:space="preserve">23.5402851104736</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7408313751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8363265991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7121810913086</t>
+    <t xml:space="preserve">23.7408294677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8363285064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.71217918396</t>
   </si>
   <si>
     <t xml:space="preserve">23.7599296569824</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">24.1610221862793</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3233699798584</t>
+    <t xml:space="preserve">24.3233661651611</t>
   </si>
   <si>
     <t xml:space="preserve">24.7340106964111</t>
@@ -2657,31 +2657,31 @@
     <t xml:space="preserve">25.2783489227295</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0682544708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0587024688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7531127929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1351013183594</t>
+    <t xml:space="preserve">25.0682582855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0587043762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7531108856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.135103225708</t>
   </si>
   <si>
     <t xml:space="preserve">26.5580253601074</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5102767944336</t>
+    <t xml:space="preserve">26.510274887085</t>
   </si>
   <si>
     <t xml:space="preserve">27.6467037200928</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2292423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5034561157227</t>
+    <t xml:space="preserve">28.2292404174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.503454208374</t>
   </si>
   <si>
     <t xml:space="preserve">27.5894031524658</t>
@@ -2690,16 +2690,16 @@
     <t xml:space="preserve">27.1596641540527</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5512046813965</t>
+    <t xml:space="preserve">27.5512065887451</t>
   </si>
   <si>
     <t xml:space="preserve">27.0164165496826</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0355129241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3793067932129</t>
+    <t xml:space="preserve">27.035514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3793087005615</t>
   </si>
   <si>
     <t xml:space="preserve">27.2265110015869</t>
@@ -2708,55 +2708,55 @@
     <t xml:space="preserve">27.054615020752</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2838134765625</t>
+    <t xml:space="preserve">27.2838115692139</t>
   </si>
   <si>
     <t xml:space="preserve">26.5675754547119</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0450649261475</t>
+    <t xml:space="preserve">27.0450668334961</t>
   </si>
   <si>
     <t xml:space="preserve">26.7108211517334</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5007247924805</t>
+    <t xml:space="preserve">26.5007266998291</t>
   </si>
   <si>
     <t xml:space="preserve">26.4529781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6630706787109</t>
+    <t xml:space="preserve">26.6630725860596</t>
   </si>
   <si>
     <t xml:space="preserve">26.5389270782471</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2619819641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4625263214111</t>
+    <t xml:space="preserve">26.2619781494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4625244140625</t>
   </si>
   <si>
     <t xml:space="preserve">27.5989551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6726226806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7585716247559</t>
+    <t xml:space="preserve">26.6726245880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7585697174072</t>
   </si>
   <si>
     <t xml:space="preserve">27.388858795166</t>
   </si>
   <si>
-    <t xml:space="preserve">27.446159362793</t>
+    <t xml:space="preserve">27.4461612701416</t>
   </si>
   <si>
     <t xml:space="preserve">28.1814937591553</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3533916473389</t>
+    <t xml:space="preserve">28.3533897399902</t>
   </si>
   <si>
     <t xml:space="preserve">28.5061874389648</t>
@@ -2777,34 +2777,34 @@
     <t xml:space="preserve">27.6562519073486</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4748077392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6849021911621</t>
+    <t xml:space="preserve">27.4748058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6849040985107</t>
   </si>
   <si>
     <t xml:space="preserve">29.3847694396973</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9673099517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1746711730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4802684783936</t>
+    <t xml:space="preserve">29.9673080444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1746730804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4802665710449</t>
   </si>
   <si>
     <t xml:space="preserve">29.833610534668</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0246086120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1651210784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3274669647217</t>
+    <t xml:space="preserve">30.0246047973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1651248931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3274707794189</t>
   </si>
   <si>
     <t xml:space="preserve">29.8049602508545</t>
@@ -2816,22 +2816,22 @@
     <t xml:space="preserve">30.9891376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7503910064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5402984619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9222869873047</t>
+    <t xml:space="preserve">30.7503929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5402965545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9222888946533</t>
   </si>
   <si>
     <t xml:space="preserve">30.7408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9318351745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7217407226562</t>
+    <t xml:space="preserve">30.9318370819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7217426300049</t>
   </si>
   <si>
     <t xml:space="preserve">30.6835460662842</t>
@@ -2840,13 +2840,13 @@
     <t xml:space="preserve">30.8172397613525</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4829998016357</t>
+    <t xml:space="preserve">30.4829978942871</t>
   </si>
   <si>
     <t xml:space="preserve">30.5593967437744</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7258319854736</t>
+    <t xml:space="preserve">28.725830078125</t>
   </si>
   <si>
     <t xml:space="preserve">29.2128715515137</t>
@@ -2855,13 +2855,13 @@
     <t xml:space="preserve">30.9031887054443</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9918670654297</t>
+    <t xml:space="preserve">31.9918689727783</t>
   </si>
   <si>
     <t xml:space="preserve">32.899097442627</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6535377502441</t>
+    <t xml:space="preserve">33.6535339355469</t>
   </si>
   <si>
     <t xml:space="preserve">33.309741973877</t>
@@ -2870,28 +2870,28 @@
     <t xml:space="preserve">32.4693603515625</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3288383483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5580368041992</t>
+    <t xml:space="preserve">33.3288421630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.558032989502</t>
   </si>
   <si>
     <t xml:space="preserve">34.1310272216797</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4338912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4461708068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8158836364746</t>
+    <t xml:space="preserve">33.4338836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8158798217773</t>
   </si>
   <si>
     <t xml:space="preserve">33.930477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6603507995605</t>
+    <t xml:space="preserve">32.6603546142578</t>
   </si>
   <si>
     <t xml:space="preserve">32.6699028015137</t>
@@ -2900,19 +2900,19 @@
     <t xml:space="preserve">32.8513526916504</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5143775939941</t>
+    <t xml:space="preserve">31.5143814086914</t>
   </si>
   <si>
     <t xml:space="preserve">31.6098728179932</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9727668762207</t>
+    <t xml:space="preserve">31.9727687835693</t>
   </si>
   <si>
     <t xml:space="preserve">32.7367553710938</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0587120056152</t>
+    <t xml:space="preserve">32.0587158203125</t>
   </si>
   <si>
     <t xml:space="preserve">31.2565307617188</t>
@@ -2921,10 +2921,10 @@
     <t xml:space="preserve">30.884090423584</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0177879333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1323871612549</t>
+    <t xml:space="preserve">31.017786026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1323833465576</t>
   </si>
   <si>
     <t xml:space="preserve">30.8745422363281</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">31.9441184997559</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4216156005859</t>
+    <t xml:space="preserve">32.4216117858887</t>
   </si>
   <si>
     <t xml:space="preserve">31.695821762085</t>
@@ -2969,19 +2969,19 @@
     <t xml:space="preserve">32.4120597839355</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0491676330566</t>
+    <t xml:space="preserve">32.0491638183594</t>
   </si>
   <si>
     <t xml:space="preserve">31.5334777832031</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2087802886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3165626525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1637649536133</t>
+    <t xml:space="preserve">31.2087841033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3165588378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1637687683105</t>
   </si>
   <si>
     <t xml:space="preserve">32.1064643859863</t>
@@ -2990,16 +2990,16 @@
     <t xml:space="preserve">32.3834114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6221542358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.650806427002</t>
+    <t xml:space="preserve">32.6221504211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6508026123047</t>
   </si>
   <si>
     <t xml:space="preserve">32.8036003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5839576721191</t>
+    <t xml:space="preserve">32.5839538574219</t>
   </si>
   <si>
     <t xml:space="preserve">32.3547592163086</t>
@@ -3011,16 +3011,16 @@
     <t xml:space="preserve">32.0396194458008</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5648574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.326114654541</t>
+    <t xml:space="preserve">32.5648536682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3261070251465</t>
   </si>
   <si>
     <t xml:space="preserve">31.9250202178955</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0423431396484</t>
+    <t xml:space="preserve">33.042350769043</t>
   </si>
   <si>
     <t xml:space="preserve">33.7967834472656</t>
@@ -3029,19 +3029,19 @@
     <t xml:space="preserve">34.5989646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4843711853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.942756652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8854598999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.000057220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8022422790527</t>
+    <t xml:space="preserve">34.4843673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9427604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8854560852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0000610351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.80224609375</t>
   </si>
   <si>
     <t xml:space="preserve">35.5539512634277</t>
@@ -3050,13 +3050,13 @@
     <t xml:space="preserve">35.3343048095703</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2551689147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9018287658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3670387268066</t>
+    <t xml:space="preserve">34.2551765441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9018249511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3670349121094</t>
   </si>
   <si>
     <t xml:space="preserve">33.3192901611328</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">31.7817707061768</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8104228973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4598121643066</t>
+    <t xml:space="preserve">31.8104209899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4598083496094</t>
   </si>
   <si>
     <t xml:space="preserve">32.7081031799316</t>
@@ -3083,22 +3083,22 @@
     <t xml:space="preserve">28.6876335144043</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0027770996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3874988555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6453456878662</t>
+    <t xml:space="preserve">29.002779006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3875007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6453437805176</t>
   </si>
   <si>
     <t xml:space="preserve">31.4761772155762</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5211963653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7312927246094</t>
+    <t xml:space="preserve">30.5211944580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7312908172607</t>
   </si>
   <si>
     <t xml:space="preserve">31.1228370666504</t>
@@ -3107,16 +3107,16 @@
     <t xml:space="preserve">30.5498466491699</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5375652313232</t>
+    <t xml:space="preserve">29.5375671386719</t>
   </si>
   <si>
     <t xml:space="preserve">30.148754119873</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6671752929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4065971374512</t>
+    <t xml:space="preserve">31.6671772003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4065990447998</t>
   </si>
   <si>
     <t xml:space="preserve">30.7694911956787</t>
@@ -3131,25 +3131,25 @@
     <t xml:space="preserve">30.9413890838623</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2756328582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.960485458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5812282562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3424816131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5007362365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9372978210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8731803894043</t>
+    <t xml:space="preserve">31.275634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9604892730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5812244415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3424797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5007400512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9373016357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8731842041016</t>
   </si>
   <si>
     <t xml:space="preserve">33.6344375610352</t>
@@ -3158,16 +3158,16 @@
     <t xml:space="preserve">33.624885559082</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1787796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2169723510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9905090332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8281631469727</t>
+    <t xml:space="preserve">34.1787719726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2169799804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9905052185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8281593322754</t>
   </si>
   <si>
     <t xml:space="preserve">34.302921295166</t>
@@ -3176,7 +3176,7 @@
     <t xml:space="preserve">33.1091957092285</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5484886169434</t>
+    <t xml:space="preserve">33.5484924316406</t>
   </si>
   <si>
     <t xml:space="preserve">33.8063316345215</t>
@@ -3188,40 +3188,40 @@
     <t xml:space="preserve">34.0928268432617</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5771408081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2688140869141</t>
+    <t xml:space="preserve">33.5771369934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2688179016113</t>
   </si>
   <si>
     <t xml:space="preserve">31.9059162139893</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8868179321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0873641967773</t>
+    <t xml:space="preserve">31.8868198394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0873603820801</t>
   </si>
   <si>
     <t xml:space="preserve">32.946849822998</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1378440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7995109558105</t>
+    <t xml:space="preserve">33.1378479003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7995147705078</t>
   </si>
   <si>
     <t xml:space="preserve">35.8851928710938</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6538200378418</t>
+    <t xml:space="preserve">36.6538238525391</t>
   </si>
   <si>
     <t xml:space="preserve">35.9620552062988</t>
   </si>
   <si>
-    <t xml:space="preserve">36.769115447998</t>
+    <t xml:space="preserve">36.7691192626953</t>
   </si>
   <si>
     <t xml:space="preserve">37.0765647888184</t>
@@ -3242,10 +3242,10 @@
     <t xml:space="preserve">38.2391090393066</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7683258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8836212158203</t>
+    <t xml:space="preserve">37.7683296203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.883617401123</t>
   </si>
   <si>
     <t xml:space="preserve">38.0181274414062</t>
@@ -3260,22 +3260,22 @@
     <t xml:space="preserve">38.642635345459</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3440093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.594596862793</t>
+    <t xml:space="preserve">39.3440055847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5946006774902</t>
   </si>
   <si>
     <t xml:space="preserve">38.7963638305664</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7194976806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6042060852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6130256652832</t>
+    <t xml:space="preserve">38.7195014953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6042098999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6130294799805</t>
   </si>
   <si>
     <t xml:space="preserve">39.6514587402344</t>
@@ -3290,25 +3290,25 @@
     <t xml:space="preserve">40.006950378418</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8051795959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9685173034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6034240722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7571449279785</t>
+    <t xml:space="preserve">39.8051834106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9685134887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6034202575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7571487426758</t>
   </si>
   <si>
     <t xml:space="preserve">39.9973449707031</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0749931335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5769538879395</t>
+    <t xml:space="preserve">39.0749893188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5769577026367</t>
   </si>
   <si>
     <t xml:space="preserve">37.5665588378906</t>
@@ -3323,10 +3323,10 @@
     <t xml:space="preserve">38.9789123535156</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1614608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4793014526367</t>
+    <t xml:space="preserve">39.1614570617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.479305267334</t>
   </si>
   <si>
     <t xml:space="preserve">39.4496955871582</t>
@@ -3362,7 +3362,7 @@
     <t xml:space="preserve">40.2567520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3336143493652</t>
+    <t xml:space="preserve">40.333610534668</t>
   </si>
   <si>
     <t xml:space="preserve">40.266357421875</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">41.3424339294434</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2271461486816</t>
+    <t xml:space="preserve">41.2271423339844</t>
   </si>
   <si>
     <t xml:space="preserve">41.2367477416992</t>
@@ -3395,40 +3395,40 @@
     <t xml:space="preserve">43.0814476013184</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2455711364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0341949462891</t>
+    <t xml:space="preserve">42.2455673217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0341987609863</t>
   </si>
   <si>
     <t xml:space="preserve">41.7651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9669418334961</t>
+    <t xml:space="preserve">41.9669456481934</t>
   </si>
   <si>
     <t xml:space="preserve">42.4665489196777</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5434112548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6683120727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9853706359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3896903991699</t>
+    <t xml:space="preserve">42.5434150695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6683158874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9853744506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3896865844727</t>
   </si>
   <si>
     <t xml:space="preserve">42.8989028930664</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0245895385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9765472412109</t>
+    <t xml:space="preserve">42.0245933532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9765510559082</t>
   </si>
   <si>
     <t xml:space="preserve">41.5345916748047</t>
@@ -3440,19 +3440,19 @@
     <t xml:space="preserve">39.7187118530273</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0061569213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0165596008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8332176208496</t>
+    <t xml:space="preserve">41.006160736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0165557861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8332214355469</t>
   </si>
   <si>
     <t xml:space="preserve">41.0638084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0718421936035</t>
+    <t xml:space="preserve">43.0718460083008</t>
   </si>
   <si>
     <t xml:space="preserve">43.1679191589355</t>
@@ -3470,7 +3470,7 @@
     <t xml:space="preserve">39.7859687805176</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2759666442871</t>
+    <t xml:space="preserve">40.2759628295898</t>
   </si>
   <si>
     <t xml:space="preserve">39.5842056274414</t>
@@ -3482,10 +3482,10 @@
     <t xml:space="preserve">39.5169486999512</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6802787780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.10302734375</t>
+    <t xml:space="preserve">39.6802825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1030235290527</t>
   </si>
   <si>
     <t xml:space="preserve">39.0077362060547</t>
@@ -3509,10 +3509,10 @@
     <t xml:space="preserve">42.7932167053223</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5730247497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1694946289062</t>
+    <t xml:space="preserve">41.5730209350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.169490814209</t>
   </si>
   <si>
     <t xml:space="preserve">42.2263565063477</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">43.0045852661133</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9653625488281</t>
+    <t xml:space="preserve">43.9653663635254</t>
   </si>
   <si>
     <t xml:space="preserve">43.8596801757812</t>
@@ -3542,13 +3542,13 @@
     <t xml:space="preserve">44.2632102966309</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7251739501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0037994384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2055587768555</t>
+    <t xml:space="preserve">43.725170135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0038032531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2055625915527</t>
   </si>
   <si>
     <t xml:space="preserve">43.436939239502</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">42.8028182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6794967651367</t>
+    <t xml:space="preserve">40.6794929504395</t>
   </si>
   <si>
     <t xml:space="preserve">41.6018447875977</t>
@@ -3581,13 +3581,13 @@
     <t xml:space="preserve">41.4192962646484</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1318550109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1606750488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2655715942383</t>
+    <t xml:space="preserve">40.1318511962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1606712341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2655754089355</t>
   </si>
   <si>
     <t xml:space="preserve">40.1798896789551</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">43.6579170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4169387817383</t>
+    <t xml:space="preserve">44.416934967041</t>
   </si>
   <si>
     <t xml:space="preserve">45.0702667236328</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">44.0518379211426</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5914535522461</t>
+    <t xml:space="preserve">42.5914497375488</t>
   </si>
   <si>
     <t xml:space="preserve">41.8708648681641</t>
@@ -3662,10 +3662,10 @@
     <t xml:space="preserve">38.383228302002</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1814651489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2014656066895</t>
+    <t xml:space="preserve">38.1814613342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2014694213867</t>
   </si>
   <si>
     <t xml:space="preserve">35.7795104980469</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">35.0397071838379</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4632339477539</t>
+    <t xml:space="preserve">34.4632377624512</t>
   </si>
   <si>
     <t xml:space="preserve">36.0581359863281</t>
@@ -3689,10 +3689,10 @@
     <t xml:space="preserve">36.7018585205078</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8644065856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.558521270752</t>
+    <t xml:space="preserve">37.8644027709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5585250854492</t>
   </si>
   <si>
     <t xml:space="preserve">34.8859825134277</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">35.116569519043</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7706909179688</t>
+    <t xml:space="preserve">34.7706871032715</t>
   </si>
   <si>
     <t xml:space="preserve">33.9636306762695</t>
@@ -3722,7 +3722,7 @@
     <t xml:space="preserve">34.2710800170898</t>
   </si>
   <si>
-    <t xml:space="preserve">34.280689239502</t>
+    <t xml:space="preserve">34.2806930541992</t>
   </si>
   <si>
     <t xml:space="preserve">34.146183013916</t>
@@ -3743,13 +3743,13 @@
     <t xml:space="preserve">35.933235168457</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9420547485352</t>
+    <t xml:space="preserve">36.9420585632324</t>
   </si>
   <si>
     <t xml:space="preserve">36.4712715148926</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4520530700684</t>
+    <t xml:space="preserve">36.4520568847656</t>
   </si>
   <si>
     <t xml:space="preserve">36.1253890991211</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">34.4344139099121</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1357879638672</t>
+    <t xml:space="preserve">35.1357841491699</t>
   </si>
   <si>
     <t xml:space="preserve">34.9244117736816</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">35.981273651123</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5200958251953</t>
+    <t xml:space="preserve">35.5200996398926</t>
   </si>
   <si>
     <t xml:space="preserve">35.0973510742188</t>
@@ -3794,28 +3794,28 @@
     <t xml:space="preserve">35.7602958679199</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2118606567383</t>
+    <t xml:space="preserve">36.211856842041</t>
   </si>
   <si>
     <t xml:space="preserve">38.5081329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0173454284668</t>
+    <t xml:space="preserve">39.0173416137695</t>
   </si>
   <si>
     <t xml:space="preserve">38.9500885009766</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2375373840332</t>
+    <t xml:space="preserve">40.2375335693359</t>
   </si>
   <si>
     <t xml:space="preserve">41.2943954467773</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8908653259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6891021728516</t>
+    <t xml:space="preserve">40.890869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6891059875488</t>
   </si>
   <si>
     <t xml:space="preserve">39.8340072631836</t>
@@ -3827,16 +3827,16 @@
     <t xml:space="preserve">39.4208717346191</t>
   </si>
   <si>
-    <t xml:space="preserve">39.219108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.623420715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9797019958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8075485229492</t>
+    <t xml:space="preserve">39.2191047668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6234245300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9796981811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.807544708252</t>
   </si>
   <si>
     <t xml:space="preserve">36.6442108154297</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">35.4528427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2502899169922</t>
+    <t xml:space="preserve">36.2502937316895</t>
   </si>
   <si>
     <t xml:space="preserve">36.7210731506348</t>
@@ -3860,16 +3860,16 @@
     <t xml:space="preserve">35.7218627929688</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3183326721191</t>
+    <t xml:space="preserve">35.3183364868164</t>
   </si>
   <si>
     <t xml:space="preserve">34.0693168640137</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2726516723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9836387634277</t>
+    <t xml:space="preserve">32.2726554870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9836349487305</t>
   </si>
   <si>
     <t xml:space="preserve">32.9740257263184</t>
@@ -3890,13 +3890,13 @@
     <t xml:space="preserve">31.2734413146973</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3414859771729</t>
+    <t xml:space="preserve">30.3414840698242</t>
   </si>
   <si>
     <t xml:space="preserve">30.6777591705322</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2105255126953</t>
+    <t xml:space="preserve">31.2105274200439</t>
   </si>
   <si>
     <t xml:space="preserve">31.0071048736572</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">31.2492733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3558235168457</t>
+    <t xml:space="preserve">31.3558254241943</t>
   </si>
   <si>
     <t xml:space="preserve">31.6948623657227</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">30.0965557098389</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6099529266357</t>
+    <t xml:space="preserve">30.6099510192871</t>
   </si>
   <si>
     <t xml:space="preserve">30.3484115600586</t>
@@ -3932,13 +3932,13 @@
     <t xml:space="preserve">30.4646530151367</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7865810394287</t>
+    <t xml:space="preserve">29.7865829467773</t>
   </si>
   <si>
     <t xml:space="preserve">28.2948322296143</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2606258392334</t>
+    <t xml:space="preserve">26.260627746582</t>
   </si>
   <si>
     <t xml:space="preserve">25.5438137054443</t>
@@ -3956,22 +3956,22 @@
     <t xml:space="preserve">25.4663181304932</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5341243743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8828430175781</t>
+    <t xml:space="preserve">25.5341262817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8828449249268</t>
   </si>
   <si>
     <t xml:space="preserve">27.9364242553711</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8663463592529</t>
+    <t xml:space="preserve">28.8663444519043</t>
   </si>
   <si>
     <t xml:space="preserve">28.934154510498</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3529529571533</t>
+    <t xml:space="preserve">28.3529510498047</t>
   </si>
   <si>
     <t xml:space="preserve">28.2560863494873</t>
@@ -3986,13 +3986,13 @@
     <t xml:space="preserve">29.9900035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7358779907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5883083343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.212797164917</t>
+    <t xml:space="preserve">30.7358798980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.588306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2127990722656</t>
   </si>
   <si>
     <t xml:space="preserve">30.1740493774414</t>
@@ -4001,10 +4001,10 @@
     <t xml:space="preserve">30.3387241363525</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2173366546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7523784637451</t>
+    <t xml:space="preserve">28.2173385620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7523765563965</t>
   </si>
   <si>
     <t xml:space="preserve">28.3238925933838</t>
@@ -4013,7 +4013,7 @@
     <t xml:space="preserve">28.924467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8469734191895</t>
+    <t xml:space="preserve">28.8469715118408</t>
   </si>
   <si>
     <t xml:space="preserve">29.6994037628174</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">30.1837368011475</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6412811279297</t>
+    <t xml:space="preserve">29.6412830352783</t>
   </si>
   <si>
     <t xml:space="preserve">29.4766082763672</t>
@@ -4040,13 +4040,13 @@
     <t xml:space="preserve">31.4236354827881</t>
   </si>
   <si>
-    <t xml:space="preserve">29.970630645752</t>
+    <t xml:space="preserve">29.9706287384033</t>
   </si>
   <si>
     <t xml:space="preserve">30.8714923858643</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0942859649658</t>
+    <t xml:space="preserve">31.0942840576172</t>
   </si>
   <si>
     <t xml:space="preserve">29.4281749725342</t>
@@ -4064,19 +4064,19 @@
     <t xml:space="preserve">29.7672100067139</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1979656219482</t>
+    <t xml:space="preserve">28.1979637145996</t>
   </si>
   <si>
     <t xml:space="preserve">27.8879909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8104953765869</t>
+    <t xml:space="preserve">27.8104972839355</t>
   </si>
   <si>
     <t xml:space="preserve">27.442403793335</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8030815124512</t>
+    <t xml:space="preserve">26.8030796051025</t>
   </si>
   <si>
     <t xml:space="preserve">26.7740211486816</t>
@@ -4094,7 +4094,7 @@
     <t xml:space="preserve">24.962610244751</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2338371276855</t>
+    <t xml:space="preserve">25.2338352203369</t>
   </si>
   <si>
     <t xml:space="preserve">24.6816959381104</t>
@@ -4115,10 +4115,10 @@
     <t xml:space="preserve">25.10791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2144622802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5073337554932</t>
+    <t xml:space="preserve">25.2144641876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5073356628418</t>
   </si>
   <si>
     <t xml:space="preserve">24.2554817199707</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">24.1779861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8970737457275</t>
+    <t xml:space="preserve">23.8970718383789</t>
   </si>
   <si>
     <t xml:space="preserve">24.4201545715332</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">24.0908069610596</t>
   </si>
   <si>
-    <t xml:space="preserve">24.013313293457</t>
+    <t xml:space="preserve">24.0133152008057</t>
   </si>
   <si>
     <t xml:space="preserve">24.1973609924316</t>
@@ -4157,10 +4157,10 @@
     <t xml:space="preserve">26.0572071075439</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5728702545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7159004211426</t>
+    <t xml:space="preserve">25.5728721618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7159023284912</t>
   </si>
   <si>
     <t xml:space="preserve">26.1928195953369</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">24.6235733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8389530181885</t>
+    <t xml:space="preserve">23.8389549255371</t>
   </si>
   <si>
     <t xml:space="preserve">22.9187183380127</t>
@@ -4196,13 +4196,13 @@
     <t xml:space="preserve">24.8366813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0475177764893</t>
+    <t xml:space="preserve">26.0475196838379</t>
   </si>
   <si>
     <t xml:space="preserve">25.3694515228271</t>
   </si>
   <si>
-    <t xml:space="preserve">25.059476852417</t>
+    <t xml:space="preserve">25.0594749450684</t>
   </si>
   <si>
     <t xml:space="preserve">25.4275703430176</t>
@@ -4226,7 +4226,7 @@
     <t xml:space="preserve">23.3643054962158</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4007816314697</t>
+    <t xml:space="preserve">24.4007797241211</t>
   </si>
   <si>
     <t xml:space="preserve">25.8150386810303</t>
@@ -4250,7 +4250,7 @@
     <t xml:space="preserve">26.7062149047852</t>
   </si>
   <si>
-    <t xml:space="preserve">26.764331817627</t>
+    <t xml:space="preserve">26.7643337249756</t>
   </si>
   <si>
     <t xml:space="preserve">26.5221672058105</t>
@@ -4262,7 +4262,7 @@
     <t xml:space="preserve">26.8321399688721</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8805732727051</t>
+    <t xml:space="preserve">26.8805751800537</t>
   </si>
   <si>
     <t xml:space="preserve">27.0065002441406</t>
@@ -4274,7 +4274,7 @@
     <t xml:space="preserve">26.0087738037109</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7837085723877</t>
+    <t xml:space="preserve">26.7837066650391</t>
   </si>
   <si>
     <t xml:space="preserve">27.6458225250244</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">26.6965274810791</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0936813354492</t>
+    <t xml:space="preserve">27.0936832427979</t>
   </si>
   <si>
     <t xml:space="preserve">27.1324291229248</t>
@@ -4319,13 +4319,13 @@
     <t xml:space="preserve">26.4543590545654</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8344097137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9700260162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6287212371826</t>
+    <t xml:space="preserve">25.8344116210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9700241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.628719329834</t>
   </si>
   <si>
     <t xml:space="preserve">26.8708896636963</t>
@@ -4334,13 +4334,13 @@
     <t xml:space="preserve">26.1443843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2509384155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9677562713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9797115325928</t>
+    <t xml:space="preserve">26.250940322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9677543640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9797134399414</t>
   </si>
   <si>
     <t xml:space="preserve">26.1056385040283</t>
@@ -4349,10 +4349,10 @@
     <t xml:space="preserve">26.5996608734131</t>
   </si>
   <si>
-    <t xml:space="preserve">26.63840675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2412528991699</t>
+    <t xml:space="preserve">26.6384048461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2412548065186</t>
   </si>
   <si>
     <t xml:space="preserve">25.6019306182861</t>
@@ -4361,7 +4361,7 @@
     <t xml:space="preserve">24.9044876098633</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0788497924805</t>
+    <t xml:space="preserve">25.0788478851318</t>
   </si>
   <si>
     <t xml:space="preserve">24.8851165771484</t>
@@ -4376,16 +4376,16 @@
     <t xml:space="preserve">24.7398147583008</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4782733917236</t>
+    <t xml:space="preserve">24.4782752990723</t>
   </si>
   <si>
     <t xml:space="preserve">27.6070785522461</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9290065765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1227416992188</t>
+    <t xml:space="preserve">26.9290084838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1227436065674</t>
   </si>
   <si>
     <t xml:space="preserve">25.7666053771973</t>
@@ -4400,7 +4400,7 @@
     <t xml:space="preserve">26.541540145874</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2025051116943</t>
+    <t xml:space="preserve">26.202507019043</t>
   </si>
   <si>
     <t xml:space="preserve">26.6190319061279</t>
@@ -4412,28 +4412,28 @@
     <t xml:space="preserve">27.3358497619629</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1763210296631</t>
+    <t xml:space="preserve">29.1763229370117</t>
   </si>
   <si>
     <t xml:space="preserve">28.5466842651367</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4401321411133</t>
+    <t xml:space="preserve">28.4401340484619</t>
   </si>
   <si>
     <t xml:space="preserve">28.7694797515869</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2367095947266</t>
+    <t xml:space="preserve">28.2367115020752</t>
   </si>
   <si>
     <t xml:space="preserve">28.1107845306396</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0310211181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4304447174072</t>
+    <t xml:space="preserve">29.0310192108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4304466247559</t>
   </si>
   <si>
     <t xml:space="preserve">28.8954067230225</t>
@@ -4472,16 +4472,16 @@
     <t xml:space="preserve">31.6754875183105</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2783336639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9176559448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9854621887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7820415496826</t>
+    <t xml:space="preserve">31.2783317565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9176540374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9854602813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7820453643799</t>
   </si>
   <si>
     <t xml:space="preserve">32.3729286193848</t>
@@ -4496,10 +4496,10 @@
     <t xml:space="preserve">32.3341865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7313423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2373161315918</t>
+    <t xml:space="preserve">32.7313385009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2373123168945</t>
   </si>
   <si>
     <t xml:space="preserve">32.0823287963867</t>
@@ -4517,10 +4517,10 @@
     <t xml:space="preserve">34.7267951965332</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3296432495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2134017944336</t>
+    <t xml:space="preserve">34.3296394348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2134056091309</t>
   </si>
   <si>
     <t xml:space="preserve">34.6686782836914</t>
@@ -4529,19 +4529,19 @@
     <t xml:space="preserve">34.8817825317383</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6105537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8259315490723</t>
+    <t xml:space="preserve">34.6105575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8259353637695</t>
   </si>
   <si>
     <t xml:space="preserve">33.0413131713867</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8475761413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1478691101074</t>
+    <t xml:space="preserve">32.8475799560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1478652954102</t>
   </si>
   <si>
     <t xml:space="preserve">33.167407989502</t>
@@ -71533,7 +71533,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6940046296</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>4674551</v>
@@ -71554,6 +71554,32 @@
         <v>2060</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6932407407</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>1842632</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>15.0050001144409</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>14.6450004577637</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>14.7600002288818</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>2051</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="2061">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="2062">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,52 +38,52 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.335205078125</t>
+    <t xml:space="preserve">7.33520460128784</t>
   </si>
   <si>
     <t xml:space="preserve">AMP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39109325408936</t>
+    <t xml:space="preserve">7.39109230041504</t>
   </si>
   <si>
     <t xml:space="preserve">7.31191873550415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36780548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15357112884521</t>
+    <t xml:space="preserve">7.36780595779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15357065200806</t>
   </si>
   <si>
     <t xml:space="preserve">6.96262311935425</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21877241134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2793173789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16288566589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0324821472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08836889266968</t>
+    <t xml:space="preserve">7.21877336502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27931833267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1628851890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03248310089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08836936950684</t>
   </si>
   <si>
     <t xml:space="preserve">7.1954870223999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98590993881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13494157791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34451961517334</t>
+    <t xml:space="preserve">6.9859094619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13494205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34451866149902</t>
   </si>
   <si>
     <t xml:space="preserve">7.23740243911743</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">7.35383367538452</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14891338348389</t>
+    <t xml:space="preserve">7.14891386032104</t>
   </si>
   <si>
     <t xml:space="preserve">7.18151473999023</t>
@@ -104,34 +104,34 @@
     <t xml:space="preserve">7.28397512435913</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13959932327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05111122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84619188308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51086711883545</t>
+    <t xml:space="preserve">7.13959836959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05111074447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84619092941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51086759567261</t>
   </si>
   <si>
     <t xml:space="preserve">6.45497989654541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5900411605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33389043807983</t>
+    <t xml:space="preserve">6.59003973007202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33389139175415</t>
   </si>
   <si>
     <t xml:space="preserve">6.29197549819946</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42237949371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61798524856567</t>
+    <t xml:space="preserve">6.42237901687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61798429489136</t>
   </si>
   <si>
     <t xml:space="preserve">6.88344955444336</t>
@@ -140,64 +140,64 @@
     <t xml:space="preserve">6.71113014221191</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83687734603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70181608200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62729978561401</t>
+    <t xml:space="preserve">6.83687591552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70181512832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62729930877686</t>
   </si>
   <si>
     <t xml:space="preserve">6.99522399902344</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8927640914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80427551269531</t>
+    <t xml:space="preserve">6.89276313781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80427503585815</t>
   </si>
   <si>
     <t xml:space="preserve">6.79961824417114</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84153366088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65990018844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63195705413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79496097564697</t>
+    <t xml:space="preserve">6.84153413772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65989971160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63195657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79496049880981</t>
   </si>
   <si>
     <t xml:space="preserve">6.78564596176147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86016321182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00919580459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.111656665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08371210098267</t>
+    <t xml:space="preserve">6.86016273498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00919628143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11165523529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08371162414551</t>
   </si>
   <si>
     <t xml:space="preserve">7.2094578742981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10699892044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04179620742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24206018447876</t>
+    <t xml:space="preserve">7.10699844360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04179668426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24205923080444</t>
   </si>
   <si>
     <t xml:space="preserve">7.09768390655518</t>
@@ -212,124 +212,124 @@
     <t xml:space="preserve">6.91605043411255</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00453805923462</t>
+    <t xml:space="preserve">7.00453853607178</t>
   </si>
   <si>
     <t xml:space="preserve">7.27000331878662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32589101791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22808790206909</t>
+    <t xml:space="preserve">7.3258900642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22808837890625</t>
   </si>
   <si>
     <t xml:space="preserve">7.50286674499512</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41437911987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48423767089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57738304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55409574508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73107385635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60066986083984</t>
+    <t xml:space="preserve">7.41437864303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48423719406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57738399505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55409622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73107290267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60066843032837</t>
   </si>
   <si>
     <t xml:space="preserve">7.64258480072021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70313024520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73572969436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88476228713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88942193984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8707914352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78696060180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94530725479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88010549545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08968257904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01760482788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09717082977295</t>
+    <t xml:space="preserve">7.7031307220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73573064804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88476419448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8894214630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87079095840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78695917129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94530820846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88010692596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08968448638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01760292053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09717178344727</t>
   </si>
   <si>
     <t xml:space="preserve">8.10653209686279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05036735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17205715179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21418285369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23758602142334</t>
+    <t xml:space="preserve">8.05036926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17205905914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21418190002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23758506774902</t>
   </si>
   <si>
     <t xml:space="preserve">8.22354412078857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15801811218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07844829559326</t>
+    <t xml:space="preserve">8.15801620483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07845020294189</t>
   </si>
   <si>
     <t xml:space="preserve">8.0831298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14397621154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01292419433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91463422775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8210244178772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64316940307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62912654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6525297164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55891990661621</t>
+    <t xml:space="preserve">8.14397430419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01292514801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91463470458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82102632522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64316749572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62912702560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65252923965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55892086029053</t>
   </si>
   <si>
     <t xml:space="preserve">7.63848829269409</t>
@@ -338,79 +338,79 @@
     <t xml:space="preserve">7.98952102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94739866256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05972766876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67593097686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71337604522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72273635864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87250900268555</t>
+    <t xml:space="preserve">7.94739818572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05972671508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67593193054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71337461471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72273588180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87250995635986</t>
   </si>
   <si>
     <t xml:space="preserve">7.92867708206177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89123106002808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81166458129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71805572509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88187122344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96143960952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91931438446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90995407104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05504608154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18142032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16737937927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19546031951904</t>
+    <t xml:space="preserve">7.89123249053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81166505813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71805620193481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88187170028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96143865585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91931533813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90995359420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05504703521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18142127990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16737842559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19546222686768</t>
   </si>
   <si>
     <t xml:space="preserve">8.19078063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3077917098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36395645141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34991550445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33119297027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29374980926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15333652496338</t>
+    <t xml:space="preserve">8.30779266357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36395835876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3499174118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33119487762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29374885559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1533374786377</t>
   </si>
   <si>
     <t xml:space="preserve">8.28906917572021</t>
@@ -419,37 +419,37 @@
     <t xml:space="preserve">8.36863708496094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50905227661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60734081268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51373291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63542461395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75711441040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65414524078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78519725799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80860042572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92093086242676</t>
+    <t xml:space="preserve">8.5090503692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60733985900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51373195648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.635422706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75711345672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65414428710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78519821166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8085994720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92092990875244</t>
   </si>
   <si>
     <t xml:space="preserve">8.84604358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81796169281006</t>
+    <t xml:space="preserve">8.81795978546143</t>
   </si>
   <si>
     <t xml:space="preserve">8.74775409698486</t>
@@ -461,46 +461,46 @@
     <t xml:space="preserve">8.82264137268066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7337121963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77115535736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76179599761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65882587432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59329891204834</t>
+    <t xml:space="preserve">8.73371124267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77115726470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76179504394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65882396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59329795837402</t>
   </si>
   <si>
     <t xml:space="preserve">8.57457733154297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56053638458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48564720153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54181575775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5324535369873</t>
+    <t xml:space="preserve">8.5605354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48564910888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54181289672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53245258331299</t>
   </si>
   <si>
     <t xml:space="preserve">8.66818714141846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49969100952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61670017242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49500942230225</t>
+    <t xml:space="preserve">8.49968910217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61670112609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49501037597656</t>
   </si>
   <si>
     <t xml:space="preserve">8.5558557510376</t>
@@ -512,40 +512,40 @@
     <t xml:space="preserve">8.46692752838135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5277738571167</t>
+    <t xml:space="preserve">8.52777290344238</t>
   </si>
   <si>
     <t xml:space="preserve">8.56521701812744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69158935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0800666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24856185913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07070350646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01453876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89284801483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93965244293213</t>
+    <t xml:space="preserve">8.69158840179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08006477355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24856281280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07070541381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01453971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89284610748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93965339660645</t>
   </si>
   <si>
     <t xml:space="preserve">8.81328010559082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50437068939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42480373382568</t>
+    <t xml:space="preserve">8.50437164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42480278015137</t>
   </si>
   <si>
     <t xml:space="preserve">8.40140151977539</t>
@@ -554,61 +554,61 @@
     <t xml:space="preserve">8.39671993255615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58393859863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34523487091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46224594116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38267803192139</t>
+    <t xml:space="preserve">8.5839376449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34523582458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46224784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3826789855957</t>
   </si>
   <si>
     <t xml:space="preserve">8.47160816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9864559173584</t>
+    <t xml:space="preserve">8.98645687103271</t>
   </si>
   <si>
     <t xml:space="preserve">9.09878730773926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06134414672852</t>
+    <t xml:space="preserve">9.06134510040283</t>
   </si>
   <si>
     <t xml:space="preserve">8.51841259002686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16269779205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31247138977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4419093132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98484086990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95675849914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38736057281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41076278686523</t>
+    <t xml:space="preserve">8.16269874572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31247234344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44190979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98484182357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95675802230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38735961914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41076183319092</t>
   </si>
   <si>
     <t xml:space="preserve">8.44820499420166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48096942901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37331676483154</t>
+    <t xml:space="preserve">8.4809684753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37331581115723</t>
   </si>
   <si>
     <t xml:space="preserve">8.23290538787842</t>
@@ -617,22 +617,22 @@
     <t xml:space="preserve">8.1860990524292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37799835205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57925796508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64946460723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72435092926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67286777496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74307346343994</t>
+    <t xml:space="preserve">8.3779993057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57925701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64946556091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72435188293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67286586761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74307250976562</t>
   </si>
   <si>
     <t xml:space="preserve">8.71031093597412</t>
@@ -644,22 +644,22 @@
     <t xml:space="preserve">8.96773529052734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14091205596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26728248596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33748912811279</t>
+    <t xml:space="preserve">9.14091110229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26728343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33749008178711</t>
   </si>
   <si>
     <t xml:space="preserve">9.40769672393799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37961673736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29536533355713</t>
+    <t xml:space="preserve">9.37961578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29536724090576</t>
   </si>
   <si>
     <t xml:space="preserve">9.3608922958374</t>
@@ -671,46 +671,46 @@
     <t xml:space="preserve">9.48258399963379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4357795715332</t>
+    <t xml:space="preserve">9.43578052520752</t>
   </si>
   <si>
     <t xml:space="preserve">9.35621166229248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11283016204834</t>
+    <t xml:space="preserve">9.11282825469971</t>
   </si>
   <si>
     <t xml:space="preserve">9.10814762115479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15963459014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4638614654541</t>
+    <t xml:space="preserve">9.15963172912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46386337280273</t>
   </si>
   <si>
     <t xml:space="preserve">9.81021404266357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95999145507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82893562316895</t>
+    <t xml:space="preserve">9.95999050140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82893753051758</t>
   </si>
   <si>
     <t xml:space="preserve">9.91318416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64171981811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70724582672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7166051864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66044139862061</t>
+    <t xml:space="preserve">9.64171886444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70724487304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71660614013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66044044494629</t>
   </si>
   <si>
     <t xml:space="preserve">9.7914924621582</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">10.2595386505127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4280347824097</t>
+    <t xml:space="preserve">10.4280338287354</t>
   </si>
   <si>
     <t xml:space="preserve">10.4748373031616</t>
@@ -740,10 +740,10 @@
     <t xml:space="preserve">10.3625078201294</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3344259262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5778093338013</t>
+    <t xml:space="preserve">10.3344249725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.577808380127</t>
   </si>
   <si>
     <t xml:space="preserve">10.5122814178467</t>
@@ -755,49 +755,49 @@
     <t xml:space="preserve">10.8118305206299</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8867177963257</t>
+    <t xml:space="preserve">10.8867168426514</t>
   </si>
   <si>
     <t xml:space="preserve">10.7182216644287</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6526956558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6433353424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6246137619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7088603973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8960800170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8399143218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9335222244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9990482330322</t>
+    <t xml:space="preserve">10.6526947021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6433343887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6246128082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7088594436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8960790634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8399133682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9335231781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9990491867065</t>
   </si>
   <si>
     <t xml:space="preserve">11.1301012039185</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0926580429077</t>
+    <t xml:space="preserve">11.0926561355591</t>
   </si>
   <si>
     <t xml:space="preserve">11.2517919540405</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9616050720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2049884796143</t>
+    <t xml:space="preserve">10.9616031646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2049894332886</t>
   </si>
   <si>
     <t xml:space="preserve">11.1675443649292</t>
@@ -809,31 +809,31 @@
     <t xml:space="preserve">11.1862668991089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2798757553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4296493530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4109258651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4577322006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5801229476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8249082565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8625640869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9472990036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9190540313721</t>
+    <t xml:space="preserve">11.2798748016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.429651260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4109268188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4577312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5801239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8249063491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8625659942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9472980499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9190549850464</t>
   </si>
   <si>
     <t xml:space="preserve">11.9284687042236</t>
@@ -842,43 +842,43 @@
     <t xml:space="preserve">11.9378833770752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9661264419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602760314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0979337692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0226144790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2109107971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1826658248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2391557693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9096403121948</t>
+    <t xml:space="preserve">11.9661283493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0602741241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0979347229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0226163864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2109117507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1826667785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2391538619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9096393585205</t>
   </si>
   <si>
     <t xml:space="preserve">12.1450071334839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4859752655029</t>
+    <t xml:space="preserve">11.4859762191772</t>
   </si>
   <si>
     <t xml:space="preserve">11.2976818084717</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6930999755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7307596206665</t>
+    <t xml:space="preserve">11.6931009292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7307586669922</t>
   </si>
   <si>
     <t xml:space="preserve">11.7684192657471</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">11.627197265625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5707092285156</t>
+    <t xml:space="preserve">11.5707082748413</t>
   </si>
   <si>
     <t xml:space="preserve">11.5236349105835</t>
@@ -905,28 +905,28 @@
     <t xml:space="preserve">11.0811424255371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834342956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6951379776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5633325576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6104068756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7422122955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9116773605347</t>
+    <t xml:space="preserve">10.88343334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6951389312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5633316040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6104078292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7422113418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.911678314209</t>
   </si>
   <si>
     <t xml:space="preserve">10.9022626876831</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9493350982666</t>
+    <t xml:space="preserve">10.9493370056152</t>
   </si>
   <si>
     <t xml:space="preserve">11.1376304626465</t>
@@ -938,40 +938,40 @@
     <t xml:space="preserve">11.3824138641357</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3447542190552</t>
+    <t xml:space="preserve">11.3447551727295</t>
   </si>
   <si>
     <t xml:space="preserve">11.4106588363647</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2694368362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5048065185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4294881820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3353404998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2788515090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2506084442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1093864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.034068107605</t>
+    <t xml:space="preserve">11.2694387435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5048055648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4294891357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3353395462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2788524627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2506074905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1093883514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0340690612793</t>
   </si>
   <si>
     <t xml:space="preserve">10.9210920333862</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6668949127197</t>
+    <t xml:space="preserve">10.6668930053711</t>
   </si>
   <si>
     <t xml:space="preserve">10.8363590240479</t>
@@ -980,43 +980,43 @@
     <t xml:space="preserve">10.78928565979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1941194534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1658754348755</t>
+    <t xml:space="preserve">11.1941213607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1658744812012</t>
   </si>
   <si>
     <t xml:space="preserve">11.0717277526855</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1282157897949</t>
+    <t xml:space="preserve">11.1282167434692</t>
   </si>
   <si>
     <t xml:space="preserve">11.3165111541748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3259258270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2411909103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0623140335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.090558052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1752910614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4389028549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7213449478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8154916763306</t>
+    <t xml:space="preserve">11.3259239196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2411918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0623121261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0905561447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1752901077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4389019012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7213439941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8154926300049</t>
   </si>
   <si>
     <t xml:space="preserve">11.984956741333</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">12.0132007598877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9567127227783</t>
+    <t xml:space="preserve">11.956711769104</t>
   </si>
   <si>
     <t xml:space="preserve">12.0508604049683</t>
@@ -1034,10 +1034,10 @@
     <t xml:space="preserve">12.0414447784424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0791063308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9755439758301</t>
+    <t xml:space="preserve">12.0791034698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9755420684814</t>
   </si>
   <si>
     <t xml:space="preserve">11.8343200683594</t>
@@ -1046,40 +1046,40 @@
     <t xml:space="preserve">12.2203254699707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1544227600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1073484420776</t>
+    <t xml:space="preserve">12.1544218063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.107349395752</t>
   </si>
   <si>
     <t xml:space="preserve">12.4839391708374</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5215969085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6439876556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7852087020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8134546279907</t>
+    <t xml:space="preserve">12.5215978622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.643988609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7852096557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8134536743164</t>
   </si>
   <si>
     <t xml:space="preserve">12.8322830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8040399551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1920804977417</t>
+    <t xml:space="preserve">12.8040409088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1920824050903</t>
   </si>
   <si>
     <t xml:space="preserve">11.7872486114502</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8531503677368</t>
+    <t xml:space="preserve">11.8531522750854</t>
   </si>
   <si>
     <t xml:space="preserve">12.0320310592651</t>
@@ -1088,34 +1088,34 @@
     <t xml:space="preserve">12.1732521057129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2768144607544</t>
+    <t xml:space="preserve">12.2768135070801</t>
   </si>
   <si>
     <t xml:space="preserve">11.9002246856689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4483156204224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5612945556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4012432098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6742696762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.77783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0885190963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0696897506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2014961242676</t>
+    <t xml:space="preserve">11.448317527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5612926483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4012422561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6742706298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7778329849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0885210037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0696887969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2014970779419</t>
   </si>
   <si>
     <t xml:space="preserve">12.1355934143066</t>
@@ -1127,10 +1127,10 @@
     <t xml:space="preserve">12.3333024978638</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1638374328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7401752471924</t>
+    <t xml:space="preserve">12.163836479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7401733398438</t>
   </si>
   <si>
     <t xml:space="preserve">12.1261777877808</t>
@@ -1139,52 +1139,52 @@
     <t xml:space="preserve">12.5404262542725</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5498418807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5027675628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6345729827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1335554122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1241407394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.086480140686</t>
+    <t xml:space="preserve">12.549840927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5027685165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6345739364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1335544586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1241397857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0864820480347</t>
   </si>
   <si>
     <t xml:space="preserve">12.9546747207642</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4254121780396</t>
+    <t xml:space="preserve">13.4254131317139</t>
   </si>
   <si>
     <t xml:space="preserve">13.4630708694458</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5383892059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5572175979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6042928695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5101432800293</t>
+    <t xml:space="preserve">13.538387298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5572166442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6042919158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5101451873779</t>
   </si>
   <si>
     <t xml:space="preserve">13.2559471130371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.472484588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3030195236206</t>
+    <t xml:space="preserve">13.4724855422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3030204772949</t>
   </si>
   <si>
     <t xml:space="preserve">12.9735040664673</t>
@@ -1196,13 +1196,13 @@
     <t xml:space="preserve">12.4086208343506</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3803768157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4651079177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5121841430664</t>
+    <t xml:space="preserve">12.3803749084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.46510887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5121822357178</t>
   </si>
   <si>
     <t xml:space="preserve">12.822868347168</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">12.8793563842773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8511123657227</t>
+    <t xml:space="preserve">12.8511114120483</t>
   </si>
   <si>
     <t xml:space="preserve">12.5969152450562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2862281799316</t>
+    <t xml:space="preserve">12.286229133606</t>
   </si>
   <si>
     <t xml:space="preserve">12.2579851150513</t>
@@ -1226,82 +1226,82 @@
     <t xml:space="preserve">12.728720664978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0394058227539</t>
+    <t xml:space="preserve">13.0394077301025</t>
   </si>
   <si>
     <t xml:space="preserve">13.0958967208862</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2653608322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4065818786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3312644958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3218488693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1617984771729</t>
+    <t xml:space="preserve">13.2653617858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4065828323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3312635421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.321849822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1617994308472</t>
   </si>
   <si>
     <t xml:space="preserve">13.3406791687012</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2465314865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8887720108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8605289459229</t>
+    <t xml:space="preserve">13.2465324401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8887710571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8605279922485</t>
   </si>
   <si>
     <t xml:space="preserve">13.293604850769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5666332244873</t>
+    <t xml:space="preserve">13.5666313171387</t>
   </si>
   <si>
     <t xml:space="preserve">13.6419506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3124361038208</t>
+    <t xml:space="preserve">13.3124351501465</t>
   </si>
   <si>
     <t xml:space="preserve">13.7925863265991</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9997100830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1409330368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3951292037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3009834289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5645933151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6022529602051</t>
+    <t xml:space="preserve">13.9997110366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1409320831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3951301574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3009815216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5645952224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6022539138794</t>
   </si>
   <si>
     <t xml:space="preserve">14.6869859695435</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9129390716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8564491271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1106491088867</t>
+    <t xml:space="preserve">14.9129400253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8564500808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1106481552124</t>
   </si>
   <si>
     <t xml:space="preserve">14.969428062439</t>
@@ -1310,64 +1310,64 @@
     <t xml:space="preserve">14.997673034668</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0353298187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9035263061523</t>
+    <t xml:space="preserve">15.0353317260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.903525352478</t>
   </si>
   <si>
     <t xml:space="preserve">14.8941106796265</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7152299880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5928382873535</t>
+    <t xml:space="preserve">14.7152309417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5928392410278</t>
   </si>
   <si>
     <t xml:space="preserve">15.1671380996704</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2707004547119</t>
+    <t xml:space="preserve">15.2706985473633</t>
   </si>
   <si>
     <t xml:space="preserve">15.2424554824829</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2518711090088</t>
+    <t xml:space="preserve">15.2518720626831</t>
   </si>
   <si>
     <t xml:space="preserve">15.4401636123657</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3930902481079</t>
+    <t xml:space="preserve">15.3930921554565</t>
   </si>
   <si>
     <t xml:space="preserve">15.5531425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6567039489746</t>
+    <t xml:space="preserve">15.6567029953003</t>
   </si>
   <si>
     <t xml:space="preserve">15.4213352203369</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0165004730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3460187911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8185272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6668338775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3444852828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6099491119385</t>
+    <t xml:space="preserve">15.0165014266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3460159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.818528175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6668348312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3444871902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6099481582642</t>
   </si>
   <si>
     <t xml:space="preserve">14.7332000732422</t>
@@ -1376,31 +1376,31 @@
     <t xml:space="preserve">14.8754119873047</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9273300170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4013719558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6194295883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6289119720459</t>
+    <t xml:space="preserve">13.9273309707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4013710021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6194305419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6289110183716</t>
   </si>
   <si>
     <t xml:space="preserve">15.1882801055908</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4916658401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1174011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4587116241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1553249359131</t>
+    <t xml:space="preserve">15.4916677474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1173992156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4587097167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1553230285645</t>
   </si>
   <si>
     <t xml:space="preserve">16.1648044586182</t>
@@ -1415,55 +1415,55 @@
     <t xml:space="preserve">16.3259792327881</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1079196929932</t>
+    <t xml:space="preserve">16.1079216003418</t>
   </si>
   <si>
     <t xml:space="preserve">16.0699977874756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.525074005127</t>
+    <t xml:space="preserve">16.5250778198242</t>
   </si>
   <si>
     <t xml:space="preserve">16.7241706848145</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6672897338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5724773406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3070182800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2596111297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6767673492432</t>
+    <t xml:space="preserve">16.6672878265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5724811553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3070163726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2596130371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6767711639404</t>
   </si>
   <si>
     <t xml:space="preserve">16.8379440307617</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8853454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0465221405029</t>
+    <t xml:space="preserve">16.885347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0465202331543</t>
   </si>
   <si>
     <t xml:space="preserve">16.9232711791992</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7715797424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.373384475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4492301940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2216892242432</t>
+    <t xml:space="preserve">16.771577835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3733825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4492321014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2216873168945</t>
   </si>
   <si>
     <t xml:space="preserve">16.4018249511719</t>
@@ -1478,10 +1478,10 @@
     <t xml:space="preserve">16.5155944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1034069061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5395259857178</t>
+    <t xml:space="preserve">17.1034049987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5395221710205</t>
   </si>
   <si>
     <t xml:space="preserve">17.9472007751465</t>
@@ -1493,10 +1493,10 @@
     <t xml:space="preserve">18.0799293518066</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1652565002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.715145111084</t>
+    <t xml:space="preserve">18.1652584075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7151470184326</t>
   </si>
   <si>
     <t xml:space="preserve">18.1368160247803</t>
@@ -1517,34 +1517,34 @@
     <t xml:space="preserve">17.6343307495117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7860260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7575817108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2979888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3738384246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2031841278076</t>
+    <t xml:space="preserve">17.7860240936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7575836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2979869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3738346099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2031803131104</t>
   </si>
   <si>
     <t xml:space="preserve">18.032527923584</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1083698272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2126636505127</t>
+    <t xml:space="preserve">18.1083736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2126617431641</t>
   </si>
   <si>
     <t xml:space="preserve">18.0609683990479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9377155303955</t>
+    <t xml:space="preserve">17.9377193450928</t>
   </si>
   <si>
     <t xml:space="preserve">18.0040836334229</t>
@@ -1556,109 +1556,109 @@
     <t xml:space="preserve">18.3927974700928</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8334293365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0135650634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7435894012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3408794403076</t>
+    <t xml:space="preserve">17.8334274291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0135631561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7435913085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3408813476562</t>
   </si>
   <si>
     <t xml:space="preserve">19.41672706604</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3788032531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1891841888428</t>
+    <t xml:space="preserve">19.3788051605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1891860961914</t>
   </si>
   <si>
     <t xml:space="preserve">19.0564556121826</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7246246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.449686050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5255279541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.772029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9616470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6867027282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1462955474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5065689086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0420093536377</t>
+    <t xml:space="preserve">18.7246265411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4496822357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5255317687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7720317840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.96164894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6867046356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.146297454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5065670013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0420074462891</t>
   </si>
   <si>
     <t xml:space="preserve">17.3025035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5629959106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.453742980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5864763259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.671802520752</t>
+    <t xml:space="preserve">16.5629978179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4537420272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5864753723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6718006134033</t>
   </si>
   <si>
     <t xml:space="preserve">15.0081443786621</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4252996444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4632234573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8045320510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7286853790283</t>
+    <t xml:space="preserve">15.4253015518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4632244110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8045339584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7286863327026</t>
   </si>
   <si>
     <t xml:space="preserve">14.9512596130371</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0745105743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9986629486084</t>
+    <t xml:space="preserve">15.0745096206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9986619949341</t>
   </si>
   <si>
     <t xml:space="preserve">14.9797010421753</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0176248550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8469696044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6573543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7047567367554</t>
+    <t xml:space="preserve">15.0176239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8469715118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6573534011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7047576904297</t>
   </si>
   <si>
     <t xml:space="preserve">14.6763153076172</t>
@@ -1670,52 +1670,52 @@
     <t xml:space="preserve">14.9322967529297</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0555477142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7900848388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8135614395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7282333374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1309404373169</t>
+    <t xml:space="preserve">15.0555486679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7900857925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8135595321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7282314300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1309413909912</t>
   </si>
   <si>
     <t xml:space="preserve">13.0835361480713</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3869218826294</t>
+    <t xml:space="preserve">13.3869228363037</t>
   </si>
   <si>
     <t xml:space="preserve">13.263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3964033126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6523857116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4912128448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2257490158081</t>
+    <t xml:space="preserve">13.3964042663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6523876190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4912109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2257499694824</t>
   </si>
   <si>
     <t xml:space="preserve">13.8704452514648</t>
   </si>
   <si>
-    <t xml:space="preserve">14.012656211853</t>
+    <t xml:space="preserve">14.0126581192017</t>
   </si>
   <si>
     <t xml:space="preserve">14.4961795806885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2212352752686</t>
+    <t xml:space="preserve">14.2212362289429</t>
   </si>
   <si>
     <t xml:space="preserve">14.1643505096436</t>
@@ -1727,22 +1727,22 @@
     <t xml:space="preserve">14.3350048065186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7945985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7377128601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5955009460449</t>
+    <t xml:space="preserve">13.7945995330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7377138137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5955018997192</t>
   </si>
   <si>
     <t xml:space="preserve">13.7566757202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8988876342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9462909698486</t>
+    <t xml:space="preserve">13.898886680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9462919235229</t>
   </si>
   <si>
     <t xml:space="preserve">14.4203329086304</t>
@@ -1751,31 +1751,31 @@
     <t xml:space="preserve">13.7756357192993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7232646942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.320556640625</t>
+    <t xml:space="preserve">12.7232666015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3205585479736</t>
   </si>
   <si>
     <t xml:space="preserve">13.1878261566162</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7471933364868</t>
+    <t xml:space="preserve">13.7471952438354</t>
   </si>
   <si>
     <t xml:space="preserve">14.0695428848267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8374910354614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2546463012695</t>
+    <t xml:space="preserve">14.8374881744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2546443939209</t>
   </si>
   <si>
     <t xml:space="preserve">14.8848924636841</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0839900970459</t>
+    <t xml:space="preserve">15.0839910507202</t>
   </si>
   <si>
     <t xml:space="preserve">15.1787986755371</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">15.1503562927246</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3115301132202</t>
+    <t xml:space="preserve">15.3115310668945</t>
   </si>
   <si>
     <t xml:space="preserve">15.3589353561401</t>
@@ -1793,13 +1793,13 @@
     <t xml:space="preserve">15.2925672531128</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1408748626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0271062850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9228172302246</t>
+    <t xml:space="preserve">15.1408767700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0271053314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9228162765503</t>
   </si>
   <si>
     <t xml:space="preserve">14.8280086517334</t>
@@ -1814,34 +1814,34 @@
     <t xml:space="preserve">15.614914894104</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7097272872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0650281906128</t>
+    <t xml:space="preserve">15.7097253799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0650291442871</t>
   </si>
   <si>
     <t xml:space="preserve">15.216721534729</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5485496520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4347829818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3968563079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7806034088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9038553237915</t>
+    <t xml:space="preserve">15.5485506057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4347810745239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3968572616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7806043624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9038543701172</t>
   </si>
   <si>
     <t xml:space="preserve">15.2262029647827</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1977615356445</t>
+    <t xml:space="preserve">15.1977605819702</t>
   </si>
   <si>
     <t xml:space="preserve">15.4442625045776</t>
@@ -1850,25 +1850,25 @@
     <t xml:space="preserve">15.3684148788452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.510627746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.738166809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.430269241333</t>
+    <t xml:space="preserve">15.5106287002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7381687164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4302654266357</t>
   </si>
   <si>
     <t xml:space="preserve">15.9657068252563</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2641267776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7855701446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6862506866455</t>
+    <t xml:space="preserve">15.2641277313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7855730056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6862487792969</t>
   </si>
   <si>
     <t xml:space="preserve">16.8474254608154</t>
@@ -1877,19 +1877,19 @@
     <t xml:space="preserve">16.4966316223145</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1932468414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2311706542969</t>
+    <t xml:space="preserve">16.1932506561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2311744689941</t>
   </si>
   <si>
     <t xml:space="preserve">16.7526149749756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4207859039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.809497833252</t>
+    <t xml:space="preserve">16.4207878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8094997406006</t>
   </si>
   <si>
     <t xml:space="preserve">16.7336521148682</t>
@@ -1901,94 +1901,94 @@
     <t xml:space="preserve">16.8663864135742</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2501316070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.899341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8898611068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9277839660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.851936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3544216156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2406539916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9183053970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5016021728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6627750396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.089412689209</t>
+    <t xml:space="preserve">16.250129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8993425369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8898620605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9277811050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8519372940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3544235229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2406482696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9183044433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5016002655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6627731323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0894107818604</t>
   </si>
   <si>
     <t xml:space="preserve">17.3119831085205</t>
   </si>
   <si>
-    <t xml:space="preserve">17.283540725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8239498138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6677436828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5743827819824</t>
+    <t xml:space="preserve">17.2835388183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8239459991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6677398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5743846893311</t>
   </si>
   <si>
     <t xml:space="preserve">18.8704280853271</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5962142944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.50071144104</t>
+    <t xml:space="preserve">19.5962162017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5007152557373</t>
   </si>
   <si>
     <t xml:space="preserve">18.9277248382568</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9468269348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9850234985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5934810638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7080783843994</t>
+    <t xml:space="preserve">18.9468250274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9850215911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5934829711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.708080291748</t>
   </si>
   <si>
     <t xml:space="preserve">18.9659252166748</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0327758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2333202362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3861179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0900707244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1951198577881</t>
+    <t xml:space="preserve">19.032772064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2333183288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.386116027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0900726318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1951217651367</t>
   </si>
   <si>
     <t xml:space="preserve">19.1187229156494</t>
@@ -1997,40 +1997,40 @@
     <t xml:space="preserve">19.252420425415</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9018058776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1501007080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2647018432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5893936157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5511932373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.799488067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9591064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8445091247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4816131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3097171783447</t>
+    <t xml:space="preserve">19.9018077850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1501045227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2646980285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.589391708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5511951446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7994899749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9591045379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8445072174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4816150665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3097190856934</t>
   </si>
   <si>
     <t xml:space="preserve">19.6344108581543</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6726131439209</t>
+    <t xml:space="preserve">19.6726112365723</t>
   </si>
   <si>
     <t xml:space="preserve">20.0928058624268</t>
@@ -2048,31 +2048,31 @@
     <t xml:space="preserve">19.7299098968506</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3028964996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2838001251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2264976501465</t>
+    <t xml:space="preserve">20.3028984069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2837982177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2264995574951</t>
   </si>
   <si>
     <t xml:space="preserve">20.7039909362793</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6848926544189</t>
+    <t xml:space="preserve">20.6848907470703</t>
   </si>
   <si>
     <t xml:space="preserve">20.4174976348877</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0355052947998</t>
+    <t xml:space="preserve">20.0355033874512</t>
   </si>
   <si>
     <t xml:space="preserve">20.1310024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1883010864258</t>
+    <t xml:space="preserve">20.1882991790771</t>
   </si>
   <si>
     <t xml:space="preserve">21.2769813537598</t>
@@ -2081,16 +2081,16 @@
     <t xml:space="preserve">21.1814804077148</t>
   </si>
   <si>
-    <t xml:space="preserve">20.436595916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0164051055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5702934265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9904861450195</t>
+    <t xml:space="preserve">20.4365940093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0164031982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5702953338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9904842376709</t>
   </si>
   <si>
     <t xml:space="preserve">21.1050834655762</t>
@@ -2099,16 +2099,16 @@
     <t xml:space="preserve">21.1623821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2578811645508</t>
+    <t xml:space="preserve">21.2578792572021</t>
   </si>
   <si>
     <t xml:space="preserve">21.0286846160889</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2960796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.849967956543</t>
+    <t xml:space="preserve">21.2960777282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8499660491943</t>
   </si>
   <si>
     <t xml:space="preserve">22.4802551269531</t>
@@ -2126,10 +2126,10 @@
     <t xml:space="preserve">22.2510585784912</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9645671844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9454650878906</t>
+    <t xml:space="preserve">21.9645652770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9454689025879</t>
   </si>
   <si>
     <t xml:space="preserve">22.3083591461182</t>
@@ -2141,52 +2141,52 @@
     <t xml:space="preserve">22.7476501464844</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8049488067627</t>
+    <t xml:space="preserve">22.8049468994141</t>
   </si>
   <si>
     <t xml:space="preserve">22.0600624084473</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2319602966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3533782958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4747943878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4556941986084</t>
+    <t xml:space="preserve">22.2319622039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3533802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.474796295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.455696105957</t>
   </si>
   <si>
     <t xml:space="preserve">21.1241836547852</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7803897857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8758869171143</t>
+    <t xml:space="preserve">20.780387878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8758888244629</t>
   </si>
   <si>
     <t xml:space="preserve">21.0859813690186</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7353706359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5061740875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2196807861328</t>
+    <t xml:space="preserve">21.7353687286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5061721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2196826934814</t>
   </si>
   <si>
     <t xml:space="preserve">21.3724765777588</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6016731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6780738830566</t>
+    <t xml:space="preserve">21.6016750335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.678071975708</t>
   </si>
   <si>
     <t xml:space="preserve">21.4870758056641</t>
@@ -2195,85 +2195,85 @@
     <t xml:space="preserve">21.5825729370117</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6466903686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6084938049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4938945770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8567886352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3792972564697</t>
+    <t xml:space="preserve">20.6466941833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.608491897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.493896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8567867279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3792991638184</t>
   </si>
   <si>
     <t xml:space="preserve">20.8949871063232</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9331855773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3219985961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3410987854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.830867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0218658447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5375556945801</t>
+    <t xml:space="preserve">20.9331874847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.32200050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3410968780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8308696746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0218620300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5375537872314</t>
   </si>
   <si>
     <t xml:space="preserve">22.6521511077881</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0150451660156</t>
+    <t xml:space="preserve">23.0150489807129</t>
   </si>
   <si>
     <t xml:space="preserve">23.4543361663818</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7217311859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.912727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5689334869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.084623336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7981300354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8745288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9700241088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3711185455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8677101135254</t>
+    <t xml:space="preserve">23.7217330932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9127292633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5689373016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0846252441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.798131942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8745269775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.970027923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3711166381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.867712020874</t>
   </si>
   <si>
     <t xml:space="preserve">25.09690284729</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3642978668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3329181671143</t>
+    <t xml:space="preserve">25.3642997741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3329162597656</t>
   </si>
   <si>
     <t xml:space="preserve">24.9823055267334</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">25.2879009246826</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9250068664551</t>
+    <t xml:space="preserve">24.9250087738037</t>
   </si>
   <si>
     <t xml:space="preserve">25.0205078125</t>
@@ -2294,10 +2294,10 @@
     <t xml:space="preserve">24.9441089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8295078277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6385116577148</t>
+    <t xml:space="preserve">24.8295097351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6385154724121</t>
   </si>
   <si>
     <t xml:space="preserve">24.4475173950195</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">24.5430145263672</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3520183563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6576137542725</t>
+    <t xml:space="preserve">24.3520202636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6576099395752</t>
   </si>
   <si>
     <t xml:space="preserve">24.6767120361328</t>
@@ -2321,19 +2321,19 @@
     <t xml:space="preserve">24.5621147155762</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5812149047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6958103179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3070011138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3451976776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8486099243164</t>
+    <t xml:space="preserve">24.5812129974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6958122253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.306999206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3451995849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8486080169678</t>
   </si>
   <si>
     <t xml:space="preserve">25.0014057159424</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">25.6125946044922</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5552959442139</t>
+    <t xml:space="preserve">25.5552940368652</t>
   </si>
   <si>
     <t xml:space="preserve">25.154203414917</t>
@@ -2369,43 +2369,43 @@
     <t xml:space="preserve">25.6698913574219</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2237815856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2810802459717</t>
+    <t xml:space="preserve">26.2237796783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.281078338623</t>
   </si>
   <si>
     <t xml:space="preserve">26.3956775665283</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1405620574951</t>
+    <t xml:space="preserve">27.1405639648438</t>
   </si>
   <si>
     <t xml:space="preserve">27.2169628143311</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5225582122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6944541931152</t>
+    <t xml:space="preserve">27.522554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6944522857666</t>
   </si>
   <si>
     <t xml:space="preserve">27.8281497955322</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1910457611084</t>
+    <t xml:space="preserve">28.1910438537598</t>
   </si>
   <si>
     <t xml:space="preserve">28.7831325531006</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2865409851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8854503631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9754867553711</t>
+    <t xml:space="preserve">28.2865428924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8854522705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9754886627197</t>
   </si>
   <si>
     <t xml:space="preserve">25.2306003570557</t>
@@ -2414,58 +2414,58 @@
     <t xml:space="preserve">24.6003150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6071338653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4666156768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4352397918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8254070281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3479175567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5852918624878</t>
+    <t xml:space="preserve">23.6071319580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4666175842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4352359771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8254089355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3479194641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5852909088135</t>
   </si>
   <si>
     <t xml:space="preserve">17.323356628418</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7285385131836</t>
+    <t xml:space="preserve">15.7285375595093</t>
   </si>
   <si>
     <t xml:space="preserve">16.120080947876</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9031658172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5239028930664</t>
+    <t xml:space="preserve">16.903169631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.523904800415</t>
   </si>
   <si>
     <t xml:space="preserve">17.7435493469238</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1350917816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8322257995605</t>
+    <t xml:space="preserve">18.1350898742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8322277069092</t>
   </si>
   <si>
     <t xml:space="preserve">18.1446418762207</t>
   </si>
   <si>
-    <t xml:space="preserve">18.221040725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1159915924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8772468566895</t>
+    <t xml:space="preserve">18.2210388183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1159896850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8772449493408</t>
   </si>
   <si>
     <t xml:space="preserve">17.3806591033936</t>
@@ -2474,28 +2474,28 @@
     <t xml:space="preserve">17.4093036651611</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8076686859131</t>
+    <t xml:space="preserve">16.8076667785645</t>
   </si>
   <si>
     <t xml:space="preserve">17.6480522155762</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7844791412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4311351776123</t>
+    <t xml:space="preserve">18.784481048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4311332702637</t>
   </si>
   <si>
     <t xml:space="preserve">18.4454612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7653789520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9536457061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8663368225098</t>
+    <t xml:space="preserve">18.7653770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9536437988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8663387298584</t>
   </si>
   <si>
     <t xml:space="preserve">19.271520614624</t>
@@ -2519,10 +2519,10 @@
     <t xml:space="preserve">19.7681102752686</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6753406524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7640209197998</t>
+    <t xml:space="preserve">20.6753425598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7640171051025</t>
   </si>
   <si>
     <t xml:space="preserve">21.3820266723633</t>
@@ -2534,13 +2534,13 @@
     <t xml:space="preserve">21.7926692962646</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0191345214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4297771453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8595161437988</t>
+    <t xml:space="preserve">21.019136428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4297752380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8595180511475</t>
   </si>
   <si>
     <t xml:space="preserve">20.9522838592529</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">21.658971786499</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0341472625732</t>
+    <t xml:space="preserve">23.034143447876</t>
   </si>
   <si>
     <t xml:space="preserve">23.1391925811768</t>
@@ -2564,19 +2564,19 @@
     <t xml:space="preserve">23.5020866394043</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8267784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5211849212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8458786010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8172264099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3588390350342</t>
+    <t xml:space="preserve">23.8267822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.521183013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8458766937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8172283172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3588352203369</t>
   </si>
   <si>
     <t xml:space="preserve">22.6903514862061</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">22.6330528259277</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8881683349609</t>
+    <t xml:space="preserve">21.8881664276123</t>
   </si>
   <si>
     <t xml:space="preserve">22.0696144104004</t>
@@ -2594,25 +2594,25 @@
     <t xml:space="preserve">22.6999015808105</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9386463165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3015403747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6808013916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.709451675415</t>
+    <t xml:space="preserve">22.938648223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3015384674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6808032989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7094497680664</t>
   </si>
   <si>
     <t xml:space="preserve">23.1487426757812</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4638843536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4229564666748</t>
+    <t xml:space="preserve">23.463888168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4229583740234</t>
   </si>
   <si>
     <t xml:space="preserve">22.4611568450928</t>
@@ -2621,43 +2621,43 @@
     <t xml:space="preserve">22.6426029205322</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7381000518799</t>
+    <t xml:space="preserve">22.7380981445312</t>
   </si>
   <si>
     <t xml:space="preserve">23.272891998291</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2442378997803</t>
+    <t xml:space="preserve">23.2442398071289</t>
   </si>
   <si>
     <t xml:space="preserve">23.5402851104736</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7408294677734</t>
+    <t xml:space="preserve">23.7408332824707</t>
   </si>
   <si>
     <t xml:space="preserve">23.8363285064697</t>
   </si>
   <si>
-    <t xml:space="preserve">23.71217918396</t>
+    <t xml:space="preserve">23.7121810913086</t>
   </si>
   <si>
     <t xml:space="preserve">23.7599296569824</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1610221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3233661651611</t>
+    <t xml:space="preserve">24.1610202789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3233680725098</t>
   </si>
   <si>
     <t xml:space="preserve">24.7340106964111</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2783489227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0682582855225</t>
+    <t xml:space="preserve">25.2783508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0682544708252</t>
   </si>
   <si>
     <t xml:space="preserve">25.0587043762207</t>
@@ -2666,10 +2666,10 @@
     <t xml:space="preserve">24.7531108856201</t>
   </si>
   <si>
-    <t xml:space="preserve">25.135103225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5580253601074</t>
+    <t xml:space="preserve">25.1351013183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5580234527588</t>
   </si>
   <si>
     <t xml:space="preserve">26.510274887085</t>
@@ -2678,22 +2678,22 @@
     <t xml:space="preserve">27.6467037200928</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2292404174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.503454208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5894031524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1596641540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5512065887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0164165496826</t>
+    <t xml:space="preserve">28.2292423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5034580230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5894050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1596660614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5512046813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0164184570312</t>
   </si>
   <si>
     <t xml:space="preserve">27.035514831543</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">27.054615020752</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2838115692139</t>
+    <t xml:space="preserve">27.2838096618652</t>
   </si>
   <si>
     <t xml:space="preserve">26.5675754547119</t>
@@ -2726,109 +2726,109 @@
     <t xml:space="preserve">26.4529781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6630725860596</t>
+    <t xml:space="preserve">26.6630744934082</t>
   </si>
   <si>
     <t xml:space="preserve">26.5389270782471</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2619781494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4625244140625</t>
+    <t xml:space="preserve">26.26198387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4625282287598</t>
   </si>
   <si>
     <t xml:space="preserve">27.5989551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6726245880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7585697174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.388858795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4461612701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1814937591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3533897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5061874389648</t>
+    <t xml:space="preserve">26.6726226806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7585716247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3888607025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4461574554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1814918518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3533916473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5061855316162</t>
   </si>
   <si>
     <t xml:space="preserve">28.9932270050049</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7926788330078</t>
+    <t xml:space="preserve">28.7926807403564</t>
   </si>
   <si>
     <t xml:space="preserve">28.6971836090088</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5798530578613</t>
+    <t xml:space="preserve">27.5798511505127</t>
   </si>
   <si>
     <t xml:space="preserve">27.6562519073486</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4748058319092</t>
+    <t xml:space="preserve">27.4748077392578</t>
   </si>
   <si>
     <t xml:space="preserve">27.6849040985107</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3847694396973</t>
+    <t xml:space="preserve">29.3847713470459</t>
   </si>
   <si>
     <t xml:space="preserve">29.9673080444336</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1746730804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4802665710449</t>
+    <t xml:space="preserve">29.1746711730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4802684783936</t>
   </si>
   <si>
     <t xml:space="preserve">29.833610534668</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0246047973633</t>
+    <t xml:space="preserve">30.0246067047119</t>
   </si>
   <si>
     <t xml:space="preserve">29.1651248931885</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3274707794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8049602508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4734477996826</t>
+    <t xml:space="preserve">29.3274688720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8049583435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.473445892334</t>
   </si>
   <si>
     <t xml:space="preserve">30.9891376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7503929138184</t>
+    <t xml:space="preserve">30.750394821167</t>
   </si>
   <si>
     <t xml:space="preserve">30.5402965545654</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9222888946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7408409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9318370819092</t>
+    <t xml:space="preserve">30.922290802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7408390045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9318389892578</t>
   </si>
   <si>
     <t xml:space="preserve">30.7217426300049</t>
@@ -2837,58 +2837,58 @@
     <t xml:space="preserve">30.6835460662842</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8172397613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4829978942871</t>
+    <t xml:space="preserve">30.8172416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4829959869385</t>
   </si>
   <si>
     <t xml:space="preserve">30.5593967437744</t>
   </si>
   <si>
-    <t xml:space="preserve">28.725830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2128715515137</t>
+    <t xml:space="preserve">28.7258319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2128734588623</t>
   </si>
   <si>
     <t xml:space="preserve">30.9031887054443</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9918689727783</t>
+    <t xml:space="preserve">31.9918651580811</t>
   </si>
   <si>
     <t xml:space="preserve">32.899097442627</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6535339355469</t>
+    <t xml:space="preserve">33.6535377502441</t>
   </si>
   <si>
     <t xml:space="preserve">33.309741973877</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4693603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3288421630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.558032989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1310272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4338836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8158798217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.930477142334</t>
+    <t xml:space="preserve">32.4693565368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3288383483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5580368041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1310234069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4338874816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4461708068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8158836364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9304809570312</t>
   </si>
   <si>
     <t xml:space="preserve">32.6603546142578</t>
@@ -2900,22 +2900,22 @@
     <t xml:space="preserve">32.8513526916504</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5143814086914</t>
+    <t xml:space="preserve">31.5143795013428</t>
   </si>
   <si>
     <t xml:space="preserve">31.6098728179932</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9727687835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7367553710938</t>
+    <t xml:space="preserve">31.9727668762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7367477416992</t>
   </si>
   <si>
     <t xml:space="preserve">32.0587158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2565307617188</t>
+    <t xml:space="preserve">31.2565326690674</t>
   </si>
   <si>
     <t xml:space="preserve">30.884090423584</t>
@@ -2924,10 +2924,10 @@
     <t xml:space="preserve">31.017786026001</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1323833465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8745422363281</t>
+    <t xml:space="preserve">31.1323852539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8745403289795</t>
   </si>
   <si>
     <t xml:space="preserve">31.0846347808838</t>
@@ -2936,10 +2936,10 @@
     <t xml:space="preserve">31.6194267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0969161987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3615798950195</t>
+    <t xml:space="preserve">32.0969200134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3615818023682</t>
   </si>
   <si>
     <t xml:space="preserve">32.1542091369629</t>
@@ -2954,22 +2954,22 @@
     <t xml:space="preserve">31.695821762085</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2115097045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7435722351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2783622741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5075607299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4120597839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0491638183594</t>
+    <t xml:space="preserve">32.2115135192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7435741424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2783584594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5075569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4120559692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0491676330566</t>
   </si>
   <si>
     <t xml:space="preserve">31.5334777832031</t>
@@ -2978,19 +2978,19 @@
     <t xml:space="preserve">31.2087841033936</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3165588378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1637687683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1064643859863</t>
+    <t xml:space="preserve">32.3165626525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1637649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1064682006836</t>
   </si>
   <si>
     <t xml:space="preserve">32.3834114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6221504211426</t>
+    <t xml:space="preserve">32.6221580505371</t>
   </si>
   <si>
     <t xml:space="preserve">32.6508026123047</t>
@@ -2999,13 +2999,13 @@
     <t xml:space="preserve">32.8036003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5839538574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3547592163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0682640075684</t>
+    <t xml:space="preserve">32.5839500427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3547668457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0682678222656</t>
   </si>
   <si>
     <t xml:space="preserve">32.0396194458008</t>
@@ -3014,16 +3014,16 @@
     <t xml:space="preserve">32.5648536682129</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3261070251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9250202178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.042350769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7967834472656</t>
+    <t xml:space="preserve">32.3261108398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9250240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0423469543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7967796325684</t>
   </si>
   <si>
     <t xml:space="preserve">34.5989646911621</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">34.9427604675293</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8854560852051</t>
+    <t xml:space="preserve">34.8854598999023</t>
   </si>
   <si>
     <t xml:space="preserve">35.0000610351562</t>
@@ -3044,28 +3044,28 @@
     <t xml:space="preserve">35.80224609375</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5539512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3343048095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2551765441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9018249511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3670349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3192901611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7817707061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8104209899902</t>
+    <t xml:space="preserve">35.5539474487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3342971801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2551727294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9018287658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3670387268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3192939758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.781774520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8104228973389</t>
   </si>
   <si>
     <t xml:space="preserve">32.4598083496094</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">28.6876335144043</t>
   </si>
   <si>
-    <t xml:space="preserve">29.002779006958</t>
+    <t xml:space="preserve">29.0027770996094</t>
   </si>
   <si>
     <t xml:space="preserve">30.3875007629395</t>
@@ -3092,16 +3092,16 @@
     <t xml:space="preserve">30.6453437805176</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4761772155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5211944580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7312908172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1228370666504</t>
+    <t xml:space="preserve">31.4761753082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5211963653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7312927246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1228332519531</t>
   </si>
   <si>
     <t xml:space="preserve">30.5498466491699</t>
@@ -3116,40 +3116,40 @@
     <t xml:space="preserve">31.6671772003174</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4065990447998</t>
+    <t xml:space="preserve">30.4066009521484</t>
   </si>
   <si>
     <t xml:space="preserve">30.7694911956787</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6644439697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3111019134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9413890838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.275634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9604892730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5812244415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3424797058105</t>
+    <t xml:space="preserve">30.6644458770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3111000061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9413909912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2756309509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9604873657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5812282562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3424816131592</t>
   </si>
   <si>
     <t xml:space="preserve">33.5007400512695</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9373016357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8731842041016</t>
+    <t xml:space="preserve">32.9372978210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8731803894043</t>
   </si>
   <si>
     <t xml:space="preserve">33.6344375610352</t>
@@ -3158,34 +3158,34 @@
     <t xml:space="preserve">33.624885559082</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1787719726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2169799804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9905052185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8281593322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.302921295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1091957092285</t>
+    <t xml:space="preserve">34.1787757873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2169761657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9905090332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8281669616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3029174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1091918945312</t>
   </si>
   <si>
     <t xml:space="preserve">33.5484924316406</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8063316345215</t>
+    <t xml:space="preserve">33.806339263916</t>
   </si>
   <si>
     <t xml:space="preserve">33.233341217041</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0928268432617</t>
+    <t xml:space="preserve">34.092830657959</t>
   </si>
   <si>
     <t xml:space="preserve">33.5771369934082</t>
@@ -3194,34 +3194,34 @@
     <t xml:space="preserve">32.2688179016113</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9059162139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8868198394775</t>
+    <t xml:space="preserve">31.9059200286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8868179321289</t>
   </si>
   <si>
     <t xml:space="preserve">32.0873603820801</t>
   </si>
   <si>
-    <t xml:space="preserve">32.946849822998</t>
+    <t xml:space="preserve">32.9468536376953</t>
   </si>
   <si>
     <t xml:space="preserve">33.1378479003906</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7995147705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8851928710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6538238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9620552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7691192626953</t>
+    <t xml:space="preserve">34.7995109558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8851890563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6538200378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9620590209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.769115447998</t>
   </si>
   <si>
     <t xml:space="preserve">37.0765647888184</t>
@@ -3230,22 +3230,22 @@
     <t xml:space="preserve">37.4224433898926</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1245994567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.018913269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6818580627441</t>
+    <t xml:space="preserve">37.1246032714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0189170837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6818542480469</t>
   </si>
   <si>
     <t xml:space="preserve">38.2391090393066</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7683296203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.883617401123</t>
+    <t xml:space="preserve">37.7683258056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8836212158203</t>
   </si>
   <si>
     <t xml:space="preserve">38.0181274414062</t>
@@ -3254,82 +3254,82 @@
     <t xml:space="preserve">39.2479286193848</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6138153076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.642635345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3440055847168</t>
+    <t xml:space="preserve">38.6138114929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6426391601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3440093994141</t>
   </si>
   <si>
     <t xml:space="preserve">38.5946006774902</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7963638305664</t>
+    <t xml:space="preserve">38.7963600158691</t>
   </si>
   <si>
     <t xml:space="preserve">38.7195014953613</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6042098999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6130294799805</t>
+    <t xml:space="preserve">38.6042060852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6130256652832</t>
   </si>
   <si>
     <t xml:space="preserve">39.6514587402344</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7475357055664</t>
+    <t xml:space="preserve">39.7475318908691</t>
   </si>
   <si>
     <t xml:space="preserve">40.4969482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">40.006950378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8051834106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9685134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6034202575684</t>
+    <t xml:space="preserve">40.0069427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8051795959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9685173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6034240722656</t>
   </si>
   <si>
     <t xml:space="preserve">39.7571487426758</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9973449707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0749893188477</t>
+    <t xml:space="preserve">39.9973411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0749855041504</t>
   </si>
   <si>
     <t xml:space="preserve">36.5769577026367</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5665588378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5569534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3736190795898</t>
+    <t xml:space="preserve">37.5665626525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.556957244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3736152648926</t>
   </si>
   <si>
     <t xml:space="preserve">38.9789123535156</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1614570617676</t>
+    <t xml:space="preserve">39.1614608764648</t>
   </si>
   <si>
     <t xml:space="preserve">38.479305267334</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4496955871582</t>
+    <t xml:space="preserve">39.4496994018555</t>
   </si>
   <si>
     <t xml:space="preserve">39.1806755065918</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">39.4304809570312</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7675361633301</t>
+    <t xml:space="preserve">38.7675399780273</t>
   </si>
   <si>
     <t xml:space="preserve">40.0453796386719</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">40.3528289794922</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7083168029785</t>
+    <t xml:space="preserve">40.7083129882812</t>
   </si>
   <si>
     <t xml:space="preserve">40.2567520141602</t>
@@ -3365,37 +3365,37 @@
     <t xml:space="preserve">40.333610534668</t>
   </si>
   <si>
-    <t xml:space="preserve">40.266357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4489059448242</t>
+    <t xml:space="preserve">40.2663536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.448902130127</t>
   </si>
   <si>
     <t xml:space="preserve">41.0157661437988</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1406707763672</t>
+    <t xml:space="preserve">41.1406669616699</t>
   </si>
   <si>
     <t xml:space="preserve">41.3424339294434</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2271423339844</t>
+    <t xml:space="preserve">41.2271385192871</t>
   </si>
   <si>
     <t xml:space="preserve">41.2367477416992</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5634117126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0822372436523</t>
+    <t xml:space="preserve">41.5634078979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0822334289551</t>
   </si>
   <si>
     <t xml:space="preserve">43.0814476013184</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2455673217773</t>
+    <t xml:space="preserve">42.2455711364746</t>
   </si>
   <si>
     <t xml:space="preserve">42.0341987609863</t>
@@ -3404,19 +3404,19 @@
     <t xml:space="preserve">41.7651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9669456481934</t>
+    <t xml:space="preserve">41.9669418334961</t>
   </si>
   <si>
     <t xml:space="preserve">42.4665489196777</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5434150695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6683158874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9853744506836</t>
+    <t xml:space="preserve">42.5434112548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6683120727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9853706359863</t>
   </si>
   <si>
     <t xml:space="preserve">42.3896865844727</t>
@@ -3425,82 +3425,82 @@
     <t xml:space="preserve">42.8989028930664</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0245933532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9765510559082</t>
+    <t xml:space="preserve">42.0245895385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9765472412109</t>
   </si>
   <si>
     <t xml:space="preserve">41.5345916748047</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4577331542969</t>
+    <t xml:space="preserve">41.4577293395996</t>
   </si>
   <si>
     <t xml:space="preserve">39.7187118530273</t>
   </si>
   <si>
-    <t xml:space="preserve">41.006160736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0165557861328</t>
+    <t xml:space="preserve">41.0061645507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0165596008301</t>
   </si>
   <si>
     <t xml:space="preserve">40.8332214355469</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0638084411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0718460083008</t>
+    <t xml:space="preserve">41.0638122558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0718421936035</t>
   </si>
   <si>
     <t xml:space="preserve">43.1679191589355</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3112487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2159576416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9477233886719</t>
+    <t xml:space="preserve">44.3112449645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2159614562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9477272033691</t>
   </si>
   <si>
     <t xml:space="preserve">39.7859687805176</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2759628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5842056274414</t>
+    <t xml:space="preserve">40.2759666442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5842018127441</t>
   </si>
   <si>
     <t xml:space="preserve">39.1902847290039</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5169486999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6802825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1030235290527</t>
+    <t xml:space="preserve">39.5169525146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6802787780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.10302734375</t>
   </si>
   <si>
     <t xml:space="preserve">39.0077362060547</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0653839111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9108695983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2087097167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2463531494141</t>
+    <t xml:space="preserve">39.0653800964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9108734130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2087135314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2463569641113</t>
   </si>
   <si>
     <t xml:space="preserve">41.6210632324219</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">41.169490814209</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2263565063477</t>
+    <t xml:space="preserve">42.2263526916504</t>
   </si>
   <si>
     <t xml:space="preserve">42.9469375610352</t>
@@ -3524,10 +3524,10 @@
     <t xml:space="preserve">42.3800811767578</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3992919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0045852661133</t>
+    <t xml:space="preserve">42.3992958068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.004581451416</t>
   </si>
   <si>
     <t xml:space="preserve">43.9653663635254</t>
@@ -3539,10 +3539,10 @@
     <t xml:space="preserve">44.7147750854492</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2632102966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.725170135498</t>
+    <t xml:space="preserve">44.2632141113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7251739501953</t>
   </si>
   <si>
     <t xml:space="preserve">44.0038032531738</t>
@@ -3560,16 +3560,16 @@
     <t xml:space="preserve">42.860466003418</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8028182983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6794929504395</t>
+    <t xml:space="preserve">42.8028221130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6794967651367</t>
   </si>
   <si>
     <t xml:space="preserve">41.6018447875977</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5449829101562</t>
+    <t xml:space="preserve">40.5449905395508</t>
   </si>
   <si>
     <t xml:space="preserve">41.0830230712891</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">41.4289016723633</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4192962646484</t>
+    <t xml:space="preserve">41.4193000793457</t>
   </si>
   <si>
     <t xml:space="preserve">40.1318511962891</t>
@@ -3590,13 +3590,13 @@
     <t xml:space="preserve">41.2655754089355</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1798896789551</t>
+    <t xml:space="preserve">40.1798858642578</t>
   </si>
   <si>
     <t xml:space="preserve">40.1414566040039</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3143997192383</t>
+    <t xml:space="preserve">40.314395904541</t>
   </si>
   <si>
     <t xml:space="preserve">41.0926322937012</t>
@@ -3614,16 +3614,16 @@
     <t xml:space="preserve">42.3704719543457</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5626258850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5330200195312</t>
+    <t xml:space="preserve">42.562629699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5330123901367</t>
   </si>
   <si>
     <t xml:space="preserve">43.6579170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">44.416934967041</t>
+    <t xml:space="preserve">44.4169387817383</t>
   </si>
   <si>
     <t xml:space="preserve">45.0702667236328</t>
@@ -3632,16 +3632,16 @@
     <t xml:space="preserve">45.3681106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5890884399414</t>
+    <t xml:space="preserve">45.5890922546387</t>
   </si>
   <si>
     <t xml:space="preserve">44.8108558654785</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8885078430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0518379211426</t>
+    <t xml:space="preserve">43.8885040283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0518341064453</t>
   </si>
   <si>
     <t xml:space="preserve">42.5914497375488</t>
@@ -3650,19 +3650,19 @@
     <t xml:space="preserve">41.8708648681641</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0261611938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2671432495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9308700561523</t>
+    <t xml:space="preserve">40.0261650085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.267147064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9308738708496</t>
   </si>
   <si>
     <t xml:space="preserve">38.383228302002</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1814613342285</t>
+    <t xml:space="preserve">38.1814651489258</t>
   </si>
   <si>
     <t xml:space="preserve">37.2014694213867</t>
@@ -3677,16 +3677,16 @@
     <t xml:space="preserve">35.001277923584</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0397071838379</t>
+    <t xml:space="preserve">35.0397109985352</t>
   </si>
   <si>
     <t xml:space="preserve">34.4632377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0581359863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7018585205078</t>
+    <t xml:space="preserve">36.0581321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7018623352051</t>
   </si>
   <si>
     <t xml:space="preserve">37.8644027709961</t>
@@ -3704,10 +3704,10 @@
     <t xml:space="preserve">33.7138252258301</t>
   </si>
   <si>
-    <t xml:space="preserve">35.116569519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7706871032715</t>
+    <t xml:space="preserve">35.1165657043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7706832885742</t>
   </si>
   <si>
     <t xml:space="preserve">33.9636306762695</t>
@@ -3716,13 +3716,13 @@
     <t xml:space="preserve">33.377555847168</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7418670654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2710800170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2806930541992</t>
+    <t xml:space="preserve">34.7418632507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2710838317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.280689239502</t>
   </si>
   <si>
     <t xml:space="preserve">34.146183013916</t>
@@ -3734,10 +3734,10 @@
     <t xml:space="preserve">33.8291206359863</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5689239501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2510757446289</t>
+    <t xml:space="preserve">34.568920135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2510795593262</t>
   </si>
   <si>
     <t xml:space="preserve">35.933235168457</t>
@@ -3746,13 +3746,13 @@
     <t xml:space="preserve">36.9420585632324</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4712715148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4520568847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1253890991211</t>
+    <t xml:space="preserve">36.4712677001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4520530700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1253852844238</t>
   </si>
   <si>
     <t xml:space="preserve">34.7802963256836</t>
@@ -3761,13 +3761,13 @@
     <t xml:space="preserve">33.588924407959</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6449966430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7042198181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4344139099121</t>
+    <t xml:space="preserve">35.6450004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7042236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4344100952148</t>
   </si>
   <si>
     <t xml:space="preserve">35.1357841491699</t>
@@ -3776,10 +3776,10 @@
     <t xml:space="preserve">34.9244117736816</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2695045471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3175468444824</t>
+    <t xml:space="preserve">36.2695083618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3175430297852</t>
   </si>
   <si>
     <t xml:space="preserve">35.981273651123</t>
@@ -3803,19 +3803,19 @@
     <t xml:space="preserve">39.0173416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9500885009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2375335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2943954467773</t>
+    <t xml:space="preserve">38.9500846862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2375373840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2943916320801</t>
   </si>
   <si>
     <t xml:space="preserve">40.890869140625</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6891059875488</t>
+    <t xml:space="preserve">40.6891021728516</t>
   </si>
   <si>
     <t xml:space="preserve">39.8340072631836</t>
@@ -3830,13 +3830,13 @@
     <t xml:space="preserve">39.2191047668457</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6234245300293</t>
+    <t xml:space="preserve">38.623420715332</t>
   </si>
   <si>
     <t xml:space="preserve">37.9796981811523</t>
   </si>
   <si>
-    <t xml:space="preserve">36.807544708252</t>
+    <t xml:space="preserve">36.8075485229492</t>
   </si>
   <si>
     <t xml:space="preserve">36.6442108154297</t>
@@ -3854,13 +3854,13 @@
     <t xml:space="preserve">36.7210731506348</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1350021362305</t>
+    <t xml:space="preserve">36.1349983215332</t>
   </si>
   <si>
     <t xml:space="preserve">35.7218627929688</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3183364868164</t>
+    <t xml:space="preserve">35.3183326721191</t>
   </si>
   <si>
     <t xml:space="preserve">34.0693168640137</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">32.2726554870605</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9836349487305</t>
+    <t xml:space="preserve">32.9836387634277</t>
   </si>
   <si>
     <t xml:space="preserve">32.9740257263184</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">32.9163780212402</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9644203186035</t>
+    <t xml:space="preserve">32.9644165039062</t>
   </si>
   <si>
     <t xml:space="preserve">31.2734413146973</t>
@@ -3905,13 +3905,13 @@
     <t xml:space="preserve">30.9489860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2492733001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3558254241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6948623657227</t>
+    <t xml:space="preserve">31.2492713928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3558235168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.694860458374</t>
   </si>
   <si>
     <t xml:space="preserve">31.0555400848389</t>
@@ -3926,13 +3926,13 @@
     <t xml:space="preserve">30.6099510192871</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3484115600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4646530151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7865829467773</t>
+    <t xml:space="preserve">30.34840965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4646511077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7865810394287</t>
   </si>
   <si>
     <t xml:space="preserve">28.2948322296143</t>
@@ -3941,13 +3941,13 @@
     <t xml:space="preserve">26.260627746582</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5438137054443</t>
+    <t xml:space="preserve">25.5438117980957</t>
   </si>
   <si>
     <t xml:space="preserve">26.3090591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3985118865967</t>
+    <t xml:space="preserve">25.398509979248</t>
   </si>
   <si>
     <t xml:space="preserve">25.4760036468506</t>
@@ -3956,7 +3956,7 @@
     <t xml:space="preserve">25.4663181304932</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5341262817383</t>
+    <t xml:space="preserve">25.5341243743896</t>
   </si>
   <si>
     <t xml:space="preserve">25.8828449249268</t>
@@ -3965,10 +3965,10 @@
     <t xml:space="preserve">27.9364242553711</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8663444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.934154510498</t>
+    <t xml:space="preserve">28.8663463592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9341564178467</t>
   </si>
   <si>
     <t xml:space="preserve">28.3529510498047</t>
@@ -3977,22 +3977,22 @@
     <t xml:space="preserve">28.2560863494873</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3335781097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4378604888916</t>
+    <t xml:space="preserve">28.3335800170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4378623962402</t>
   </si>
   <si>
     <t xml:space="preserve">29.9900035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7358798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.588306427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2127990722656</t>
+    <t xml:space="preserve">30.7358779907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5883083343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.212797164917</t>
   </si>
   <si>
     <t xml:space="preserve">30.1740493774414</t>
@@ -4001,19 +4001,19 @@
     <t xml:space="preserve">30.3387241363525</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2173385620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7523765563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3238925933838</t>
+    <t xml:space="preserve">28.2173366546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7523746490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3238906860352</t>
   </si>
   <si>
     <t xml:space="preserve">28.924467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8469715118408</t>
+    <t xml:space="preserve">28.8469753265381</t>
   </si>
   <si>
     <t xml:space="preserve">29.6994037628174</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">31.2008399963379</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4236354827881</t>
+    <t xml:space="preserve">31.4236335754395</t>
   </si>
   <si>
     <t xml:space="preserve">29.9706287384033</t>
@@ -4052,10 +4052,10 @@
     <t xml:space="preserve">29.4281749725342</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7381477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9922752380371</t>
+    <t xml:space="preserve">29.738151550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9922733306885</t>
   </si>
   <si>
     <t xml:space="preserve">29.4572353363037</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">29.7672100067139</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1979637145996</t>
+    <t xml:space="preserve">28.1979675292969</t>
   </si>
   <si>
     <t xml:space="preserve">27.8879909515381</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">27.442403793335</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8030796051025</t>
+    <t xml:space="preserve">26.8030815124512</t>
   </si>
   <si>
     <t xml:space="preserve">26.7740211486816</t>
@@ -4097,10 +4097,10 @@
     <t xml:space="preserve">25.2338352203369</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6816959381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0885372161865</t>
+    <t xml:space="preserve">24.6816940307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0885353088379</t>
   </si>
   <si>
     <t xml:space="preserve">25.0497894287109</t>
@@ -4118,49 +4118,49 @@
     <t xml:space="preserve">25.2144641876221</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5073356628418</t>
+    <t xml:space="preserve">24.5073337554932</t>
   </si>
   <si>
     <t xml:space="preserve">24.2554817199707</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1779861450195</t>
+    <t xml:space="preserve">24.1779880523682</t>
   </si>
   <si>
     <t xml:space="preserve">23.8970718383789</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4201545715332</t>
+    <t xml:space="preserve">24.4201526641846</t>
   </si>
   <si>
     <t xml:space="preserve">23.8292675018311</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0908069610596</t>
+    <t xml:space="preserve">24.0908088684082</t>
   </si>
   <si>
     <t xml:space="preserve">24.0133152008057</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1973609924316</t>
+    <t xml:space="preserve">24.197359085083</t>
   </si>
   <si>
     <t xml:space="preserve">24.8463687896729</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8053512573242</t>
+    <t xml:space="preserve">25.8053493499756</t>
   </si>
   <si>
     <t xml:space="preserve">25.291955947876</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0572071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5728721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7159023284912</t>
+    <t xml:space="preserve">26.0572032928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5728702545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7159004211426</t>
   </si>
   <si>
     <t xml:space="preserve">26.1928195953369</t>
@@ -4169,28 +4169,28 @@
     <t xml:space="preserve">25.9312782287598</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6309909820557</t>
+    <t xml:space="preserve">25.630989074707</t>
   </si>
   <si>
     <t xml:space="preserve">25.3307037353516</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6235733032227</t>
+    <t xml:space="preserve">24.6235752105713</t>
   </si>
   <si>
     <t xml:space="preserve">23.8389549255371</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9187183380127</t>
+    <t xml:space="preserve">22.9187164306641</t>
   </si>
   <si>
     <t xml:space="preserve">23.916446685791</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4395275115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3500785827637</t>
+    <t xml:space="preserve">24.4395294189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.350076675415</t>
   </si>
   <si>
     <t xml:space="preserve">24.8366813659668</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">25.3694515228271</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0594749450684</t>
+    <t xml:space="preserve">25.059476852417</t>
   </si>
   <si>
     <t xml:space="preserve">25.4275703430176</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">23.7517738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">23.906759262085</t>
+    <t xml:space="preserve">23.9067611694336</t>
   </si>
   <si>
     <t xml:space="preserve">24.3523483276367</t>
@@ -4226,7 +4226,7 @@
     <t xml:space="preserve">23.3643054962158</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4007797241211</t>
+    <t xml:space="preserve">24.4007816314697</t>
   </si>
   <si>
     <t xml:space="preserve">25.8150386810303</t>
@@ -4238,28 +4238,28 @@
     <t xml:space="preserve">27.2680416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1398448944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6748828887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7426891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7062149047852</t>
+    <t xml:space="preserve">28.1398429870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6748809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7426910400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7062129974365</t>
   </si>
   <si>
     <t xml:space="preserve">26.7643337249756</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5221672058105</t>
+    <t xml:space="preserve">26.5221652984619</t>
   </si>
   <si>
     <t xml:space="preserve">26.3187465667725</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8321399688721</t>
+    <t xml:space="preserve">26.8321418762207</t>
   </si>
   <si>
     <t xml:space="preserve">26.8805751800537</t>
@@ -4268,7 +4268,7 @@
     <t xml:space="preserve">27.0065002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1421146392822</t>
+    <t xml:space="preserve">27.1421165466309</t>
   </si>
   <si>
     <t xml:space="preserve">26.0087738037109</t>
@@ -4277,10 +4277,10 @@
     <t xml:space="preserve">26.7837066650391</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6458225250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9483833312988</t>
+    <t xml:space="preserve">27.645824432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9483814239502</t>
   </si>
   <si>
     <t xml:space="preserve">26.1540718078613</t>
@@ -4289,10 +4289,10 @@
     <t xml:space="preserve">26.6771545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6965274810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0936832427979</t>
+    <t xml:space="preserve">26.6965255737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0936813354492</t>
   </si>
   <si>
     <t xml:space="preserve">27.1324291229248</t>
@@ -4301,19 +4301,19 @@
     <t xml:space="preserve">27.6651954650879</t>
   </si>
   <si>
-    <t xml:space="preserve">27.975170135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.444673538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0959510803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0668926239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8925323486328</t>
+    <t xml:space="preserve">27.9751682281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4446716308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0959529876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0668907165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8925304412842</t>
   </si>
   <si>
     <t xml:space="preserve">26.4543590545654</t>
@@ -4328,7 +4328,7 @@
     <t xml:space="preserve">26.628719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8708896636963</t>
+    <t xml:space="preserve">26.8708877563477</t>
   </si>
   <si>
     <t xml:space="preserve">26.1443843841553</t>
@@ -4340,7 +4340,7 @@
     <t xml:space="preserve">26.9677543640137</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9797134399414</t>
+    <t xml:space="preserve">25.9797115325928</t>
   </si>
   <si>
     <t xml:space="preserve">26.1056385040283</t>
@@ -4349,46 +4349,46 @@
     <t xml:space="preserve">26.5996608734131</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6384048461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2412548065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6019306182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9044876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0788478851318</t>
+    <t xml:space="preserve">26.6384086608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2412528991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6019325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9044895172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0788497924805</t>
   </si>
   <si>
     <t xml:space="preserve">24.8851165771484</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9916687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9335498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7398147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4782752990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6070785522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9290084838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1227436065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7666053771973</t>
+    <t xml:space="preserve">24.9916706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9335479736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7398166656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4782772064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6070766448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9290065765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1227416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7666034698486</t>
   </si>
   <si>
     <t xml:space="preserve">26.483419418335</t>
@@ -4403,67 +4403,67 @@
     <t xml:space="preserve">26.202507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6190319061279</t>
+    <t xml:space="preserve">26.6190338134766</t>
   </si>
   <si>
     <t xml:space="preserve">26.5027942657471</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3358497619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1763229370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5466842651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4401340484619</t>
+    <t xml:space="preserve">27.3358478546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1763210296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5466861724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4401321411133</t>
   </si>
   <si>
     <t xml:space="preserve">28.7694797515869</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2367115020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1107845306396</t>
+    <t xml:space="preserve">28.2367095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1107864379883</t>
   </si>
   <si>
     <t xml:space="preserve">29.0310192108154</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4304466247559</t>
+    <t xml:space="preserve">28.4304447174072</t>
   </si>
   <si>
     <t xml:space="preserve">28.8954067230225</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1860084533691</t>
+    <t xml:space="preserve">29.1860065460205</t>
   </si>
   <si>
     <t xml:space="preserve">29.6606559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6583862304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9392986297607</t>
+    <t xml:space="preserve">30.6583843231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9393005371094</t>
   </si>
   <si>
     <t xml:space="preserve">30.8327445983887</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2589588165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4817543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6173667907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5689353942871</t>
+    <t xml:space="preserve">31.258960723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4817523956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6173648834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5689315795898</t>
   </si>
   <si>
     <t xml:space="preserve">32.1404495239258</t>
@@ -4472,19 +4472,19 @@
     <t xml:space="preserve">31.6754875183105</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2783317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9176540374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9854602813721</t>
+    <t xml:space="preserve">31.2783355712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9176559448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9854621887207</t>
   </si>
   <si>
     <t xml:space="preserve">31.7820453643799</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3729286193848</t>
+    <t xml:space="preserve">32.3729248046875</t>
   </si>
   <si>
     <t xml:space="preserve">32.508544921875</t>
@@ -4499,19 +4499,19 @@
     <t xml:space="preserve">32.7313385009766</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2373123168945</t>
+    <t xml:space="preserve">32.2373161315918</t>
   </si>
   <si>
     <t xml:space="preserve">32.0823287963867</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3780746459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7678146362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7655410766602</t>
+    <t xml:space="preserve">34.3780784606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7678184509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7655448913574</t>
   </si>
   <si>
     <t xml:space="preserve">34.7267951965332</t>
@@ -4526,34 +4526,34 @@
     <t xml:space="preserve">34.6686782836914</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8817825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6105575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8259353637695</t>
+    <t xml:space="preserve">34.881778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6105537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8259315490723</t>
   </si>
   <si>
     <t xml:space="preserve">33.0413131713867</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8475799560547</t>
+    <t xml:space="preserve">32.8475761413574</t>
   </si>
   <si>
     <t xml:space="preserve">33.1478652954102</t>
   </si>
   <si>
-    <t xml:space="preserve">33.167407989502</t>
+    <t xml:space="preserve">33.1674041748047</t>
   </si>
   <si>
     <t xml:space="preserve">32.297924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0536842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4577445983887</t>
+    <t xml:space="preserve">32.0536880493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4577465057373</t>
   </si>
   <si>
     <t xml:space="preserve">32.2393035888672</t>
@@ -4565,22 +4565,22 @@
     <t xml:space="preserve">32.1513786315918</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5359020233154</t>
+    <t xml:space="preserve">31.5359001159668</t>
   </si>
   <si>
     <t xml:space="preserve">31.6238231658936</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6789321899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9489631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2908935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0466537475586</t>
+    <t xml:space="preserve">32.6789283752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9489669799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2908973693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0466575622559</t>
   </si>
   <si>
     <t xml:space="preserve">34.1638946533203</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">34.6816749572754</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4179000854492</t>
+    <t xml:space="preserve">34.417896270752</t>
   </si>
   <si>
     <t xml:space="preserve">34.2225074768066</t>
@@ -4604,7 +4604,7 @@
     <t xml:space="preserve">33.7438049316406</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6656455993652</t>
+    <t xml:space="preserve">33.6656494140625</t>
   </si>
   <si>
     <t xml:space="preserve">33.216251373291</t>
@@ -4625,10 +4625,10 @@
     <t xml:space="preserve">32.4835395812988</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9853000640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.887601852417</t>
+    <t xml:space="preserve">31.9852981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8875999450684</t>
   </si>
   <si>
     <t xml:space="preserve">30.0997867584229</t>
@@ -4655,19 +4655,19 @@
     <t xml:space="preserve">31.1451206207275</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0474262237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3440246582031</t>
+    <t xml:space="preserve">31.0474281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3440227508545</t>
   </si>
   <si>
     <t xml:space="preserve">30.2560977935791</t>
   </si>
   <si>
-    <t xml:space="preserve">30.363561630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.451488494873</t>
+    <t xml:space="preserve">30.3635635375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4514865875244</t>
   </si>
   <si>
     <t xml:space="preserve">30.9204235076904</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">30.8520374298096</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7152652740479</t>
+    <t xml:space="preserve">30.7152633666992</t>
   </si>
   <si>
     <t xml:space="preserve">30.0802478790283</t>
@@ -4700,16 +4700,16 @@
     <t xml:space="preserve">29.2009925842285</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6406192779541</t>
+    <t xml:space="preserve">29.6406211853027</t>
   </si>
   <si>
     <t xml:space="preserve">29.3182277679443</t>
   </si>
   <si>
-    <t xml:space="preserve">29.415922164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0739898681641</t>
+    <t xml:space="preserve">29.4159240722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0739917755127</t>
   </si>
   <si>
     <t xml:space="preserve">28.5562057495117</t>
@@ -4721,7 +4721,7 @@
     <t xml:space="preserve">29.0935287475586</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2889194488525</t>
+    <t xml:space="preserve">29.2889175415039</t>
   </si>
   <si>
     <t xml:space="preserve">29.1814556121826</t>
@@ -4733,10 +4733,10 @@
     <t xml:space="preserve">29.7578544616699</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5722332000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3475360870361</t>
+    <t xml:space="preserve">29.5722351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3475379943848</t>
   </si>
   <si>
     <t xml:space="preserve">28.800443649292</t>
@@ -4760,19 +4760,19 @@
     <t xml:space="preserve">28.2240447998047</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3217391967773</t>
+    <t xml:space="preserve">28.321741104126</t>
   </si>
   <si>
     <t xml:space="preserve">28.5952854156494</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3119716644287</t>
+    <t xml:space="preserve">28.3119697570801</t>
   </si>
   <si>
     <t xml:space="preserve">27.9309597015381</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0677337646484</t>
+    <t xml:space="preserve">28.0677318572998</t>
   </si>
   <si>
     <t xml:space="preserve">29.650390625</t>
@@ -4814,13 +4814,13 @@
     <t xml:space="preserve">26.6706962585449</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5143852233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0028591156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1005554199219</t>
+    <t xml:space="preserve">26.51438331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.002857208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1005535125732</t>
   </si>
   <si>
     <t xml:space="preserve">27.4620246887207</t>
@@ -4829,7 +4829,7 @@
     <t xml:space="preserve">26.709774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2799186706543</t>
+    <t xml:space="preserve">26.2799167633057</t>
   </si>
   <si>
     <t xml:space="preserve">26.4557685852051</t>
@@ -4838,13 +4838,13 @@
     <t xml:space="preserve">26.6120796203613</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4362297058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6511573791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6609287261963</t>
+    <t xml:space="preserve">26.4362277984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.651159286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6609268188477</t>
   </si>
   <si>
     <t xml:space="preserve">26.2213001251221</t>
@@ -4853,31 +4853,31 @@
     <t xml:space="preserve">25.1661968231201</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7949562072754</t>
+    <t xml:space="preserve">24.7949542999268</t>
   </si>
   <si>
     <t xml:space="preserve">26.0259094238281</t>
   </si>
   <si>
-    <t xml:space="preserve">25.889139175415</t>
+    <t xml:space="preserve">25.8891372680664</t>
   </si>
   <si>
     <t xml:space="preserve">26.8953952789307</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0614757537842</t>
+    <t xml:space="preserve">27.0614776611328</t>
   </si>
   <si>
     <t xml:space="preserve">27.1200923919678</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9344730377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9149322509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.475305557251</t>
+    <t xml:space="preserve">26.9344711303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9149341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4753074645996</t>
   </si>
   <si>
     <t xml:space="preserve">26.3385334014893</t>
@@ -4886,13 +4886,13 @@
     <t xml:space="preserve">27.5890274047852</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7683906555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3776111602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8856258392334</t>
+    <t xml:space="preserve">26.7683925628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.377613067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8856239318848</t>
   </si>
   <si>
     <t xml:space="preserve">27.5206432342529</t>
@@ -4907,25 +4907,25 @@
     <t xml:space="preserve">27.6085662841797</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7648773193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9505004882812</t>
+    <t xml:space="preserve">27.7648792266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9504985809326</t>
   </si>
   <si>
     <t xml:space="preserve">27.5499515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8723449707031</t>
+    <t xml:space="preserve">27.8723430633545</t>
   </si>
   <si>
     <t xml:space="preserve">27.3154811859131</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0517082214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9735527038574</t>
+    <t xml:space="preserve">27.0517063140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9735507965088</t>
   </si>
   <si>
     <t xml:space="preserve">28.0775032043457</t>
@@ -4958,7 +4958,7 @@
     <t xml:space="preserve">30.6175689697266</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5296440124512</t>
+    <t xml:space="preserve">30.5296421051025</t>
   </si>
   <si>
     <t xml:space="preserve">29.796932220459</t>
@@ -4970,7 +4970,7 @@
     <t xml:space="preserve">30.8715763092041</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6761856079102</t>
+    <t xml:space="preserve">30.6761837005615</t>
   </si>
   <si>
     <t xml:space="preserve">30.8911151885986</t>
@@ -4997,7 +4997,7 @@
     <t xml:space="preserve">29.1912231445312</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1619167327881</t>
+    <t xml:space="preserve">29.1619148254395</t>
   </si>
   <si>
     <t xml:space="preserve">29.9337043762207</t>
@@ -5015,10 +5015,10 @@
     <t xml:space="preserve">29.0544509887695</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4612560272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.510103225708</t>
+    <t xml:space="preserve">30.4612579345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5101051330566</t>
   </si>
   <si>
     <t xml:space="preserve">30.7738800048828</t>
@@ -5030,13 +5030,13 @@
     <t xml:space="preserve">30.1584033966064</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4221801757812</t>
+    <t xml:space="preserve">30.4221782684326</t>
   </si>
   <si>
     <t xml:space="preserve">30.8813457489014</t>
   </si>
   <si>
-    <t xml:space="preserve">31.125581741333</t>
+    <t xml:space="preserve">31.1255836486816</t>
   </si>
   <si>
     <t xml:space="preserve">30.744571685791</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">30.2658672332764</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0439147949219</t>
+    <t xml:space="preserve">32.0439109802246</t>
   </si>
   <si>
     <t xml:space="preserve">32.893856048584</t>
@@ -5078,7 +5078,7 @@
     <t xml:space="preserve">32.2002258300781</t>
   </si>
   <si>
-    <t xml:space="preserve">33.030632019043</t>
+    <t xml:space="preserve">33.0306358337402</t>
   </si>
   <si>
     <t xml:space="preserve">32.8547821044922</t>
@@ -5090,7 +5090,7 @@
     <t xml:space="preserve">31.6433639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9888095855713</t>
+    <t xml:space="preserve">30.9888076782227</t>
   </si>
   <si>
     <t xml:space="preserve">31.2916622161865</t>
@@ -5099,16 +5099,16 @@
     <t xml:space="preserve">31.1158142089844</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3858489990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2357940673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2650985717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0208625793457</t>
+    <t xml:space="preserve">32.3858451843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2357902526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2651023864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0208587646484</t>
   </si>
   <si>
     <t xml:space="preserve">32.4933090209961</t>
@@ -5123,7 +5123,7 @@
     <t xml:space="preserve">31.1646614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7605991363525</t>
+    <t xml:space="preserve">31.7605953216553</t>
   </si>
   <si>
     <t xml:space="preserve">30.1290950775146</t>
@@ -5132,10 +5132,10 @@
     <t xml:space="preserve">30.4026412963867</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1193237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8422679901123</t>
+    <t xml:space="preserve">30.1193256378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8422660827637</t>
   </si>
   <si>
     <t xml:space="preserve">31.2818927764893</t>
@@ -5147,16 +5147,16 @@
     <t xml:space="preserve">30.3049449920654</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7836494445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.705493927002</t>
+    <t xml:space="preserve">30.7836513519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7054958343506</t>
   </si>
   <si>
     <t xml:space="preserve">30.8227272033691</t>
   </si>
   <si>
-    <t xml:space="preserve">33.069709777832</t>
+    <t xml:space="preserve">33.0697059631348</t>
   </si>
   <si>
     <t xml:space="preserve">32.591007232666</t>
@@ -5180,7 +5180,7 @@
     <t xml:space="preserve">33.5972595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5679512023926</t>
+    <t xml:space="preserve">33.5679550170898</t>
   </si>
   <si>
     <t xml:space="preserve">34.0310287475586</t>
@@ -6195,6 +6195,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.7200002670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.539999961853</t>
   </si>
 </sst>
 </file>
@@ -71559,7 +71562,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6932407407</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>1842632</v>
@@ -71580,6 +71583,32 @@
         <v>2051</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6911458333</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>1444780</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>14.7650003433228</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>14.4849996566772</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>14.7250003814697</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>14.539999961853</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>2061</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33520460128784</t>
+    <t xml:space="preserve">7.335205078125</t>
   </si>
   <si>
     <t xml:space="preserve">AMP.MI</t>
@@ -53,40 +53,40 @@
     <t xml:space="preserve">7.36780595779419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15357065200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96262311935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21877336502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27931833267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1628851890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03248310089111</t>
+    <t xml:space="preserve">7.15357112884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96262359619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21877241134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2793173789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16288614273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0324821472168</t>
   </si>
   <si>
     <t xml:space="preserve">7.08836936950684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1954870223999</t>
+    <t xml:space="preserve">7.19548654556274</t>
   </si>
   <si>
     <t xml:space="preserve">6.9859094619751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13494205474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34451866149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23740243911743</t>
+    <t xml:space="preserve">7.13494253158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34451913833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23740196228027</t>
   </si>
   <si>
     <t xml:space="preserve">7.35383367538452</t>
@@ -98,61 +98,61 @@
     <t xml:space="preserve">7.18151473999023</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40972137451172</t>
+    <t xml:space="preserve">7.40972185134888</t>
   </si>
   <si>
     <t xml:space="preserve">7.28397512435913</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13959836959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05111074447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84619092941284</t>
+    <t xml:space="preserve">7.13959980010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05111122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84619188308716</t>
   </si>
   <si>
     <t xml:space="preserve">6.51086759567261</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45497989654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59003973007202</t>
+    <t xml:space="preserve">6.45498037338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5900411605835</t>
   </si>
   <si>
     <t xml:space="preserve">6.33389139175415</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29197549819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42237901687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61798429489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88344955444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71113014221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83687591552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70181512832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62729930877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99522399902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89276313781738</t>
+    <t xml:space="preserve">6.29197597503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42237949371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61798524856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8834490776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71113061904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83687734603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70181608200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6272988319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9952244758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89276504516602</t>
   </si>
   <si>
     <t xml:space="preserve">6.80427503585815</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">6.65989971160889</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63195657730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79496049880981</t>
+    <t xml:space="preserve">6.63195610046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79496097564697</t>
   </si>
   <si>
     <t xml:space="preserve">6.78564596176147</t>
@@ -179,19 +179,19 @@
     <t xml:space="preserve">6.86016273498535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00919628143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11165523529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08371162414551</t>
+    <t xml:space="preserve">7.00919580459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11165618896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08371210098267</t>
   </si>
   <si>
     <t xml:space="preserve">7.2094578742981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10699844360352</t>
+    <t xml:space="preserve">7.10699892044067</t>
   </si>
   <si>
     <t xml:space="preserve">7.04179668426514</t>
@@ -203,13 +203,13 @@
     <t xml:space="preserve">7.09768390655518</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17220020294189</t>
+    <t xml:space="preserve">7.17219972610474</t>
   </si>
   <si>
     <t xml:space="preserve">6.93467903137207</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91605043411255</t>
+    <t xml:space="preserve">6.91605091094971</t>
   </si>
   <si>
     <t xml:space="preserve">7.00453853607178</t>
@@ -218,118 +218,118 @@
     <t xml:space="preserve">7.27000331878662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3258900642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22808837890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50286674499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41437864303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48423719406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57738399505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55409622192383</t>
+    <t xml:space="preserve">7.32588958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22808742523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50286769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41437816619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48423671722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57738351821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55409574508667</t>
   </si>
   <si>
     <t xml:space="preserve">7.73107290267944</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60066843032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64258480072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7031307220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73573064804077</t>
+    <t xml:space="preserve">7.60066986083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64258527755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70312976837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73573017120361</t>
   </si>
   <si>
     <t xml:space="preserve">7.88476419448853</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8894214630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87079095840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78695917129517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94530820846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88010692596436</t>
+    <t xml:space="preserve">7.88942050933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87079000473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78696012496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94530630111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88010549545288</t>
   </si>
   <si>
     <t xml:space="preserve">8.08968448638916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01760292053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09717178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10653209686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05036926269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17205905914307</t>
+    <t xml:space="preserve">8.01760387420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09717082977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10653305053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.050368309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17205715179443</t>
   </si>
   <si>
     <t xml:space="preserve">8.21418190002441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23758506774902</t>
+    <t xml:space="preserve">8.23758697509766</t>
   </si>
   <si>
     <t xml:space="preserve">8.22354412078857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15801620483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07845020294189</t>
+    <t xml:space="preserve">8.1580171585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07844924926758</t>
   </si>
   <si>
     <t xml:space="preserve">8.0831298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14397430419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01292514801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91463470458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82102632522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64316749572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62912702560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65252923965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55892086029053</t>
+    <t xml:space="preserve">8.14397525787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01292419433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91463375091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82102537155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64316844940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62912607192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6525297164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55892038345337</t>
   </si>
   <si>
     <t xml:space="preserve">7.63848829269409</t>
@@ -341,73 +341,73 @@
     <t xml:space="preserve">7.94739818572998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05972671508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67593193054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71337461471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72273588180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87250995635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92867708206177</t>
+    <t xml:space="preserve">8.05972766876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67593240737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71337509155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72273635864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87251043319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92867755889893</t>
   </si>
   <si>
     <t xml:space="preserve">7.89123249053955</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81166505813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71805620193481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88187170028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96143865585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91931533813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90995359420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05504703521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18142127990723</t>
+    <t xml:space="preserve">7.81166458129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7180552482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88187074661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96143960952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91931438446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90995311737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0550479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18141937255859</t>
   </si>
   <si>
     <t xml:space="preserve">8.16737842559814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19546222686768</t>
+    <t xml:space="preserve">8.19546031951904</t>
   </si>
   <si>
     <t xml:space="preserve">8.19078063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30779266357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36395835876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3499174118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33119487762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29374885559082</t>
+    <t xml:space="preserve">8.3077917098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36395740509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34991550445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3311939239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29375076293945</t>
   </si>
   <si>
     <t xml:space="preserve">8.1533374786377</t>
@@ -419,37 +419,37 @@
     <t xml:space="preserve">8.36863708496094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5090503692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60733985900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51373195648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.635422706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75711345672607</t>
+    <t xml:space="preserve">8.50905132293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60734176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51373291015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63542366027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75711441040039</t>
   </si>
   <si>
     <t xml:space="preserve">8.65414428710938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78519821166992</t>
+    <t xml:space="preserve">8.78519630432129</t>
   </si>
   <si>
     <t xml:space="preserve">8.8085994720459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92092990875244</t>
+    <t xml:space="preserve">8.92093086242676</t>
   </si>
   <si>
     <t xml:space="preserve">8.84604358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81795978546143</t>
+    <t xml:space="preserve">8.81796073913574</t>
   </si>
   <si>
     <t xml:space="preserve">8.74775409698486</t>
@@ -458,64 +458,64 @@
     <t xml:space="preserve">8.75243473052979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82264137268066</t>
+    <t xml:space="preserve">8.82264232635498</t>
   </si>
   <si>
     <t xml:space="preserve">8.73371124267578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77115726470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76179504394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65882396697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59329795837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57457733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5605354309082</t>
+    <t xml:space="preserve">8.77115535736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76179313659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6588249206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59329986572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57457828521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56053733825684</t>
   </si>
   <si>
     <t xml:space="preserve">8.48564910888672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54181289672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53245258331299</t>
+    <t xml:space="preserve">8.54181385040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5324535369873</t>
   </si>
   <si>
     <t xml:space="preserve">8.66818714141846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49968910217285</t>
+    <t xml:space="preserve">8.49969005584717</t>
   </si>
   <si>
     <t xml:space="preserve">8.61670112609863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49501037597656</t>
+    <t xml:space="preserve">8.49500846862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.5558557510376</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61202144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46692752838135</t>
+    <t xml:space="preserve">8.61202049255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46692657470703</t>
   </si>
   <si>
     <t xml:space="preserve">8.52777290344238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56521701812744</t>
+    <t xml:space="preserve">8.56521606445312</t>
   </si>
   <si>
     <t xml:space="preserve">8.69158840179443</t>
@@ -530,25 +530,25 @@
     <t xml:space="preserve">9.07070541381836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01453971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89284610748291</t>
+    <t xml:space="preserve">9.01453876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89284801483154</t>
   </si>
   <si>
     <t xml:space="preserve">8.93965339660645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81328010559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50437164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42480278015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40140151977539</t>
+    <t xml:space="preserve">8.81328105926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50437068939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42480373382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40140056610107</t>
   </si>
   <si>
     <t xml:space="preserve">8.39671993255615</t>
@@ -557,25 +557,25 @@
     <t xml:space="preserve">8.5839376449585</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34523582458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46224784851074</t>
+    <t xml:space="preserve">8.34523677825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46224689483643</t>
   </si>
   <si>
     <t xml:space="preserve">8.3826789855957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47160816192627</t>
+    <t xml:space="preserve">8.47160720825195</t>
   </si>
   <si>
     <t xml:space="preserve">8.98645687103271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09878730773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06134510040283</t>
+    <t xml:space="preserve">9.09878826141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0613431930542</t>
   </si>
   <si>
     <t xml:space="preserve">8.51841259002686</t>
@@ -587,28 +587,28 @@
     <t xml:space="preserve">8.31247234344482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44190979003906</t>
+    <t xml:space="preserve">7.4419093132019</t>
   </si>
   <si>
     <t xml:space="preserve">7.98484182357788</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95675802230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38735961914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41076183319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44820499420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4809684753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37331581115723</t>
+    <t xml:space="preserve">7.95675897598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38736057281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41075992584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44820308685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48096942901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37331771850586</t>
   </si>
   <si>
     <t xml:space="preserve">8.23290538787842</t>
@@ -617,16 +617,16 @@
     <t xml:space="preserve">8.1860990524292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3779993057251</t>
+    <t xml:space="preserve">8.37799835205078</t>
   </si>
   <si>
     <t xml:space="preserve">8.57925701141357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64946556091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72435188293457</t>
+    <t xml:space="preserve">8.64946460723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72435092926025</t>
   </si>
   <si>
     <t xml:space="preserve">8.67286586761475</t>
@@ -638,43 +638,43 @@
     <t xml:space="preserve">8.71031093597412</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15495204925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96773529052734</t>
+    <t xml:space="preserve">9.15495300292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96773433685303</t>
   </si>
   <si>
     <t xml:space="preserve">9.14091110229492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26728343963623</t>
+    <t xml:space="preserve">9.2672815322876</t>
   </si>
   <si>
     <t xml:space="preserve">9.33749008178711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40769672393799</t>
+    <t xml:space="preserve">9.4076976776123</t>
   </si>
   <si>
     <t xml:space="preserve">9.37961578369141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29536724090576</t>
+    <t xml:space="preserve">9.29536533355713</t>
   </si>
   <si>
     <t xml:space="preserve">9.3608922958374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44514083862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48258399963379</t>
+    <t xml:space="preserve">9.44513893127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48258495330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.43578052520752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35621166229248</t>
+    <t xml:space="preserve">9.35621070861816</t>
   </si>
   <si>
     <t xml:space="preserve">9.11282825469971</t>
@@ -683,28 +683,28 @@
     <t xml:space="preserve">9.10814762115479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15963172912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46386337280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81021404266357</t>
+    <t xml:space="preserve">9.15963363647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4638614654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81021499633789</t>
   </si>
   <si>
     <t xml:space="preserve">9.95999050140381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82893753051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91318416595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64171886444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70724487304688</t>
+    <t xml:space="preserve">9.82893657684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91318511962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6417179107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70724582672119</t>
   </si>
   <si>
     <t xml:space="preserve">9.71660614013672</t>
@@ -713,37 +713,37 @@
     <t xml:space="preserve">9.66044044494629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7914924621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0255155563354</t>
+    <t xml:space="preserve">9.79149341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0255165100098</t>
   </si>
   <si>
     <t xml:space="preserve">10.0067939758301</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1846513748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.240816116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2595386505127</t>
+    <t xml:space="preserve">10.1846504211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2408170700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2595376968384</t>
   </si>
   <si>
     <t xml:space="preserve">10.4280338287354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4748373031616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3625078201294</t>
+    <t xml:space="preserve">10.4748382568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3625068664551</t>
   </si>
   <si>
     <t xml:space="preserve">10.3344249725342</t>
   </si>
   <si>
-    <t xml:space="preserve">10.577808380127</t>
+    <t xml:space="preserve">10.5778112411499</t>
   </si>
   <si>
     <t xml:space="preserve">10.5122814178467</t>
@@ -752,25 +752,25 @@
     <t xml:space="preserve">10.5029211044312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8118305206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8867168426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7182216644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6526947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6433343887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6246128082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7088594436646</t>
+    <t xml:space="preserve">10.8118314743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8867177963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7182207107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6526956558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6433334350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6246137619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7088603973389</t>
   </si>
   <si>
     <t xml:space="preserve">10.8960790634155</t>
@@ -782,19 +782,19 @@
     <t xml:space="preserve">10.9335231781006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9990491867065</t>
+    <t xml:space="preserve">10.9990482330322</t>
   </si>
   <si>
     <t xml:space="preserve">11.1301012039185</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0926561355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2517919540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9616031646729</t>
+    <t xml:space="preserve">11.0926570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2517929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9616050720215</t>
   </si>
   <si>
     <t xml:space="preserve">11.2049894332886</t>
@@ -806,16 +806,16 @@
     <t xml:space="preserve">11.1488227844238</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862668991089</t>
+    <t xml:space="preserve">11.1862659454346</t>
   </si>
   <si>
     <t xml:space="preserve">11.2798748016357</t>
   </si>
   <si>
-    <t xml:space="preserve">11.429651260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4109268188477</t>
+    <t xml:space="preserve">11.4296493530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.410927772522</t>
   </si>
   <si>
     <t xml:space="preserve">11.4577312469482</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">11.5801239013672</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8249063491821</t>
+    <t xml:space="preserve">11.8249082565308</t>
   </si>
   <si>
     <t xml:space="preserve">11.8625659942627</t>
@@ -833,154 +833,154 @@
     <t xml:space="preserve">11.9472980499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9190549850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9284687042236</t>
+    <t xml:space="preserve">11.9190540313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9284696578979</t>
   </si>
   <si>
     <t xml:space="preserve">11.9378833770752</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9661283493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602741241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0979347229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0226163864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2109117507935</t>
+    <t xml:space="preserve">11.9661273956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0602750778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0979337692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0226173400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2109107971191</t>
   </si>
   <si>
     <t xml:space="preserve">12.1826667785645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2391538619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9096393585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1450071334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4859762191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2976818084717</t>
+    <t xml:space="preserve">12.2391557693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9096403121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1450080871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4859752655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2976808547974</t>
   </si>
   <si>
     <t xml:space="preserve">11.6931009292603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7307586669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7684192657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7590036392212</t>
+    <t xml:space="preserve">11.7307605743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7684173583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7590026855469</t>
   </si>
   <si>
     <t xml:space="preserve">11.627197265625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5707082748413</t>
+    <t xml:space="preserve">11.5707092285156</t>
   </si>
   <si>
     <t xml:space="preserve">11.5236349105835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4671478271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3729991912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0811424255371</t>
+    <t xml:space="preserve">11.4671468734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3729982376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0811433792114</t>
   </si>
   <si>
     <t xml:space="preserve">10.88343334198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6951389312744</t>
+    <t xml:space="preserve">10.6951379776001</t>
   </si>
   <si>
     <t xml:space="preserve">10.5633316040039</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6104078292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7422113418579</t>
+    <t xml:space="preserve">10.610405921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7422122955322</t>
   </si>
   <si>
     <t xml:space="preserve">10.911678314209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9022626876831</t>
+    <t xml:space="preserve">10.9022636413574</t>
   </si>
   <si>
     <t xml:space="preserve">10.9493370056152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1376304626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3541707992554</t>
+    <t xml:space="preserve">11.1376314163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3541688919067</t>
   </si>
   <si>
     <t xml:space="preserve">11.3824138641357</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3447551727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4106588363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2694387435913</t>
+    <t xml:space="preserve">11.3447561264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4106569290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.269437789917</t>
   </si>
   <si>
     <t xml:space="preserve">11.5048055648804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4294891357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3353395462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2788524627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2506074905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1093883514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0340690612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9210920333862</t>
+    <t xml:space="preserve">11.4294872283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3353404998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2788515090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2506084442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1093873977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0340700149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9210929870605</t>
   </si>
   <si>
     <t xml:space="preserve">10.6668930053711</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8363590240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.78928565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1941213607788</t>
+    <t xml:space="preserve">10.8363609313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7892866134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1941194534302</t>
   </si>
   <si>
     <t xml:space="preserve">11.1658744812012</t>
@@ -995,19 +995,19 @@
     <t xml:space="preserve">11.3165111541748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3259239196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2411918640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0623121261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0905561447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1752901077271</t>
+    <t xml:space="preserve">11.3259248733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2411937713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.062313079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0905570983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1752891540527</t>
   </si>
   <si>
     <t xml:space="preserve">11.4389019012451</t>
@@ -1022,70 +1022,70 @@
     <t xml:space="preserve">11.984956741333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0132007598877</t>
+    <t xml:space="preserve">12.013201713562</t>
   </si>
   <si>
     <t xml:space="preserve">11.956711769104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0508604049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0414447784424</t>
+    <t xml:space="preserve">12.0508594512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.041446685791</t>
   </si>
   <si>
     <t xml:space="preserve">12.0791034698486</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9755420684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8343200683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2203254699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1544218063354</t>
+    <t xml:space="preserve">11.9755411148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.834321975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.220326423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1544208526611</t>
   </si>
   <si>
     <t xml:space="preserve">12.107349395752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4839391708374</t>
+    <t xml:space="preserve">12.4839372634888</t>
   </si>
   <si>
     <t xml:space="preserve">12.5215978622437</t>
   </si>
   <si>
-    <t xml:space="preserve">12.643988609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7852096557617</t>
+    <t xml:space="preserve">12.6439895629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.785210609436</t>
   </si>
   <si>
     <t xml:space="preserve">12.8134536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8322830200195</t>
+    <t xml:space="preserve">12.8322839736938</t>
   </si>
   <si>
     <t xml:space="preserve">12.8040409088135</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1920824050903</t>
+    <t xml:space="preserve">12.1920804977417</t>
   </si>
   <si>
     <t xml:space="preserve">11.7872486114502</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8531522750854</t>
+    <t xml:space="preserve">11.8531513214111</t>
   </si>
   <si>
     <t xml:space="preserve">12.0320310592651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1732521057129</t>
+    <t xml:space="preserve">12.1732511520386</t>
   </si>
   <si>
     <t xml:space="preserve">12.2768135070801</t>
@@ -1097,70 +1097,70 @@
     <t xml:space="preserve">11.448317527771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5612926483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4012422561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6742706298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7778329849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0885210037231</t>
+    <t xml:space="preserve">11.5612936019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4012432098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6742715835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7778339385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0885190963745</t>
   </si>
   <si>
     <t xml:space="preserve">12.0696887969971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2014970779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1355934143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3615465164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3333024978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.163836479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7401733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1261777877808</t>
+    <t xml:space="preserve">12.2014961242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.135594367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3615455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3333034515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1638374328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7401742935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1261787414551</t>
   </si>
   <si>
     <t xml:space="preserve">12.5404262542725</t>
   </si>
   <si>
-    <t xml:space="preserve">12.549840927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5027685165405</t>
+    <t xml:space="preserve">12.5498428344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5027675628662</t>
   </si>
   <si>
     <t xml:space="preserve">12.6345739364624</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1335544586182</t>
+    <t xml:space="preserve">13.1335563659668</t>
   </si>
   <si>
     <t xml:space="preserve">13.1241397857666</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0864820480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9546747207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4254131317139</t>
+    <t xml:space="preserve">13.086480140686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9546737670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4254121780396</t>
   </si>
   <si>
     <t xml:space="preserve">13.4630708694458</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">13.538387298584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5572166442871</t>
+    <t xml:space="preserve">13.5572175979614</t>
   </si>
   <si>
     <t xml:space="preserve">13.6042919158936</t>
@@ -1178,79 +1178,79 @@
     <t xml:space="preserve">13.5101451873779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2559471130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4724855422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3030204772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9735040664673</t>
+    <t xml:space="preserve">13.2559452056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4724864959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3030185699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9735021591187</t>
   </si>
   <si>
     <t xml:space="preserve">12.615743637085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4086208343506</t>
+    <t xml:space="preserve">12.408618927002</t>
   </si>
   <si>
     <t xml:space="preserve">12.3803749084473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.46510887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5121822357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.822868347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8793563842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8511114120483</t>
+    <t xml:space="preserve">12.4651079177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5121831893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8228693008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8793573379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8511123657227</t>
   </si>
   <si>
     <t xml:space="preserve">12.5969152450562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.286229133606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2579851150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.728720664978</t>
+    <t xml:space="preserve">12.2862281799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.257984161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7287225723267</t>
   </si>
   <si>
     <t xml:space="preserve">13.0394077301025</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0958967208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2653617858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4065828323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3312635421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.321849822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1617994308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3406791687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2465324401855</t>
+    <t xml:space="preserve">13.0958957672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.26535987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4065818786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3312644958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3218488693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1617984771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3406782150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2465305328369</t>
   </si>
   <si>
     <t xml:space="preserve">12.8887710571289</t>
@@ -1262,10 +1262,10 @@
     <t xml:space="preserve">13.293604850769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5666313171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6419506072998</t>
+    <t xml:space="preserve">13.5666332244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6419496536255</t>
   </si>
   <si>
     <t xml:space="preserve">13.3124351501465</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">13.7925863265991</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9997110366821</t>
+    <t xml:space="preserve">13.9997100830078</t>
   </si>
   <si>
     <t xml:space="preserve">14.1409320831299</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">14.3951301574707</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3009815216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5645952224731</t>
+    <t xml:space="preserve">14.3009805679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5645942687988</t>
   </si>
   <si>
     <t xml:space="preserve">14.6022539138794</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6869859695435</t>
+    <t xml:space="preserve">14.6869869232178</t>
   </si>
   <si>
     <t xml:space="preserve">14.9129400253296</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">15.1106481552124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.969428062439</t>
+    <t xml:space="preserve">14.9694271087646</t>
   </si>
   <si>
     <t xml:space="preserve">14.997673034668</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">14.903525352478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8941106796265</t>
+    <t xml:space="preserve">14.8941097259521</t>
   </si>
   <si>
     <t xml:space="preserve">14.7152309417725</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">14.5928392410278</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1671380996704</t>
+    <t xml:space="preserve">15.1671371459961</t>
   </si>
   <si>
     <t xml:space="preserve">15.2706985473633</t>
@@ -1334,55 +1334,55 @@
     <t xml:space="preserve">15.2424554824829</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2518720626831</t>
+    <t xml:space="preserve">15.2518701553345</t>
   </si>
   <si>
     <t xml:space="preserve">15.4401636123657</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3930921554565</t>
+    <t xml:space="preserve">15.3930912017822</t>
   </si>
   <si>
     <t xml:space="preserve">15.5531425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6567029953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4213352203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0165014266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3460159301758</t>
+    <t xml:space="preserve">15.656702041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4213342666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0165023803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3460178375244</t>
   </si>
   <si>
     <t xml:space="preserve">14.818528175354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6668348312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3444871902466</t>
+    <t xml:space="preserve">14.6668338775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3444881439209</t>
   </si>
   <si>
     <t xml:space="preserve">14.6099481582642</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7332000732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8754119873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9273309707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4013710021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6194305419922</t>
+    <t xml:space="preserve">14.7331991195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.875412940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9273300170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4013700485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6194295883179</t>
   </si>
   <si>
     <t xml:space="preserve">14.6289110183716</t>
@@ -1391,19 +1391,19 @@
     <t xml:space="preserve">15.1882801055908</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4916677474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1173992156982</t>
+    <t xml:space="preserve">15.4916667938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1174011230469</t>
   </si>
   <si>
     <t xml:space="preserve">16.4587097167969</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1553230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1648044586182</t>
+    <t xml:space="preserve">16.1553249359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">16.2027282714844</t>
@@ -1412,16 +1412,16 @@
     <t xml:space="preserve">16.2122077941895</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3259792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1079216003418</t>
+    <t xml:space="preserve">16.3259773254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1079196929932</t>
   </si>
   <si>
     <t xml:space="preserve">16.0699977874756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5250778198242</t>
+    <t xml:space="preserve">16.5250759124756</t>
   </si>
   <si>
     <t xml:space="preserve">16.7241706848145</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">16.6672878265381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5724811553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3070163726807</t>
+    <t xml:space="preserve">16.5724792480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3070201873779</t>
   </si>
   <si>
     <t xml:space="preserve">16.2596130371094</t>
@@ -1442,31 +1442,31 @@
     <t xml:space="preserve">16.6767711639404</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8379440307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.885347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0465202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9232711791992</t>
+    <t xml:space="preserve">16.8379421234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8853454589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0465183258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9232692718506</t>
   </si>
   <si>
     <t xml:space="preserve">16.771577835083</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3733825683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4492321014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2216873168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4018249511719</t>
+    <t xml:space="preserve">16.373384475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4492301940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2216892242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4018230438232</t>
   </si>
   <si>
     <t xml:space="preserve">16.5535182952881</t>
@@ -1478,28 +1478,28 @@
     <t xml:space="preserve">16.5155944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1034049987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5395221710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9472007751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4447135925293</t>
+    <t xml:space="preserve">17.1034069061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5395240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9471988677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4447154998779</t>
   </si>
   <si>
     <t xml:space="preserve">18.0799293518066</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1652584075928</t>
+    <t xml:space="preserve">18.1652603149414</t>
   </si>
   <si>
     <t xml:space="preserve">18.7151470184326</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1368160247803</t>
+    <t xml:space="preserve">18.1368141174316</t>
   </si>
   <si>
     <t xml:space="preserve">18.4117584228516</t>
@@ -1511,28 +1511,28 @@
     <t xml:space="preserve">18.0704517364502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8618717193604</t>
+    <t xml:space="preserve">17.8618698120117</t>
   </si>
   <si>
     <t xml:space="preserve">17.6343307495117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7860240936279</t>
+    <t xml:space="preserve">17.7860260009766</t>
   </si>
   <si>
     <t xml:space="preserve">17.7575836181641</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2979869842529</t>
+    <t xml:space="preserve">18.2979888916016</t>
   </si>
   <si>
     <t xml:space="preserve">18.3738346099854</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2031803131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.032527923584</t>
+    <t xml:space="preserve">18.203182220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0325298309326</t>
   </si>
   <si>
     <t xml:space="preserve">18.1083736419678</t>
@@ -1550,19 +1550,19 @@
     <t xml:space="preserve">18.0040836334229</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5774478912354</t>
+    <t xml:space="preserve">17.577449798584</t>
   </si>
   <si>
     <t xml:space="preserve">18.3927974700928</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8334274291992</t>
+    <t xml:space="preserve">17.8334255218506</t>
   </si>
   <si>
     <t xml:space="preserve">18.0135631561279</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7435913085938</t>
+    <t xml:space="preserve">18.7435894012451</t>
   </si>
   <si>
     <t xml:space="preserve">19.3408813476562</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">18.7246265411377</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4496822357178</t>
+    <t xml:space="preserve">18.4496803283691</t>
   </si>
   <si>
     <t xml:space="preserve">18.5255317687988</t>
@@ -1592,19 +1592,19 @@
     <t xml:space="preserve">18.7720317840576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.96164894104</t>
+    <t xml:space="preserve">18.9616470336914</t>
   </si>
   <si>
     <t xml:space="preserve">18.6867046356201</t>
   </si>
   <si>
-    <t xml:space="preserve">18.146297454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5065670013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0420074462891</t>
+    <t xml:space="preserve">18.1462955474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5065689086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0420093536377</t>
   </si>
   <si>
     <t xml:space="preserve">17.3025035858154</t>
@@ -1613,46 +1613,46 @@
     <t xml:space="preserve">16.5629978179932</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4537420272827</t>
+    <t xml:space="preserve">15.453742980957</t>
   </si>
   <si>
     <t xml:space="preserve">15.5864753723145</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6718006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0081443786621</t>
+    <t xml:space="preserve">15.6718034744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0081434249878</t>
   </si>
   <si>
     <t xml:space="preserve">15.4253015518188</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4632244110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8045339584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7286863327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9512596130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0745096206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9986619949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9797010421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0176239013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8469715118408</t>
+    <t xml:space="preserve">15.4632234573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8045330047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7286853790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9512586593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0745086669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9986629486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9797019958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0176248550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8469696044922</t>
   </si>
   <si>
     <t xml:space="preserve">14.6573534011841</t>
@@ -1661,13 +1661,13 @@
     <t xml:space="preserve">14.7047576904297</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6763153076172</t>
+    <t xml:space="preserve">14.6763143539429</t>
   </si>
   <si>
     <t xml:space="preserve">14.6478719711304</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9322967529297</t>
+    <t xml:space="preserve">14.932297706604</t>
   </si>
   <si>
     <t xml:space="preserve">15.0555486679077</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">13.8135595321655</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7282314300537</t>
+    <t xml:space="preserve">13.728232383728</t>
   </si>
   <si>
     <t xml:space="preserve">13.1309413909912</t>
@@ -1694,10 +1694,10 @@
     <t xml:space="preserve">13.263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3964042663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6523876190186</t>
+    <t xml:space="preserve">13.3964033126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6523857116699</t>
   </si>
   <si>
     <t xml:space="preserve">13.4912109375</t>
@@ -1706,10 +1706,10 @@
     <t xml:space="preserve">13.2257499694824</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8704452514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0126581192017</t>
+    <t xml:space="preserve">13.8704462051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0126571655273</t>
   </si>
   <si>
     <t xml:space="preserve">14.4961795806885</t>
@@ -1721,16 +1721,16 @@
     <t xml:space="preserve">14.1643505096436</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3065624237061</t>
+    <t xml:space="preserve">14.3065633773804</t>
   </si>
   <si>
     <t xml:space="preserve">14.3350048065186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7945995330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7377138137817</t>
+    <t xml:space="preserve">13.7946004867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7377128601074</t>
   </si>
   <si>
     <t xml:space="preserve">13.5955018997192</t>
@@ -1739,34 +1739,34 @@
     <t xml:space="preserve">13.7566757202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.898886680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9462919235229</t>
+    <t xml:space="preserve">13.8988876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9462928771973</t>
   </si>
   <si>
     <t xml:space="preserve">14.4203329086304</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7756357192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7232666015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3205585479736</t>
+    <t xml:space="preserve">13.7756376266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7232656478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3205575942993</t>
   </si>
   <si>
     <t xml:space="preserve">13.1878261566162</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7471952438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0695428848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8374881744385</t>
+    <t xml:space="preserve">13.7471942901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.069543838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8374900817871</t>
   </si>
   <si>
     <t xml:space="preserve">15.2546443939209</t>
@@ -1784,40 +1784,40 @@
     <t xml:space="preserve">15.1503562927246</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3115310668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3589353561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2925672531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1408767700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0271053314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9228162765503</t>
+    <t xml:space="preserve">15.3115301132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3589344024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2925682067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1408758163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0271062850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.922815322876</t>
   </si>
   <si>
     <t xml:space="preserve">14.8280086517334</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8659324645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9417791366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.614914894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7097253799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0650291442871</t>
+    <t xml:space="preserve">14.8659315109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9417781829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6149158477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7097244262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0650300979614</t>
   </si>
   <si>
     <t xml:space="preserve">15.216721534729</t>
@@ -1835,10 +1835,10 @@
     <t xml:space="preserve">14.7806043624878</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9038543701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2262029647827</t>
+    <t xml:space="preserve">14.9038553237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2262020111084</t>
   </si>
   <si>
     <t xml:space="preserve">15.1977605819702</t>
@@ -1853,55 +1853,55 @@
     <t xml:space="preserve">15.5106287002563</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7381687164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4302654266357</t>
+    <t xml:space="preserve">15.7381677627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4302673339844</t>
   </si>
   <si>
     <t xml:space="preserve">15.9657068252563</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2641277313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7855730056763</t>
+    <t xml:space="preserve">15.2641267776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7855710983276</t>
   </si>
   <si>
     <t xml:space="preserve">16.6862487792969</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8474254608154</t>
+    <t xml:space="preserve">16.8474235534668</t>
   </si>
   <si>
     <t xml:space="preserve">16.4966316223145</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1932506561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2311744689941</t>
+    <t xml:space="preserve">16.1932487487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2311725616455</t>
   </si>
   <si>
     <t xml:space="preserve">16.7526149749756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4207878112793</t>
+    <t xml:space="preserve">16.4207859039307</t>
   </si>
   <si>
     <t xml:space="preserve">16.8094997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7336521148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8948268890381</t>
+    <t xml:space="preserve">16.7336559295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8948287963867</t>
   </si>
   <si>
     <t xml:space="preserve">16.8663864135742</t>
   </si>
   <si>
-    <t xml:space="preserve">16.250129699707</t>
+    <t xml:space="preserve">16.2501316070557</t>
   </si>
   <si>
     <t xml:space="preserve">15.8993425369263</t>
@@ -1910,31 +1910,31 @@
     <t xml:space="preserve">15.8898620605469</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9277811050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8519372940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3544235229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2406482696533</t>
+    <t xml:space="preserve">15.9277830123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.851936340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.354419708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.240650177002</t>
   </si>
   <si>
     <t xml:space="preserve">15.9183044433594</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5016002655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6627731323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0894107818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3119831085205</t>
+    <t xml:space="preserve">17.5015983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6627750396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.089412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3119812011719</t>
   </si>
   <si>
     <t xml:space="preserve">17.2835388183594</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">17.8239459991455</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6677398681641</t>
+    <t xml:space="preserve">18.6677417755127</t>
   </si>
   <si>
     <t xml:space="preserve">18.5743846893311</t>
@@ -1952,13 +1952,13 @@
     <t xml:space="preserve">18.8704280853271</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5962162017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5007152557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9277248382568</t>
+    <t xml:space="preserve">19.5962142944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5007171630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9277267456055</t>
   </si>
   <si>
     <t xml:space="preserve">18.9468250274658</t>
@@ -1967,19 +1967,19 @@
     <t xml:space="preserve">18.9850215911865</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5934829711914</t>
+    <t xml:space="preserve">18.59348487854</t>
   </si>
   <si>
     <t xml:space="preserve">18.708080291748</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9659252166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.032772064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2333183288574</t>
+    <t xml:space="preserve">18.9659233093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0327739715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2333202362061</t>
   </si>
   <si>
     <t xml:space="preserve">19.386116027832</t>
@@ -1988,13 +1988,13 @@
     <t xml:space="preserve">19.0900726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1951217651367</t>
+    <t xml:space="preserve">19.1951236724854</t>
   </si>
   <si>
     <t xml:space="preserve">19.1187229156494</t>
   </si>
   <si>
-    <t xml:space="preserve">19.252420425415</t>
+    <t xml:space="preserve">19.2524185180664</t>
   </si>
   <si>
     <t xml:space="preserve">19.9018077850342</t>
@@ -2006,19 +2006,19 @@
     <t xml:space="preserve">20.2646980285645</t>
   </si>
   <si>
-    <t xml:space="preserve">20.589391708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5511951446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7994899749756</t>
+    <t xml:space="preserve">20.5893936157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5511932373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.799488067627</t>
   </si>
   <si>
     <t xml:space="preserve">19.9591045379639</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8445072174072</t>
+    <t xml:space="preserve">19.8445091247559</t>
   </si>
   <si>
     <t xml:space="preserve">19.4816150665283</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">19.6344108581543</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6726112365723</t>
+    <t xml:space="preserve">19.6726131439209</t>
   </si>
   <si>
     <t xml:space="preserve">20.0928058624268</t>
@@ -2048,13 +2048,13 @@
     <t xml:space="preserve">19.7299098968506</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3028984069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2837982177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2264995574951</t>
+    <t xml:space="preserve">20.3029003143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2838001251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2265014648438</t>
   </si>
   <si>
     <t xml:space="preserve">20.7039909362793</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">20.6848907470703</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4174976348877</t>
+    <t xml:space="preserve">20.4174957275391</t>
   </si>
   <si>
     <t xml:space="preserve">20.0355033874512</t>
@@ -2078,37 +2078,37 @@
     <t xml:space="preserve">21.2769813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1814804077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4365940093994</t>
+    <t xml:space="preserve">21.1814823150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.436595916748</t>
   </si>
   <si>
     <t xml:space="preserve">20.0164031982422</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5702953338623</t>
+    <t xml:space="preserve">20.5702972412109</t>
   </si>
   <si>
     <t xml:space="preserve">20.9904842376709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1050834655762</t>
+    <t xml:space="preserve">21.1050815582275</t>
   </si>
   <si>
     <t xml:space="preserve">21.1623821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2578792572021</t>
+    <t xml:space="preserve">21.2578773498535</t>
   </si>
   <si>
     <t xml:space="preserve">21.0286846160889</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2960777282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8499660491943</t>
+    <t xml:space="preserve">21.2960796356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.849967956543</t>
   </si>
   <si>
     <t xml:space="preserve">22.4802551269531</t>
@@ -2129,13 +2129,13 @@
     <t xml:space="preserve">21.9645652770996</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9454689025879</t>
+    <t xml:space="preserve">21.9454669952393</t>
   </si>
   <si>
     <t xml:space="preserve">22.3083591461182</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5948543548584</t>
+    <t xml:space="preserve">22.5948524475098</t>
   </si>
   <si>
     <t xml:space="preserve">22.7476501464844</t>
@@ -2147,16 +2147,16 @@
     <t xml:space="preserve">22.0600624084473</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2319622039795</t>
+    <t xml:space="preserve">22.2319602966309</t>
   </si>
   <si>
     <t xml:space="preserve">21.3533802032471</t>
   </si>
   <si>
-    <t xml:space="preserve">20.474796295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.455696105957</t>
+    <t xml:space="preserve">20.4747943878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4556980133057</t>
   </si>
   <si>
     <t xml:space="preserve">21.1241836547852</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">21.0859813690186</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7353687286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5061721801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2196826934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3724765777588</t>
+    <t xml:space="preserve">21.7353706359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5061740875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2196807861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3724784851074</t>
   </si>
   <si>
     <t xml:space="preserve">21.6016750335693</t>
@@ -2198,43 +2198,43 @@
     <t xml:space="preserve">20.6466941833496</t>
   </si>
   <si>
-    <t xml:space="preserve">20.608491897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.493896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8567867279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3792991638184</t>
+    <t xml:space="preserve">20.6084938049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4938945770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8567886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3792972564697</t>
   </si>
   <si>
     <t xml:space="preserve">20.8949871063232</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9331874847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.32200050354</t>
+    <t xml:space="preserve">20.9331855773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3219985961914</t>
   </si>
   <si>
     <t xml:space="preserve">20.3410968780518</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8308696746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0218620300293</t>
+    <t xml:space="preserve">21.830867767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0218639373779</t>
   </si>
   <si>
     <t xml:space="preserve">22.5375537872314</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6521511077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0150489807129</t>
+    <t xml:space="preserve">22.6521492004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0150470733643</t>
   </si>
   <si>
     <t xml:space="preserve">23.4543361663818</t>
@@ -2246,13 +2246,13 @@
     <t xml:space="preserve">23.9127292633057</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5689373016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0846252441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.798131942749</t>
+    <t xml:space="preserve">23.5689353942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.084623336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7981300354004</t>
   </si>
   <si>
     <t xml:space="preserve">23.8745269775391</t>
@@ -2261,28 +2261,28 @@
     <t xml:space="preserve">23.970027923584</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3711166381836</t>
+    <t xml:space="preserve">24.3711185455322</t>
   </si>
   <si>
     <t xml:space="preserve">24.867712020874</t>
   </si>
   <si>
-    <t xml:space="preserve">25.09690284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3642997741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3329162597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9823055267334</t>
+    <t xml:space="preserve">25.0969047546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3642978668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3329181671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.982307434082</t>
   </si>
   <si>
     <t xml:space="preserve">25.2879009246826</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9250087738037</t>
+    <t xml:space="preserve">24.9250068664551</t>
   </si>
   <si>
     <t xml:space="preserve">25.0205078125</t>
@@ -2297,46 +2297,46 @@
     <t xml:space="preserve">24.8295097351074</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6385154724121</t>
+    <t xml:space="preserve">24.6385135650635</t>
   </si>
   <si>
     <t xml:space="preserve">24.4475173950195</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5430145263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3520202636719</t>
+    <t xml:space="preserve">24.5430164337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3520183563232</t>
   </si>
   <si>
     <t xml:space="preserve">24.6576099395752</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6767120361328</t>
+    <t xml:space="preserve">24.6767139434814</t>
   </si>
   <si>
     <t xml:space="preserve">24.4857139587402</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5621147155762</t>
+    <t xml:space="preserve">24.5621166229248</t>
   </si>
   <si>
     <t xml:space="preserve">24.5812129974365</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6958122253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.306999206543</t>
+    <t xml:space="preserve">24.6958141326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3070011138916</t>
   </si>
   <si>
     <t xml:space="preserve">25.3451995849609</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8486080169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0014057159424</t>
+    <t xml:space="preserve">24.8486099243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.001407623291</t>
   </si>
   <si>
     <t xml:space="preserve">25.2115001678467</t>
@@ -2357,19 +2357,19 @@
     <t xml:space="preserve">25.8226909637451</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7722110748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5239162445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9059085845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6698913574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2237796783447</t>
+    <t xml:space="preserve">24.7722091674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5239143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9059066772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6698932647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2237815856934</t>
   </si>
   <si>
     <t xml:space="preserve">26.281078338623</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">27.2169628143311</t>
   </si>
   <si>
-    <t xml:space="preserve">27.522554397583</t>
+    <t xml:space="preserve">27.5225563049316</t>
   </si>
   <si>
     <t xml:space="preserve">27.6944522857666</t>
@@ -2399,25 +2399,25 @@
     <t xml:space="preserve">28.7831325531006</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2865428924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8854522705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9754886627197</t>
+    <t xml:space="preserve">28.2865409851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8854503631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9754867553711</t>
   </si>
   <si>
     <t xml:space="preserve">25.2306003570557</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6003150939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6071319580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4666175842285</t>
+    <t xml:space="preserve">24.6003131866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6071338653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4666156768799</t>
   </si>
   <si>
     <t xml:space="preserve">23.4352359771729</t>
@@ -2429,19 +2429,19 @@
     <t xml:space="preserve">19.3479194641113</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5852909088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.323356628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7285375595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.120080947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.903169631958</t>
+    <t xml:space="preserve">15.5852918624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3233585357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7285394668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1200790405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9031677246094</t>
   </si>
   <si>
     <t xml:space="preserve">17.523904800415</t>
@@ -2459,28 +2459,28 @@
     <t xml:space="preserve">18.1446418762207</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2210388183594</t>
+    <t xml:space="preserve">18.221040725708</t>
   </si>
   <si>
     <t xml:space="preserve">18.1159896850586</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8772449493408</t>
+    <t xml:space="preserve">17.8772430419922</t>
   </si>
   <si>
     <t xml:space="preserve">17.3806591033936</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4093036651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8076667785645</t>
+    <t xml:space="preserve">17.4093055725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8076686859131</t>
   </si>
   <si>
     <t xml:space="preserve">17.6480522155762</t>
   </si>
   <si>
-    <t xml:space="preserve">18.784481048584</t>
+    <t xml:space="preserve">18.7844791412354</t>
   </si>
   <si>
     <t xml:space="preserve">18.4311332702637</t>
@@ -2489,16 +2489,16 @@
     <t xml:space="preserve">18.4454612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7653770446777</t>
+    <t xml:space="preserve">18.7653789520264</t>
   </si>
   <si>
     <t xml:space="preserve">17.9536437988281</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8663387298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.271520614624</t>
+    <t xml:space="preserve">20.866340637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2715187072754</t>
   </si>
   <si>
     <t xml:space="preserve">18.8465538024902</t>
@@ -2507,43 +2507,43 @@
     <t xml:space="preserve">20.0068550109863</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2456016540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9877548217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9686546325684</t>
+    <t xml:space="preserve">20.2455997467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9877529144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.968656539917</t>
   </si>
   <si>
     <t xml:space="preserve">19.7681102752686</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6753425598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7640171051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3820266723633</t>
+    <t xml:space="preserve">20.6753406524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7640190124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3820247650146</t>
   </si>
   <si>
     <t xml:space="preserve">22.337007522583</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7926692962646</t>
+    <t xml:space="preserve">21.7926712036133</t>
   </si>
   <si>
     <t xml:space="preserve">21.019136428833</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4297752380371</t>
+    <t xml:space="preserve">21.4297771453857</t>
   </si>
   <si>
     <t xml:space="preserve">21.8595180511475</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9522838592529</t>
+    <t xml:space="preserve">20.9522857666016</t>
   </si>
   <si>
     <t xml:space="preserve">21.9932155609131</t>
@@ -2552,25 +2552,25 @@
     <t xml:space="preserve">21.658971786499</t>
   </si>
   <si>
-    <t xml:space="preserve">23.034143447876</t>
+    <t xml:space="preserve">23.0341453552246</t>
   </si>
   <si>
     <t xml:space="preserve">23.1391925811768</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2797088623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5020866394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8267822265625</t>
+    <t xml:space="preserve">22.279712677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5020847320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8267803192139</t>
   </si>
   <si>
     <t xml:space="preserve">23.521183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8458766937256</t>
+    <t xml:space="preserve">23.8458786010742</t>
   </si>
   <si>
     <t xml:space="preserve">23.8172283172607</t>
@@ -2579,7 +2579,7 @@
     <t xml:space="preserve">23.3588352203369</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6903514862061</t>
+    <t xml:space="preserve">22.6903533935547</t>
   </si>
   <si>
     <t xml:space="preserve">22.6330528259277</t>
@@ -2591,19 +2591,19 @@
     <t xml:space="preserve">22.0696144104004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6999015808105</t>
+    <t xml:space="preserve">22.6999034881592</t>
   </si>
   <si>
     <t xml:space="preserve">22.938648223877</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3015384674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6808032989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7094497680664</t>
+    <t xml:space="preserve">23.3015403747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6808013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.709451675415</t>
   </si>
   <si>
     <t xml:space="preserve">23.1487426757812</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">22.6426029205322</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7380981445312</t>
+    <t xml:space="preserve">22.7381000518799</t>
   </si>
   <si>
     <t xml:space="preserve">23.272891998291</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">23.5402851104736</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7408332824707</t>
+    <t xml:space="preserve">23.7408313751221</t>
   </si>
   <si>
     <t xml:space="preserve">23.8363285064697</t>
@@ -2651,13 +2651,13 @@
     <t xml:space="preserve">24.3233680725098</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7340106964111</t>
+    <t xml:space="preserve">24.7340087890625</t>
   </si>
   <si>
     <t xml:space="preserve">25.2783508300781</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0682544708252</t>
+    <t xml:space="preserve">25.0682525634766</t>
   </si>
   <si>
     <t xml:space="preserve">25.0587043762207</t>
@@ -2672,28 +2672,28 @@
     <t xml:space="preserve">26.5580234527588</t>
   </si>
   <si>
-    <t xml:space="preserve">26.510274887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6467037200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2292423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5034580230713</t>
+    <t xml:space="preserve">26.5102787017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6467056274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2292404174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5034561157227</t>
   </si>
   <si>
     <t xml:space="preserve">27.5894050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1596660614014</t>
+    <t xml:space="preserve">27.1596641540527</t>
   </si>
   <si>
     <t xml:space="preserve">27.5512046813965</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0164184570312</t>
+    <t xml:space="preserve">27.0164165496826</t>
   </si>
   <si>
     <t xml:space="preserve">27.035514831543</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">27.3793087005615</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2265110015869</t>
+    <t xml:space="preserve">27.2265129089355</t>
   </si>
   <si>
     <t xml:space="preserve">27.054615020752</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">26.5675754547119</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0450668334961</t>
+    <t xml:space="preserve">27.0450649261475</t>
   </si>
   <si>
     <t xml:space="preserve">26.7108211517334</t>
@@ -2729,19 +2729,19 @@
     <t xml:space="preserve">26.6630744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5389270782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.26198387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4625282287598</t>
+    <t xml:space="preserve">26.5389289855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2619819641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4625263214111</t>
   </si>
   <si>
     <t xml:space="preserve">27.5989551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6726226806641</t>
+    <t xml:space="preserve">26.6726245880127</t>
   </si>
   <si>
     <t xml:space="preserve">26.7585716247559</t>
@@ -2759,25 +2759,25 @@
     <t xml:space="preserve">28.3533916473389</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5061855316162</t>
+    <t xml:space="preserve">28.5061874389648</t>
   </si>
   <si>
     <t xml:space="preserve">28.9932270050049</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7926807403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6971836090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5798511505127</t>
+    <t xml:space="preserve">28.7926826477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6971797943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5798530578613</t>
   </si>
   <si>
     <t xml:space="preserve">27.6562519073486</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4748077392578</t>
+    <t xml:space="preserve">27.4748058319092</t>
   </si>
   <si>
     <t xml:space="preserve">27.6849040985107</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">29.3847713470459</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9673080444336</t>
+    <t xml:space="preserve">29.967306137085</t>
   </si>
   <si>
     <t xml:space="preserve">29.1746711730957</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">29.4802684783936</t>
   </si>
   <si>
-    <t xml:space="preserve">29.833610534668</t>
+    <t xml:space="preserve">29.8336124420166</t>
   </si>
   <si>
     <t xml:space="preserve">30.0246067047119</t>
@@ -2804,19 +2804,19 @@
     <t xml:space="preserve">29.1651248931885</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3274688720703</t>
+    <t xml:space="preserve">29.3274669647217</t>
   </si>
   <si>
     <t xml:space="preserve">29.8049583435059</t>
   </si>
   <si>
-    <t xml:space="preserve">30.473445892334</t>
+    <t xml:space="preserve">30.4734477996826</t>
   </si>
   <si>
     <t xml:space="preserve">30.9891376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">30.750394821167</t>
+    <t xml:space="preserve">30.7503929138184</t>
   </si>
   <si>
     <t xml:space="preserve">30.5402965545654</t>
@@ -2825,22 +2825,22 @@
     <t xml:space="preserve">30.922290802002</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7408390045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9318389892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7217426300049</t>
+    <t xml:space="preserve">30.7408409118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9318408966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7217407226562</t>
   </si>
   <si>
     <t xml:space="preserve">30.6835460662842</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8172416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4829959869385</t>
+    <t xml:space="preserve">30.8172397613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4829998016357</t>
   </si>
   <si>
     <t xml:space="preserve">30.5593967437744</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">29.2128734588623</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9031887054443</t>
+    <t xml:space="preserve">30.903190612793</t>
   </si>
   <si>
     <t xml:space="preserve">31.9918651580811</t>
@@ -2864,19 +2864,19 @@
     <t xml:space="preserve">33.6535377502441</t>
   </si>
   <si>
-    <t xml:space="preserve">33.309741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4693565368652</t>
+    <t xml:space="preserve">33.3097457885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4693603515625</t>
   </si>
   <si>
     <t xml:space="preserve">33.3288383483887</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5580368041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1310234069824</t>
+    <t xml:space="preserve">33.5580406188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1310272216797</t>
   </si>
   <si>
     <t xml:space="preserve">33.4338874816895</t>
@@ -2891,16 +2891,16 @@
     <t xml:space="preserve">33.9304809570312</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6603546142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6699028015137</t>
+    <t xml:space="preserve">32.6603584289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6699066162109</t>
   </si>
   <si>
     <t xml:space="preserve">32.8513526916504</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5143795013428</t>
+    <t xml:space="preserve">31.5143756866455</t>
   </si>
   <si>
     <t xml:space="preserve">31.6098728179932</t>
@@ -2915,28 +2915,28 @@
     <t xml:space="preserve">32.0587158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2565326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.884090423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.017786026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1323852539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8745403289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0846347808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6194267272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0969200134277</t>
+    <t xml:space="preserve">31.256534576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8840885162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0177841186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1323833465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8745384216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0846366882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6194248199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0969161987305</t>
   </si>
   <si>
     <t xml:space="preserve">31.3615818023682</t>
@@ -2945,19 +2945,19 @@
     <t xml:space="preserve">32.1542091369629</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9441184997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4216117858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.695821762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2115135192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7435741424561</t>
+    <t xml:space="preserve">31.9441146850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4216079711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6958255767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2115097045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7435779571533</t>
   </si>
   <si>
     <t xml:space="preserve">32.2783584594727</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">31.5334777832031</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2087841033936</t>
+    <t xml:space="preserve">31.2087860107422</t>
   </si>
   <si>
     <t xml:space="preserve">32.3165626525879</t>
@@ -2990,19 +2990,19 @@
     <t xml:space="preserve">32.3834114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6221580505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6508026123047</t>
+    <t xml:space="preserve">32.6221542358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.650806427002</t>
   </si>
   <si>
     <t xml:space="preserve">32.8036003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5839500427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3547668457031</t>
+    <t xml:space="preserve">32.5839538574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3547592163086</t>
   </si>
   <si>
     <t xml:space="preserve">32.0682678222656</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">32.3261108398438</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9250240325928</t>
+    <t xml:space="preserve">31.9250202178955</t>
   </si>
   <si>
     <t xml:space="preserve">33.0423469543457</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">33.7967796325684</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5989646911621</t>
+    <t xml:space="preserve">34.5989608764648</t>
   </si>
   <si>
     <t xml:space="preserve">34.4843673706055</t>
@@ -3038,40 +3038,40 @@
     <t xml:space="preserve">34.8854598999023</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0000610351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.80224609375</t>
+    <t xml:space="preserve">35.000057220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8022384643555</t>
   </si>
   <si>
     <t xml:space="preserve">35.5539474487305</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3342971801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2551727294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9018287658691</t>
+    <t xml:space="preserve">35.334300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2551689147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9018325805664</t>
   </si>
   <si>
     <t xml:space="preserve">33.3670387268066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3192939758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.781774520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8104228973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4598083496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7081031799316</t>
+    <t xml:space="preserve">33.3192901611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7817707061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8104190826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4598045349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7080993652344</t>
   </si>
   <si>
     <t xml:space="preserve">29.9768562316895</t>
@@ -3080,64 +3080,64 @@
     <t xml:space="preserve">29.4898166656494</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6876335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0027770996094</t>
+    <t xml:space="preserve">28.6876354217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0027751922607</t>
   </si>
   <si>
     <t xml:space="preserve">30.3875007629395</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6453437805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4761753082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5211963653564</t>
+    <t xml:space="preserve">30.6453456878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4761772155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5211944580078</t>
   </si>
   <si>
     <t xml:space="preserve">30.7312927246094</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1228332519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5498466491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5375671386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.148754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6671772003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4066009521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7694911956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6644458770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3111000061035</t>
+    <t xml:space="preserve">31.1228313446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5498447418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5375690460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1487522125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6671752929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4065990447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7694931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6644439697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3111019134521</t>
   </si>
   <si>
     <t xml:space="preserve">30.9413909912109</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2756309509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9604873657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5812282562256</t>
+    <t xml:space="preserve">31.2756290435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.960485458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5812244415283</t>
   </si>
   <si>
     <t xml:space="preserve">31.3424816131592</t>
@@ -3146,25 +3146,25 @@
     <t xml:space="preserve">33.5007400512695</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9372978210449</t>
+    <t xml:space="preserve">32.9373016357422</t>
   </si>
   <si>
     <t xml:space="preserve">33.8731803894043</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6344375610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.624885559082</t>
+    <t xml:space="preserve">33.6344337463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6248817443848</t>
   </si>
   <si>
     <t xml:space="preserve">34.1787757873535</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2169761657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9905090332031</t>
+    <t xml:space="preserve">34.216983795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9905128479004</t>
   </si>
   <si>
     <t xml:space="preserve">34.8281669616699</t>
@@ -3173,13 +3173,13 @@
     <t xml:space="preserve">34.3029174804688</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1091918945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5484924316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.806339263916</t>
+    <t xml:space="preserve">33.1091957092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5484886169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8063354492188</t>
   </si>
   <si>
     <t xml:space="preserve">33.233341217041</t>
@@ -3200,19 +3200,19 @@
     <t xml:space="preserve">31.8868179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0873603820801</t>
+    <t xml:space="preserve">32.0873680114746</t>
   </si>
   <si>
     <t xml:space="preserve">32.9468536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1378479003906</t>
+    <t xml:space="preserve">33.1378440856934</t>
   </si>
   <si>
     <t xml:space="preserve">34.7995109558105</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8851890563965</t>
+    <t xml:space="preserve">35.8851928710938</t>
   </si>
   <si>
     <t xml:space="preserve">36.6538200378418</t>
@@ -3233,7 +3233,7 @@
     <t xml:space="preserve">37.1246032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0189170837402</t>
+    <t xml:space="preserve">37.018913269043</t>
   </si>
   <si>
     <t xml:space="preserve">37.6818542480469</t>
@@ -3242,16 +3242,16 @@
     <t xml:space="preserve">38.2391090393066</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7683258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8836212158203</t>
+    <t xml:space="preserve">37.7683296203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.883617401123</t>
   </si>
   <si>
     <t xml:space="preserve">38.0181274414062</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2479286193848</t>
+    <t xml:space="preserve">39.247932434082</t>
   </si>
   <si>
     <t xml:space="preserve">38.6138114929199</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">38.6426391601562</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3440093994141</t>
+    <t xml:space="preserve">39.3440055847168</t>
   </si>
   <si>
     <t xml:space="preserve">38.5946006774902</t>
@@ -3269,19 +3269,19 @@
     <t xml:space="preserve">38.7963600158691</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7195014953613</t>
+    <t xml:space="preserve">38.7195053100586</t>
   </si>
   <si>
     <t xml:space="preserve">38.6042060852051</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6130256652832</t>
+    <t xml:space="preserve">39.6130294799805</t>
   </si>
   <si>
     <t xml:space="preserve">39.6514587402344</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7475318908691</t>
+    <t xml:space="preserve">39.7475357055664</t>
   </si>
   <si>
     <t xml:space="preserve">40.4969482421875</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">39.8051795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9685173034668</t>
+    <t xml:space="preserve">39.9685134887695</t>
   </si>
   <si>
     <t xml:space="preserve">39.6034240722656</t>
@@ -3308,16 +3308,16 @@
     <t xml:space="preserve">39.0749855041504</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5769577026367</t>
+    <t xml:space="preserve">36.576961517334</t>
   </si>
   <si>
     <t xml:space="preserve">37.5665626525879</t>
   </si>
   <si>
-    <t xml:space="preserve">37.556957244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3736152648926</t>
+    <t xml:space="preserve">37.5569534301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3736190795898</t>
   </si>
   <si>
     <t xml:space="preserve">38.9789123535156</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">39.1614608764648</t>
   </si>
   <si>
-    <t xml:space="preserve">38.479305267334</t>
+    <t xml:space="preserve">38.4793014526367</t>
   </si>
   <si>
     <t xml:space="preserve">39.4496994018555</t>
@@ -3338,10 +3338,10 @@
     <t xml:space="preserve">38.8540115356445</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4304809570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7675399780273</t>
+    <t xml:space="preserve">39.430477142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7675361633301</t>
   </si>
   <si>
     <t xml:space="preserve">40.0453796386719</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">40.3528289794922</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7083129882812</t>
+    <t xml:space="preserve">40.7083168029785</t>
   </si>
   <si>
     <t xml:space="preserve">40.2567520141602</t>
@@ -3368,13 +3368,13 @@
     <t xml:space="preserve">40.2663536071777</t>
   </si>
   <si>
-    <t xml:space="preserve">40.448902130127</t>
+    <t xml:space="preserve">40.4489059448242</t>
   </si>
   <si>
     <t xml:space="preserve">41.0157661437988</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1406669616699</t>
+    <t xml:space="preserve">41.1406707763672</t>
   </si>
   <si>
     <t xml:space="preserve">41.3424339294434</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">41.5634078979492</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0822334289551</t>
+    <t xml:space="preserve">42.0822372436523</t>
   </si>
   <si>
     <t xml:space="preserve">43.0814476013184</t>
@@ -3398,13 +3398,13 @@
     <t xml:space="preserve">42.2455711364746</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0341987609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7651786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9669418334961</t>
+    <t xml:space="preserve">42.0342025756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7651824951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9669456481934</t>
   </si>
   <si>
     <t xml:space="preserve">42.4665489196777</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">42.5434112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6683120727539</t>
+    <t xml:space="preserve">42.6683158874512</t>
   </si>
   <si>
     <t xml:space="preserve">42.9853706359863</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">40.8332214355469</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0638122558594</t>
+    <t xml:space="preserve">41.0638084411621</t>
   </si>
   <si>
     <t xml:space="preserve">43.0718421936035</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">44.3112449645996</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2159614562988</t>
+    <t xml:space="preserve">43.2159576416016</t>
   </si>
   <si>
     <t xml:space="preserve">41.9477272033691</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">40.2759666442871</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5842018127441</t>
+    <t xml:space="preserve">39.5842056274414</t>
   </si>
   <si>
     <t xml:space="preserve">39.1902847290039</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">39.5169525146484</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6802787780762</t>
+    <t xml:space="preserve">39.6802825927734</t>
   </si>
   <si>
     <t xml:space="preserve">40.10302734375</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">39.0653800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9108734130859</t>
+    <t xml:space="preserve">39.9108772277832</t>
   </si>
   <si>
     <t xml:space="preserve">40.2087135314941</t>
@@ -3509,16 +3509,16 @@
     <t xml:space="preserve">42.7932167053223</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5730209350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.169490814209</t>
+    <t xml:space="preserve">41.5730247497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1694946289062</t>
   </si>
   <si>
     <t xml:space="preserve">42.2263526916504</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9469375610352</t>
+    <t xml:space="preserve">42.9469413757324</t>
   </si>
   <si>
     <t xml:space="preserve">42.3800811767578</t>
@@ -3527,25 +3527,25 @@
     <t xml:space="preserve">42.3992958068848</t>
   </si>
   <si>
-    <t xml:space="preserve">43.004581451416</t>
+    <t xml:space="preserve">43.0045852661133</t>
   </si>
   <si>
     <t xml:space="preserve">43.9653663635254</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8596801757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7147750854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2632141113281</t>
+    <t xml:space="preserve">43.8596839904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7147789001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2632102966309</t>
   </si>
   <si>
     <t xml:space="preserve">43.7251739501953</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0038032531738</t>
+    <t xml:space="preserve">44.0037994384766</t>
   </si>
   <si>
     <t xml:space="preserve">44.2055625915527</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">42.2551765441895</t>
   </si>
   <si>
-    <t xml:space="preserve">42.860466003418</t>
+    <t xml:space="preserve">42.8604698181152</t>
   </si>
   <si>
     <t xml:space="preserve">42.8028221130371</t>
@@ -3587,10 +3587,10 @@
     <t xml:space="preserve">40.1606712341309</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2655754089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1798858642578</t>
+    <t xml:space="preserve">41.2655715942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1798896789551</t>
   </si>
   <si>
     <t xml:space="preserve">40.1414566040039</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">42.562629699707</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5330123901367</t>
+    <t xml:space="preserve">43.533016204834</t>
   </si>
   <si>
     <t xml:space="preserve">43.6579170227051</t>
@@ -3638,10 +3638,10 @@
     <t xml:space="preserve">44.8108558654785</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8885040283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0518341064453</t>
+    <t xml:space="preserve">43.8885078430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0518379211426</t>
   </si>
   <si>
     <t xml:space="preserve">42.5914497375488</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">41.8708648681641</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0261650085449</t>
+    <t xml:space="preserve">40.0261611938477</t>
   </si>
   <si>
     <t xml:space="preserve">39.267147064209</t>
@@ -3662,10 +3662,10 @@
     <t xml:space="preserve">38.383228302002</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1814651489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2014694213867</t>
+    <t xml:space="preserve">38.1814613342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2014656066895</t>
   </si>
   <si>
     <t xml:space="preserve">35.7795104980469</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">35.0397109985352</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4632377624512</t>
+    <t xml:space="preserve">34.4632339477539</t>
   </si>
   <si>
     <t xml:space="preserve">36.0581321716309</t>
@@ -3701,7 +3701,7 @@
     <t xml:space="preserve">34.6553955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7138252258301</t>
+    <t xml:space="preserve">33.7138290405273</t>
   </si>
   <si>
     <t xml:space="preserve">35.1165657043457</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">34.7418632507324</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2710838317871</t>
+    <t xml:space="preserve">34.2710800170898</t>
   </si>
   <si>
     <t xml:space="preserve">34.280689239502</t>
@@ -3743,10 +3743,10 @@
     <t xml:space="preserve">35.933235168457</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9420585632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4712677001953</t>
+    <t xml:space="preserve">36.9420547485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4712715148926</t>
   </si>
   <si>
     <t xml:space="preserve">36.4520530700684</t>
@@ -3767,16 +3767,16 @@
     <t xml:space="preserve">33.7042236328125</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4344100952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1357841491699</t>
+    <t xml:space="preserve">34.4344139099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1357803344727</t>
   </si>
   <si>
     <t xml:space="preserve">34.9244117736816</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2695083618164</t>
+    <t xml:space="preserve">36.2695121765137</t>
   </si>
   <si>
     <t xml:space="preserve">36.3175430297852</t>
@@ -3791,19 +3791,19 @@
     <t xml:space="preserve">35.0973510742188</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7602958679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.211856842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5081329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0173416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9500846862793</t>
+    <t xml:space="preserve">35.7602920532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2118606567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.508129119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0173454284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9500885009766</t>
   </si>
   <si>
     <t xml:space="preserve">40.2375373840332</t>
@@ -3812,7 +3812,7 @@
     <t xml:space="preserve">41.2943916320801</t>
   </si>
   <si>
-    <t xml:space="preserve">40.890869140625</t>
+    <t xml:space="preserve">40.8908653259277</t>
   </si>
   <si>
     <t xml:space="preserve">40.6891021728516</t>
@@ -3821,16 +3821,16 @@
     <t xml:space="preserve">39.8340072631836</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6330261230469</t>
+    <t xml:space="preserve">38.6330299377441</t>
   </si>
   <si>
     <t xml:space="preserve">39.4208717346191</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2191047668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.623420715332</t>
+    <t xml:space="preserve">39.219108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6234245300293</t>
   </si>
   <si>
     <t xml:space="preserve">37.9796981811523</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">36.7210731506348</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1349983215332</t>
+    <t xml:space="preserve">36.1350021362305</t>
   </si>
   <si>
     <t xml:space="preserve">35.7218627929688</t>
@@ -3866,10 +3866,10 @@
     <t xml:space="preserve">34.0693168640137</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2726554870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9836387634277</t>
+    <t xml:space="preserve">32.2726593017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9836349487305</t>
   </si>
   <si>
     <t xml:space="preserve">32.9740257263184</t>
@@ -3878,16 +3878,16 @@
     <t xml:space="preserve">31.0524616241455</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9067726135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9163780212402</t>
+    <t xml:space="preserve">32.9067687988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.916374206543</t>
   </si>
   <si>
     <t xml:space="preserve">32.9644165039062</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2734413146973</t>
+    <t xml:space="preserve">31.2734432220459</t>
   </si>
   <si>
     <t xml:space="preserve">30.3414840698242</t>
@@ -71588,7 +71588,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6911458333</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>1444780</v>
@@ -71609,6 +71609,32 @@
         <v>2061</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6920833333</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>1121183</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>14.6499996185303</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>14.4250001907349</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>14.5749998092651</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>2052</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -47,25 +47,25 @@
     <t xml:space="preserve">7.39109230041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31191873550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36780595779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15357112884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96262359619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21877241134644</t>
+    <t xml:space="preserve">7.31191825866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36780500411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15357065200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96262264251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21877288818359</t>
   </si>
   <si>
     <t xml:space="preserve">7.2793173789978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16288614273071</t>
+    <t xml:space="preserve">7.16288566589355</t>
   </si>
   <si>
     <t xml:space="preserve">7.0324821472168</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">6.9859094619751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13494253158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34451913833618</t>
+    <t xml:space="preserve">7.13494205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34451961517334</t>
   </si>
   <si>
     <t xml:space="preserve">7.23740196228027</t>
@@ -92,13 +92,13 @@
     <t xml:space="preserve">7.35383367538452</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14891386032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18151473999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40972185134888</t>
+    <t xml:space="preserve">7.14891481399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18151521682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40972089767456</t>
   </si>
   <si>
     <t xml:space="preserve">7.28397512435913</t>
@@ -107,19 +107,19 @@
     <t xml:space="preserve">7.13959980010986</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05111122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84619188308716</t>
+    <t xml:space="preserve">7.05111169815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84619140625</t>
   </si>
   <si>
     <t xml:space="preserve">6.51086759567261</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45498037338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5900411605835</t>
+    <t xml:space="preserve">6.45498085021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59004163742065</t>
   </si>
   <si>
     <t xml:space="preserve">6.33389139175415</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">6.29197597503662</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42237949371338</t>
+    <t xml:space="preserve">6.42237997055054</t>
   </si>
   <si>
     <t xml:space="preserve">6.61798524856567</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8834490776062</t>
+    <t xml:space="preserve">6.88344955444336</t>
   </si>
   <si>
     <t xml:space="preserve">6.71113061904907</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">6.83687734603882</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70181608200073</t>
+    <t xml:space="preserve">6.70181655883789</t>
   </si>
   <si>
     <t xml:space="preserve">6.6272988319397</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">6.9952244758606</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89276504516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80427503585815</t>
+    <t xml:space="preserve">6.89276456832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80427598953247</t>
   </si>
   <si>
     <t xml:space="preserve">6.79961824417114</t>
@@ -164,16 +164,16 @@
     <t xml:space="preserve">6.84153413772583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65989971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63195610046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79496097564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78564596176147</t>
+    <t xml:space="preserve">6.6599006652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63195705413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79496145248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78564643859863</t>
   </si>
   <si>
     <t xml:space="preserve">6.86016273498535</t>
@@ -182,130 +182,130 @@
     <t xml:space="preserve">7.00919580459595</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11165618896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08371210098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2094578742981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10699892044067</t>
+    <t xml:space="preserve">7.11165571212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08371162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20945739746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10699796676636</t>
   </si>
   <si>
     <t xml:space="preserve">7.04179668426514</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24205923080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09768390655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17219972610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93467903137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91605091094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00453853607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27000331878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32588958740234</t>
+    <t xml:space="preserve">7.2420597076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09768438339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17220020294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93467950820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91605043411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00453805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27000284194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32589054107666</t>
   </si>
   <si>
     <t xml:space="preserve">7.22808742523193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50286769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41437816619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48423671722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57738351821899</t>
+    <t xml:space="preserve">7.50286674499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41437864303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48423719406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57738304138184</t>
   </si>
   <si>
     <t xml:space="preserve">7.55409574508667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73107290267944</t>
+    <t xml:space="preserve">7.73107385635376</t>
   </si>
   <si>
     <t xml:space="preserve">7.60066986083984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64258527755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70312976837158</t>
+    <t xml:space="preserve">7.64258623123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70313024520874</t>
   </si>
   <si>
     <t xml:space="preserve">7.73573017120361</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88476419448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88942050933838</t>
+    <t xml:space="preserve">7.88476276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88942193984985</t>
   </si>
   <si>
     <t xml:space="preserve">7.87079000473022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78696012496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94530630111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88010549545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08968448638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01760387420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09717082977295</t>
+    <t xml:space="preserve">7.78696060180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94530773162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88010501861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08968162536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01760482788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09717178344727</t>
   </si>
   <si>
     <t xml:space="preserve">8.10653305053711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.050368309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17205715179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21418190002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23758697509766</t>
+    <t xml:space="preserve">8.05036926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17205905914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21418380737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23758602142334</t>
   </si>
   <si>
     <t xml:space="preserve">8.22354412078857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1580171585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07844924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0831298828125</t>
+    <t xml:space="preserve">8.15801811218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07845115661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08313083648682</t>
   </si>
   <si>
     <t xml:space="preserve">8.14397525787354</t>
@@ -314,37 +314,37 @@
     <t xml:space="preserve">8.01292419433594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91463375091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82102537155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64316844940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62912607192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6525297164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55892038345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63848829269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98952102661133</t>
+    <t xml:space="preserve">7.91463422775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8210244178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64316892623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62912654876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65253114700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55891990661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63848876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9895224571228</t>
   </si>
   <si>
     <t xml:space="preserve">7.94739818572998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05972766876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67593240737915</t>
+    <t xml:space="preserve">8.05972862243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67593097686768</t>
   </si>
   <si>
     <t xml:space="preserve">7.71337509155273</t>
@@ -353,61 +353,61 @@
     <t xml:space="preserve">7.72273635864258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87251043319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92867755889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89123249053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81166458129883</t>
+    <t xml:space="preserve">7.87250995635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92867708206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89123201370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81166553497314</t>
   </si>
   <si>
     <t xml:space="preserve">7.7180552482605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88187074661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96143960952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91931438446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90995311737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0550479888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18141937255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16737842559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19546031951904</t>
+    <t xml:space="preserve">7.88186979293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96143817901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91931390762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90995264053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05504703521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18141841888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16737747192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19546127319336</t>
   </si>
   <si>
     <t xml:space="preserve">8.19078063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3077917098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36395740509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34991550445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3311939239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29375076293945</t>
+    <t xml:space="preserve">8.30779266357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36395835876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34991645812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33119297027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29374885559082</t>
   </si>
   <si>
     <t xml:space="preserve">8.1533374786377</t>
@@ -416,40 +416,40 @@
     <t xml:space="preserve">8.28906917572021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36863708496094</t>
+    <t xml:space="preserve">8.36863803863525</t>
   </si>
   <si>
     <t xml:space="preserve">8.50905132293701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60734176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51373291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63542366027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75711441040039</t>
+    <t xml:space="preserve">8.60734081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51373386383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63542175292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75711345672607</t>
   </si>
   <si>
     <t xml:space="preserve">8.65414428710938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78519630432129</t>
+    <t xml:space="preserve">8.78519725799561</t>
   </si>
   <si>
     <t xml:space="preserve">8.8085994720459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92093086242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84604358673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81796073913574</t>
+    <t xml:space="preserve">8.92092990875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84604263305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81796169281006</t>
   </si>
   <si>
     <t xml:space="preserve">8.74775409698486</t>
@@ -458,43 +458,43 @@
     <t xml:space="preserve">8.75243473052979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82264232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73371124267578</t>
+    <t xml:space="preserve">8.82264137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7337121963501</t>
   </si>
   <si>
     <t xml:space="preserve">8.77115535736084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76179313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6588249206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59329986572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57457828521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56053733825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48564910888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54181385040283</t>
+    <t xml:space="preserve">8.761794090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65882587432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59329891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57457733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56053638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4856481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54181480407715</t>
   </si>
   <si>
     <t xml:space="preserve">8.5324535369873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66818714141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49969005584717</t>
+    <t xml:space="preserve">8.66818618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49969100952148</t>
   </si>
   <si>
     <t xml:space="preserve">8.61670112609863</t>
@@ -503,61 +503,61 @@
     <t xml:space="preserve">8.49500846862793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5558557510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61202049255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46692657470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52777290344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56521606445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69158840179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08006477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24856281280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07070541381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01453876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89284801483154</t>
+    <t xml:space="preserve">8.55585670471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61202144622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46692752838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5277738571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56521701812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69158935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0800666809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24856090545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07070255279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01453971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89284706115723</t>
   </si>
   <si>
     <t xml:space="preserve">8.93965339660645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81328105926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50437068939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42480373382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40140056610107</t>
+    <t xml:space="preserve">8.8132791519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50437164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42480278015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40140151977539</t>
   </si>
   <si>
     <t xml:space="preserve">8.39671993255615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5839376449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34523677825928</t>
+    <t xml:space="preserve">8.58393859863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34523487091064</t>
   </si>
   <si>
     <t xml:space="preserve">8.46224689483643</t>
@@ -566,13 +566,13 @@
     <t xml:space="preserve">8.3826789855957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47160720825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98645687103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09878826141357</t>
+    <t xml:space="preserve">8.47160625457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9864559173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09878730773926</t>
   </si>
   <si>
     <t xml:space="preserve">9.0613431930542</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">8.51841259002686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16269874572754</t>
+    <t xml:space="preserve">8.16269969940186</t>
   </si>
   <si>
     <t xml:space="preserve">8.31247234344482</t>
@@ -590,46 +590,46 @@
     <t xml:space="preserve">7.4419093132019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98484182357788</t>
+    <t xml:space="preserve">7.98484086990356</t>
   </si>
   <si>
     <t xml:space="preserve">7.95675897598267</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38736057281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41075992584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44820308685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48096942901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37331771850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23290538787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1860990524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37799835205078</t>
+    <t xml:space="preserve">8.38735866546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41076183319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44820499420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48096752166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37331676483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23290348052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18610000610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37799739837646</t>
   </si>
   <si>
     <t xml:space="preserve">8.57925701141357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64946460723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72435092926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67286586761475</t>
+    <t xml:space="preserve">8.64946365356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72435188293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67286777496338</t>
   </si>
   <si>
     <t xml:space="preserve">8.74307250976562</t>
@@ -638,46 +638,46 @@
     <t xml:space="preserve">8.71031093597412</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15495300292969</t>
+    <t xml:space="preserve">9.15495204925537</t>
   </si>
   <si>
     <t xml:space="preserve">8.96773433685303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14091110229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2672815322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33749008178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4076976776123</t>
+    <t xml:space="preserve">9.14091205596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26728248596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33748912811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40769672393799</t>
   </si>
   <si>
     <t xml:space="preserve">9.37961578369141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29536533355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3608922958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44513893127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48258495330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43578052520752</t>
+    <t xml:space="preserve">9.29536628723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36089134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44514179229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48258304595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4357795715332</t>
   </si>
   <si>
     <t xml:space="preserve">9.35621070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11282825469971</t>
+    <t xml:space="preserve">9.11282730102539</t>
   </si>
   <si>
     <t xml:space="preserve">9.10814762115479</t>
@@ -686,46 +686,46 @@
     <t xml:space="preserve">9.15963363647461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4638614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81021499633789</t>
+    <t xml:space="preserve">9.46386241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81021595001221</t>
   </si>
   <si>
     <t xml:space="preserve">9.95999050140381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82893657684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91318511962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6417179107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70724582672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71660614013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66044044494629</t>
+    <t xml:space="preserve">9.82893562316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91318607330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64171886444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70724678039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71660709381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66043949127197</t>
   </si>
   <si>
     <t xml:space="preserve">9.79149341583252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0255165100098</t>
+    <t xml:space="preserve">10.0255155563354</t>
   </si>
   <si>
     <t xml:space="preserve">10.0067939758301</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1846504211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2408170700073</t>
+    <t xml:space="preserve">10.1846513748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.240816116333</t>
   </si>
   <si>
     <t xml:space="preserve">10.2595376968384</t>
@@ -737,13 +737,13 @@
     <t xml:space="preserve">10.4748382568359</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3625068664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3344249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5778112411499</t>
+    <t xml:space="preserve">10.3625078201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3344259262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.577808380127</t>
   </si>
   <si>
     <t xml:space="preserve">10.5122814178467</t>
@@ -764,22 +764,22 @@
     <t xml:space="preserve">10.6526956558228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6433334350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6246137619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7088603973389</t>
+    <t xml:space="preserve">10.6433343887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6246118545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7088594436646</t>
   </si>
   <si>
     <t xml:space="preserve">10.8960790634155</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8399133682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9335231781006</t>
+    <t xml:space="preserve">10.8399143218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9335222244263</t>
   </si>
   <si>
     <t xml:space="preserve">10.9990482330322</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">11.1301012039185</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0926570892334</t>
+    <t xml:space="preserve">11.0926580429077</t>
   </si>
   <si>
     <t xml:space="preserve">11.2517929077148</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">10.9616050720215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2049894332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1675443649292</t>
+    <t xml:space="preserve">11.2049875259399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1675462722778</t>
   </si>
   <si>
     <t xml:space="preserve">11.1488227844238</t>
@@ -812,13 +812,13 @@
     <t xml:space="preserve">11.2798748016357</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4296493530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.410927772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4577312469482</t>
+    <t xml:space="preserve">11.4296503067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4109268188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4577322006226</t>
   </si>
   <si>
     <t xml:space="preserve">11.5801239013672</t>
@@ -830,31 +830,31 @@
     <t xml:space="preserve">11.8625659942627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9472980499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9190540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9284696578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9378833770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9661273956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602750778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0979337692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0226173400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2109107971191</t>
+    <t xml:space="preserve">11.9472990036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9190530776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9284687042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9378843307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9661283493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0602741241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0979347229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0226163864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2109117507935</t>
   </si>
   <si>
     <t xml:space="preserve">12.1826667785645</t>
@@ -863,28 +863,28 @@
     <t xml:space="preserve">12.2391557693481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9096403121948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1450080871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4859752655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2976808547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6931009292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7307605743408</t>
+    <t xml:space="preserve">11.9096393585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1450071334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4859762191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2976818084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6930999755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7307596206665</t>
   </si>
   <si>
     <t xml:space="preserve">11.7684173583984</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7590026855469</t>
+    <t xml:space="preserve">11.7590045928955</t>
   </si>
   <si>
     <t xml:space="preserve">11.627197265625</t>
@@ -893,25 +893,25 @@
     <t xml:space="preserve">11.5707092285156</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5236349105835</t>
+    <t xml:space="preserve">11.5236358642578</t>
   </si>
   <si>
     <t xml:space="preserve">11.4671468734741</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3729982376099</t>
+    <t xml:space="preserve">11.3730001449585</t>
   </si>
   <si>
     <t xml:space="preserve">11.0811433792114</t>
   </si>
   <si>
-    <t xml:space="preserve">10.88343334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6951379776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5633316040039</t>
+    <t xml:space="preserve">10.8834323883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6951370239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5633325576782</t>
   </si>
   <si>
     <t xml:space="preserve">10.610405921936</t>
@@ -920,19 +920,19 @@
     <t xml:space="preserve">10.7422122955322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.911678314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9022636413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9493370056152</t>
+    <t xml:space="preserve">10.9116773605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9022617340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9493360519409</t>
   </si>
   <si>
     <t xml:space="preserve">11.1376314163208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3541688919067</t>
+    <t xml:space="preserve">11.3541698455811</t>
   </si>
   <si>
     <t xml:space="preserve">11.3824138641357</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">11.3447561264038</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4106569290161</t>
+    <t xml:space="preserve">11.4106597900391</t>
   </si>
   <si>
     <t xml:space="preserve">11.269437789917</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">11.5048055648804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4294872283936</t>
+    <t xml:space="preserve">11.4294881820679</t>
   </si>
   <si>
     <t xml:space="preserve">11.3353404998779</t>
@@ -959,46 +959,46 @@
     <t xml:space="preserve">11.2788515090942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2506084442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1093873977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0340700149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9210929870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6668930053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8363609313965</t>
+    <t xml:space="preserve">11.2506065368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1093854904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0340690612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9210910797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6668949127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8363590240479</t>
   </si>
   <si>
     <t xml:space="preserve">10.7892866134644</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1941194534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1658744812012</t>
+    <t xml:space="preserve">11.1941204071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1658754348755</t>
   </si>
   <si>
     <t xml:space="preserve">11.0717277526855</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1282167434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3165111541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3259248733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2411937713623</t>
+    <t xml:space="preserve">11.1282157897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3165102005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3259258270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.241192817688</t>
   </si>
   <si>
     <t xml:space="preserve">11.062313079834</t>
@@ -1016,61 +1016,61 @@
     <t xml:space="preserve">11.7213439941406</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8154926300049</t>
+    <t xml:space="preserve">11.8154916763306</t>
   </si>
   <si>
     <t xml:space="preserve">11.984956741333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.013201713562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.956711769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0508594512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.041446685791</t>
+    <t xml:space="preserve">12.0132026672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9567136764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0508604049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0414447784424</t>
   </si>
   <si>
     <t xml:space="preserve">12.0791034698486</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9755411148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.834321975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.220326423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1544208526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.107349395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4839372634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5215978622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6439895629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.785210609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8134536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8322839736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8040409088135</t>
+    <t xml:space="preserve">11.9755420684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8343210220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2203254699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1544227600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1073474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4839382171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.521595954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.643988609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7852096557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8134546279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8322830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8040399551392</t>
   </si>
   <si>
     <t xml:space="preserve">12.1920804977417</t>
@@ -1079,22 +1079,22 @@
     <t xml:space="preserve">11.7872486114502</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8531513214111</t>
+    <t xml:space="preserve">11.8531494140625</t>
   </si>
   <si>
     <t xml:space="preserve">12.0320310592651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1732511520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2768135070801</t>
+    <t xml:space="preserve">12.1732530593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2768144607544</t>
   </si>
   <si>
     <t xml:space="preserve">11.9002246856689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.448317527771</t>
+    <t xml:space="preserve">11.4483165740967</t>
   </si>
   <si>
     <t xml:space="preserve">11.5612936019897</t>
@@ -1103,43 +1103,43 @@
     <t xml:space="preserve">11.4012432098389</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6742715835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7778339385986</t>
+    <t xml:space="preserve">11.6742706298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7778329849243</t>
   </si>
   <si>
     <t xml:space="preserve">12.0885190963745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0696887969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2014961242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.135594367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3615455627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3333034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1638374328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7401742935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1261787414551</t>
+    <t xml:space="preserve">12.0696897506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2014970779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1355934143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3615474700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3333024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1638383865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7401752471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1261777877808</t>
   </si>
   <si>
     <t xml:space="preserve">12.5404262542725</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5498428344727</t>
+    <t xml:space="preserve">12.5498418807983</t>
   </si>
   <si>
     <t xml:space="preserve">12.5027675628662</t>
@@ -1148,16 +1148,16 @@
     <t xml:space="preserve">12.6345739364624</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1335563659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1241397857666</t>
+    <t xml:space="preserve">13.1335525512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1241388320923</t>
   </si>
   <si>
     <t xml:space="preserve">13.086480140686</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9546737670898</t>
+    <t xml:space="preserve">12.9546747207642</t>
   </si>
   <si>
     <t xml:space="preserve">13.4254121780396</t>
@@ -1175,37 +1175,37 @@
     <t xml:space="preserve">13.6042919158936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5101451873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2559452056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4724864959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3030185699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9735021591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.615743637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.408618927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3803749084473</t>
+    <t xml:space="preserve">13.5101442337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2559471130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.472484588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3030195236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9735040664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6157445907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4086208343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3803758621216</t>
   </si>
   <si>
     <t xml:space="preserve">12.4651079177856</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5121831893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8228693008423</t>
+    <t xml:space="preserve">12.5121822357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.822868347168</t>
   </si>
   <si>
     <t xml:space="preserve">12.8793573379517</t>
@@ -1223,22 +1223,22 @@
     <t xml:space="preserve">12.257984161377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7287225723267</t>
+    <t xml:space="preserve">12.7287216186523</t>
   </si>
   <si>
     <t xml:space="preserve">13.0394077301025</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0958957672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.26535987854</t>
+    <t xml:space="preserve">13.0958948135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2653608322144</t>
   </si>
   <si>
     <t xml:space="preserve">13.4065818786621</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3312644958496</t>
+    <t xml:space="preserve">13.3312635421753</t>
   </si>
   <si>
     <t xml:space="preserve">13.3218488693237</t>
@@ -1247,58 +1247,58 @@
     <t xml:space="preserve">13.1617984771729</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3406782150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2465305328369</t>
+    <t xml:space="preserve">13.3406772613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2465314865112</t>
   </si>
   <si>
     <t xml:space="preserve">12.8887710571289</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8605279922485</t>
+    <t xml:space="preserve">12.8605270385742</t>
   </si>
   <si>
     <t xml:space="preserve">13.293604850769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5666332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6419496536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3124351501465</t>
+    <t xml:space="preserve">13.566632270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6419515609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3124341964722</t>
   </si>
   <si>
     <t xml:space="preserve">13.7925863265991</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9997100830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1409320831299</t>
+    <t xml:space="preserve">13.9997110366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1409311294556</t>
   </si>
   <si>
     <t xml:space="preserve">14.3951301574707</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3009805679321</t>
+    <t xml:space="preserve">14.3009824752808</t>
   </si>
   <si>
     <t xml:space="preserve">14.5645942687988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6022539138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6869869232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9129400253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8564500808716</t>
+    <t xml:space="preserve">14.6022548675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6869859695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9129409790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8564510345459</t>
   </si>
   <si>
     <t xml:space="preserve">15.1106481552124</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">14.9694271087646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.997673034668</t>
+    <t xml:space="preserve">14.9976711273193</t>
   </si>
   <si>
     <t xml:space="preserve">15.0353317260742</t>
@@ -1316,97 +1316,97 @@
     <t xml:space="preserve">14.903525352478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8941097259521</t>
+    <t xml:space="preserve">14.8941087722778</t>
   </si>
   <si>
     <t xml:space="preserve">14.7152309417725</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5928392410278</t>
+    <t xml:space="preserve">14.5928373336792</t>
   </si>
   <si>
     <t xml:space="preserve">15.1671371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2706985473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2424554824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2518701553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4401636123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3930912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5531425476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.656702041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4213342666626</t>
+    <t xml:space="preserve">15.2706995010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2424564361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2518720626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.44016456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3930902481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5531435012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6567039489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4213352203369</t>
   </si>
   <si>
     <t xml:space="preserve">15.0165023803711</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3460178375244</t>
+    <t xml:space="preserve">15.3460187911987</t>
   </si>
   <si>
     <t xml:space="preserve">14.818528175354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6668338775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3444881439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6099481582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7331991195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.875412940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9273300170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4013700485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6194295883179</t>
+    <t xml:space="preserve">14.6668357849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3444871902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6099500656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7332000732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8754119873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9273290634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4013710021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6194305419922</t>
   </si>
   <si>
     <t xml:space="preserve">14.6289110183716</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1882801055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4916667938232</t>
+    <t xml:space="preserve">15.1882791519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4916658401489</t>
   </si>
   <si>
     <t xml:space="preserve">16.1174011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4587097167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1553249359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1648025512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2027282714844</t>
+    <t xml:space="preserve">16.4587116241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1553268432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1648044586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.202730178833</t>
   </si>
   <si>
     <t xml:space="preserve">16.2122077941895</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">16.3259773254395</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1079196929932</t>
+    <t xml:space="preserve">16.1079177856445</t>
   </si>
   <si>
     <t xml:space="preserve">16.0699977874756</t>
@@ -1424,37 +1424,37 @@
     <t xml:space="preserve">16.5250759124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7241706848145</t>
+    <t xml:space="preserve">16.7241744995117</t>
   </si>
   <si>
     <t xml:space="preserve">16.6672878265381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5724792480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3070201873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2596130371094</t>
+    <t xml:space="preserve">16.5724811553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3070182800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2596111297607</t>
   </si>
   <si>
     <t xml:space="preserve">16.6767711639404</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8379421234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8853454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0465183258057</t>
+    <t xml:space="preserve">16.8379440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.885347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0465221405029</t>
   </si>
   <si>
     <t xml:space="preserve">16.9232692718506</t>
   </si>
   <si>
-    <t xml:space="preserve">16.771577835083</t>
+    <t xml:space="preserve">16.7715759277344</t>
   </si>
   <si>
     <t xml:space="preserve">16.373384475708</t>
@@ -1472,28 +1472,28 @@
     <t xml:space="preserve">16.5535182952881</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3639011383057</t>
+    <t xml:space="preserve">16.3639030456543</t>
   </si>
   <si>
     <t xml:space="preserve">16.5155944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1034069061279</t>
+    <t xml:space="preserve">17.1034088134766</t>
   </si>
   <si>
     <t xml:space="preserve">17.5395240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9471988677979</t>
+    <t xml:space="preserve">17.9472007751465</t>
   </si>
   <si>
     <t xml:space="preserve">17.4447154998779</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0799293518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1652603149414</t>
+    <t xml:space="preserve">18.0799331665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1652584075928</t>
   </si>
   <si>
     <t xml:space="preserve">18.7151470184326</t>
@@ -1502,43 +1502,43 @@
     <t xml:space="preserve">18.1368141174316</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4117584228516</t>
+    <t xml:space="preserve">18.4117565155029</t>
   </si>
   <si>
     <t xml:space="preserve">18.2505855560303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0704517364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8618698120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6343307495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7860260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7575836181641</t>
+    <t xml:space="preserve">18.0704498291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8618717193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.634334564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7860279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7575817108154</t>
   </si>
   <si>
     <t xml:space="preserve">18.2979888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3738346099854</t>
+    <t xml:space="preserve">18.373836517334</t>
   </si>
   <si>
     <t xml:space="preserve">18.203182220459</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0325298309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1083736419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2126617431641</t>
+    <t xml:space="preserve">18.0325260162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1083717346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2126598358154</t>
   </si>
   <si>
     <t xml:space="preserve">18.0609683990479</t>
@@ -1556,37 +1556,37 @@
     <t xml:space="preserve">18.3927974700928</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8334255218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0135631561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7435894012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3408813476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.41672706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3788051605225</t>
+    <t xml:space="preserve">17.8334293365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0135650634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7435874938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.340877532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4167289733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3788032531738</t>
   </si>
   <si>
     <t xml:space="preserve">19.1891860961914</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0564556121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7246265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4496803283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5255317687988</t>
+    <t xml:space="preserve">19.0564575195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7246284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4496822357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5255298614502</t>
   </si>
   <si>
     <t xml:space="preserve">18.7720317840576</t>
@@ -1604,55 +1604,55 @@
     <t xml:space="preserve">18.5065689086914</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0420093536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3025035858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5629978179932</t>
+    <t xml:space="preserve">18.0420074462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3025016784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5629997253418</t>
   </si>
   <si>
     <t xml:space="preserve">15.453742980957</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5864753723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6718034744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0081434249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4253015518188</t>
+    <t xml:space="preserve">15.5864772796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.671802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0081443786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4252996444702</t>
   </si>
   <si>
     <t xml:space="preserve">15.4632234573364</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8045330047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7286853790283</t>
+    <t xml:space="preserve">15.8045320510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7286863327026</t>
   </si>
   <si>
     <t xml:space="preserve">14.9512586593628</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0745086669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9986629486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9797019958496</t>
+    <t xml:space="preserve">15.0745096206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9986610412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9797029495239</t>
   </si>
   <si>
     <t xml:space="preserve">15.0176248550415</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8469696044922</t>
+    <t xml:space="preserve">14.8469686508179</t>
   </si>
   <si>
     <t xml:space="preserve">14.6573534011841</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">14.7047576904297</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6763143539429</t>
+    <t xml:space="preserve">14.6763153076172</t>
   </si>
   <si>
     <t xml:space="preserve">14.6478719711304</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">15.0555486679077</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7900857925415</t>
+    <t xml:space="preserve">14.7900848388672</t>
   </si>
   <si>
     <t xml:space="preserve">13.8135595321655</t>
@@ -1685,25 +1685,25 @@
     <t xml:space="preserve">13.1309413909912</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0835361480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3869228363037</t>
+    <t xml:space="preserve">13.0835371017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.386923789978</t>
   </si>
   <si>
     <t xml:space="preserve">13.263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3964033126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6523857116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2257499694824</t>
+    <t xml:space="preserve">13.3964042663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6523866653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4912118911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2257480621338</t>
   </si>
   <si>
     <t xml:space="preserve">13.8704462051392</t>
@@ -1721,10 +1721,10 @@
     <t xml:space="preserve">14.1643505096436</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3065633773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3350048065186</t>
+    <t xml:space="preserve">14.3065624237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3350057601929</t>
   </si>
   <si>
     <t xml:space="preserve">13.7946004867554</t>
@@ -1739,25 +1739,25 @@
     <t xml:space="preserve">13.7566757202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8988876342773</t>
+    <t xml:space="preserve">13.898886680603</t>
   </si>
   <si>
     <t xml:space="preserve">13.9462928771973</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4203329086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7756376266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7232656478882</t>
+    <t xml:space="preserve">14.4203338623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7756357192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7232646942139</t>
   </si>
   <si>
     <t xml:space="preserve">13.3205575942993</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1878261566162</t>
+    <t xml:space="preserve">13.1878252029419</t>
   </si>
   <si>
     <t xml:space="preserve">13.7471942901611</t>
@@ -1766,13 +1766,13 @@
     <t xml:space="preserve">14.069543838501</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8374900817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2546443939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8848924636841</t>
+    <t xml:space="preserve">14.8374881744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2546453475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8848934173584</t>
   </si>
   <si>
     <t xml:space="preserve">15.0839910507202</t>
@@ -1781,19 +1781,19 @@
     <t xml:space="preserve">15.1787986755371</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1503562927246</t>
+    <t xml:space="preserve">15.1503572463989</t>
   </si>
   <si>
     <t xml:space="preserve">15.3115301132202</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3589344024658</t>
+    <t xml:space="preserve">15.3589363098145</t>
   </si>
   <si>
     <t xml:space="preserve">15.2925682067871</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1408758163452</t>
+    <t xml:space="preserve">15.1408748626709</t>
   </si>
   <si>
     <t xml:space="preserve">15.0271062850952</t>
@@ -1811,88 +1811,88 @@
     <t xml:space="preserve">14.9417781829834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6149158477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7097244262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0650300979614</t>
+    <t xml:space="preserve">15.6149168014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7097225189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0650291442871</t>
   </si>
   <si>
     <t xml:space="preserve">15.216721534729</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5485506057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4347810745239</t>
+    <t xml:space="preserve">15.5485496520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4347829818726</t>
   </si>
   <si>
     <t xml:space="preserve">15.3968572616577</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7806043624878</t>
+    <t xml:space="preserve">14.7806053161621</t>
   </si>
   <si>
     <t xml:space="preserve">14.9038553237915</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2262020111084</t>
+    <t xml:space="preserve">15.226203918457</t>
   </si>
   <si>
     <t xml:space="preserve">15.1977605819702</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4442625045776</t>
+    <t xml:space="preserve">15.4442615509033</t>
   </si>
   <si>
     <t xml:space="preserve">15.3684148788452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5106287002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7381677627563</t>
+    <t xml:space="preserve">15.5106296539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7381687164307</t>
   </si>
   <si>
     <t xml:space="preserve">16.4302673339844</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9657068252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2641267776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7855710983276</t>
+    <t xml:space="preserve">15.9657096862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2641258239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7855701446533</t>
   </si>
   <si>
     <t xml:space="preserve">16.6862487792969</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8474235534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4966316223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1932487487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2311725616455</t>
+    <t xml:space="preserve">16.8474254608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4966335296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1932468414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2311687469482</t>
   </si>
   <si>
     <t xml:space="preserve">16.7526149749756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4207859039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8094997406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7336559295654</t>
+    <t xml:space="preserve">16.4207878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8095016479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7336540222168</t>
   </si>
   <si>
     <t xml:space="preserve">16.8948287963867</t>
@@ -1907,19 +1907,19 @@
     <t xml:space="preserve">15.8993425369263</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8898620605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9277830123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.851936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.354419708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.240650177002</t>
+    <t xml:space="preserve">15.8898611068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9277820587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8519353866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3544235229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2406482696533</t>
   </si>
   <si>
     <t xml:space="preserve">15.9183044433594</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">17.5015983581543</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6627750396729</t>
+    <t xml:space="preserve">17.6627731323242</t>
   </si>
   <si>
     <t xml:space="preserve">18.089412689209</t>
@@ -1937,43 +1937,43 @@
     <t xml:space="preserve">17.3119812011719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2835388183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8239459991455</t>
+    <t xml:space="preserve">17.2835445404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8239498138428</t>
   </si>
   <si>
     <t xml:space="preserve">18.6677417755127</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5743846893311</t>
+    <t xml:space="preserve">18.5743827819824</t>
   </si>
   <si>
     <t xml:space="preserve">18.8704280853271</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5962142944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5007171630859</t>
+    <t xml:space="preserve">19.596212387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5007133483887</t>
   </si>
   <si>
     <t xml:space="preserve">18.9277267456055</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9468250274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9850215911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.59348487854</t>
+    <t xml:space="preserve">18.9468231201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9850254058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5934810638428</t>
   </si>
   <si>
     <t xml:space="preserve">18.708080291748</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9659233093262</t>
+    <t xml:space="preserve">18.9659252166748</t>
   </si>
   <si>
     <t xml:space="preserve">19.0327739715576</t>
@@ -1982,16 +1982,16 @@
     <t xml:space="preserve">19.2333202362061</t>
   </si>
   <si>
-    <t xml:space="preserve">19.386116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0900726318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1951236724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1187229156494</t>
+    <t xml:space="preserve">19.3861179351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0900707244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1951198577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1187210083008</t>
   </si>
   <si>
     <t xml:space="preserve">19.2524185180664</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">19.9018077850342</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1501045227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2646980285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5893936157227</t>
+    <t xml:space="preserve">20.1501007080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2646999359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.589391708374</t>
   </si>
   <si>
     <t xml:space="preserve">20.5511932373047</t>
@@ -2018,25 +2018,25 @@
     <t xml:space="preserve">19.9591045379639</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8445091247559</t>
+    <t xml:space="preserve">19.8445072174072</t>
   </si>
   <si>
     <t xml:space="preserve">19.4816150665283</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3097190856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6344108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6726131439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0928058624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9400043487549</t>
+    <t xml:space="preserve">19.3097171783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6344127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6726093292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0928039550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9400062561035</t>
   </si>
   <si>
     <t xml:space="preserve">19.6535110473633</t>
@@ -2045,40 +2045,40 @@
     <t xml:space="preserve">19.558012008667</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7299098968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3029003143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2838001251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2265014648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7039909362793</t>
+    <t xml:space="preserve">19.7299118041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3028984069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2837982177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2264995574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7039928436279</t>
   </si>
   <si>
     <t xml:space="preserve">20.6848907470703</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4174957275391</t>
+    <t xml:space="preserve">20.4174976348877</t>
   </si>
   <si>
     <t xml:space="preserve">20.0355033874512</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1310024261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1882991790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2769813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1814823150635</t>
+    <t xml:space="preserve">20.1310005187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1883010864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2769794464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1814804077148</t>
   </si>
   <si>
     <t xml:space="preserve">20.436595916748</t>
@@ -2087,10 +2087,10 @@
     <t xml:space="preserve">20.0164031982422</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5702972412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9904842376709</t>
+    <t xml:space="preserve">20.5702934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9904861450195</t>
   </si>
   <si>
     <t xml:space="preserve">21.1050815582275</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">21.1623821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2578773498535</t>
+    <t xml:space="preserve">21.2578792572021</t>
   </si>
   <si>
     <t xml:space="preserve">21.0286846160889</t>
@@ -2111,10 +2111,10 @@
     <t xml:space="preserve">21.849967956543</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4802551269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5566558837891</t>
+    <t xml:space="preserve">22.4802570343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5566539764404</t>
   </si>
   <si>
     <t xml:space="preserve">22.5184555053711</t>
@@ -2123,19 +2123,19 @@
     <t xml:space="preserve">22.0982627868652</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2510585784912</t>
+    <t xml:space="preserve">22.2510623931885</t>
   </si>
   <si>
     <t xml:space="preserve">21.9645652770996</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9454669952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3083591461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5948524475098</t>
+    <t xml:space="preserve">21.9454689025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3083610534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5948543548584</t>
   </si>
   <si>
     <t xml:space="preserve">22.7476501464844</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">22.8049468994141</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0600624084473</t>
+    <t xml:space="preserve">22.0600643157959</t>
   </si>
   <si>
     <t xml:space="preserve">22.2319602966309</t>
@@ -2153,19 +2153,19 @@
     <t xml:space="preserve">21.3533802032471</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4747943878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4556980133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1241836547852</t>
+    <t xml:space="preserve">20.474796295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4556941986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1241855621338</t>
   </si>
   <si>
     <t xml:space="preserve">20.780387878418</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8758888244629</t>
+    <t xml:space="preserve">20.8758869171143</t>
   </si>
   <si>
     <t xml:space="preserve">21.0859813690186</t>
@@ -2180,46 +2180,46 @@
     <t xml:space="preserve">21.2196807861328</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3724784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6016750335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.678071975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4870758056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5825729370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6466941833496</t>
+    <t xml:space="preserve">21.3724765777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6016731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6780700683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4870777130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5825748443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.646692276001</t>
   </si>
   <si>
     <t xml:space="preserve">20.6084938049316</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4938945770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8567886352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3792972564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8949871063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9331855773926</t>
+    <t xml:space="preserve">20.4938926696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8567867279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3792953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8949851989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9331874847412</t>
   </si>
   <si>
     <t xml:space="preserve">20.3219985961914</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3410968780518</t>
+    <t xml:space="preserve">20.3410987854004</t>
   </si>
   <si>
     <t xml:space="preserve">21.830867767334</t>
@@ -2231,22 +2231,22 @@
     <t xml:space="preserve">22.5375537872314</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6521492004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0150470733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4543361663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7217330932617</t>
+    <t xml:space="preserve">22.6521511077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0150451660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4543342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7217311859131</t>
   </si>
   <si>
     <t xml:space="preserve">23.9127292633057</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5689353942871</t>
+    <t xml:space="preserve">23.5689334869385</t>
   </si>
   <si>
     <t xml:space="preserve">24.084623336792</t>
@@ -2258,13 +2258,13 @@
     <t xml:space="preserve">23.8745269775391</t>
   </si>
   <si>
-    <t xml:space="preserve">23.970027923584</t>
+    <t xml:space="preserve">23.9700260162354</t>
   </si>
   <si>
     <t xml:space="preserve">24.3711185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">24.867712020874</t>
+    <t xml:space="preserve">24.8677101135254</t>
   </si>
   <si>
     <t xml:space="preserve">25.0969047546387</t>
@@ -2276,13 +2276,13 @@
     <t xml:space="preserve">24.3329181671143</t>
   </si>
   <si>
-    <t xml:space="preserve">24.982307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2879009246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9250068664551</t>
+    <t xml:space="preserve">24.9823055267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.287899017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9250087738037</t>
   </si>
   <si>
     <t xml:space="preserve">25.0205078125</t>
@@ -2297,67 +2297,67 @@
     <t xml:space="preserve">24.8295097351074</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6385135650635</t>
+    <t xml:space="preserve">24.6385116577148</t>
   </si>
   <si>
     <t xml:space="preserve">24.4475173950195</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5430164337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3520183563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6576099395752</t>
+    <t xml:space="preserve">24.5430145263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3520164489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6576137542725</t>
   </si>
   <si>
     <t xml:space="preserve">24.6767139434814</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4857139587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5621166229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5812129974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6958141326904</t>
+    <t xml:space="preserve">24.4857158660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5621147155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5812149047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6958103179932</t>
   </si>
   <si>
     <t xml:space="preserve">25.3070011138916</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3451995849609</t>
+    <t xml:space="preserve">25.3451976776123</t>
   </si>
   <si>
     <t xml:space="preserve">24.8486099243164</t>
   </si>
   <si>
-    <t xml:space="preserve">25.001407623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2115001678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7653903961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6125946044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5552940368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.154203414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8226909637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7722091674805</t>
+    <t xml:space="preserve">25.0014038085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2115020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7653923034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6125926971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5552959442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1542015075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8226890563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7722110748291</t>
   </si>
   <si>
     <t xml:space="preserve">24.5239143371582</t>
@@ -2369,46 +2369,46 @@
     <t xml:space="preserve">25.6698932647705</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2237815856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.281078338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3956775665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1405639648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2169628143311</t>
+    <t xml:space="preserve">26.223783493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2810821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.395679473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1405620574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2169647216797</t>
   </si>
   <si>
     <t xml:space="preserve">27.5225563049316</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6944522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8281497955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1910438537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7831325531006</t>
+    <t xml:space="preserve">27.6944541931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8281517028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1910419464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.783130645752</t>
   </si>
   <si>
     <t xml:space="preserve">28.2865409851074</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8854503631592</t>
+    <t xml:space="preserve">27.8854484558105</t>
   </si>
   <si>
     <t xml:space="preserve">25.9754867553711</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2306003570557</t>
+    <t xml:space="preserve">25.2306022644043</t>
   </si>
   <si>
     <t xml:space="preserve">24.6003131866455</t>
@@ -2426,16 +2426,16 @@
     <t xml:space="preserve">19.8254089355469</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3479194641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5852918624878</t>
+    <t xml:space="preserve">19.3479175567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5852909088135</t>
   </si>
   <si>
     <t xml:space="preserve">17.3233585357666</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7285394668579</t>
+    <t xml:space="preserve">15.728536605835</t>
   </si>
   <si>
     <t xml:space="preserve">16.1200790405273</t>
@@ -2444,28 +2444,28 @@
     <t xml:space="preserve">16.9031677246094</t>
   </si>
   <si>
-    <t xml:space="preserve">17.523904800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7435493469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1350898742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8322277069092</t>
+    <t xml:space="preserve">17.5239028930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7435531616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1350917816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8322257995605</t>
   </si>
   <si>
     <t xml:space="preserve">18.1446418762207</t>
   </si>
   <si>
-    <t xml:space="preserve">18.221040725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1159896850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8772430419922</t>
+    <t xml:space="preserve">18.2210388183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1159915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8772449493408</t>
   </si>
   <si>
     <t xml:space="preserve">17.3806591033936</t>
@@ -2480,13 +2480,13 @@
     <t xml:space="preserve">17.6480522155762</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7844791412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4311332702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4454612731934</t>
+    <t xml:space="preserve">18.7844772338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4311351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4454593658447</t>
   </si>
   <si>
     <t xml:space="preserve">18.7653789520264</t>
@@ -2495,10 +2495,10 @@
     <t xml:space="preserve">17.9536437988281</t>
   </si>
   <si>
-    <t xml:space="preserve">20.866340637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2715187072754</t>
+    <t xml:space="preserve">20.8663368225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.271520614624</t>
   </si>
   <si>
     <t xml:space="preserve">18.8465538024902</t>
@@ -2510,28 +2510,28 @@
     <t xml:space="preserve">20.2455997467041</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9877529144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.968656539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7681102752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6753406524658</t>
+    <t xml:space="preserve">19.9877548217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9686546325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7681083679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6753425598145</t>
   </si>
   <si>
     <t xml:space="preserve">21.7640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3820247650146</t>
+    <t xml:space="preserve">21.3820285797119</t>
   </si>
   <si>
     <t xml:space="preserve">22.337007522583</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7926712036133</t>
+    <t xml:space="preserve">21.7926692962646</t>
   </si>
   <si>
     <t xml:space="preserve">21.019136428833</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">21.4297771453857</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8595180511475</t>
+    <t xml:space="preserve">21.8595161437988</t>
   </si>
   <si>
     <t xml:space="preserve">20.9522857666016</t>
@@ -2549,16 +2549,16 @@
     <t xml:space="preserve">21.9932155609131</t>
   </si>
   <si>
-    <t xml:space="preserve">21.658971786499</t>
+    <t xml:space="preserve">21.6589736938477</t>
   </si>
   <si>
     <t xml:space="preserve">23.0341453552246</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1391925811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.279712677002</t>
+    <t xml:space="preserve">23.1391906738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2797107696533</t>
   </si>
   <si>
     <t xml:space="preserve">23.5020847320557</t>
@@ -2576,43 +2576,43 @@
     <t xml:space="preserve">23.8172283172607</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3588352203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6903533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6330528259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8881664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0696144104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6999034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.938648223877</t>
+    <t xml:space="preserve">23.3588371276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6903514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6330509185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8881683349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0696125030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6999015808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9386463165283</t>
   </si>
   <si>
     <t xml:space="preserve">23.3015403747559</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6808013916016</t>
+    <t xml:space="preserve">22.6807994842529</t>
   </si>
   <si>
     <t xml:space="preserve">22.709451675415</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1487426757812</t>
+    <t xml:space="preserve">23.1487407684326</t>
   </si>
   <si>
     <t xml:space="preserve">23.463888168335</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4229583740234</t>
+    <t xml:space="preserve">22.4229564666748</t>
   </si>
   <si>
     <t xml:space="preserve">22.4611568450928</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">22.6426029205322</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7381000518799</t>
+    <t xml:space="preserve">22.7381019592285</t>
   </si>
   <si>
     <t xml:space="preserve">23.272891998291</t>
@@ -2633,13 +2633,13 @@
     <t xml:space="preserve">23.5402851104736</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7408313751221</t>
+    <t xml:space="preserve">23.7408294677734</t>
   </si>
   <si>
     <t xml:space="preserve">23.8363285064697</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7121810913086</t>
+    <t xml:space="preserve">23.71217918396</t>
   </si>
   <si>
     <t xml:space="preserve">23.7599296569824</t>
@@ -2648,16 +2648,16 @@
     <t xml:space="preserve">24.1610202789307</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3233680725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7340087890625</t>
+    <t xml:space="preserve">24.3233661651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7340126037598</t>
   </si>
   <si>
     <t xml:space="preserve">25.2783508300781</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0682525634766</t>
+    <t xml:space="preserve">25.0682544708252</t>
   </si>
   <si>
     <t xml:space="preserve">25.0587043762207</t>
@@ -2666,19 +2666,19 @@
     <t xml:space="preserve">24.7531108856201</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1351013183594</t>
+    <t xml:space="preserve">25.1351051330566</t>
   </si>
   <si>
     <t xml:space="preserve">26.5580234527588</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5102787017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6467056274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2292404174805</t>
+    <t xml:space="preserve">26.5102767944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6467037200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2292423248291</t>
   </si>
   <si>
     <t xml:space="preserve">27.5034561157227</t>
@@ -2687,10 +2687,10 @@
     <t xml:space="preserve">27.5894050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1596641540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5512046813965</t>
+    <t xml:space="preserve">27.1596622467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5512065887451</t>
   </si>
   <si>
     <t xml:space="preserve">27.0164165496826</t>
@@ -2705,37 +2705,37 @@
     <t xml:space="preserve">27.2265129089355</t>
   </si>
   <si>
-    <t xml:space="preserve">27.054615020752</t>
+    <t xml:space="preserve">27.0546169281006</t>
   </si>
   <si>
     <t xml:space="preserve">27.2838096618652</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5675754547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0450649261475</t>
+    <t xml:space="preserve">26.5675773620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0450668334961</t>
   </si>
   <si>
     <t xml:space="preserve">26.7108211517334</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5007266998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4529781341553</t>
+    <t xml:space="preserve">26.5007247924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4529762268066</t>
   </si>
   <si>
     <t xml:space="preserve">26.6630744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5389289855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2619819641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4625263214111</t>
+    <t xml:space="preserve">26.5389270782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2619800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4625244140625</t>
   </si>
   <si>
     <t xml:space="preserve">27.5989551544189</t>
@@ -2756,79 +2756,79 @@
     <t xml:space="preserve">28.1814918518066</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3533916473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5061874389648</t>
+    <t xml:space="preserve">28.3533897399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5061893463135</t>
   </si>
   <si>
     <t xml:space="preserve">28.9932270050049</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7926826477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6971797943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5798530578613</t>
+    <t xml:space="preserve">28.7926807403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6971836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.57985496521</t>
   </si>
   <si>
     <t xml:space="preserve">27.6562519073486</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4748058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6849040985107</t>
+    <t xml:space="preserve">27.4748077392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6849021911621</t>
   </si>
   <si>
     <t xml:space="preserve">29.3847713470459</t>
   </si>
   <si>
-    <t xml:space="preserve">29.967306137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1746711730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4802684783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8336124420166</t>
+    <t xml:space="preserve">29.9673080444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1746692657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4802665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.833610534668</t>
   </si>
   <si>
     <t xml:space="preserve">30.0246067047119</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1651248931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3274669647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8049583435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4734477996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9891376495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7503929138184</t>
+    <t xml:space="preserve">29.1651229858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3274707794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8049602508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.473445892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9891357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7503910064697</t>
   </si>
   <si>
     <t xml:space="preserve">30.5402965545654</t>
   </si>
   <si>
-    <t xml:space="preserve">30.922290802002</t>
+    <t xml:space="preserve">30.9222888946533</t>
   </si>
   <si>
     <t xml:space="preserve">30.7408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9318408966064</t>
+    <t xml:space="preserve">30.9318389892578</t>
   </si>
   <si>
     <t xml:space="preserve">30.7217407226562</t>
@@ -2840,10 +2840,10 @@
     <t xml:space="preserve">30.8172397613525</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4829998016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5593967437744</t>
+    <t xml:space="preserve">30.4829978942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5593948364258</t>
   </si>
   <si>
     <t xml:space="preserve">28.7258319854736</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">29.2128734588623</t>
   </si>
   <si>
-    <t xml:space="preserve">30.903190612793</t>
+    <t xml:space="preserve">30.9031887054443</t>
   </si>
   <si>
     <t xml:space="preserve">31.9918651580811</t>
@@ -2864,19 +2864,19 @@
     <t xml:space="preserve">33.6535377502441</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3097457885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4693603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3288383483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5580406188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1310272216797</t>
+    <t xml:space="preserve">33.309741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4693565368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3288421630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5580368041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.131031036377</t>
   </si>
   <si>
     <t xml:space="preserve">33.4338874816895</t>
@@ -2891,76 +2891,76 @@
     <t xml:space="preserve">33.9304809570312</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6603584289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6699066162109</t>
+    <t xml:space="preserve">32.6603546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6699028015137</t>
   </si>
   <si>
     <t xml:space="preserve">32.8513526916504</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5143756866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6098728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9727668762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7367477416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0587158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.256534576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8840885162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0177841186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1323833465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8745384216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0846366882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6194248199463</t>
+    <t xml:space="preserve">31.5143775939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6098709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.972770690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7367553710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0587120056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2565326690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8840923309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0177879333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1323852539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8745441436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0846328735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6194267272949</t>
   </si>
   <si>
     <t xml:space="preserve">32.0969161987305</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3615818023682</t>
+    <t xml:space="preserve">31.3615760803223</t>
   </si>
   <si>
     <t xml:space="preserve">32.1542091369629</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9441146850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4216079711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6958255767822</t>
+    <t xml:space="preserve">31.9441204071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4216156005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6958236694336</t>
   </si>
   <si>
     <t xml:space="preserve">32.2115097045898</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7435779571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2783584594727</t>
+    <t xml:space="preserve">31.7435684204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2783622741699</t>
   </si>
   <si>
     <t xml:space="preserve">32.5075569152832</t>
@@ -2972,22 +2972,22 @@
     <t xml:space="preserve">32.0491676330566</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5334777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2087860107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3165626525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1637649536133</t>
+    <t xml:space="preserve">31.5334758758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2087821960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3165588378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1637687683105</t>
   </si>
   <si>
     <t xml:space="preserve">32.1064682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3834114074707</t>
+    <t xml:space="preserve">32.3834075927734</t>
   </si>
   <si>
     <t xml:space="preserve">32.6221542358398</t>
@@ -2996,10 +2996,10 @@
     <t xml:space="preserve">32.650806427002</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8036003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5839538574219</t>
+    <t xml:space="preserve">32.8036041259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5839576721191</t>
   </si>
   <si>
     <t xml:space="preserve">32.3547592163086</t>
@@ -3011,13 +3011,13 @@
     <t xml:space="preserve">32.0396194458008</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5648536682129</t>
+    <t xml:space="preserve">32.5648574829102</t>
   </si>
   <si>
     <t xml:space="preserve">32.3261108398438</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9250202178955</t>
+    <t xml:space="preserve">31.9250164031982</t>
   </si>
   <si>
     <t xml:space="preserve">33.0423469543457</t>
@@ -3026,22 +3026,22 @@
     <t xml:space="preserve">33.7967796325684</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5989608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4843673706055</t>
+    <t xml:space="preserve">34.5989646911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4843711853027</t>
   </si>
   <si>
     <t xml:space="preserve">34.9427604675293</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8854598999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.000057220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8022384643555</t>
+    <t xml:space="preserve">34.8854560852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0000648498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8022422790527</t>
   </si>
   <si>
     <t xml:space="preserve">35.5539474487305</t>
@@ -3050,10 +3050,10 @@
     <t xml:space="preserve">35.334300994873</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2551689147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9018325805664</t>
+    <t xml:space="preserve">34.2551727294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9018287658691</t>
   </si>
   <si>
     <t xml:space="preserve">33.3670387268066</t>
@@ -3062,64 +3062,64 @@
     <t xml:space="preserve">33.3192901611328</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7817707061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8104190826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4598045349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7080993652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9768562316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4898166656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6876354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0027751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3875007629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6453456878662</t>
+    <t xml:space="preserve">31.7817726135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8104248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4598121643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7081031799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9768581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4898147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6876335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0027770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3874988555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6453437805176</t>
   </si>
   <si>
     <t xml:space="preserve">31.4761772155762</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5211944580078</t>
+    <t xml:space="preserve">30.5211963653564</t>
   </si>
   <si>
     <t xml:space="preserve">30.7312927246094</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1228313446045</t>
+    <t xml:space="preserve">31.1228351593018</t>
   </si>
   <si>
     <t xml:space="preserve">30.5498447418213</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5375690460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1487522125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6671752929688</t>
+    <t xml:space="preserve">29.5375652313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1487560272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6671772003174</t>
   </si>
   <si>
     <t xml:space="preserve">30.4065990447998</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7694931030273</t>
+    <t xml:space="preserve">30.7694911956787</t>
   </si>
   <si>
     <t xml:space="preserve">30.6644439697266</t>
@@ -3128,13 +3128,13 @@
     <t xml:space="preserve">30.3111019134521</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9413909912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2756290435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.960485458374</t>
+    <t xml:space="preserve">30.9413890838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2756328582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9604873657227</t>
   </si>
   <si>
     <t xml:space="preserve">31.5812244415283</t>
@@ -3143,49 +3143,49 @@
     <t xml:space="preserve">31.3424816131592</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5007400512695</t>
+    <t xml:space="preserve">33.5007362365723</t>
   </si>
   <si>
     <t xml:space="preserve">32.9373016357422</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8731803894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6344337463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6248817443848</t>
+    <t xml:space="preserve">33.8731880187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6344375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.624885559082</t>
   </si>
   <si>
     <t xml:space="preserve">34.1787757873535</t>
   </si>
   <si>
-    <t xml:space="preserve">34.216983795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9905128479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8281669616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3029174804688</t>
+    <t xml:space="preserve">34.2169761657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9905052185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8281593322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.302921295166</t>
   </si>
   <si>
     <t xml:space="preserve">33.1091957092285</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5484886169434</t>
+    <t xml:space="preserve">33.5484924316406</t>
   </si>
   <si>
     <t xml:space="preserve">33.8063354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">33.233341217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.092830657959</t>
+    <t xml:space="preserve">33.2333450317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0928268432617</t>
   </si>
   <si>
     <t xml:space="preserve">33.5771369934082</t>
@@ -3197,31 +3197,31 @@
     <t xml:space="preserve">31.9059200286865</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8868179321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0873680114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9468536376953</t>
+    <t xml:space="preserve">31.8868217468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0873603820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.946849822998</t>
   </si>
   <si>
     <t xml:space="preserve">33.1378440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7995109558105</t>
+    <t xml:space="preserve">34.7995071411133</t>
   </si>
   <si>
     <t xml:space="preserve">35.8851928710938</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6538200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9620590209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.769115447998</t>
+    <t xml:space="preserve">36.6538238525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9620552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7691192626953</t>
   </si>
   <si>
     <t xml:space="preserve">37.0765647888184</t>
@@ -3236,61 +3236,61 @@
     <t xml:space="preserve">37.018913269043</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6818542480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2391090393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7683296203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.883617401123</t>
+    <t xml:space="preserve">37.6818580627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2391128540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7683258056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8836212158203</t>
   </si>
   <si>
     <t xml:space="preserve">38.0181274414062</t>
   </si>
   <si>
-    <t xml:space="preserve">39.247932434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6138114929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6426391601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3440055847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5946006774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7963600158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7195053100586</t>
+    <t xml:space="preserve">39.2479286193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6138191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.642635345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3440093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.594596862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7963638305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7194976806641</t>
   </si>
   <si>
     <t xml:space="preserve">38.6042060852051</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6130294799805</t>
+    <t xml:space="preserve">39.6130256652832</t>
   </si>
   <si>
     <t xml:space="preserve">39.6514587402344</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7475357055664</t>
+    <t xml:space="preserve">39.7475395202637</t>
   </si>
   <si>
     <t xml:space="preserve">40.4969482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0069427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8051795959473</t>
+    <t xml:space="preserve">40.006950378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8051834106445</t>
   </si>
   <si>
     <t xml:space="preserve">39.9685134887695</t>
@@ -3305,31 +3305,31 @@
     <t xml:space="preserve">39.9973411560059</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0749855041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.576961517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5665626525879</t>
+    <t xml:space="preserve">39.0749893188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5769577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5665588378906</t>
   </si>
   <si>
     <t xml:space="preserve">37.5569534301758</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3736190795898</t>
+    <t xml:space="preserve">38.3736152648926</t>
   </si>
   <si>
     <t xml:space="preserve">38.9789123535156</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1614608764648</t>
+    <t xml:space="preserve">39.1614570617676</t>
   </si>
   <si>
     <t xml:space="preserve">38.4793014526367</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4496994018555</t>
+    <t xml:space="preserve">39.4496955871582</t>
   </si>
   <si>
     <t xml:space="preserve">39.1806755065918</t>
@@ -3338,19 +3338,19 @@
     <t xml:space="preserve">38.8540115356445</t>
   </si>
   <si>
-    <t xml:space="preserve">39.430477142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7675361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0453796386719</t>
+    <t xml:space="preserve">39.4304809570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7675399780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0453834533691</t>
   </si>
   <si>
     <t xml:space="preserve">40.6410636901855</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7275314331055</t>
+    <t xml:space="preserve">40.7275352478027</t>
   </si>
   <si>
     <t xml:space="preserve">40.3528289794922</t>
@@ -3362,10 +3362,10 @@
     <t xml:space="preserve">40.2567520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">40.333610534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2663536071777</t>
+    <t xml:space="preserve">40.3336143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2663612365723</t>
   </si>
   <si>
     <t xml:space="preserve">40.4489059448242</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">41.2367477416992</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5634078979492</t>
+    <t xml:space="preserve">41.5634155273438</t>
   </si>
   <si>
     <t xml:space="preserve">42.0822372436523</t>
@@ -3398,19 +3398,19 @@
     <t xml:space="preserve">42.2455711364746</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0342025756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7651824951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9669456481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4665489196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5434112548828</t>
+    <t xml:space="preserve">42.0341949462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7651786804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9669418334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4665451049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5434150695801</t>
   </si>
   <si>
     <t xml:space="preserve">42.6683158874512</t>
@@ -3428,19 +3428,19 @@
     <t xml:space="preserve">42.0245895385742</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9765472412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5345916748047</t>
+    <t xml:space="preserve">41.9765510559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.534595489502</t>
   </si>
   <si>
     <t xml:space="preserve">41.4577293395996</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7187118530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0061645507812</t>
+    <t xml:space="preserve">39.7187156677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0061569213867</t>
   </si>
   <si>
     <t xml:space="preserve">40.0165596008301</t>
@@ -3458,10 +3458,10 @@
     <t xml:space="preserve">43.1679191589355</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3112449645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2159576416016</t>
+    <t xml:space="preserve">44.3112487792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2159614562988</t>
   </si>
   <si>
     <t xml:space="preserve">41.9477272033691</t>
@@ -3470,19 +3470,19 @@
     <t xml:space="preserve">39.7859687805176</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2759666442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5842056274414</t>
+    <t xml:space="preserve">40.2759628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5842018127441</t>
   </si>
   <si>
     <t xml:space="preserve">39.1902847290039</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5169525146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6802825927734</t>
+    <t xml:space="preserve">39.5169486999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6802787780762</t>
   </si>
   <si>
     <t xml:space="preserve">40.10302734375</t>
@@ -3494,10 +3494,10 @@
     <t xml:space="preserve">39.0653800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9108772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2087135314941</t>
+    <t xml:space="preserve">39.9108734130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2087097167969</t>
   </si>
   <si>
     <t xml:space="preserve">41.2463569641113</t>
@@ -3509,22 +3509,22 @@
     <t xml:space="preserve">42.7932167053223</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5730247497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1694946289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2263526916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9469413757324</t>
+    <t xml:space="preserve">41.5730209350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1694869995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2263565063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9469375610352</t>
   </si>
   <si>
     <t xml:space="preserve">42.3800811767578</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3992958068848</t>
+    <t xml:space="preserve">42.3992919921875</t>
   </si>
   <si>
     <t xml:space="preserve">43.0045852661133</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">43.9653663635254</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8596839904785</t>
+    <t xml:space="preserve">43.8596801757812</t>
   </si>
   <si>
     <t xml:space="preserve">44.7147789001465</t>
@@ -3542,13 +3542,13 @@
     <t xml:space="preserve">44.2632102966309</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7251739501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0037994384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2055625915527</t>
+    <t xml:space="preserve">43.725170135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0038032531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2055587768555</t>
   </si>
   <si>
     <t xml:space="preserve">43.436939239502</t>
@@ -3566,10 +3566,10 @@
     <t xml:space="preserve">40.6794967651367</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6018447875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5449905395508</t>
+    <t xml:space="preserve">41.6018486022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5449829101562</t>
   </si>
   <si>
     <t xml:space="preserve">41.0830230712891</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">41.4289016723633</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4193000793457</t>
+    <t xml:space="preserve">41.4192962646484</t>
   </si>
   <si>
     <t xml:space="preserve">40.1318511962891</t>
@@ -3590,13 +3590,13 @@
     <t xml:space="preserve">41.2655715942383</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1798896789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1414566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.314395904541</t>
+    <t xml:space="preserve">40.1798858642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1414604187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3143997192383</t>
   </si>
   <si>
     <t xml:space="preserve">41.0926322937012</t>
@@ -3605,19 +3605,19 @@
     <t xml:space="preserve">41.9861602783203</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5057678222656</t>
+    <t xml:space="preserve">41.5057716369629</t>
   </si>
   <si>
     <t xml:space="preserve">42.3512573242188</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3704719543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.562629699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.533016204834</t>
+    <t xml:space="preserve">42.3704681396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5626220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5330200195312</t>
   </si>
   <si>
     <t xml:space="preserve">43.6579170227051</t>
@@ -3638,10 +3638,10 @@
     <t xml:space="preserve">44.8108558654785</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8885078430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0518379211426</t>
+    <t xml:space="preserve">43.8885040283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0518341064453</t>
   </si>
   <si>
     <t xml:space="preserve">42.5914497375488</t>
@@ -3653,10 +3653,10 @@
     <t xml:space="preserve">40.0261611938477</t>
   </si>
   <si>
-    <t xml:space="preserve">39.267147064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9308738708496</t>
+    <t xml:space="preserve">39.2671432495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9308700561523</t>
   </si>
   <si>
     <t xml:space="preserve">38.383228302002</t>
@@ -3668,28 +3668,28 @@
     <t xml:space="preserve">37.2014656066895</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7795104980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.520881652832</t>
+    <t xml:space="preserve">35.7795066833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5208854675293</t>
   </si>
   <si>
     <t xml:space="preserve">35.001277923584</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0397109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4632339477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0581321716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7018623352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8644027709961</t>
+    <t xml:space="preserve">35.0397033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4632377624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0581359863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7018585205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8643989562988</t>
   </si>
   <si>
     <t xml:space="preserve">35.5585250854492</t>
@@ -3701,25 +3701,25 @@
     <t xml:space="preserve">34.6553955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7138290405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1165657043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7706832885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9636306762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.377555847168</t>
+    <t xml:space="preserve">33.7138252258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.116569519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7706871032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9636268615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3775596618652</t>
   </si>
   <si>
     <t xml:space="preserve">34.7418632507324</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2710800170898</t>
+    <t xml:space="preserve">34.2710838317871</t>
   </si>
   <si>
     <t xml:space="preserve">34.280689239502</t>
@@ -3731,28 +3731,28 @@
     <t xml:space="preserve">33.7714767456055</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8291206359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.568920135498</t>
+    <t xml:space="preserve">33.8291244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5689239501953</t>
   </si>
   <si>
     <t xml:space="preserve">35.2510795593262</t>
   </si>
   <si>
-    <t xml:space="preserve">35.933235168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9420547485352</t>
+    <t xml:space="preserve">35.9332313537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9420509338379</t>
   </si>
   <si>
     <t xml:space="preserve">36.4712715148926</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4520530700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1253852844238</t>
+    <t xml:space="preserve">36.4520568847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1253890991211</t>
   </si>
   <si>
     <t xml:space="preserve">34.7802963256836</t>
@@ -3761,7 +3761,7 @@
     <t xml:space="preserve">33.588924407959</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6450004577637</t>
+    <t xml:space="preserve">35.6449966430664</t>
   </si>
   <si>
     <t xml:space="preserve">33.7042236328125</t>
@@ -3770,16 +3770,16 @@
     <t xml:space="preserve">34.4344139099121</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1357803344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9244117736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2695121765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3175430297852</t>
+    <t xml:space="preserve">35.1357841491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9244155883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2695083618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3175468444824</t>
   </si>
   <si>
     <t xml:space="preserve">35.981273651123</t>
@@ -3791,16 +3791,16 @@
     <t xml:space="preserve">35.0973510742188</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7602920532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2118606567383</t>
+    <t xml:space="preserve">35.7602958679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.211856842041</t>
   </si>
   <si>
     <t xml:space="preserve">38.508129119873</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0173454284668</t>
+    <t xml:space="preserve">39.0173416137695</t>
   </si>
   <si>
     <t xml:space="preserve">38.9500885009766</t>
@@ -3809,10 +3809,10 @@
     <t xml:space="preserve">40.2375373840332</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2943916320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8908653259277</t>
+    <t xml:space="preserve">41.2943954467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.890869140625</t>
   </si>
   <si>
     <t xml:space="preserve">40.6891021728516</t>
@@ -3821,16 +3821,16 @@
     <t xml:space="preserve">39.8340072631836</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6330299377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4208717346191</t>
+    <t xml:space="preserve">38.6330261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4208679199219</t>
   </si>
   <si>
     <t xml:space="preserve">39.219108581543</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6234245300293</t>
+    <t xml:space="preserve">38.623420715332</t>
   </si>
   <si>
     <t xml:space="preserve">37.9796981811523</t>
@@ -3848,55 +3848,55 @@
     <t xml:space="preserve">35.4528427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2502937316895</t>
+    <t xml:space="preserve">36.2502899169922</t>
   </si>
   <si>
     <t xml:space="preserve">36.7210731506348</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1350021362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7218627929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3183326721191</t>
+    <t xml:space="preserve">36.1349983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7218589782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3183364868164</t>
   </si>
   <si>
     <t xml:space="preserve">34.0693168640137</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2726593017578</t>
+    <t xml:space="preserve">32.2726554870605</t>
   </si>
   <si>
     <t xml:space="preserve">32.9836349487305</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9740257263184</t>
+    <t xml:space="preserve">32.9740295410156</t>
   </si>
   <si>
     <t xml:space="preserve">31.0524616241455</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9067687988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.916374206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9644165039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2734432220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3414840698242</t>
+    <t xml:space="preserve">32.9067726135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9163780212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9644203186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2734413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3414859771729</t>
   </si>
   <si>
     <t xml:space="preserve">30.6777591705322</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2105274200439</t>
+    <t xml:space="preserve">31.2105255126953</t>
   </si>
   <si>
     <t xml:space="preserve">31.0071048736572</t>
@@ -3905,13 +3905,13 @@
     <t xml:space="preserve">30.9489860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2492713928223</t>
+    <t xml:space="preserve">31.2492733001709</t>
   </si>
   <si>
     <t xml:space="preserve">31.3558235168457</t>
   </si>
   <si>
-    <t xml:space="preserve">31.694860458374</t>
+    <t xml:space="preserve">31.6948623657227</t>
   </si>
   <si>
     <t xml:space="preserve">31.0555400848389</t>
@@ -3923,13 +3923,13 @@
     <t xml:space="preserve">30.0965557098389</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6099510192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.34840965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4646511077881</t>
+    <t xml:space="preserve">30.6099529266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3484115600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4646530151367</t>
   </si>
   <si>
     <t xml:space="preserve">29.7865810394287</t>
@@ -3938,16 +3938,16 @@
     <t xml:space="preserve">28.2948322296143</t>
   </si>
   <si>
-    <t xml:space="preserve">26.260627746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5438117980957</t>
+    <t xml:space="preserve">26.2606258392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5438137054443</t>
   </si>
   <si>
     <t xml:space="preserve">26.3090591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.398509979248</t>
+    <t xml:space="preserve">25.3985118865967</t>
   </si>
   <si>
     <t xml:space="preserve">25.4760036468506</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">25.5341243743896</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8828449249268</t>
+    <t xml:space="preserve">25.8828430175781</t>
   </si>
   <si>
     <t xml:space="preserve">27.9364242553711</t>
@@ -3968,19 +3968,19 @@
     <t xml:space="preserve">28.8663463592529</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9341564178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3529510498047</t>
+    <t xml:space="preserve">28.934154510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3529529571533</t>
   </si>
   <si>
     <t xml:space="preserve">28.2560863494873</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3335800170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4378623962402</t>
+    <t xml:space="preserve">28.3335781097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4378604888916</t>
   </si>
   <si>
     <t xml:space="preserve">29.9900035858154</t>
@@ -4004,16 +4004,16 @@
     <t xml:space="preserve">28.2173366546631</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7523746490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3238906860352</t>
+    <t xml:space="preserve">27.7523784637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3238925933838</t>
   </si>
   <si>
     <t xml:space="preserve">28.924467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8469753265381</t>
+    <t xml:space="preserve">28.8469734191895</t>
   </si>
   <si>
     <t xml:space="preserve">29.6994037628174</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">30.1837368011475</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6412830352783</t>
+    <t xml:space="preserve">29.6412811279297</t>
   </si>
   <si>
     <t xml:space="preserve">29.4766082763672</t>
@@ -4037,25 +4037,25 @@
     <t xml:space="preserve">31.2008399963379</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4236335754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9706287384033</t>
+    <t xml:space="preserve">31.4236354827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.970630645752</t>
   </si>
   <si>
     <t xml:space="preserve">30.8714923858643</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0942840576172</t>
+    <t xml:space="preserve">31.0942859649658</t>
   </si>
   <si>
     <t xml:space="preserve">29.4281749725342</t>
   </si>
   <si>
-    <t xml:space="preserve">29.738151550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9922733306885</t>
+    <t xml:space="preserve">29.7381477355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9922752380371</t>
   </si>
   <si>
     <t xml:space="preserve">29.4572353363037</t>
@@ -4064,13 +4064,13 @@
     <t xml:space="preserve">29.7672100067139</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1979675292969</t>
+    <t xml:space="preserve">28.1979656219482</t>
   </si>
   <si>
     <t xml:space="preserve">27.8879909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8104972839355</t>
+    <t xml:space="preserve">27.8104953765869</t>
   </si>
   <si>
     <t xml:space="preserve">27.442403793335</t>
@@ -4094,13 +4094,13 @@
     <t xml:space="preserve">24.962610244751</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2338352203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6816940307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0885353088379</t>
+    <t xml:space="preserve">25.2338371276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6816959381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0885372161865</t>
   </si>
   <si>
     <t xml:space="preserve">25.0497894287109</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">25.10791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2144641876221</t>
+    <t xml:space="preserve">25.2144622802734</t>
   </si>
   <si>
     <t xml:space="preserve">24.5073337554932</t>
@@ -4124,37 +4124,37 @@
     <t xml:space="preserve">24.2554817199707</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1779880523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8970718383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4201526641846</t>
+    <t xml:space="preserve">24.1779861450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8970737457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4201545715332</t>
   </si>
   <si>
     <t xml:space="preserve">23.8292675018311</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0908088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0133152008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.197359085083</t>
+    <t xml:space="preserve">24.0908069610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.013313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1973609924316</t>
   </si>
   <si>
     <t xml:space="preserve">24.8463687896729</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8053493499756</t>
+    <t xml:space="preserve">25.8053512573242</t>
   </si>
   <si>
     <t xml:space="preserve">25.291955947876</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0572032928467</t>
+    <t xml:space="preserve">26.0572071075439</t>
   </si>
   <si>
     <t xml:space="preserve">25.5728702545166</t>
@@ -4169,34 +4169,34 @@
     <t xml:space="preserve">25.9312782287598</t>
   </si>
   <si>
-    <t xml:space="preserve">25.630989074707</t>
+    <t xml:space="preserve">25.6309909820557</t>
   </si>
   <si>
     <t xml:space="preserve">25.3307037353516</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6235752105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8389549255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9187164306641</t>
+    <t xml:space="preserve">24.6235733032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8389530181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9187183380127</t>
   </si>
   <si>
     <t xml:space="preserve">23.916446685791</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4395294189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.350076675415</t>
+    <t xml:space="preserve">24.4395275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3500785827637</t>
   </si>
   <si>
     <t xml:space="preserve">24.8366813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0475196838379</t>
+    <t xml:space="preserve">26.0475177764893</t>
   </si>
   <si>
     <t xml:space="preserve">25.3694515228271</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">23.7517738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9067611694336</t>
+    <t xml:space="preserve">23.906759262085</t>
   </si>
   <si>
     <t xml:space="preserve">24.3523483276367</t>
@@ -4238,49 +4238,49 @@
     <t xml:space="preserve">27.2680416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1398429870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6748809814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7426910400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7062129974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7643337249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5221652984619</t>
+    <t xml:space="preserve">28.1398448944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6748828887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7426891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7062149047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.764331817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5221672058105</t>
   </si>
   <si>
     <t xml:space="preserve">26.3187465667725</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8321418762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8805751800537</t>
+    <t xml:space="preserve">26.8321399688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8805732727051</t>
   </si>
   <si>
     <t xml:space="preserve">27.0065002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1421165466309</t>
+    <t xml:space="preserve">27.1421146392822</t>
   </si>
   <si>
     <t xml:space="preserve">26.0087738037109</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7837066650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.645824432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9483814239502</t>
+    <t xml:space="preserve">26.7837085723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6458225250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9483833312988</t>
   </si>
   <si>
     <t xml:space="preserve">26.1540718078613</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">26.6771545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6965255737305</t>
+    <t xml:space="preserve">26.6965274810791</t>
   </si>
   <si>
     <t xml:space="preserve">27.0936813354492</t>
@@ -4301,43 +4301,43 @@
     <t xml:space="preserve">27.6651954650879</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9751682281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4446716308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0959529876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0668907165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8925304412842</t>
+    <t xml:space="preserve">27.975170135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.444673538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0959510803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0668926239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8925323486328</t>
   </si>
   <si>
     <t xml:space="preserve">26.4543590545654</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8344116210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9700241088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.628719329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8708877563477</t>
+    <t xml:space="preserve">25.8344097137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9700260162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6287212371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8708896636963</t>
   </si>
   <si>
     <t xml:space="preserve">26.1443843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">26.250940322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9677543640137</t>
+    <t xml:space="preserve">26.2509384155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9677562713623</t>
   </si>
   <si>
     <t xml:space="preserve">25.9797115325928</t>
@@ -4349,16 +4349,16 @@
     <t xml:space="preserve">26.5996608734131</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6384086608887</t>
+    <t xml:space="preserve">26.63840675354</t>
   </si>
   <si>
     <t xml:space="preserve">26.2412528991699</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6019325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9044895172119</t>
+    <t xml:space="preserve">25.6019306182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9044876098633</t>
   </si>
   <si>
     <t xml:space="preserve">25.0788497924805</t>
@@ -4367,19 +4367,19 @@
     <t xml:space="preserve">24.8851165771484</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9916706085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9335479736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7398166656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4782772064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6070766448975</t>
+    <t xml:space="preserve">24.9916687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9335498809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7398147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4782733917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6070785522461</t>
   </si>
   <si>
     <t xml:space="preserve">26.9290065765381</t>
@@ -4388,7 +4388,7 @@
     <t xml:space="preserve">27.1227416992188</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7666034698486</t>
+    <t xml:space="preserve">25.7666053771973</t>
   </si>
   <si>
     <t xml:space="preserve">26.483419418335</t>
@@ -4400,22 +4400,22 @@
     <t xml:space="preserve">26.541540145874</t>
   </si>
   <si>
-    <t xml:space="preserve">26.202507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6190338134766</t>
+    <t xml:space="preserve">26.2025051116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6190319061279</t>
   </si>
   <si>
     <t xml:space="preserve">26.5027942657471</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3358478546143</t>
+    <t xml:space="preserve">27.3358497619629</t>
   </si>
   <si>
     <t xml:space="preserve">29.1763210296631</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5466861724854</t>
+    <t xml:space="preserve">28.5466842651367</t>
   </si>
   <si>
     <t xml:space="preserve">28.4401321411133</t>
@@ -4427,10 +4427,10 @@
     <t xml:space="preserve">28.2367095947266</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1107864379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0310192108154</t>
+    <t xml:space="preserve">28.1107845306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0310211181641</t>
   </si>
   <si>
     <t xml:space="preserve">28.4304447174072</t>
@@ -4439,31 +4439,31 @@
     <t xml:space="preserve">28.8954067230225</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1860065460205</t>
+    <t xml:space="preserve">29.1860084533691</t>
   </si>
   <si>
     <t xml:space="preserve">29.6606559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6583843231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9393005371094</t>
+    <t xml:space="preserve">30.6583862304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9392986297607</t>
   </si>
   <si>
     <t xml:space="preserve">30.8327445983887</t>
   </si>
   <si>
-    <t xml:space="preserve">31.258960723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4817523956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6173648834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5689315795898</t>
+    <t xml:space="preserve">31.2589588165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4817543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6173667907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5689353942871</t>
   </si>
   <si>
     <t xml:space="preserve">32.1404495239258</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">31.6754875183105</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2783355712891</t>
+    <t xml:space="preserve">31.2783336639404</t>
   </si>
   <si>
     <t xml:space="preserve">31.9176559448242</t>
@@ -4481,10 +4481,10 @@
     <t xml:space="preserve">31.9854621887207</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7820453643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3729248046875</t>
+    <t xml:space="preserve">31.7820415496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3729286193848</t>
   </si>
   <si>
     <t xml:space="preserve">32.508544921875</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">32.3341865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7313385009766</t>
+    <t xml:space="preserve">32.7313423156738</t>
   </si>
   <si>
     <t xml:space="preserve">32.2373161315918</t>
@@ -4505,28 +4505,28 @@
     <t xml:space="preserve">32.0823287963867</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3780784606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7678184509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7655448913574</t>
+    <t xml:space="preserve">34.3780746459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7678146362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7655410766602</t>
   </si>
   <si>
     <t xml:space="preserve">34.7267951965332</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3296394348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2134056091309</t>
+    <t xml:space="preserve">34.3296432495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2134017944336</t>
   </si>
   <si>
     <t xml:space="preserve">34.6686782836914</t>
   </si>
   <si>
-    <t xml:space="preserve">34.881778717041</t>
+    <t xml:space="preserve">34.8817825317383</t>
   </si>
   <si>
     <t xml:space="preserve">34.6105537414551</t>
@@ -4541,19 +4541,19 @@
     <t xml:space="preserve">32.8475761413574</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1478652954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1674041748047</t>
+    <t xml:space="preserve">33.1478691101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.167407989502</t>
   </si>
   <si>
     <t xml:space="preserve">32.297924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0536880493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4577465057373</t>
+    <t xml:space="preserve">32.0536842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4577445983887</t>
   </si>
   <si>
     <t xml:space="preserve">32.2393035888672</t>
@@ -4565,22 +4565,22 @@
     <t xml:space="preserve">32.1513786315918</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5359001159668</t>
+    <t xml:space="preserve">31.5359020233154</t>
   </si>
   <si>
     <t xml:space="preserve">31.6238231658936</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6789283752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9489669799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2908973693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0466575622559</t>
+    <t xml:space="preserve">32.6789321899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9489631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2908935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0466537475586</t>
   </si>
   <si>
     <t xml:space="preserve">34.1638946533203</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">34.6816749572754</t>
   </si>
   <si>
-    <t xml:space="preserve">34.417896270752</t>
+    <t xml:space="preserve">34.4179000854492</t>
   </si>
   <si>
     <t xml:space="preserve">34.2225074768066</t>
@@ -4604,7 +4604,7 @@
     <t xml:space="preserve">33.7438049316406</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6656494140625</t>
+    <t xml:space="preserve">33.6656455993652</t>
   </si>
   <si>
     <t xml:space="preserve">33.216251373291</t>
@@ -4625,10 +4625,10 @@
     <t xml:space="preserve">32.4835395812988</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9852981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8875999450684</t>
+    <t xml:space="preserve">31.9853000640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.887601852417</t>
   </si>
   <si>
     <t xml:space="preserve">30.0997867584229</t>
@@ -4655,19 +4655,19 @@
     <t xml:space="preserve">31.1451206207275</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0474281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3440227508545</t>
+    <t xml:space="preserve">31.0474262237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3440246582031</t>
   </si>
   <si>
     <t xml:space="preserve">30.2560977935791</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3635635375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4514865875244</t>
+    <t xml:space="preserve">30.363561630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.451488494873</t>
   </si>
   <si>
     <t xml:space="preserve">30.9204235076904</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">30.8520374298096</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7152633666992</t>
+    <t xml:space="preserve">30.7152652740479</t>
   </si>
   <si>
     <t xml:space="preserve">30.0802478790283</t>
@@ -4700,16 +4700,16 @@
     <t xml:space="preserve">29.2009925842285</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6406211853027</t>
+    <t xml:space="preserve">29.6406192779541</t>
   </si>
   <si>
     <t xml:space="preserve">29.3182277679443</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4159240722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0739917755127</t>
+    <t xml:space="preserve">29.415922164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0739898681641</t>
   </si>
   <si>
     <t xml:space="preserve">28.5562057495117</t>
@@ -4721,7 +4721,7 @@
     <t xml:space="preserve">29.0935287475586</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2889175415039</t>
+    <t xml:space="preserve">29.2889194488525</t>
   </si>
   <si>
     <t xml:space="preserve">29.1814556121826</t>
@@ -4733,10 +4733,10 @@
     <t xml:space="preserve">29.7578544616699</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5722351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3475379943848</t>
+    <t xml:space="preserve">29.5722332000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3475360870361</t>
   </si>
   <si>
     <t xml:space="preserve">28.800443649292</t>
@@ -4760,19 +4760,19 @@
     <t xml:space="preserve">28.2240447998047</t>
   </si>
   <si>
-    <t xml:space="preserve">28.321741104126</t>
+    <t xml:space="preserve">28.3217391967773</t>
   </si>
   <si>
     <t xml:space="preserve">28.5952854156494</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3119697570801</t>
+    <t xml:space="preserve">28.3119716644287</t>
   </si>
   <si>
     <t xml:space="preserve">27.9309597015381</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0677318572998</t>
+    <t xml:space="preserve">28.0677337646484</t>
   </si>
   <si>
     <t xml:space="preserve">29.650390625</t>
@@ -4814,13 +4814,13 @@
     <t xml:space="preserve">26.6706962585449</t>
   </si>
   <si>
-    <t xml:space="preserve">26.51438331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.002857208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1005535125732</t>
+    <t xml:space="preserve">26.5143852233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0028591156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1005554199219</t>
   </si>
   <si>
     <t xml:space="preserve">27.4620246887207</t>
@@ -4829,7 +4829,7 @@
     <t xml:space="preserve">26.709774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2799167633057</t>
+    <t xml:space="preserve">26.2799186706543</t>
   </si>
   <si>
     <t xml:space="preserve">26.4557685852051</t>
@@ -4838,13 +4838,13 @@
     <t xml:space="preserve">26.6120796203613</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4362277984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.651159286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6609268188477</t>
+    <t xml:space="preserve">26.4362297058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6511573791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6609287261963</t>
   </si>
   <si>
     <t xml:space="preserve">26.2213001251221</t>
@@ -4853,31 +4853,31 @@
     <t xml:space="preserve">25.1661968231201</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7949542999268</t>
+    <t xml:space="preserve">24.7949562072754</t>
   </si>
   <si>
     <t xml:space="preserve">26.0259094238281</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8891372680664</t>
+    <t xml:space="preserve">25.889139175415</t>
   </si>
   <si>
     <t xml:space="preserve">26.8953952789307</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0614776611328</t>
+    <t xml:space="preserve">27.0614757537842</t>
   </si>
   <si>
     <t xml:space="preserve">27.1200923919678</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9344711303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9149341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4753074645996</t>
+    <t xml:space="preserve">26.9344730377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9149322509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.475305557251</t>
   </si>
   <si>
     <t xml:space="preserve">26.3385334014893</t>
@@ -4886,13 +4886,13 @@
     <t xml:space="preserve">27.5890274047852</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7683925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.377613067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8856239318848</t>
+    <t xml:space="preserve">26.7683906555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3776111602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8856258392334</t>
   </si>
   <si>
     <t xml:space="preserve">27.5206432342529</t>
@@ -4907,25 +4907,25 @@
     <t xml:space="preserve">27.6085662841797</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7648792266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9504985809326</t>
+    <t xml:space="preserve">27.7648773193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9505004882812</t>
   </si>
   <si>
     <t xml:space="preserve">27.5499515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8723430633545</t>
+    <t xml:space="preserve">27.8723449707031</t>
   </si>
   <si>
     <t xml:space="preserve">27.3154811859131</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0517063140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9735507965088</t>
+    <t xml:space="preserve">27.0517082214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9735527038574</t>
   </si>
   <si>
     <t xml:space="preserve">28.0775032043457</t>
@@ -4958,7 +4958,7 @@
     <t xml:space="preserve">30.6175689697266</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5296421051025</t>
+    <t xml:space="preserve">30.5296440124512</t>
   </si>
   <si>
     <t xml:space="preserve">29.796932220459</t>
@@ -4970,7 +4970,7 @@
     <t xml:space="preserve">30.8715763092041</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6761837005615</t>
+    <t xml:space="preserve">30.6761856079102</t>
   </si>
   <si>
     <t xml:space="preserve">30.8911151885986</t>
@@ -4997,7 +4997,7 @@
     <t xml:space="preserve">29.1912231445312</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1619148254395</t>
+    <t xml:space="preserve">29.1619167327881</t>
   </si>
   <si>
     <t xml:space="preserve">29.9337043762207</t>
@@ -5015,10 +5015,10 @@
     <t xml:space="preserve">29.0544509887695</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4612579345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5101051330566</t>
+    <t xml:space="preserve">30.4612560272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.510103225708</t>
   </si>
   <si>
     <t xml:space="preserve">30.7738800048828</t>
@@ -5030,13 +5030,13 @@
     <t xml:space="preserve">30.1584033966064</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4221782684326</t>
+    <t xml:space="preserve">30.4221801757812</t>
   </si>
   <si>
     <t xml:space="preserve">30.8813457489014</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1255836486816</t>
+    <t xml:space="preserve">31.125581741333</t>
   </si>
   <si>
     <t xml:space="preserve">30.744571685791</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">30.2658672332764</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0439109802246</t>
+    <t xml:space="preserve">32.0439147949219</t>
   </si>
   <si>
     <t xml:space="preserve">32.893856048584</t>
@@ -5078,7 +5078,7 @@
     <t xml:space="preserve">32.2002258300781</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0306358337402</t>
+    <t xml:space="preserve">33.030632019043</t>
   </si>
   <si>
     <t xml:space="preserve">32.8547821044922</t>
@@ -5090,7 +5090,7 @@
     <t xml:space="preserve">31.6433639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9888076782227</t>
+    <t xml:space="preserve">30.9888095855713</t>
   </si>
   <si>
     <t xml:space="preserve">31.2916622161865</t>
@@ -5099,16 +5099,16 @@
     <t xml:space="preserve">31.1158142089844</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3858451843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2357902526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2651023864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0208587646484</t>
+    <t xml:space="preserve">32.3858489990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2357940673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2650985717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0208625793457</t>
   </si>
   <si>
     <t xml:space="preserve">32.4933090209961</t>
@@ -5123,7 +5123,7 @@
     <t xml:space="preserve">31.1646614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7605953216553</t>
+    <t xml:space="preserve">31.7605991363525</t>
   </si>
   <si>
     <t xml:space="preserve">30.1290950775146</t>
@@ -5132,10 +5132,10 @@
     <t xml:space="preserve">30.4026412963867</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1193256378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8422660827637</t>
+    <t xml:space="preserve">30.1193237304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8422679901123</t>
   </si>
   <si>
     <t xml:space="preserve">31.2818927764893</t>
@@ -5147,16 +5147,16 @@
     <t xml:space="preserve">30.3049449920654</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7836513519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7054958343506</t>
+    <t xml:space="preserve">30.7836494445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.705493927002</t>
   </si>
   <si>
     <t xml:space="preserve">30.8227272033691</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0697059631348</t>
+    <t xml:space="preserve">33.069709777832</t>
   </si>
   <si>
     <t xml:space="preserve">32.591007232666</t>
@@ -5180,7 +5180,7 @@
     <t xml:space="preserve">33.5972595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5679550170898</t>
+    <t xml:space="preserve">33.5679512023926</t>
   </si>
   <si>
     <t xml:space="preserve">34.0310287475586</t>
@@ -71614,7 +71614,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6920833333</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>1121183</v>
@@ -71635,6 +71635,32 @@
         <v>2052</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6911458333</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>1196470</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>14.8649997711182</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>14.3950004577637</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>14.4700002670288</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>14.6400003433228</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>2030</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="2062">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="2063">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.335205078125</t>
+    <t xml:space="preserve">7.33520555496216</t>
   </si>
   <si>
     <t xml:space="preserve">AMP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39109230041504</t>
+    <t xml:space="preserve">7.39109134674072</t>
   </si>
   <si>
     <t xml:space="preserve">7.31191825866699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36780500411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15357065200806</t>
+    <t xml:space="preserve">7.36780595779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15357208251953</t>
   </si>
   <si>
     <t xml:space="preserve">6.96262264251709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21877288818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2793173789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16288566589355</t>
+    <t xml:space="preserve">7.21877336502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27931785583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1628851890564</t>
   </si>
   <si>
     <t xml:space="preserve">7.0324821472168</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08836936950684</t>
+    <t xml:space="preserve">7.08836984634399</t>
   </si>
   <si>
     <t xml:space="preserve">7.19548654556274</t>
@@ -89,25 +89,25 @@
     <t xml:space="preserve">7.23740196228027</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35383367538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14891481399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18151521682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40972089767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28397512435913</t>
+    <t xml:space="preserve">7.35383415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14891386032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18151473999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4097204208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28397560119629</t>
   </si>
   <si>
     <t xml:space="preserve">7.13959980010986</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05111169815063</t>
+    <t xml:space="preserve">7.05111074447632</t>
   </si>
   <si>
     <t xml:space="preserve">6.84619140625</t>
@@ -116,40 +116,40 @@
     <t xml:space="preserve">6.51086759567261</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45498085021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59004163742065</t>
+    <t xml:space="preserve">6.45498037338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5900411605835</t>
   </si>
   <si>
     <t xml:space="preserve">6.33389139175415</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29197597503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42237997055054</t>
+    <t xml:space="preserve">6.29197692871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42237901687622</t>
   </si>
   <si>
     <t xml:space="preserve">6.61798524856567</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88344955444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71113061904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83687734603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70181655883789</t>
+    <t xml:space="preserve">6.88345003128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71112966537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83687686920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70181608200073</t>
   </si>
   <si>
     <t xml:space="preserve">6.6272988319397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9952244758606</t>
+    <t xml:space="preserve">6.99522399902344</t>
   </si>
   <si>
     <t xml:space="preserve">6.89276456832886</t>
@@ -158,49 +158,49 @@
     <t xml:space="preserve">6.80427598953247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79961824417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84153413772583</t>
+    <t xml:space="preserve">6.7996187210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84153366088867</t>
   </si>
   <si>
     <t xml:space="preserve">6.6599006652832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63195705413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79496145248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78564643859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86016273498535</t>
+    <t xml:space="preserve">6.63195657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79496097564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78564691543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86016321182251</t>
   </si>
   <si>
     <t xml:space="preserve">7.00919580459595</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11165571212769</t>
+    <t xml:space="preserve">7.11165618896484</t>
   </si>
   <si>
     <t xml:space="preserve">7.08371162414551</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20945739746094</t>
+    <t xml:space="preserve">7.20945930480957</t>
   </si>
   <si>
     <t xml:space="preserve">7.10699796676636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04179668426514</t>
+    <t xml:space="preserve">7.04179716110229</t>
   </si>
   <si>
     <t xml:space="preserve">7.2420597076416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09768438339233</t>
+    <t xml:space="preserve">7.09768390655518</t>
   </si>
   <si>
     <t xml:space="preserve">7.17220020294189</t>
@@ -215,130 +215,130 @@
     <t xml:space="preserve">7.00453805923462</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27000284194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32589054107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22808742523193</t>
+    <t xml:space="preserve">7.27000331878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3258900642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22808694839478</t>
   </si>
   <si>
     <t xml:space="preserve">7.50286674499512</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41437864303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48423719406128</t>
+    <t xml:space="preserve">7.41437959671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48423767089844</t>
   </si>
   <si>
     <t xml:space="preserve">7.57738304138184</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55409574508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73107385635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60066986083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64258623123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70313024520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73573017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88476276397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88942193984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87079000473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78696060180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94530773162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88010501861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08968162536621</t>
+    <t xml:space="preserve">7.55409669876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73107290267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60066938400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64258480072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70312976837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73573064804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88476419448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88942098617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87079048156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78696012496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94530725479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88010597229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08968448638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.01760482788086</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09717178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10653305053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05036926269531</t>
+    <t xml:space="preserve">8.09717082977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10653209686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05036735534668</t>
   </si>
   <si>
     <t xml:space="preserve">8.17205905914307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21418380737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23758602142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22354412078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15801811218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07845115661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08313083648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14397525787354</t>
+    <t xml:space="preserve">8.21418476104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23758411407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22354221343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1580171585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07845020294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0831298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14397621154785</t>
   </si>
   <si>
     <t xml:space="preserve">8.01292419433594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91463422775269</t>
+    <t xml:space="preserve">7.91463565826416</t>
   </si>
   <si>
     <t xml:space="preserve">7.8210244178772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64316892623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62912654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65253114700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55891990661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63848876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9895224571228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94739818572998</t>
+    <t xml:space="preserve">7.64316844940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62912702560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65252923965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55892038345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63848829269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98952198028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94739770889282</t>
   </si>
   <si>
     <t xml:space="preserve">8.05972862243652</t>
@@ -353,97 +353,97 @@
     <t xml:space="preserve">7.72273635864258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87250995635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92867708206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89123201370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81166553497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7180552482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88186979293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96143817901611</t>
+    <t xml:space="preserve">7.87251091003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92867612838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89123249053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81166458129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71805572509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88187170028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96143865585327</t>
   </si>
   <si>
     <t xml:space="preserve">7.91931390762329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90995264053345</t>
+    <t xml:space="preserve">7.90995311737061</t>
   </si>
   <si>
     <t xml:space="preserve">8.05504703521729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18141841888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16737747192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19546127319336</t>
+    <t xml:space="preserve">8.18141937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16738033294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19546031951904</t>
   </si>
   <si>
     <t xml:space="preserve">8.19078063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30779266357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36395835876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34991645812988</t>
+    <t xml:space="preserve">8.30779075622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36395740509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34991550445557</t>
   </si>
   <si>
     <t xml:space="preserve">8.33119297027588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29374885559082</t>
+    <t xml:space="preserve">8.29375076293945</t>
   </si>
   <si>
     <t xml:space="preserve">8.1533374786377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28906917572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36863803863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50905132293701</t>
+    <t xml:space="preserve">8.28907012939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36863708496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50904941558838</t>
   </si>
   <si>
     <t xml:space="preserve">8.60734081268311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51373386383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63542175292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75711345672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65414428710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78519725799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8085994720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92092990875244</t>
+    <t xml:space="preserve">8.51373195648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.635422706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75711441040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65414524078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78519821166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80859756469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92092800140381</t>
   </si>
   <si>
     <t xml:space="preserve">8.84604263305664</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">8.75243473052979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82264137268066</t>
+    <t xml:space="preserve">8.82264041900635</t>
   </si>
   <si>
     <t xml:space="preserve">8.7337121963501</t>
@@ -467,37 +467,37 @@
     <t xml:space="preserve">8.77115535736084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.761794090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65882587432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59329891204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57457733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56053638458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4856481552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54181480407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5324535369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66818618774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49969100952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61670112609863</t>
+    <t xml:space="preserve">8.76179504394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6588249206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59330081939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57457542419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56053733825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48564910888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54181385040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53245258331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66818809509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49969005584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61670207977295</t>
   </si>
   <si>
     <t xml:space="preserve">8.49500846862793</t>
@@ -506,31 +506,31 @@
     <t xml:space="preserve">8.55585670471191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61202144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46692752838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5277738571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56521701812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69158935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0800666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24856090545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07070255279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01453971862793</t>
+    <t xml:space="preserve">8.61202049255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46692657470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52777194976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56521511077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69158744812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08006572723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24856185913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07070446014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01453876495361</t>
   </si>
   <si>
     <t xml:space="preserve">8.89284706115723</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">8.93965339660645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8132791519165</t>
+    <t xml:space="preserve">8.81328010559082</t>
   </si>
   <si>
     <t xml:space="preserve">8.50437164306641</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">8.42480278015137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40140151977539</t>
+    <t xml:space="preserve">8.40140056610107</t>
   </si>
   <si>
     <t xml:space="preserve">8.39671993255615</t>
@@ -560,28 +560,28 @@
     <t xml:space="preserve">8.34523487091064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46224689483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3826789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47160625457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9864559173584</t>
+    <t xml:space="preserve">8.46224594116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38267803192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47160816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98645687103271</t>
   </si>
   <si>
     <t xml:space="preserve">9.09878730773926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0613431930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51841259002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16269969940186</t>
+    <t xml:space="preserve">9.06134414672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51841354370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16269779205322</t>
   </si>
   <si>
     <t xml:space="preserve">8.31247234344482</t>
@@ -590,142 +590,142 @@
     <t xml:space="preserve">7.4419093132019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98484086990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95675897598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38735866546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41076183319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44820499420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48096752166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37331676483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23290348052979</t>
+    <t xml:space="preserve">7.98483991622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95675754547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38735961914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4107608795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44820404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4809684753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37331867218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2329044342041</t>
   </si>
   <si>
     <t xml:space="preserve">8.18610000610352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37799739837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57925701141357</t>
+    <t xml:space="preserve">8.3779993057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57925796508789</t>
   </si>
   <si>
     <t xml:space="preserve">8.64946365356445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72435188293457</t>
+    <t xml:space="preserve">8.72435092926025</t>
   </si>
   <si>
     <t xml:space="preserve">8.67286777496338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74307250976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71031093597412</t>
+    <t xml:space="preserve">8.74307441711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7103099822998</t>
   </si>
   <si>
     <t xml:space="preserve">9.15495204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96773433685303</t>
+    <t xml:space="preserve">8.96773338317871</t>
   </si>
   <si>
     <t xml:space="preserve">9.14091205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26728248596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33748912811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40769672393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37961578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29536628723145</t>
+    <t xml:space="preserve">9.26728343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33749103546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40769577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37961483001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29536533355713</t>
   </si>
   <si>
     <t xml:space="preserve">9.36089134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44514179229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48258304595947</t>
+    <t xml:space="preserve">9.44514083862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48258399963379</t>
   </si>
   <si>
     <t xml:space="preserve">9.4357795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35621070861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11282730102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10814762115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15963363647461</t>
+    <t xml:space="preserve">9.35621166229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11282825469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1081485748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15963268280029</t>
   </si>
   <si>
     <t xml:space="preserve">9.46386241912842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81021595001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95999050140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82893562316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91318607330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64171886444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70724678039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71660709381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66043949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79149341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0255155563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0067939758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1846513748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.240816116333</t>
+    <t xml:space="preserve">9.81021404266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95998954772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82893657684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91318416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64171981811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70724582672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71660614013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66044139862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79149436950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0255146026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0067949295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1846494674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2408151626587</t>
   </si>
   <si>
     <t xml:space="preserve">10.2595376968384</t>
@@ -737,31 +737,31 @@
     <t xml:space="preserve">10.4748382568359</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3625078201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3344259262085</t>
+    <t xml:space="preserve">10.3625068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3344240188599</t>
   </si>
   <si>
     <t xml:space="preserve">10.577808380127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5122814178467</t>
+    <t xml:space="preserve">10.512282371521</t>
   </si>
   <si>
     <t xml:space="preserve">10.5029211044312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8118314743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8867177963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7182207107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6526956558228</t>
+    <t xml:space="preserve">10.8118324279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.88671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7182216644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6526947021484</t>
   </si>
   <si>
     <t xml:space="preserve">10.6433343887329</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">10.6246118545532</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7088594436646</t>
+    <t xml:space="preserve">10.7088603973389</t>
   </si>
   <si>
     <t xml:space="preserve">10.8960790634155</t>
@@ -782,100 +782,100 @@
     <t xml:space="preserve">10.9335222244263</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9990482330322</t>
+    <t xml:space="preserve">10.9990491867065</t>
   </si>
   <si>
     <t xml:space="preserve">11.1301012039185</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0926580429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2517929077148</t>
+    <t xml:space="preserve">11.0926570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2517938613892</t>
   </si>
   <si>
     <t xml:space="preserve">10.9616050720215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2049875259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1675462722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1488227844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1862659454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2798748016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4296503067017</t>
+    <t xml:space="preserve">11.2049884796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1675453186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1488208770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1862649917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2798776626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4296493530273</t>
   </si>
   <si>
     <t xml:space="preserve">11.4109268188477</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4577322006226</t>
+    <t xml:space="preserve">11.4577331542969</t>
   </si>
   <si>
     <t xml:space="preserve">11.5801239013672</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8249082565308</t>
+    <t xml:space="preserve">11.8249073028564</t>
   </si>
   <si>
     <t xml:space="preserve">11.8625659942627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9472990036011</t>
+    <t xml:space="preserve">11.9472980499268</t>
   </si>
   <si>
     <t xml:space="preserve">11.9190530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9284687042236</t>
+    <t xml:space="preserve">11.9284696578979</t>
   </si>
   <si>
     <t xml:space="preserve">11.9378843307495</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9661283493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602741241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0979347229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0226163864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2109117507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1826667785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2391557693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9096393585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1450071334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4859762191772</t>
+    <t xml:space="preserve">11.9661273956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0602750778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0979337692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0226173400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2109107971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1826658248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2391538619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9096384048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1450080871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4859752655029</t>
   </si>
   <si>
     <t xml:space="preserve">11.2976818084717</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6930999755859</t>
+    <t xml:space="preserve">11.6931009292603</t>
   </si>
   <si>
     <t xml:space="preserve">11.7307596206665</t>
@@ -884,73 +884,73 @@
     <t xml:space="preserve">11.7684173583984</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7590045928955</t>
+    <t xml:space="preserve">11.7590036392212</t>
   </si>
   <si>
     <t xml:space="preserve">11.627197265625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5707092285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5236358642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4671468734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3730001449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0811433792114</t>
+    <t xml:space="preserve">11.5707082748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5236349105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4671478271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3729991912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0811424255371</t>
   </si>
   <si>
     <t xml:space="preserve">10.8834323883057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6951370239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5633325576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.610405921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7422122955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9116773605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9022617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9493360519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1376314163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3541698455811</t>
+    <t xml:space="preserve">10.6951389312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5633316040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6104068756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7422113418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9116764068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9022636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9493370056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1376304626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3541707992554</t>
   </si>
   <si>
     <t xml:space="preserve">11.3824138641357</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3447561264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4106597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.269437789917</t>
+    <t xml:space="preserve">11.3447570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4106588363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2694368362427</t>
   </si>
   <si>
     <t xml:space="preserve">11.5048055648804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4294881820679</t>
+    <t xml:space="preserve">11.4294872283936</t>
   </si>
   <si>
     <t xml:space="preserve">11.3353404998779</t>
@@ -959,28 +959,28 @@
     <t xml:space="preserve">11.2788515090942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2506065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1093854904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0340690612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9210910797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6668949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8363590240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7892866134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1941204071045</t>
+    <t xml:space="preserve">11.2506074905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1093864440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.034068107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9210920333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6668939590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8363599777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.78928565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1941194534302</t>
   </si>
   <si>
     <t xml:space="preserve">11.1658754348755</t>
@@ -992,40 +992,40 @@
     <t xml:space="preserve">11.1282157897949</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3165102005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3259258270264</t>
+    <t xml:space="preserve">11.3165121078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3259239196777</t>
   </si>
   <si>
     <t xml:space="preserve">11.241192817688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.062313079834</t>
+    <t xml:space="preserve">11.0623149871826</t>
   </si>
   <si>
     <t xml:space="preserve">11.0905570983887</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1752891540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4389019012451</t>
+    <t xml:space="preserve">11.1752901077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4389009475708</t>
   </si>
   <si>
     <t xml:space="preserve">11.7213439941406</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8154916763306</t>
+    <t xml:space="preserve">11.8154926300049</t>
   </si>
   <si>
     <t xml:space="preserve">11.984956741333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0132026672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9567136764526</t>
+    <t xml:space="preserve">12.0132007598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.956711769104</t>
   </si>
   <si>
     <t xml:space="preserve">12.0508604049683</t>
@@ -1034,43 +1034,43 @@
     <t xml:space="preserve">12.0414447784424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0791034698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9755420684814</t>
+    <t xml:space="preserve">12.0791053771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9755439758301</t>
   </si>
   <si>
     <t xml:space="preserve">11.8343210220337</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2203254699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1544227600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1073474884033</t>
+    <t xml:space="preserve">12.220326423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1544218063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.107349395752</t>
   </si>
   <si>
     <t xml:space="preserve">12.4839382171631</t>
   </si>
   <si>
-    <t xml:space="preserve">12.521595954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.643988609314</t>
+    <t xml:space="preserve">12.5215978622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6439895629883</t>
   </si>
   <si>
     <t xml:space="preserve">12.7852096557617</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8134546279907</t>
+    <t xml:space="preserve">12.8134536743164</t>
   </si>
   <si>
     <t xml:space="preserve">12.8322830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8040399551392</t>
+    <t xml:space="preserve">12.8040390014648</t>
   </si>
   <si>
     <t xml:space="preserve">12.1920804977417</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">11.7872486114502</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8531494140625</t>
+    <t xml:space="preserve">11.8531513214111</t>
   </si>
   <si>
     <t xml:space="preserve">12.0320310592651</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">12.1732530593872</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2768144607544</t>
+    <t xml:space="preserve">12.2768135070801</t>
   </si>
   <si>
     <t xml:space="preserve">11.9002246856689</t>
@@ -1100,37 +1100,37 @@
     <t xml:space="preserve">11.5612936019897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4012432098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6742706298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7778329849243</t>
+    <t xml:space="preserve">11.4012441635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6742696762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7778339385986</t>
   </si>
   <si>
     <t xml:space="preserve">12.0885190963745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0696897506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2014970779419</t>
+    <t xml:space="preserve">12.0696887969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2014961242676</t>
   </si>
   <si>
     <t xml:space="preserve">12.1355934143066</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3615474700928</t>
+    <t xml:space="preserve">12.3615465164185</t>
   </si>
   <si>
     <t xml:space="preserve">12.3333024978638</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1638383865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7401752471924</t>
+    <t xml:space="preserve">12.1638374328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7401742935181</t>
   </si>
   <si>
     <t xml:space="preserve">12.1261777877808</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">12.5404262542725</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5498418807983</t>
+    <t xml:space="preserve">12.549840927124</t>
   </si>
   <si>
     <t xml:space="preserve">12.5027675628662</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">12.6345739364624</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1335525512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1241388320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.086480140686</t>
+    <t xml:space="preserve">13.1335554122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1241397857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0864810943604</t>
   </si>
   <si>
     <t xml:space="preserve">12.9546747207642</t>
@@ -1163,31 +1163,31 @@
     <t xml:space="preserve">13.4254121780396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4630708694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.538387298584</t>
+    <t xml:space="preserve">13.4630718231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5383882522583</t>
   </si>
   <si>
     <t xml:space="preserve">13.5572175979614</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6042919158936</t>
+    <t xml:space="preserve">13.6042909622192</t>
   </si>
   <si>
     <t xml:space="preserve">13.5101442337036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2559471130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.472484588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3030195236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9735040664673</t>
+    <t xml:space="preserve">13.2559461593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4724864959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3030204772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.973503112793</t>
   </si>
   <si>
     <t xml:space="preserve">12.6157445907593</t>
@@ -1196,13 +1196,13 @@
     <t xml:space="preserve">12.4086208343506</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3803758621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4651079177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5121822357178</t>
+    <t xml:space="preserve">12.3803749084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.46510887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5121812820435</t>
   </si>
   <si>
     <t xml:space="preserve">12.822868347168</t>
@@ -1214,19 +1214,19 @@
     <t xml:space="preserve">12.8511123657227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5969152450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2862281799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.257984161377</t>
+    <t xml:space="preserve">12.5969161987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.286229133606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2579860687256</t>
   </si>
   <si>
     <t xml:space="preserve">12.7287216186523</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0394077301025</t>
+    <t xml:space="preserve">13.0394067764282</t>
   </si>
   <si>
     <t xml:space="preserve">13.0958948135376</t>
@@ -1238,34 +1238,34 @@
     <t xml:space="preserve">13.4065818786621</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3312635421753</t>
+    <t xml:space="preserve">13.3312644958496</t>
   </si>
   <si>
     <t xml:space="preserve">13.3218488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1617984771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3406772613525</t>
+    <t xml:space="preserve">13.1617994308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3406791687012</t>
   </si>
   <si>
     <t xml:space="preserve">13.2465314865112</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8887710571289</t>
+    <t xml:space="preserve">12.8887729644775</t>
   </si>
   <si>
     <t xml:space="preserve">12.8605270385742</t>
   </si>
   <si>
-    <t xml:space="preserve">13.293604850769</t>
+    <t xml:space="preserve">13.2936058044434</t>
   </si>
   <si>
     <t xml:space="preserve">13.566632270813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6419515609741</t>
+    <t xml:space="preserve">13.6419496536255</t>
   </si>
   <si>
     <t xml:space="preserve">13.3124341964722</t>
@@ -1274,13 +1274,13 @@
     <t xml:space="preserve">13.7925863265991</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9997110366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1409311294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3951301574707</t>
+    <t xml:space="preserve">13.9997100830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1409320831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3951272964478</t>
   </si>
   <si>
     <t xml:space="preserve">14.3009824752808</t>
@@ -1289,13 +1289,13 @@
     <t xml:space="preserve">14.5645942687988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6022548675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6869859695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9129409790039</t>
+    <t xml:space="preserve">14.6022539138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6869850158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.912938117981</t>
   </si>
   <si>
     <t xml:space="preserve">14.8564510345459</t>
@@ -1307,79 +1307,79 @@
     <t xml:space="preserve">14.9694271087646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9976711273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0353317260742</t>
+    <t xml:space="preserve">14.997673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0353307723999</t>
   </si>
   <si>
     <t xml:space="preserve">14.903525352478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8941087722778</t>
+    <t xml:space="preserve">14.8941097259521</t>
   </si>
   <si>
     <t xml:space="preserve">14.7152309417725</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5928373336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1671371459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2706995010376</t>
+    <t xml:space="preserve">14.5928382873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1671380996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2706985473633</t>
   </si>
   <si>
     <t xml:space="preserve">15.2424564361572</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2518720626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.44016456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3930902481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5531435012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6567039489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4213352203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0165023803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3460187911987</t>
+    <t xml:space="preserve">15.2518701553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4401636123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3930912017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5531406402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.656699180603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4213342666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0165014266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3460168838501</t>
   </si>
   <si>
     <t xml:space="preserve">14.818528175354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6668357849121</t>
+    <t xml:space="preserve">14.6668338775635</t>
   </si>
   <si>
     <t xml:space="preserve">14.3444871902466</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6099500656128</t>
+    <t xml:space="preserve">14.6099491119385</t>
   </si>
   <si>
     <t xml:space="preserve">14.7332000732422</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8754119873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9273290634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4013710021973</t>
+    <t xml:space="preserve">14.875412940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9273300170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4013719558716</t>
   </si>
   <si>
     <t xml:space="preserve">14.6194305419922</t>
@@ -1388,82 +1388,82 @@
     <t xml:space="preserve">14.6289110183716</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1882791519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4916658401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1174011230469</t>
+    <t xml:space="preserve">15.1882801055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4916648864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1173992156982</t>
   </si>
   <si>
     <t xml:space="preserve">16.4587116241455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1553268432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1648044586182</t>
+    <t xml:space="preserve">16.1553249359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">16.202730178833</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2122077941895</t>
+    <t xml:space="preserve">16.2122097015381</t>
   </si>
   <si>
     <t xml:space="preserve">16.3259773254395</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1079177856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0699977874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5250759124756</t>
+    <t xml:space="preserve">16.1079196929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.069995880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5250778198242</t>
   </si>
   <si>
     <t xml:space="preserve">16.7241744995117</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6672878265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5724811553955</t>
+    <t xml:space="preserve">16.6672897338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5724792480469</t>
   </si>
   <si>
     <t xml:space="preserve">16.3070182800293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596111297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6767711639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8379440307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.885347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0465221405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9232692718506</t>
+    <t xml:space="preserve">16.2596130371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6767692565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8379421234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8853454589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0465240478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9232730865479</t>
   </si>
   <si>
     <t xml:space="preserve">16.7715759277344</t>
   </si>
   <si>
-    <t xml:space="preserve">16.373384475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4492301940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2216892242432</t>
+    <t xml:space="preserve">16.3733825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4492282867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2216873168945</t>
   </si>
   <si>
     <t xml:space="preserve">16.4018230438232</t>
@@ -1484,13 +1484,13 @@
     <t xml:space="preserve">17.5395240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9472007751465</t>
+    <t xml:space="preserve">17.9471988677979</t>
   </si>
   <si>
     <t xml:space="preserve">17.4447154998779</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0799331665039</t>
+    <t xml:space="preserve">18.0799312591553</t>
   </si>
   <si>
     <t xml:space="preserve">18.1652584075928</t>
@@ -1502,22 +1502,22 @@
     <t xml:space="preserve">18.1368141174316</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4117565155029</t>
+    <t xml:space="preserve">18.4117584228516</t>
   </si>
   <si>
     <t xml:space="preserve">18.2505855560303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0704498291016</t>
+    <t xml:space="preserve">18.0704479217529</t>
   </si>
   <si>
     <t xml:space="preserve">17.8618717193604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.634334564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7860279083252</t>
+    <t xml:space="preserve">17.6343326568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7860260009766</t>
   </si>
   <si>
     <t xml:space="preserve">17.7575817108154</t>
@@ -1535,43 +1535,43 @@
     <t xml:space="preserve">18.0325260162354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1083717346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2126598358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0609683990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9377193450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0040836334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.577449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3927974700928</t>
+    <t xml:space="preserve">18.1083755493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2126617431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0609664916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9377174377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0040817260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5774459838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3927993774414</t>
   </si>
   <si>
     <t xml:space="preserve">17.8334293365479</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0135650634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7435874938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.340877532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4167289733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3788032531738</t>
+    <t xml:space="preserve">18.0135631561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7435894012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3408813476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4167251586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3788051605225</t>
   </si>
   <si>
     <t xml:space="preserve">19.1891860961914</t>
@@ -1580,43 +1580,43 @@
     <t xml:space="preserve">19.0564575195312</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7246284484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4496822357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5255298614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7720317840576</t>
+    <t xml:space="preserve">18.7246265411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.449686050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5255279541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.772029876709</t>
   </si>
   <si>
     <t xml:space="preserve">18.9616470336914</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6867046356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1462955474854</t>
+    <t xml:space="preserve">18.6867027282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.146297454834</t>
   </si>
   <si>
     <t xml:space="preserve">18.5065689086914</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0420074462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3025016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5629997253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.453742980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5864772796631</t>
+    <t xml:space="preserve">18.0420093536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3025035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5629978179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4537420272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5864744186401</t>
   </si>
   <si>
     <t xml:space="preserve">15.671802520752</t>
@@ -1631,58 +1631,58 @@
     <t xml:space="preserve">15.4632234573364</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8045320510864</t>
+    <t xml:space="preserve">15.8045349121094</t>
   </si>
   <si>
     <t xml:space="preserve">15.7286863327026</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9512586593628</t>
+    <t xml:space="preserve">14.9512596130371</t>
   </si>
   <si>
     <t xml:space="preserve">15.0745096206665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9986610412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9797029495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0176248550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8469686508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6573534011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7047576904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6763153076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6478719711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.932297706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0555486679077</t>
+    <t xml:space="preserve">14.9986629486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9797019958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0176239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8469705581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6573524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.704758644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6763162612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6478729248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9322996139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0555477142334</t>
   </si>
   <si>
     <t xml:space="preserve">14.7900848388672</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8135595321655</t>
+    <t xml:space="preserve">13.8135604858398</t>
   </si>
   <si>
     <t xml:space="preserve">13.728232383728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1309413909912</t>
+    <t xml:space="preserve">13.1309404373169</t>
   </si>
   <si>
     <t xml:space="preserve">13.0835371017456</t>
@@ -1691,43 +1691,43 @@
     <t xml:space="preserve">13.386923789978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3964042663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6523866653442</t>
+    <t xml:space="preserve">13.2636728286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3964052200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6523847579956</t>
   </si>
   <si>
     <t xml:space="preserve">13.4912118911743</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2257480621338</t>
+    <t xml:space="preserve">13.2257499694824</t>
   </si>
   <si>
     <t xml:space="preserve">13.8704462051392</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0126571655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4961795806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2212362289429</t>
+    <t xml:space="preserve">14.0126581192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4961776733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2212352752686</t>
   </si>
   <si>
     <t xml:space="preserve">14.1643505096436</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3065624237061</t>
+    <t xml:space="preserve">14.3065633773804</t>
   </si>
   <si>
     <t xml:space="preserve">14.3350057601929</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946004867554</t>
+    <t xml:space="preserve">13.7945985794067</t>
   </si>
   <si>
     <t xml:space="preserve">13.7377128601074</t>
@@ -1739,19 +1739,19 @@
     <t xml:space="preserve">13.7566757202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.898886680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9462928771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4203338623047</t>
+    <t xml:space="preserve">13.8988876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9462919235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4203319549561</t>
   </si>
   <si>
     <t xml:space="preserve">13.7756357192993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7232646942139</t>
+    <t xml:space="preserve">12.7232666015625</t>
   </si>
   <si>
     <t xml:space="preserve">13.3205575942993</t>
@@ -1760,61 +1760,61 @@
     <t xml:space="preserve">13.1878252029419</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7471942901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.069543838501</t>
+    <t xml:space="preserve">13.7471952438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0695428848267</t>
   </si>
   <si>
     <t xml:space="preserve">14.8374881744385</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2546453475952</t>
+    <t xml:space="preserve">15.2546463012695</t>
   </si>
   <si>
     <t xml:space="preserve">14.8848934173584</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0839910507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1787986755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1503572463989</t>
+    <t xml:space="preserve">15.0839891433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1787996292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1503562927246</t>
   </si>
   <si>
     <t xml:space="preserve">15.3115301132202</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3589363098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2925682067871</t>
+    <t xml:space="preserve">15.3589344024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2925691604614</t>
   </si>
   <si>
     <t xml:space="preserve">15.1408748626709</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0271062850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.922815322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8280086517334</t>
+    <t xml:space="preserve">15.0271053314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9228172302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8280076980591</t>
   </si>
   <si>
     <t xml:space="preserve">14.8659315109253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9417781829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6149168014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7097225189209</t>
+    <t xml:space="preserve">14.9417772293091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6149158477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7097253799438</t>
   </si>
   <si>
     <t xml:space="preserve">15.0650291442871</t>
@@ -1826,46 +1826,46 @@
     <t xml:space="preserve">15.5485496520996</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4347829818726</t>
+    <t xml:space="preserve">15.4347820281982</t>
   </si>
   <si>
     <t xml:space="preserve">15.3968572616577</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7806053161621</t>
+    <t xml:space="preserve">14.7806043624878</t>
   </si>
   <si>
     <t xml:space="preserve">14.9038553237915</t>
   </si>
   <si>
-    <t xml:space="preserve">15.226203918457</t>
+    <t xml:space="preserve">15.2262029647827</t>
   </si>
   <si>
     <t xml:space="preserve">15.1977605819702</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4442615509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3684148788452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5106296539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7381687164307</t>
+    <t xml:space="preserve">15.4442625045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3684139251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5106287002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7381677627563</t>
   </si>
   <si>
     <t xml:space="preserve">16.4302673339844</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9657096862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2641258239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7855701446533</t>
+    <t xml:space="preserve">15.9657077789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2641267776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7855710983276</t>
   </si>
   <si>
     <t xml:space="preserve">16.6862487792969</t>
@@ -1874,58 +1874,58 @@
     <t xml:space="preserve">16.8474254608154</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4966335296631</t>
+    <t xml:space="preserve">16.4966316223145</t>
   </si>
   <si>
     <t xml:space="preserve">16.1932468414307</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2311687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7526149749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4207878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8095016479492</t>
+    <t xml:space="preserve">16.2311725616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7526168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4207859039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8094997406006</t>
   </si>
   <si>
     <t xml:space="preserve">16.7336540222168</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8948287963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8663864135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2501316070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8993425369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8898611068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9277820587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8519353866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3544235229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2406482696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9183044433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5015983581543</t>
+    <t xml:space="preserve">16.8948268890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8663883209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.250129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8993434906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8898601531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9277830123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8519372940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3544216156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.240650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9183034896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5016002655029</t>
   </si>
   <si>
     <t xml:space="preserve">17.6627731323242</t>
@@ -1934,16 +1934,16 @@
     <t xml:space="preserve">18.089412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3119812011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2835445404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8239498138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6677417755127</t>
+    <t xml:space="preserve">17.3119850158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.283540725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8239479064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6677436828613</t>
   </si>
   <si>
     <t xml:space="preserve">18.5743827819824</t>
@@ -1952,22 +1952,22 @@
     <t xml:space="preserve">18.8704280853271</t>
   </si>
   <si>
-    <t xml:space="preserve">19.596212387085</t>
+    <t xml:space="preserve">19.5962142944336</t>
   </si>
   <si>
     <t xml:space="preserve">19.5007133483887</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9277267456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9468231201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9850254058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5934810638428</t>
+    <t xml:space="preserve">18.9277248382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9468269348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9850234985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5934829711914</t>
   </si>
   <si>
     <t xml:space="preserve">18.708080291748</t>
@@ -1982,70 +1982,70 @@
     <t xml:space="preserve">19.2333202362061</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3861179351807</t>
+    <t xml:space="preserve">19.3861141204834</t>
   </si>
   <si>
     <t xml:space="preserve">19.0900707244873</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1951198577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1187210083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2524185180664</t>
+    <t xml:space="preserve">19.1951217651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1187229156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.252420425415</t>
   </si>
   <si>
     <t xml:space="preserve">19.9018077850342</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1501007080078</t>
+    <t xml:space="preserve">20.1501026153564</t>
   </si>
   <si>
     <t xml:space="preserve">20.2646999359131</t>
   </si>
   <si>
-    <t xml:space="preserve">20.589391708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5511932373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.799488067627</t>
+    <t xml:space="preserve">20.5893898010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5511951446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7994899749756</t>
   </si>
   <si>
     <t xml:space="preserve">19.9591045379639</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8445072174072</t>
+    <t xml:space="preserve">19.8445091247559</t>
   </si>
   <si>
     <t xml:space="preserve">19.4816150665283</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3097171783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6344127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6726093292236</t>
+    <t xml:space="preserve">19.3097190856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6344108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6726131439209</t>
   </si>
   <si>
     <t xml:space="preserve">20.0928039550781</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9400062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6535110473633</t>
+    <t xml:space="preserve">19.9400024414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6535129547119</t>
   </si>
   <si>
     <t xml:space="preserve">19.558012008667</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7299118041992</t>
+    <t xml:space="preserve">19.7299098968506</t>
   </si>
   <si>
     <t xml:space="preserve">20.3028984069824</t>
@@ -2057,10 +2057,10 @@
     <t xml:space="preserve">20.2264995574951</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7039928436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6848907470703</t>
+    <t xml:space="preserve">20.7039909362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6848888397217</t>
   </si>
   <si>
     <t xml:space="preserve">20.4174976348877</t>
@@ -2069,10 +2069,10 @@
     <t xml:space="preserve">20.0355033874512</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1310005187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1883010864258</t>
+    <t xml:space="preserve">20.1310043334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1882991790771</t>
   </si>
   <si>
     <t xml:space="preserve">21.2769794464111</t>
@@ -2087,13 +2087,13 @@
     <t xml:space="preserve">20.0164031982422</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5702934265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9904861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1050815582275</t>
+    <t xml:space="preserve">20.5702953338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9904842376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1050853729248</t>
   </si>
   <si>
     <t xml:space="preserve">21.1623821258545</t>
@@ -2105,16 +2105,16 @@
     <t xml:space="preserve">21.0286846160889</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2960796356201</t>
+    <t xml:space="preserve">21.2960777282715</t>
   </si>
   <si>
     <t xml:space="preserve">21.849967956543</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4802570343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5566539764404</t>
+    <t xml:space="preserve">22.4802551269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5566558837891</t>
   </si>
   <si>
     <t xml:space="preserve">22.5184555053711</t>
@@ -2123,34 +2123,34 @@
     <t xml:space="preserve">22.0982627868652</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2510623931885</t>
+    <t xml:space="preserve">22.2510585784912</t>
   </si>
   <si>
     <t xml:space="preserve">21.9645652770996</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9454689025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3083610534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5948543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7476501464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8049468994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0600643157959</t>
+    <t xml:space="preserve">21.9454669952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3083591461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5948524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7476482391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8049488067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0600662231445</t>
   </si>
   <si>
     <t xml:space="preserve">22.2319602966309</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3533802032471</t>
+    <t xml:space="preserve">21.3533782958984</t>
   </si>
   <si>
     <t xml:space="preserve">20.474796295166</t>
@@ -2159,70 +2159,70 @@
     <t xml:space="preserve">20.4556941986084</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1241855621338</t>
+    <t xml:space="preserve">21.1241836547852</t>
   </si>
   <si>
     <t xml:space="preserve">20.780387878418</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8758869171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0859813690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7353706359863</t>
+    <t xml:space="preserve">20.8758907318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0859832763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7353687286377</t>
   </si>
   <si>
     <t xml:space="preserve">21.5061740875244</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2196807861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3724765777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6016731262207</t>
+    <t xml:space="preserve">21.2196826934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3724784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6016750335693</t>
   </si>
   <si>
     <t xml:space="preserve">21.6780700683594</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4870777130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5825748443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.646692276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6084938049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4938926696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8567867279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3792953491211</t>
+    <t xml:space="preserve">21.4870738983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5825729370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6466941833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.608491897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.493896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8567886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3792991638184</t>
   </si>
   <si>
     <t xml:space="preserve">20.8949851989746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9331874847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3219985961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3410987854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.830867767334</t>
+    <t xml:space="preserve">20.9331855773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.32200050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3410968780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8308696746826</t>
   </si>
   <si>
     <t xml:space="preserve">22.0218639373779</t>
@@ -2231,13 +2231,13 @@
     <t xml:space="preserve">22.5375537872314</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6521511077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0150451660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4543342590332</t>
+    <t xml:space="preserve">22.6521530151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0150489807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4543361663818</t>
   </si>
   <si>
     <t xml:space="preserve">23.7217311859131</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">23.8745269775391</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9700260162354</t>
+    <t xml:space="preserve">23.970027923584</t>
   </si>
   <si>
     <t xml:space="preserve">24.3711185455322</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">24.9823055267334</t>
   </si>
   <si>
-    <t xml:space="preserve">25.287899017334</t>
+    <t xml:space="preserve">25.2879009246826</t>
   </si>
   <si>
     <t xml:space="preserve">24.9250087738037</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0205078125</t>
+    <t xml:space="preserve">25.0205059051514</t>
   </si>
   <si>
     <t xml:space="preserve">24.6194133758545</t>
@@ -2294,10 +2294,10 @@
     <t xml:space="preserve">24.9441089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8295097351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6385116577148</t>
+    <t xml:space="preserve">24.8295078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6385135650635</t>
   </si>
   <si>
     <t xml:space="preserve">24.4475173950195</t>
@@ -2306,40 +2306,40 @@
     <t xml:space="preserve">24.5430145263672</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3520164489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6576137542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6767139434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4857158660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5621147155762</t>
+    <t xml:space="preserve">24.3520202636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6576118469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6767120361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4857139587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5621166229248</t>
   </si>
   <si>
     <t xml:space="preserve">24.5812149047852</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6958103179932</t>
+    <t xml:space="preserve">24.6958141326904</t>
   </si>
   <si>
     <t xml:space="preserve">25.3070011138916</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3451976776123</t>
+    <t xml:space="preserve">25.3451995849609</t>
   </si>
   <si>
     <t xml:space="preserve">24.8486099243164</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0014038085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2115020751953</t>
+    <t xml:space="preserve">25.0014057159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2115001678467</t>
   </si>
   <si>
     <t xml:space="preserve">25.7653923034668</t>
@@ -2351,13 +2351,13 @@
     <t xml:space="preserve">25.5552959442139</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1542015075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8226890563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7722110748291</t>
+    <t xml:space="preserve">25.154203414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8226909637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7722091674805</t>
   </si>
   <si>
     <t xml:space="preserve">24.5239143371582</t>
@@ -2366,49 +2366,49 @@
     <t xml:space="preserve">24.9059066772461</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6698932647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.223783493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2810821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.395679473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1405620574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2169647216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5225563049316</t>
+    <t xml:space="preserve">25.6698913574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2237815856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2810802459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3956775665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1405639648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2169628143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.522554397583</t>
   </si>
   <si>
     <t xml:space="preserve">27.6944541931152</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8281517028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1910419464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.783130645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2865409851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8854484558105</t>
+    <t xml:space="preserve">27.8281497955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1910438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7831325531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2865447998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8854503631592</t>
   </si>
   <si>
     <t xml:space="preserve">25.9754867553711</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2306022644043</t>
+    <t xml:space="preserve">25.2306003570557</t>
   </si>
   <si>
     <t xml:space="preserve">24.6003131866455</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">23.6071338653564</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4666156768799</t>
+    <t xml:space="preserve">24.4666175842285</t>
   </si>
   <si>
     <t xml:space="preserve">23.4352359771729</t>
@@ -2429,16 +2429,16 @@
     <t xml:space="preserve">19.3479175567627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5852909088135</t>
+    <t xml:space="preserve">15.5852918624878</t>
   </si>
   <si>
     <t xml:space="preserve">17.3233585357666</t>
   </si>
   <si>
-    <t xml:space="preserve">15.728536605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1200790405273</t>
+    <t xml:space="preserve">15.7285385131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.120080947876</t>
   </si>
   <si>
     <t xml:space="preserve">16.9031677246094</t>
@@ -2447,46 +2447,46 @@
     <t xml:space="preserve">17.5239028930664</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7435531616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1350917816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8322257995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1446418762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2210388183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1159915924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8772449493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3806591033936</t>
+    <t xml:space="preserve">17.7435493469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1350898742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8322277069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1446399688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.221040725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1159896850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8772468566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3806571960449</t>
   </si>
   <si>
     <t xml:space="preserve">17.4093055725098</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8076686859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6480522155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7844772338867</t>
+    <t xml:space="preserve">16.8076667785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6480503082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7844791412354</t>
   </si>
   <si>
     <t xml:space="preserve">18.4311351776123</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4454593658447</t>
+    <t xml:space="preserve">18.4454612731934</t>
   </si>
   <si>
     <t xml:space="preserve">18.7653789520264</t>
@@ -2498,13 +2498,13 @@
     <t xml:space="preserve">20.8663368225098</t>
   </si>
   <si>
-    <t xml:space="preserve">19.271520614624</t>
+    <t xml:space="preserve">19.2715187072754</t>
   </si>
   <si>
     <t xml:space="preserve">18.8465538024902</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0068550109863</t>
+    <t xml:space="preserve">20.006856918335</t>
   </si>
   <si>
     <t xml:space="preserve">20.2455997467041</t>
@@ -2516,7 +2516,7 @@
     <t xml:space="preserve">19.9686546325684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7681083679199</t>
+    <t xml:space="preserve">19.7681102752686</t>
   </si>
   <si>
     <t xml:space="preserve">20.6753425598145</t>
@@ -2525,19 +2525,19 @@
     <t xml:space="preserve">21.7640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3820285797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.337007522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7926692962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.019136428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4297771453857</t>
+    <t xml:space="preserve">21.3820247650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3370056152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.792667388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0191345214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4297752380371</t>
   </si>
   <si>
     <t xml:space="preserve">21.8595161437988</t>
@@ -2546,19 +2546,19 @@
     <t xml:space="preserve">20.9522857666016</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9932155609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6589736938477</t>
+    <t xml:space="preserve">21.9932174682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.658971786499</t>
   </si>
   <si>
     <t xml:space="preserve">23.0341453552246</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1391906738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2797107696533</t>
+    <t xml:space="preserve">23.1391944885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2797088623047</t>
   </si>
   <si>
     <t xml:space="preserve">23.5020847320557</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">23.521183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8458786010742</t>
+    <t xml:space="preserve">23.8458766937256</t>
   </si>
   <si>
     <t xml:space="preserve">23.8172283172607</t>
@@ -2585,61 +2585,61 @@
     <t xml:space="preserve">22.6330509185791</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8881683349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0696125030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6999015808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9386463165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3015403747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6807994842529</t>
+    <t xml:space="preserve">21.8881664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0696144104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6999034881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.938648223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3015384674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6808013916016</t>
   </si>
   <si>
     <t xml:space="preserve">22.709451675415</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1487407684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.463888168335</t>
+    <t xml:space="preserve">23.1487426757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4638862609863</t>
   </si>
   <si>
     <t xml:space="preserve">22.4229564666748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4611568450928</t>
+    <t xml:space="preserve">22.4611549377441</t>
   </si>
   <si>
     <t xml:space="preserve">22.6426029205322</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7381019592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.272891998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2442398071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5402851104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7408294677734</t>
+    <t xml:space="preserve">22.7381000518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2728900909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2442417144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5402870178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7408332824707</t>
   </si>
   <si>
     <t xml:space="preserve">23.8363285064697</t>
   </si>
   <si>
-    <t xml:space="preserve">23.71217918396</t>
+    <t xml:space="preserve">23.7121810913086</t>
   </si>
   <si>
     <t xml:space="preserve">23.7599296569824</t>
@@ -2648,10 +2648,10 @@
     <t xml:space="preserve">24.1610202789307</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3233661651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7340126037598</t>
+    <t xml:space="preserve">24.3233699798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7340106964111</t>
   </si>
   <si>
     <t xml:space="preserve">25.2783508300781</t>
@@ -2666,10 +2666,10 @@
     <t xml:space="preserve">24.7531108856201</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1351051330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5580234527588</t>
+    <t xml:space="preserve">25.1351013183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5580253601074</t>
   </si>
   <si>
     <t xml:space="preserve">26.5102767944336</t>
@@ -2681,40 +2681,40 @@
     <t xml:space="preserve">28.2292423248291</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5034561157227</t>
+    <t xml:space="preserve">27.503454208374</t>
   </si>
   <si>
     <t xml:space="preserve">27.5894050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1596622467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5512065887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0164165496826</t>
+    <t xml:space="preserve">27.1596641540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5512046813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0164184570312</t>
   </si>
   <si>
     <t xml:space="preserve">27.035514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3793087005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2265129089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0546169281006</t>
+    <t xml:space="preserve">27.3793067932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2265110015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.054615020752</t>
   </si>
   <si>
     <t xml:space="preserve">27.2838096618652</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5675773620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0450668334961</t>
+    <t xml:space="preserve">26.5675735473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0450649261475</t>
   </si>
   <si>
     <t xml:space="preserve">26.7108211517334</t>
@@ -2732,25 +2732,25 @@
     <t xml:space="preserve">26.5389270782471</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2619800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4625244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5989551544189</t>
+    <t xml:space="preserve">26.2619819641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4625282287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5989532470703</t>
   </si>
   <si>
     <t xml:space="preserve">26.6726245880127</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7585716247559</t>
+    <t xml:space="preserve">26.7585697174072</t>
   </si>
   <si>
     <t xml:space="preserve">27.3888607025146</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4461574554443</t>
+    <t xml:space="preserve">27.446159362793</t>
   </si>
   <si>
     <t xml:space="preserve">28.1814918518066</t>
@@ -2759,7 +2759,7 @@
     <t xml:space="preserve">28.3533897399902</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5061893463135</t>
+    <t xml:space="preserve">28.5061855316162</t>
   </si>
   <si>
     <t xml:space="preserve">28.9932270050049</t>
@@ -2771,88 +2771,88 @@
     <t xml:space="preserve">28.6971836090088</t>
   </si>
   <si>
-    <t xml:space="preserve">27.57985496521</t>
+    <t xml:space="preserve">27.5798530578613</t>
   </si>
   <si>
     <t xml:space="preserve">27.6562519073486</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4748077392578</t>
+    <t xml:space="preserve">27.4748058319092</t>
   </si>
   <si>
     <t xml:space="preserve">27.6849021911621</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3847713470459</t>
+    <t xml:space="preserve">29.3847675323486</t>
   </si>
   <si>
     <t xml:space="preserve">29.9673080444336</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1746692657471</t>
+    <t xml:space="preserve">29.1746711730957</t>
   </si>
   <si>
     <t xml:space="preserve">29.4802665710449</t>
   </si>
   <si>
-    <t xml:space="preserve">29.833610534668</t>
+    <t xml:space="preserve">29.8336124420166</t>
   </si>
   <si>
     <t xml:space="preserve">30.0246067047119</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1651229858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3274707794189</t>
+    <t xml:space="preserve">29.1651248931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3274688720703</t>
   </si>
   <si>
     <t xml:space="preserve">29.8049602508545</t>
   </si>
   <si>
-    <t xml:space="preserve">30.473445892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9891357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7503910064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5402965545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9222888946533</t>
+    <t xml:space="preserve">30.4734477996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9891376495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7503929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5402946472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.922290802002</t>
   </si>
   <si>
     <t xml:space="preserve">30.7408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9318389892578</t>
+    <t xml:space="preserve">30.9318408966064</t>
   </si>
   <si>
     <t xml:space="preserve">30.7217407226562</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6835460662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8172397613525</t>
+    <t xml:space="preserve">30.6835441589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8172416687012</t>
   </si>
   <si>
     <t xml:space="preserve">30.4829978942871</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5593948364258</t>
+    <t xml:space="preserve">30.5593967437744</t>
   </si>
   <si>
     <t xml:space="preserve">28.7258319854736</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2128734588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9031887054443</t>
+    <t xml:space="preserve">29.2128753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.903190612793</t>
   </si>
   <si>
     <t xml:space="preserve">31.9918651580811</t>
@@ -2873,28 +2873,28 @@
     <t xml:space="preserve">33.3288421630859</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5580368041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.131031036377</t>
+    <t xml:space="preserve">33.558032989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1310234069824</t>
   </si>
   <si>
     <t xml:space="preserve">33.4338874816895</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4461708068848</t>
+    <t xml:space="preserve">34.4461669921875</t>
   </si>
   <si>
     <t xml:space="preserve">33.8158836364746</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9304809570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6603546142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6699028015137</t>
+    <t xml:space="preserve">33.930477142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6603584289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6699066162109</t>
   </si>
   <si>
     <t xml:space="preserve">32.8513526916504</t>
@@ -2903,34 +2903,34 @@
     <t xml:space="preserve">31.5143775939941</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6098709106445</t>
+    <t xml:space="preserve">31.6098728179932</t>
   </si>
   <si>
     <t xml:space="preserve">31.972770690918</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7367553710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0587120056152</t>
+    <t xml:space="preserve">32.7367477416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0587158203125</t>
   </si>
   <si>
     <t xml:space="preserve">31.2565326690674</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8840923309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0177879333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1323852539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8745441436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0846328735352</t>
+    <t xml:space="preserve">30.884090423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.017786026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1323833465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8745422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0846366882324</t>
   </si>
   <si>
     <t xml:space="preserve">31.6194267272949</t>
@@ -2939,94 +2939,94 @@
     <t xml:space="preserve">32.0969161987305</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3615760803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1542091369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9441204071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4216156005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6958236694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2115097045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7435684204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2783622741699</t>
+    <t xml:space="preserve">31.3615837097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1542129516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9441184997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4216117858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.695821762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2115135192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7435741424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2783584594727</t>
   </si>
   <si>
     <t xml:space="preserve">32.5075569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4120559692383</t>
+    <t xml:space="preserve">32.4120597839355</t>
   </si>
   <si>
     <t xml:space="preserve">32.0491676330566</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5334758758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2087821960449</t>
+    <t xml:space="preserve">31.5334796905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2087802886963</t>
   </si>
   <si>
     <t xml:space="preserve">32.3165588378906</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1637687683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1064682006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3834075927734</t>
+    <t xml:space="preserve">32.1637649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1064643859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3834114074707</t>
   </si>
   <si>
     <t xml:space="preserve">32.6221542358398</t>
   </si>
   <si>
-    <t xml:space="preserve">32.650806427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8036041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5839576721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3547592163086</t>
+    <t xml:space="preserve">32.6507987976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8036003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5839500427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3547630310059</t>
   </si>
   <si>
     <t xml:space="preserve">32.0682678222656</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0396194458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5648574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3261108398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9250164031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0423469543457</t>
+    <t xml:space="preserve">32.0396156311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5648536682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.326114654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9250202178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0423431396484</t>
   </si>
   <si>
     <t xml:space="preserve">33.7967796325684</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5989646911621</t>
+    <t xml:space="preserve">34.5989685058594</t>
   </si>
   <si>
     <t xml:space="preserve">34.4843711853027</t>
@@ -3035,10 +3035,10 @@
     <t xml:space="preserve">34.9427604675293</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8854560852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0000648498535</t>
+    <t xml:space="preserve">34.8854598999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0000610351562</t>
   </si>
   <si>
     <t xml:space="preserve">35.8022422790527</t>
@@ -3050,7 +3050,7 @@
     <t xml:space="preserve">35.334300994873</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2551727294922</t>
+    <t xml:space="preserve">34.2551689147949</t>
   </si>
   <si>
     <t xml:space="preserve">33.9018287658691</t>
@@ -3059,25 +3059,25 @@
     <t xml:space="preserve">33.3670387268066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3192901611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7817726135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8104248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4598121643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7081031799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9768581390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4898147583008</t>
+    <t xml:space="preserve">33.3192939758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.781774520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8104267120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4598083496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7080993652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9768543243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4898166656494</t>
   </si>
   <si>
     <t xml:space="preserve">28.6876335144043</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">29.0027770996094</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3874988555908</t>
+    <t xml:space="preserve">30.3874969482422</t>
   </si>
   <si>
     <t xml:space="preserve">30.6453437805176</t>
@@ -3098,49 +3098,49 @@
     <t xml:space="preserve">30.5211963653564</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7312927246094</t>
+    <t xml:space="preserve">30.731294631958</t>
   </si>
   <si>
     <t xml:space="preserve">31.1228351593018</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5498447418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5375652313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1487560272217</t>
+    <t xml:space="preserve">30.5498466491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5375671386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.148754119873</t>
   </si>
   <si>
     <t xml:space="preserve">31.6671772003174</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4065990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7694911956787</t>
+    <t xml:space="preserve">30.4066009521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7694931030273</t>
   </si>
   <si>
     <t xml:space="preserve">30.6644439697266</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3111019134521</t>
+    <t xml:space="preserve">30.3111000061035</t>
   </si>
   <si>
     <t xml:space="preserve">30.9413890838623</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2756328582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9604873657227</t>
+    <t xml:space="preserve">31.2756290435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.960485458374</t>
   </si>
   <si>
     <t xml:space="preserve">31.5812244415283</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3424816131592</t>
+    <t xml:space="preserve">31.3424797058105</t>
   </si>
   <si>
     <t xml:space="preserve">33.5007362365723</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">32.9373016357422</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8731880187988</t>
+    <t xml:space="preserve">33.8731842041016</t>
   </si>
   <si>
     <t xml:space="preserve">33.6344375610352</t>
@@ -3161,19 +3161,19 @@
     <t xml:space="preserve">34.1787757873535</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2169761657715</t>
+    <t xml:space="preserve">34.2169799804688</t>
   </si>
   <si>
     <t xml:space="preserve">34.9905052185059</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8281593322754</t>
+    <t xml:space="preserve">34.8281669616699</t>
   </si>
   <si>
     <t xml:space="preserve">34.302921295166</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1091957092285</t>
+    <t xml:space="preserve">33.1091918945312</t>
   </si>
   <si>
     <t xml:space="preserve">33.5484924316406</t>
@@ -3182,13 +3182,13 @@
     <t xml:space="preserve">33.8063354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2333450317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0928268432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5771369934082</t>
+    <t xml:space="preserve">33.233341217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.092830657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5771408081055</t>
   </si>
   <si>
     <t xml:space="preserve">32.2688179016113</t>
@@ -3197,10 +3197,10 @@
     <t xml:space="preserve">31.9059200286865</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8868217468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0873603820801</t>
+    <t xml:space="preserve">31.8868179321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0873641967773</t>
   </si>
   <si>
     <t xml:space="preserve">32.946849822998</t>
@@ -3209,58 +3209,58 @@
     <t xml:space="preserve">33.1378440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7995071411133</t>
+    <t xml:space="preserve">34.7995109558105</t>
   </si>
   <si>
     <t xml:space="preserve">35.8851928710938</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6538238525391</t>
+    <t xml:space="preserve">36.6538200378418</t>
   </si>
   <si>
     <t xml:space="preserve">35.9620552062988</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7691192626953</t>
+    <t xml:space="preserve">36.769115447998</t>
   </si>
   <si>
     <t xml:space="preserve">37.0765647888184</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4224433898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1246032714844</t>
+    <t xml:space="preserve">37.4224472045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1245994567871</t>
   </si>
   <si>
     <t xml:space="preserve">37.018913269043</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6818580627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2391128540039</t>
+    <t xml:space="preserve">37.6818542480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2391090393066</t>
   </si>
   <si>
     <t xml:space="preserve">37.7683258056641</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8836212158203</t>
+    <t xml:space="preserve">37.883617401123</t>
   </si>
   <si>
     <t xml:space="preserve">38.0181274414062</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2479286193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6138191223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.642635345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3440093994141</t>
+    <t xml:space="preserve">39.247932434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6138153076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6426391601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3440055847168</t>
   </si>
   <si>
     <t xml:space="preserve">38.594596862793</t>
@@ -3269,13 +3269,13 @@
     <t xml:space="preserve">38.7963638305664</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7194976806641</t>
+    <t xml:space="preserve">38.7195014953613</t>
   </si>
   <si>
     <t xml:space="preserve">38.6042060852051</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6130256652832</t>
+    <t xml:space="preserve">39.6130294799805</t>
   </si>
   <si>
     <t xml:space="preserve">39.6514587402344</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">40.4969482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">40.006950378418</t>
+    <t xml:space="preserve">40.0069465637207</t>
   </si>
   <si>
     <t xml:space="preserve">39.8051834106445</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">39.9685134887695</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6034240722656</t>
+    <t xml:space="preserve">39.6034202575684</t>
   </si>
   <si>
     <t xml:space="preserve">39.7571487426758</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">36.5769577026367</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5665588378906</t>
+    <t xml:space="preserve">37.5665626525879</t>
   </si>
   <si>
     <t xml:space="preserve">37.5569534301758</t>
@@ -3323,13 +3323,13 @@
     <t xml:space="preserve">38.9789123535156</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1614570617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4793014526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4496955871582</t>
+    <t xml:space="preserve">39.1614608764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.479305267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4496994018555</t>
   </si>
   <si>
     <t xml:space="preserve">39.1806755065918</t>
@@ -3338,19 +3338,19 @@
     <t xml:space="preserve">38.8540115356445</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4304809570312</t>
+    <t xml:space="preserve">39.430477142334</t>
   </si>
   <si>
     <t xml:space="preserve">38.7675399780273</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0453834533691</t>
+    <t xml:space="preserve">40.0453796386719</t>
   </si>
   <si>
     <t xml:space="preserve">40.6410636901855</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7275352478027</t>
+    <t xml:space="preserve">40.7275314331055</t>
   </si>
   <si>
     <t xml:space="preserve">40.3528289794922</t>
@@ -3359,16 +3359,16 @@
     <t xml:space="preserve">40.7083168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2567520141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3336143493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2663612365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4489059448242</t>
+    <t xml:space="preserve">40.2567558288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.333610534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.266357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4489097595215</t>
   </si>
   <si>
     <t xml:space="preserve">41.0157661437988</t>
@@ -3377,16 +3377,16 @@
     <t xml:space="preserve">41.1406707763672</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3424339294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2271385192871</t>
+    <t xml:space="preserve">41.3424301147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2271423339844</t>
   </si>
   <si>
     <t xml:space="preserve">41.2367477416992</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5634155273438</t>
+    <t xml:space="preserve">41.5634078979492</t>
   </si>
   <si>
     <t xml:space="preserve">42.0822372436523</t>
@@ -3398,19 +3398,19 @@
     <t xml:space="preserve">42.2455711364746</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0341949462891</t>
+    <t xml:space="preserve">42.0342025756836</t>
   </si>
   <si>
     <t xml:space="preserve">41.7651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9669418334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4665451049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5434150695801</t>
+    <t xml:space="preserve">41.9669456481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.466552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5434112548828</t>
   </si>
   <si>
     <t xml:space="preserve">42.6683158874512</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">42.3896865844727</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8989028930664</t>
+    <t xml:space="preserve">42.8988990783691</t>
   </si>
   <si>
     <t xml:space="preserve">42.0245895385742</t>
@@ -3437,10 +3437,10 @@
     <t xml:space="preserve">41.4577293395996</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7187156677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0061569213867</t>
+    <t xml:space="preserve">39.7187118530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0061645507812</t>
   </si>
   <si>
     <t xml:space="preserve">40.0165596008301</t>
@@ -3449,46 +3449,46 @@
     <t xml:space="preserve">40.8332214355469</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0638084411621</t>
+    <t xml:space="preserve">41.0638046264648</t>
   </si>
   <si>
     <t xml:space="preserve">43.0718421936035</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1679191589355</t>
+    <t xml:space="preserve">43.1679229736328</t>
   </si>
   <si>
     <t xml:space="preserve">44.3112487792969</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2159614562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9477272033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7859687805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2759628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5842018127441</t>
+    <t xml:space="preserve">43.2159576416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9477310180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7859649658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2759666442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5842056274414</t>
   </si>
   <si>
     <t xml:space="preserve">39.1902847290039</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5169486999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6802787780762</t>
+    <t xml:space="preserve">39.5169525146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6802825927734</t>
   </si>
   <si>
     <t xml:space="preserve">40.10302734375</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0077362060547</t>
+    <t xml:space="preserve">39.0077323913574</t>
   </si>
   <si>
     <t xml:space="preserve">39.0653800964355</t>
@@ -3503,37 +3503,37 @@
     <t xml:space="preserve">41.2463569641113</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6210632324219</t>
+    <t xml:space="preserve">41.6210594177246</t>
   </si>
   <si>
     <t xml:space="preserve">42.7932167053223</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5730209350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1694869995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2263565063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9469375610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3800811767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3992919921875</t>
+    <t xml:space="preserve">41.5730247497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1694946289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2263526916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9469413757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3800773620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3992958068848</t>
   </si>
   <si>
     <t xml:space="preserve">43.0045852661133</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9653663635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8596801757812</t>
+    <t xml:space="preserve">43.9653701782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8596839904785</t>
   </si>
   <si>
     <t xml:space="preserve">44.7147789001465</t>
@@ -3542,13 +3542,13 @@
     <t xml:space="preserve">44.2632102966309</t>
   </si>
   <si>
-    <t xml:space="preserve">43.725170135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0038032531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2055587768555</t>
+    <t xml:space="preserve">43.7251739501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0037994384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2055625915527</t>
   </si>
   <si>
     <t xml:space="preserve">43.436939239502</t>
@@ -3557,28 +3557,28 @@
     <t xml:space="preserve">42.2551765441895</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8604698181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8028221130371</t>
+    <t xml:space="preserve">42.8604736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8028259277344</t>
   </si>
   <si>
     <t xml:space="preserve">40.6794967651367</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6018486022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5449829101562</t>
+    <t xml:space="preserve">41.6018447875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5449867248535</t>
   </si>
   <si>
     <t xml:space="preserve">41.0830230712891</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4289016723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4192962646484</t>
+    <t xml:space="preserve">41.428897857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4193000793457</t>
   </si>
   <si>
     <t xml:space="preserve">40.1318511962891</t>
@@ -3593,40 +3593,40 @@
     <t xml:space="preserve">40.1798858642578</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1414604187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3143997192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0926322937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9861602783203</t>
+    <t xml:space="preserve">40.1414566040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.314395904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0926284790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.986156463623</t>
   </si>
   <si>
     <t xml:space="preserve">41.5057716369629</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3512573242188</t>
+    <t xml:space="preserve">42.3512535095215</t>
   </si>
   <si>
     <t xml:space="preserve">42.3704681396484</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5626220703125</t>
+    <t xml:space="preserve">42.5626258850098</t>
   </si>
   <si>
     <t xml:space="preserve">43.5330200195312</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6579170227051</t>
+    <t xml:space="preserve">43.6579208374023</t>
   </si>
   <si>
     <t xml:space="preserve">44.4169387817383</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0702667236328</t>
+    <t xml:space="preserve">45.0702629089355</t>
   </si>
   <si>
     <t xml:space="preserve">45.3681106567383</t>
@@ -3638,13 +3638,13 @@
     <t xml:space="preserve">44.8108558654785</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8885040283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0518341064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5914497375488</t>
+    <t xml:space="preserve">43.8885078430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0518417358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5914459228516</t>
   </si>
   <si>
     <t xml:space="preserve">41.8708648681641</t>
@@ -3659,16 +3659,16 @@
     <t xml:space="preserve">38.9308700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">38.383228302002</t>
+    <t xml:space="preserve">38.3832244873047</t>
   </si>
   <si>
     <t xml:space="preserve">38.1814613342285</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2014656066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7795066833496</t>
+    <t xml:space="preserve">37.2014694213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7795104980469</t>
   </si>
   <si>
     <t xml:space="preserve">34.5208854675293</t>
@@ -3677,64 +3677,64 @@
     <t xml:space="preserve">35.001277923584</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0397033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4632377624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0581359863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7018585205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8643989562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5585250854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8859825134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6553955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7138252258301</t>
+    <t xml:space="preserve">35.0397109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4632339477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0581321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7018623352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8644065856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5585289001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.885986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6553916931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7138290405273</t>
   </si>
   <si>
     <t xml:space="preserve">35.116569519043</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7706871032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9636268615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3775596618652</t>
+    <t xml:space="preserve">34.7706832885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9636306762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.377555847168</t>
   </si>
   <si>
     <t xml:space="preserve">34.7418632507324</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2710838317871</t>
+    <t xml:space="preserve">34.2710800170898</t>
   </si>
   <si>
     <t xml:space="preserve">34.280689239502</t>
   </si>
   <si>
-    <t xml:space="preserve">34.146183013916</t>
+    <t xml:space="preserve">34.1461868286133</t>
   </si>
   <si>
     <t xml:space="preserve">33.7714767456055</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8291244506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5689239501953</t>
+    <t xml:space="preserve">33.8291206359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.568920135498</t>
   </si>
   <si>
     <t xml:space="preserve">35.2510795593262</t>
@@ -3743,43 +3743,43 @@
     <t xml:space="preserve">35.9332313537598</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9420509338379</t>
+    <t xml:space="preserve">36.9420547485352</t>
   </si>
   <si>
     <t xml:space="preserve">36.4712715148926</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4520568847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1253890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7802963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.588924407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6449966430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7042236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4344139099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1357841491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9244155883789</t>
+    <t xml:space="preserve">36.4520530700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1253852844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7803001403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5889282226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6450004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7042198181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4344100952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1357803344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9244117736816</t>
   </si>
   <si>
     <t xml:space="preserve">36.2695083618164</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3175468444824</t>
+    <t xml:space="preserve">36.3175430297852</t>
   </si>
   <si>
     <t xml:space="preserve">35.981273651123</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">35.0973510742188</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7602958679199</t>
+    <t xml:space="preserve">35.7602920532227</t>
   </si>
   <si>
     <t xml:space="preserve">36.211856842041</t>
@@ -3803,13 +3803,13 @@
     <t xml:space="preserve">39.0173416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9500885009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2375373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2943954467773</t>
+    <t xml:space="preserve">38.9500923156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2375335693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2943916320801</t>
   </si>
   <si>
     <t xml:space="preserve">40.890869140625</t>
@@ -3821,10 +3821,10 @@
     <t xml:space="preserve">39.8340072631836</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6330261230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4208679199219</t>
+    <t xml:space="preserve">38.6330299377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4208717346191</t>
   </si>
   <si>
     <t xml:space="preserve">39.219108581543</t>
@@ -3839,31 +3839,31 @@
     <t xml:space="preserve">36.8075485229492</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6442108154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3367614746094</t>
+    <t xml:space="preserve">36.644214630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3367652893066</t>
   </si>
   <si>
     <t xml:space="preserve">35.4528427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2502899169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7210731506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1349983215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7218589782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3183364868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0693168640137</t>
+    <t xml:space="preserve">36.2502937316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.721076965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1350021362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7218627929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3183288574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0693130493164</t>
   </si>
   <si>
     <t xml:space="preserve">32.2726554870605</t>
@@ -3872,31 +3872,31 @@
     <t xml:space="preserve">32.9836349487305</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9740295410156</t>
+    <t xml:space="preserve">32.9740257263184</t>
   </si>
   <si>
     <t xml:space="preserve">31.0524616241455</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9067726135254</t>
+    <t xml:space="preserve">32.9067687988281</t>
   </si>
   <si>
     <t xml:space="preserve">32.9163780212402</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9644203186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2734413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3414859771729</t>
+    <t xml:space="preserve">32.9644165039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2734432220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3414840698242</t>
   </si>
   <si>
     <t xml:space="preserve">30.6777591705322</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2105255126953</t>
+    <t xml:space="preserve">31.2105274200439</t>
   </si>
   <si>
     <t xml:space="preserve">31.0071048736572</t>
@@ -3905,13 +3905,13 @@
     <t xml:space="preserve">30.9489860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2492733001709</t>
+    <t xml:space="preserve">31.2492713928223</t>
   </si>
   <si>
     <t xml:space="preserve">31.3558235168457</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6948623657227</t>
+    <t xml:space="preserve">31.694860458374</t>
   </si>
   <si>
     <t xml:space="preserve">31.0555400848389</t>
@@ -3923,13 +3923,13 @@
     <t xml:space="preserve">30.0965557098389</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6099529266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3484115600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4646530151367</t>
+    <t xml:space="preserve">30.6099510192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.34840965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4646511077881</t>
   </si>
   <si>
     <t xml:space="preserve">29.7865810394287</t>
@@ -3938,16 +3938,16 @@
     <t xml:space="preserve">28.2948322296143</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2606258392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5438137054443</t>
+    <t xml:space="preserve">26.260627746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5438117980957</t>
   </si>
   <si>
     <t xml:space="preserve">26.3090591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3985118865967</t>
+    <t xml:space="preserve">25.398509979248</t>
   </si>
   <si>
     <t xml:space="preserve">25.4760036468506</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">25.5341243743896</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8828430175781</t>
+    <t xml:space="preserve">25.8828449249268</t>
   </si>
   <si>
     <t xml:space="preserve">27.9364242553711</t>
@@ -3968,19 +3968,19 @@
     <t xml:space="preserve">28.8663463592529</t>
   </si>
   <si>
-    <t xml:space="preserve">28.934154510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3529529571533</t>
+    <t xml:space="preserve">28.9341564178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3529510498047</t>
   </si>
   <si>
     <t xml:space="preserve">28.2560863494873</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3335781097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4378604888916</t>
+    <t xml:space="preserve">28.3335800170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4378623962402</t>
   </si>
   <si>
     <t xml:space="preserve">29.9900035858154</t>
@@ -4004,16 +4004,16 @@
     <t xml:space="preserve">28.2173366546631</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7523784637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3238925933838</t>
+    <t xml:space="preserve">27.7523746490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3238906860352</t>
   </si>
   <si>
     <t xml:space="preserve">28.924467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8469734191895</t>
+    <t xml:space="preserve">28.8469753265381</t>
   </si>
   <si>
     <t xml:space="preserve">29.6994037628174</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">30.1837368011475</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6412811279297</t>
+    <t xml:space="preserve">29.6412830352783</t>
   </si>
   <si>
     <t xml:space="preserve">29.4766082763672</t>
@@ -4037,25 +4037,25 @@
     <t xml:space="preserve">31.2008399963379</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4236354827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.970630645752</t>
+    <t xml:space="preserve">31.4236335754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9706287384033</t>
   </si>
   <si>
     <t xml:space="preserve">30.8714923858643</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0942859649658</t>
+    <t xml:space="preserve">31.0942840576172</t>
   </si>
   <si>
     <t xml:space="preserve">29.4281749725342</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7381477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9922752380371</t>
+    <t xml:space="preserve">29.738151550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9922733306885</t>
   </si>
   <si>
     <t xml:space="preserve">29.4572353363037</t>
@@ -4064,13 +4064,13 @@
     <t xml:space="preserve">29.7672100067139</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1979656219482</t>
+    <t xml:space="preserve">28.1979675292969</t>
   </si>
   <si>
     <t xml:space="preserve">27.8879909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8104953765869</t>
+    <t xml:space="preserve">27.8104972839355</t>
   </si>
   <si>
     <t xml:space="preserve">27.442403793335</t>
@@ -4094,13 +4094,13 @@
     <t xml:space="preserve">24.962610244751</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2338371276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6816959381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0885372161865</t>
+    <t xml:space="preserve">25.2338352203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6816940307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0885353088379</t>
   </si>
   <si>
     <t xml:space="preserve">25.0497894287109</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">25.10791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2144622802734</t>
+    <t xml:space="preserve">25.2144641876221</t>
   </si>
   <si>
     <t xml:space="preserve">24.5073337554932</t>
@@ -4124,37 +4124,37 @@
     <t xml:space="preserve">24.2554817199707</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1779861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8970737457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4201545715332</t>
+    <t xml:space="preserve">24.1779880523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8970718383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4201526641846</t>
   </si>
   <si>
     <t xml:space="preserve">23.8292675018311</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0908069610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.013313293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1973609924316</t>
+    <t xml:space="preserve">24.0908088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0133152008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.197359085083</t>
   </si>
   <si>
     <t xml:space="preserve">24.8463687896729</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8053512573242</t>
+    <t xml:space="preserve">25.8053493499756</t>
   </si>
   <si>
     <t xml:space="preserve">25.291955947876</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0572071075439</t>
+    <t xml:space="preserve">26.0572032928467</t>
   </si>
   <si>
     <t xml:space="preserve">25.5728702545166</t>
@@ -4169,34 +4169,34 @@
     <t xml:space="preserve">25.9312782287598</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6309909820557</t>
+    <t xml:space="preserve">25.630989074707</t>
   </si>
   <si>
     <t xml:space="preserve">25.3307037353516</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6235733032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8389530181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9187183380127</t>
+    <t xml:space="preserve">24.6235752105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8389549255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9187164306641</t>
   </si>
   <si>
     <t xml:space="preserve">23.916446685791</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4395275115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3500785827637</t>
+    <t xml:space="preserve">24.4395294189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.350076675415</t>
   </si>
   <si>
     <t xml:space="preserve">24.8366813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0475177764893</t>
+    <t xml:space="preserve">26.0475196838379</t>
   </si>
   <si>
     <t xml:space="preserve">25.3694515228271</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">23.7517738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">23.906759262085</t>
+    <t xml:space="preserve">23.9067611694336</t>
   </si>
   <si>
     <t xml:space="preserve">24.3523483276367</t>
@@ -4238,49 +4238,49 @@
     <t xml:space="preserve">27.2680416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1398448944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6748828887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7426891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7062149047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.764331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5221672058105</t>
+    <t xml:space="preserve">28.1398429870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6748809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7426910400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7062129974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7643337249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5221652984619</t>
   </si>
   <si>
     <t xml:space="preserve">26.3187465667725</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8321399688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8805732727051</t>
+    <t xml:space="preserve">26.8321418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8805751800537</t>
   </si>
   <si>
     <t xml:space="preserve">27.0065002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1421146392822</t>
+    <t xml:space="preserve">27.1421165466309</t>
   </si>
   <si>
     <t xml:space="preserve">26.0087738037109</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7837085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6458225250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9483833312988</t>
+    <t xml:space="preserve">26.7837066650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.645824432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9483814239502</t>
   </si>
   <si>
     <t xml:space="preserve">26.1540718078613</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">26.6771545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6965274810791</t>
+    <t xml:space="preserve">26.6965255737305</t>
   </si>
   <si>
     <t xml:space="preserve">27.0936813354492</t>
@@ -4301,43 +4301,43 @@
     <t xml:space="preserve">27.6651954650879</t>
   </si>
   <si>
-    <t xml:space="preserve">27.975170135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.444673538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0959510803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0668926239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8925323486328</t>
+    <t xml:space="preserve">27.9751682281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4446716308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0959529876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0668907165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8925304412842</t>
   </si>
   <si>
     <t xml:space="preserve">26.4543590545654</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8344097137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9700260162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6287212371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8708896636963</t>
+    <t xml:space="preserve">25.8344116210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9700241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.628719329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8708877563477</t>
   </si>
   <si>
     <t xml:space="preserve">26.1443843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2509384155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9677562713623</t>
+    <t xml:space="preserve">26.250940322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9677543640137</t>
   </si>
   <si>
     <t xml:space="preserve">25.9797115325928</t>
@@ -4349,16 +4349,16 @@
     <t xml:space="preserve">26.5996608734131</t>
   </si>
   <si>
-    <t xml:space="preserve">26.63840675354</t>
+    <t xml:space="preserve">26.6384086608887</t>
   </si>
   <si>
     <t xml:space="preserve">26.2412528991699</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6019306182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9044876098633</t>
+    <t xml:space="preserve">25.6019325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9044895172119</t>
   </si>
   <si>
     <t xml:space="preserve">25.0788497924805</t>
@@ -4367,19 +4367,19 @@
     <t xml:space="preserve">24.8851165771484</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9916687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9335498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7398147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4782733917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6070785522461</t>
+    <t xml:space="preserve">24.9916706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9335479736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7398166656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4782772064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6070766448975</t>
   </si>
   <si>
     <t xml:space="preserve">26.9290065765381</t>
@@ -4388,7 +4388,7 @@
     <t xml:space="preserve">27.1227416992188</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7666053771973</t>
+    <t xml:space="preserve">25.7666034698486</t>
   </si>
   <si>
     <t xml:space="preserve">26.483419418335</t>
@@ -4400,22 +4400,22 @@
     <t xml:space="preserve">26.541540145874</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2025051116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6190319061279</t>
+    <t xml:space="preserve">26.202507019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6190338134766</t>
   </si>
   <si>
     <t xml:space="preserve">26.5027942657471</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3358497619629</t>
+    <t xml:space="preserve">27.3358478546143</t>
   </si>
   <si>
     <t xml:space="preserve">29.1763210296631</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5466842651367</t>
+    <t xml:space="preserve">28.5466861724854</t>
   </si>
   <si>
     <t xml:space="preserve">28.4401321411133</t>
@@ -4427,10 +4427,10 @@
     <t xml:space="preserve">28.2367095947266</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1107845306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0310211181641</t>
+    <t xml:space="preserve">28.1107864379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0310192108154</t>
   </si>
   <si>
     <t xml:space="preserve">28.4304447174072</t>
@@ -4439,31 +4439,31 @@
     <t xml:space="preserve">28.8954067230225</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1860084533691</t>
+    <t xml:space="preserve">29.1860065460205</t>
   </si>
   <si>
     <t xml:space="preserve">29.6606559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6583862304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9392986297607</t>
+    <t xml:space="preserve">30.6583843231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9393005371094</t>
   </si>
   <si>
     <t xml:space="preserve">30.8327445983887</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2589588165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4817543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6173667907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5689353942871</t>
+    <t xml:space="preserve">31.258960723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4817523956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6173648834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5689315795898</t>
   </si>
   <si>
     <t xml:space="preserve">32.1404495239258</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">31.6754875183105</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2783336639404</t>
+    <t xml:space="preserve">31.2783355712891</t>
   </si>
   <si>
     <t xml:space="preserve">31.9176559448242</t>
@@ -4481,10 +4481,10 @@
     <t xml:space="preserve">31.9854621887207</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7820415496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3729286193848</t>
+    <t xml:space="preserve">31.7820453643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3729248046875</t>
   </si>
   <si>
     <t xml:space="preserve">32.508544921875</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">32.3341865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7313423156738</t>
+    <t xml:space="preserve">32.7313385009766</t>
   </si>
   <si>
     <t xml:space="preserve">32.2373161315918</t>
@@ -4505,28 +4505,28 @@
     <t xml:space="preserve">32.0823287963867</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3780746459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7678146362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7655410766602</t>
+    <t xml:space="preserve">34.3780784606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7678184509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7655448913574</t>
   </si>
   <si>
     <t xml:space="preserve">34.7267951965332</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3296432495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2134017944336</t>
+    <t xml:space="preserve">34.3296394348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2134056091309</t>
   </si>
   <si>
     <t xml:space="preserve">34.6686782836914</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8817825317383</t>
+    <t xml:space="preserve">34.881778717041</t>
   </si>
   <si>
     <t xml:space="preserve">34.6105537414551</t>
@@ -4541,19 +4541,19 @@
     <t xml:space="preserve">32.8475761413574</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1478691101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.167407989502</t>
+    <t xml:space="preserve">33.1478652954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1674041748047</t>
   </si>
   <si>
     <t xml:space="preserve">32.297924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0536842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4577445983887</t>
+    <t xml:space="preserve">32.0536880493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4577465057373</t>
   </si>
   <si>
     <t xml:space="preserve">32.2393035888672</t>
@@ -4565,22 +4565,22 @@
     <t xml:space="preserve">32.1513786315918</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5359020233154</t>
+    <t xml:space="preserve">31.5359001159668</t>
   </si>
   <si>
     <t xml:space="preserve">31.6238231658936</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6789321899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9489631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2908935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0466537475586</t>
+    <t xml:space="preserve">32.6789283752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9489669799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2908973693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0466575622559</t>
   </si>
   <si>
     <t xml:space="preserve">34.1638946533203</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">34.6816749572754</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4179000854492</t>
+    <t xml:space="preserve">34.417896270752</t>
   </si>
   <si>
     <t xml:space="preserve">34.2225074768066</t>
@@ -4604,7 +4604,7 @@
     <t xml:space="preserve">33.7438049316406</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6656455993652</t>
+    <t xml:space="preserve">33.6656494140625</t>
   </si>
   <si>
     <t xml:space="preserve">33.216251373291</t>
@@ -4625,10 +4625,10 @@
     <t xml:space="preserve">32.4835395812988</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9853000640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.887601852417</t>
+    <t xml:space="preserve">31.9852981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8875999450684</t>
   </si>
   <si>
     <t xml:space="preserve">30.0997867584229</t>
@@ -4655,19 +4655,19 @@
     <t xml:space="preserve">31.1451206207275</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0474262237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3440246582031</t>
+    <t xml:space="preserve">31.0474281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3440227508545</t>
   </si>
   <si>
     <t xml:space="preserve">30.2560977935791</t>
   </si>
   <si>
-    <t xml:space="preserve">30.363561630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.451488494873</t>
+    <t xml:space="preserve">30.3635635375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4514865875244</t>
   </si>
   <si>
     <t xml:space="preserve">30.9204235076904</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">30.8520374298096</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7152652740479</t>
+    <t xml:space="preserve">30.7152633666992</t>
   </si>
   <si>
     <t xml:space="preserve">30.0802478790283</t>
@@ -4700,16 +4700,16 @@
     <t xml:space="preserve">29.2009925842285</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6406192779541</t>
+    <t xml:space="preserve">29.6406211853027</t>
   </si>
   <si>
     <t xml:space="preserve">29.3182277679443</t>
   </si>
   <si>
-    <t xml:space="preserve">29.415922164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0739898681641</t>
+    <t xml:space="preserve">29.4159240722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0739917755127</t>
   </si>
   <si>
     <t xml:space="preserve">28.5562057495117</t>
@@ -4721,7 +4721,7 @@
     <t xml:space="preserve">29.0935287475586</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2889194488525</t>
+    <t xml:space="preserve">29.2889175415039</t>
   </si>
   <si>
     <t xml:space="preserve">29.1814556121826</t>
@@ -4733,10 +4733,10 @@
     <t xml:space="preserve">29.7578544616699</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5722332000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3475360870361</t>
+    <t xml:space="preserve">29.5722351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3475379943848</t>
   </si>
   <si>
     <t xml:space="preserve">28.800443649292</t>
@@ -4760,19 +4760,19 @@
     <t xml:space="preserve">28.2240447998047</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3217391967773</t>
+    <t xml:space="preserve">28.321741104126</t>
   </si>
   <si>
     <t xml:space="preserve">28.5952854156494</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3119716644287</t>
+    <t xml:space="preserve">28.3119697570801</t>
   </si>
   <si>
     <t xml:space="preserve">27.9309597015381</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0677337646484</t>
+    <t xml:space="preserve">28.0677318572998</t>
   </si>
   <si>
     <t xml:space="preserve">29.650390625</t>
@@ -4814,13 +4814,13 @@
     <t xml:space="preserve">26.6706962585449</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5143852233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0028591156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1005554199219</t>
+    <t xml:space="preserve">26.51438331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.002857208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1005535125732</t>
   </si>
   <si>
     <t xml:space="preserve">27.4620246887207</t>
@@ -4829,7 +4829,7 @@
     <t xml:space="preserve">26.709774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2799186706543</t>
+    <t xml:space="preserve">26.2799167633057</t>
   </si>
   <si>
     <t xml:space="preserve">26.4557685852051</t>
@@ -4838,13 +4838,13 @@
     <t xml:space="preserve">26.6120796203613</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4362297058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6511573791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6609287261963</t>
+    <t xml:space="preserve">26.4362277984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.651159286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6609268188477</t>
   </si>
   <si>
     <t xml:space="preserve">26.2213001251221</t>
@@ -4853,31 +4853,31 @@
     <t xml:space="preserve">25.1661968231201</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7949562072754</t>
+    <t xml:space="preserve">24.7949542999268</t>
   </si>
   <si>
     <t xml:space="preserve">26.0259094238281</t>
   </si>
   <si>
-    <t xml:space="preserve">25.889139175415</t>
+    <t xml:space="preserve">25.8891372680664</t>
   </si>
   <si>
     <t xml:space="preserve">26.8953952789307</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0614757537842</t>
+    <t xml:space="preserve">27.0614776611328</t>
   </si>
   <si>
     <t xml:space="preserve">27.1200923919678</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9344730377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9149322509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.475305557251</t>
+    <t xml:space="preserve">26.9344711303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9149341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4753074645996</t>
   </si>
   <si>
     <t xml:space="preserve">26.3385334014893</t>
@@ -4886,13 +4886,13 @@
     <t xml:space="preserve">27.5890274047852</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7683906555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3776111602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8856258392334</t>
+    <t xml:space="preserve">26.7683925628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.377613067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8856239318848</t>
   </si>
   <si>
     <t xml:space="preserve">27.5206432342529</t>
@@ -4907,25 +4907,25 @@
     <t xml:space="preserve">27.6085662841797</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7648773193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9505004882812</t>
+    <t xml:space="preserve">27.7648792266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9504985809326</t>
   </si>
   <si>
     <t xml:space="preserve">27.5499515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8723449707031</t>
+    <t xml:space="preserve">27.8723430633545</t>
   </si>
   <si>
     <t xml:space="preserve">27.3154811859131</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0517082214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9735527038574</t>
+    <t xml:space="preserve">27.0517063140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9735507965088</t>
   </si>
   <si>
     <t xml:space="preserve">28.0775032043457</t>
@@ -4958,7 +4958,7 @@
     <t xml:space="preserve">30.6175689697266</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5296440124512</t>
+    <t xml:space="preserve">30.5296421051025</t>
   </si>
   <si>
     <t xml:space="preserve">29.796932220459</t>
@@ -4970,7 +4970,7 @@
     <t xml:space="preserve">30.8715763092041</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6761856079102</t>
+    <t xml:space="preserve">30.6761837005615</t>
   </si>
   <si>
     <t xml:space="preserve">30.8911151885986</t>
@@ -4997,7 +4997,7 @@
     <t xml:space="preserve">29.1912231445312</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1619167327881</t>
+    <t xml:space="preserve">29.1619148254395</t>
   </si>
   <si>
     <t xml:space="preserve">29.9337043762207</t>
@@ -5015,10 +5015,10 @@
     <t xml:space="preserve">29.0544509887695</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4612560272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.510103225708</t>
+    <t xml:space="preserve">30.4612579345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5101051330566</t>
   </si>
   <si>
     <t xml:space="preserve">30.7738800048828</t>
@@ -5030,13 +5030,13 @@
     <t xml:space="preserve">30.1584033966064</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4221801757812</t>
+    <t xml:space="preserve">30.4221782684326</t>
   </si>
   <si>
     <t xml:space="preserve">30.8813457489014</t>
   </si>
   <si>
-    <t xml:space="preserve">31.125581741333</t>
+    <t xml:space="preserve">31.1255836486816</t>
   </si>
   <si>
     <t xml:space="preserve">30.744571685791</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">30.2658672332764</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0439147949219</t>
+    <t xml:space="preserve">32.0439109802246</t>
   </si>
   <si>
     <t xml:space="preserve">32.893856048584</t>
@@ -5078,7 +5078,7 @@
     <t xml:space="preserve">32.2002258300781</t>
   </si>
   <si>
-    <t xml:space="preserve">33.030632019043</t>
+    <t xml:space="preserve">33.0306358337402</t>
   </si>
   <si>
     <t xml:space="preserve">32.8547821044922</t>
@@ -5090,7 +5090,7 @@
     <t xml:space="preserve">31.6433639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9888095855713</t>
+    <t xml:space="preserve">30.9888076782227</t>
   </si>
   <si>
     <t xml:space="preserve">31.2916622161865</t>
@@ -5099,16 +5099,16 @@
     <t xml:space="preserve">31.1158142089844</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3858489990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2357940673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2650985717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0208625793457</t>
+    <t xml:space="preserve">32.3858451843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2357902526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2651023864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0208587646484</t>
   </si>
   <si>
     <t xml:space="preserve">32.4933090209961</t>
@@ -5123,7 +5123,7 @@
     <t xml:space="preserve">31.1646614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7605991363525</t>
+    <t xml:space="preserve">31.7605953216553</t>
   </si>
   <si>
     <t xml:space="preserve">30.1290950775146</t>
@@ -5132,10 +5132,10 @@
     <t xml:space="preserve">30.4026412963867</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1193237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8422679901123</t>
+    <t xml:space="preserve">30.1193256378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8422660827637</t>
   </si>
   <si>
     <t xml:space="preserve">31.2818927764893</t>
@@ -5147,16 +5147,16 @@
     <t xml:space="preserve">30.3049449920654</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7836494445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.705493927002</t>
+    <t xml:space="preserve">30.7836513519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7054958343506</t>
   </si>
   <si>
     <t xml:space="preserve">30.8227272033691</t>
   </si>
   <si>
-    <t xml:space="preserve">33.069709777832</t>
+    <t xml:space="preserve">33.0697059631348</t>
   </si>
   <si>
     <t xml:space="preserve">32.591007232666</t>
@@ -5180,7 +5180,7 @@
     <t xml:space="preserve">33.5972595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5679512023926</t>
+    <t xml:space="preserve">33.5679550170898</t>
   </si>
   <si>
     <t xml:space="preserve">34.0310287475586</t>
@@ -6198,6 +6198,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.539999961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2399997711182</t>
   </si>
 </sst>
 </file>
@@ -71640,25 +71643,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6911458333</v>
+        <v>45967.6914930556</v>
       </c>
       <c r="B2505" t="n">
-        <v>1196470</v>
+        <v>1506201</v>
       </c>
       <c r="C2505" t="n">
-        <v>14.8649997711182</v>
+        <v>14.6350002288818</v>
       </c>
       <c r="D2505" t="n">
-        <v>14.3950004577637</v>
+        <v>14.1949996948242</v>
       </c>
       <c r="E2505" t="n">
-        <v>14.4700002670288</v>
+        <v>14.5299997329712</v>
       </c>
       <c r="F2505" t="n">
-        <v>14.6400003433228</v>
+        <v>14.2399997711182</v>
       </c>
       <c r="G2505" t="s">
-        <v>2030</v>
+        <v>2062</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="2065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2066" uniqueCount="2066">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,52 +38,52 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33520555496216</t>
+    <t xml:space="preserve">7.33520603179932</t>
   </si>
   <si>
     <t xml:space="preserve">AMP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39109230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31191778182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36780548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15357160568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96262264251709</t>
+    <t xml:space="preserve">7.39109182357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31191825866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36780595779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15357112884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96262311935425</t>
   </si>
   <si>
     <t xml:space="preserve">7.21877288818359</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27931785583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16288661956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0324821472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08836889266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1954870223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98590993881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13494253158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34451961517334</t>
+    <t xml:space="preserve">7.2793173789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16288566589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03248262405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08836936950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19548606872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9859094619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13494157791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34452104568481</t>
   </si>
   <si>
     <t xml:space="preserve">7.23740243911743</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">7.35383415222168</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14891481399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18151473999023</t>
+    <t xml:space="preserve">7.1489143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18151426315308</t>
   </si>
   <si>
     <t xml:space="preserve">7.40972089767456</t>
@@ -104,34 +104,34 @@
     <t xml:space="preserve">7.28397464752197</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13959932327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05111169815063</t>
+    <t xml:space="preserve">7.13959980010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05111122131348</t>
   </si>
   <si>
     <t xml:space="preserve">6.84619092941284</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51086807250977</t>
+    <t xml:space="preserve">6.51086759567261</t>
   </si>
   <si>
     <t xml:space="preserve">6.45498037338257</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59004068374634</t>
+    <t xml:space="preserve">6.5900411605835</t>
   </si>
   <si>
     <t xml:space="preserve">6.33389186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29197597503662</t>
+    <t xml:space="preserve">6.29197645187378</t>
   </si>
   <si>
     <t xml:space="preserve">6.42237949371338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61798477172852</t>
+    <t xml:space="preserve">6.61798524856567</t>
   </si>
   <si>
     <t xml:space="preserve">6.8834490776062</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">6.70181608200073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6272988319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9952244758606</t>
+    <t xml:space="preserve">6.62729930877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99522495269775</t>
   </si>
   <si>
     <t xml:space="preserve">6.8927640914917</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">6.80427551269531</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79961824417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84153413772583</t>
+    <t xml:space="preserve">6.7996187210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84153366088867</t>
   </si>
   <si>
     <t xml:space="preserve">6.6599006652832</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">6.78564643859863</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86016225814819</t>
+    <t xml:space="preserve">6.86016273498535</t>
   </si>
   <si>
     <t xml:space="preserve">7.00919580459595</t>
@@ -185,28 +185,28 @@
     <t xml:space="preserve">7.11165571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08371162414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20945882797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10699892044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04179668426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24205923080444</t>
+    <t xml:space="preserve">7.08371210098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20945835113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10699844360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04179763793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24206018447876</t>
   </si>
   <si>
     <t xml:space="preserve">7.09768390655518</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17220020294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93467950820923</t>
+    <t xml:space="preserve">7.17220067977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93467903137207</t>
   </si>
   <si>
     <t xml:space="preserve">6.91604995727539</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">7.32589054107666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22808790206909</t>
+    <t xml:space="preserve">7.22808742523193</t>
   </si>
   <si>
     <t xml:space="preserve">7.50286722183228</t>
@@ -230,61 +230,61 @@
     <t xml:space="preserve">7.41437768936157</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48423719406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57738399505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55409574508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73107242584229</t>
+    <t xml:space="preserve">7.48423671722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57738351821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5540976524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73107290267944</t>
   </si>
   <si>
     <t xml:space="preserve">7.60066938400269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64258432388306</t>
+    <t xml:space="preserve">7.64258480072021</t>
   </si>
   <si>
     <t xml:space="preserve">7.70312976837158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73573017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88476228713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88942098617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87079000473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78696012496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94530820846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88010406494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08968257904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01760482788086</t>
+    <t xml:space="preserve">7.73572969436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88476371765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88942050933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8707914352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78696060180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94530773162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88010597229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08968448638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01760387420654</t>
   </si>
   <si>
     <t xml:space="preserve">8.09717178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10653400421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.050368309021</t>
+    <t xml:space="preserve">8.10653209686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05036735534668</t>
   </si>
   <si>
     <t xml:space="preserve">8.17205810546875</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">8.23758506774902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22354602813721</t>
+    <t xml:space="preserve">8.22354412078857</t>
   </si>
   <si>
     <t xml:space="preserve">8.1580171585083</t>
@@ -308,37 +308,37 @@
     <t xml:space="preserve">8.0831298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14397525787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01292419433594</t>
+    <t xml:space="preserve">8.14397621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01292514801025</t>
   </si>
   <si>
     <t xml:space="preserve">7.91463422775269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82102632522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64316892623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62912607192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65253019332886</t>
+    <t xml:space="preserve">7.82102537155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6431679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62912750244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6525297164917</t>
   </si>
   <si>
     <t xml:space="preserve">7.55892038345337</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63848924636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98952198028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94739723205566</t>
+    <t xml:space="preserve">7.63848829269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98952150344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94739627838135</t>
   </si>
   <si>
     <t xml:space="preserve">8.05972766876221</t>
@@ -347,31 +347,31 @@
     <t xml:space="preserve">7.67593145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71337509155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72273683547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87250900268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92867708206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89123296737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8116660118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71805572509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88187122344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96143913269043</t>
+    <t xml:space="preserve">7.71337413787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72273540496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87250995635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92867612838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89123249053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81166410446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7180552482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88187170028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9614372253418</t>
   </si>
   <si>
     <t xml:space="preserve">7.91931486129761</t>
@@ -380,97 +380,97 @@
     <t xml:space="preserve">7.90995407104492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05504703521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18141937255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16737937927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19546031951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19078063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3077917098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36395740509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34991550445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33119487762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29375076293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15333557128906</t>
+    <t xml:space="preserve">8.0550479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18141841888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16737651824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19546222686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19078159332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30779266357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36395645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34991645812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33119201660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29374885559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15333652496338</t>
   </si>
   <si>
     <t xml:space="preserve">8.28906917572021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36863613128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50905227661133</t>
+    <t xml:space="preserve">8.36863708496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50905132293701</t>
   </si>
   <si>
     <t xml:space="preserve">8.60733985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51373291015625</t>
+    <t xml:space="preserve">8.51373195648193</t>
   </si>
   <si>
     <t xml:space="preserve">8.63542366027832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75711345672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65414428710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78519725799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80860042572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92093086242676</t>
+    <t xml:space="preserve">8.75711536407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65414619445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78519821166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80859851837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92092990875244</t>
   </si>
   <si>
     <t xml:space="preserve">8.84604358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81796073913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74775314331055</t>
+    <t xml:space="preserve">8.81796169281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74775409698486</t>
   </si>
   <si>
     <t xml:space="preserve">8.75243473052979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82264232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7337121963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77115535736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.761794090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65882587432861</t>
+    <t xml:space="preserve">8.82264137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73371124267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77115726470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76179599761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6588249206543</t>
   </si>
   <si>
     <t xml:space="preserve">8.59329986572266</t>
@@ -479,40 +479,40 @@
     <t xml:space="preserve">8.57457733154297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56053733825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4856481552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54181289672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5324535369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66818618774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49969100952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61670207977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49500846862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55585670471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61202144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46692657470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52777290344238</t>
+    <t xml:space="preserve">8.56053638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48564910888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54181385040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53245258331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66818714141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49969005584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61670112609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49500942230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5558557510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61202239990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46692848205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52777194976807</t>
   </si>
   <si>
     <t xml:space="preserve">8.56521606445312</t>
@@ -521,127 +521,127 @@
     <t xml:space="preserve">8.69158840179443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0800666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24856185913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07070446014404</t>
+    <t xml:space="preserve">9.08006477355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24856090545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07070350646973</t>
   </si>
   <si>
     <t xml:space="preserve">9.01453876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89284801483154</t>
+    <t xml:space="preserve">8.89284896850586</t>
   </si>
   <si>
     <t xml:space="preserve">8.93965148925781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81328201293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50437164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42480278015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40140056610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39672183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58393955230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34523582458496</t>
+    <t xml:space="preserve">8.81328010559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50436973571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42480373382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40140151977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39672088623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5839376449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34523391723633</t>
   </si>
   <si>
     <t xml:space="preserve">8.46224594116211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3826789855957</t>
+    <t xml:space="preserve">8.38267993927002</t>
   </si>
   <si>
     <t xml:space="preserve">8.47160720825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98645687103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09878826141357</t>
+    <t xml:space="preserve">8.9864559173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09878635406494</t>
   </si>
   <si>
     <t xml:space="preserve">9.0613431930542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51841259002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16269683837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31247234344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44190979003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98484086990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95675897598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38736057281494</t>
+    <t xml:space="preserve">8.51841163635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16269779205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31247138977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4419093132019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98483991622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95675802230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38735961914062</t>
   </si>
   <si>
     <t xml:space="preserve">8.41076183319092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44820404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4809684753418</t>
+    <t xml:space="preserve">8.44820499420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48096942901611</t>
   </si>
   <si>
     <t xml:space="preserve">8.37331771850586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23290538787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1860990524292</t>
+    <t xml:space="preserve">8.2329044342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18610095977783</t>
   </si>
   <si>
     <t xml:space="preserve">8.37799835205078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57925796508789</t>
+    <t xml:space="preserve">8.57925891876221</t>
   </si>
   <si>
     <t xml:space="preserve">8.64946365356445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72435188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67286682128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74307346343994</t>
+    <t xml:space="preserve">8.72435092926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6728687286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74307250976562</t>
   </si>
   <si>
     <t xml:space="preserve">8.71031093597412</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15495300292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96773433685303</t>
+    <t xml:space="preserve">9.15495204925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96773529052734</t>
   </si>
   <si>
     <t xml:space="preserve">9.14091110229492</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">9.26728248596191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33749008178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40769863128662</t>
+    <t xml:space="preserve">9.33748912811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40769672393799</t>
   </si>
   <si>
     <t xml:space="preserve">9.37961483001709</t>
@@ -665,19 +665,19 @@
     <t xml:space="preserve">9.3608922958374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44513988494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48258399963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4357795715332</t>
+    <t xml:space="preserve">9.44514083862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48258304595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43577861785889</t>
   </si>
   <si>
     <t xml:space="preserve">9.35621166229248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11282825469971</t>
+    <t xml:space="preserve">9.11282730102539</t>
   </si>
   <si>
     <t xml:space="preserve">9.10814762115479</t>
@@ -689,28 +689,28 @@
     <t xml:space="preserve">9.46386241912842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81021404266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95998954772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82893657684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91318511962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64171886444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70724582672119</t>
+    <t xml:space="preserve">9.81021499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95999050140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82893753051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91318607330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64171981811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70724487304688</t>
   </si>
   <si>
     <t xml:space="preserve">9.71660614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66044139862061</t>
+    <t xml:space="preserve">9.66044044494629</t>
   </si>
   <si>
     <t xml:space="preserve">9.79149341583252</t>
@@ -719,49 +719,49 @@
     <t xml:space="preserve">10.0255155563354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0067949295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1846494674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.240816116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.259539604187</t>
+    <t xml:space="preserve">10.0067939758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1846504211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2408142089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2595376968384</t>
   </si>
   <si>
     <t xml:space="preserve">10.4280338287354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4748382568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3625078201294</t>
+    <t xml:space="preserve">10.4748373031616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3625087738037</t>
   </si>
   <si>
     <t xml:space="preserve">10.3344249725342</t>
   </si>
   <si>
-    <t xml:space="preserve">10.577808380127</t>
+    <t xml:space="preserve">10.5778074264526</t>
   </si>
   <si>
     <t xml:space="preserve">10.5122814178467</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5029201507568</t>
+    <t xml:space="preserve">10.5029211044312</t>
   </si>
   <si>
     <t xml:space="preserve">10.8118314743042</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8867197036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7182216644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6526956558228</t>
+    <t xml:space="preserve">10.8867177963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7182207107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6526947021484</t>
   </si>
   <si>
     <t xml:space="preserve">10.6433343887329</t>
@@ -770,16 +770,16 @@
     <t xml:space="preserve">10.6246128082275</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7088613510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8960790634155</t>
+    <t xml:space="preserve">10.7088603973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8960800170898</t>
   </si>
   <si>
     <t xml:space="preserve">10.8399124145508</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9335231781006</t>
+    <t xml:space="preserve">10.9335241317749</t>
   </si>
   <si>
     <t xml:space="preserve">10.9990482330322</t>
@@ -788,94 +788,94 @@
     <t xml:space="preserve">11.1301002502441</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0926580429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2517919540405</t>
+    <t xml:space="preserve">11.0926570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2517910003662</t>
   </si>
   <si>
     <t xml:space="preserve">10.9616050720215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2049884796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1675462722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1488218307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1862659454346</t>
+    <t xml:space="preserve">11.2049875259399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1675443649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1488227844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1862649917603</t>
   </si>
   <si>
     <t xml:space="preserve">11.2798757553101</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4296493530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.410927772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4577331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5801248550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8249073028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8625659942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9472970962524</t>
+    <t xml:space="preserve">11.4296503067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4109268188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4577312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5801239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8249082565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8625650405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9472961425781</t>
   </si>
   <si>
     <t xml:space="preserve">11.9190540313721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9284696578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9378833770752</t>
+    <t xml:space="preserve">11.9284687042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9378843307495</t>
   </si>
   <si>
     <t xml:space="preserve">11.9661283493042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0602750778198</t>
+    <t xml:space="preserve">12.0602741241455</t>
   </si>
   <si>
     <t xml:space="preserve">12.0979347229004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0226163864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2109127044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1826658248901</t>
+    <t xml:space="preserve">12.0226173400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2109098434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1826667785645</t>
   </si>
   <si>
     <t xml:space="preserve">12.2391557693481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9096374511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1450080871582</t>
+    <t xml:space="preserve">11.9096393585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1450071334839</t>
   </si>
   <si>
     <t xml:space="preserve">11.4859762191772</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2976818084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6931009292603</t>
+    <t xml:space="preserve">11.2976808547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6930999755859</t>
   </si>
   <si>
     <t xml:space="preserve">11.7307596206665</t>
@@ -884,19 +884,19 @@
     <t xml:space="preserve">11.7684183120728</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7590036392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.627197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5707092285156</t>
+    <t xml:space="preserve">11.7590045928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6271991729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5707101821899</t>
   </si>
   <si>
     <t xml:space="preserve">11.5236349105835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4671468734741</t>
+    <t xml:space="preserve">11.4671459197998</t>
   </si>
   <si>
     <t xml:space="preserve">11.3729991912842</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">11.0811424255371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834352493286</t>
+    <t xml:space="preserve">10.8834342956543</t>
   </si>
   <si>
     <t xml:space="preserve">10.6951379776001</t>
@@ -920,61 +920,61 @@
     <t xml:space="preserve">10.7422113418579</t>
   </si>
   <si>
-    <t xml:space="preserve">10.911678314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9022626876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9493379592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1376304626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3541698455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3824138641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3447561264038</t>
+    <t xml:space="preserve">10.9116764068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9022617340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9493370056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1376314163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3541707992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3824148178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3447551727295</t>
   </si>
   <si>
     <t xml:space="preserve">11.4106588363647</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2694387435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5048065185547</t>
+    <t xml:space="preserve">11.2694368362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5048046112061</t>
   </si>
   <si>
     <t xml:space="preserve">11.4294881820679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3353395462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2788515090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2506084442139</t>
+    <t xml:space="preserve">11.3353404998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2788505554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2506065368652</t>
   </si>
   <si>
     <t xml:space="preserve">11.1093864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0340690612793</t>
+    <t xml:space="preserve">11.0340700149536</t>
   </si>
   <si>
     <t xml:space="preserve">10.9210920333862</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6668949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8363599777222</t>
+    <t xml:space="preserve">10.6668939590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8363590240479</t>
   </si>
   <si>
     <t xml:space="preserve">10.7892875671387</t>
@@ -983,43 +983,43 @@
     <t xml:space="preserve">11.1941194534302</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1658744812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0717287063599</t>
+    <t xml:space="preserve">11.1658754348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0717277526855</t>
   </si>
   <si>
     <t xml:space="preserve">11.1282167434692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3165121078491</t>
+    <t xml:space="preserve">11.3165102005005</t>
   </si>
   <si>
     <t xml:space="preserve">11.3259248733521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.241192817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0623149871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.090558052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1752891540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4389019012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7213439941406</t>
+    <t xml:space="preserve">11.2411918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0623121261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0905570983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1752901077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4389028549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7213449478149</t>
   </si>
   <si>
     <t xml:space="preserve">11.8154916763306</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9849576950073</t>
+    <t xml:space="preserve">11.984956741333</t>
   </si>
   <si>
     <t xml:space="preserve">12.013201713562</t>
@@ -1028,16 +1028,16 @@
     <t xml:space="preserve">11.9567136764526</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0508613586426</t>
+    <t xml:space="preserve">12.0508604049683</t>
   </si>
   <si>
     <t xml:space="preserve">12.0414457321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0791044235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9755420684814</t>
+    <t xml:space="preserve">12.0791025161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9755430221558</t>
   </si>
   <si>
     <t xml:space="preserve">11.834321975708</t>
@@ -1049,16 +1049,16 @@
     <t xml:space="preserve">12.1544218063354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1073484420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4839382171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5215978622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6439895629883</t>
+    <t xml:space="preserve">12.107349395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4839363098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5215969085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6439905166626</t>
   </si>
   <si>
     <t xml:space="preserve">12.7852096557617</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">12.8322830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8040390014648</t>
+    <t xml:space="preserve">12.8040399551392</t>
   </si>
   <si>
     <t xml:space="preserve">12.192081451416</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7872476577759</t>
+    <t xml:space="preserve">11.7872486114502</t>
   </si>
   <si>
     <t xml:space="preserve">11.8531503677368</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">12.0320310592651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1732521057129</t>
+    <t xml:space="preserve">12.1732530593872</t>
   </si>
   <si>
     <t xml:space="preserve">12.2768125534058</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">11.9002246856689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4483165740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5612926483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4012432098389</t>
+    <t xml:space="preserve">11.4483156204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5612945556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4012441635132</t>
   </si>
   <si>
     <t xml:space="preserve">11.6742706298828</t>
@@ -1112,40 +1112,40 @@
     <t xml:space="preserve">12.0885190963745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0696878433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2014951705933</t>
+    <t xml:space="preserve">12.0696887969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2014970779419</t>
   </si>
   <si>
     <t xml:space="preserve">12.1355924606323</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3615465164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3333034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1638374328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7401742935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1261777877808</t>
+    <t xml:space="preserve">12.3615484237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3333024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1638383865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7401733398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1261787414551</t>
   </si>
   <si>
     <t xml:space="preserve">12.5404262542725</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5498428344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5027666091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6345739364624</t>
+    <t xml:space="preserve">12.549840927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5027675628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6345748901367</t>
   </si>
   <si>
     <t xml:space="preserve">13.1335544586182</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">13.1241407394409</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0864820480347</t>
+    <t xml:space="preserve">13.0864810943604</t>
   </si>
   <si>
     <t xml:space="preserve">12.9546747207642</t>
@@ -1163,22 +1163,22 @@
     <t xml:space="preserve">13.4254112243652</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4630699157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5383892059326</t>
+    <t xml:space="preserve">13.4630718231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5383882522583</t>
   </si>
   <si>
     <t xml:space="preserve">13.5572166442871</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6042909622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5101442337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2559461593628</t>
+    <t xml:space="preserve">13.6042919158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5101451873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2559471130371</t>
   </si>
   <si>
     <t xml:space="preserve">13.4724855422974</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">12.4086198806763</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3803758621216</t>
+    <t xml:space="preserve">12.3803768157959</t>
   </si>
   <si>
     <t xml:space="preserve">12.4651079177856</t>
@@ -1214,10 +1214,10 @@
     <t xml:space="preserve">12.8511123657227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5969142913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.286229133606</t>
+    <t xml:space="preserve">12.5969152450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2862272262573</t>
   </si>
   <si>
     <t xml:space="preserve">12.2579851150513</t>
@@ -1229,16 +1229,16 @@
     <t xml:space="preserve">13.0394077301025</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0958957672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2653608322144</t>
+    <t xml:space="preserve">13.0958948135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2653617858887</t>
   </si>
   <si>
     <t xml:space="preserve">13.4065818786621</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3312635421753</t>
+    <t xml:space="preserve">13.3312644958496</t>
   </si>
   <si>
     <t xml:space="preserve">13.321849822998</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">13.3406791687012</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2465324401855</t>
+    <t xml:space="preserve">13.2465314865112</t>
   </si>
   <si>
     <t xml:space="preserve">12.8887710571289</t>
@@ -1262,22 +1262,22 @@
     <t xml:space="preserve">13.293604850769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5666332244873</t>
+    <t xml:space="preserve">13.566632270813</t>
   </si>
   <si>
     <t xml:space="preserve">13.6419506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3124361038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7925844192505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9997110366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1409320831299</t>
+    <t xml:space="preserve">13.3124351501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7925863265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9997091293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1409330368042</t>
   </si>
   <si>
     <t xml:space="preserve">14.3951292037964</t>
@@ -1292,25 +1292,25 @@
     <t xml:space="preserve">14.6022529602051</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6869859695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9129400253296</t>
+    <t xml:space="preserve">14.6869850158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9129390716553</t>
   </si>
   <si>
     <t xml:space="preserve">14.8564510345459</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1106472015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9694290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.997673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0353326797485</t>
+    <t xml:space="preserve">15.1106481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9694271087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9976720809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0353317260742</t>
   </si>
   <si>
     <t xml:space="preserve">14.903525352478</t>
@@ -1328,49 +1328,49 @@
     <t xml:space="preserve">15.1671380996704</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2706995010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2424554824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2518711090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4401636123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3930912017822</t>
+    <t xml:space="preserve">15.2707014083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2424564361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2518701553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.44016456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3930921554565</t>
   </si>
   <si>
     <t xml:space="preserve">15.5531435012817</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6567010879517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4213352203369</t>
+    <t xml:space="preserve">15.6567029953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4213371276855</t>
   </si>
   <si>
     <t xml:space="preserve">15.0165014266968</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3460159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8185272216797</t>
+    <t xml:space="preserve">15.3460168838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.818528175354</t>
   </si>
   <si>
     <t xml:space="preserve">14.6668348312378</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3444862365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6099500656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7332000732422</t>
+    <t xml:space="preserve">14.3444852828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6099491119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7332010269165</t>
   </si>
   <si>
     <t xml:space="preserve">14.8754119873047</t>
@@ -1382,10 +1382,10 @@
     <t xml:space="preserve">14.4013710021973</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6194305419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6289110183716</t>
+    <t xml:space="preserve">14.6194295883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6289100646973</t>
   </si>
   <si>
     <t xml:space="preserve">15.1882801055908</t>
@@ -1394,52 +1394,52 @@
     <t xml:space="preserve">15.4916658401489</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1173973083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4587116241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1553268432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1648025512695</t>
+    <t xml:space="preserve">16.1174011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4587097167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1553249359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1648044586182</t>
   </si>
   <si>
     <t xml:space="preserve">16.2027282714844</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2122097015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3259792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1079196929932</t>
+    <t xml:space="preserve">16.2122116088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3259773254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1079216003418</t>
   </si>
   <si>
     <t xml:space="preserve">16.069995880127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5250759124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7241706848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6672859191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5724792480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.307014465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2596130371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6767692565918</t>
+    <t xml:space="preserve">16.525074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7241725921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6672878265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5724811553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3070182800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2596111297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6767673492432</t>
   </si>
   <si>
     <t xml:space="preserve">16.8379440307617</t>
@@ -1448,13 +1448,13 @@
     <t xml:space="preserve">16.8853435516357</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0465202331543</t>
+    <t xml:space="preserve">17.0465221405029</t>
   </si>
   <si>
     <t xml:space="preserve">16.9232711791992</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7715797424316</t>
+    <t xml:space="preserve">16.771577835083</t>
   </si>
   <si>
     <t xml:space="preserve">16.3733825683594</t>
@@ -1469,22 +1469,22 @@
     <t xml:space="preserve">16.4018268585205</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5535163879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.363899230957</t>
+    <t xml:space="preserve">16.5535202026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3639030456543</t>
   </si>
   <si>
     <t xml:space="preserve">16.5155963897705</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1034069061279</t>
+    <t xml:space="preserve">17.1034088134766</t>
   </si>
   <si>
     <t xml:space="preserve">17.5395240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9471988677979</t>
+    <t xml:space="preserve">17.9472007751465</t>
   </si>
   <si>
     <t xml:space="preserve">17.4447154998779</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">18.1652584075928</t>
   </si>
   <si>
-    <t xml:space="preserve">18.715145111084</t>
+    <t xml:space="preserve">18.7151489257812</t>
   </si>
   <si>
     <t xml:space="preserve">18.1368141174316</t>
@@ -1505,16 +1505,16 @@
     <t xml:space="preserve">18.4117584228516</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2505836486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0704498291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8618698120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6343307495117</t>
+    <t xml:space="preserve">18.2505855560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0704479217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8618717193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.634334564209</t>
   </si>
   <si>
     <t xml:space="preserve">17.7860260009766</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">17.7575817108154</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2979888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.373836517334</t>
+    <t xml:space="preserve">18.2979907989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3738384246826</t>
   </si>
   <si>
     <t xml:space="preserve">18.203182220459</t>
@@ -1538,13 +1538,13 @@
     <t xml:space="preserve">18.1083736419678</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2126636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0609683990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9377174377441</t>
+    <t xml:space="preserve">18.2126617431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0609664916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9377193450928</t>
   </si>
   <si>
     <t xml:space="preserve">18.0040836334229</t>
@@ -1553,22 +1553,22 @@
     <t xml:space="preserve">17.5774478912354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3927993774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8334274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0135650634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7435874938965</t>
+    <t xml:space="preserve">18.3927955627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8334293365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0135669708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7435894012451</t>
   </si>
   <si>
     <t xml:space="preserve">19.3408794403076</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4167289733887</t>
+    <t xml:space="preserve">19.41672706604</t>
   </si>
   <si>
     <t xml:space="preserve">19.3788051605225</t>
@@ -1577,22 +1577,22 @@
     <t xml:space="preserve">19.18918800354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0564575195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7246265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4496841430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5255279541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7720279693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9616470336914</t>
+    <t xml:space="preserve">19.0564556121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7246284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4496822357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5255317687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.772029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.96164894104</t>
   </si>
   <si>
     <t xml:space="preserve">18.6867008209229</t>
@@ -1601,25 +1601,25 @@
     <t xml:space="preserve">18.146297454834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.50657081604</t>
+    <t xml:space="preserve">18.5065689086914</t>
   </si>
   <si>
     <t xml:space="preserve">18.0420074462891</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3025035858154</t>
+    <t xml:space="preserve">17.3025054931641</t>
   </si>
   <si>
     <t xml:space="preserve">16.5629997253418</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4537410736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5864763259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.671802520752</t>
+    <t xml:space="preserve">15.453742980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5864753723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6718034744263</t>
   </si>
   <si>
     <t xml:space="preserve">15.0081443786621</t>
@@ -1628,19 +1628,19 @@
     <t xml:space="preserve">15.4253005981445</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4632225036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8045339584351</t>
+    <t xml:space="preserve">15.4632234573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8045320510864</t>
   </si>
   <si>
     <t xml:space="preserve">15.7286863327026</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9512596130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0745105743408</t>
+    <t xml:space="preserve">14.9512605667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0745096206665</t>
   </si>
   <si>
     <t xml:space="preserve">14.9986629486084</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">15.0176248550415</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8469705581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6573534011841</t>
+    <t xml:space="preserve">14.8469696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6573553085327</t>
   </si>
   <si>
     <t xml:space="preserve">14.7047576904297</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">14.6763143539429</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6478719711304</t>
+    <t xml:space="preserve">14.6478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">14.932297706604</t>
@@ -1676,49 +1676,49 @@
     <t xml:space="preserve">14.7900848388672</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8135604858398</t>
+    <t xml:space="preserve">13.8135585784912</t>
   </si>
   <si>
     <t xml:space="preserve">13.7282314300537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1309413909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0835371017456</t>
+    <t xml:space="preserve">13.1309404373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0835380554199</t>
   </si>
   <si>
     <t xml:space="preserve">13.3869228363037</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2636709213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3964042663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6523847579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4912109375</t>
+    <t xml:space="preserve">13.2636728286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3964033126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6523866653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4912118911743</t>
   </si>
   <si>
     <t xml:space="preserve">13.2257490158081</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8704471588135</t>
+    <t xml:space="preserve">13.8704462051392</t>
   </si>
   <si>
     <t xml:space="preserve">14.012656211853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4961795806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2212362289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1643495559692</t>
+    <t xml:space="preserve">14.4961786270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2212352752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1643505096436</t>
   </si>
   <si>
     <t xml:space="preserve">14.3065624237061</t>
@@ -1727,13 +1727,13 @@
     <t xml:space="preserve">14.3350057601929</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7945985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7377138137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5955009460449</t>
+    <t xml:space="preserve">13.7945995330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7377128601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5955018997192</t>
   </si>
   <si>
     <t xml:space="preserve">13.7566766738892</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">13.8988876342773</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9462909698486</t>
+    <t xml:space="preserve">13.9462919235229</t>
   </si>
   <si>
     <t xml:space="preserve">14.4203329086304</t>
@@ -1754,112 +1754,112 @@
     <t xml:space="preserve">12.7232656478882</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3205575942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1878261566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7471933364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0695419311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8374891281128</t>
+    <t xml:space="preserve">13.320556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1878252029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7471952438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0695428848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8374881744385</t>
   </si>
   <si>
     <t xml:space="preserve">15.2546453475952</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8848915100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0839900970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1787986755371</t>
+    <t xml:space="preserve">14.8848934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0839910507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1787996292114</t>
   </si>
   <si>
     <t xml:space="preserve">15.1503562927246</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3115301132202</t>
+    <t xml:space="preserve">15.3115310668945</t>
   </si>
   <si>
     <t xml:space="preserve">15.3589353561401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2925672531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1408767700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0271072387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9228162765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8280076980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8659324645996</t>
+    <t xml:space="preserve">15.2925682067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1408758163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0271062850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.922815322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8280086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8659334182739</t>
   </si>
   <si>
     <t xml:space="preserve">14.9417781829834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.614917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7097253799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0650281906128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2167205810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5485496520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4347820281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3968572616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7806053161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9038562774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2262020111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1977615356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.444263458252</t>
+    <t xml:space="preserve">15.6149168014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7097225189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0650291442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.216721534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5485515594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4347810745239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.396858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7806043624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9038553237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2262029647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1977605819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4442615509033</t>
   </si>
   <si>
     <t xml:space="preserve">15.3684148788452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5106287002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.738166809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.430269241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.965708732605</t>
+    <t xml:space="preserve">15.510627746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7381677627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4302673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9657077789307</t>
   </si>
   <si>
     <t xml:space="preserve">15.2641267776489</t>
@@ -1868,64 +1868,64 @@
     <t xml:space="preserve">15.785572052002</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6862525939941</t>
+    <t xml:space="preserve">16.6862487792969</t>
   </si>
   <si>
     <t xml:space="preserve">16.8474254608154</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4966316223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.193244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2311706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7526149749756</t>
+    <t xml:space="preserve">16.4966335296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1932468414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2311725616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7526168823242</t>
   </si>
   <si>
     <t xml:space="preserve">16.4207859039307</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8095016479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7336521148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8948268890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8663864135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.250129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.899341583252</t>
+    <t xml:space="preserve">16.8094997406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7336540222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8948287963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8663845062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2501316070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8993425369263</t>
   </si>
   <si>
     <t xml:space="preserve">15.8898591995239</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9277820587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.851936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3544216156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2406520843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9183053970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5015983581543</t>
+    <t xml:space="preserve">15.9277839660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8519382476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.354419708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2406482696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.918306350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5016002655029</t>
   </si>
   <si>
     <t xml:space="preserve">17.6627731323242</t>
@@ -1937,40 +1937,40 @@
     <t xml:space="preserve">17.3119850158691</t>
   </si>
   <si>
-    <t xml:space="preserve">17.283540725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8239479064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6677436828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5743827819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8704261779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5962142944336</t>
+    <t xml:space="preserve">17.2835426330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8239498138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6677417755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5743808746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8704280853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5962104797363</t>
   </si>
   <si>
     <t xml:space="preserve">19.5007133483887</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9277248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9468288421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9850234985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5934810638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7080821990967</t>
+    <t xml:space="preserve">18.9277267456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9468250274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9850254058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5934791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.708080291748</t>
   </si>
   <si>
     <t xml:space="preserve">18.9659252166748</t>
@@ -1982,31 +1982,31 @@
     <t xml:space="preserve">19.2333183288574</t>
   </si>
   <si>
-    <t xml:space="preserve">19.386116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0900707244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1951217651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.118724822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2524185180664</t>
+    <t xml:space="preserve">19.3861179351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0900745391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1951198577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1187229156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.252420425415</t>
   </si>
   <si>
     <t xml:space="preserve">19.9018077850342</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1501026153564</t>
+    <t xml:space="preserve">20.1501007080078</t>
   </si>
   <si>
     <t xml:space="preserve">20.2646980285645</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5893955230713</t>
+    <t xml:space="preserve">20.589391708374</t>
   </si>
   <si>
     <t xml:space="preserve">20.5511932373047</t>
@@ -2018,22 +2018,22 @@
     <t xml:space="preserve">19.9591045379639</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8445072174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4816112518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3097152709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6344127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6726112365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0928020477295</t>
+    <t xml:space="preserve">19.8445091247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4816150665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3097171783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6344108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6726093292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0928039550781</t>
   </si>
   <si>
     <t xml:space="preserve">19.9400062561035</t>
@@ -2042,19 +2042,19 @@
     <t xml:space="preserve">19.6535110473633</t>
   </si>
   <si>
-    <t xml:space="preserve">19.558012008667</t>
+    <t xml:space="preserve">19.5580139160156</t>
   </si>
   <si>
     <t xml:space="preserve">19.7299098968506</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3028984069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2837982177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2264995574951</t>
+    <t xml:space="preserve">20.3029003143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2838001251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2265014648438</t>
   </si>
   <si>
     <t xml:space="preserve">20.7039909362793</t>
@@ -2063,64 +2063,64 @@
     <t xml:space="preserve">20.6848907470703</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4174976348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0355033874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1310005187988</t>
+    <t xml:space="preserve">20.4174938201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0355014801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1310024261475</t>
   </si>
   <si>
     <t xml:space="preserve">20.1882991790771</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2769813537598</t>
+    <t xml:space="preserve">21.2769794464111</t>
   </si>
   <si>
     <t xml:space="preserve">21.1814804077148</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4365940093994</t>
+    <t xml:space="preserve">20.436595916748</t>
   </si>
   <si>
     <t xml:space="preserve">20.0164031982422</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5702953338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9904861450195</t>
+    <t xml:space="preserve">20.5702934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9904842376709</t>
   </si>
   <si>
     <t xml:space="preserve">21.1050834655762</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1623821258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2578811645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0286865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2960777282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8499660491943</t>
+    <t xml:space="preserve">21.1623802185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2578792572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0286827087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2960796356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.849967956543</t>
   </si>
   <si>
     <t xml:space="preserve">22.4802570343018</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5566558837891</t>
+    <t xml:space="preserve">22.5566539764404</t>
   </si>
   <si>
     <t xml:space="preserve">22.5184555053711</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0982608795166</t>
+    <t xml:space="preserve">22.0982627868652</t>
   </si>
   <si>
     <t xml:space="preserve">22.2510585784912</t>
@@ -2129,31 +2129,31 @@
     <t xml:space="preserve">21.9645671844482</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9454650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3083591461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5948505401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7476501464844</t>
+    <t xml:space="preserve">21.9454669952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3083610534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5948543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.747652053833</t>
   </si>
   <si>
     <t xml:space="preserve">22.8049488067627</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0600643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2319622039795</t>
+    <t xml:space="preserve">22.0600662231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2319602966309</t>
   </si>
   <si>
     <t xml:space="preserve">21.3533782958984</t>
   </si>
   <si>
-    <t xml:space="preserve">20.474796295166</t>
+    <t xml:space="preserve">20.4747943878174</t>
   </si>
   <si>
     <t xml:space="preserve">20.455696105957</t>
@@ -2162,139 +2162,139 @@
     <t xml:space="preserve">21.1241817474365</t>
   </si>
   <si>
-    <t xml:space="preserve">20.780387878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8758869171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0859851837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7353706359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.506175994873</t>
+    <t xml:space="preserve">20.7803897857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8758850097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0859832763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.735372543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5061740875244</t>
   </si>
   <si>
     <t xml:space="preserve">21.2196788787842</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3724765777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6016731262207</t>
+    <t xml:space="preserve">21.3724784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6016750335693</t>
   </si>
   <si>
     <t xml:space="preserve">21.678071975708</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4870738983154</t>
+    <t xml:space="preserve">21.4870777130127</t>
   </si>
   <si>
     <t xml:space="preserve">21.5825748443604</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6466941833496</t>
+    <t xml:space="preserve">20.646692276001</t>
   </si>
   <si>
     <t xml:space="preserve">20.608491897583</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4938945770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8567886352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3792972564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8949871063232</t>
+    <t xml:space="preserve">20.4938926696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8567867279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3792991638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8949851989746</t>
   </si>
   <si>
     <t xml:space="preserve">20.9331874847412</t>
   </si>
   <si>
-    <t xml:space="preserve">20.32200050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3410987854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.830867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0218639373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5375537872314</t>
+    <t xml:space="preserve">20.3219966888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3410949707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8308696746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0218658447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5375556945801</t>
   </si>
   <si>
     <t xml:space="preserve">22.6521530151367</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0150451660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4543380737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7217292785645</t>
+    <t xml:space="preserve">23.0150470733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4543361663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7217311859131</t>
   </si>
   <si>
     <t xml:space="preserve">23.912727355957</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5689334869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0846252441406</t>
+    <t xml:space="preserve">23.5689353942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0846214294434</t>
   </si>
   <si>
     <t xml:space="preserve">23.7981300354004</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8745269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9700260162354</t>
+    <t xml:space="preserve">23.8745288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.970027923584</t>
   </si>
   <si>
     <t xml:space="preserve">24.3711185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8677101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0969047546387</t>
+    <t xml:space="preserve">24.8677082061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.09690284729</t>
   </si>
   <si>
     <t xml:space="preserve">25.3642978668213</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3329200744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.982307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2878971099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9250087738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0205059051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6194133758545</t>
+    <t xml:space="preserve">24.3329181671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9823055267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.287899017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9250068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0205039978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6194114685059</t>
   </si>
   <si>
     <t xml:space="preserve">24.9441070556641</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8295116424561</t>
+    <t xml:space="preserve">24.8295097351074</t>
   </si>
   <si>
     <t xml:space="preserve">24.6385116577148</t>
@@ -2309,13 +2309,13 @@
     <t xml:space="preserve">24.3520183563232</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6576118469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6767120361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4857139587402</t>
+    <t xml:space="preserve">24.6576137542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6767139434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4857158660889</t>
   </si>
   <si>
     <t xml:space="preserve">24.5621147155762</t>
@@ -2330,31 +2330,31 @@
     <t xml:space="preserve">25.306999206543</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3451995849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8486080169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.001407623291</t>
+    <t xml:space="preserve">25.3451976776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8486099243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0014057159424</t>
   </si>
   <si>
     <t xml:space="preserve">25.2115020751953</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7653903961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6125946044922</t>
+    <t xml:space="preserve">25.7653884887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6125907897949</t>
   </si>
   <si>
     <t xml:space="preserve">25.5552959442139</t>
   </si>
   <si>
-    <t xml:space="preserve">25.154203414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8226909637451</t>
+    <t xml:space="preserve">25.1542015075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8226890563965</t>
   </si>
   <si>
     <t xml:space="preserve">24.7722110748291</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">24.5239162445068</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9059085845947</t>
+    <t xml:space="preserve">24.9059066772461</t>
   </si>
   <si>
     <t xml:space="preserve">25.6698913574219</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">26.2237815856934</t>
   </si>
   <si>
-    <t xml:space="preserve">26.281078338623</t>
+    <t xml:space="preserve">26.2810821533203</t>
   </si>
   <si>
     <t xml:space="preserve">26.395679473877</t>
@@ -2381,16 +2381,16 @@
     <t xml:space="preserve">27.1405639648438</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2169609069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5225582122803</t>
+    <t xml:space="preserve">27.2169628143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.522554397583</t>
   </si>
   <si>
     <t xml:space="preserve">27.6944541931152</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8281497955322</t>
+    <t xml:space="preserve">27.8281478881836</t>
   </si>
   <si>
     <t xml:space="preserve">28.1910438537598</t>
@@ -2402,25 +2402,25 @@
     <t xml:space="preserve">28.2865409851074</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8854484558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9754867553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2306003570557</t>
+    <t xml:space="preserve">27.8854503631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9754848480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2306022644043</t>
   </si>
   <si>
     <t xml:space="preserve">24.6003131866455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6071338653564</t>
+    <t xml:space="preserve">23.6071319580078</t>
   </si>
   <si>
     <t xml:space="preserve">24.4666156768799</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4352397918701</t>
+    <t xml:space="preserve">23.4352378845215</t>
   </si>
   <si>
     <t xml:space="preserve">19.8254089355469</t>
@@ -2429,16 +2429,16 @@
     <t xml:space="preserve">19.3479175567627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5852928161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.323356628418</t>
+    <t xml:space="preserve">15.5852909088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3233585357666</t>
   </si>
   <si>
     <t xml:space="preserve">15.7285394668579</t>
   </si>
   <si>
-    <t xml:space="preserve">16.120080947876</t>
+    <t xml:space="preserve">16.1200790405273</t>
   </si>
   <si>
     <t xml:space="preserve">16.9031677246094</t>
@@ -2447,76 +2447,76 @@
     <t xml:space="preserve">17.5239028930664</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7435474395752</t>
+    <t xml:space="preserve">17.7435512542725</t>
   </si>
   <si>
     <t xml:space="preserve">18.1350898742676</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8322277069092</t>
+    <t xml:space="preserve">18.8322296142578</t>
   </si>
   <si>
     <t xml:space="preserve">18.1446418762207</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2210388183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1159934997559</t>
+    <t xml:space="preserve">18.221040725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1159896850586</t>
   </si>
   <si>
     <t xml:space="preserve">17.8772468566895</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3806591033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4093074798584</t>
+    <t xml:space="preserve">17.3806571960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4093055725098</t>
   </si>
   <si>
     <t xml:space="preserve">16.8076686859131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6480541229248</t>
+    <t xml:space="preserve">17.6480522155762</t>
   </si>
   <si>
     <t xml:space="preserve">18.7844791412354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4311332702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4454612731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7653770446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9536476135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8663387298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.271520614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8465518951416</t>
+    <t xml:space="preserve">18.4311351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4454593658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7653789520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9536437988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8663368225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2715187072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8465538024902</t>
   </si>
   <si>
     <t xml:space="preserve">20.006856918335</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2456016540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9877548217773</t>
+    <t xml:space="preserve">20.2455997467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.987756729126</t>
   </si>
   <si>
     <t xml:space="preserve">19.9686546325684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7681121826172</t>
+    <t xml:space="preserve">19.7681083679199</t>
   </si>
   <si>
     <t xml:space="preserve">20.6753406524658</t>
@@ -2525,16 +2525,16 @@
     <t xml:space="preserve">21.7640209197998</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3820247650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.337007522583</t>
+    <t xml:space="preserve">21.3820266723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3370056152344</t>
   </si>
   <si>
     <t xml:space="preserve">21.7926692962646</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0191345214844</t>
+    <t xml:space="preserve">21.019136428833</t>
   </si>
   <si>
     <t xml:space="preserve">21.4297771453857</t>
@@ -2543,37 +2543,37 @@
     <t xml:space="preserve">21.8595161437988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9522857666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9932174682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6589698791504</t>
+    <t xml:space="preserve">20.9522838592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9932155609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6589736938477</t>
   </si>
   <si>
     <t xml:space="preserve">23.0341453552246</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1391925811768</t>
+    <t xml:space="preserve">23.1391906738281</t>
   </si>
   <si>
     <t xml:space="preserve">22.2797107696533</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5020866394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8267784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5211849212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8458805084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8172283172607</t>
+    <t xml:space="preserve">23.5020847320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8267803192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.521183013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8458786010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8172302246094</t>
   </si>
   <si>
     <t xml:space="preserve">23.3588371276855</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">22.6903514862061</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6330547332764</t>
+    <t xml:space="preserve">22.6330528259277</t>
   </si>
   <si>
     <t xml:space="preserve">21.8881683349609</t>
@@ -2591,19 +2591,19 @@
     <t xml:space="preserve">22.0696125030518</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6999034881592</t>
+    <t xml:space="preserve">22.6999015808105</t>
   </si>
   <si>
     <t xml:space="preserve">22.938648223877</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3015384674072</t>
+    <t xml:space="preserve">23.3015403747559</t>
   </si>
   <si>
     <t xml:space="preserve">22.6808013916016</t>
   </si>
   <si>
-    <t xml:space="preserve">22.709451675415</t>
+    <t xml:space="preserve">22.7094497680664</t>
   </si>
   <si>
     <t xml:space="preserve">23.1487426757812</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">23.4638843536377</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4229545593262</t>
+    <t xml:space="preserve">22.4229564666748</t>
   </si>
   <si>
     <t xml:space="preserve">22.4611587524414</t>
@@ -2624,13 +2624,13 @@
     <t xml:space="preserve">22.7381000518799</t>
   </si>
   <si>
-    <t xml:space="preserve">23.272891998291</t>
+    <t xml:space="preserve">23.2728900909424</t>
   </si>
   <si>
     <t xml:space="preserve">23.2442398071289</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5402851104736</t>
+    <t xml:space="preserve">23.540283203125</t>
   </si>
   <si>
     <t xml:space="preserve">23.7408313751221</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">24.7340106964111</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2783508300781</t>
+    <t xml:space="preserve">25.2783489227295</t>
   </si>
   <si>
     <t xml:space="preserve">25.0682544708252</t>
@@ -2672,13 +2672,13 @@
     <t xml:space="preserve">26.5580253601074</t>
   </si>
   <si>
-    <t xml:space="preserve">26.510274887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6467037200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2292404174805</t>
+    <t xml:space="preserve">26.5102787017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6467056274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2292423248291</t>
   </si>
   <si>
     <t xml:space="preserve">27.5034561157227</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">27.5894031524658</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1596622467041</t>
+    <t xml:space="preserve">27.1596641540527</t>
   </si>
   <si>
     <t xml:space="preserve">27.5512065887451</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">27.0164165496826</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0355167388916</t>
+    <t xml:space="preserve">27.035514831543</t>
   </si>
   <si>
     <t xml:space="preserve">27.3793087005615</t>
@@ -2705,19 +2705,19 @@
     <t xml:space="preserve">27.2265129089355</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0546169281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2838115692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5675773620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0450649261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.710823059082</t>
+    <t xml:space="preserve">27.054615020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2838096618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5675754547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0450668334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7108211517334</t>
   </si>
   <si>
     <t xml:space="preserve">26.5007266998291</t>
@@ -2726,16 +2726,16 @@
     <t xml:space="preserve">26.4529762268066</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6630725860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5389270782471</t>
+    <t xml:space="preserve">26.6630744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5389251708984</t>
   </si>
   <si>
     <t xml:space="preserve">26.2619819641113</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4625263214111</t>
+    <t xml:space="preserve">26.4625244140625</t>
   </si>
   <si>
     <t xml:space="preserve">27.5989551544189</t>
@@ -2744,34 +2744,34 @@
     <t xml:space="preserve">26.6726245880127</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7585697174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.388858795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.446159362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1814956665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3533916473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5061874389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9932289123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7926826477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6971817016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5798530578613</t>
+    <t xml:space="preserve">26.7585735321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3888607025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4461574554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1814918518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3533897399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5061893463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9932270050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7926807403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6971836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.57985496521</t>
   </si>
   <si>
     <t xml:space="preserve">27.6562519073486</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">27.4748077392578</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6849002838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3847675323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9673042297363</t>
+    <t xml:space="preserve">27.6849021911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3847713470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.967306137085</t>
   </si>
   <si>
     <t xml:space="preserve">29.1746730804443</t>
@@ -2795,19 +2795,19 @@
     <t xml:space="preserve">29.4802703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8336124420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0246086120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1651248931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3274688720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8049602508545</t>
+    <t xml:space="preserve">29.833610534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0246067047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1651229858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3274707794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8049583435059</t>
   </si>
   <si>
     <t xml:space="preserve">30.4734477996826</t>
@@ -2822,43 +2822,43 @@
     <t xml:space="preserve">30.5402946472168</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9222888946533</t>
+    <t xml:space="preserve">30.922290802002</t>
   </si>
   <si>
     <t xml:space="preserve">30.7408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9318370819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7217426300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6835460662842</t>
+    <t xml:space="preserve">30.9318389892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7217407226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6835441589355</t>
   </si>
   <si>
     <t xml:space="preserve">30.8172397613525</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4829998016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5593967437744</t>
+    <t xml:space="preserve">30.4829959869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5593948364258</t>
   </si>
   <si>
     <t xml:space="preserve">28.7258319854736</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2128715515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9031925201416</t>
+    <t xml:space="preserve">29.2128734588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.903190612793</t>
   </si>
   <si>
     <t xml:space="preserve">31.9918689727783</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8991012573242</t>
+    <t xml:space="preserve">32.899097442627</t>
   </si>
   <si>
     <t xml:space="preserve">33.6535377502441</t>
@@ -2867,16 +2867,16 @@
     <t xml:space="preserve">33.309741973877</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4693603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3288459777832</t>
+    <t xml:space="preserve">32.4693565368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3288383483887</t>
   </si>
   <si>
     <t xml:space="preserve">33.5580368041992</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1310272216797</t>
+    <t xml:space="preserve">34.1310234069824</t>
   </si>
   <si>
     <t xml:space="preserve">33.4338874816895</t>
@@ -2888,52 +2888,52 @@
     <t xml:space="preserve">33.8158798217773</t>
   </si>
   <si>
-    <t xml:space="preserve">33.930477142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6603584289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6699028015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8513565063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5143756866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6098728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9727687835693</t>
+    <t xml:space="preserve">33.9304809570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6603546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6699066162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8513488769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5143775939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6098747253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9727668762207</t>
   </si>
   <si>
     <t xml:space="preserve">32.7367515563965</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0587158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2565288543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8840885162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0177841186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1323833465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8745403289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0846347808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6194267272949</t>
+    <t xml:space="preserve">32.0587196350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2565326690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8840923309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0177879333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1323852539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8745422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0846309661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6194248199463</t>
   </si>
   <si>
     <t xml:space="preserve">32.0969161987305</t>
@@ -2945,43 +2945,43 @@
     <t xml:space="preserve">32.1542091369629</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9441184997559</t>
+    <t xml:space="preserve">31.9441204071045</t>
   </si>
   <si>
     <t xml:space="preserve">32.4216079711914</t>
   </si>
   <si>
-    <t xml:space="preserve">31.695821762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2115135192871</t>
+    <t xml:space="preserve">31.6958198547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2115173339844</t>
   </si>
   <si>
     <t xml:space="preserve">31.7435722351074</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2783622741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5075645446777</t>
+    <t xml:space="preserve">32.2783584594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5075569152832</t>
   </si>
   <si>
     <t xml:space="preserve">32.4120559692383</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0491676330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5334777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2087841033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3165626525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1637687683105</t>
+    <t xml:space="preserve">32.0491638183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5334739685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2087821960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3165588378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.163761138916</t>
   </si>
   <si>
     <t xml:space="preserve">32.1064643859863</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">32.8036003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5839538574219</t>
+    <t xml:space="preserve">32.5839500427246</t>
   </si>
   <si>
     <t xml:space="preserve">32.3547592163086</t>
@@ -3008,85 +3008,85 @@
     <t xml:space="preserve">32.0682678222656</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0396156311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5648536682129</t>
+    <t xml:space="preserve">32.0396194458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5648574829102</t>
   </si>
   <si>
     <t xml:space="preserve">32.3261108398438</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9250202178955</t>
+    <t xml:space="preserve">31.9250164031982</t>
   </si>
   <si>
     <t xml:space="preserve">33.0423469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7967834472656</t>
+    <t xml:space="preserve">33.7967796325684</t>
   </si>
   <si>
     <t xml:space="preserve">34.5989646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4843711853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.942756652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8854598999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.000057220459</t>
+    <t xml:space="preserve">34.4843673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9427604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8854560852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0000610351562</t>
   </si>
   <si>
     <t xml:space="preserve">35.8022422790527</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5539474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3342971801758</t>
+    <t xml:space="preserve">35.5539512634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.334300994873</t>
   </si>
   <si>
     <t xml:space="preserve">34.2551727294922</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9018287658691</t>
+    <t xml:space="preserve">33.9018325805664</t>
   </si>
   <si>
     <t xml:space="preserve">33.3670387268066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3192901611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.781774520874</t>
+    <t xml:space="preserve">33.3192939758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7817687988281</t>
   </si>
   <si>
     <t xml:space="preserve">31.8104209899902</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4598121643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7081069946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9768581390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4898166656494</t>
+    <t xml:space="preserve">32.4598083496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7081031799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9768562316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4898147583008</t>
   </si>
   <si>
     <t xml:space="preserve">28.6876335144043</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0027770996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3875007629395</t>
+    <t xml:space="preserve">29.002779006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3874988555908</t>
   </si>
   <si>
     <t xml:space="preserve">30.6453437805176</t>
@@ -3104,43 +3104,43 @@
     <t xml:space="preserve">31.1228351593018</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5498485565186</t>
+    <t xml:space="preserve">30.5498447418213</t>
   </si>
   <si>
     <t xml:space="preserve">29.5375671386719</t>
   </si>
   <si>
-    <t xml:space="preserve">30.148754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6671733856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4065971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7694911956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6644458770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3111019134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9413871765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2756309509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9604892730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5812244415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3424835205078</t>
+    <t xml:space="preserve">30.1487560272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6671752929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4065990447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7694931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6644439697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3111000061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9413890838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.275634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9604873657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5812282562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3424816131592</t>
   </si>
   <si>
     <t xml:space="preserve">33.5007400512695</t>
@@ -3149,22 +3149,22 @@
     <t xml:space="preserve">32.9373016357422</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8731842041016</t>
+    <t xml:space="preserve">33.8731803894043</t>
   </si>
   <si>
     <t xml:space="preserve">33.6344375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6248817443848</t>
+    <t xml:space="preserve">33.624885559082</t>
   </si>
   <si>
     <t xml:space="preserve">34.1787719726562</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2169761657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9905052185059</t>
+    <t xml:space="preserve">34.2169723510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9905090332031</t>
   </si>
   <si>
     <t xml:space="preserve">34.8281631469727</t>
@@ -3182,25 +3182,25 @@
     <t xml:space="preserve">33.8063354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2333374023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0928268432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5771293640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2688179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9059200286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8868198394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0873603820801</t>
+    <t xml:space="preserve">33.2333450317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0928230285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5771408081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2688102722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9059238433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8868217468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0873641967773</t>
   </si>
   <si>
     <t xml:space="preserve">32.946849822998</t>
@@ -3218,22 +3218,22 @@
     <t xml:space="preserve">36.6538200378418</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9620590209961</t>
+    <t xml:space="preserve">35.9620552062988</t>
   </si>
   <si>
     <t xml:space="preserve">36.769115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0765609741211</t>
+    <t xml:space="preserve">37.0765647888184</t>
   </si>
   <si>
     <t xml:space="preserve">37.4224433898926</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1246070861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.018913269043</t>
+    <t xml:space="preserve">37.1246032714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0189170837402</t>
   </si>
   <si>
     <t xml:space="preserve">37.6818542480469</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">37.8836212158203</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0181312561035</t>
+    <t xml:space="preserve">38.0181274414062</t>
   </si>
   <si>
     <t xml:space="preserve">39.2479286193848</t>
@@ -3257,22 +3257,22 @@
     <t xml:space="preserve">38.6138114929199</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6426391601562</t>
+    <t xml:space="preserve">38.642635345459</t>
   </si>
   <si>
     <t xml:space="preserve">39.3440093994141</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5946006774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7963600158691</t>
+    <t xml:space="preserve">38.594596862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7963638305664</t>
   </si>
   <si>
     <t xml:space="preserve">38.7195014953613</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6042098999023</t>
+    <t xml:space="preserve">38.6042060852051</t>
   </si>
   <si>
     <t xml:space="preserve">39.6130294799805</t>
@@ -3281,28 +3281,28 @@
     <t xml:space="preserve">39.6514587402344</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7475357055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4969444274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0069465637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8051834106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9685173034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6034202575684</t>
+    <t xml:space="preserve">39.7475395202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4969482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0069427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8051872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9685134887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6034240722656</t>
   </si>
   <si>
     <t xml:space="preserve">39.7571487426758</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9973411560059</t>
+    <t xml:space="preserve">39.9973373413086</t>
   </si>
   <si>
     <t xml:space="preserve">39.0749855041504</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">38.9789123535156</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1614570617676</t>
+    <t xml:space="preserve">39.1614608764648</t>
   </si>
   <si>
     <t xml:space="preserve">38.4793014526367</t>
@@ -3332,19 +3332,19 @@
     <t xml:space="preserve">39.4496994018555</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1806755065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8540077209473</t>
+    <t xml:space="preserve">39.1806793212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8540115356445</t>
   </si>
   <si>
     <t xml:space="preserve">39.430477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7675361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0453796386719</t>
+    <t xml:space="preserve">38.7675399780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0453834533691</t>
   </si>
   <si>
     <t xml:space="preserve">40.6410636901855</t>
@@ -3389,19 +3389,19 @@
     <t xml:space="preserve">41.5634117126465</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0822410583496</t>
+    <t xml:space="preserve">42.0822372436523</t>
   </si>
   <si>
     <t xml:space="preserve">43.0814476013184</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2455711364746</t>
+    <t xml:space="preserve">42.2455749511719</t>
   </si>
   <si>
     <t xml:space="preserve">42.0341949462891</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7651824951172</t>
+    <t xml:space="preserve">41.7651786804199</t>
   </si>
   <si>
     <t xml:space="preserve">41.9669418334961</t>
@@ -3416,19 +3416,19 @@
     <t xml:space="preserve">42.6683120727539</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9853744506836</t>
+    <t xml:space="preserve">42.9853706359863</t>
   </si>
   <si>
     <t xml:space="preserve">42.3896865844727</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8989028930664</t>
+    <t xml:space="preserve">42.8988990783691</t>
   </si>
   <si>
     <t xml:space="preserve">42.0245895385742</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9765472412109</t>
+    <t xml:space="preserve">41.9765510559082</t>
   </si>
   <si>
     <t xml:space="preserve">41.5345916748047</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">41.4577331542969</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7187118530273</t>
+    <t xml:space="preserve">39.7187156677246</t>
   </si>
   <si>
     <t xml:space="preserve">41.0061645507812</t>
@@ -3446,16 +3446,16 @@
     <t xml:space="preserve">40.0165557861328</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8332252502441</t>
+    <t xml:space="preserve">40.8332214355469</t>
   </si>
   <si>
     <t xml:space="preserve">41.0638084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0718421936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1679191589355</t>
+    <t xml:space="preserve">43.0718383789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1679229736328</t>
   </si>
   <si>
     <t xml:space="preserve">44.3112487792969</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">43.2159576416016</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9477272033691</t>
+    <t xml:space="preserve">41.9477310180664</t>
   </si>
   <si>
     <t xml:space="preserve">39.7859687805176</t>
@@ -3473,10 +3473,10 @@
     <t xml:space="preserve">40.2759628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5842056274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1902809143066</t>
+    <t xml:space="preserve">39.5842018127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1902847290039</t>
   </si>
   <si>
     <t xml:space="preserve">39.5169486999512</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">39.6802787780762</t>
   </si>
   <si>
-    <t xml:space="preserve">40.10302734375</t>
+    <t xml:space="preserve">40.1030311584473</t>
   </si>
   <si>
     <t xml:space="preserve">39.0077362060547</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">41.169490814209</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2263565063477</t>
+    <t xml:space="preserve">42.2263526916504</t>
   </si>
   <si>
     <t xml:space="preserve">42.9469375610352</t>
@@ -3530,28 +3530,28 @@
     <t xml:space="preserve">43.0045852661133</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9653663635254</t>
+    <t xml:space="preserve">43.9653625488281</t>
   </si>
   <si>
     <t xml:space="preserve">43.8596839904785</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7147750854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2632141113281</t>
+    <t xml:space="preserve">44.7147789001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2632102966309</t>
   </si>
   <si>
     <t xml:space="preserve">43.725170135498</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0037956237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.20556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4369354248047</t>
+    <t xml:space="preserve">44.0037994384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2055625915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.436939239502</t>
   </si>
   <si>
     <t xml:space="preserve">42.2551803588867</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">41.4192962646484</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1318473815918</t>
+    <t xml:space="preserve">40.1318511962891</t>
   </si>
   <si>
     <t xml:space="preserve">40.1606712341309</t>
@@ -3602,7 +3602,7 @@
     <t xml:space="preserve">41.0926322937012</t>
   </si>
   <si>
-    <t xml:space="preserve">41.986156463623</t>
+    <t xml:space="preserve">41.9861602783203</t>
   </si>
   <si>
     <t xml:space="preserve">41.5057678222656</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">42.5626258850098</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5330200195312</t>
+    <t xml:space="preserve">43.533016204834</t>
   </si>
   <si>
     <t xml:space="preserve">43.6579170227051</t>
@@ -3626,13 +3626,13 @@
     <t xml:space="preserve">44.416934967041</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0702705383301</t>
+    <t xml:space="preserve">45.0702667236328</t>
   </si>
   <si>
     <t xml:space="preserve">45.3681106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5890884399414</t>
+    <t xml:space="preserve">45.5890922546387</t>
   </si>
   <si>
     <t xml:space="preserve">44.8108558654785</t>
@@ -3647,43 +3647,43 @@
     <t xml:space="preserve">42.5914497375488</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8708610534668</t>
+    <t xml:space="preserve">41.8708648681641</t>
   </si>
   <si>
     <t xml:space="preserve">40.0261650085449</t>
   </si>
   <si>
-    <t xml:space="preserve">39.267147064209</t>
+    <t xml:space="preserve">39.2671432495117</t>
   </si>
   <si>
     <t xml:space="preserve">38.9308700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">38.383228302002</t>
+    <t xml:space="preserve">38.3832321166992</t>
   </si>
   <si>
     <t xml:space="preserve">38.1814613342285</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2014694213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7795143127441</t>
+    <t xml:space="preserve">37.2014656066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7795104980469</t>
   </si>
   <si>
     <t xml:space="preserve">34.5208854675293</t>
   </si>
   <si>
-    <t xml:space="preserve">35.001277923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0397109985352</t>
+    <t xml:space="preserve">35.0012741088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0397071838379</t>
   </si>
   <si>
     <t xml:space="preserve">34.4632377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0581359863281</t>
+    <t xml:space="preserve">36.0581398010254</t>
   </si>
   <si>
     <t xml:space="preserve">36.7018585205078</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">33.7138252258301</t>
   </si>
   <si>
-    <t xml:space="preserve">35.116569519043</t>
+    <t xml:space="preserve">35.1165657043457</t>
   </si>
   <si>
     <t xml:space="preserve">34.7706871032715</t>
@@ -3722,7 +3722,7 @@
     <t xml:space="preserve">34.2710800170898</t>
   </si>
   <si>
-    <t xml:space="preserve">34.280689239502</t>
+    <t xml:space="preserve">34.2806930541992</t>
   </si>
   <si>
     <t xml:space="preserve">34.1461791992188</t>
@@ -3737,10 +3737,10 @@
     <t xml:space="preserve">34.5689239501953</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2510757446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9332389831543</t>
+    <t xml:space="preserve">35.2510795593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.933235168457</t>
   </si>
   <si>
     <t xml:space="preserve">36.9420547485352</t>
@@ -3749,19 +3749,19 @@
     <t xml:space="preserve">36.4712677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4520568847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1253852844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7802925109863</t>
+    <t xml:space="preserve">36.4520530700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1253890991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7802963256836</t>
   </si>
   <si>
     <t xml:space="preserve">33.5889282226562</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6449966430664</t>
+    <t xml:space="preserve">35.6450004577637</t>
   </si>
   <si>
     <t xml:space="preserve">33.7042236328125</t>
@@ -3773,28 +3773,28 @@
     <t xml:space="preserve">35.1357841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9244079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2695045471191</t>
+    <t xml:space="preserve">34.9244117736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2695083618164</t>
   </si>
   <si>
     <t xml:space="preserve">36.3175430297852</t>
   </si>
   <si>
-    <t xml:space="preserve">35.981273651123</t>
+    <t xml:space="preserve">35.9812698364258</t>
   </si>
   <si>
     <t xml:space="preserve">35.5200996398926</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0973510742188</t>
+    <t xml:space="preserve">35.0973472595215</t>
   </si>
   <si>
     <t xml:space="preserve">35.7602958679199</t>
   </si>
   <si>
-    <t xml:space="preserve">36.211856842041</t>
+    <t xml:space="preserve">36.2118606567383</t>
   </si>
   <si>
     <t xml:space="preserve">38.508129119873</t>
@@ -3812,25 +3812,25 @@
     <t xml:space="preserve">41.2943954467773</t>
   </si>
   <si>
-    <t xml:space="preserve">40.890869140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6891059875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8340034484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6330299377441</t>
+    <t xml:space="preserve">40.8908653259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6891021728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8340072631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6330261230469</t>
   </si>
   <si>
     <t xml:space="preserve">39.4208679199219</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2191047668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6234245300293</t>
+    <t xml:space="preserve">39.219108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.623420715332</t>
   </si>
   <si>
     <t xml:space="preserve">37.9796981811523</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">36.1349983215332</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7218627929688</t>
+    <t xml:space="preserve">35.7218589782715</t>
   </si>
   <si>
     <t xml:space="preserve">35.3183326721191</t>
@@ -3866,7 +3866,7 @@
     <t xml:space="preserve">34.0693168640137</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2726593017578</t>
+    <t xml:space="preserve">32.2726554870605</t>
   </si>
   <si>
     <t xml:space="preserve">32.9836387634277</t>
@@ -3878,16 +3878,16 @@
     <t xml:space="preserve">31.0524616241455</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9067726135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9163780212402</t>
+    <t xml:space="preserve">32.9067687988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.916374206543</t>
   </si>
   <si>
     <t xml:space="preserve">32.9644203186035</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2734413146973</t>
+    <t xml:space="preserve">31.2734394073486</t>
   </si>
   <si>
     <t xml:space="preserve">30.3414840698242</t>
@@ -6207,6 +6207,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.0900001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4849996566772</t>
   </si>
 </sst>
 </file>
@@ -71727,7 +71730,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.691087963</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>1211542</v>
@@ -71748,6 +71751,32 @@
         <v>2064</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6911226852</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>1114368</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>14.5349998474121</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>14.0900001525879</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>14.1450004577637</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>14.4849996566772</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>2065</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2070" uniqueCount="2070">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2071" uniqueCount="2071">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,64 +47,64 @@
     <t xml:space="preserve">7.39109182357788</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31191873550415</t>
+    <t xml:space="preserve">7.31191825866699</t>
   </si>
   <si>
     <t xml:space="preserve">7.36780595779419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15357112884521</t>
+    <t xml:space="preserve">7.15357065200806</t>
   </si>
   <si>
     <t xml:space="preserve">6.96262311935425</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21877336502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27931690216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16288614273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03248167037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08836984634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1954870223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9859094619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13494157791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3445200920105</t>
+    <t xml:space="preserve">7.21877241134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2793173789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16288661956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03248262405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08836889266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19548654556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98590993881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13494205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34451913833618</t>
   </si>
   <si>
     <t xml:space="preserve">7.23740196228027</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35383415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14891386032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18151473999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40972185134888</t>
+    <t xml:space="preserve">7.35383367538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1489143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18151426315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40972232818604</t>
   </si>
   <si>
     <t xml:space="preserve">7.28397512435913</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13959884643555</t>
+    <t xml:space="preserve">7.13959932327271</t>
   </si>
   <si>
     <t xml:space="preserve">7.05111122131348</t>
@@ -116,34 +116,34 @@
     <t xml:space="preserve">6.51086711883545</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45497989654541</t>
+    <t xml:space="preserve">6.45498037338257</t>
   </si>
   <si>
     <t xml:space="preserve">6.59004068374634</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33389186859131</t>
+    <t xml:space="preserve">6.33389139175415</t>
   </si>
   <si>
     <t xml:space="preserve">6.29197549819946</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42237949371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61798477172852</t>
+    <t xml:space="preserve">6.42237997055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61798524856567</t>
   </si>
   <si>
     <t xml:space="preserve">6.88344955444336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71112966537476</t>
+    <t xml:space="preserve">6.71113014221191</t>
   </si>
   <si>
     <t xml:space="preserve">6.8368763923645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70181655883789</t>
+    <t xml:space="preserve">6.70181512832642</t>
   </si>
   <si>
     <t xml:space="preserve">6.6272988319397</t>
@@ -152,34 +152,34 @@
     <t xml:space="preserve">6.9952244758606</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8927640914917</t>
+    <t xml:space="preserve">6.89276456832886</t>
   </si>
   <si>
     <t xml:space="preserve">6.80427551269531</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7996187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84153366088867</t>
+    <t xml:space="preserve">6.79961824417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84153413772583</t>
   </si>
   <si>
     <t xml:space="preserve">6.65990018844604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63195610046387</t>
+    <t xml:space="preserve">6.63195657730103</t>
   </si>
   <si>
     <t xml:space="preserve">6.79496145248413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78564596176147</t>
+    <t xml:space="preserve">6.78564643859863</t>
   </si>
   <si>
     <t xml:space="preserve">6.86016368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00919628143311</t>
+    <t xml:space="preserve">7.00919532775879</t>
   </si>
   <si>
     <t xml:space="preserve">7.11165618896484</t>
@@ -188,97 +188,97 @@
     <t xml:space="preserve">7.08371210098267</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20945882797241</t>
+    <t xml:space="preserve">7.20945835113525</t>
   </si>
   <si>
     <t xml:space="preserve">7.10699844360352</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04179620742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2420597076416</t>
+    <t xml:space="preserve">7.04179668426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24205923080444</t>
   </si>
   <si>
     <t xml:space="preserve">7.09768390655518</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17219924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93467903137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91604995727539</t>
+    <t xml:space="preserve">7.17219972610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93467855453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91605043411255</t>
   </si>
   <si>
     <t xml:space="preserve">7.00453853607178</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27000331878662</t>
+    <t xml:space="preserve">7.27000284194946</t>
   </si>
   <si>
     <t xml:space="preserve">7.3258900642395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22808742523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50286769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41437911987305</t>
+    <t xml:space="preserve">7.22808837890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50286722183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41437864303589</t>
   </si>
   <si>
     <t xml:space="preserve">7.48423719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57738304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55409622192383</t>
+    <t xml:space="preserve">7.57738399505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55409574508667</t>
   </si>
   <si>
     <t xml:space="preserve">7.73107385635376</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60066938400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64258480072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70313024520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73573017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88476467132568</t>
+    <t xml:space="preserve">7.60066986083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64258527755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70312976837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73573064804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88476228713989</t>
   </si>
   <si>
     <t xml:space="preserve">7.8894214630127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87079095840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78696012496948</t>
+    <t xml:space="preserve">7.87079191207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78695964813232</t>
   </si>
   <si>
     <t xml:space="preserve">7.94530725479126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88010549545288</t>
+    <t xml:space="preserve">7.8801064491272</t>
   </si>
   <si>
     <t xml:space="preserve">8.08968353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01760387420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09717178344727</t>
+    <t xml:space="preserve">8.01760482788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09717082977295</t>
   </si>
   <si>
     <t xml:space="preserve">8.10653209686279</t>
@@ -287,31 +287,31 @@
     <t xml:space="preserve">8.050368309021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17205715179443</t>
+    <t xml:space="preserve">8.17205905914307</t>
   </si>
   <si>
     <t xml:space="preserve">8.21418380737305</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23758411407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22354507446289</t>
+    <t xml:space="preserve">8.23758506774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22354412078857</t>
   </si>
   <si>
     <t xml:space="preserve">8.15801811218262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07845020294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0831298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14397716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0129222869873</t>
+    <t xml:space="preserve">8.07845115661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08313083648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14397621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01292324066162</t>
   </si>
   <si>
     <t xml:space="preserve">7.91463470458984</t>
@@ -320,10 +320,10 @@
     <t xml:space="preserve">7.82102537155151</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64316701889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62912750244141</t>
+    <t xml:space="preserve">7.6431679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62912654876709</t>
   </si>
   <si>
     <t xml:space="preserve">7.65252876281738</t>
@@ -332,22 +332,22 @@
     <t xml:space="preserve">7.55892038345337</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63848876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98952102661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94739770889282</t>
+    <t xml:space="preserve">7.63848781585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98952198028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94739723205566</t>
   </si>
   <si>
     <t xml:space="preserve">8.05972766876221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67593097686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71337461471558</t>
+    <t xml:space="preserve">7.67593193054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71337509155273</t>
   </si>
   <si>
     <t xml:space="preserve">7.72273540496826</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">7.87251043319702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92867612838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89123249053955</t>
+    <t xml:space="preserve">7.92867660522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89123058319092</t>
   </si>
   <si>
     <t xml:space="preserve">7.81166553497314</t>
@@ -368,37 +368,37 @@
     <t xml:space="preserve">7.71805620193481</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88187217712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96143865585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91931343078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90995311737061</t>
+    <t xml:space="preserve">7.88187170028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96143960952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91931629180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90995407104492</t>
   </si>
   <si>
     <t xml:space="preserve">8.05504703521729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18142127990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16738033294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19546031951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19078063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30779266357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36395835876465</t>
+    <t xml:space="preserve">8.18141937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16737747192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19546127319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19078159332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3077917098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36395645141602</t>
   </si>
   <si>
     <t xml:space="preserve">8.34991550445557</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">8.29374980926514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15333652496338</t>
+    <t xml:space="preserve">8.1533374786377</t>
   </si>
   <si>
     <t xml:space="preserve">8.28906917572021</t>
@@ -425,28 +425,28 @@
     <t xml:space="preserve">8.60734081268311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51373100280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.635422706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75711345672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65414428710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78519821166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80859851837158</t>
+    <t xml:space="preserve">8.51373195648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63542366027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75711441040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65414524078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78519725799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8085994720459</t>
   </si>
   <si>
     <t xml:space="preserve">8.92092990875244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84604263305664</t>
+    <t xml:space="preserve">8.84604167938232</t>
   </si>
   <si>
     <t xml:space="preserve">8.81796073913574</t>
@@ -467,10 +467,10 @@
     <t xml:space="preserve">8.77115631103516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76179599761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6588249206543</t>
+    <t xml:space="preserve">8.76179504394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65882396697998</t>
   </si>
   <si>
     <t xml:space="preserve">8.59329986572266</t>
@@ -482,22 +482,22 @@
     <t xml:space="preserve">8.56053733825684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48564910888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54181385040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53245162963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66818618774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49969005584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61670207977295</t>
+    <t xml:space="preserve">8.4856481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54181289672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53245258331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66818809509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49968910217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61670112609863</t>
   </si>
   <si>
     <t xml:space="preserve">8.49501037597656</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">8.5558557510376</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61201953887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46692657470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52777290344238</t>
+    <t xml:space="preserve">8.61202144622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46692752838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52777194976807</t>
   </si>
   <si>
     <t xml:space="preserve">8.56521606445312</t>
@@ -521,19 +521,19 @@
     <t xml:space="preserve">8.69158744812012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0800666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24856185913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07070541381836</t>
+    <t xml:space="preserve">9.08006381988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24856281280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07070446014404</t>
   </si>
   <si>
     <t xml:space="preserve">9.01453971862793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89284801483154</t>
+    <t xml:space="preserve">8.89284610748291</t>
   </si>
   <si>
     <t xml:space="preserve">8.93965339660645</t>
@@ -551,49 +551,49 @@
     <t xml:space="preserve">8.40140056610107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39672088623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58393859863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34523582458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46224689483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3826789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47160816192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9864559173584</t>
+    <t xml:space="preserve">8.39671993255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5839376449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34523487091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46224784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38267803192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47160720825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98645687103271</t>
   </si>
   <si>
     <t xml:space="preserve">9.09878730773926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0613431930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51841259002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16269779205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31247234344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4419093132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98484182357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95675849914551</t>
+    <t xml:space="preserve">9.06134414672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51841068267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16269874572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31247138977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44190979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98484086990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95675897598267</t>
   </si>
   <si>
     <t xml:space="preserve">8.38735961914062</t>
@@ -602,37 +602,37 @@
     <t xml:space="preserve">8.4107608795166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44820404052734</t>
+    <t xml:space="preserve">8.44820499420166</t>
   </si>
   <si>
     <t xml:space="preserve">8.4809684753418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37331867218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2329044342041</t>
+    <t xml:space="preserve">8.37331771850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23290538787842</t>
   </si>
   <si>
     <t xml:space="preserve">8.1860990524292</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37799835205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57925701141357</t>
+    <t xml:space="preserve">8.37800025939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57925796508789</t>
   </si>
   <si>
     <t xml:space="preserve">8.64946460723877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72434997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67286777496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74307441711426</t>
+    <t xml:space="preserve">8.72435092926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67286586761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74307537078857</t>
   </si>
   <si>
     <t xml:space="preserve">8.71031093597412</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">9.26728343963623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33749103546143</t>
+    <t xml:space="preserve">9.33749008178711</t>
   </si>
   <si>
     <t xml:space="preserve">9.40769672393799</t>
@@ -659,28 +659,28 @@
     <t xml:space="preserve">9.37961387634277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29536628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3608922958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44513988494873</t>
+    <t xml:space="preserve">9.29536533355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36089324951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44514083862305</t>
   </si>
   <si>
     <t xml:space="preserve">9.48258304595947</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4357795715332</t>
+    <t xml:space="preserve">9.43578052520752</t>
   </si>
   <si>
     <t xml:space="preserve">9.35621166229248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11283016204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10814666748047</t>
+    <t xml:space="preserve">9.11282920837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10814762115479</t>
   </si>
   <si>
     <t xml:space="preserve">9.15963268280029</t>
@@ -689,28 +689,28 @@
     <t xml:space="preserve">9.46386241912842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81021499633789</t>
+    <t xml:space="preserve">9.81021595001221</t>
   </si>
   <si>
     <t xml:space="preserve">9.95998954772949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82893657684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91318511962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64171981811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70724487304688</t>
+    <t xml:space="preserve">9.82893562316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91318607330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6417179107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70724582672119</t>
   </si>
   <si>
     <t xml:space="preserve">9.71660614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66044044494629</t>
+    <t xml:space="preserve">9.66043949127197</t>
   </si>
   <si>
     <t xml:space="preserve">9.79149341583252</t>
@@ -737,64 +737,64 @@
     <t xml:space="preserve">10.4748382568359</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3625087738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3344240188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5778074264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5122814178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5029220581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8118314743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8867168426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7182207107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6526947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6433334350586</t>
+    <t xml:space="preserve">10.3625078201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3344259262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5778093338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5122804641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5029201507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8118305206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8867177963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7182216644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6526956558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6433343887329</t>
   </si>
   <si>
     <t xml:space="preserve">10.6246137619019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7088594436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8960790634155</t>
+    <t xml:space="preserve">10.7088603973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8960800170898</t>
   </si>
   <si>
     <t xml:space="preserve">10.8399143218994</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9335222244263</t>
+    <t xml:space="preserve">10.9335231781006</t>
   </si>
   <si>
     <t xml:space="preserve">10.9990482330322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1301012039185</t>
+    <t xml:space="preserve">11.1301021575928</t>
   </si>
   <si>
     <t xml:space="preserve">11.0926570892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2517938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9616050720215</t>
+    <t xml:space="preserve">11.2517929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9616041183472</t>
   </si>
   <si>
     <t xml:space="preserve">11.2049875259399</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">11.1862659454346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2798748016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4296503067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4109268188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4577312469482</t>
+    <t xml:space="preserve">11.2798738479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.429651260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.410927772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4577302932739</t>
   </si>
   <si>
     <t xml:space="preserve">11.5801239013672</t>
@@ -833,28 +833,28 @@
     <t xml:space="preserve">11.9472980499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9190559387207</t>
+    <t xml:space="preserve">11.9190549850464</t>
   </si>
   <si>
     <t xml:space="preserve">11.9284687042236</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9378833770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9661273956299</t>
+    <t xml:space="preserve">11.9378843307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9661264419556</t>
   </si>
   <si>
     <t xml:space="preserve">12.0602750778198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0979347229004</t>
+    <t xml:space="preserve">12.0979337692261</t>
   </si>
   <si>
     <t xml:space="preserve">12.0226163864136</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2109117507935</t>
+    <t xml:space="preserve">12.2109127044678</t>
   </si>
   <si>
     <t xml:space="preserve">12.1826667785645</t>
@@ -872,46 +872,46 @@
     <t xml:space="preserve">11.4859771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">11.297682762146</t>
+    <t xml:space="preserve">11.2976808547974</t>
   </si>
   <si>
     <t xml:space="preserve">11.6930999755859</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7307586669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7684183120728</t>
+    <t xml:space="preserve">11.7307596206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7684192657471</t>
   </si>
   <si>
     <t xml:space="preserve">11.7590026855469</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6271982192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5707101821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5236349105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4671478271484</t>
+    <t xml:space="preserve">11.627197265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5707092285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5236339569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4671468734741</t>
   </si>
   <si>
     <t xml:space="preserve">11.3729982376099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0811433792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.88343334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6951379776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5633325576782</t>
+    <t xml:space="preserve">11.0811424255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8834342956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6951370239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5633316040039</t>
   </si>
   <si>
     <t xml:space="preserve">10.6104078292847</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">10.9493370056152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1376295089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3541707992554</t>
+    <t xml:space="preserve">11.1376304626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3541698455811</t>
   </si>
   <si>
     <t xml:space="preserve">11.4577322006226</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">11.3824138641357</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3447542190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4106588363647</t>
+    <t xml:space="preserve">11.3447551727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4106578826904</t>
   </si>
   <si>
     <t xml:space="preserve">11.2694368362427</t>
@@ -959,25 +959,25 @@
     <t xml:space="preserve">11.3353395462036</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2788524627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2506084442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1093864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.034068107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9210929870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6668949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8363599777222</t>
+    <t xml:space="preserve">11.2788515090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2506074905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1093873977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0340690612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9210939407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6668939590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8363590240479</t>
   </si>
   <si>
     <t xml:space="preserve">10.78928565979</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">11.1941204071045</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1658744812012</t>
+    <t xml:space="preserve">11.1658754348755</t>
   </si>
   <si>
     <t xml:space="preserve">11.0717287063599</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1282148361206</t>
+    <t xml:space="preserve">11.1282157897949</t>
   </si>
   <si>
     <t xml:space="preserve">11.3165111541748</t>
@@ -1001,73 +1001,73 @@
     <t xml:space="preserve">11.3259248733521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.241192817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.062313079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.090558052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1752910614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4389019012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7213439941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8154935836792</t>
+    <t xml:space="preserve">11.2411918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0623121261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0905570983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1752901077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4389028549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7213449478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8154916763306</t>
   </si>
   <si>
     <t xml:space="preserve">11.984956741333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0132007598877</t>
+    <t xml:space="preserve">12.013201713562</t>
   </si>
   <si>
     <t xml:space="preserve">11.956711769104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0508604049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0414447784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0791053771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9755439758301</t>
+    <t xml:space="preserve">12.0508594512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.041446685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0791044235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9755430221558</t>
   </si>
   <si>
     <t xml:space="preserve">11.8343210220337</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2203245162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1544227600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.107349395752</t>
+    <t xml:space="preserve">12.220326423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1544218063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1073474884033</t>
   </si>
   <si>
     <t xml:space="preserve">12.4839391708374</t>
   </si>
   <si>
-    <t xml:space="preserve">12.521595954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.643988609314</t>
+    <t xml:space="preserve">12.5215978622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6439876556396</t>
   </si>
   <si>
     <t xml:space="preserve">12.7852096557617</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8134536743164</t>
+    <t xml:space="preserve">12.813455581665</t>
   </si>
   <si>
     <t xml:space="preserve">12.8322839736938</t>
@@ -1076,34 +1076,34 @@
     <t xml:space="preserve">12.8040409088135</t>
   </si>
   <si>
-    <t xml:space="preserve">12.192081451416</t>
+    <t xml:space="preserve">12.1920824050903</t>
   </si>
   <si>
     <t xml:space="preserve">11.7872486114502</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8531513214111</t>
+    <t xml:space="preserve">11.8531503677368</t>
   </si>
   <si>
     <t xml:space="preserve">12.0320301055908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1732511520386</t>
+    <t xml:space="preserve">12.1732521057129</t>
   </si>
   <si>
     <t xml:space="preserve">12.2768135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9002246856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4483156204224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5612945556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4012441635132</t>
+    <t xml:space="preserve">11.9002256393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.448317527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5612936019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4012432098389</t>
   </si>
   <si>
     <t xml:space="preserve">11.6742696762085</t>
@@ -1118,40 +1118,40 @@
     <t xml:space="preserve">12.0696887969971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2014961242676</t>
+    <t xml:space="preserve">12.2014970779419</t>
   </si>
   <si>
     <t xml:space="preserve">12.1355934143066</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3615455627441</t>
+    <t xml:space="preserve">12.3615465164185</t>
   </si>
   <si>
     <t xml:space="preserve">12.3333024978638</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1638374328613</t>
+    <t xml:space="preserve">12.163836479187</t>
   </si>
   <si>
     <t xml:space="preserve">11.7401742935181</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1261787414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5404262542725</t>
+    <t xml:space="preserve">12.1261777877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5404272079468</t>
   </si>
   <si>
     <t xml:space="preserve">12.549840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5027675628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6345729827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1335535049438</t>
+    <t xml:space="preserve">12.5027685165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6345739364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1335544586182</t>
   </si>
   <si>
     <t xml:space="preserve">13.1241397857666</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">13.0864820480347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9546756744385</t>
+    <t xml:space="preserve">12.9546747207642</t>
   </si>
   <si>
     <t xml:space="preserve">13.4254112243652</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">13.4630708694458</t>
   </si>
   <si>
-    <t xml:space="preserve">13.538387298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5572175979614</t>
+    <t xml:space="preserve">13.5383882522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5572156906128</t>
   </si>
   <si>
     <t xml:space="preserve">13.6042919158936</t>
@@ -1181,10 +1181,10 @@
     <t xml:space="preserve">13.5101451873779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2559461593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4724864959717</t>
+    <t xml:space="preserve">13.2559452056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4724855422974</t>
   </si>
   <si>
     <t xml:space="preserve">13.3030204772949</t>
@@ -1196,34 +1196,34 @@
     <t xml:space="preserve">12.6157445907593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4086198806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3803739547729</t>
+    <t xml:space="preserve">12.4086208343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3803758621216</t>
   </si>
   <si>
     <t xml:space="preserve">12.46510887146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5121822357178</t>
+    <t xml:space="preserve">12.5121831893921</t>
   </si>
   <si>
     <t xml:space="preserve">12.822868347168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.879358291626</t>
+    <t xml:space="preserve">12.8793563842773</t>
   </si>
   <si>
     <t xml:space="preserve">12.8511123657227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5969161987305</t>
+    <t xml:space="preserve">12.5969152450562</t>
   </si>
   <si>
     <t xml:space="preserve">12.286229133606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2579860687256</t>
+    <t xml:space="preserve">12.257984161377</t>
   </si>
   <si>
     <t xml:space="preserve">12.7287216186523</t>
@@ -1232,28 +1232,28 @@
     <t xml:space="preserve">13.0394077301025</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0958967208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2653608322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4065828323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3312635421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3218479156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1617994308472</t>
+    <t xml:space="preserve">13.0958976745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.26535987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4065818786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3312644958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3218488693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1617984771729</t>
   </si>
   <si>
     <t xml:space="preserve">13.3406782150269</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2465314865112</t>
+    <t xml:space="preserve">13.2465305328369</t>
   </si>
   <si>
     <t xml:space="preserve">12.8887710571289</t>
@@ -1265,40 +1265,40 @@
     <t xml:space="preserve">13.2936058044434</t>
   </si>
   <si>
-    <t xml:space="preserve">13.566632270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6419496536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3124351501465</t>
+    <t xml:space="preserve">13.5666313171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6419506072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3124361038208</t>
   </si>
   <si>
     <t xml:space="preserve">13.7925872802734</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9997110366821</t>
+    <t xml:space="preserve">13.9997100830078</t>
   </si>
   <si>
     <t xml:space="preserve">14.1409320831299</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3951292037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3009834289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5645952224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6022529602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6869859695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9129400253296</t>
+    <t xml:space="preserve">14.3951301574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3009815216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5645942687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6022539138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6869878768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9129409790039</t>
   </si>
   <si>
     <t xml:space="preserve">14.8564500808716</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">15.1106491088867</t>
   </si>
   <si>
-    <t xml:space="preserve">14.969428062439</t>
+    <t xml:space="preserve">14.9694290161133</t>
   </si>
   <si>
     <t xml:space="preserve">14.997673034668</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0353317260742</t>
+    <t xml:space="preserve">15.0353307723999</t>
   </si>
   <si>
     <t xml:space="preserve">14.903525352478</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">14.7152299880981</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5928392410278</t>
+    <t xml:space="preserve">14.5928382873535</t>
   </si>
   <si>
     <t xml:space="preserve">15.1671380996704</t>
@@ -1340,22 +1340,22 @@
     <t xml:space="preserve">15.2518720626831</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4401655197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3930902481079</t>
+    <t xml:space="preserve">15.4401636123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3930912017822</t>
   </si>
   <si>
     <t xml:space="preserve">15.5531425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6567001342773</t>
+    <t xml:space="preserve">15.6567029953003</t>
   </si>
   <si>
     <t xml:space="preserve">15.4213342666626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0165004730225</t>
+    <t xml:space="preserve">15.0165014266968</t>
   </si>
   <si>
     <t xml:space="preserve">15.3460168838501</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">14.6099481582642</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7332000732422</t>
+    <t xml:space="preserve">14.7331991195679</t>
   </si>
   <si>
     <t xml:space="preserve">14.8754119873047</t>
@@ -1394,49 +1394,49 @@
     <t xml:space="preserve">15.1882801055908</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4916658401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1173992156982</t>
+    <t xml:space="preserve">15.4916667938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1174011230469</t>
   </si>
   <si>
     <t xml:space="preserve">16.4587097167969</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1553230285645</t>
+    <t xml:space="preserve">16.1553249359131</t>
   </si>
   <si>
     <t xml:space="preserve">16.1648044586182</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2027263641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2122077941895</t>
+    <t xml:space="preserve">16.202730178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2122097015381</t>
   </si>
   <si>
     <t xml:space="preserve">16.3259773254395</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1079177856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.069995880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5250778198242</t>
+    <t xml:space="preserve">16.1079196929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0699977874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5250759124756</t>
   </si>
   <si>
     <t xml:space="preserve">16.7241706848145</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6672878265381</t>
+    <t xml:space="preserve">16.6672859191895</t>
   </si>
   <si>
     <t xml:space="preserve">16.5724811553955</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3070163726807</t>
+    <t xml:space="preserve">16.3070182800293</t>
   </si>
   <si>
     <t xml:space="preserve">16.2596130371094</t>
@@ -1445,13 +1445,13 @@
     <t xml:space="preserve">16.6767692565918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8379421234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.885347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0465221405029</t>
+    <t xml:space="preserve">16.8379440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8853454589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0465202331543</t>
   </si>
   <si>
     <t xml:space="preserve">16.9232711791992</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">16.7715759277344</t>
   </si>
   <si>
-    <t xml:space="preserve">16.373384475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4492282867432</t>
+    <t xml:space="preserve">16.3733825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4492301940918</t>
   </si>
   <si>
     <t xml:space="preserve">16.2216892242432</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">16.3639011383057</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5155963897705</t>
+    <t xml:space="preserve">16.5155944824219</t>
   </si>
   <si>
     <t xml:space="preserve">17.1034069061279</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">17.5395240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9471969604492</t>
+    <t xml:space="preserve">17.9472007751465</t>
   </si>
   <si>
     <t xml:space="preserve">17.4447154998779</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">18.0799293518066</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1652603149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.715145111084</t>
+    <t xml:space="preserve">18.1652584075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7151470184326</t>
   </si>
   <si>
     <t xml:space="preserve">18.1368141174316</t>
@@ -1511,16 +1511,16 @@
     <t xml:space="preserve">18.2505855560303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0704517364502</t>
+    <t xml:space="preserve">18.0704498291016</t>
   </si>
   <si>
     <t xml:space="preserve">17.8618717193604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6343326568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7860240936279</t>
+    <t xml:space="preserve">17.634334564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7860260009766</t>
   </si>
   <si>
     <t xml:space="preserve">17.7575817108154</t>
@@ -1532,37 +1532,37 @@
     <t xml:space="preserve">18.3738346099854</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2031841278076</t>
+    <t xml:space="preserve">18.203182220459</t>
   </si>
   <si>
     <t xml:space="preserve">18.032527923584</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1083755493164</t>
+    <t xml:space="preserve">18.1083717346191</t>
   </si>
   <si>
     <t xml:space="preserve">18.2126617431641</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0609683990479</t>
+    <t xml:space="preserve">18.0609664916992</t>
   </si>
   <si>
     <t xml:space="preserve">17.9377193450928</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0040817260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.577449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3927993774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8334293365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0135650634766</t>
+    <t xml:space="preserve">18.0040836334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5774478912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3927974700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8334274291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0135631561279</t>
   </si>
   <si>
     <t xml:space="preserve">18.7435874938965</t>
@@ -1574,16 +1574,16 @@
     <t xml:space="preserve">19.41672706604</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3788051605225</t>
+    <t xml:space="preserve">19.3788032531738</t>
   </si>
   <si>
     <t xml:space="preserve">19.1891860961914</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0564575195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7246265411377</t>
+    <t xml:space="preserve">19.056453704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7246284484863</t>
   </si>
   <si>
     <t xml:space="preserve">18.4496822357178</t>
@@ -1592,43 +1592,43 @@
     <t xml:space="preserve">18.5255317687988</t>
   </si>
   <si>
-    <t xml:space="preserve">18.772029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9616451263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6867008209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.146297454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5065689086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0420093536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3025035858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5629978179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.453742980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5864753723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.671802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0081434249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4253005981445</t>
+    <t xml:space="preserve">18.7720317840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9616470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6867027282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1462955474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5065670013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0420112609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3025054931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5629997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4537420272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5864763259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6718034744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0081424713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4253015518188</t>
   </si>
   <si>
     <t xml:space="preserve">15.4632234573364</t>
@@ -1637,28 +1637,28 @@
     <t xml:space="preserve">15.8045349121094</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7286863327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9512586593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0745096206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9986629486084</t>
+    <t xml:space="preserve">15.7286853790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9512596130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0745086669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9986639022827</t>
   </si>
   <si>
     <t xml:space="preserve">14.9797010421753</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0176239013672</t>
+    <t xml:space="preserve">15.0176258087158</t>
   </si>
   <si>
     <t xml:space="preserve">14.8469696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6573524475098</t>
+    <t xml:space="preserve">14.6573543548584</t>
   </si>
   <si>
     <t xml:space="preserve">14.7047576904297</t>
@@ -1673,13 +1673,13 @@
     <t xml:space="preserve">14.932297706604</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0555477142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7900857925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8135604858398</t>
+    <t xml:space="preserve">15.0555486679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7900848388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8135595321655</t>
   </si>
   <si>
     <t xml:space="preserve">13.728232383728</t>
@@ -1700,55 +1700,55 @@
     <t xml:space="preserve">13.3964042663574</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6523857116699</t>
+    <t xml:space="preserve">13.6523866653442</t>
   </si>
   <si>
     <t xml:space="preserve">13.4912118911743</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2257499694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8704462051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0126581192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4961786270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2212352752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1643495559692</t>
+    <t xml:space="preserve">13.2257490158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8704452514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0126571655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4961795806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2212362289429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1643505096436</t>
   </si>
   <si>
     <t xml:space="preserve">14.3065633773804</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3350057601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7945976257324</t>
+    <t xml:space="preserve">14.3350048065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7945985794067</t>
   </si>
   <si>
     <t xml:space="preserve">13.7377138137817</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5955018997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7566766738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8988876342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9462909698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4203329086304</t>
+    <t xml:space="preserve">13.5955009460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7566747665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8988885879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9462919235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4203338623047</t>
   </si>
   <si>
     <t xml:space="preserve">13.7756366729736</t>
@@ -1760,37 +1760,37 @@
     <t xml:space="preserve">13.3205575942993</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1878261566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7471952438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.069540977478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8374881744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2546453475952</t>
+    <t xml:space="preserve">13.1878252029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7471942901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0695419311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8374900817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2546443939209</t>
   </si>
   <si>
     <t xml:space="preserve">14.8848924636841</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0839900970459</t>
+    <t xml:space="preserve">15.0839910507202</t>
   </si>
   <si>
     <t xml:space="preserve">15.1787996292114</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1503562927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3115301132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3589353561401</t>
+    <t xml:space="preserve">15.1503572463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3115310668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3589334487915</t>
   </si>
   <si>
     <t xml:space="preserve">15.2925682067871</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">15.1408758163452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0271053314209</t>
+    <t xml:space="preserve">15.0271062850952</t>
   </si>
   <si>
     <t xml:space="preserve">14.9228162765503</t>
@@ -1808,28 +1808,28 @@
     <t xml:space="preserve">14.8280086517334</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8659324645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9417772293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.614914894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7097244262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0650291442871</t>
+    <t xml:space="preserve">14.8659315109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9417791366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.614917755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7097253799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0650300979614</t>
   </si>
   <si>
     <t xml:space="preserve">15.216721534729</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5485506057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4347820281982</t>
+    <t xml:space="preserve">15.5485496520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4347801208496</t>
   </si>
   <si>
     <t xml:space="preserve">15.396858215332</t>
@@ -1838,76 +1838,76 @@
     <t xml:space="preserve">14.7806043624878</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9038553237915</t>
+    <t xml:space="preserve">14.9038562774658</t>
   </si>
   <si>
     <t xml:space="preserve">15.2262020111084</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1977605819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.444263458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3684158325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5106287002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.738166809082</t>
+    <t xml:space="preserve">15.1977615356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4442644119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3684148788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.510627746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7381658554077</t>
   </si>
   <si>
     <t xml:space="preserve">16.430269241333</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9657077789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2641267776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.785572052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6862506866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8474235534668</t>
+    <t xml:space="preserve">15.9657068252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2641277313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.785569190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6862487792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8474254608154</t>
   </si>
   <si>
     <t xml:space="preserve">16.4966335296631</t>
   </si>
   <si>
-    <t xml:space="preserve">16.193244934082</t>
+    <t xml:space="preserve">16.1932468414307</t>
   </si>
   <si>
     <t xml:space="preserve">16.2311687469482</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7526149749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4207878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8094997406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7336521148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8948307037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8663883209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.250129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8993434906006</t>
+    <t xml:space="preserve">16.7526168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4207859039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8095016479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7336540222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8948287963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8663864135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2501335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8993425369263</t>
   </si>
   <si>
     <t xml:space="preserve">15.8898620605469</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">16.240650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9183034896851</t>
+    <t xml:space="preserve">15.9183025360107</t>
   </si>
   <si>
     <t xml:space="preserve">17.5016002655029</t>
@@ -1934,13 +1934,13 @@
     <t xml:space="preserve">17.6627750396729</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0894107818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3119850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2835388183594</t>
+    <t xml:space="preserve">18.089412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3119831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.283540725708</t>
   </si>
   <si>
     <t xml:space="preserve">17.8239479064941</t>
@@ -1949,34 +1949,34 @@
     <t xml:space="preserve">18.6677436828613</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5743808746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8704261779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5962104797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5007133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9277267456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9468250274658</t>
+    <t xml:space="preserve">18.5743846893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8704280853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.596212387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5007152557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9277248382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9468269348145</t>
   </si>
   <si>
     <t xml:space="preserve">18.9850234985352</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5934791564941</t>
+    <t xml:space="preserve">18.5934829711914</t>
   </si>
   <si>
     <t xml:space="preserve">18.708080291748</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9659271240234</t>
+    <t xml:space="preserve">18.9659252166748</t>
   </si>
   <si>
     <t xml:space="preserve">19.0327739715576</t>
@@ -1985,16 +1985,16 @@
     <t xml:space="preserve">19.2333183288574</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3861179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0900726318359</t>
+    <t xml:space="preserve">19.3861141204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0900707244873</t>
   </si>
   <si>
     <t xml:space="preserve">19.1951217651367</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1187229156494</t>
+    <t xml:space="preserve">19.118724822998</t>
   </si>
   <si>
     <t xml:space="preserve">19.252420425415</t>
@@ -2006,10 +2006,10 @@
     <t xml:space="preserve">20.1501026153564</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2646980285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.589391708374</t>
+    <t xml:space="preserve">20.2646999359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5893936157227</t>
   </si>
   <si>
     <t xml:space="preserve">20.5511932373047</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">20.799488067627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9591045379639</t>
+    <t xml:space="preserve">19.9591064453125</t>
   </si>
   <si>
     <t xml:space="preserve">19.8445091247559</t>
@@ -2027,67 +2027,67 @@
     <t xml:space="preserve">19.4816150665283</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3097171783447</t>
+    <t xml:space="preserve">19.3097190856934</t>
   </si>
   <si>
     <t xml:space="preserve">19.6344108581543</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6726093292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0928020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9400062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6535129547119</t>
+    <t xml:space="preserve">19.6726131439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0928039550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9400043487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6535110473633</t>
   </si>
   <si>
     <t xml:space="preserve">19.5580139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">19.729907989502</t>
+    <t xml:space="preserve">19.7299098968506</t>
   </si>
   <si>
     <t xml:space="preserve">20.3028984069824</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2837963104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2264976501465</t>
+    <t xml:space="preserve">20.2837982177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2265014648438</t>
   </si>
   <si>
     <t xml:space="preserve">20.7039909362793</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6848888397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4174938201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0355014801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1310005187988</t>
+    <t xml:space="preserve">20.6848907470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4174957275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0355033874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1310024261475</t>
   </si>
   <si>
     <t xml:space="preserve">20.1882991790771</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2769794464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1814804077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.436595916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0164051055908</t>
+    <t xml:space="preserve">21.2769813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1814823150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4365940093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0164031982422</t>
   </si>
   <si>
     <t xml:space="preserve">20.5702953338623</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">20.9904842376709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1050834655762</t>
+    <t xml:space="preserve">21.1050815582275</t>
   </si>
   <si>
     <t xml:space="preserve">21.1623802185059</t>
@@ -2105,43 +2105,43 @@
     <t xml:space="preserve">21.2578792572021</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0286865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2960796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.849967956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4802570343018</t>
+    <t xml:space="preserve">21.0286846160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2960777282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8499660491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4802551269531</t>
   </si>
   <si>
     <t xml:space="preserve">22.5566558837891</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5184555053711</t>
+    <t xml:space="preserve">22.5184574127197</t>
   </si>
   <si>
     <t xml:space="preserve">22.0982627868652</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2510604858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9645652770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9454669952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3083610534668</t>
+    <t xml:space="preserve">22.2510585784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9645671844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9454650878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3083591461182</t>
   </si>
   <si>
     <t xml:space="preserve">22.5948524475098</t>
   </si>
   <si>
-    <t xml:space="preserve">22.747652053833</t>
+    <t xml:space="preserve">22.7476501464844</t>
   </si>
   <si>
     <t xml:space="preserve">22.8049488067627</t>
@@ -2153,10 +2153,10 @@
     <t xml:space="preserve">22.2319602966309</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3533782958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.474796295166</t>
+    <t xml:space="preserve">21.3533763885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4747943878174</t>
   </si>
   <si>
     <t xml:space="preserve">20.455696105957</t>
@@ -2165,10 +2165,10 @@
     <t xml:space="preserve">21.1241836547852</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7803859710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8758850097656</t>
+    <t xml:space="preserve">20.780387878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8758888244629</t>
   </si>
   <si>
     <t xml:space="preserve">21.0859832763672</t>
@@ -2180,64 +2180,64 @@
     <t xml:space="preserve">21.506175994873</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2196788787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3724765777588</t>
+    <t xml:space="preserve">21.2196807861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3724784851074</t>
   </si>
   <si>
     <t xml:space="preserve">21.6016731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">21.678071975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4870777130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5825748443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.646692276001</t>
+    <t xml:space="preserve">21.6780738830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4870738983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5825729370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6466941833496</t>
   </si>
   <si>
     <t xml:space="preserve">20.608491897583</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4938926696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8567848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3792991638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8949871063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9331874847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3219966888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3410987854004</t>
+    <t xml:space="preserve">20.4938945770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8567886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3792972564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8949851989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9331855773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.32200050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3410968780518</t>
   </si>
   <si>
     <t xml:space="preserve">21.8308696746826</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0218677520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5375537872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6521530151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0150451660156</t>
+    <t xml:space="preserve">22.0218658447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5375518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6521511077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0150470733643</t>
   </si>
   <si>
     <t xml:space="preserve">23.4543361663818</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">23.7217311859131</t>
   </si>
   <si>
-    <t xml:space="preserve">23.912727355957</t>
+    <t xml:space="preserve">23.9127292633057</t>
   </si>
   <si>
     <t xml:space="preserve">23.5689353942871</t>
@@ -2255,13 +2255,13 @@
     <t xml:space="preserve">24.084623336792</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7981300354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8745269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9700241088867</t>
+    <t xml:space="preserve">23.7981281280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8745288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.970027923584</t>
   </si>
   <si>
     <t xml:space="preserve">24.3711185455322</t>
@@ -2273,34 +2273,34 @@
     <t xml:space="preserve">25.09690284729</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3642978668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3329181671143</t>
+    <t xml:space="preserve">25.3642997741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3329200744629</t>
   </si>
   <si>
     <t xml:space="preserve">24.9823055267334</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2878971099854</t>
+    <t xml:space="preserve">25.287899017334</t>
   </si>
   <si>
     <t xml:space="preserve">24.9250068664551</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0205059051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6194133758545</t>
+    <t xml:space="preserve">25.0205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6194152832031</t>
   </si>
   <si>
     <t xml:space="preserve">24.9441089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8295097351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6385116577148</t>
+    <t xml:space="preserve">24.8295078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6385135650635</t>
   </si>
   <si>
     <t xml:space="preserve">24.4475173950195</t>
@@ -2309,7 +2309,7 @@
     <t xml:space="preserve">24.5430145263672</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3520183563232</t>
+    <t xml:space="preserve">24.3520164489746</t>
   </si>
   <si>
     <t xml:space="preserve">24.6576118469238</t>
@@ -2318,46 +2318,46 @@
     <t xml:space="preserve">24.6767120361328</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4857158660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5621128082275</t>
+    <t xml:space="preserve">24.4857139587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5621166229248</t>
   </si>
   <si>
     <t xml:space="preserve">24.5812149047852</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6958103179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.306999206543</t>
+    <t xml:space="preserve">24.6958122253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3070011138916</t>
   </si>
   <si>
     <t xml:space="preserve">25.3451995849609</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8486099243164</t>
+    <t xml:space="preserve">24.8486080169678</t>
   </si>
   <si>
     <t xml:space="preserve">25.0014057159424</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2115020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7653903961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6125926971436</t>
+    <t xml:space="preserve">25.2115039825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7653923034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6125946044922</t>
   </si>
   <si>
     <t xml:space="preserve">25.5552940368652</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1541996002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8226890563965</t>
+    <t xml:space="preserve">25.1542015075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8226909637451</t>
   </si>
   <si>
     <t xml:space="preserve">24.7722110748291</t>
@@ -2369,28 +2369,28 @@
     <t xml:space="preserve">24.9059066772461</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6698913574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2237815856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2810802459717</t>
+    <t xml:space="preserve">25.6698932647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2237796783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.281078338623</t>
   </si>
   <si>
     <t xml:space="preserve">26.395679473877</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1405658721924</t>
+    <t xml:space="preserve">27.1405639648438</t>
   </si>
   <si>
     <t xml:space="preserve">27.2169628143311</t>
   </si>
   <si>
-    <t xml:space="preserve">27.522554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6944541931152</t>
+    <t xml:space="preserve">27.5225563049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6944522857666</t>
   </si>
   <si>
     <t xml:space="preserve">27.8281497955322</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">28.2865409851074</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8854484558105</t>
+    <t xml:space="preserve">27.8854503631592</t>
   </si>
   <si>
     <t xml:space="preserve">25.9754848480225</t>
@@ -2417,13 +2417,13 @@
     <t xml:space="preserve">24.6003112792969</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6071300506592</t>
+    <t xml:space="preserve">23.6071338653564</t>
   </si>
   <si>
     <t xml:space="preserve">24.4666156768799</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4352378845215</t>
+    <t xml:space="preserve">23.4352359771729</t>
   </si>
   <si>
     <t xml:space="preserve">19.8254089355469</t>
@@ -2435,34 +2435,34 @@
     <t xml:space="preserve">15.5852928161621</t>
   </si>
   <si>
-    <t xml:space="preserve">17.323356628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7285375595093</t>
+    <t xml:space="preserve">17.3233585357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7285404205322</t>
   </si>
   <si>
     <t xml:space="preserve">16.1200790405273</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9031677246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5239028930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7435512542725</t>
+    <t xml:space="preserve">16.9031658172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.523904800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7435493469238</t>
   </si>
   <si>
     <t xml:space="preserve">18.1350898742676</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8322296142578</t>
+    <t xml:space="preserve">18.8322277069092</t>
   </si>
   <si>
     <t xml:space="preserve">18.1446418762207</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2210388183594</t>
+    <t xml:space="preserve">18.221040725708</t>
   </si>
   <si>
     <t xml:space="preserve">18.1159915924072</t>
@@ -2474,61 +2474,61 @@
     <t xml:space="preserve">17.3806591033936</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4093036651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8076686859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6480541229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7844791412354</t>
+    <t xml:space="preserve">17.4093055725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8076667785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6480522155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7844772338867</t>
   </si>
   <si>
     <t xml:space="preserve">18.4311351776123</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4454612731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7653770446777</t>
+    <t xml:space="preserve">18.4454593658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7653789520264</t>
   </si>
   <si>
     <t xml:space="preserve">17.9536437988281</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8663368225098</t>
+    <t xml:space="preserve">20.866340637207</t>
   </si>
   <si>
     <t xml:space="preserve">19.271520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8465538024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0068550109863</t>
+    <t xml:space="preserve">18.8465518951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0068531036377</t>
   </si>
   <si>
     <t xml:space="preserve">20.2455997467041</t>
   </si>
   <si>
-    <t xml:space="preserve">19.987756729126</t>
+    <t xml:space="preserve">19.9877548217773</t>
   </si>
   <si>
     <t xml:space="preserve">19.968656539917</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7681083679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6753406524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7640209197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3820266723633</t>
+    <t xml:space="preserve">19.7681121826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6753425598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7640190124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3820247650146</t>
   </si>
   <si>
     <t xml:space="preserve">22.337007522583</t>
@@ -2537,43 +2537,43 @@
     <t xml:space="preserve">21.7926692962646</t>
   </si>
   <si>
-    <t xml:space="preserve">21.019136428833</t>
+    <t xml:space="preserve">21.0191345214844</t>
   </si>
   <si>
     <t xml:space="preserve">21.4297771453857</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8595161437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9522857666016</t>
+    <t xml:space="preserve">21.8595199584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9522876739502</t>
   </si>
   <si>
     <t xml:space="preserve">21.9932155609131</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6589736938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0341453552246</t>
+    <t xml:space="preserve">21.658971786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.034143447876</t>
   </si>
   <si>
     <t xml:space="preserve">23.1391906738281</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2797088623047</t>
+    <t xml:space="preserve">22.2797107696533</t>
   </si>
   <si>
     <t xml:space="preserve">23.502082824707</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8267803192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.521183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8458805084229</t>
+    <t xml:space="preserve">23.8267784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5211849212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8458786010742</t>
   </si>
   <si>
     <t xml:space="preserve">23.8172302246094</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">23.3588371276855</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6903514862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6330547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8881683349609</t>
+    <t xml:space="preserve">22.6903533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6330528259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8881664276123</t>
   </si>
   <si>
     <t xml:space="preserve">22.0696144104004</t>
@@ -2600,28 +2600,28 @@
     <t xml:space="preserve">22.938648223877</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3015403747559</t>
+    <t xml:space="preserve">23.3015384674072</t>
   </si>
   <si>
     <t xml:space="preserve">22.6808013916016</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7094535827637</t>
+    <t xml:space="preserve">22.709451675415</t>
   </si>
   <si>
     <t xml:space="preserve">23.1487426757812</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4638843536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4229545593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4611568450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6426010131836</t>
+    <t xml:space="preserve">23.463888168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4229564666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4611587524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6426029205322</t>
   </si>
   <si>
     <t xml:space="preserve">22.7381000518799</t>
@@ -2630,10 +2630,10 @@
     <t xml:space="preserve">23.2728900909424</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2442398071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.540283203125</t>
+    <t xml:space="preserve">23.2442417144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5402851104736</t>
   </si>
   <si>
     <t xml:space="preserve">23.7408313751221</t>
@@ -2642,10 +2642,10 @@
     <t xml:space="preserve">23.8363285064697</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7121829986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7599315643311</t>
+    <t xml:space="preserve">23.7121810913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7599296569824</t>
   </si>
   <si>
     <t xml:space="preserve">24.1610202789307</t>
@@ -2663,13 +2663,13 @@
     <t xml:space="preserve">25.0682544708252</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0587024688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7531108856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.135103225708</t>
+    <t xml:space="preserve">25.0587043762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7531127929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1351013183594</t>
   </si>
   <si>
     <t xml:space="preserve">26.5580253601074</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">27.6467037200928</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2292423248291</t>
+    <t xml:space="preserve">28.2292404174805</t>
   </si>
   <si>
     <t xml:space="preserve">27.5034561157227</t>
@@ -2690,10 +2690,10 @@
     <t xml:space="preserve">27.5894050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1596622467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5512046813965</t>
+    <t xml:space="preserve">27.1596641540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5512065887451</t>
   </si>
   <si>
     <t xml:space="preserve">27.0164165496826</t>
@@ -2717,31 +2717,31 @@
     <t xml:space="preserve">26.5675754547119</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0450668334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7108211517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5007266998291</t>
+    <t xml:space="preserve">27.0450649261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.710823059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5007247924805</t>
   </si>
   <si>
     <t xml:space="preserve">26.4529800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6630744934082</t>
+    <t xml:space="preserve">26.6630725860596</t>
   </si>
   <si>
     <t xml:space="preserve">26.5389270782471</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2619819641113</t>
+    <t xml:space="preserve">26.26198387146</t>
   </si>
   <si>
     <t xml:space="preserve">26.4625263214111</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5989551544189</t>
+    <t xml:space="preserve">27.5989532470703</t>
   </si>
   <si>
     <t xml:space="preserve">26.6726245880127</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">26.7585735321045</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3888607025146</t>
+    <t xml:space="preserve">27.388858795166</t>
   </si>
   <si>
     <t xml:space="preserve">27.4461574554443</t>
@@ -2771,16 +2771,16 @@
     <t xml:space="preserve">28.7926807403564</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6971836090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5798568725586</t>
+    <t xml:space="preserve">28.6971797943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5798530578613</t>
   </si>
   <si>
     <t xml:space="preserve">27.6562519073486</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4748058319092</t>
+    <t xml:space="preserve">27.4748077392578</t>
   </si>
   <si>
     <t xml:space="preserve">27.6849021911621</t>
@@ -2798,19 +2798,19 @@
     <t xml:space="preserve">29.4802684783936</t>
   </si>
   <si>
-    <t xml:space="preserve">29.833610534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0246067047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1651229858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3274707794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8049621582031</t>
+    <t xml:space="preserve">29.8336124420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0246086120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1651248931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3274688720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8049602508545</t>
   </si>
   <si>
     <t xml:space="preserve">30.4734477996826</t>
@@ -2825,13 +2825,13 @@
     <t xml:space="preserve">30.5402946472168</t>
   </si>
   <si>
-    <t xml:space="preserve">30.922290802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7408409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9318370819092</t>
+    <t xml:space="preserve">30.9222888946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7408428192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9318389892578</t>
   </si>
   <si>
     <t xml:space="preserve">30.7217407226562</t>
@@ -2843,10 +2843,10 @@
     <t xml:space="preserve">30.8172397613525</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4829959869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5593948364258</t>
+    <t xml:space="preserve">30.4829978942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.559398651123</t>
   </si>
   <si>
     <t xml:space="preserve">28.7258319854736</t>
@@ -2858,10 +2858,10 @@
     <t xml:space="preserve">30.903190612793</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9918689727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8991012573242</t>
+    <t xml:space="preserve">31.9918651580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.899097442627</t>
   </si>
   <si>
     <t xml:space="preserve">33.6535415649414</t>
@@ -2870,55 +2870,55 @@
     <t xml:space="preserve">33.309741973877</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4693565368652</t>
+    <t xml:space="preserve">32.4693603515625</t>
   </si>
   <si>
     <t xml:space="preserve">33.3288421630859</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5580368041992</t>
+    <t xml:space="preserve">33.5580406188965</t>
   </si>
   <si>
     <t xml:space="preserve">34.1310272216797</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4338874816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8158798217773</t>
+    <t xml:space="preserve">33.4338912963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4461708068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8158836364746</t>
   </si>
   <si>
     <t xml:space="preserve">33.9304809570312</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6603546142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6699066162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8513488769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5143775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6098747253418</t>
+    <t xml:space="preserve">32.6603584289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6699028015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8513526916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5143756866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6098728179932</t>
   </si>
   <si>
     <t xml:space="preserve">31.9727668762207</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7367477416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0587196350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2565307617188</t>
+    <t xml:space="preserve">32.7367515563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0587158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2565326690674</t>
   </si>
   <si>
     <t xml:space="preserve">30.8840885162354</t>
@@ -2927,10 +2927,10 @@
     <t xml:space="preserve">31.0177879333496</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1323852539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8745403289795</t>
+    <t xml:space="preserve">31.1323833465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8745384216309</t>
   </si>
   <si>
     <t xml:space="preserve">31.0846347808838</t>
@@ -2939,31 +2939,31 @@
     <t xml:space="preserve">31.6194248199463</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0969161987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3615779876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1542091369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9441242218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4216079711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6958198547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2115173339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7435760498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2783584594727</t>
+    <t xml:space="preserve">32.0969123840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3615818023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1542129516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9441184997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4216117858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.695821762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2115097045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7435779571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2783622741699</t>
   </si>
   <si>
     <t xml:space="preserve">32.5075569152832</t>
@@ -2972,13 +2972,13 @@
     <t xml:space="preserve">32.4120559692383</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0491676330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5334739685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2087821960449</t>
+    <t xml:space="preserve">32.0491714477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5334777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2087841033936</t>
   </si>
   <si>
     <t xml:space="preserve">32.3165588378906</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">32.3834114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6221504211426</t>
+    <t xml:space="preserve">32.6221542358398</t>
   </si>
   <si>
     <t xml:space="preserve">32.650806427002</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">32.803596496582</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5839500427246</t>
+    <t xml:space="preserve">32.5839538574219</t>
   </si>
   <si>
     <t xml:space="preserve">32.3547592163086</t>
@@ -3017,28 +3017,28 @@
     <t xml:space="preserve">32.5648574829102</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3261108398438</t>
+    <t xml:space="preserve">32.326114654541</t>
   </si>
   <si>
     <t xml:space="preserve">31.9250202178955</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0423469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7967758178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5989646911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4843711853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.942756652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8854560852051</t>
+    <t xml:space="preserve">33.042350769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7967796325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5989608764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4843673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9427604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8854598999023</t>
   </si>
   <si>
     <t xml:space="preserve">35.000057220459</t>
@@ -3056,19 +3056,19 @@
     <t xml:space="preserve">34.2551727294922</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9018249511719</t>
+    <t xml:space="preserve">33.9018287658691</t>
   </si>
   <si>
     <t xml:space="preserve">33.3670387268066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3192939758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7817726135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8104209899902</t>
+    <t xml:space="preserve">33.3192901611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7817707061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8104190826416</t>
   </si>
   <si>
     <t xml:space="preserve">32.4598083496094</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">32.7081031799316</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9768581390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4898166656494</t>
+    <t xml:space="preserve">29.9768562316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4898147583008</t>
   </si>
   <si>
     <t xml:space="preserve">28.6876354217529</t>
@@ -3089,10 +3089,10 @@
     <t xml:space="preserve">29.0027770996094</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3874988555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6453437805176</t>
+    <t xml:space="preserve">30.3875007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6453418731689</t>
   </si>
   <si>
     <t xml:space="preserve">31.4761772155762</t>
@@ -3104,7 +3104,7 @@
     <t xml:space="preserve">30.7312927246094</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1228370666504</t>
+    <t xml:space="preserve">31.1228351593018</t>
   </si>
   <si>
     <t xml:space="preserve">30.5498466491699</t>
@@ -3122,34 +3122,34 @@
     <t xml:space="preserve">30.4065990447998</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7694931030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6644439697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3111000061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9413909912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2756309509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9604892730713</t>
+    <t xml:space="preserve">30.7694911956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6644458770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3111019134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9413871765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2756328582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9604873657227</t>
   </si>
   <si>
     <t xml:space="preserve">31.5812244415283</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3424816131592</t>
+    <t xml:space="preserve">31.3424797058105</t>
   </si>
   <si>
     <t xml:space="preserve">33.5007400512695</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9373054504395</t>
+    <t xml:space="preserve">32.9373016357422</t>
   </si>
   <si>
     <t xml:space="preserve">33.8731803894043</t>
@@ -3158,43 +3158,43 @@
     <t xml:space="preserve">33.6344337463379</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6248817443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1787719726562</t>
+    <t xml:space="preserve">33.624885559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1787757873535</t>
   </si>
   <si>
     <t xml:space="preserve">34.2169761657715</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9905052185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8281593322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3029251098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1091957092285</t>
+    <t xml:space="preserve">34.9905090332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8281669616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.302921295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1091918945312</t>
   </si>
   <si>
     <t xml:space="preserve">33.5484886169434</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8063354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2333450317383</t>
+    <t xml:space="preserve">33.8063316345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.233341217041</t>
   </si>
   <si>
     <t xml:space="preserve">34.0928268432617</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5771369934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2688140869141</t>
+    <t xml:space="preserve">33.5771331787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2688179016113</t>
   </si>
   <si>
     <t xml:space="preserve">31.9059200286865</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">32.0873603820801</t>
   </si>
   <si>
-    <t xml:space="preserve">32.946849822998</t>
+    <t xml:space="preserve">32.9468536376953</t>
   </si>
   <si>
     <t xml:space="preserve">33.1378440856934</t>
@@ -3218,10 +3218,10 @@
     <t xml:space="preserve">35.8851928710938</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6538238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9620552062988</t>
+    <t xml:space="preserve">36.6538200378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9620590209961</t>
   </si>
   <si>
     <t xml:space="preserve">36.769115447998</t>
@@ -3233,46 +3233,46 @@
     <t xml:space="preserve">37.4224433898926</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1245994567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0189170837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6818580627441</t>
+    <t xml:space="preserve">37.1246032714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.018913269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6818542480469</t>
   </si>
   <si>
     <t xml:space="preserve">38.2391090393066</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7683258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8836212158203</t>
+    <t xml:space="preserve">37.7683296203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.883617401123</t>
   </si>
   <si>
     <t xml:space="preserve">38.0181274414062</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2479286193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6138153076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.642635345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3440093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.594596862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7963638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7195014953613</t>
+    <t xml:space="preserve">39.247932434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6138114929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6426391601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3440055847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5946006774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7963600158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7195053100586</t>
   </si>
   <si>
     <t xml:space="preserve">38.6042060852051</t>
@@ -3284,16 +3284,16 @@
     <t xml:space="preserve">39.6514587402344</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7475395202637</t>
+    <t xml:space="preserve">39.7475357055664</t>
   </si>
   <si>
     <t xml:space="preserve">40.4969482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0069465637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8051834106445</t>
+    <t xml:space="preserve">40.0069427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8051795959473</t>
   </si>
   <si>
     <t xml:space="preserve">39.9685134887695</t>
@@ -3308,13 +3308,13 @@
     <t xml:space="preserve">39.9973411560059</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0749893188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5769577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5665588378906</t>
+    <t xml:space="preserve">39.0749855041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.576961517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5665626525879</t>
   </si>
   <si>
     <t xml:space="preserve">37.5569534301758</t>
@@ -3341,19 +3341,19 @@
     <t xml:space="preserve">38.8540115356445</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4304809570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7675437927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0453834533691</t>
+    <t xml:space="preserve">39.430477142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7675361633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0453796386719</t>
   </si>
   <si>
     <t xml:space="preserve">40.6410636901855</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7275352478027</t>
+    <t xml:space="preserve">40.7275314331055</t>
   </si>
   <si>
     <t xml:space="preserve">40.3528289794922</t>
@@ -3368,7 +3368,7 @@
     <t xml:space="preserve">40.333610534668</t>
   </si>
   <si>
-    <t xml:space="preserve">40.266357421875</t>
+    <t xml:space="preserve">40.2663536071777</t>
   </si>
   <si>
     <t xml:space="preserve">40.4489059448242</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">41.1406707763672</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3424301147461</t>
+    <t xml:space="preserve">41.3424339294434</t>
   </si>
   <si>
     <t xml:space="preserve">41.2271385192871</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">41.2367477416992</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5634117126465</t>
+    <t xml:space="preserve">41.5634078979492</t>
   </si>
   <si>
     <t xml:space="preserve">42.0822372436523</t>
@@ -3401,13 +3401,13 @@
     <t xml:space="preserve">42.2455711364746</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0341949462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7651786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9669418334961</t>
+    <t xml:space="preserve">42.0342025756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7651824951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9669456481934</t>
   </si>
   <si>
     <t xml:space="preserve">42.4665489196777</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">42.5434112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6683120727539</t>
+    <t xml:space="preserve">42.6683158874512</t>
   </si>
   <si>
     <t xml:space="preserve">42.9853706359863</t>
@@ -3425,43 +3425,43 @@
     <t xml:space="preserve">42.3896865844727</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8988990783691</t>
+    <t xml:space="preserve">42.8989028930664</t>
   </si>
   <si>
     <t xml:space="preserve">42.0245895385742</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9765510559082</t>
+    <t xml:space="preserve">41.9765472412109</t>
   </si>
   <si>
     <t xml:space="preserve">41.5345916748047</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4577331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7187156677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.006160736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0165557861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8332176208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0638122558594</t>
+    <t xml:space="preserve">41.4577293395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7187118530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0061645507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0165596008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8332214355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0638084411621</t>
   </si>
   <si>
     <t xml:space="preserve">43.0718421936035</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1679229736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3112487792969</t>
+    <t xml:space="preserve">43.1679191589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3112449645996</t>
   </si>
   <si>
     <t xml:space="preserve">43.2159576416016</t>
@@ -3473,37 +3473,37 @@
     <t xml:space="preserve">39.7859687805176</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2759628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5842018127441</t>
+    <t xml:space="preserve">40.2759666442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5842056274414</t>
   </si>
   <si>
     <t xml:space="preserve">39.1902847290039</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5169486999512</t>
+    <t xml:space="preserve">39.5169525146484</t>
   </si>
   <si>
     <t xml:space="preserve">39.6802825927734</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1030311584473</t>
+    <t xml:space="preserve">40.10302734375</t>
   </si>
   <si>
     <t xml:space="preserve">39.0077362060547</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0653839111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9108695983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2087097167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2463531494141</t>
+    <t xml:space="preserve">39.0653800964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9108772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2087135314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2463569641113</t>
   </si>
   <si>
     <t xml:space="preserve">41.6210632324219</t>
@@ -3512,16 +3512,16 @@
     <t xml:space="preserve">42.7932167053223</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5730209350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1694869995117</t>
+    <t xml:space="preserve">41.5730247497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1694946289062</t>
   </si>
   <si>
     <t xml:space="preserve">42.2263526916504</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9469375610352</t>
+    <t xml:space="preserve">42.9469413757324</t>
   </si>
   <si>
     <t xml:space="preserve">42.3800811767578</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">43.0045852661133</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9653625488281</t>
+    <t xml:space="preserve">43.9653663635254</t>
   </si>
   <si>
     <t xml:space="preserve">43.8596839904785</t>
@@ -3542,10 +3542,10 @@
     <t xml:space="preserve">44.7147789001465</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2632064819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.725170135498</t>
+    <t xml:space="preserve">44.2632102966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7251739501953</t>
   </si>
   <si>
     <t xml:space="preserve">44.0037994384766</t>
@@ -3572,19 +3572,19 @@
     <t xml:space="preserve">41.6018447875977</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5449829101562</t>
+    <t xml:space="preserve">40.5449905395508</t>
   </si>
   <si>
     <t xml:space="preserve">41.0830230712891</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4289054870605</t>
+    <t xml:space="preserve">41.4289016723633</t>
   </si>
   <si>
     <t xml:space="preserve">41.4193000793457</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1318550109863</t>
+    <t xml:space="preserve">40.1318511962891</t>
   </si>
   <si>
     <t xml:space="preserve">40.1606712341309</t>
@@ -3593,13 +3593,13 @@
     <t xml:space="preserve">41.2655715942383</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1798858642578</t>
+    <t xml:space="preserve">40.1798896789551</t>
   </si>
   <si>
     <t xml:space="preserve">40.1414566040039</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3143997192383</t>
+    <t xml:space="preserve">40.314395904541</t>
   </si>
   <si>
     <t xml:space="preserve">41.0926322937012</t>
@@ -3617,16 +3617,16 @@
     <t xml:space="preserve">42.3704719543457</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5626220703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5330200195312</t>
+    <t xml:space="preserve">42.562629699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.533016204834</t>
   </si>
   <si>
     <t xml:space="preserve">43.6579170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">44.416934967041</t>
+    <t xml:space="preserve">44.4169387817383</t>
   </si>
   <si>
     <t xml:space="preserve">45.0702667236328</t>
@@ -3653,16 +3653,16 @@
     <t xml:space="preserve">41.8708648681641</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0261650085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2671432495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9308700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3832321166992</t>
+    <t xml:space="preserve">40.0261611938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.267147064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9308738708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.383228302002</t>
   </si>
   <si>
     <t xml:space="preserve">38.1814613342285</t>
@@ -3671,25 +3671,25 @@
     <t xml:space="preserve">37.2014656066895</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7795066833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5208854675293</t>
+    <t xml:space="preserve">35.7795104980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.520881652832</t>
   </si>
   <si>
     <t xml:space="preserve">35.001277923584</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0397033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4632377624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0581359863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7018585205078</t>
+    <t xml:space="preserve">35.0397109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4632339477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0581321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7018623352051</t>
   </si>
   <si>
     <t xml:space="preserve">37.8644027709961</t>
@@ -3704,13 +3704,13 @@
     <t xml:space="preserve">34.6553955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7138252258301</t>
+    <t xml:space="preserve">33.7138290405273</t>
   </si>
   <si>
     <t xml:space="preserve">35.1165657043457</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7706871032715</t>
+    <t xml:space="preserve">34.7706832885742</t>
   </si>
   <si>
     <t xml:space="preserve">33.9636306762695</t>
@@ -3725,10 +3725,10 @@
     <t xml:space="preserve">34.2710800170898</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2806930541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1461791992188</t>
+    <t xml:space="preserve">34.280689239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.146183013916</t>
   </si>
   <si>
     <t xml:space="preserve">33.7714767456055</t>
@@ -3737,13 +3737,13 @@
     <t xml:space="preserve">33.8291206359863</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5689239501953</t>
+    <t xml:space="preserve">34.568920135498</t>
   </si>
   <si>
     <t xml:space="preserve">35.2510795593262</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9332313537598</t>
+    <t xml:space="preserve">35.933235168457</t>
   </si>
   <si>
     <t xml:space="preserve">36.9420547485352</t>
@@ -3755,34 +3755,34 @@
     <t xml:space="preserve">36.4520530700684</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1253890991211</t>
+    <t xml:space="preserve">36.1253852844238</t>
   </si>
   <si>
     <t xml:space="preserve">34.7802963256836</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5889282226562</t>
+    <t xml:space="preserve">33.588924407959</t>
   </si>
   <si>
     <t xml:space="preserve">35.6450004577637</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7042198181152</t>
+    <t xml:space="preserve">33.7042236328125</t>
   </si>
   <si>
     <t xml:space="preserve">34.4344139099121</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1357841491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9244155883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2695083618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3175468444824</t>
+    <t xml:space="preserve">35.1357803344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9244117736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2695121765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3175430297852</t>
   </si>
   <si>
     <t xml:space="preserve">35.981273651123</t>
@@ -3791,10 +3791,10 @@
     <t xml:space="preserve">35.5200996398926</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0973472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7602958679199</t>
+    <t xml:space="preserve">35.0973510742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7602920532227</t>
   </si>
   <si>
     <t xml:space="preserve">36.2118606567383</t>
@@ -3803,16 +3803,16 @@
     <t xml:space="preserve">38.508129119873</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0173416137695</t>
+    <t xml:space="preserve">39.0173454284668</t>
   </si>
   <si>
     <t xml:space="preserve">38.9500885009766</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2375335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2943954467773</t>
+    <t xml:space="preserve">40.2375373840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2943916320801</t>
   </si>
   <si>
     <t xml:space="preserve">40.8908653259277</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">39.8340072631836</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6330261230469</t>
+    <t xml:space="preserve">38.6330299377441</t>
   </si>
   <si>
     <t xml:space="preserve">39.4208717346191</t>
@@ -3833,13 +3833,13 @@
     <t xml:space="preserve">39.219108581543</t>
   </si>
   <si>
-    <t xml:space="preserve">38.623420715332</t>
+    <t xml:space="preserve">38.6234245300293</t>
   </si>
   <si>
     <t xml:space="preserve">37.9796981811523</t>
   </si>
   <si>
-    <t xml:space="preserve">36.807544708252</t>
+    <t xml:space="preserve">36.8075485229492</t>
   </si>
   <si>
     <t xml:space="preserve">36.6442108154297</t>
@@ -3851,25 +3851,25 @@
     <t xml:space="preserve">35.4528427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2502899169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.721076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1349983215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7218589782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3183364868164</t>
+    <t xml:space="preserve">36.2502937316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7210731506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1350021362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7218627929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3183326721191</t>
   </si>
   <si>
     <t xml:space="preserve">34.0693168640137</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2726554870605</t>
+    <t xml:space="preserve">32.2726593017578</t>
   </si>
   <si>
     <t xml:space="preserve">32.9836349487305</t>
@@ -3881,16 +3881,16 @@
     <t xml:space="preserve">31.0524616241455</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9067726135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9163780212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9644241333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2734394073486</t>
+    <t xml:space="preserve">32.9067687988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.916374206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9644165039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2734432220459</t>
   </si>
   <si>
     <t xml:space="preserve">30.3414840698242</t>
@@ -3908,13 +3908,13 @@
     <t xml:space="preserve">30.9489860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2492733001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3558254241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6948623657227</t>
+    <t xml:space="preserve">31.2492713928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3558235168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.694860458374</t>
   </si>
   <si>
     <t xml:space="preserve">31.0555400848389</t>
@@ -3929,13 +3929,13 @@
     <t xml:space="preserve">30.6099510192871</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3484115600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4646530151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7865829467773</t>
+    <t xml:space="preserve">30.34840965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4646511077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7865810394287</t>
   </si>
   <si>
     <t xml:space="preserve">28.2948322296143</t>
@@ -3944,13 +3944,13 @@
     <t xml:space="preserve">26.260627746582</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5438137054443</t>
+    <t xml:space="preserve">25.5438117980957</t>
   </si>
   <si>
     <t xml:space="preserve">26.3090591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3985118865967</t>
+    <t xml:space="preserve">25.398509979248</t>
   </si>
   <si>
     <t xml:space="preserve">25.4760036468506</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">25.4663181304932</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5341262817383</t>
+    <t xml:space="preserve">25.5341243743896</t>
   </si>
   <si>
     <t xml:space="preserve">25.8828449249268</t>
@@ -3968,10 +3968,10 @@
     <t xml:space="preserve">27.9364242553711</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8663444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.934154510498</t>
+    <t xml:space="preserve">28.8663463592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9341564178467</t>
   </si>
   <si>
     <t xml:space="preserve">28.3529510498047</t>
@@ -3980,22 +3980,22 @@
     <t xml:space="preserve">28.2560863494873</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3335781097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4378604888916</t>
+    <t xml:space="preserve">28.3335800170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4378623962402</t>
   </si>
   <si>
     <t xml:space="preserve">29.9900035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7358798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.588306427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2127990722656</t>
+    <t xml:space="preserve">30.7358779907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5883083343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.212797164917</t>
   </si>
   <si>
     <t xml:space="preserve">30.1740493774414</t>
@@ -4004,19 +4004,19 @@
     <t xml:space="preserve">30.3387241363525</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2173385620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7523765563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3238925933838</t>
+    <t xml:space="preserve">28.2173366546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7523746490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3238906860352</t>
   </si>
   <si>
     <t xml:space="preserve">28.924467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8469715118408</t>
+    <t xml:space="preserve">28.8469753265381</t>
   </si>
   <si>
     <t xml:space="preserve">29.6994037628174</t>
@@ -4040,7 +4040,7 @@
     <t xml:space="preserve">31.2008399963379</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4236354827881</t>
+    <t xml:space="preserve">31.4236335754395</t>
   </si>
   <si>
     <t xml:space="preserve">29.9706287384033</t>
@@ -4055,10 +4055,10 @@
     <t xml:space="preserve">29.4281749725342</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7381477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9922752380371</t>
+    <t xml:space="preserve">29.738151550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9922733306885</t>
   </si>
   <si>
     <t xml:space="preserve">29.4572353363037</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">29.7672100067139</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1979637145996</t>
+    <t xml:space="preserve">28.1979675292969</t>
   </si>
   <si>
     <t xml:space="preserve">27.8879909515381</t>
@@ -4079,7 +4079,7 @@
     <t xml:space="preserve">27.442403793335</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8030796051025</t>
+    <t xml:space="preserve">26.8030815124512</t>
   </si>
   <si>
     <t xml:space="preserve">26.7740211486816</t>
@@ -4100,10 +4100,10 @@
     <t xml:space="preserve">25.2338352203369</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6816959381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0885372161865</t>
+    <t xml:space="preserve">24.6816940307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0885353088379</t>
   </si>
   <si>
     <t xml:space="preserve">25.0497894287109</t>
@@ -4121,49 +4121,49 @@
     <t xml:space="preserve">25.2144641876221</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5073356628418</t>
+    <t xml:space="preserve">24.5073337554932</t>
   </si>
   <si>
     <t xml:space="preserve">24.2554817199707</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1779861450195</t>
+    <t xml:space="preserve">24.1779880523682</t>
   </si>
   <si>
     <t xml:space="preserve">23.8970718383789</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4201545715332</t>
+    <t xml:space="preserve">24.4201526641846</t>
   </si>
   <si>
     <t xml:space="preserve">23.8292675018311</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0908069610596</t>
+    <t xml:space="preserve">24.0908088684082</t>
   </si>
   <si>
     <t xml:space="preserve">24.0133152008057</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1973609924316</t>
+    <t xml:space="preserve">24.197359085083</t>
   </si>
   <si>
     <t xml:space="preserve">24.8463687896729</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8053512573242</t>
+    <t xml:space="preserve">25.8053493499756</t>
   </si>
   <si>
     <t xml:space="preserve">25.291955947876</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0572071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5728721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7159023284912</t>
+    <t xml:space="preserve">26.0572032928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5728702545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7159004211426</t>
   </si>
   <si>
     <t xml:space="preserve">26.1928195953369</t>
@@ -4172,28 +4172,28 @@
     <t xml:space="preserve">25.9312782287598</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6309909820557</t>
+    <t xml:space="preserve">25.630989074707</t>
   </si>
   <si>
     <t xml:space="preserve">25.3307037353516</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6235733032227</t>
+    <t xml:space="preserve">24.6235752105713</t>
   </si>
   <si>
     <t xml:space="preserve">23.8389549255371</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9187183380127</t>
+    <t xml:space="preserve">22.9187164306641</t>
   </si>
   <si>
     <t xml:space="preserve">23.916446685791</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4395275115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3500785827637</t>
+    <t xml:space="preserve">24.4395294189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.350076675415</t>
   </si>
   <si>
     <t xml:space="preserve">24.8366813659668</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">25.3694515228271</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0594749450684</t>
+    <t xml:space="preserve">25.059476852417</t>
   </si>
   <si>
     <t xml:space="preserve">25.4275703430176</t>
@@ -4217,7 +4217,7 @@
     <t xml:space="preserve">23.7517738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">23.906759262085</t>
+    <t xml:space="preserve">23.9067611694336</t>
   </si>
   <si>
     <t xml:space="preserve">24.3523483276367</t>
@@ -4229,7 +4229,7 @@
     <t xml:space="preserve">23.3643054962158</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4007797241211</t>
+    <t xml:space="preserve">24.4007816314697</t>
   </si>
   <si>
     <t xml:space="preserve">25.8150386810303</t>
@@ -4241,28 +4241,28 @@
     <t xml:space="preserve">27.2680416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1398448944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6748828887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7426891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7062149047852</t>
+    <t xml:space="preserve">28.1398429870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6748809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7426910400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7062129974365</t>
   </si>
   <si>
     <t xml:space="preserve">26.7643337249756</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5221672058105</t>
+    <t xml:space="preserve">26.5221652984619</t>
   </si>
   <si>
     <t xml:space="preserve">26.3187465667725</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8321399688721</t>
+    <t xml:space="preserve">26.8321418762207</t>
   </si>
   <si>
     <t xml:space="preserve">26.8805751800537</t>
@@ -4271,7 +4271,7 @@
     <t xml:space="preserve">27.0065002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1421146392822</t>
+    <t xml:space="preserve">27.1421165466309</t>
   </si>
   <si>
     <t xml:space="preserve">26.0087738037109</t>
@@ -4280,10 +4280,10 @@
     <t xml:space="preserve">26.7837066650391</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6458225250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9483833312988</t>
+    <t xml:space="preserve">27.645824432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9483814239502</t>
   </si>
   <si>
     <t xml:space="preserve">26.1540718078613</t>
@@ -4292,10 +4292,10 @@
     <t xml:space="preserve">26.6771545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6965274810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0936832427979</t>
+    <t xml:space="preserve">26.6965255737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0936813354492</t>
   </si>
   <si>
     <t xml:space="preserve">27.1324291229248</t>
@@ -4304,19 +4304,19 @@
     <t xml:space="preserve">27.6651954650879</t>
   </si>
   <si>
-    <t xml:space="preserve">27.975170135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.444673538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0959510803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0668926239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8925323486328</t>
+    <t xml:space="preserve">27.9751682281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4446716308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0959529876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0668907165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8925304412842</t>
   </si>
   <si>
     <t xml:space="preserve">26.4543590545654</t>
@@ -4331,7 +4331,7 @@
     <t xml:space="preserve">26.628719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8708896636963</t>
+    <t xml:space="preserve">26.8708877563477</t>
   </si>
   <si>
     <t xml:space="preserve">26.1443843841553</t>
@@ -4343,7 +4343,7 @@
     <t xml:space="preserve">26.9677543640137</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9797134399414</t>
+    <t xml:space="preserve">25.9797115325928</t>
   </si>
   <si>
     <t xml:space="preserve">26.1056385040283</t>
@@ -4352,46 +4352,46 @@
     <t xml:space="preserve">26.5996608734131</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6384048461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2412548065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6019306182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9044876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0788478851318</t>
+    <t xml:space="preserve">26.6384086608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2412528991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6019325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9044895172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0788497924805</t>
   </si>
   <si>
     <t xml:space="preserve">24.8851165771484</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9916687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9335498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7398147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4782752990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6070785522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9290084838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1227436065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7666053771973</t>
+    <t xml:space="preserve">24.9916706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9335479736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7398166656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4782772064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6070766448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9290065765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1227416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7666034698486</t>
   </si>
   <si>
     <t xml:space="preserve">26.483419418335</t>
@@ -4406,67 +4406,67 @@
     <t xml:space="preserve">26.202507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6190319061279</t>
+    <t xml:space="preserve">26.6190338134766</t>
   </si>
   <si>
     <t xml:space="preserve">26.5027942657471</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3358497619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1763229370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5466842651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4401340484619</t>
+    <t xml:space="preserve">27.3358478546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1763210296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5466861724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4401321411133</t>
   </si>
   <si>
     <t xml:space="preserve">28.7694797515869</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2367115020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1107845306396</t>
+    <t xml:space="preserve">28.2367095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1107864379883</t>
   </si>
   <si>
     <t xml:space="preserve">29.0310192108154</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4304466247559</t>
+    <t xml:space="preserve">28.4304447174072</t>
   </si>
   <si>
     <t xml:space="preserve">28.8954067230225</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1860084533691</t>
+    <t xml:space="preserve">29.1860065460205</t>
   </si>
   <si>
     <t xml:space="preserve">29.6606559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6583862304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9392986297607</t>
+    <t xml:space="preserve">30.6583843231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9393005371094</t>
   </si>
   <si>
     <t xml:space="preserve">30.8327445983887</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2589588165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4817543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6173667907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5689353942871</t>
+    <t xml:space="preserve">31.258960723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4817523956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6173648834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5689315795898</t>
   </si>
   <si>
     <t xml:space="preserve">32.1404495239258</t>
@@ -4475,19 +4475,19 @@
     <t xml:space="preserve">31.6754875183105</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2783317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9176540374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9854602813721</t>
+    <t xml:space="preserve">31.2783355712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9176559448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9854621887207</t>
   </si>
   <si>
     <t xml:space="preserve">31.7820453643799</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3729286193848</t>
+    <t xml:space="preserve">32.3729248046875</t>
   </si>
   <si>
     <t xml:space="preserve">32.508544921875</t>
@@ -4502,19 +4502,19 @@
     <t xml:space="preserve">32.7313385009766</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2373123168945</t>
+    <t xml:space="preserve">32.2373161315918</t>
   </si>
   <si>
     <t xml:space="preserve">32.0823287963867</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3780746459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7678146362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7655410766602</t>
+    <t xml:space="preserve">34.3780784606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7678184509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7655448913574</t>
   </si>
   <si>
     <t xml:space="preserve">34.7267951965332</t>
@@ -4529,34 +4529,34 @@
     <t xml:space="preserve">34.6686782836914</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8817825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6105575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8259353637695</t>
+    <t xml:space="preserve">34.881778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6105537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8259315490723</t>
   </si>
   <si>
     <t xml:space="preserve">33.0413131713867</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8475799560547</t>
+    <t xml:space="preserve">32.8475761413574</t>
   </si>
   <si>
     <t xml:space="preserve">33.1478652954102</t>
   </si>
   <si>
-    <t xml:space="preserve">33.167407989502</t>
+    <t xml:space="preserve">33.1674041748047</t>
   </si>
   <si>
     <t xml:space="preserve">32.297924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0536842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4577445983887</t>
+    <t xml:space="preserve">32.0536880493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4577465057373</t>
   </si>
   <si>
     <t xml:space="preserve">32.2393035888672</t>
@@ -4568,22 +4568,22 @@
     <t xml:space="preserve">32.1513786315918</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5359020233154</t>
+    <t xml:space="preserve">31.5359001159668</t>
   </si>
   <si>
     <t xml:space="preserve">31.6238231658936</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6789321899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9489631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2908935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0466537475586</t>
+    <t xml:space="preserve">32.6789283752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9489669799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2908973693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0466575622559</t>
   </si>
   <si>
     <t xml:space="preserve">34.1638946533203</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">34.6816749572754</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4179000854492</t>
+    <t xml:space="preserve">34.417896270752</t>
   </si>
   <si>
     <t xml:space="preserve">34.2225074768066</t>
@@ -4607,7 +4607,7 @@
     <t xml:space="preserve">33.7438049316406</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6656455993652</t>
+    <t xml:space="preserve">33.6656494140625</t>
   </si>
   <si>
     <t xml:space="preserve">33.216251373291</t>
@@ -4628,10 +4628,10 @@
     <t xml:space="preserve">32.4835395812988</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9853000640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.887601852417</t>
+    <t xml:space="preserve">31.9852981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8875999450684</t>
   </si>
   <si>
     <t xml:space="preserve">30.0997867584229</t>
@@ -4658,19 +4658,19 @@
     <t xml:space="preserve">31.1451206207275</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0474262237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3440246582031</t>
+    <t xml:space="preserve">31.0474281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3440227508545</t>
   </si>
   <si>
     <t xml:space="preserve">30.2560977935791</t>
   </si>
   <si>
-    <t xml:space="preserve">30.363561630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.451488494873</t>
+    <t xml:space="preserve">30.3635635375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4514865875244</t>
   </si>
   <si>
     <t xml:space="preserve">30.9204235076904</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">30.8520374298096</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7152652740479</t>
+    <t xml:space="preserve">30.7152633666992</t>
   </si>
   <si>
     <t xml:space="preserve">30.0802478790283</t>
@@ -4703,16 +4703,16 @@
     <t xml:space="preserve">29.2009925842285</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6406192779541</t>
+    <t xml:space="preserve">29.6406211853027</t>
   </si>
   <si>
     <t xml:space="preserve">29.3182277679443</t>
   </si>
   <si>
-    <t xml:space="preserve">29.415922164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0739898681641</t>
+    <t xml:space="preserve">29.4159240722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0739917755127</t>
   </si>
   <si>
     <t xml:space="preserve">28.5562057495117</t>
@@ -4724,7 +4724,7 @@
     <t xml:space="preserve">29.0935287475586</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2889194488525</t>
+    <t xml:space="preserve">29.2889175415039</t>
   </si>
   <si>
     <t xml:space="preserve">29.1814556121826</t>
@@ -4736,10 +4736,10 @@
     <t xml:space="preserve">29.7578544616699</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5722332000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3475360870361</t>
+    <t xml:space="preserve">29.5722351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3475379943848</t>
   </si>
   <si>
     <t xml:space="preserve">28.800443649292</t>
@@ -4763,19 +4763,19 @@
     <t xml:space="preserve">28.2240447998047</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3217391967773</t>
+    <t xml:space="preserve">28.321741104126</t>
   </si>
   <si>
     <t xml:space="preserve">28.5952854156494</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3119716644287</t>
+    <t xml:space="preserve">28.3119697570801</t>
   </si>
   <si>
     <t xml:space="preserve">27.9309597015381</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0677337646484</t>
+    <t xml:space="preserve">28.0677318572998</t>
   </si>
   <si>
     <t xml:space="preserve">29.650390625</t>
@@ -4817,13 +4817,13 @@
     <t xml:space="preserve">26.6706962585449</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5143852233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0028591156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1005554199219</t>
+    <t xml:space="preserve">26.51438331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.002857208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1005535125732</t>
   </si>
   <si>
     <t xml:space="preserve">27.4620246887207</t>
@@ -4832,7 +4832,7 @@
     <t xml:space="preserve">26.709774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2799186706543</t>
+    <t xml:space="preserve">26.2799167633057</t>
   </si>
   <si>
     <t xml:space="preserve">26.4557685852051</t>
@@ -4841,13 +4841,13 @@
     <t xml:space="preserve">26.6120796203613</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4362297058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6511573791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6609287261963</t>
+    <t xml:space="preserve">26.4362277984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.651159286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6609268188477</t>
   </si>
   <si>
     <t xml:space="preserve">26.2213001251221</t>
@@ -4856,31 +4856,31 @@
     <t xml:space="preserve">25.1661968231201</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7949562072754</t>
+    <t xml:space="preserve">24.7949542999268</t>
   </si>
   <si>
     <t xml:space="preserve">26.0259094238281</t>
   </si>
   <si>
-    <t xml:space="preserve">25.889139175415</t>
+    <t xml:space="preserve">25.8891372680664</t>
   </si>
   <si>
     <t xml:space="preserve">26.8953952789307</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0614757537842</t>
+    <t xml:space="preserve">27.0614776611328</t>
   </si>
   <si>
     <t xml:space="preserve">27.1200923919678</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9344730377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9149322509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.475305557251</t>
+    <t xml:space="preserve">26.9344711303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9149341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4753074645996</t>
   </si>
   <si>
     <t xml:space="preserve">26.3385334014893</t>
@@ -4889,13 +4889,13 @@
     <t xml:space="preserve">27.5890274047852</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7683906555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3776111602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8856258392334</t>
+    <t xml:space="preserve">26.7683925628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.377613067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8856239318848</t>
   </si>
   <si>
     <t xml:space="preserve">27.5206432342529</t>
@@ -4910,25 +4910,25 @@
     <t xml:space="preserve">27.6085662841797</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7648773193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9505004882812</t>
+    <t xml:space="preserve">27.7648792266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9504985809326</t>
   </si>
   <si>
     <t xml:space="preserve">27.5499515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8723449707031</t>
+    <t xml:space="preserve">27.8723430633545</t>
   </si>
   <si>
     <t xml:space="preserve">27.3154811859131</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0517082214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9735527038574</t>
+    <t xml:space="preserve">27.0517063140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9735507965088</t>
   </si>
   <si>
     <t xml:space="preserve">28.0775032043457</t>
@@ -4961,7 +4961,7 @@
     <t xml:space="preserve">30.6175689697266</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5296440124512</t>
+    <t xml:space="preserve">30.5296421051025</t>
   </si>
   <si>
     <t xml:space="preserve">29.796932220459</t>
@@ -4973,7 +4973,7 @@
     <t xml:space="preserve">30.8715763092041</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6761856079102</t>
+    <t xml:space="preserve">30.6761837005615</t>
   </si>
   <si>
     <t xml:space="preserve">30.8911151885986</t>
@@ -5000,7 +5000,7 @@
     <t xml:space="preserve">29.1912231445312</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1619167327881</t>
+    <t xml:space="preserve">29.1619148254395</t>
   </si>
   <si>
     <t xml:space="preserve">29.9337043762207</t>
@@ -5018,10 +5018,10 @@
     <t xml:space="preserve">29.0544509887695</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4612560272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.510103225708</t>
+    <t xml:space="preserve">30.4612579345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5101051330566</t>
   </si>
   <si>
     <t xml:space="preserve">30.7738800048828</t>
@@ -5033,13 +5033,13 @@
     <t xml:space="preserve">30.1584033966064</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4221801757812</t>
+    <t xml:space="preserve">30.4221782684326</t>
   </si>
   <si>
     <t xml:space="preserve">30.8813457489014</t>
   </si>
   <si>
-    <t xml:space="preserve">31.125581741333</t>
+    <t xml:space="preserve">31.1255836486816</t>
   </si>
   <si>
     <t xml:space="preserve">30.744571685791</t>
@@ -5072,7 +5072,7 @@
     <t xml:space="preserve">30.2658672332764</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0439147949219</t>
+    <t xml:space="preserve">32.0439109802246</t>
   </si>
   <si>
     <t xml:space="preserve">32.893856048584</t>
@@ -5081,7 +5081,7 @@
     <t xml:space="preserve">32.2002258300781</t>
   </si>
   <si>
-    <t xml:space="preserve">33.030632019043</t>
+    <t xml:space="preserve">33.0306358337402</t>
   </si>
   <si>
     <t xml:space="preserve">32.8547821044922</t>
@@ -5093,7 +5093,7 @@
     <t xml:space="preserve">31.6433639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9888095855713</t>
+    <t xml:space="preserve">30.9888076782227</t>
   </si>
   <si>
     <t xml:space="preserve">31.2916622161865</t>
@@ -5102,16 +5102,16 @@
     <t xml:space="preserve">31.1158142089844</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3858489990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2357940673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2650985717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0208625793457</t>
+    <t xml:space="preserve">32.3858451843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2357902526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2651023864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0208587646484</t>
   </si>
   <si>
     <t xml:space="preserve">32.4933090209961</t>
@@ -5126,7 +5126,7 @@
     <t xml:space="preserve">31.1646614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7605991363525</t>
+    <t xml:space="preserve">31.7605953216553</t>
   </si>
   <si>
     <t xml:space="preserve">30.1290950775146</t>
@@ -5135,10 +5135,10 @@
     <t xml:space="preserve">30.4026412963867</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1193237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8422679901123</t>
+    <t xml:space="preserve">30.1193256378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8422660827637</t>
   </si>
   <si>
     <t xml:space="preserve">31.2818927764893</t>
@@ -5150,16 +5150,16 @@
     <t xml:space="preserve">30.3049449920654</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7836494445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.705493927002</t>
+    <t xml:space="preserve">30.7836513519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7054958343506</t>
   </si>
   <si>
     <t xml:space="preserve">30.8227272033691</t>
   </si>
   <si>
-    <t xml:space="preserve">33.069709777832</t>
+    <t xml:space="preserve">33.0697059631348</t>
   </si>
   <si>
     <t xml:space="preserve">32.591007232666</t>
@@ -5183,7 +5183,7 @@
     <t xml:space="preserve">33.5972595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5679512023926</t>
+    <t xml:space="preserve">33.5679550170898</t>
   </si>
   <si>
     <t xml:space="preserve">34.0310287475586</t>
@@ -6222,6 +6222,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.6499996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4399995803833</t>
   </si>
 </sst>
 </file>
@@ -71846,7 +71849,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6940393519</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>2439238</v>
@@ -71867,6 +71870,32 @@
         <v>2069</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.6911689815</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>1064650</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>13.7150001525879</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>13.4350004196167</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>13.6700000762939</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>13.4399995803833</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>2070</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2073" uniqueCount="2073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="2074">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.335205078125</t>
+    <t xml:space="preserve">7.33520460128784</t>
   </si>
   <si>
     <t xml:space="preserve">AMP.MI</t>
@@ -50,25 +50,25 @@
     <t xml:space="preserve">7.31191873550415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36780548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15357160568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96262359619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21877384185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27931833267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16288614273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03248262405396</t>
+    <t xml:space="preserve">7.36780595779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1535701751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96262311935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21877336502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27931785583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16288566589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0324821472168</t>
   </si>
   <si>
     <t xml:space="preserve">7.08836936950684</t>
@@ -77,25 +77,25 @@
     <t xml:space="preserve">7.19548606872559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98590993881226</t>
+    <t xml:space="preserve">6.9859094619751</t>
   </si>
   <si>
     <t xml:space="preserve">7.13494205474854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34451913833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23740243911743</t>
+    <t xml:space="preserve">7.34451961517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23740291595459</t>
   </si>
   <si>
     <t xml:space="preserve">7.35383415222168</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14891481399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18151521682739</t>
+    <t xml:space="preserve">7.1489143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18151473999023</t>
   </si>
   <si>
     <t xml:space="preserve">7.40972137451172</t>
@@ -104,91 +104,91 @@
     <t xml:space="preserve">7.28397464752197</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13959980010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05111122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84619188308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51086711883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45497941970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5900411605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33389186859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29197597503662</t>
+    <t xml:space="preserve">7.13959932327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05111169815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51086759567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45498037338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59004068374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33389139175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29197549819946</t>
   </si>
   <si>
     <t xml:space="preserve">6.42237901687622</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61798429489136</t>
+    <t xml:space="preserve">6.61798477172852</t>
   </si>
   <si>
     <t xml:space="preserve">6.88344955444336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71112966537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83687734603882</t>
+    <t xml:space="preserve">6.71113014221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8368763923645</t>
   </si>
   <si>
     <t xml:space="preserve">6.70181560516357</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6272988319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9952244758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8927640914917</t>
+    <t xml:space="preserve">6.62729930877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99522399902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89276361465454</t>
   </si>
   <si>
     <t xml:space="preserve">6.80427598953247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7996187210083</t>
+    <t xml:space="preserve">6.79961824417114</t>
   </si>
   <si>
     <t xml:space="preserve">6.84153366088867</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6599006652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63195753097534</t>
+    <t xml:space="preserve">6.65990018844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63195705413818</t>
   </si>
   <si>
     <t xml:space="preserve">6.79496145248413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78564691543579</t>
+    <t xml:space="preserve">6.78564643859863</t>
   </si>
   <si>
     <t xml:space="preserve">6.86016273498535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00919628143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11165618896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08371210098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20945930480957</t>
+    <t xml:space="preserve">7.00919580459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11165571212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08371257781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20945835113525</t>
   </si>
   <si>
     <t xml:space="preserve">7.10699892044067</t>
@@ -200,196 +200,196 @@
     <t xml:space="preserve">7.24205923080444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09768390655518</t>
+    <t xml:space="preserve">7.09768438339233</t>
   </si>
   <si>
     <t xml:space="preserve">7.17220020294189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93467950820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91604995727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00453901290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27000284194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32589054107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22808790206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50286674499512</t>
+    <t xml:space="preserve">6.93467903137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91605091094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00453805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27000331878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3258900642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22808837890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50286722183228</t>
   </si>
   <si>
     <t xml:space="preserve">7.41437768936157</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48423719406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57738399505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55409669876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7310733795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60066890716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64258527755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70312929153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73573017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88476371765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88942098617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8707914352417</t>
+    <t xml:space="preserve">7.48423767089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57738351821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55409622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73107242584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.600670337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64258480072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70313024520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73573112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88476467132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88942050933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87079095840454</t>
   </si>
   <si>
     <t xml:space="preserve">7.78696012496948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9453067779541</t>
+    <t xml:space="preserve">7.94530820846558</t>
   </si>
   <si>
     <t xml:space="preserve">7.8801064491272</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08968353271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01760387420654</t>
+    <t xml:space="preserve">8.08968448638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01760578155518</t>
   </si>
   <si>
     <t xml:space="preserve">8.09717178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10653114318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.050368309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17205905914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21418380737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23758602142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22354316711426</t>
+    <t xml:space="preserve">8.10653209686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05036926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21418285369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23758506774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22354507446289</t>
   </si>
   <si>
     <t xml:space="preserve">8.15801811218262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07844924926758</t>
+    <t xml:space="preserve">8.07845020294189</t>
   </si>
   <si>
     <t xml:space="preserve">8.08313083648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14397621154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01292514801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91463375091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82102489471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64316844940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62912654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65252923965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55891990661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63848733901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98952150344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94739723205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05972766876221</t>
+    <t xml:space="preserve">8.14397525787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01292324066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91463327407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82102584838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6431679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62912702560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65252876281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55892038345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63848781585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98952102661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94739580154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05972862243652</t>
   </si>
   <si>
     <t xml:space="preserve">7.67593145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71337509155273</t>
+    <t xml:space="preserve">7.71337556838989</t>
   </si>
   <si>
     <t xml:space="preserve">7.72273635864258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87250995635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92867565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89123249053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81166553497314</t>
+    <t xml:space="preserve">7.87251043319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92867517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89123106002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8116660118103</t>
   </si>
   <si>
     <t xml:space="preserve">7.71805572509766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88187170028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96143865585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91931581497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90995216369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05504703521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18141841888428</t>
+    <t xml:space="preserve">7.88187074661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96143960952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91931533813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90995311737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05504608154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18142032623291</t>
   </si>
   <si>
     <t xml:space="preserve">8.16737937927246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19546222686768</t>
+    <t xml:space="preserve">8.19546127319336</t>
   </si>
   <si>
     <t xml:space="preserve">8.19078159332275</t>
@@ -398,58 +398,58 @@
     <t xml:space="preserve">8.30779266357422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36395740509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34991550445557</t>
+    <t xml:space="preserve">8.36395835876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34991645812988</t>
   </si>
   <si>
     <t xml:space="preserve">8.3311939239502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29374885559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15333557128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28906917572021</t>
+    <t xml:space="preserve">8.29375076293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1533374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28907012939453</t>
   </si>
   <si>
     <t xml:space="preserve">8.36863803863525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50905132293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60733890533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51373291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63542366027832</t>
+    <t xml:space="preserve">8.5090503692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60733985900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51373195648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.635422706604</t>
   </si>
   <si>
     <t xml:space="preserve">8.75711441040039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65414333343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78519821166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80860042572021</t>
+    <t xml:space="preserve">8.65414524078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78519916534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80859851837158</t>
   </si>
   <si>
     <t xml:space="preserve">8.92092990875244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84604358673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81795883178711</t>
+    <t xml:space="preserve">8.84604263305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81796169281006</t>
   </si>
   <si>
     <t xml:space="preserve">8.74775314331055</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">8.7524356842041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82264041900635</t>
+    <t xml:space="preserve">8.82264232635498</t>
   </si>
   <si>
     <t xml:space="preserve">8.7337121963501</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77115440368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76179504394531</t>
+    <t xml:space="preserve">8.77115631103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76179599761963</t>
   </si>
   <si>
     <t xml:space="preserve">8.65882587432861</t>
@@ -479,28 +479,28 @@
     <t xml:space="preserve">8.57457733154297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5605354309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48564910888672</t>
+    <t xml:space="preserve">8.56053638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4856481552124</t>
   </si>
   <si>
     <t xml:space="preserve">8.54181385040283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5324535369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66818714141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49969005584717</t>
+    <t xml:space="preserve">8.53245258331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66818809509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49968910217285</t>
   </si>
   <si>
     <t xml:space="preserve">8.61670112609863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49500846862793</t>
+    <t xml:space="preserve">8.49501132965088</t>
   </si>
   <si>
     <t xml:space="preserve">8.55585670471191</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">8.46692752838135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52777194976807</t>
+    <t xml:space="preserve">8.52777290344238</t>
   </si>
   <si>
     <t xml:space="preserve">8.56521606445312</t>
@@ -521,34 +521,34 @@
     <t xml:space="preserve">8.69158744812012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08006572723389</t>
+    <t xml:space="preserve">9.08006477355957</t>
   </si>
   <si>
     <t xml:space="preserve">9.24856185913086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07070350646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0145378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89284706115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93965244293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81328105926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50437164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42480278015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40140056610107</t>
+    <t xml:space="preserve">9.07070255279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01453971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89284801483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93965148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81328010559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50437068939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42480373382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40140151977539</t>
   </si>
   <si>
     <t xml:space="preserve">8.39672088623047</t>
@@ -560,40 +560,40 @@
     <t xml:space="preserve">8.34523487091064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46224689483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3826789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47160720825195</t>
+    <t xml:space="preserve">8.46224594116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38267803192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47160816192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.98645687103271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09878826141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0613431930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51841259002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16269779205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31247329711914</t>
+    <t xml:space="preserve">9.09878730773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06134414672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51841163635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16269874572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31247138977051</t>
   </si>
   <si>
     <t xml:space="preserve">7.44190979003906</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98484182357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95675802230835</t>
+    <t xml:space="preserve">7.9848427772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95675754547119</t>
   </si>
   <si>
     <t xml:space="preserve">8.38735961914062</t>
@@ -602,55 +602,55 @@
     <t xml:space="preserve">8.4107608795166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44820499420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48096942901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37331867218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23290538787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18610095977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37799835205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57925796508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64946460723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72434997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67286682128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74307250976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7103099822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15495109558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96773433685303</t>
+    <t xml:space="preserve">8.44820404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48096752166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37331676483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23290348052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18610000610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3779993057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57925605773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64946365356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72435092926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67286586761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74307346343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71030902862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15495300292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96773529052734</t>
   </si>
   <si>
     <t xml:space="preserve">9.14091110229492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26728343963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33749008178711</t>
+    <t xml:space="preserve">9.26728248596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33748912811279</t>
   </si>
   <si>
     <t xml:space="preserve">9.40769672393799</t>
@@ -659,79 +659,79 @@
     <t xml:space="preserve">9.37961387634277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29536628723145</t>
+    <t xml:space="preserve">9.29536724090576</t>
   </si>
   <si>
     <t xml:space="preserve">9.3608922958374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44514083862305</t>
+    <t xml:space="preserve">9.44513988494873</t>
   </si>
   <si>
     <t xml:space="preserve">9.48258304595947</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43577861785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35621166229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11282825469971</t>
+    <t xml:space="preserve">9.4357795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35621070861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11282920837402</t>
   </si>
   <si>
     <t xml:space="preserve">9.10814762115479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15963172912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46386241912842</t>
+    <t xml:space="preserve">9.15963363647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4638614654541</t>
   </si>
   <si>
     <t xml:space="preserve">9.81021499633789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95998954772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82893753051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91318607330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64171981811523</t>
+    <t xml:space="preserve">9.95999050140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82893657684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91318511962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64171886444092</t>
   </si>
   <si>
     <t xml:space="preserve">9.70724487304688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71660614013672</t>
+    <t xml:space="preserve">9.71660709381104</t>
   </si>
   <si>
     <t xml:space="preserve">9.66044044494629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79149341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0255165100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0067939758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1846504211426</t>
+    <t xml:space="preserve">9.7914924621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0255146026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0067930221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1846513748169</t>
   </si>
   <si>
     <t xml:space="preserve">10.2408151626587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2595386505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4280347824097</t>
+    <t xml:space="preserve">10.259539604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4280338287354</t>
   </si>
   <si>
     <t xml:space="preserve">10.4748392105103</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">10.3625078201294</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3344249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.577808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5122814178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5029220581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8118305206299</t>
+    <t xml:space="preserve">10.3344259262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5778074264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5122804641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5029201507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8118314743042</t>
   </si>
   <si>
     <t xml:space="preserve">10.8867177963257</t>
@@ -764,25 +764,25 @@
     <t xml:space="preserve">10.6526956558228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6433343887329</t>
+    <t xml:space="preserve">10.6433334350586</t>
   </si>
   <si>
     <t xml:space="preserve">10.6246137619019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7088603973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8960790634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8399124145508</t>
+    <t xml:space="preserve">10.7088594436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8960800170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8399133682251</t>
   </si>
   <si>
     <t xml:space="preserve">10.9335222244263</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9990491867065</t>
+    <t xml:space="preserve">10.9990482330322</t>
   </si>
   <si>
     <t xml:space="preserve">11.1301012039185</t>
@@ -791,37 +791,37 @@
     <t xml:space="preserve">11.0926580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2517919540405</t>
+    <t xml:space="preserve">11.2517938613892</t>
   </si>
   <si>
     <t xml:space="preserve">10.9616041183472</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2049894332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1675443649292</t>
+    <t xml:space="preserve">11.2049875259399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1675434112549</t>
   </si>
   <si>
     <t xml:space="preserve">11.1488227844238</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862659454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2798757553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.429648399353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4109287261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4577331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5801248550415</t>
+    <t xml:space="preserve">11.1862668991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2798738479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.429651260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4109268188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4577322006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5801239013672</t>
   </si>
   <si>
     <t xml:space="preserve">11.8249063491821</t>
@@ -830,37 +830,37 @@
     <t xml:space="preserve">11.8625659942627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9472970962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9190530776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9284696578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9378843307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9661283493042</t>
+    <t xml:space="preserve">11.9472980499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9190559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9284687042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9378833770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9661273956299</t>
   </si>
   <si>
     <t xml:space="preserve">12.0602750778198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0979337692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0226163864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2109117507935</t>
+    <t xml:space="preserve">12.0979347229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0226154327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2109107971191</t>
   </si>
   <si>
     <t xml:space="preserve">12.1826667785645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2391548156738</t>
+    <t xml:space="preserve">12.2391557693481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9096393585205</t>
@@ -869,16 +869,16 @@
     <t xml:space="preserve">12.1450071334839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4859771728516</t>
+    <t xml:space="preserve">11.4859762191772</t>
   </si>
   <si>
     <t xml:space="preserve">11.2976818084717</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6931009292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7307605743408</t>
+    <t xml:space="preserve">11.6930990219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7307596206665</t>
   </si>
   <si>
     <t xml:space="preserve">11.7684183120728</t>
@@ -890,76 +890,76 @@
     <t xml:space="preserve">11.6271982192993</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5707082748413</t>
+    <t xml:space="preserve">11.5707101821899</t>
   </si>
   <si>
     <t xml:space="preserve">11.5236358642578</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4671459197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3729982376099</t>
+    <t xml:space="preserve">11.4671478271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3729991912842</t>
   </si>
   <si>
     <t xml:space="preserve">11.0811424255371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.88343334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6951379776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5633325576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6104068756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7422113418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9116764068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9022626876831</t>
+    <t xml:space="preserve">10.8834342956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6951389312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5633316040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6104078292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7422122955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.911678314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9022636413574</t>
   </si>
   <si>
     <t xml:space="preserve">10.9493360519409</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1376314163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3541707992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4577322006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3824148178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3447561264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4106578826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2694387435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5048065185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4294881820679</t>
+    <t xml:space="preserve">11.1376295089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3541698455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4577312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3824138641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3447542190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4106588363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2694368362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.504807472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4294872283936</t>
   </si>
   <si>
     <t xml:space="preserve">11.3353404998779</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2788515090942</t>
+    <t xml:space="preserve">11.2788524627686</t>
   </si>
   <si>
     <t xml:space="preserve">11.2506084442139</t>
@@ -968,34 +968,34 @@
     <t xml:space="preserve">11.1093873977661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0340690612793</t>
+    <t xml:space="preserve">11.034068107605</t>
   </si>
   <si>
     <t xml:space="preserve">10.9210929870605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6668939590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8363599777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7892866134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1941194534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1658735275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0717296600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1282157897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3165111541748</t>
+    <t xml:space="preserve">10.6668949127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8363590240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.78928565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1941204071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1658744812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0717277526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1282148361206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3165121078491</t>
   </si>
   <si>
     <t xml:space="preserve">11.3259248733521</t>
@@ -1007,10 +1007,10 @@
     <t xml:space="preserve">11.062313079834</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0905570983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1752891540527</t>
+    <t xml:space="preserve">11.090558052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1752910614014</t>
   </si>
   <si>
     <t xml:space="preserve">11.4389028549194</t>
@@ -1019,40 +1019,40 @@
     <t xml:space="preserve">11.7213449478149</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8154916763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9849576950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.013201713562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9567127227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0508613586426</t>
+    <t xml:space="preserve">11.8154935836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.984956741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0132007598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.956711769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0508604049683</t>
   </si>
   <si>
     <t xml:space="preserve">12.0414457321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0791053771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9755430221558</t>
+    <t xml:space="preserve">12.0791044235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9755439758301</t>
   </si>
   <si>
     <t xml:space="preserve">11.834321975708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.220326423645</t>
+    <t xml:space="preserve">12.2203245162964</t>
   </si>
   <si>
     <t xml:space="preserve">12.1544218063354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1073484420776</t>
+    <t xml:space="preserve">12.107349395752</t>
   </si>
   <si>
     <t xml:space="preserve">12.4839391708374</t>
@@ -1067,37 +1067,37 @@
     <t xml:space="preserve">12.7852096557617</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8134527206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8322830200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8040399551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1920795440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7872486114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8531503677368</t>
+    <t xml:space="preserve">12.8134536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8322839736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8040409088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1920824050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7872495651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8531513214111</t>
   </si>
   <si>
     <t xml:space="preserve">12.0320310592651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1732511520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2768144607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9002237319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.448317527771</t>
+    <t xml:space="preserve">12.1732521057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2768135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9002246856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4483165740967</t>
   </si>
   <si>
     <t xml:space="preserve">11.5612936019897</t>
@@ -1106,73 +1106,73 @@
     <t xml:space="preserve">11.4012432098389</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6742706298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7778339385986</t>
+    <t xml:space="preserve">11.6742696762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7778329849243</t>
   </si>
   <si>
     <t xml:space="preserve">12.0885181427002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0696897506714</t>
+    <t xml:space="preserve">12.0696887969971</t>
   </si>
   <si>
     <t xml:space="preserve">12.2014961242676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1355934143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3615474700928</t>
+    <t xml:space="preserve">12.135594367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3615465164185</t>
   </si>
   <si>
     <t xml:space="preserve">12.3333024978638</t>
   </si>
   <si>
-    <t xml:space="preserve">12.163836479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7401742935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1261777877808</t>
+    <t xml:space="preserve">12.1638383865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7401733398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1261787414551</t>
   </si>
   <si>
     <t xml:space="preserve">12.5404262542725</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5498418807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5027685165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6345739364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1335544586182</t>
+    <t xml:space="preserve">12.549840927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5027675628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6345729827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1335535049438</t>
   </si>
   <si>
     <t xml:space="preserve">13.1241397857666</t>
   </si>
   <si>
-    <t xml:space="preserve">13.086480140686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9546737670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4254121780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4630718231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5383882522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5572185516357</t>
+    <t xml:space="preserve">13.0864820480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9546756744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4254112243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4630708694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.538387298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5572166442871</t>
   </si>
   <si>
     <t xml:space="preserve">13.6042919158936</t>
@@ -1193,19 +1193,19 @@
     <t xml:space="preserve">12.9735040664673</t>
   </si>
   <si>
-    <t xml:space="preserve">12.615743637085</t>
+    <t xml:space="preserve">12.6157445907593</t>
   </si>
   <si>
     <t xml:space="preserve">12.4086198806763</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3803739547729</t>
+    <t xml:space="preserve">12.3803749084473</t>
   </si>
   <si>
     <t xml:space="preserve">12.46510887146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5121822357178</t>
+    <t xml:space="preserve">12.5121831893921</t>
   </si>
   <si>
     <t xml:space="preserve">12.822868347168</t>
@@ -1214,49 +1214,49 @@
     <t xml:space="preserve">12.8793573379517</t>
   </si>
   <si>
-    <t xml:space="preserve">12.851113319397</t>
+    <t xml:space="preserve">12.8511123657227</t>
   </si>
   <si>
     <t xml:space="preserve">12.5969152450562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.286229133606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2579860687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7287216186523</t>
+    <t xml:space="preserve">12.2862281799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2579851150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.728720664978</t>
   </si>
   <si>
     <t xml:space="preserve">13.0394077301025</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0958957672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2653617858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4065828323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3312644958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3218488693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1617984771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3406772613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2465314865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8887710571289</t>
+    <t xml:space="preserve">13.0958976745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2653608322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4065818786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.331262588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3218479156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1617994308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3406782150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2465305328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8887720108032</t>
   </si>
   <si>
     <t xml:space="preserve">12.8605270385742</t>
@@ -1265,97 +1265,97 @@
     <t xml:space="preserve">13.2936058044434</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5666332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6419506072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3124351501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7925863265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9997100830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1409320831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3951282501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3009805679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5645952224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6022529602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6869859695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9129390716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8564510345459</t>
+    <t xml:space="preserve">13.566632270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6419496536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3124361038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7925872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9997110366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1409330368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3951292037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3009834289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5645942687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6022539138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6869869232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9129400253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8564500808716</t>
   </si>
   <si>
     <t xml:space="preserve">15.1106481552124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.969428062439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9976739883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0353326797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.903525352478</t>
+    <t xml:space="preserve">14.9694290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.997673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0353317260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9035243988037</t>
   </si>
   <si>
     <t xml:space="preserve">14.8941097259521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7152309417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5928373336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1671361923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2706995010376</t>
+    <t xml:space="preserve">14.7152299880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5928382873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1671380996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2706985473633</t>
   </si>
   <si>
     <t xml:space="preserve">15.2424564361572</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2518711090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4401626586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3930902481079</t>
+    <t xml:space="preserve">15.2518720626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.44016456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3930892944336</t>
   </si>
   <si>
     <t xml:space="preserve">15.5531425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">15.656702041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4213371276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0165023803711</t>
+    <t xml:space="preserve">15.6567001342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4213342666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0165014266968</t>
   </si>
   <si>
     <t xml:space="preserve">15.3460178375244</t>
@@ -1364,22 +1364,22 @@
     <t xml:space="preserve">14.818528175354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6668348312378</t>
+    <t xml:space="preserve">14.6668338775635</t>
   </si>
   <si>
     <t xml:space="preserve">14.3444871902466</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6099481582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7332010269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8754119873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9273300170898</t>
+    <t xml:space="preserve">14.6099491119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7331991195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8754110336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9273281097412</t>
   </si>
   <si>
     <t xml:space="preserve">14.4013700485229</t>
@@ -1388,58 +1388,58 @@
     <t xml:space="preserve">14.6194305419922</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6289119720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1882810592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4916667938232</t>
+    <t xml:space="preserve">14.6289110183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1882791519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4916658401489</t>
   </si>
   <si>
     <t xml:space="preserve">16.1174011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4587097167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1553230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1648044586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2027244567871</t>
+    <t xml:space="preserve">16.4587116241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1553249359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1648025512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2027263641357</t>
   </si>
   <si>
     <t xml:space="preserve">16.2122097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3259773254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1079177856445</t>
+    <t xml:space="preserve">16.3259792327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1079196929932</t>
   </si>
   <si>
     <t xml:space="preserve">16.069995880127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5250778198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7241725921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6672878265381</t>
+    <t xml:space="preserve">16.5250759124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7241706848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6672859191895</t>
   </si>
   <si>
     <t xml:space="preserve">16.5724792480469</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3070201873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2596130371094</t>
+    <t xml:space="preserve">16.3070163726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2596111297607</t>
   </si>
   <si>
     <t xml:space="preserve">16.6767711639404</t>
@@ -1448,25 +1448,25 @@
     <t xml:space="preserve">16.8379421234131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8853454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0465202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9232730865479</t>
+    <t xml:space="preserve">16.885347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0465221405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9232711791992</t>
   </si>
   <si>
     <t xml:space="preserve">16.771577835083</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3733825683594</t>
+    <t xml:space="preserve">16.373384475708</t>
   </si>
   <si>
     <t xml:space="preserve">16.4492301940918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2216911315918</t>
+    <t xml:space="preserve">16.2216892242432</t>
   </si>
   <si>
     <t xml:space="preserve">16.4018249511719</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">16.3639011383057</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5155944824219</t>
+    <t xml:space="preserve">16.5155963897705</t>
   </si>
   <si>
     <t xml:space="preserve">17.1034069061279</t>
@@ -1487,13 +1487,13 @@
     <t xml:space="preserve">17.5395240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9471988677979</t>
+    <t xml:space="preserve">17.9471969604492</t>
   </si>
   <si>
     <t xml:space="preserve">17.4447154998779</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0799293518066</t>
+    <t xml:space="preserve">18.0799312591553</t>
   </si>
   <si>
     <t xml:space="preserve">18.1652584075928</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">18.1368141174316</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4117622375488</t>
+    <t xml:space="preserve">18.4117584228516</t>
   </si>
   <si>
     <t xml:space="preserve">18.2505855560303</t>
@@ -1514,55 +1514,55 @@
     <t xml:space="preserve">18.0704517364502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8618698120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6343307495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7860221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7575817108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2979869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3738327026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.203182220459</t>
+    <t xml:space="preserve">17.8618717193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6343326568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7860240936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7575836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2979888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.373836517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2031841278076</t>
   </si>
   <si>
     <t xml:space="preserve">18.032527923584</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1083755493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2126617431641</t>
+    <t xml:space="preserve">18.1083736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2126636505127</t>
   </si>
   <si>
     <t xml:space="preserve">18.0609703063965</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9377193450928</t>
+    <t xml:space="preserve">17.9377174377441</t>
   </si>
   <si>
     <t xml:space="preserve">18.0040836334229</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5774459838867</t>
+    <t xml:space="preserve">17.5774478912354</t>
   </si>
   <si>
     <t xml:space="preserve">18.3927974700928</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8334274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0135669708252</t>
+    <t xml:space="preserve">17.8334293365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0135650634766</t>
   </si>
   <si>
     <t xml:space="preserve">18.7435894012451</t>
@@ -1571,16 +1571,16 @@
     <t xml:space="preserve">19.3408794403076</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4167232513428</t>
+    <t xml:space="preserve">19.41672706604</t>
   </si>
   <si>
     <t xml:space="preserve">19.3788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">19.18918800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0564575195312</t>
+    <t xml:space="preserve">19.1891860961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0564556121826</t>
   </si>
   <si>
     <t xml:space="preserve">18.7246265411377</t>
@@ -1589,16 +1589,16 @@
     <t xml:space="preserve">18.4496822357178</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5255317687988</t>
+    <t xml:space="preserve">18.5255298614502</t>
   </si>
   <si>
     <t xml:space="preserve">18.772029876709</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9616470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6867027282715</t>
+    <t xml:space="preserve">18.9616451263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6867008209229</t>
   </si>
   <si>
     <t xml:space="preserve">18.146297454834</t>
@@ -1607,10 +1607,10 @@
     <t xml:space="preserve">18.5065689086914</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0420074462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3025016784668</t>
+    <t xml:space="preserve">18.0420093536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3025035858154</t>
   </si>
   <si>
     <t xml:space="preserve">16.5629978179932</t>
@@ -1619,109 +1619,109 @@
     <t xml:space="preserve">15.453742980957</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5864753723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6718034744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0081434249878</t>
+    <t xml:space="preserve">15.5864763259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.671802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0081424713135</t>
   </si>
   <si>
     <t xml:space="preserve">15.4253005981445</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4632244110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8045310974121</t>
+    <t xml:space="preserve">15.4632225036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8045358657837</t>
   </si>
   <si>
     <t xml:space="preserve">15.7286863327026</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9512586593628</t>
+    <t xml:space="preserve">14.9512596130371</t>
   </si>
   <si>
     <t xml:space="preserve">15.0745096206665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9986619949341</t>
+    <t xml:space="preserve">14.9986639022827</t>
   </si>
   <si>
     <t xml:space="preserve">14.9797019958496</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0176258087158</t>
+    <t xml:space="preserve">15.0176248550415</t>
   </si>
   <si>
     <t xml:space="preserve">14.8469696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6573524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7047567367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6763153076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6478710174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.932297706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0555486679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7900857925415</t>
+    <t xml:space="preserve">14.6573543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7047576904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6763143539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6478719711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9322986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0555477142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7900848388672</t>
   </si>
   <si>
     <t xml:space="preserve">13.8135604858398</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7282314300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1309413909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0835371017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3869228363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2636728286743</t>
+    <t xml:space="preserve">13.728232383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1309423446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0835361480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3869209289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.263671875</t>
   </si>
   <si>
     <t xml:space="preserve">13.3964042663574</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6523876190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4912118911743</t>
+    <t xml:space="preserve">13.6523847579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4912128448486</t>
   </si>
   <si>
     <t xml:space="preserve">13.2257490158081</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8704452514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0126571655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4961795806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2212362289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1643505096436</t>
+    <t xml:space="preserve">13.8704462051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.012656211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4961786270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2212352752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1643495559692</t>
   </si>
   <si>
     <t xml:space="preserve">14.3065633773804</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">13.7945985794067</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7377128601074</t>
+    <t xml:space="preserve">13.7377138137817</t>
   </si>
   <si>
     <t xml:space="preserve">13.5955018997192</t>
@@ -1745,22 +1745,22 @@
     <t xml:space="preserve">13.8988876342773</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9462928771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4203338623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7756366729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7232646942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3205575942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1878271102905</t>
+    <t xml:space="preserve">13.9462909698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4203329086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7756357192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7232656478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.320556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1878261566162</t>
   </si>
   <si>
     <t xml:space="preserve">13.7471942901611</t>
@@ -1769,55 +1769,55 @@
     <t xml:space="preserve">14.0695419311523</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8374881744385</t>
+    <t xml:space="preserve">14.8374891281128</t>
   </si>
   <si>
     <t xml:space="preserve">15.2546453475952</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8848924636841</t>
+    <t xml:space="preserve">14.8848934173584</t>
   </si>
   <si>
     <t xml:space="preserve">15.0839910507202</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1787977218628</t>
+    <t xml:space="preserve">15.1787996292114</t>
   </si>
   <si>
     <t xml:space="preserve">15.1503562927246</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3115310668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3589363098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2925672531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1408767700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0271072387695</t>
+    <t xml:space="preserve">15.3115301132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3589353561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2925682067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1408758163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0271053314209</t>
   </si>
   <si>
     <t xml:space="preserve">14.9228162765503</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8280096054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8659324645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9417781829834</t>
+    <t xml:space="preserve">14.8280086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8659334182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9417772293091</t>
   </si>
   <si>
     <t xml:space="preserve">15.614914894104</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7097263336182</t>
+    <t xml:space="preserve">15.7097244262695</t>
   </si>
   <si>
     <t xml:space="preserve">15.0650300979614</t>
@@ -1826,10 +1826,10 @@
     <t xml:space="preserve">15.2167205810547</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5485496520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4347810745239</t>
+    <t xml:space="preserve">15.5485486984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4347820281982</t>
   </si>
   <si>
     <t xml:space="preserve">15.3968572616577</t>
@@ -1838,31 +1838,31 @@
     <t xml:space="preserve">14.7806043624878</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9038543701172</t>
+    <t xml:space="preserve">14.9038553237915</t>
   </si>
   <si>
     <t xml:space="preserve">15.2262029647827</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1977605819702</t>
+    <t xml:space="preserve">15.1977615356445</t>
   </si>
   <si>
     <t xml:space="preserve">15.444263458252</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3684129714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5106287002563</t>
+    <t xml:space="preserve">15.3684148788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.510627746582</t>
   </si>
   <si>
     <t xml:space="preserve">15.738166809082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.430269241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9657077789307</t>
+    <t xml:space="preserve">16.4302673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.965708732605</t>
   </si>
   <si>
     <t xml:space="preserve">15.2641267776489</t>
@@ -1874,28 +1874,28 @@
     <t xml:space="preserve">16.6862506866455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8474235534668</t>
+    <t xml:space="preserve">16.8474254608154</t>
   </si>
   <si>
     <t xml:space="preserve">16.4966316223145</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1932487487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2311706542969</t>
+    <t xml:space="preserve">16.193244934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2311687469482</t>
   </si>
   <si>
     <t xml:space="preserve">16.7526149749756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.420783996582</t>
+    <t xml:space="preserve">16.4207859039307</t>
   </si>
   <si>
     <t xml:space="preserve">16.8094997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7336559295654</t>
+    <t xml:space="preserve">16.7336521148682</t>
   </si>
   <si>
     <t xml:space="preserve">16.8948287963867</t>
@@ -1907,10 +1907,10 @@
     <t xml:space="preserve">16.250129699707</t>
   </si>
   <si>
-    <t xml:space="preserve">15.899341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8898611068726</t>
+    <t xml:space="preserve">15.8993434906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8898630142212</t>
   </si>
   <si>
     <t xml:space="preserve">15.9277820587158</t>
@@ -1919,13 +1919,13 @@
     <t xml:space="preserve">15.851936340332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3544216156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2406520843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9183044433594</t>
+    <t xml:space="preserve">16.3544235229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.240650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9183034896851</t>
   </si>
   <si>
     <t xml:space="preserve">17.5016002655029</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">18.0894107818604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3119850158691</t>
+    <t xml:space="preserve">17.3119831085205</t>
   </si>
   <si>
     <t xml:space="preserve">17.283540725708</t>
@@ -1949,34 +1949,34 @@
     <t xml:space="preserve">18.6677417755127</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5743846893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8704280853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5962142944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5007152557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9277267456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9468250274658</t>
+    <t xml:space="preserve">18.5743827819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8704261779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.596212387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5007133483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9277248382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9468269348145</t>
   </si>
   <si>
     <t xml:space="preserve">18.9850234985352</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5934810638428</t>
+    <t xml:space="preserve">18.5934791564941</t>
   </si>
   <si>
     <t xml:space="preserve">18.7080821990967</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9659252166748</t>
+    <t xml:space="preserve">18.9659271240234</t>
   </si>
   <si>
     <t xml:space="preserve">19.0327739715576</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">19.3861179351807</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0900745391846</t>
+    <t xml:space="preserve">19.0900707244873</t>
   </si>
   <si>
     <t xml:space="preserve">19.1951217651367</t>
@@ -2000,85 +2000,85 @@
     <t xml:space="preserve">19.252420425415</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9018096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1501007080078</t>
+    <t xml:space="preserve">19.9018077850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1501026153564</t>
   </si>
   <si>
     <t xml:space="preserve">20.2646980285645</t>
   </si>
   <si>
-    <t xml:space="preserve">20.589391708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5511951446533</t>
+    <t xml:space="preserve">20.5893936157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5511932373047</t>
   </si>
   <si>
     <t xml:space="preserve">20.799488067627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9591026306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8445072174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4816150665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3097190856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6344127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6726093292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0928058624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9400043487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6535091400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5580101013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7299098968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3029003143311</t>
+    <t xml:space="preserve">19.9591045379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8445091247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4816131591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3097171783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6344108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6726112365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0928020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9400062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6535110473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5580139160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.729907989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3028984069824</t>
   </si>
   <si>
     <t xml:space="preserve">20.2837963104248</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2265033721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7039928436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6848926544189</t>
+    <t xml:space="preserve">20.2264976501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7039909362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6848907470703</t>
   </si>
   <si>
     <t xml:space="preserve">20.4174957275391</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0355052947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1310043334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1883010864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2769813537598</t>
+    <t xml:space="preserve">20.0355033874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1310005187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1882991790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2769794464111</t>
   </si>
   <si>
     <t xml:space="preserve">21.1814804077148</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">20.5702953338623</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9904842376709</t>
+    <t xml:space="preserve">20.9904861450195</t>
   </si>
   <si>
     <t xml:space="preserve">21.1050834655762</t>
@@ -2102,19 +2102,19 @@
     <t xml:space="preserve">21.1623821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2578792572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0286846160889</t>
+    <t xml:space="preserve">21.2578811645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0286865234375</t>
   </si>
   <si>
     <t xml:space="preserve">21.2960777282715</t>
   </si>
   <si>
-    <t xml:space="preserve">21.849967956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4802551269531</t>
+    <t xml:space="preserve">21.8499660491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4802570343018</t>
   </si>
   <si>
     <t xml:space="preserve">22.5566558837891</t>
@@ -2126,37 +2126,37 @@
     <t xml:space="preserve">22.0982608795166</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2510585784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9645671844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9454689025879</t>
+    <t xml:space="preserve">22.2510604858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9645652770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9454650878906</t>
   </si>
   <si>
     <t xml:space="preserve">22.3083591461182</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5948543548584</t>
+    <t xml:space="preserve">22.5948524475098</t>
   </si>
   <si>
     <t xml:space="preserve">22.7476501464844</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8049468994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0600662231445</t>
+    <t xml:space="preserve">22.8049488067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0600643157959</t>
   </si>
   <si>
     <t xml:space="preserve">22.2319602966309</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3533802032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4747943878174</t>
+    <t xml:space="preserve">21.3533763885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.474796295166</t>
   </si>
   <si>
     <t xml:space="preserve">20.455696105957</t>
@@ -2165,37 +2165,37 @@
     <t xml:space="preserve">21.1241836547852</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7803897857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8758869171143</t>
+    <t xml:space="preserve">20.780387878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8758850097656</t>
   </si>
   <si>
     <t xml:space="preserve">21.0859851837158</t>
   </si>
   <si>
-    <t xml:space="preserve">21.735372543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5061721801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2196807861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3724765777588</t>
+    <t xml:space="preserve">21.7353706359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.506175994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2196788787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3724746704102</t>
   </si>
   <si>
     <t xml:space="preserve">21.6016731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6780738830566</t>
+    <t xml:space="preserve">21.678071975708</t>
   </si>
   <si>
     <t xml:space="preserve">21.4870758056641</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5825729370117</t>
+    <t xml:space="preserve">21.5825748443604</t>
   </si>
   <si>
     <t xml:space="preserve">20.646692276001</t>
@@ -2210,58 +2210,58 @@
     <t xml:space="preserve">20.8567867279053</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3792972564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8949871063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9331855773926</t>
+    <t xml:space="preserve">20.3792991638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8949890136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9331874847412</t>
   </si>
   <si>
     <t xml:space="preserve">20.3219985961914</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3410968780518</t>
+    <t xml:space="preserve">20.341100692749</t>
   </si>
   <si>
     <t xml:space="preserve">21.830867767334</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0218620300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5375556945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6521511077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0150451660156</t>
+    <t xml:space="preserve">22.0218658447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5375537872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6521530151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.015043258667</t>
   </si>
   <si>
     <t xml:space="preserve">23.4543361663818</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7217330932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9127292633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5689353942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0846214294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.798131942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8745250701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9700260162354</t>
+    <t xml:space="preserve">23.7217311859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.912727355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5689334869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0846252441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7981300354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8745269775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9700241088867</t>
   </si>
   <si>
     <t xml:space="preserve">24.3711185455322</t>
@@ -2270,34 +2270,34 @@
     <t xml:space="preserve">24.8677101135254</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0969047546387</t>
+    <t xml:space="preserve">25.09690284729</t>
   </si>
   <si>
     <t xml:space="preserve">25.3642978668213</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3329181671143</t>
+    <t xml:space="preserve">24.3329200744629</t>
   </si>
   <si>
     <t xml:space="preserve">24.982307434082</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2879009246826</t>
+    <t xml:space="preserve">25.2878971099854</t>
   </si>
   <si>
     <t xml:space="preserve">24.9250068664551</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6194152832031</t>
+    <t xml:space="preserve">25.0205059051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6194133758545</t>
   </si>
   <si>
     <t xml:space="preserve">24.9441089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8295097351074</t>
+    <t xml:space="preserve">24.8295116424561</t>
   </si>
   <si>
     <t xml:space="preserve">24.6385116577148</t>
@@ -2318,13 +2318,13 @@
     <t xml:space="preserve">24.6767120361328</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4857158660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5621147155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5812129974365</t>
+    <t xml:space="preserve">24.4857139587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5621128082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5812149047852</t>
   </si>
   <si>
     <t xml:space="preserve">24.6958122253418</t>
@@ -2336,13 +2336,13 @@
     <t xml:space="preserve">25.3452014923096</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8486080169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0014057159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2115001678467</t>
+    <t xml:space="preserve">24.8486099243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.001407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2115020751953</t>
   </si>
   <si>
     <t xml:space="preserve">25.7653903961182</t>
@@ -2354,49 +2354,49 @@
     <t xml:space="preserve">25.5552959442139</t>
   </si>
   <si>
-    <t xml:space="preserve">25.154203414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8226890563965</t>
+    <t xml:space="preserve">25.1542015075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8226909637451</t>
   </si>
   <si>
     <t xml:space="preserve">24.7722110748291</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5239143371582</t>
+    <t xml:space="preserve">24.5239181518555</t>
   </si>
   <si>
     <t xml:space="preserve">24.9059085845947</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6698932647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2237796783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2810802459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3956775665283</t>
+    <t xml:space="preserve">25.6698913574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2237815856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.281078338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.395679473877</t>
   </si>
   <si>
     <t xml:space="preserve">27.1405639648438</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2169609069824</t>
+    <t xml:space="preserve">27.2169628143311</t>
   </si>
   <si>
     <t xml:space="preserve">27.5225563049316</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6944522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8281517028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1910419464111</t>
+    <t xml:space="preserve">27.6944541931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8281497955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1910438537598</t>
   </si>
   <si>
     <t xml:space="preserve">28.783130645752</t>
@@ -2408,22 +2408,22 @@
     <t xml:space="preserve">27.8854484558105</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9754886627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2306022644043</t>
+    <t xml:space="preserve">25.9754867553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2306003570557</t>
   </si>
   <si>
     <t xml:space="preserve">24.6003131866455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6071338653564</t>
+    <t xml:space="preserve">23.6071319580078</t>
   </si>
   <si>
     <t xml:space="preserve">24.4666156768799</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4352378845215</t>
+    <t xml:space="preserve">23.4352397918701</t>
   </si>
   <si>
     <t xml:space="preserve">19.8254089355469</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">19.3479175567627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5852909088135</t>
+    <t xml:space="preserve">15.5852928161621</t>
   </si>
   <si>
     <t xml:space="preserve">17.323356628418</t>
@@ -2444,13 +2444,13 @@
     <t xml:space="preserve">16.120080947876</t>
   </si>
   <si>
-    <t xml:space="preserve">16.903169631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.523904800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7435512542725</t>
+    <t xml:space="preserve">16.9031677246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5239028930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7435493469238</t>
   </si>
   <si>
     <t xml:space="preserve">18.1350917816162</t>
@@ -2465,13 +2465,13 @@
     <t xml:space="preserve">18.2210388183594</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1159915924072</t>
+    <t xml:space="preserve">18.1159934997559</t>
   </si>
   <si>
     <t xml:space="preserve">17.8772468566895</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3806571960449</t>
+    <t xml:space="preserve">17.3806591033936</t>
   </si>
   <si>
     <t xml:space="preserve">17.4093055725098</t>
@@ -2480,37 +2480,37 @@
     <t xml:space="preserve">16.8076686859131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6480522155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7844791412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4311332702637</t>
+    <t xml:space="preserve">17.6480541229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.784481048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4311351776123</t>
   </si>
   <si>
     <t xml:space="preserve">18.4454612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7653789520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9536437988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8663387298584</t>
+    <t xml:space="preserve">18.7653770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9536457061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8663368225098</t>
   </si>
   <si>
     <t xml:space="preserve">19.271520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8465518951416</t>
+    <t xml:space="preserve">18.8465538024902</t>
   </si>
   <si>
     <t xml:space="preserve">20.0068550109863</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2455997467041</t>
+    <t xml:space="preserve">20.2456016540527</t>
   </si>
   <si>
     <t xml:space="preserve">19.9877548217773</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">19.968656539917</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7681083679199</t>
+    <t xml:space="preserve">19.7681102752686</t>
   </si>
   <si>
     <t xml:space="preserve">20.6753406524658</t>
@@ -2528,16 +2528,16 @@
     <t xml:space="preserve">21.7640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3820285797119</t>
+    <t xml:space="preserve">21.3820247650146</t>
   </si>
   <si>
     <t xml:space="preserve">22.337007522583</t>
   </si>
   <si>
-    <t xml:space="preserve">21.792667388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0191345214844</t>
+    <t xml:space="preserve">21.7926692962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.019136428833</t>
   </si>
   <si>
     <t xml:space="preserve">21.4297771453857</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">21.8595161437988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9522857666016</t>
+    <t xml:space="preserve">20.9522876739502</t>
   </si>
   <si>
     <t xml:space="preserve">21.9932155609131</t>
@@ -2570,67 +2570,67 @@
     <t xml:space="preserve">23.8267784118652</t>
   </si>
   <si>
-    <t xml:space="preserve">23.521183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8458786010742</t>
+    <t xml:space="preserve">23.5211849212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8458805084229</t>
   </si>
   <si>
     <t xml:space="preserve">23.8172302246094</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3588352203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6903495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6330528259277</t>
+    <t xml:space="preserve">23.3588371276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6903514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6330547332764</t>
   </si>
   <si>
     <t xml:space="preserve">21.8881683349609</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0696125030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6999015808105</t>
+    <t xml:space="preserve">22.0696144104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6999034881592</t>
   </si>
   <si>
     <t xml:space="preserve">22.938648223877</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3015384674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6808032989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.709451675415</t>
+    <t xml:space="preserve">23.3015403747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6808013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7094535827637</t>
   </si>
   <si>
     <t xml:space="preserve">23.1487426757812</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4638862609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4229564666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4611587524414</t>
+    <t xml:space="preserve">23.4638843536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4229545593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4611568450928</t>
   </si>
   <si>
     <t xml:space="preserve">22.6426010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7380981445312</t>
+    <t xml:space="preserve">22.7381000518799</t>
   </si>
   <si>
     <t xml:space="preserve">23.272891998291</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2442417144775</t>
+    <t xml:space="preserve">23.2442398071289</t>
   </si>
   <si>
     <t xml:space="preserve">23.5402851104736</t>
@@ -2639,16 +2639,16 @@
     <t xml:space="preserve">23.7408313751221</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8363304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.71217918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7599277496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1610221862793</t>
+    <t xml:space="preserve">23.8363285064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7121829986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7599315643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1610202789307</t>
   </si>
   <si>
     <t xml:space="preserve">24.3233680725098</t>
@@ -2657,37 +2657,37 @@
     <t xml:space="preserve">24.7340087890625</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2783508300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0682544708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0587043762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7531127929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1351013183594</t>
+    <t xml:space="preserve">25.2783489227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0682563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0587024688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7531108856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.135103225708</t>
   </si>
   <si>
     <t xml:space="preserve">26.5580253601074</t>
   </si>
   <si>
-    <t xml:space="preserve">26.510274887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6467056274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2292423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5034580230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5894031524658</t>
+    <t xml:space="preserve">26.5102767944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6467037200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2292404174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.503454208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5894050598145</t>
   </si>
   <si>
     <t xml:space="preserve">27.1596622467041</t>
@@ -2699,16 +2699,16 @@
     <t xml:space="preserve">27.0164165496826</t>
   </si>
   <si>
-    <t xml:space="preserve">27.035514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3793087005615</t>
+    <t xml:space="preserve">27.0355167388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3793067932129</t>
   </si>
   <si>
     <t xml:space="preserve">27.2265129089355</t>
   </si>
   <si>
-    <t xml:space="preserve">27.054615020752</t>
+    <t xml:space="preserve">27.0546169281006</t>
   </si>
   <si>
     <t xml:space="preserve">27.2838115692139</t>
@@ -2720,7 +2720,7 @@
     <t xml:space="preserve">27.0450668334961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7108211517334</t>
+    <t xml:space="preserve">26.710823059082</t>
   </si>
   <si>
     <t xml:space="preserve">26.5007266998291</t>
@@ -2729,22 +2729,22 @@
     <t xml:space="preserve">26.4529781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6630744934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5389270782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.26198387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4625263214111</t>
+    <t xml:space="preserve">26.6630725860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5389289855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2619819641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4625282287598</t>
   </si>
   <si>
     <t xml:space="preserve">27.5989551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6726226806641</t>
+    <t xml:space="preserve">26.6726245880127</t>
   </si>
   <si>
     <t xml:space="preserve">26.7585716247559</t>
@@ -2753,76 +2753,76 @@
     <t xml:space="preserve">27.3888607025146</t>
   </si>
   <si>
-    <t xml:space="preserve">27.446159362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1814918518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3533897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5061855316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9932270050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7926826477051</t>
+    <t xml:space="preserve">27.4461574554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1814956665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3533916473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5061874389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9932289123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7926807403564</t>
   </si>
   <si>
     <t xml:space="preserve">28.6971817016602</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5798530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.65625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4748077392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6849040985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3847713470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9673080444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1746711730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4802665710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.833610534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0246047973633</t>
+    <t xml:space="preserve">27.57985496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6562519073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4748058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6849021911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3847675323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9673042297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1746730804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4802684783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8336124420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0246067047119</t>
   </si>
   <si>
     <t xml:space="preserve">29.1651248931885</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3274688720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8049602508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.473445892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9891376495361</t>
+    <t xml:space="preserve">29.3274707794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8049621582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4734477996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9891395568848</t>
   </si>
   <si>
     <t xml:space="preserve">30.7503929138184</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5402965545654</t>
+    <t xml:space="preserve">30.5402946472168</t>
   </si>
   <si>
     <t xml:space="preserve">30.922290802002</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">30.9318370819092</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7217407226562</t>
+    <t xml:space="preserve">30.7217426300049</t>
   </si>
   <si>
     <t xml:space="preserve">30.6835460662842</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">30.4829978942871</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5593948364258</t>
+    <t xml:space="preserve">30.5593967437744</t>
   </si>
   <si>
     <t xml:space="preserve">28.7258319854736</t>
@@ -2858,16 +2858,16 @@
     <t xml:space="preserve">30.903190612793</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9918670654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.899097442627</t>
+    <t xml:space="preserve">31.9918689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8991012573242</t>
   </si>
   <si>
     <t xml:space="preserve">33.6535377502441</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3097381591797</t>
+    <t xml:space="preserve">33.309741973877</t>
   </si>
   <si>
     <t xml:space="preserve">32.4693603515625</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">33.3288459777832</t>
   </si>
   <si>
-    <t xml:space="preserve">33.558032989502</t>
+    <t xml:space="preserve">33.5580368041992</t>
   </si>
   <si>
     <t xml:space="preserve">34.1310272216797</t>
@@ -2885,43 +2885,43 @@
     <t xml:space="preserve">33.4338874816895</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4461708068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8158836364746</t>
+    <t xml:space="preserve">34.4461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8158798217773</t>
   </si>
   <si>
     <t xml:space="preserve">33.930477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6603546142578</t>
+    <t xml:space="preserve">32.6603584289551</t>
   </si>
   <si>
     <t xml:space="preserve">32.6699028015137</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8513565063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5143775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6098690032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9727668762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7367515563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0587158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2565326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8840885162354</t>
+    <t xml:space="preserve">32.8513526916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5143756866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6098728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9727687835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7367477416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0587196350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2565288543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8840866088867</t>
   </si>
   <si>
     <t xml:space="preserve">31.017786026001</t>
@@ -2930,28 +2930,28 @@
     <t xml:space="preserve">31.1323852539062</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8745422363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0846366882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6194305419922</t>
+    <t xml:space="preserve">30.8745403289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0846347808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6194267272949</t>
   </si>
   <si>
     <t xml:space="preserve">32.0969161987305</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3615798950195</t>
+    <t xml:space="preserve">31.3615779876709</t>
   </si>
   <si>
     <t xml:space="preserve">32.1542091369629</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9441184997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4216117858887</t>
+    <t xml:space="preserve">31.9441223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4216079711914</t>
   </si>
   <si>
     <t xml:space="preserve">31.695821762085</t>
@@ -2960,49 +2960,49 @@
     <t xml:space="preserve">32.2115135192871</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7435722351074</t>
+    <t xml:space="preserve">31.7435760498047</t>
   </si>
   <si>
     <t xml:space="preserve">32.2783584594727</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5075569152832</t>
+    <t xml:space="preserve">32.5075607299805</t>
   </si>
   <si>
     <t xml:space="preserve">32.4120559692383</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0491676330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5334758758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2087841033936</t>
+    <t xml:space="preserve">32.0491714477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5334739685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2087821960449</t>
   </si>
   <si>
     <t xml:space="preserve">32.3165626525879</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1637649536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1064643859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3834075927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6221580505371</t>
+    <t xml:space="preserve">32.1637687683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1064682006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3834114074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6221504211426</t>
   </si>
   <si>
     <t xml:space="preserve">32.650806427002</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8036003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5839576721191</t>
+    <t xml:space="preserve">32.803596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5839538574219</t>
   </si>
   <si>
     <t xml:space="preserve">32.3547592163086</t>
@@ -3035,40 +3035,40 @@
     <t xml:space="preserve">34.4843711853027</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9427604675293</t>
+    <t xml:space="preserve">34.942756652832</t>
   </si>
   <si>
     <t xml:space="preserve">34.8854598999023</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0000610351562</t>
+    <t xml:space="preserve">35.000057220459</t>
   </si>
   <si>
     <t xml:space="preserve">35.8022422790527</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5539474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3343048095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2551689147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9018287658691</t>
+    <t xml:space="preserve">35.5539436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.334300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2551727294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9018249511719</t>
   </si>
   <si>
     <t xml:space="preserve">33.3670387268066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3192863464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7817726135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8104228973389</t>
+    <t xml:space="preserve">33.3192901611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.781774520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8104209899902</t>
   </si>
   <si>
     <t xml:space="preserve">32.4598083496094</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">32.7081031799316</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9768562316895</t>
+    <t xml:space="preserve">29.9768581390381</t>
   </si>
   <si>
     <t xml:space="preserve">29.4898166656494</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">30.3875007629395</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6453456878662</t>
+    <t xml:space="preserve">30.6453437805176</t>
   </si>
   <si>
     <t xml:space="preserve">31.4761772155762</t>
@@ -3104,76 +3104,76 @@
     <t xml:space="preserve">30.7312927246094</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1228313446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5498466491699</t>
+    <t xml:space="preserve">31.1228370666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5498485565186</t>
   </si>
   <si>
     <t xml:space="preserve">29.5375671386719</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1487522125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6671772003174</t>
+    <t xml:space="preserve">30.148754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6671733856201</t>
   </si>
   <si>
     <t xml:space="preserve">30.4065990447998</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7694892883301</t>
+    <t xml:space="preserve">30.7694911956787</t>
   </si>
   <si>
     <t xml:space="preserve">30.6644439697266</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3111000061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9413909912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2756328582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9604835510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5812225341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3424816131592</t>
+    <t xml:space="preserve">30.3111019134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9413890838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2756309509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9604892730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5812244415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3424797058105</t>
   </si>
   <si>
     <t xml:space="preserve">33.5007400512695</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9372978210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8731803894043</t>
+    <t xml:space="preserve">32.9373054504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8731842041016</t>
   </si>
   <si>
     <t xml:space="preserve">33.6344337463379</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6248893737793</t>
+    <t xml:space="preserve">33.6248817443848</t>
   </si>
   <si>
     <t xml:space="preserve">34.1787719726562</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2169761657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9905090332031</t>
+    <t xml:space="preserve">34.2169799804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9905052185059</t>
   </si>
   <si>
     <t xml:space="preserve">34.8281593322754</t>
   </si>
   <si>
-    <t xml:space="preserve">34.302921295166</t>
+    <t xml:space="preserve">34.3029251098633</t>
   </si>
   <si>
     <t xml:space="preserve">33.1091957092285</t>
@@ -3182,28 +3182,28 @@
     <t xml:space="preserve">33.5484886169434</t>
   </si>
   <si>
-    <t xml:space="preserve">33.806339263916</t>
+    <t xml:space="preserve">33.8063354492188</t>
   </si>
   <si>
     <t xml:space="preserve">33.233341217041</t>
   </si>
   <si>
-    <t xml:space="preserve">34.092830657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5771369934082</t>
+    <t xml:space="preserve">34.0928268432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5771331787109</t>
   </si>
   <si>
     <t xml:space="preserve">32.2688140869141</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9059238433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8868179321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0873641967773</t>
+    <t xml:space="preserve">31.9059200286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8868198394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0873603820801</t>
   </si>
   <si>
     <t xml:space="preserve">32.946849822998</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">33.1378479003906</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7995071411133</t>
+    <t xml:space="preserve">34.7995109558105</t>
   </si>
   <si>
     <t xml:space="preserve">35.8851928710938</t>
@@ -3221,13 +3221,13 @@
     <t xml:space="preserve">36.6538238525391</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9620552062988</t>
+    <t xml:space="preserve">35.9620590209961</t>
   </si>
   <si>
     <t xml:space="preserve">36.769115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0765647888184</t>
+    <t xml:space="preserve">37.0765609741211</t>
   </si>
   <si>
     <t xml:space="preserve">37.4224433898926</t>
@@ -3236,10 +3236,10 @@
     <t xml:space="preserve">37.1246032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0189170837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6818542480469</t>
+    <t xml:space="preserve">37.018913269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6818580627441</t>
   </si>
   <si>
     <t xml:space="preserve">38.2391090393066</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">37.8836212158203</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0181274414062</t>
+    <t xml:space="preserve">38.0181312561035</t>
   </si>
   <si>
     <t xml:space="preserve">39.2479286193848</t>
@@ -3269,43 +3269,43 @@
     <t xml:space="preserve">38.5946006774902</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7963638305664</t>
+    <t xml:space="preserve">38.7963600158691</t>
   </si>
   <si>
     <t xml:space="preserve">38.7195014953613</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6042060852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6130256652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6514625549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7475395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4969482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0069465637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8051834106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9685134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6034240722656</t>
+    <t xml:space="preserve">38.6042098999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6130294799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6514587402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7475357055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4969444274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.006950378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8051795959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9685173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6034202575684</t>
   </si>
   <si>
     <t xml:space="preserve">39.7571487426758</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9973411560059</t>
+    <t xml:space="preserve">39.9973449707031</t>
   </si>
   <si>
     <t xml:space="preserve">39.0749893188477</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">37.5665588378906</t>
   </si>
   <si>
-    <t xml:space="preserve">37.556957244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3736152648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9789161682129</t>
+    <t xml:space="preserve">37.5569534301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3736190795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9789123535156</t>
   </si>
   <si>
     <t xml:space="preserve">39.1614570617676</t>
@@ -3332,22 +3332,22 @@
     <t xml:space="preserve">38.4793014526367</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4496955871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1806755065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8540115356445</t>
+    <t xml:space="preserve">39.4496994018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1806716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8540077209473</t>
   </si>
   <si>
     <t xml:space="preserve">39.4304809570312</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7675361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0453834533691</t>
+    <t xml:space="preserve">38.7675399780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0453796386719</t>
   </si>
   <si>
     <t xml:space="preserve">40.6410636901855</t>
@@ -3365,13 +3365,13 @@
     <t xml:space="preserve">40.2567520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3336143493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2663612365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.448902130127</t>
+    <t xml:space="preserve">40.333610534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.266357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4489059448242</t>
   </si>
   <si>
     <t xml:space="preserve">41.0157661437988</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">41.1406707763672</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3424339294434</t>
+    <t xml:space="preserve">41.3424301147461</t>
   </si>
   <si>
     <t xml:space="preserve">41.2271385192871</t>
@@ -3389,22 +3389,22 @@
     <t xml:space="preserve">41.2367477416992</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5634155273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0822372436523</t>
+    <t xml:space="preserve">41.5634117126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0822410583496</t>
   </si>
   <si>
     <t xml:space="preserve">43.0814476013184</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2455749511719</t>
+    <t xml:space="preserve">42.2455673217773</t>
   </si>
   <si>
     <t xml:space="preserve">42.0341949462891</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7651786804199</t>
+    <t xml:space="preserve">41.7651824951172</t>
   </si>
   <si>
     <t xml:space="preserve">41.9669418334961</t>
@@ -3416,13 +3416,13 @@
     <t xml:space="preserve">42.5434112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6683158874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9853668212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3896827697754</t>
+    <t xml:space="preserve">42.6683120727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9853744506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3896865844727</t>
   </si>
   <si>
     <t xml:space="preserve">42.8989028930664</t>
@@ -3437,55 +3437,55 @@
     <t xml:space="preserve">41.5345916748047</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4577255249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7187156677246</t>
+    <t xml:space="preserve">41.4577331542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7187118530273</t>
   </si>
   <si>
     <t xml:space="preserve">41.006160736084</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0165596008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8332176208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0638084411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0718421936035</t>
+    <t xml:space="preserve">40.0165557861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8332214355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0638122558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0718460083008</t>
   </si>
   <si>
     <t xml:space="preserve">43.1679191589355</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3112449645996</t>
+    <t xml:space="preserve">44.3112487792969</t>
   </si>
   <si>
     <t xml:space="preserve">43.2159576416016</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9477272033691</t>
+    <t xml:space="preserve">41.9477233886719</t>
   </si>
   <si>
     <t xml:space="preserve">39.7859687805176</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2759666442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5842018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1902847290039</t>
+    <t xml:space="preserve">40.2759628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5842056274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1902809143066</t>
   </si>
   <si>
     <t xml:space="preserve">39.5169486999512</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6802787780762</t>
+    <t xml:space="preserve">39.6802825927734</t>
   </si>
   <si>
     <t xml:space="preserve">40.10302734375</t>
@@ -3494,16 +3494,16 @@
     <t xml:space="preserve">39.0077362060547</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0653800964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9108734130859</t>
+    <t xml:space="preserve">39.0653839111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9108695983887</t>
   </si>
   <si>
     <t xml:space="preserve">40.2087097167969</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2463569641113</t>
+    <t xml:space="preserve">41.2463531494141</t>
   </si>
   <si>
     <t xml:space="preserve">41.6210632324219</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">42.7932167053223</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5730247497559</t>
+    <t xml:space="preserve">41.5730209350586</t>
   </si>
   <si>
     <t xml:space="preserve">41.1694869995117</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">42.2263565063477</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9469413757324</t>
+    <t xml:space="preserve">42.9469375610352</t>
   </si>
   <si>
     <t xml:space="preserve">42.3800811767578</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">43.8596839904785</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7147827148438</t>
+    <t xml:space="preserve">44.7147750854492</t>
   </si>
   <si>
     <t xml:space="preserve">44.2632102966309</t>
@@ -3548,13 +3548,13 @@
     <t xml:space="preserve">43.725170135498</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0038032531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2055587768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.436939239502</t>
+    <t xml:space="preserve">44.0037994384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.20556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4369354248047</t>
   </si>
   <si>
     <t xml:space="preserve">42.2551765441895</t>
@@ -3566,7 +3566,7 @@
     <t xml:space="preserve">42.8028221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6794929504395</t>
+    <t xml:space="preserve">40.6794967651367</t>
   </si>
   <si>
     <t xml:space="preserve">41.6018447875977</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">41.0830230712891</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4289016723633</t>
+    <t xml:space="preserve">41.4289054870605</t>
   </si>
   <si>
     <t xml:space="preserve">41.4193000793457</t>
@@ -3587,13 +3587,13 @@
     <t xml:space="preserve">40.1318511962891</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1606674194336</t>
+    <t xml:space="preserve">40.1606712341309</t>
   </si>
   <si>
     <t xml:space="preserve">41.2655715942383</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1798896789551</t>
+    <t xml:space="preserve">40.1798858642578</t>
   </si>
   <si>
     <t xml:space="preserve">40.1414566040039</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">41.0926322937012</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9861602783203</t>
+    <t xml:space="preserve">41.986156463623</t>
   </si>
   <si>
     <t xml:space="preserve">41.5057678222656</t>
@@ -3617,82 +3617,82 @@
     <t xml:space="preserve">42.3704719543457</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5626258850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.533016204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6579132080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4169387817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0702667236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.368106842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5890922546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8108596801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8885040283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0518341064453</t>
+    <t xml:space="preserve">42.5626220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5330238342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6579170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.416934967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0702705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3681106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5890884399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8108558654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8885078430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0518379211426</t>
   </si>
   <si>
     <t xml:space="preserve">42.5914497375488</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8708648681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0261611938477</t>
+    <t xml:space="preserve">41.8708610534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0261650085449</t>
   </si>
   <si>
     <t xml:space="preserve">39.267147064209</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9308738708496</t>
+    <t xml:space="preserve">38.9308700561523</t>
   </si>
   <si>
     <t xml:space="preserve">38.383228302002</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1814651489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2014656066895</t>
+    <t xml:space="preserve">38.1814613342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2014694213867</t>
   </si>
   <si>
     <t xml:space="preserve">35.7795104980469</t>
   </si>
   <si>
-    <t xml:space="preserve">34.520881652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0012741088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0397033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4632339477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0581359863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7018623352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8643989562988</t>
+    <t xml:space="preserve">34.5208854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0012817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0397071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4632377624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0581321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7018585205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8644027709961</t>
   </si>
   <si>
     <t xml:space="preserve">35.5585250854492</t>
@@ -3722,7 +3722,7 @@
     <t xml:space="preserve">34.7418632507324</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2710838317871</t>
+    <t xml:space="preserve">34.2710800170898</t>
   </si>
   <si>
     <t xml:space="preserve">34.280689239502</t>
@@ -3734,13 +3734,13 @@
     <t xml:space="preserve">33.7714767456055</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8291244506836</t>
+    <t xml:space="preserve">33.8291206359863</t>
   </si>
   <si>
     <t xml:space="preserve">34.5689239501953</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2510833740234</t>
+    <t xml:space="preserve">35.2510757446289</t>
   </si>
   <si>
     <t xml:space="preserve">35.933235168457</t>
@@ -3755,19 +3755,19 @@
     <t xml:space="preserve">36.4520568847656</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1253890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7802963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.588924407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6450004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7042236328125</t>
+    <t xml:space="preserve">36.1253852844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7802925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5889282226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6449966430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7042198181152</t>
   </si>
   <si>
     <t xml:space="preserve">34.4344139099121</t>
@@ -3776,10 +3776,10 @@
     <t xml:space="preserve">35.1357841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9244155883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2695083618164</t>
+    <t xml:space="preserve">34.9244117736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2695045471191</t>
   </si>
   <si>
     <t xml:space="preserve">36.3175468444824</t>
@@ -3794,10 +3794,10 @@
     <t xml:space="preserve">35.0973510742188</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7602920532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2118606567383</t>
+    <t xml:space="preserve">35.7602958679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.211856842041</t>
   </si>
   <si>
     <t xml:space="preserve">38.508129119873</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">38.9500885009766</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2375373840332</t>
+    <t xml:space="preserve">40.2375335693359</t>
   </si>
   <si>
     <t xml:space="preserve">41.2943954467773</t>
@@ -3818,19 +3818,19 @@
     <t xml:space="preserve">40.890869140625</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6891021728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8340072631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6330261230469</t>
+    <t xml:space="preserve">40.6891059875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8340034484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6330299377441</t>
   </si>
   <si>
     <t xml:space="preserve">39.4208717346191</t>
   </si>
   <si>
-    <t xml:space="preserve">39.219108581543</t>
+    <t xml:space="preserve">39.2191047668457</t>
   </si>
   <si>
     <t xml:space="preserve">38.6234245300293</t>
@@ -3839,13 +3839,13 @@
     <t xml:space="preserve">37.9796981811523</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8075485229492</t>
+    <t xml:space="preserve">36.807544708252</t>
   </si>
   <si>
     <t xml:space="preserve">36.6442108154297</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3367576599121</t>
+    <t xml:space="preserve">36.3367614746094</t>
   </si>
   <si>
     <t xml:space="preserve">35.4528427124023</t>
@@ -3854,52 +3854,52 @@
     <t xml:space="preserve">36.2502899169922</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7210731506348</t>
+    <t xml:space="preserve">36.721076965332</t>
   </si>
   <si>
     <t xml:space="preserve">36.1349983215332</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7218589782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3183326721191</t>
+    <t xml:space="preserve">35.7218627929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3183364868164</t>
   </si>
   <si>
     <t xml:space="preserve">34.0693168640137</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2726554870605</t>
+    <t xml:space="preserve">32.2726593017578</t>
   </si>
   <si>
     <t xml:space="preserve">32.9836349487305</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9740295410156</t>
+    <t xml:space="preserve">32.9740257263184</t>
   </si>
   <si>
     <t xml:space="preserve">31.0524616241455</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9067726135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9163780212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9644203186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2734432220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3414859771729</t>
+    <t xml:space="preserve">32.9067764282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9163818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9644241333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2734413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3414840698242</t>
   </si>
   <si>
     <t xml:space="preserve">30.6777591705322</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2105255126953</t>
+    <t xml:space="preserve">31.2105274200439</t>
   </si>
   <si>
     <t xml:space="preserve">31.0071048736572</t>
@@ -3908,10 +3908,10 @@
     <t xml:space="preserve">30.9489860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2492713928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3558235168457</t>
+    <t xml:space="preserve">31.2492733001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3558254241943</t>
   </si>
   <si>
     <t xml:space="preserve">31.6948623657227</t>
@@ -3920,61 +3920,61 @@
     <t xml:space="preserve">31.0555400848389</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1934223175049</t>
+    <t xml:space="preserve">30.1934242248535</t>
   </si>
   <si>
     <t xml:space="preserve">30.0965557098389</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6099529266357</t>
+    <t xml:space="preserve">30.6099510192871</t>
   </si>
   <si>
     <t xml:space="preserve">30.3484115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4646511077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7865810394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2948303222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2606258392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5438117980957</t>
+    <t xml:space="preserve">30.4646530151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7865829467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2948322296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.260627746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5438137054443</t>
   </si>
   <si>
     <t xml:space="preserve">26.3090591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.398509979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.476001739502</t>
+    <t xml:space="preserve">25.3985118865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4760036468506</t>
   </si>
   <si>
     <t xml:space="preserve">25.4663181304932</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5341243743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8828430175781</t>
+    <t xml:space="preserve">25.5341262817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8828449249268</t>
   </si>
   <si>
     <t xml:space="preserve">27.9364242553711</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8663463592529</t>
+    <t xml:space="preserve">28.8663444519043</t>
   </si>
   <si>
     <t xml:space="preserve">28.934154510498</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3529529571533</t>
+    <t xml:space="preserve">28.3529510498047</t>
   </si>
   <si>
     <t xml:space="preserve">28.2560863494873</t>
@@ -3983,19 +3983,19 @@
     <t xml:space="preserve">28.3335781097412</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4378623962402</t>
+    <t xml:space="preserve">29.4378604888916</t>
   </si>
   <si>
     <t xml:space="preserve">29.9900035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7358779907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5883083343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.212797164917</t>
+    <t xml:space="preserve">30.7358798980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.588306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2127990722656</t>
   </si>
   <si>
     <t xml:space="preserve">30.1740493774414</t>
@@ -4004,7 +4004,7 @@
     <t xml:space="preserve">30.3387241363525</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2173366546631</t>
+    <t xml:space="preserve">28.2173385620117</t>
   </si>
   <si>
     <t xml:space="preserve">27.7523765563965</t>
@@ -4013,22 +4013,22 @@
     <t xml:space="preserve">28.3238925933838</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9244689941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8469734191895</t>
+    <t xml:space="preserve">28.924467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8469715118408</t>
   </si>
   <si>
     <t xml:space="preserve">29.6994037628174</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1837387084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6412811279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4766063690186</t>
+    <t xml:space="preserve">30.1837368011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6412830352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4766082763672</t>
   </si>
   <si>
     <t xml:space="preserve">30.358097076416</t>
@@ -4040,10 +4040,10 @@
     <t xml:space="preserve">31.2008399963379</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4236335754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.970630645752</t>
+    <t xml:space="preserve">31.4236354827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9706287384033</t>
   </si>
   <si>
     <t xml:space="preserve">30.8714923858643</t>
@@ -4052,13 +4052,13 @@
     <t xml:space="preserve">31.0942840576172</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4281730651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7381496429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9922733306885</t>
+    <t xml:space="preserve">29.4281749725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7381477355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9922752380371</t>
   </si>
   <si>
     <t xml:space="preserve">29.4572353363037</t>
@@ -4067,22 +4067,22 @@
     <t xml:space="preserve">29.7672100067139</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1979656219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8879928588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8104953765869</t>
+    <t xml:space="preserve">28.1979637145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8879909515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8104972839355</t>
   </si>
   <si>
     <t xml:space="preserve">27.442403793335</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8030815124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.774019241333</t>
+    <t xml:space="preserve">26.8030796051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7740211486816</t>
   </si>
   <si>
     <t xml:space="preserve">26.8612003326416</t>
@@ -4100,10 +4100,10 @@
     <t xml:space="preserve">25.2338352203369</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6816940307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0885353088379</t>
+    <t xml:space="preserve">24.6816959381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0885372161865</t>
   </si>
   <si>
     <t xml:space="preserve">25.0497894287109</t>
@@ -4121,16 +4121,16 @@
     <t xml:space="preserve">25.2144641876221</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5073337554932</t>
+    <t xml:space="preserve">24.5073356628418</t>
   </si>
   <si>
     <t xml:space="preserve">24.2554817199707</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1779880523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8970737457275</t>
+    <t xml:space="preserve">24.1779861450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8970718383789</t>
   </si>
   <si>
     <t xml:space="preserve">24.4201545715332</t>
@@ -4139,13 +4139,13 @@
     <t xml:space="preserve">23.8292675018311</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0908088684082</t>
+    <t xml:space="preserve">24.0908069610596</t>
   </si>
   <si>
     <t xml:space="preserve">24.0133152008057</t>
   </si>
   <si>
-    <t xml:space="preserve">24.197359085083</t>
+    <t xml:space="preserve">24.1973609924316</t>
   </si>
   <si>
     <t xml:space="preserve">24.8463687896729</t>
@@ -4154,16 +4154,16 @@
     <t xml:space="preserve">25.8053512573242</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2919578552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0572052001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.572868347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7159004211426</t>
+    <t xml:space="preserve">25.291955947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0572071075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5728721618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7159023284912</t>
   </si>
   <si>
     <t xml:space="preserve">26.1928195953369</t>
@@ -4178,13 +4178,13 @@
     <t xml:space="preserve">25.3307037353516</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6235752105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8389530181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9187164306641</t>
+    <t xml:space="preserve">24.6235733032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8389549255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9187183380127</t>
   </si>
   <si>
     <t xml:space="preserve">23.916446685791</t>
@@ -4193,19 +4193,19 @@
     <t xml:space="preserve">24.4395275115967</t>
   </si>
   <si>
-    <t xml:space="preserve">25.350076675415</t>
+    <t xml:space="preserve">25.3500785827637</t>
   </si>
   <si>
     <t xml:space="preserve">24.8366813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0475177764893</t>
+    <t xml:space="preserve">26.0475196838379</t>
   </si>
   <si>
     <t xml:space="preserve">25.3694515228271</t>
   </si>
   <si>
-    <t xml:space="preserve">25.059476852417</t>
+    <t xml:space="preserve">25.0594749450684</t>
   </si>
   <si>
     <t xml:space="preserve">25.4275703430176</t>
@@ -4229,10 +4229,10 @@
     <t xml:space="preserve">23.3643054962158</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4007835388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8150367736816</t>
+    <t xml:space="preserve">24.4007797241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8150386810303</t>
   </si>
   <si>
     <t xml:space="preserve">25.7278575897217</t>
@@ -4250,7 +4250,7 @@
     <t xml:space="preserve">27.7426891326904</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7062129974365</t>
+    <t xml:space="preserve">26.7062149047852</t>
   </si>
   <si>
     <t xml:space="preserve">26.7643337249756</t>
@@ -4262,7 +4262,7 @@
     <t xml:space="preserve">26.3187465667725</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8321418762207</t>
+    <t xml:space="preserve">26.8321399688721</t>
   </si>
   <si>
     <t xml:space="preserve">26.8805751800537</t>
@@ -4271,13 +4271,13 @@
     <t xml:space="preserve">27.0065002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1421165466309</t>
+    <t xml:space="preserve">27.1421146392822</t>
   </si>
   <si>
     <t xml:space="preserve">26.0087738037109</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7837085723877</t>
+    <t xml:space="preserve">26.7837066650391</t>
   </si>
   <si>
     <t xml:space="preserve">27.6458225250244</t>
@@ -4286,16 +4286,16 @@
     <t xml:space="preserve">26.9483833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">26.15407371521</t>
+    <t xml:space="preserve">26.1540718078613</t>
   </si>
   <si>
     <t xml:space="preserve">26.6771545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6965255737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0936813354492</t>
+    <t xml:space="preserve">26.6965274810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0936832427979</t>
   </si>
   <si>
     <t xml:space="preserve">27.1324291229248</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">27.6651954650879</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9751682281494</t>
+    <t xml:space="preserve">27.975170135498</t>
   </si>
   <si>
     <t xml:space="preserve">26.444673538208</t>
@@ -4322,16 +4322,16 @@
     <t xml:space="preserve">26.4543590545654</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8344097137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9700260162354</t>
+    <t xml:space="preserve">25.8344116210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9700241088867</t>
   </si>
   <si>
     <t xml:space="preserve">26.628719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8708877563477</t>
+    <t xml:space="preserve">26.8708896636963</t>
   </si>
   <si>
     <t xml:space="preserve">26.1443843841553</t>
@@ -4343,28 +4343,28 @@
     <t xml:space="preserve">26.9677543640137</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9797115325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.105640411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5996589660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6384086608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2412528991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6019325256348</t>
+    <t xml:space="preserve">25.9797134399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1056385040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5996608734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6384048461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2412548065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6019306182861</t>
   </si>
   <si>
     <t xml:space="preserve">24.9044876098633</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0788497924805</t>
+    <t xml:space="preserve">25.0788478851318</t>
   </si>
   <si>
     <t xml:space="preserve">24.8851165771484</t>
@@ -4373,25 +4373,25 @@
     <t xml:space="preserve">24.9916687011719</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9335479736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7398166656494</t>
+    <t xml:space="preserve">24.9335498809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7398147583008</t>
   </si>
   <si>
     <t xml:space="preserve">24.4782752990723</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6070766448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9290065765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1227416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7666034698486</t>
+    <t xml:space="preserve">27.6070785522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9290084838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1227436065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7666053771973</t>
   </si>
   <si>
     <t xml:space="preserve">26.483419418335</t>
@@ -4400,58 +4400,58 @@
     <t xml:space="preserve">27.2777290344238</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5415420532227</t>
+    <t xml:space="preserve">26.541540145874</t>
   </si>
   <si>
     <t xml:space="preserve">26.202507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6190338134766</t>
+    <t xml:space="preserve">26.6190319061279</t>
   </si>
   <si>
     <t xml:space="preserve">26.5027942657471</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3358478546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1763210296631</t>
+    <t xml:space="preserve">27.3358497619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1763229370117</t>
   </si>
   <si>
     <t xml:space="preserve">28.5466842651367</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4401321411133</t>
+    <t xml:space="preserve">28.4401340484619</t>
   </si>
   <si>
     <t xml:space="preserve">28.7694797515869</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2367095947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1107864379883</t>
+    <t xml:space="preserve">28.2367115020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1107845306396</t>
   </si>
   <si>
     <t xml:space="preserve">29.0310192108154</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4304447174072</t>
+    <t xml:space="preserve">28.4304466247559</t>
   </si>
   <si>
     <t xml:space="preserve">28.8954067230225</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1860065460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6606578826904</t>
+    <t xml:space="preserve">29.1860084533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6606559753418</t>
   </si>
   <si>
     <t xml:space="preserve">30.6583862304688</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9393005371094</t>
+    <t xml:space="preserve">30.9392986297607</t>
   </si>
   <si>
     <t xml:space="preserve">30.8327445983887</t>
@@ -4463,10 +4463,10 @@
     <t xml:space="preserve">31.4817543029785</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6173648834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5689315795898</t>
+    <t xml:space="preserve">31.6173667907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5689353942871</t>
   </si>
   <si>
     <t xml:space="preserve">32.1404495239258</t>
@@ -4475,13 +4475,13 @@
     <t xml:space="preserve">31.6754875183105</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2783355712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9176559448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9854621887207</t>
+    <t xml:space="preserve">31.2783317565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9176540374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9854602813721</t>
   </si>
   <si>
     <t xml:space="preserve">31.7820453643799</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">32.7313385009766</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2373161315918</t>
+    <t xml:space="preserve">32.2373123168945</t>
   </si>
   <si>
     <t xml:space="preserve">32.0823287963867</t>
@@ -4511,7 +4511,7 @@
     <t xml:space="preserve">34.3780746459961</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7678184509277</t>
+    <t xml:space="preserve">33.7678146362305</t>
   </si>
   <si>
     <t xml:space="preserve">34.7655410766602</t>
@@ -4523,40 +4523,40 @@
     <t xml:space="preserve">34.3296394348145</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2134017944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6686744689941</t>
+    <t xml:space="preserve">34.2134056091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6686782836914</t>
   </si>
   <si>
     <t xml:space="preserve">34.8817825317383</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6105537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8259315490723</t>
+    <t xml:space="preserve">34.6105575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8259353637695</t>
   </si>
   <si>
     <t xml:space="preserve">33.0413131713867</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8475761413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1478691101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1674041748047</t>
+    <t xml:space="preserve">32.8475799560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1478652954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.167407989502</t>
   </si>
   <si>
     <t xml:space="preserve">32.297924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0536880493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4577465057373</t>
+    <t xml:space="preserve">32.0536842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4577445983887</t>
   </si>
   <si>
     <t xml:space="preserve">32.2393035888672</t>
@@ -4568,22 +4568,22 @@
     <t xml:space="preserve">32.1513786315918</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5359001159668</t>
+    <t xml:space="preserve">31.5359020233154</t>
   </si>
   <si>
     <t xml:space="preserve">31.6238231658936</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6789283752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9489669799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2908973693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0466575622559</t>
+    <t xml:space="preserve">32.6789321899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9489631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2908935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0466537475586</t>
   </si>
   <si>
     <t xml:space="preserve">34.1638946533203</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">34.6816749572754</t>
   </si>
   <si>
-    <t xml:space="preserve">34.417896270752</t>
+    <t xml:space="preserve">34.4179000854492</t>
   </si>
   <si>
     <t xml:space="preserve">34.2225074768066</t>
@@ -4607,7 +4607,7 @@
     <t xml:space="preserve">33.7438049316406</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6656494140625</t>
+    <t xml:space="preserve">33.6656455993652</t>
   </si>
   <si>
     <t xml:space="preserve">33.216251373291</t>
@@ -4628,10 +4628,10 @@
     <t xml:space="preserve">32.4835395812988</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9852981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8875999450684</t>
+    <t xml:space="preserve">31.9853000640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.887601852417</t>
   </si>
   <si>
     <t xml:space="preserve">30.0997867584229</t>
@@ -4658,19 +4658,19 @@
     <t xml:space="preserve">31.1451206207275</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0474281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3440227508545</t>
+    <t xml:space="preserve">31.0474262237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3440246582031</t>
   </si>
   <si>
     <t xml:space="preserve">30.2560977935791</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3635635375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4514865875244</t>
+    <t xml:space="preserve">30.363561630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.451488494873</t>
   </si>
   <si>
     <t xml:space="preserve">30.9204235076904</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">30.8520374298096</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7152633666992</t>
+    <t xml:space="preserve">30.7152652740479</t>
   </si>
   <si>
     <t xml:space="preserve">30.0802478790283</t>
@@ -4703,16 +4703,16 @@
     <t xml:space="preserve">29.2009925842285</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6406211853027</t>
+    <t xml:space="preserve">29.6406192779541</t>
   </si>
   <si>
     <t xml:space="preserve">29.3182277679443</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4159240722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0739917755127</t>
+    <t xml:space="preserve">29.415922164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0739898681641</t>
   </si>
   <si>
     <t xml:space="preserve">28.5562057495117</t>
@@ -4724,7 +4724,7 @@
     <t xml:space="preserve">29.0935287475586</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2889175415039</t>
+    <t xml:space="preserve">29.2889194488525</t>
   </si>
   <si>
     <t xml:space="preserve">29.1814556121826</t>
@@ -4736,10 +4736,10 @@
     <t xml:space="preserve">29.7578544616699</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5722351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3475379943848</t>
+    <t xml:space="preserve">29.5722332000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3475360870361</t>
   </si>
   <si>
     <t xml:space="preserve">28.800443649292</t>
@@ -4763,19 +4763,19 @@
     <t xml:space="preserve">28.2240447998047</t>
   </si>
   <si>
-    <t xml:space="preserve">28.321741104126</t>
+    <t xml:space="preserve">28.3217391967773</t>
   </si>
   <si>
     <t xml:space="preserve">28.5952854156494</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3119697570801</t>
+    <t xml:space="preserve">28.3119716644287</t>
   </si>
   <si>
     <t xml:space="preserve">27.9309597015381</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0677318572998</t>
+    <t xml:space="preserve">28.0677337646484</t>
   </si>
   <si>
     <t xml:space="preserve">29.650390625</t>
@@ -4817,13 +4817,13 @@
     <t xml:space="preserve">26.6706962585449</t>
   </si>
   <si>
-    <t xml:space="preserve">26.51438331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.002857208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1005535125732</t>
+    <t xml:space="preserve">26.5143852233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0028591156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1005554199219</t>
   </si>
   <si>
     <t xml:space="preserve">27.4620246887207</t>
@@ -4832,7 +4832,7 @@
     <t xml:space="preserve">26.709774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2799167633057</t>
+    <t xml:space="preserve">26.2799186706543</t>
   </si>
   <si>
     <t xml:space="preserve">26.4557685852051</t>
@@ -4841,13 +4841,13 @@
     <t xml:space="preserve">26.6120796203613</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4362277984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.651159286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6609268188477</t>
+    <t xml:space="preserve">26.4362297058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6511573791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6609287261963</t>
   </si>
   <si>
     <t xml:space="preserve">26.2213001251221</t>
@@ -4856,31 +4856,31 @@
     <t xml:space="preserve">25.1661968231201</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7949542999268</t>
+    <t xml:space="preserve">24.7949562072754</t>
   </si>
   <si>
     <t xml:space="preserve">26.0259094238281</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8891372680664</t>
+    <t xml:space="preserve">25.889139175415</t>
   </si>
   <si>
     <t xml:space="preserve">26.8953952789307</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0614776611328</t>
+    <t xml:space="preserve">27.0614757537842</t>
   </si>
   <si>
     <t xml:space="preserve">27.1200923919678</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9344711303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9149341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4753074645996</t>
+    <t xml:space="preserve">26.9344730377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9149322509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.475305557251</t>
   </si>
   <si>
     <t xml:space="preserve">26.3385334014893</t>
@@ -4889,13 +4889,13 @@
     <t xml:space="preserve">27.5890274047852</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7683925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.377613067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8856239318848</t>
+    <t xml:space="preserve">26.7683906555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3776111602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8856258392334</t>
   </si>
   <si>
     <t xml:space="preserve">27.5206432342529</t>
@@ -4910,25 +4910,25 @@
     <t xml:space="preserve">27.6085662841797</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7648792266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9504985809326</t>
+    <t xml:space="preserve">27.7648773193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9505004882812</t>
   </si>
   <si>
     <t xml:space="preserve">27.5499515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8723430633545</t>
+    <t xml:space="preserve">27.8723449707031</t>
   </si>
   <si>
     <t xml:space="preserve">27.3154811859131</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0517063140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9735507965088</t>
+    <t xml:space="preserve">27.0517082214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9735527038574</t>
   </si>
   <si>
     <t xml:space="preserve">28.0775032043457</t>
@@ -4961,7 +4961,7 @@
     <t xml:space="preserve">30.6175689697266</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5296421051025</t>
+    <t xml:space="preserve">30.5296440124512</t>
   </si>
   <si>
     <t xml:space="preserve">29.796932220459</t>
@@ -4973,7 +4973,7 @@
     <t xml:space="preserve">30.8715763092041</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6761837005615</t>
+    <t xml:space="preserve">30.6761856079102</t>
   </si>
   <si>
     <t xml:space="preserve">30.8911151885986</t>
@@ -5000,7 +5000,7 @@
     <t xml:space="preserve">29.1912231445312</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1619148254395</t>
+    <t xml:space="preserve">29.1619167327881</t>
   </si>
   <si>
     <t xml:space="preserve">29.9337043762207</t>
@@ -5018,10 +5018,10 @@
     <t xml:space="preserve">29.0544509887695</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4612579345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5101051330566</t>
+    <t xml:space="preserve">30.4612560272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.510103225708</t>
   </si>
   <si>
     <t xml:space="preserve">30.7738800048828</t>
@@ -5033,13 +5033,13 @@
     <t xml:space="preserve">30.1584033966064</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4221782684326</t>
+    <t xml:space="preserve">30.4221801757812</t>
   </si>
   <si>
     <t xml:space="preserve">30.8813457489014</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1255836486816</t>
+    <t xml:space="preserve">31.125581741333</t>
   </si>
   <si>
     <t xml:space="preserve">30.744571685791</t>
@@ -5072,7 +5072,7 @@
     <t xml:space="preserve">30.2658672332764</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0439109802246</t>
+    <t xml:space="preserve">32.0439147949219</t>
   </si>
   <si>
     <t xml:space="preserve">32.893856048584</t>
@@ -5081,7 +5081,7 @@
     <t xml:space="preserve">32.2002258300781</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0306358337402</t>
+    <t xml:space="preserve">33.030632019043</t>
   </si>
   <si>
     <t xml:space="preserve">32.8547821044922</t>
@@ -5093,7 +5093,7 @@
     <t xml:space="preserve">31.6433639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9888076782227</t>
+    <t xml:space="preserve">30.9888095855713</t>
   </si>
   <si>
     <t xml:space="preserve">31.2916622161865</t>
@@ -5102,16 +5102,16 @@
     <t xml:space="preserve">31.1158142089844</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3858451843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2357902526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2651023864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0208587646484</t>
+    <t xml:space="preserve">32.3858489990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2357940673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2650985717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0208625793457</t>
   </si>
   <si>
     <t xml:space="preserve">32.4933090209961</t>
@@ -5126,7 +5126,7 @@
     <t xml:space="preserve">31.1646614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7605953216553</t>
+    <t xml:space="preserve">31.7605991363525</t>
   </si>
   <si>
     <t xml:space="preserve">30.1290950775146</t>
@@ -5135,10 +5135,10 @@
     <t xml:space="preserve">30.4026412963867</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1193256378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8422660827637</t>
+    <t xml:space="preserve">30.1193237304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8422679901123</t>
   </si>
   <si>
     <t xml:space="preserve">31.2818927764893</t>
@@ -5150,16 +5150,16 @@
     <t xml:space="preserve">30.3049449920654</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7836513519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7054958343506</t>
+    <t xml:space="preserve">30.7836494445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.705493927002</t>
   </si>
   <si>
     <t xml:space="preserve">30.8227272033691</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0697059631348</t>
+    <t xml:space="preserve">33.069709777832</t>
   </si>
   <si>
     <t xml:space="preserve">32.591007232666</t>
@@ -5183,7 +5183,7 @@
     <t xml:space="preserve">33.5972595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5679550170898</t>
+    <t xml:space="preserve">33.5679512023926</t>
   </si>
   <si>
     <t xml:space="preserve">34.0310287475586</t>
@@ -6231,6 +6231,9 @@
   </si>
   <si>
     <t xml:space="preserve">12.960000038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9499998092651</t>
   </si>
 </sst>
 </file>
@@ -71933,7 +71936,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6910300926</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>1072614</v>
@@ -71954,6 +71957,32 @@
         <v>2072</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6931481481</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>1041636</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>13.1999998092651</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>12.9300003051758</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>13.085000038147</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>2073</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="2074">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2075" uniqueCount="2075">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.335205078125</t>
+    <t xml:space="preserve">7.33520555496216</t>
   </si>
   <si>
     <t xml:space="preserve">AMP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39109182357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31191873550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36780595779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15357160568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96262264251709</t>
+    <t xml:space="preserve">7.39109230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31191825866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36780548095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15357112884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96262311935425</t>
   </si>
   <si>
     <t xml:space="preserve">7.21877288818359</t>
@@ -65,37 +65,37 @@
     <t xml:space="preserve">7.27931833267212</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16288566589355</t>
+    <t xml:space="preserve">7.16288614273071</t>
   </si>
   <si>
     <t xml:space="preserve">7.03248262405396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08836889266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19548606872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98590993881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13494157791138</t>
+    <t xml:space="preserve">7.08836984634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19548654556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9859094619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13494205474854</t>
   </si>
   <si>
     <t xml:space="preserve">7.3445200920105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23740339279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35383415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1489143371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18151521682739</t>
+    <t xml:space="preserve">7.23740291595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35383367538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14891481399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18151426315308</t>
   </si>
   <si>
     <t xml:space="preserve">7.40972137451172</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">7.28397464752197</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13959884643555</t>
+    <t xml:space="preserve">7.13959932327271</t>
   </si>
   <si>
     <t xml:space="preserve">7.05111122131348</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">6.84619092941284</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51086759567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45497989654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59004068374634</t>
+    <t xml:space="preserve">6.51086711883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45498085021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59004163742065</t>
   </si>
   <si>
     <t xml:space="preserve">6.33389186859131</t>
@@ -134,10 +134,10 @@
     <t xml:space="preserve">6.61798524856567</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8834490776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71113061904907</t>
+    <t xml:space="preserve">6.88344955444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71113014221191</t>
   </si>
   <si>
     <t xml:space="preserve">6.83687734603882</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">6.70181608200073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62729978561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9952244758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89276361465454</t>
+    <t xml:space="preserve">6.6272988319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99522399902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8927640914917</t>
   </si>
   <si>
     <t xml:space="preserve">6.80427503585815</t>
@@ -167,31 +167,31 @@
     <t xml:space="preserve">6.65990018844604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63195610046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79496145248413</t>
+    <t xml:space="preserve">6.63195657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79496097564697</t>
   </si>
   <si>
     <t xml:space="preserve">6.78564643859863</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86016321182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00919580459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.111656665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08371210098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20945835113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10699844360352</t>
+    <t xml:space="preserve">6.86016273498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00919532775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11165618896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08371162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20945882797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10699796676636</t>
   </si>
   <si>
     <t xml:space="preserve">7.04179668426514</t>
@@ -209,13 +209,13 @@
     <t xml:space="preserve">6.93467950820923</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91605043411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00453758239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27000331878662</t>
+    <t xml:space="preserve">6.91604995727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00453853607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2700023651123</t>
   </si>
   <si>
     <t xml:space="preserve">7.32589054107666</t>
@@ -230,55 +230,55 @@
     <t xml:space="preserve">7.41437911987305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4842381477356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57738304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55409622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73107385635376</t>
+    <t xml:space="preserve">7.48423767089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57738351821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55409669876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7310733795166</t>
   </si>
   <si>
     <t xml:space="preserve">7.60066986083984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64258432388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70312976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73573160171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88476419448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8894214630127</t>
+    <t xml:space="preserve">7.64258575439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70313024520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73573017120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88476276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88942289352417</t>
   </si>
   <si>
     <t xml:space="preserve">7.87079048156738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78696012496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94530820846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88010501861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08968448638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01760387420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09717082977295</t>
+    <t xml:space="preserve">7.78695869445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94530725479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88010549545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08968353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01760292053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09717178344727</t>
   </si>
   <si>
     <t xml:space="preserve">8.10653305053711</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.05036735534668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17205715179443</t>
+    <t xml:space="preserve">8.17205905914307</t>
   </si>
   <si>
     <t xml:space="preserve">8.21418285369873</t>
@@ -299,43 +299,43 @@
     <t xml:space="preserve">8.22354316711426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15801620483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07844924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0831298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14397621154785</t>
+    <t xml:space="preserve">8.15801811218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07845115661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08312892913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14397525787354</t>
   </si>
   <si>
     <t xml:space="preserve">8.01292419433594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91463375091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82102489471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64316844940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62912559509277</t>
+    <t xml:space="preserve">7.914635181427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82102537155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64316892623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62912654876709</t>
   </si>
   <si>
     <t xml:space="preserve">7.65253067016602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55891942977905</t>
+    <t xml:space="preserve">7.55891990661621</t>
   </si>
   <si>
     <t xml:space="preserve">7.63848829269409</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9895224571228</t>
+    <t xml:space="preserve">7.98952198028564</t>
   </si>
   <si>
     <t xml:space="preserve">7.94739723205566</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">7.67593193054199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71337509155273</t>
+    <t xml:space="preserve">7.71337556838989</t>
   </si>
   <si>
     <t xml:space="preserve">7.72273635864258</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">7.87250995635986</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92867660522461</t>
+    <t xml:space="preserve">7.92867755889893</t>
   </si>
   <si>
     <t xml:space="preserve">7.89123058319092</t>
@@ -368,37 +368,37 @@
     <t xml:space="preserve">7.71805572509766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88187122344971</t>
+    <t xml:space="preserve">7.88187074661255</t>
   </si>
   <si>
     <t xml:space="preserve">7.96143913269043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91931343078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90995454788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05504608154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18141841888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16737747192383</t>
+    <t xml:space="preserve">7.91931438446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90995359420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05504703521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18141937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16737937927246</t>
   </si>
   <si>
     <t xml:space="preserve">8.19546031951904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19078063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3077917098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36395740509033</t>
+    <t xml:space="preserve">8.19077968597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30779266357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36395835876465</t>
   </si>
   <si>
     <t xml:space="preserve">8.34991550445557</t>
@@ -407,28 +407,28 @@
     <t xml:space="preserve">8.3311939239502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29375076293945</t>
+    <t xml:space="preserve">8.29374980926514</t>
   </si>
   <si>
     <t xml:space="preserve">8.15333652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28907012939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36863613128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50905227661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60733985900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51373100280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63542461395264</t>
+    <t xml:space="preserve">8.28906917572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36863803863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50905132293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60734081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51373291015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.635422706604</t>
   </si>
   <si>
     <t xml:space="preserve">8.75711345672607</t>
@@ -437,22 +437,22 @@
     <t xml:space="preserve">8.65414524078369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78519630432129</t>
+    <t xml:space="preserve">8.78519725799561</t>
   </si>
   <si>
     <t xml:space="preserve">8.8085994720459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92093086242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84604263305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81796169281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74775409698486</t>
+    <t xml:space="preserve">8.92092990875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84604358673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81796073913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74775505065918</t>
   </si>
   <si>
     <t xml:space="preserve">8.75243473052979</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">8.82264137268066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73371124267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77115631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76179504394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65882587432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59329891204834</t>
+    <t xml:space="preserve">8.73371315002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77115535736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76179599761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6588249206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59329986572266</t>
   </si>
   <si>
     <t xml:space="preserve">8.57457828521729</t>
@@ -482,61 +482,61 @@
     <t xml:space="preserve">8.56053733825684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48564910888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54181575775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5324535369873</t>
+    <t xml:space="preserve">8.48564720153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54181480407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53245449066162</t>
   </si>
   <si>
     <t xml:space="preserve">8.66818618774414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4996919631958</t>
+    <t xml:space="preserve">8.49969100952148</t>
   </si>
   <si>
     <t xml:space="preserve">8.61670112609863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49500942230225</t>
+    <t xml:space="preserve">8.49500846862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.55585670471191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61202144622803</t>
+    <t xml:space="preserve">8.61202049255371</t>
   </si>
   <si>
     <t xml:space="preserve">8.46692657470703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52777290344238</t>
+    <t xml:space="preserve">8.5277738571167</t>
   </si>
   <si>
     <t xml:space="preserve">8.56521701812744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69158840179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08006763458252</t>
+    <t xml:space="preserve">8.69158744812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08006572723389</t>
   </si>
   <si>
     <t xml:space="preserve">9.24856185913086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07070446014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01453971862793</t>
+    <t xml:space="preserve">9.07070255279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01453876495361</t>
   </si>
   <si>
     <t xml:space="preserve">8.89284706115723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93965339660645</t>
+    <t xml:space="preserve">8.93965244293213</t>
   </si>
   <si>
     <t xml:space="preserve">8.81328010559082</t>
@@ -548,25 +548,25 @@
     <t xml:space="preserve">8.42480278015137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40140056610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39671993255615</t>
+    <t xml:space="preserve">8.40139961242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39672183990479</t>
   </si>
   <si>
     <t xml:space="preserve">8.58393859863281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34523487091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46224784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3826789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47160816192627</t>
+    <t xml:space="preserve">8.34523582458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46224689483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38267803192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47160625457764</t>
   </si>
   <si>
     <t xml:space="preserve">8.98645687103271</t>
@@ -578,13 +578,13 @@
     <t xml:space="preserve">9.06134414672852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51841259002686</t>
+    <t xml:space="preserve">8.51841354370117</t>
   </si>
   <si>
     <t xml:space="preserve">8.16269779205322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31247138977051</t>
+    <t xml:space="preserve">8.31247234344482</t>
   </si>
   <si>
     <t xml:space="preserve">7.44190979003906</t>
@@ -593,10 +593,10 @@
     <t xml:space="preserve">7.98484086990356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95675849914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38735961914062</t>
+    <t xml:space="preserve">7.95675992965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38735866546631</t>
   </si>
   <si>
     <t xml:space="preserve">8.41076183319092</t>
@@ -605,52 +605,52 @@
     <t xml:space="preserve">8.44820404052734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48096942901611</t>
+    <t xml:space="preserve">8.48096752166748</t>
   </si>
   <si>
     <t xml:space="preserve">8.37331771850586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2329044342041</t>
+    <t xml:space="preserve">8.23290634155273</t>
   </si>
   <si>
     <t xml:space="preserve">8.18610000610352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37799835205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57925891876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64946460723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72435283660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67286586761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74307346343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7103099822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15495204925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96773433685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14091300964355</t>
+    <t xml:space="preserve">8.3779993057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57925701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64946269989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72435092926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67286682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74307250976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71031093597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.154953956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96773529052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14091110229492</t>
   </si>
   <si>
     <t xml:space="preserve">9.26728248596191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33749103546143</t>
+    <t xml:space="preserve">9.33749008178711</t>
   </si>
   <si>
     <t xml:space="preserve">9.40769672393799</t>
@@ -659,37 +659,37 @@
     <t xml:space="preserve">9.37961578369141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29536628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3608922958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44514083862305</t>
+    <t xml:space="preserve">9.29536533355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36089134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44514179229736</t>
   </si>
   <si>
     <t xml:space="preserve">9.48258304595947</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43578052520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35621166229248</t>
+    <t xml:space="preserve">9.4357795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35621070861816</t>
   </si>
   <si>
     <t xml:space="preserve">9.11282825469971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1081485748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15963459014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46386051177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81021499633789</t>
+    <t xml:space="preserve">9.10814762115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15963268280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4638614654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81021308898926</t>
   </si>
   <si>
     <t xml:space="preserve">9.95999050140381</t>
@@ -698,16 +698,16 @@
     <t xml:space="preserve">9.82893657684326</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91318416595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6417179107666</t>
+    <t xml:space="preserve">9.91318702697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64171886444092</t>
   </si>
   <si>
     <t xml:space="preserve">9.70724487304688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71660709381104</t>
+    <t xml:space="preserve">9.71660804748535</t>
   </si>
   <si>
     <t xml:space="preserve">9.66044044494629</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">9.79149341583252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0255165100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0067949295044</t>
+    <t xml:space="preserve">10.0255155563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0067939758301</t>
   </si>
   <si>
     <t xml:space="preserve">10.1846504211426</t>
@@ -728,49 +728,49 @@
     <t xml:space="preserve">10.240816116333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2595367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4280347824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4748373031616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3625078201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3344249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5778093338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5122814178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5029211044312</t>
+    <t xml:space="preserve">10.2595376968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.428032875061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4748382568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3625068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3344259262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.577808380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5122833251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5029220581055</t>
   </si>
   <si>
     <t xml:space="preserve">10.8118314743042</t>
   </si>
   <si>
-    <t xml:space="preserve">10.88671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7182207107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6526947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6433343887329</t>
+    <t xml:space="preserve">10.8867168426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.718222618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6526956558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6433334350586</t>
   </si>
   <si>
     <t xml:space="preserve">10.6246128082275</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7088594436646</t>
+    <t xml:space="preserve">10.7088603973389</t>
   </si>
   <si>
     <t xml:space="preserve">10.8960800170898</t>
@@ -782,61 +782,61 @@
     <t xml:space="preserve">10.9335222244263</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9990472793579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1301002502441</t>
+    <t xml:space="preserve">10.9990482330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1301021575928</t>
   </si>
   <si>
     <t xml:space="preserve">11.0926580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2517929077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9616050720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2049894332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1675434112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1488218307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1862668991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2798738479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4296493530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4109258651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4577322006226</t>
+    <t xml:space="preserve">11.2517919540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9616041183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2049875259399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1675462722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1488227844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1862659454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2798748016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4296503067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.410927772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4577331542969</t>
   </si>
   <si>
     <t xml:space="preserve">11.5801248550415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8249063491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8625650405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9472990036011</t>
+    <t xml:space="preserve">11.8249073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.862566947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9472980499268</t>
   </si>
   <si>
     <t xml:space="preserve">11.9190540313721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9284687042236</t>
+    <t xml:space="preserve">11.9284696578979</t>
   </si>
   <si>
     <t xml:space="preserve">11.9378843307495</t>
@@ -845,34 +845,34 @@
     <t xml:space="preserve">11.9661273956299</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0602741241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0979337692261</t>
+    <t xml:space="preserve">12.0602750778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0979347229004</t>
   </si>
   <si>
     <t xml:space="preserve">12.0226163864136</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2109107971191</t>
+    <t xml:space="preserve">12.2109117507935</t>
   </si>
   <si>
     <t xml:space="preserve">12.1826658248901</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2391548156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9096384048462</t>
+    <t xml:space="preserve">12.2391557693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9096393585205</t>
   </si>
   <si>
     <t xml:space="preserve">12.1450071334839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4859752655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2976808547974</t>
+    <t xml:space="preserve">11.4859762191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.297682762146</t>
   </si>
   <si>
     <t xml:space="preserve">11.6931009292603</t>
@@ -881,52 +881,52 @@
     <t xml:space="preserve">11.7307586669922</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7684192657471</t>
+    <t xml:space="preserve">11.7684183120728</t>
   </si>
   <si>
     <t xml:space="preserve">11.7590036392212</t>
   </si>
   <si>
-    <t xml:space="preserve">11.627197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5707082748413</t>
+    <t xml:space="preserve">11.6271982192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5707092285156</t>
   </si>
   <si>
     <t xml:space="preserve">11.5236358642578</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4671468734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3729991912842</t>
+    <t xml:space="preserve">11.4671459197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3730010986328</t>
   </si>
   <si>
     <t xml:space="preserve">11.0811424255371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.88343334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6951379776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5633325576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6104068756104</t>
+    <t xml:space="preserve">10.8834342956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6951370239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5633335113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6104049682617</t>
   </si>
   <si>
     <t xml:space="preserve">10.7422122955322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.911675453186</t>
+    <t xml:space="preserve">10.9116773605347</t>
   </si>
   <si>
     <t xml:space="preserve">10.9022626876831</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9493360519409</t>
+    <t xml:space="preserve">10.9493350982666</t>
   </si>
   <si>
     <t xml:space="preserve">11.1376314163208</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">11.3447551727295</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4106569290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.269437789917</t>
+    <t xml:space="preserve">11.4106578826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2694387435913</t>
   </si>
   <si>
     <t xml:space="preserve">11.5048055648804</t>
@@ -959,25 +959,25 @@
     <t xml:space="preserve">11.2788524627686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2506074905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1093864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0340690612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9210929870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6668939590454</t>
+    <t xml:space="preserve">11.2506065368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1093873977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0340700149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9210920333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6668949127197</t>
   </si>
   <si>
     <t xml:space="preserve">10.8363590240479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7892866134644</t>
+    <t xml:space="preserve">10.78928565979</t>
   </si>
   <si>
     <t xml:space="preserve">11.1941204071045</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">11.1658744812012</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0717267990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1282157897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3165121078491</t>
+    <t xml:space="preserve">11.0717277526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1282167434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3165111541748</t>
   </si>
   <si>
     <t xml:space="preserve">11.3259258270264</t>
@@ -1001,67 +1001,67 @@
     <t xml:space="preserve">11.2411918640137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0623121261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0905570983887</t>
+    <t xml:space="preserve">11.0623140335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0905561447144</t>
   </si>
   <si>
     <t xml:space="preserve">11.1752901077271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4389028549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7213459014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8154926300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.984956741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.013201713562</t>
+    <t xml:space="preserve">11.4389019012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7213430404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8154916763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9849576950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0132026672363</t>
   </si>
   <si>
     <t xml:space="preserve">11.9567127227783</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0508604049683</t>
+    <t xml:space="preserve">12.0508613586426</t>
   </si>
   <si>
     <t xml:space="preserve">12.0414457321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0791053771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9755430221558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8343210220337</t>
+    <t xml:space="preserve">12.0791034698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9755420684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.834321975708</t>
   </si>
   <si>
     <t xml:space="preserve">12.2203245162964</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1544237136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.107349395752</t>
+    <t xml:space="preserve">12.1544218063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1073484420776</t>
   </si>
   <si>
     <t xml:space="preserve">12.4839382171631</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5215969085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.643988609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.785210609436</t>
+    <t xml:space="preserve">12.5215978622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6439895629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7852077484131</t>
   </si>
   <si>
     <t xml:space="preserve">12.8134527206421</t>
@@ -1073,16 +1073,16 @@
     <t xml:space="preserve">12.8040399551392</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1920824050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7872476577759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8531522750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0320320129395</t>
+    <t xml:space="preserve">12.1920804977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7872486114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8531503677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0320310592651</t>
   </si>
   <si>
     <t xml:space="preserve">12.1732521057129</t>
@@ -1094,46 +1094,46 @@
     <t xml:space="preserve">11.9002246856689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.448317527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5612936019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4012441635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6742706298828</t>
+    <t xml:space="preserve">11.4483184814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5612926483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4012422561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6742725372314</t>
   </si>
   <si>
     <t xml:space="preserve">11.7778329849243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0885181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0696897506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2014961242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1355924606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3615455627441</t>
+    <t xml:space="preserve">12.0885200500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0696887969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2014970779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.135594367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3615474700928</t>
   </si>
   <si>
     <t xml:space="preserve">12.3333024978638</t>
   </si>
   <si>
-    <t xml:space="preserve">12.163836479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7401742935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1261796951294</t>
+    <t xml:space="preserve">12.1638374328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7401752471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1261777877808</t>
   </si>
   <si>
     <t xml:space="preserve">12.5404262542725</t>
@@ -1142,25 +1142,25 @@
     <t xml:space="preserve">12.5498418807983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5027666091919</t>
+    <t xml:space="preserve">12.5027675628662</t>
   </si>
   <si>
     <t xml:space="preserve">12.6345729827881</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1335544586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1241407394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.086480140686</t>
+    <t xml:space="preserve">13.1335535049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1241397857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0864810943604</t>
   </si>
   <si>
     <t xml:space="preserve">12.9546756744385</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4254112243652</t>
+    <t xml:space="preserve">13.4254102706909</t>
   </si>
   <si>
     <t xml:space="preserve">13.4630718231201</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">13.5572175979614</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6042928695679</t>
+    <t xml:space="preserve">13.6042909622192</t>
   </si>
   <si>
     <t xml:space="preserve">13.5101432800293</t>
@@ -1181,25 +1181,25 @@
     <t xml:space="preserve">13.2559461593628</t>
   </si>
   <si>
-    <t xml:space="preserve">13.472484588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3030204772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9735040664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6157445907593</t>
+    <t xml:space="preserve">13.4724855422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3030195236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.973503112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.615743637085</t>
   </si>
   <si>
     <t xml:space="preserve">12.4086198806763</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3803768157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.46510887146</t>
+    <t xml:space="preserve">12.3803749084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4651079177856</t>
   </si>
   <si>
     <t xml:space="preserve">12.5121831893921</t>
@@ -1208,34 +1208,34 @@
     <t xml:space="preserve">12.822868347168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.879358291626</t>
+    <t xml:space="preserve">12.8793563842773</t>
   </si>
   <si>
     <t xml:space="preserve">12.851113319397</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5969142913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2862281799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.257984161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7287225723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0394067764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0958957672119</t>
+    <t xml:space="preserve">12.5969161987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.286229133606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2579851150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7287216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0394077301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0958948135376</t>
   </si>
   <si>
     <t xml:space="preserve">13.2653608322144</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4065818786621</t>
+    <t xml:space="preserve">13.4065828323364</t>
   </si>
   <si>
     <t xml:space="preserve">13.3312654495239</t>
@@ -1244,268 +1244,268 @@
     <t xml:space="preserve">13.321849822998</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1617984771729</t>
+    <t xml:space="preserve">13.1617994308472</t>
   </si>
   <si>
     <t xml:space="preserve">13.3406782150269</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2465314865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8887720108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8605260848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.293604850769</t>
+    <t xml:space="preserve">13.2465324401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8887710571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8605270385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2936058044434</t>
   </si>
   <si>
     <t xml:space="preserve">13.566632270813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6419515609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3124341964722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7925863265991</t>
+    <t xml:space="preserve">13.6419496536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3124361038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7925853729248</t>
   </si>
   <si>
     <t xml:space="preserve">13.9997110366821</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1409311294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.395131111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3009824752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5645942687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6022539138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6869859695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9129390716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8564500808716</t>
+    <t xml:space="preserve">14.1409320831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3951292037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3009815216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5645952224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6022529602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6869869232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9129400253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8564510345459</t>
   </si>
   <si>
     <t xml:space="preserve">15.1106481552124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.969428062439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9976720809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0353298187256</t>
+    <t xml:space="preserve">14.9694271087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.997673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0353317260742</t>
   </si>
   <si>
     <t xml:space="preserve">14.903525352478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8941097259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7152290344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5928392410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1671380996704</t>
+    <t xml:space="preserve">14.8941087722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7152309417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5928382873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.167140007019</t>
   </si>
   <si>
     <t xml:space="preserve">15.2706995010376</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2424564361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2518711090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4401655197144</t>
+    <t xml:space="preserve">15.2424554824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2518730163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.44016456604</t>
   </si>
   <si>
     <t xml:space="preserve">15.3930902481079</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5531415939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6567039489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4213361740112</t>
+    <t xml:space="preserve">15.5531425476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6567049026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4213342666626</t>
   </si>
   <si>
     <t xml:space="preserve">15.0165014266968</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3460178375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8185272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6668338775635</t>
+    <t xml:space="preserve">15.3460168838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.818528175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6668348312378</t>
   </si>
   <si>
     <t xml:space="preserve">14.3444862365723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6099510192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7331991195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.875412940979</t>
+    <t xml:space="preserve">14.6099491119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7332000732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8754110336304</t>
   </si>
   <si>
     <t xml:space="preserve">13.9273290634155</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4013719558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6194305419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6289119720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1882801055908</t>
+    <t xml:space="preserve">14.4013710021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6194295883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6289110183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1882791519165</t>
   </si>
   <si>
     <t xml:space="preserve">15.4916648864746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1173992156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4587097167969</t>
+    <t xml:space="preserve">16.1174030303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4587116241455</t>
   </si>
   <si>
     <t xml:space="preserve">16.1553249359131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1648025512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2027282714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2122077941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3259792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1079216003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.069995880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.525074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7241725921631</t>
+    <t xml:space="preserve">16.1648044586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.202730178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2122097015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3259773254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1079196929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0699977874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5250759124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7241744995117</t>
   </si>
   <si>
     <t xml:space="preserve">16.6672878265381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5724792480469</t>
+    <t xml:space="preserve">16.5724811553955</t>
   </si>
   <si>
     <t xml:space="preserve">16.3070182800293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596111297607</t>
+    <t xml:space="preserve">16.2596130371094</t>
   </si>
   <si>
     <t xml:space="preserve">16.6767692565918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8379421234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8853454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0465202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9232711791992</t>
+    <t xml:space="preserve">16.8379440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.885347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0465240478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9232692718506</t>
   </si>
   <si>
     <t xml:space="preserve">16.771577835083</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3733825683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4492282867432</t>
+    <t xml:space="preserve">16.373384475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4492301940918</t>
   </si>
   <si>
     <t xml:space="preserve">16.2216892242432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4018268585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5535182952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3639011383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5155944824219</t>
+    <t xml:space="preserve">16.4018230438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5535163879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3639030456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5155963897705</t>
   </si>
   <si>
     <t xml:space="preserve">17.1034069061279</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5395259857178</t>
+    <t xml:space="preserve">17.5395240783691</t>
   </si>
   <si>
     <t xml:space="preserve">17.9472007751465</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4447135925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0799293518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1652584075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7151470184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1368160247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4117603302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2505855560303</t>
+    <t xml:space="preserve">17.4447154998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0799331665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1652603149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.715145111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1368141174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4117584228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2505874633789</t>
   </si>
   <si>
     <t xml:space="preserve">18.0704498291016</t>
@@ -1523,43 +1523,43 @@
     <t xml:space="preserve">17.7575817108154</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2979907989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3738346099854</t>
+    <t xml:space="preserve">18.2979888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.373836517334</t>
   </si>
   <si>
     <t xml:space="preserve">18.203182220459</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0325260162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1083736419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2126598358154</t>
+    <t xml:space="preserve">18.032527923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1083717346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2126617431641</t>
   </si>
   <si>
     <t xml:space="preserve">18.0609683990479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9377193450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0040855407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5774478912354</t>
+    <t xml:space="preserve">17.9377174377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0040836334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.577449798584</t>
   </si>
   <si>
     <t xml:space="preserve">18.3927974700928</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8334312438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0135631561279</t>
+    <t xml:space="preserve">17.8334293365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0135650634766</t>
   </si>
   <si>
     <t xml:space="preserve">18.7435894012451</t>
@@ -1568,37 +1568,37 @@
     <t xml:space="preserve">19.3408794403076</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4167251586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3788051605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1891860961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.056453704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7246265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4496841430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5255279541016</t>
+    <t xml:space="preserve">19.41672706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3788032531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.18918800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0564556121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7246284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4496803283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5255317687988</t>
   </si>
   <si>
     <t xml:space="preserve">18.7720317840576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9616451263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6867008209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.146297454834</t>
+    <t xml:space="preserve">18.9616470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6867046356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1462955474854</t>
   </si>
   <si>
     <t xml:space="preserve">18.5065689086914</t>
@@ -1607,46 +1607,46 @@
     <t xml:space="preserve">18.0420074462891</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3025016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5629997253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.453742980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5864744186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6718034744263</t>
+    <t xml:space="preserve">17.3025054931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5629978179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4537420272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5864772796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6718053817749</t>
   </si>
   <si>
     <t xml:space="preserve">15.0081443786621</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4252996444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4632225036621</t>
+    <t xml:space="preserve">15.4253005981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4632234573364</t>
   </si>
   <si>
     <t xml:space="preserve">15.8045320510864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7286863327026</t>
+    <t xml:space="preserve">15.7286853790283</t>
   </si>
   <si>
     <t xml:space="preserve">14.9512586593628</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0745096206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9986629486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9797019958496</t>
+    <t xml:space="preserve">15.0745086669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9986619949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9797029495239</t>
   </si>
   <si>
     <t xml:space="preserve">15.0176248550415</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">14.6573543548584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.704758644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6763153076172</t>
+    <t xml:space="preserve">14.7047576904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6763143539429</t>
   </si>
   <si>
     <t xml:space="preserve">14.6478729248047</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">14.932297706604</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0555477142334</t>
+    <t xml:space="preserve">15.055549621582</t>
   </si>
   <si>
     <t xml:space="preserve">14.7900857925415</t>
@@ -1679,61 +1679,61 @@
     <t xml:space="preserve">13.8135604858398</t>
   </si>
   <si>
-    <t xml:space="preserve">13.728232383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1309404373169</t>
+    <t xml:space="preserve">13.7282333374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1309413909912</t>
   </si>
   <si>
     <t xml:space="preserve">13.0835380554199</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3869228363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3964042663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6523866653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4912128448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2257490158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8704452514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0126571655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4961805343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2212362289429</t>
+    <t xml:space="preserve">13.386923789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2636728286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3964033126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6523857116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4912118911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2257480621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8704462051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.012656211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4961795806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2212352752686</t>
   </si>
   <si>
     <t xml:space="preserve">14.1643495559692</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3065633773804</t>
+    <t xml:space="preserve">14.3065624237061</t>
   </si>
   <si>
     <t xml:space="preserve">14.3350057601929</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7945976257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7377138137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5955009460449</t>
+    <t xml:space="preserve">13.7945995330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7377128601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5955018997192</t>
   </si>
   <si>
     <t xml:space="preserve">13.7566757202148</t>
@@ -1748,82 +1748,82 @@
     <t xml:space="preserve">14.4203329086304</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7756376266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7232656478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.320556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1878271102905</t>
+    <t xml:space="preserve">13.7756366729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7232646942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3205575942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1878252029419</t>
   </si>
   <si>
     <t xml:space="preserve">13.7471942901611</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0695419311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8374891281128</t>
+    <t xml:space="preserve">14.069543838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8374881744385</t>
   </si>
   <si>
     <t xml:space="preserve">15.2546453475952</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8848943710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0839910507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1787996292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1503553390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3115291595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3589353561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2925691604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1408739089966</t>
+    <t xml:space="preserve">14.8848934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0839900970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1787986755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1503572463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3115310668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3589372634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2925682067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1408758163452</t>
   </si>
   <si>
     <t xml:space="preserve">15.0271053314209</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9228162765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8280076980591</t>
+    <t xml:space="preserve">14.922815322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8280086517334</t>
   </si>
   <si>
     <t xml:space="preserve">14.8659315109253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9417791366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.614914894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7097234725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0650291442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2167224884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5485525131226</t>
+    <t xml:space="preserve">14.9417772293091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6149158477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7097225189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0650300979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.216721534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5485506057739</t>
   </si>
   <si>
     <t xml:space="preserve">15.4347820281982</t>
@@ -1832,16 +1832,16 @@
     <t xml:space="preserve">15.3968572616577</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7806034088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9038562774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2262029647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1977615356445</t>
+    <t xml:space="preserve">14.7806043624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9038553237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.226203918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1977605819702</t>
   </si>
   <si>
     <t xml:space="preserve">15.4442625045776</t>
@@ -1850,13 +1850,13 @@
     <t xml:space="preserve">15.3684148788452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5106287002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.738166809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4302654266357</t>
+    <t xml:space="preserve">15.5106296539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7381687164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4302673339844</t>
   </si>
   <si>
     <t xml:space="preserve">15.9657077789307</t>
@@ -1865,19 +1865,19 @@
     <t xml:space="preserve">15.2641267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7855710983276</t>
+    <t xml:space="preserve">15.7855701446533</t>
   </si>
   <si>
     <t xml:space="preserve">16.6862487792969</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8474254608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4966316223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.193244934082</t>
+    <t xml:space="preserve">16.8474235534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4966335296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1932468414307</t>
   </si>
   <si>
     <t xml:space="preserve">16.2311706542969</t>
@@ -1892,13 +1892,13 @@
     <t xml:space="preserve">16.8095016479492</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7336540222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8948307037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8663864135742</t>
+    <t xml:space="preserve">16.7336521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8948287963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8663845062256</t>
   </si>
   <si>
     <t xml:space="preserve">16.2501335144043</t>
@@ -1907,40 +1907,40 @@
     <t xml:space="preserve">15.8993425369263</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8898620605469</t>
+    <t xml:space="preserve">15.8898611068726</t>
   </si>
   <si>
     <t xml:space="preserve">15.9277820587158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8519382476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.354419708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.240650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9183053970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5016021728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6627712249756</t>
+    <t xml:space="preserve">15.8519372940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3544216156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2406482696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9183044433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5015983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6627731323242</t>
   </si>
   <si>
     <t xml:space="preserve">18.089412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3119850158691</t>
+    <t xml:space="preserve">17.3119831085205</t>
   </si>
   <si>
     <t xml:space="preserve">17.2835426330566</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8239459991455</t>
+    <t xml:space="preserve">17.8239498138428</t>
   </si>
   <si>
     <t xml:space="preserve">18.6677417755127</t>
@@ -1949,28 +1949,28 @@
     <t xml:space="preserve">18.5743827819824</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8704261779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.596212387085</t>
+    <t xml:space="preserve">18.8704280853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5962104797363</t>
   </si>
   <si>
     <t xml:space="preserve">19.5007133483887</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9277248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9468250274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9850234985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5934829711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7080783843994</t>
+    <t xml:space="preserve">18.9277267456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9468231201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9850254058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5934810638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.708080291748</t>
   </si>
   <si>
     <t xml:space="preserve">18.9659252166748</t>
@@ -1979,19 +1979,19 @@
     <t xml:space="preserve">19.0327739715576</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2333221435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.386116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0900707244873</t>
+    <t xml:space="preserve">19.2333202362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3861179351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0900726318359</t>
   </si>
   <si>
     <t xml:space="preserve">19.1951198577881</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1187210083008</t>
+    <t xml:space="preserve">19.1187229156494</t>
   </si>
   <si>
     <t xml:space="preserve">19.252420425415</t>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">19.9018077850342</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1501007080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2646999359131</t>
+    <t xml:space="preserve">20.1501026153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2646980285645</t>
   </si>
   <si>
     <t xml:space="preserve">20.5893936157227</t>
@@ -2012,67 +2012,67 @@
     <t xml:space="preserve">20.5511932373047</t>
   </si>
   <si>
-    <t xml:space="preserve">20.799488067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9591064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8445072174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4816131591797</t>
+    <t xml:space="preserve">20.7994899749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9591045379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8445091247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4816150665283</t>
   </si>
   <si>
     <t xml:space="preserve">19.3097171783447</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6344127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6726112365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0928020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9400043487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6535110473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.558012008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7299118041992</t>
+    <t xml:space="preserve">19.6344108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6726093292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0928039550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9400062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6535091400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5580139160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7299098968506</t>
   </si>
   <si>
     <t xml:space="preserve">20.3028984069824</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2837982177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2264995574951</t>
+    <t xml:space="preserve">20.2838001251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2265014648438</t>
   </si>
   <si>
     <t xml:space="preserve">20.7039909362793</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6848926544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4174976348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0355033874512</t>
+    <t xml:space="preserve">20.6848907470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4174957275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0355014801025</t>
   </si>
   <si>
     <t xml:space="preserve">20.1310024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1883010864258</t>
+    <t xml:space="preserve">20.1882991790771</t>
   </si>
   <si>
     <t xml:space="preserve">21.2769794464111</t>
@@ -2087,46 +2087,46 @@
     <t xml:space="preserve">20.0164031982422</t>
   </si>
   <si>
-    <t xml:space="preserve">20.570291519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9904861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1050815582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1623821258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2578811645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0286827087402</t>
+    <t xml:space="preserve">20.5702953338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9904842376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1050834655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1623802185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2578792572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0286846160889</t>
   </si>
   <si>
     <t xml:space="preserve">21.2960796356201</t>
   </si>
   <si>
-    <t xml:space="preserve">21.849967956543</t>
+    <t xml:space="preserve">21.8499660491943</t>
   </si>
   <si>
     <t xml:space="preserve">22.4802570343018</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5566520690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5184574127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0982608795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2510623931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9645671844482</t>
+    <t xml:space="preserve">22.5566539764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5184535980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0982627868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2510585784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9645652770996</t>
   </si>
   <si>
     <t xml:space="preserve">21.9454669952393</t>
@@ -2156,10 +2156,10 @@
     <t xml:space="preserve">20.474796295166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4556941986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1241817474365</t>
+    <t xml:space="preserve">20.455696105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1241836547852</t>
   </si>
   <si>
     <t xml:space="preserve">20.7803897857666</t>
@@ -2174,67 +2174,67 @@
     <t xml:space="preserve">21.7353706359863</t>
   </si>
   <si>
-    <t xml:space="preserve">21.506175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2196788787842</t>
+    <t xml:space="preserve">21.5061740875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2196807861328</t>
   </si>
   <si>
     <t xml:space="preserve">21.3724765777588</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6016731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6780700683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4870758056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5825729370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.646692276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6084938049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4938945770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8567886352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3792953491211</t>
+    <t xml:space="preserve">21.6016750335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.678071975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4870777130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5825748443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6466941833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.608491897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4938926696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8567867279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3792991638184</t>
   </si>
   <si>
     <t xml:space="preserve">20.8949851989746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9331855773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3219985961914</t>
+    <t xml:space="preserve">20.9331874847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3219966888428</t>
   </si>
   <si>
     <t xml:space="preserve">20.3410968780518</t>
   </si>
   <si>
-    <t xml:space="preserve">21.830867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0218658447266</t>
+    <t xml:space="preserve">21.8308696746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0218639373779</t>
   </si>
   <si>
     <t xml:space="preserve">22.5375556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6521511077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.015043258667</t>
+    <t xml:space="preserve">22.6521530151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0150470733643</t>
   </si>
   <si>
     <t xml:space="preserve">23.4543361663818</t>
@@ -2252,19 +2252,19 @@
     <t xml:space="preserve">24.084623336792</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7981281280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8745307922363</t>
+    <t xml:space="preserve">23.7981300354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8745288848877</t>
   </si>
   <si>
     <t xml:space="preserve">23.970027923584</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3711204528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8677101135254</t>
+    <t xml:space="preserve">24.3711185455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8677082061768</t>
   </si>
   <si>
     <t xml:space="preserve">25.0969047546387</t>
@@ -2273,94 +2273,94 @@
     <t xml:space="preserve">25.3642978668213</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3329200744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9823055267334</t>
+    <t xml:space="preserve">24.3329181671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.982307434082</t>
   </si>
   <si>
     <t xml:space="preserve">25.287899017334</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9250087738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6194114685059</t>
+    <t xml:space="preserve">24.9250068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0205059051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6194133758545</t>
   </si>
   <si>
     <t xml:space="preserve">24.9441070556641</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8295078277588</t>
+    <t xml:space="preserve">24.8295097351074</t>
   </si>
   <si>
     <t xml:space="preserve">24.6385116577148</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4475154876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5430145263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3520164489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6576156616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6767120361328</t>
+    <t xml:space="preserve">24.4475173950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5430164337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3520183563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6576137542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6767139434814</t>
   </si>
   <si>
     <t xml:space="preserve">24.4857158660889</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5621147155762</t>
+    <t xml:space="preserve">24.5621166229248</t>
   </si>
   <si>
     <t xml:space="preserve">24.5812149047852</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6958141326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3070011138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3451995849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8486080169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0014038085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2115020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7653923034668</t>
+    <t xml:space="preserve">24.6958103179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.306999206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3451976776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8486099243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0014057159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2115039825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7653884887695</t>
   </si>
   <si>
     <t xml:space="preserve">25.6125926971436</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5552940368652</t>
+    <t xml:space="preserve">25.5552959442139</t>
   </si>
   <si>
     <t xml:space="preserve">25.1542015075684</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8226909637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7722091674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5239143371582</t>
+    <t xml:space="preserve">25.8226890563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7722110748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5239162445068</t>
   </si>
   <si>
     <t xml:space="preserve">24.9059066772461</t>
@@ -2372,67 +2372,67 @@
     <t xml:space="preserve">26.2237815856934</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2810802459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3956775665283</t>
+    <t xml:space="preserve">26.2810821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.395679473877</t>
   </si>
   <si>
     <t xml:space="preserve">27.1405620574951</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2169647216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5225563049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.694450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8281517028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1910438537598</t>
+    <t xml:space="preserve">27.2169628143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.522554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6944541931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8281497955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1910419464111</t>
   </si>
   <si>
     <t xml:space="preserve">28.783130645752</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2865409851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8854484558105</t>
+    <t xml:space="preserve">28.2865428924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8854503631592</t>
   </si>
   <si>
     <t xml:space="preserve">25.9754867553711</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2306003570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6003170013428</t>
+    <t xml:space="preserve">25.2306022644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6003131866455</t>
   </si>
   <si>
     <t xml:space="preserve">23.6071319580078</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4666175842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4352340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8254070281982</t>
+    <t xml:space="preserve">24.4666156768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4352397918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8254089355469</t>
   </si>
   <si>
     <t xml:space="preserve">19.3479175567627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5852918624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.323356628418</t>
+    <t xml:space="preserve">15.5852909088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3233585357666</t>
   </si>
   <si>
     <t xml:space="preserve">15.7285385131836</t>
@@ -2441,10 +2441,10 @@
     <t xml:space="preserve">16.1200790405273</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9031658172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5239028930664</t>
+    <t xml:space="preserve">16.9031677246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.523904800415</t>
   </si>
   <si>
     <t xml:space="preserve">17.7435512542725</t>
@@ -2453,10 +2453,10 @@
     <t xml:space="preserve">18.1350917816162</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8322257995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1446399688721</t>
+    <t xml:space="preserve">18.8322296142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1446418762207</t>
   </si>
   <si>
     <t xml:space="preserve">18.221040725708</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">17.8772449493408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3806591033936</t>
+    <t xml:space="preserve">17.3806571960449</t>
   </si>
   <si>
     <t xml:space="preserve">17.4093055725098</t>
@@ -2480,7 +2480,7 @@
     <t xml:space="preserve">17.6480503082275</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7844772338867</t>
+    <t xml:space="preserve">18.7844791412354</t>
   </si>
   <si>
     <t xml:space="preserve">18.4311351776123</t>
@@ -2495,49 +2495,49 @@
     <t xml:space="preserve">17.9536437988281</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8663387298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2715187072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8465557098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0068531036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2456016540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.987756729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9686527252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7681083679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6753425598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7640190124512</t>
+    <t xml:space="preserve">20.8663368225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.271520614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8465538024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.006856918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2455997467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9877548217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9686546325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7681102752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6753406524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7640209197998</t>
   </si>
   <si>
     <t xml:space="preserve">21.3820266723633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3370094299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7926712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0191345214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4297771453857</t>
+    <t xml:space="preserve">22.337007522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.792667388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.019136428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4297752380371</t>
   </si>
   <si>
     <t xml:space="preserve">21.8595161437988</t>
@@ -2549,10 +2549,10 @@
     <t xml:space="preserve">21.9932155609131</t>
   </si>
   <si>
-    <t xml:space="preserve">21.658971786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0341472625732</t>
+    <t xml:space="preserve">21.6589736938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0341453552246</t>
   </si>
   <si>
     <t xml:space="preserve">23.1391906738281</t>
@@ -2567,19 +2567,19 @@
     <t xml:space="preserve">23.8267803192139</t>
   </si>
   <si>
-    <t xml:space="preserve">23.521183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8458786010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8172302246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3588390350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6903514862061</t>
+    <t xml:space="preserve">23.5211849212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8458766937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8172283172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3588371276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6903495788574</t>
   </si>
   <si>
     <t xml:space="preserve">22.6330528259277</t>
@@ -2597,16 +2597,16 @@
     <t xml:space="preserve">22.9386463165283</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3015384674072</t>
+    <t xml:space="preserve">23.3015403747559</t>
   </si>
   <si>
     <t xml:space="preserve">22.6808013916016</t>
   </si>
   <si>
-    <t xml:space="preserve">22.709451675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1487426757812</t>
+    <t xml:space="preserve">22.7094497680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1487407684326</t>
   </si>
   <si>
     <t xml:space="preserve">23.4638862609863</t>
@@ -2615,10 +2615,10 @@
     <t xml:space="preserve">22.4229564666748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4611549377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6426010131836</t>
+    <t xml:space="preserve">22.4611568450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6426029205322</t>
   </si>
   <si>
     <t xml:space="preserve">22.7381000518799</t>
@@ -2630,16 +2630,16 @@
     <t xml:space="preserve">23.2442398071289</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5402851104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7408294677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8363265991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7121810913086</t>
+    <t xml:space="preserve">23.540283203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7408313751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8363285064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.71217918396</t>
   </si>
   <si>
     <t xml:space="preserve">23.7599296569824</t>
@@ -2651,16 +2651,16 @@
     <t xml:space="preserve">24.3233680725098</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7340106964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2783508300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0682563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0587043762207</t>
+    <t xml:space="preserve">24.7340126037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2783489227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0682544708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0587024688721</t>
   </si>
   <si>
     <t xml:space="preserve">24.7531108856201</t>
@@ -2672,43 +2672,43 @@
     <t xml:space="preserve">26.5580253601074</t>
   </si>
   <si>
-    <t xml:space="preserve">26.510274887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6467018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2292404174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.503454208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5894031524658</t>
+    <t xml:space="preserve">26.5102787017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6467056274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2292423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5034561157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5894050598145</t>
   </si>
   <si>
     <t xml:space="preserve">27.1596641540527</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5512046813965</t>
+    <t xml:space="preserve">27.5512065887451</t>
   </si>
   <si>
     <t xml:space="preserve">27.0164184570312</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0355129241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3793087005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2265110015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0546169281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2838115692139</t>
+    <t xml:space="preserve">27.035514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3793106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2265129089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.054615020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2838096618652</t>
   </si>
   <si>
     <t xml:space="preserve">26.5675754547119</t>
@@ -2717,7 +2717,7 @@
     <t xml:space="preserve">27.0450668334961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7108211517334</t>
+    <t xml:space="preserve">26.710823059082</t>
   </si>
   <si>
     <t xml:space="preserve">26.5007266998291</t>
@@ -2726,25 +2726,25 @@
     <t xml:space="preserve">26.4529762268066</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6630744934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5389251708984</t>
+    <t xml:space="preserve">26.6630725860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5389270782471</t>
   </si>
   <si>
     <t xml:space="preserve">26.2619800567627</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4625263214111</t>
+    <t xml:space="preserve">26.4625244140625</t>
   </si>
   <si>
     <t xml:space="preserve">27.5989551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6726226806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7585716247559</t>
+    <t xml:space="preserve">26.6726245880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7585735321045</t>
   </si>
   <si>
     <t xml:space="preserve">27.3888607025146</t>
@@ -2756,10 +2756,10 @@
     <t xml:space="preserve">28.1814918518066</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3533935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5061874389648</t>
+    <t xml:space="preserve">28.3533897399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5061893463135</t>
   </si>
   <si>
     <t xml:space="preserve">28.9932270050049</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">27.57985496521</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6562538146973</t>
+    <t xml:space="preserve">27.6562519073486</t>
   </si>
   <si>
     <t xml:space="preserve">27.4748077392578</t>
@@ -2783,28 +2783,28 @@
     <t xml:space="preserve">27.6849021911621</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3847694396973</t>
+    <t xml:space="preserve">29.3847713470459</t>
   </si>
   <si>
     <t xml:space="preserve">29.967306137085</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1746711730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4802665710449</t>
+    <t xml:space="preserve">29.1746730804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4802684783936</t>
   </si>
   <si>
     <t xml:space="preserve">29.8336124420166</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0246086120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1651229858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3274688720703</t>
+    <t xml:space="preserve">30.0246067047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1651248931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3274707794189</t>
   </si>
   <si>
     <t xml:space="preserve">29.8049602508545</t>
@@ -2813,22 +2813,22 @@
     <t xml:space="preserve">30.4734477996826</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9891357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7503910064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5402984619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9222888946533</t>
+    <t xml:space="preserve">30.9891376495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7503929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5402965545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.922290802002</t>
   </si>
   <si>
     <t xml:space="preserve">30.7408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9318370819092</t>
+    <t xml:space="preserve">30.9318408966064</t>
   </si>
   <si>
     <t xml:space="preserve">30.7217407226562</t>
@@ -2843,52 +2843,52 @@
     <t xml:space="preserve">30.4829978942871</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5593967437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7258338928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2128715515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9031887054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9918613433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8991012573242</t>
+    <t xml:space="preserve">30.5593948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7258319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2128734588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.903190612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9918689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.899097442627</t>
   </si>
   <si>
     <t xml:space="preserve">33.6535377502441</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3097457885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4693603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3288421630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5580368041992</t>
+    <t xml:space="preserve">33.309741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4693565368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3288383483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.558032989502</t>
   </si>
   <si>
     <t xml:space="preserve">34.1310272216797</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4338912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4461708068848</t>
+    <t xml:space="preserve">33.4338874816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4461669921875</t>
   </si>
   <si>
     <t xml:space="preserve">33.8158798217773</t>
   </si>
   <si>
-    <t xml:space="preserve">33.930477142334</t>
+    <t xml:space="preserve">33.9304809570312</t>
   </si>
   <si>
     <t xml:space="preserve">32.6603546142578</t>
@@ -2900,28 +2900,28 @@
     <t xml:space="preserve">32.8513526916504</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5143756866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6098728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9727687835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7367553710938</t>
+    <t xml:space="preserve">31.5143737792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6098747253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9727668762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7367515563965</t>
   </si>
   <si>
     <t xml:space="preserve">32.0587158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2565307617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.884090423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.017786026001</t>
+    <t xml:space="preserve">31.2565326690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8840923309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0177879333496</t>
   </si>
   <si>
     <t xml:space="preserve">31.1323852539062</t>
@@ -2930,19 +2930,19 @@
     <t xml:space="preserve">30.8745422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0846347808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6194248199463</t>
+    <t xml:space="preserve">31.0846309661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6194267272949</t>
   </si>
   <si>
     <t xml:space="preserve">32.0969161987305</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3615779876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1542129516602</t>
+    <t xml:space="preserve">31.3615798950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1542091369629</t>
   </si>
   <si>
     <t xml:space="preserve">31.9441204071045</t>
@@ -2951,55 +2951,55 @@
     <t xml:space="preserve">32.4216117858887</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6958236694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2115097045898</t>
+    <t xml:space="preserve">31.6958198547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2115135192871</t>
   </si>
   <si>
     <t xml:space="preserve">31.7435722351074</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2783622741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5075531005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4120597839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0491638183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5334758758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2087802886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3165588378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.163761138916</t>
+    <t xml:space="preserve">32.2783584594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5075607299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4120559692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0491676330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5334739685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2087821960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3165626525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1637649536133</t>
   </si>
   <si>
     <t xml:space="preserve">32.1064643859863</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3834075927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6221504211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6508026123047</t>
+    <t xml:space="preserve">32.3834114074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6221542358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.650806427002</t>
   </si>
   <si>
     <t xml:space="preserve">32.8036041259766</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5839614868164</t>
+    <t xml:space="preserve">32.5839500427246</t>
   </si>
   <si>
     <t xml:space="preserve">32.3547630310059</t>
@@ -3011,91 +3011,91 @@
     <t xml:space="preserve">32.0396194458008</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5648536682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.326114654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9250164031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.042350769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7967834472656</t>
+    <t xml:space="preserve">32.5648574829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3261108398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9250202178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0423431396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7967796325684</t>
   </si>
   <si>
     <t xml:space="preserve">34.5989646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4843711853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9427642822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8854598999023</t>
+    <t xml:space="preserve">34.4843673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9427604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8854522705078</t>
   </si>
   <si>
     <t xml:space="preserve">35.0000648498535</t>
   </si>
   <si>
-    <t xml:space="preserve">35.80224609375</t>
+    <t xml:space="preserve">35.8022422790527</t>
   </si>
   <si>
     <t xml:space="preserve">35.5539474487305</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3343048095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2551765441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9018287658691</t>
+    <t xml:space="preserve">35.3342971801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2551727294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9018325805664</t>
   </si>
   <si>
     <t xml:space="preserve">33.3670387268066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3192901611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7817707061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8104248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4598121643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7081031799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9768581390381</t>
+    <t xml:space="preserve">33.3192939758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7817687988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8104209899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4598083496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7080993652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9768562316895</t>
   </si>
   <si>
     <t xml:space="preserve">29.4898147583008</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6876335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.002779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3875007629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6453456878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4761772155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5211944580078</t>
+    <t xml:space="preserve">28.6876354217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0027770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3874988555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6453437805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4761753082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5211982727051</t>
   </si>
   <si>
     <t xml:space="preserve">30.7312927246094</t>
@@ -3110,16 +3110,16 @@
     <t xml:space="preserve">29.5375652313232</t>
   </si>
   <si>
-    <t xml:space="preserve">30.148754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.667179107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4065971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7694931030273</t>
+    <t xml:space="preserve">30.1487560272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6671733856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4065990447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.769495010376</t>
   </si>
   <si>
     <t xml:space="preserve">30.6644439697266</t>
@@ -3128,43 +3128,43 @@
     <t xml:space="preserve">30.3111019134521</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9413909912109</t>
+    <t xml:space="preserve">30.9413890838623</t>
   </si>
   <si>
     <t xml:space="preserve">31.2756328582764</t>
   </si>
   <si>
-    <t xml:space="preserve">30.960485458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5812244415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3424816131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5007400512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9372978210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8731803894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6344375610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.624885559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1787796020508</t>
+    <t xml:space="preserve">30.9604873657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5812282562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3424797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5007362365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9373016357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8731842041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6344413757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6248817443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1787757873535</t>
   </si>
   <si>
     <t xml:space="preserve">34.2169761657715</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9905052185059</t>
+    <t xml:space="preserve">34.9905090332031</t>
   </si>
   <si>
     <t xml:space="preserve">34.8281631469727</t>
@@ -3173,28 +3173,28 @@
     <t xml:space="preserve">34.302921295166</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1091957092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5484886169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8063316345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.233341217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.092830657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5771408081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2688179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9059143066406</t>
+    <t xml:space="preserve">33.1091918945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5484924316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8063354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2333450317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0928268432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5771369934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2688102722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9059238433838</t>
   </si>
   <si>
     <t xml:space="preserve">31.8868217468262</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">33.1378440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7995109558105</t>
+    <t xml:space="preserve">34.7995071411133</t>
   </si>
   <si>
     <t xml:space="preserve">35.8851928710938</t>
@@ -3233,13 +3233,13 @@
     <t xml:space="preserve">37.1246032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">37.018913269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6818580627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2391128540039</t>
+    <t xml:space="preserve">37.0189170837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6818542480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2391090393066</t>
   </si>
   <si>
     <t xml:space="preserve">37.7683258056641</t>
@@ -3254,10 +3254,10 @@
     <t xml:space="preserve">39.2479286193848</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6138153076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6426391601562</t>
+    <t xml:space="preserve">38.6138114929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.642635345459</t>
   </si>
   <si>
     <t xml:space="preserve">39.3440093994141</t>
@@ -3269,31 +3269,31 @@
     <t xml:space="preserve">38.7963638305664</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7194976806641</t>
+    <t xml:space="preserve">38.7195014953613</t>
   </si>
   <si>
     <t xml:space="preserve">38.6042060852051</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6130256652832</t>
+    <t xml:space="preserve">39.6130294799805</t>
   </si>
   <si>
     <t xml:space="preserve">39.6514587402344</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7475357055664</t>
+    <t xml:space="preserve">39.7475395202637</t>
   </si>
   <si>
     <t xml:space="preserve">40.4969482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0069465637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8051795959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9685173034668</t>
+    <t xml:space="preserve">40.0069427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8051872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9685134887695</t>
   </si>
   <si>
     <t xml:space="preserve">39.6034240722656</t>
@@ -3302,13 +3302,13 @@
     <t xml:space="preserve">39.7571487426758</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9973411560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0749893188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5769538879395</t>
+    <t xml:space="preserve">39.9973373413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0749855041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5769577026367</t>
   </si>
   <si>
     <t xml:space="preserve">37.5665588378906</t>
@@ -3329,28 +3329,28 @@
     <t xml:space="preserve">38.4793014526367</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4496955871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1806755065918</t>
+    <t xml:space="preserve">39.4496994018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1806793212891</t>
   </si>
   <si>
     <t xml:space="preserve">38.8540115356445</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4304809570312</t>
+    <t xml:space="preserve">39.430477142334</t>
   </si>
   <si>
     <t xml:space="preserve">38.7675399780273</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0453796386719</t>
+    <t xml:space="preserve">40.0453834533691</t>
   </si>
   <si>
     <t xml:space="preserve">40.6410636901855</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7275314331055</t>
+    <t xml:space="preserve">40.7275352478027</t>
   </si>
   <si>
     <t xml:space="preserve">40.3528289794922</t>
@@ -3359,16 +3359,16 @@
     <t xml:space="preserve">40.7083168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2567520141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3336143493652</t>
+    <t xml:space="preserve">40.2567558288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.333610534668</t>
   </si>
   <si>
     <t xml:space="preserve">40.266357421875</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4489059448242</t>
+    <t xml:space="preserve">40.448902130127</t>
   </si>
   <si>
     <t xml:space="preserve">41.0157661437988</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">41.1406707763672</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3424339294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2271423339844</t>
+    <t xml:space="preserve">41.3424301147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2271385192871</t>
   </si>
   <si>
     <t xml:space="preserve">41.2367477416992</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">43.0814476013184</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2455673217773</t>
+    <t xml:space="preserve">42.2455749511719</t>
   </si>
   <si>
     <t xml:space="preserve">42.0341949462891</t>
@@ -3416,46 +3416,46 @@
     <t xml:space="preserve">42.6683120727539</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9853744506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3896903991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8989028930664</t>
+    <t xml:space="preserve">42.9853706359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3896865844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8988990783691</t>
   </si>
   <si>
     <t xml:space="preserve">42.0245895385742</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9765472412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.534595489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4577293395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7187118530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.006160736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0165596008301</t>
+    <t xml:space="preserve">41.9765510559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5345916748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4577331542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7187156677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0061645507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0165557861328</t>
   </si>
   <si>
     <t xml:space="preserve">40.8332214355469</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0638046264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0718421936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1679191589355</t>
+    <t xml:space="preserve">41.0638084411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0718383789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1679229736328</t>
   </si>
   <si>
     <t xml:space="preserve">44.3112487792969</t>
@@ -3464,16 +3464,16 @@
     <t xml:space="preserve">43.2159576416016</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9477272033691</t>
+    <t xml:space="preserve">41.9477310180664</t>
   </si>
   <si>
     <t xml:space="preserve">39.7859687805176</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2759666442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5842056274414</t>
+    <t xml:space="preserve">40.2759628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5842018127441</t>
   </si>
   <si>
     <t xml:space="preserve">39.1902847290039</t>
@@ -3485,19 +3485,19 @@
     <t xml:space="preserve">39.6802787780762</t>
   </si>
   <si>
-    <t xml:space="preserve">40.10302734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0077323913574</t>
+    <t xml:space="preserve">40.1030311584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0077362060547</t>
   </si>
   <si>
     <t xml:space="preserve">39.0653800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9108734130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2087097167969</t>
+    <t xml:space="preserve">39.9108695983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2087135314941</t>
   </si>
   <si>
     <t xml:space="preserve">41.2463531494141</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">41.169490814209</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2263565063477</t>
+    <t xml:space="preserve">42.2263526916504</t>
   </si>
   <si>
     <t xml:space="preserve">42.9469375610352</t>
@@ -3524,58 +3524,58 @@
     <t xml:space="preserve">42.3800811767578</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3992919921875</t>
+    <t xml:space="preserve">42.3992958068848</t>
   </si>
   <si>
     <t xml:space="preserve">43.0045852661133</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9653663635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8596801757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7147750854492</t>
+    <t xml:space="preserve">43.9653625488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8596839904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7147789001465</t>
   </si>
   <si>
     <t xml:space="preserve">44.2632102966309</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7251739501953</t>
+    <t xml:space="preserve">43.725170135498</t>
   </si>
   <si>
     <t xml:space="preserve">44.0037994384766</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2055587768555</t>
+    <t xml:space="preserve">44.2055625915527</t>
   </si>
   <si>
     <t xml:space="preserve">43.436939239502</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2551765441895</t>
+    <t xml:space="preserve">42.2551803588867</t>
   </si>
   <si>
     <t xml:space="preserve">42.8604698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8028221130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.679500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6018486022949</t>
+    <t xml:space="preserve">42.8028182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6794967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6018447875977</t>
   </si>
   <si>
     <t xml:space="preserve">40.5449867248535</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0830230712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4289016723633</t>
+    <t xml:space="preserve">41.0830192565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4289054870605</t>
   </si>
   <si>
     <t xml:space="preserve">41.4192962646484</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">40.1318511962891</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1606750488281</t>
+    <t xml:space="preserve">40.1606712341309</t>
   </si>
   <si>
     <t xml:space="preserve">41.2655715942383</t>
@@ -3596,7 +3596,7 @@
     <t xml:space="preserve">40.1414566040039</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3143997192383</t>
+    <t xml:space="preserve">40.314395904541</t>
   </si>
   <si>
     <t xml:space="preserve">41.0926322937012</t>
@@ -3611,13 +3611,13 @@
     <t xml:space="preserve">42.3512573242188</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3704681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5626220703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5330200195312</t>
+    <t xml:space="preserve">42.3704719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5626258850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.533016204834</t>
   </si>
   <si>
     <t xml:space="preserve">43.6579170227051</t>
@@ -3632,25 +3632,25 @@
     <t xml:space="preserve">45.3681106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5890884399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8108520507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8885040283203</t>
+    <t xml:space="preserve">45.5890922546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8108558654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8885078430176</t>
   </si>
   <si>
     <t xml:space="preserve">44.0518379211426</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5914535522461</t>
+    <t xml:space="preserve">42.5914497375488</t>
   </si>
   <si>
     <t xml:space="preserve">41.8708648681641</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0261611938477</t>
+    <t xml:space="preserve">40.0261650085449</t>
   </si>
   <si>
     <t xml:space="preserve">39.2671432495117</t>
@@ -3659,22 +3659,22 @@
     <t xml:space="preserve">38.9308700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">38.383228302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1814651489258</t>
+    <t xml:space="preserve">38.3832321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1814613342285</t>
   </si>
   <si>
     <t xml:space="preserve">37.2014656066895</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7795066833496</t>
+    <t xml:space="preserve">35.7795104980469</t>
   </si>
   <si>
     <t xml:space="preserve">34.5208854675293</t>
   </si>
   <si>
-    <t xml:space="preserve">35.001277923584</t>
+    <t xml:space="preserve">35.0012741088867</t>
   </si>
   <si>
     <t xml:space="preserve">35.0397071838379</t>
@@ -3683,7 +3683,7 @@
     <t xml:space="preserve">34.4632377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0581321716309</t>
+    <t xml:space="preserve">36.0581398010254</t>
   </si>
   <si>
     <t xml:space="preserve">36.7018585205078</t>
@@ -3698,22 +3698,22 @@
     <t xml:space="preserve">34.8859825134277</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6553955078125</t>
+    <t xml:space="preserve">34.6553916931152</t>
   </si>
   <si>
     <t xml:space="preserve">33.7138252258301</t>
   </si>
   <si>
-    <t xml:space="preserve">35.116569519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7706909179688</t>
+    <t xml:space="preserve">35.1165657043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7706871032715</t>
   </si>
   <si>
     <t xml:space="preserve">33.9636306762695</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3775596618652</t>
+    <t xml:space="preserve">33.377555847168</t>
   </si>
   <si>
     <t xml:space="preserve">34.7418632507324</t>
@@ -3722,10 +3722,10 @@
     <t xml:space="preserve">34.2710800170898</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2806854248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.146183013916</t>
+    <t xml:space="preserve">34.2806930541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1461791992188</t>
   </si>
   <si>
     <t xml:space="preserve">33.7714767456055</t>
@@ -3737,31 +3737,31 @@
     <t xml:space="preserve">34.5689239501953</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2510757446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9332313537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9420509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4712715148926</t>
+    <t xml:space="preserve">35.2510795593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.933235168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9420547485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4712677001953</t>
   </si>
   <si>
     <t xml:space="preserve">36.4520530700684</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1253852844238</t>
+    <t xml:space="preserve">36.1253890991211</t>
   </si>
   <si>
     <t xml:space="preserve">34.7802963256836</t>
   </si>
   <si>
-    <t xml:space="preserve">33.588924407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6449966430664</t>
+    <t xml:space="preserve">33.5889282226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6450004577637</t>
   </si>
   <si>
     <t xml:space="preserve">33.7042236328125</t>
@@ -3779,16 +3779,16 @@
     <t xml:space="preserve">36.2695083618164</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3175468444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.981273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5200958251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.097354888916</t>
+    <t xml:space="preserve">36.3175430297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9812698364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5200996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0973472595215</t>
   </si>
   <si>
     <t xml:space="preserve">35.7602958679199</t>
@@ -3797,13 +3797,13 @@
     <t xml:space="preserve">36.2118606567383</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5081329345703</t>
+    <t xml:space="preserve">38.508129119873</t>
   </si>
   <si>
     <t xml:space="preserve">39.0173416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9500846862793</t>
+    <t xml:space="preserve">38.9500885009766</t>
   </si>
   <si>
     <t xml:space="preserve">40.2375373840332</t>
@@ -3812,7 +3812,7 @@
     <t xml:space="preserve">41.2943954467773</t>
   </si>
   <si>
-    <t xml:space="preserve">40.890869140625</t>
+    <t xml:space="preserve">40.8908653259277</t>
   </si>
   <si>
     <t xml:space="preserve">40.6891021728516</t>
@@ -3821,40 +3821,40 @@
     <t xml:space="preserve">39.8340072631836</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6330299377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4208717346191</t>
+    <t xml:space="preserve">38.6330261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4208679199219</t>
   </si>
   <si>
     <t xml:space="preserve">39.219108581543</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6234169006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9797019958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8075485229492</t>
+    <t xml:space="preserve">38.623420715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9796981811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.807544708252</t>
   </si>
   <si>
     <t xml:space="preserve">36.6442108154297</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3367652893066</t>
+    <t xml:space="preserve">36.3367614746094</t>
   </si>
   <si>
     <t xml:space="preserve">35.4528427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2502861022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7210731506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1350021362305</t>
+    <t xml:space="preserve">36.2502899169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.721076965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1349983215332</t>
   </si>
   <si>
     <t xml:space="preserve">35.7218589782715</t>
@@ -3872,31 +3872,31 @@
     <t xml:space="preserve">32.9836387634277</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9740257263184</t>
+    <t xml:space="preserve">32.9740295410156</t>
   </si>
   <si>
     <t xml:space="preserve">31.0524616241455</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9067726135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9163780212402</t>
+    <t xml:space="preserve">32.9067687988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.916374206543</t>
   </si>
   <si>
     <t xml:space="preserve">32.9644203186035</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2734413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3414859771729</t>
+    <t xml:space="preserve">31.2734394073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3414840698242</t>
   </si>
   <si>
     <t xml:space="preserve">30.6777591705322</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2105255126953</t>
+    <t xml:space="preserve">31.2105293273926</t>
   </si>
   <si>
     <t xml:space="preserve">31.0071048736572</t>
@@ -3905,10 +3905,10 @@
     <t xml:space="preserve">30.9489860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2492733001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3558235168457</t>
+    <t xml:space="preserve">31.2492713928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.355827331543</t>
   </si>
   <si>
     <t xml:space="preserve">31.6948623657227</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">30.0965557098389</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6099529266357</t>
+    <t xml:space="preserve">30.6099510192871</t>
   </si>
   <si>
     <t xml:space="preserve">30.3484115600586</t>
@@ -3932,13 +3932,13 @@
     <t xml:space="preserve">30.4646530151367</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7865810394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2948322296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2606258392334</t>
+    <t xml:space="preserve">29.7865829467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2948303222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.260627746582</t>
   </si>
   <si>
     <t xml:space="preserve">25.5438137054443</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">26.3090591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3985118865967</t>
+    <t xml:space="preserve">25.398509979248</t>
   </si>
   <si>
     <t xml:space="preserve">25.4760036468506</t>
@@ -3956,10 +3956,10 @@
     <t xml:space="preserve">25.4663181304932</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5341243743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8828430175781</t>
+    <t xml:space="preserve">25.5341262817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8828449249268</t>
   </si>
   <si>
     <t xml:space="preserve">27.9364242553711</t>
@@ -3977,7 +3977,7 @@
     <t xml:space="preserve">28.2560863494873</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3335781097412</t>
+    <t xml:space="preserve">28.3335800170898</t>
   </si>
   <si>
     <t xml:space="preserve">29.4378604888916</t>
@@ -3986,13 +3986,13 @@
     <t xml:space="preserve">29.9900035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7358779907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5883083343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.212797164917</t>
+    <t xml:space="preserve">30.7358798980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5883102416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2127990722656</t>
   </si>
   <si>
     <t xml:space="preserve">30.1740493774414</t>
@@ -4001,10 +4001,10 @@
     <t xml:space="preserve">30.3387241363525</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2173366546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7523784637451</t>
+    <t xml:space="preserve">28.2173385620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7523746490479</t>
   </si>
   <si>
     <t xml:space="preserve">28.3238925933838</t>
@@ -4016,13 +4016,13 @@
     <t xml:space="preserve">28.8469734191895</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6994037628174</t>
+    <t xml:space="preserve">29.6994018554688</t>
   </si>
   <si>
     <t xml:space="preserve">30.1837368011475</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6412811279297</t>
+    <t xml:space="preserve">29.6412830352783</t>
   </si>
   <si>
     <t xml:space="preserve">29.4766082763672</t>
@@ -4031,13 +4031,13 @@
     <t xml:space="preserve">30.358097076416</t>
   </si>
   <si>
-    <t xml:space="preserve">31.365514755249</t>
+    <t xml:space="preserve">31.3655166625977</t>
   </si>
   <si>
     <t xml:space="preserve">31.2008399963379</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4236354827881</t>
+    <t xml:space="preserve">31.4236335754395</t>
   </si>
   <si>
     <t xml:space="preserve">29.970630645752</t>
@@ -4046,16 +4046,16 @@
     <t xml:space="preserve">30.8714923858643</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0942859649658</t>
+    <t xml:space="preserve">31.0942840576172</t>
   </si>
   <si>
     <t xml:space="preserve">29.4281749725342</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7381477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9922752380371</t>
+    <t xml:space="preserve">29.7381496429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9922733306885</t>
   </si>
   <si>
     <t xml:space="preserve">29.4572353363037</t>
@@ -4070,10 +4070,10 @@
     <t xml:space="preserve">27.8879909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8104953765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.442403793335</t>
+    <t xml:space="preserve">27.8104972839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4424018859863</t>
   </si>
   <si>
     <t xml:space="preserve">26.8030815124512</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">24.1779861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8970737457275</t>
+    <t xml:space="preserve">23.8970718383789</t>
   </si>
   <si>
     <t xml:space="preserve">24.4201545715332</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">24.0908069610596</t>
   </si>
   <si>
-    <t xml:space="preserve">24.013313293457</t>
+    <t xml:space="preserve">24.0133152008057</t>
   </si>
   <si>
     <t xml:space="preserve">24.1973609924316</t>
@@ -4154,19 +4154,19 @@
     <t xml:space="preserve">25.291955947876</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0572071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5728702545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7159004211426</t>
+    <t xml:space="preserve">26.0572052001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5728721618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7159023284912</t>
   </si>
   <si>
     <t xml:space="preserve">26.1928195953369</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9312782287598</t>
+    <t xml:space="preserve">25.9312801361084</t>
   </si>
   <si>
     <t xml:space="preserve">25.6309909820557</t>
@@ -4175,10 +4175,10 @@
     <t xml:space="preserve">25.3307037353516</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6235733032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8389530181885</t>
+    <t xml:space="preserve">24.6235752105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8389549255371</t>
   </si>
   <si>
     <t xml:space="preserve">22.9187183380127</t>
@@ -4190,7 +4190,7 @@
     <t xml:space="preserve">24.4395275115967</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3500785827637</t>
+    <t xml:space="preserve">25.350076675415</t>
   </si>
   <si>
     <t xml:space="preserve">24.8366813659668</t>
@@ -4202,13 +4202,13 @@
     <t xml:space="preserve">25.3694515228271</t>
   </si>
   <si>
-    <t xml:space="preserve">25.059476852417</t>
+    <t xml:space="preserve">25.0594749450684</t>
   </si>
   <si>
     <t xml:space="preserve">25.4275703430176</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3620338439941</t>
+    <t xml:space="preserve">24.3620319366455</t>
   </si>
   <si>
     <t xml:space="preserve">23.7517738342285</t>
@@ -4217,7 +4217,7 @@
     <t xml:space="preserve">23.906759262085</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3523483276367</t>
+    <t xml:space="preserve">24.3523464202881</t>
   </si>
   <si>
     <t xml:space="preserve">24.3039150238037</t>
@@ -4238,7 +4238,7 @@
     <t xml:space="preserve">27.2680416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1398448944092</t>
+    <t xml:space="preserve">28.1398429870605</t>
   </si>
   <si>
     <t xml:space="preserve">27.6748828887939</t>
@@ -4253,7 +4253,7 @@
     <t xml:space="preserve">26.764331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5221672058105</t>
+    <t xml:space="preserve">26.5221652984619</t>
   </si>
   <si>
     <t xml:space="preserve">26.3187465667725</t>
@@ -4262,13 +4262,13 @@
     <t xml:space="preserve">26.8321399688721</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8805732727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0065002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1421146392822</t>
+    <t xml:space="preserve">26.8805751800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0065021514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1421165466309</t>
   </si>
   <si>
     <t xml:space="preserve">26.0087738037109</t>
@@ -4277,10 +4277,10 @@
     <t xml:space="preserve">26.7837085723877</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6458225250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9483833312988</t>
+    <t xml:space="preserve">27.645824432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9483814239502</t>
   </si>
   <si>
     <t xml:space="preserve">26.1540718078613</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">26.6965274810791</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0936813354492</t>
+    <t xml:space="preserve">27.0936832427979</t>
   </si>
   <si>
     <t xml:space="preserve">27.1324291229248</t>
@@ -4307,25 +4307,25 @@
     <t xml:space="preserve">26.444673538208</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0959510803223</t>
+    <t xml:space="preserve">26.0959529876709</t>
   </si>
   <si>
     <t xml:space="preserve">26.0668926239014</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8925323486328</t>
+    <t xml:space="preserve">25.8925304412842</t>
   </si>
   <si>
     <t xml:space="preserve">26.4543590545654</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8344097137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9700260162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6287212371826</t>
+    <t xml:space="preserve">25.8344116210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9700241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.628719329834</t>
   </si>
   <si>
     <t xml:space="preserve">26.8708896636963</t>
@@ -4334,25 +4334,25 @@
     <t xml:space="preserve">26.1443843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2509384155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9677562713623</t>
+    <t xml:space="preserve">26.250940322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9677543640137</t>
   </si>
   <si>
     <t xml:space="preserve">25.9797115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1056385040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5996608734131</t>
+    <t xml:space="preserve">26.105640411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5996589660645</t>
   </si>
   <si>
     <t xml:space="preserve">26.63840675354</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2412528991699</t>
+    <t xml:space="preserve">26.2412548065186</t>
   </si>
   <si>
     <t xml:space="preserve">25.6019306182861</t>
@@ -4361,7 +4361,7 @@
     <t xml:space="preserve">24.9044876098633</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0788497924805</t>
+    <t xml:space="preserve">25.0788478851318</t>
   </si>
   <si>
     <t xml:space="preserve">24.8851165771484</t>
@@ -4373,16 +4373,16 @@
     <t xml:space="preserve">24.9335498809814</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7398147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4782733917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6070785522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9290065765381</t>
+    <t xml:space="preserve">24.7398166656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4782752990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6070766448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9290084838867</t>
   </si>
   <si>
     <t xml:space="preserve">27.1227416992188</t>
@@ -4391,7 +4391,7 @@
     <t xml:space="preserve">25.7666053771973</t>
   </si>
   <si>
-    <t xml:space="preserve">26.483419418335</t>
+    <t xml:space="preserve">26.4834213256836</t>
   </si>
   <si>
     <t xml:space="preserve">27.2777290344238</t>
@@ -4403,7 +4403,7 @@
     <t xml:space="preserve">26.2025051116943</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6190319061279</t>
+    <t xml:space="preserve">26.6190338134766</t>
   </si>
   <si>
     <t xml:space="preserve">26.5027942657471</t>
@@ -4418,37 +4418,37 @@
     <t xml:space="preserve">28.5466842651367</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4401321411133</t>
+    <t xml:space="preserve">28.4401340484619</t>
   </si>
   <si>
     <t xml:space="preserve">28.7694797515869</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2367095947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1107845306396</t>
+    <t xml:space="preserve">28.2367115020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1107864379883</t>
   </si>
   <si>
     <t xml:space="preserve">29.0310211181641</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4304447174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8954067230225</t>
+    <t xml:space="preserve">28.4304466247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8954086303711</t>
   </si>
   <si>
     <t xml:space="preserve">29.1860084533691</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6606559753418</t>
+    <t xml:space="preserve">29.6606578826904</t>
   </si>
   <si>
     <t xml:space="preserve">30.6583862304688</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9392986297607</t>
+    <t xml:space="preserve">30.9393005371094</t>
   </si>
   <si>
     <t xml:space="preserve">30.8327445983887</t>
@@ -4457,7 +4457,7 @@
     <t xml:space="preserve">31.2589588165283</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4817543029785</t>
+    <t xml:space="preserve">31.4817523956299</t>
   </si>
   <si>
     <t xml:space="preserve">31.6173667907715</t>
@@ -4472,16 +4472,16 @@
     <t xml:space="preserve">31.6754875183105</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2783336639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9176559448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9854621887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7820415496826</t>
+    <t xml:space="preserve">31.2783355712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9176578521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9854602813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7820453643799</t>
   </si>
   <si>
     <t xml:space="preserve">32.3729286193848</t>
@@ -4496,16 +4496,16 @@
     <t xml:space="preserve">32.3341865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7313423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2373161315918</t>
+    <t xml:space="preserve">32.7313346862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2373123168945</t>
   </si>
   <si>
     <t xml:space="preserve">32.0823287963867</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3780746459961</t>
+    <t xml:space="preserve">34.3780784606934</t>
   </si>
   <si>
     <t xml:space="preserve">33.7678146362305</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">34.8817825317383</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6105537414551</t>
+    <t xml:space="preserve">34.6105575561523</t>
   </si>
   <si>
     <t xml:space="preserve">33.8259315490723</t>
@@ -4538,10 +4538,10 @@
     <t xml:space="preserve">33.0413131713867</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8475761413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1478691101074</t>
+    <t xml:space="preserve">32.8475799560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1478652954102</t>
   </si>
   <si>
     <t xml:space="preserve">33.167407989502</t>
@@ -6234,6 +6234,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.2049999237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4200000762939</t>
   </si>
 </sst>
 </file>
@@ -71988,7 +71991,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.6912962963</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>1284966</v>
@@ -72009,6 +72012,32 @@
         <v>2073</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.6909722222</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>1000514</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>13.4899997711182</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>13.2349996566772</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>13.3199996948242</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>13.4200000762939</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>2074</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2075" uniqueCount="2075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2076" uniqueCount="2076">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33520555496216</t>
+    <t xml:space="preserve">7.335205078125</t>
   </si>
   <si>
     <t xml:space="preserve">AMP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39109230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31191825866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36780548095703</t>
+    <t xml:space="preserve">7.3910927772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31191873550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36780500411987</t>
   </si>
   <si>
     <t xml:space="preserve">7.15357112884521</t>
@@ -59,49 +59,49 @@
     <t xml:space="preserve">6.96262311935425</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21877288818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27931833267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16288614273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03248262405396</t>
+    <t xml:space="preserve">7.21877336502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27931785583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16288566589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0324821472168</t>
   </si>
   <si>
     <t xml:space="preserve">7.08836984634399</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19548654556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9859094619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13494205474854</t>
+    <t xml:space="preserve">7.19548606872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98590993881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13494253158569</t>
   </si>
   <si>
     <t xml:space="preserve">7.3445200920105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23740291595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35383367538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14891481399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18151426315308</t>
+    <t xml:space="preserve">7.23740243911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35383462905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14891386032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18151473999023</t>
   </si>
   <si>
     <t xml:space="preserve">7.40972137451172</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28397464752197</t>
+    <t xml:space="preserve">7.28397560119629</t>
   </si>
   <si>
     <t xml:space="preserve">7.13959932327271</t>
@@ -110,31 +110,31 @@
     <t xml:space="preserve">7.05111122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84619092941284</t>
+    <t xml:space="preserve">6.84619140625</t>
   </si>
   <si>
     <t xml:space="preserve">6.51086711883545</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45498085021973</t>
+    <t xml:space="preserve">6.45497989654541</t>
   </si>
   <si>
     <t xml:space="preserve">6.59004163742065</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33389186859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29197645187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42237997055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61798524856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88344955444336</t>
+    <t xml:space="preserve">6.33389234542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29197597503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42237949371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61798429489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88344860076904</t>
   </si>
   <si>
     <t xml:space="preserve">6.71113014221191</t>
@@ -143,25 +143,25 @@
     <t xml:space="preserve">6.83687734603882</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70181608200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6272988319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99522399902344</t>
+    <t xml:space="preserve">6.70181560516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62729930877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99522495269775</t>
   </si>
   <si>
     <t xml:space="preserve">6.8927640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80427503585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7996187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84153366088867</t>
+    <t xml:space="preserve">6.80427551269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79961824417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84153318405151</t>
   </si>
   <si>
     <t xml:space="preserve">6.65990018844604</t>
@@ -182,85 +182,85 @@
     <t xml:space="preserve">7.00919532775879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11165618896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08371162414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20945882797241</t>
+    <t xml:space="preserve">7.111656665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08371210098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20945835113525</t>
   </si>
   <si>
     <t xml:space="preserve">7.10699796676636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04179668426514</t>
+    <t xml:space="preserve">7.04179716110229</t>
   </si>
   <si>
     <t xml:space="preserve">7.2420597076416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09768390655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17219972610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93467950820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91604995727539</t>
+    <t xml:space="preserve">7.09768342971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17220020294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93467855453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91605091094971</t>
   </si>
   <si>
     <t xml:space="preserve">7.00453853607178</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2700023651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32589054107666</t>
+    <t xml:space="preserve">7.27000284194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3258900642395</t>
   </si>
   <si>
     <t xml:space="preserve">7.22808790206909</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50286674499512</t>
+    <t xml:space="preserve">7.50286722183228</t>
   </si>
   <si>
     <t xml:space="preserve">7.41437911987305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48423767089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57738351821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55409669876099</t>
+    <t xml:space="preserve">7.4842381477356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57738304138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55409622192383</t>
   </si>
   <si>
     <t xml:space="preserve">7.7310733795166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60066986083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64258575439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70313024520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73573017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88476276397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88942289352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87079048156738</t>
+    <t xml:space="preserve">7.60066938400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64258527755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70312976837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73573112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88476371765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88941955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87079191207886</t>
   </si>
   <si>
     <t xml:space="preserve">7.78695869445801</t>
@@ -272,31 +272,31 @@
     <t xml:space="preserve">7.88010549545288</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08968353271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01760292053223</t>
+    <t xml:space="preserve">8.08968448638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01760196685791</t>
   </si>
   <si>
     <t xml:space="preserve">8.09717178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10653305053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05036735534668</t>
+    <t xml:space="preserve">8.10653400421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.050368309021</t>
   </si>
   <si>
     <t xml:space="preserve">8.17205905914307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21418285369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23758506774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22354316711426</t>
+    <t xml:space="preserve">8.21418190002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23758602142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22354507446289</t>
   </si>
   <si>
     <t xml:space="preserve">8.15801811218262</t>
@@ -305,85 +305,85 @@
     <t xml:space="preserve">8.07845115661621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08312892913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14397525787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01292419433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.914635181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82102537155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64316892623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62912654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65253067016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55891990661621</t>
+    <t xml:space="preserve">8.08313083648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14397621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01292324066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91463375091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82102584838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64316844940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62912797927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65252923965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55892038345337</t>
   </si>
   <si>
     <t xml:space="preserve">7.63848829269409</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98952198028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94739723205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05972766876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67593193054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71337556838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72273635864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87250995635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92867755889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89123058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81166458129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71805572509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88187074661255</t>
+    <t xml:space="preserve">7.98952102661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94739627838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05972671508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67593145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71337509155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72273683547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87250900268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92867565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89123249053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8116660118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7180552482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88187170028687</t>
   </si>
   <si>
     <t xml:space="preserve">7.96143913269043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91931438446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90995359420776</t>
+    <t xml:space="preserve">7.91931486129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90995502471924</t>
   </si>
   <si>
     <t xml:space="preserve">8.05504703521729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18141937255859</t>
+    <t xml:space="preserve">8.18142032623291</t>
   </si>
   <si>
     <t xml:space="preserve">8.16737937927246</t>
@@ -392,28 +392,28 @@
     <t xml:space="preserve">8.19546031951904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19077968597412</t>
+    <t xml:space="preserve">8.19078063964844</t>
   </si>
   <si>
     <t xml:space="preserve">8.30779266357422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36395835876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34991550445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3311939239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29374980926514</t>
+    <t xml:space="preserve">8.36395645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34991645812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33119297027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29375076293945</t>
   </si>
   <si>
     <t xml:space="preserve">8.15333652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28906917572021</t>
+    <t xml:space="preserve">8.28906726837158</t>
   </si>
   <si>
     <t xml:space="preserve">8.36863803863525</t>
@@ -425,22 +425,22 @@
     <t xml:space="preserve">8.60734081268311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51373291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.635422706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75711345672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65414524078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78519725799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8085994720459</t>
+    <t xml:space="preserve">8.51373386383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63542366027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75711250305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65414333343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78519821166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80859756469727</t>
   </si>
   <si>
     <t xml:space="preserve">8.92092990875244</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">8.81796073913574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74775505065918</t>
+    <t xml:space="preserve">8.74775409698486</t>
   </si>
   <si>
     <t xml:space="preserve">8.75243473052979</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">8.82264137268066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73371315002441</t>
+    <t xml:space="preserve">8.7337121963501</t>
   </si>
   <si>
     <t xml:space="preserve">8.77115535736084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76179599761963</t>
+    <t xml:space="preserve">8.76179504394531</t>
   </si>
   <si>
     <t xml:space="preserve">8.6588249206543</t>
@@ -476,34 +476,34 @@
     <t xml:space="preserve">8.59329986572266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57457828521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56053733825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48564720153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54181480407715</t>
+    <t xml:space="preserve">8.57457733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56053638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4856481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54181289672852</t>
   </si>
   <si>
     <t xml:space="preserve">8.53245449066162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66818618774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49969100952148</t>
+    <t xml:space="preserve">8.66818714141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49969005584717</t>
   </si>
   <si>
     <t xml:space="preserve">8.61670112609863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49500846862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55585670471191</t>
+    <t xml:space="preserve">8.49500942230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5558557510376</t>
   </si>
   <si>
     <t xml:space="preserve">8.61202049255371</t>
@@ -512,28 +512,28 @@
     <t xml:space="preserve">8.46692657470703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5277738571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56521701812744</t>
+    <t xml:space="preserve">8.52777194976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56521606445312</t>
   </si>
   <si>
     <t xml:space="preserve">8.69158744812012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08006572723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24856185913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07070255279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01453876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89284706115723</t>
+    <t xml:space="preserve">9.08006381988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24856281280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07070350646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01453971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89284801483154</t>
   </si>
   <si>
     <t xml:space="preserve">8.93965244293213</t>
@@ -542,22 +542,22 @@
     <t xml:space="preserve">8.81328010559082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50437164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42480278015137</t>
+    <t xml:space="preserve">8.50437068939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42480182647705</t>
   </si>
   <si>
     <t xml:space="preserve">8.40139961242676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39672183990479</t>
+    <t xml:space="preserve">8.39672088623047</t>
   </si>
   <si>
     <t xml:space="preserve">8.58393859863281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34523582458496</t>
+    <t xml:space="preserve">8.34523487091064</t>
   </si>
   <si>
     <t xml:space="preserve">8.46224689483643</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">8.38267803192139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47160625457764</t>
+    <t xml:space="preserve">8.47160720825195</t>
   </si>
   <si>
     <t xml:space="preserve">8.98645687103271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09878826141357</t>
+    <t xml:space="preserve">9.09878635406494</t>
   </si>
   <si>
     <t xml:space="preserve">9.06134414672852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51841354370117</t>
+    <t xml:space="preserve">8.51841259002686</t>
   </si>
   <si>
     <t xml:space="preserve">8.16269779205322</t>
@@ -587,31 +587,31 @@
     <t xml:space="preserve">8.31247234344482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44190979003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98484086990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95675992965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38735866546631</t>
+    <t xml:space="preserve">7.4419093132019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98484182357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95675802230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38735961914062</t>
   </si>
   <si>
     <t xml:space="preserve">8.41076183319092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44820404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48096752166748</t>
+    <t xml:space="preserve">8.44820499420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4809684753418</t>
   </si>
   <si>
     <t xml:space="preserve">8.37331771850586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23290634155273</t>
+    <t xml:space="preserve">8.23290538787842</t>
   </si>
   <si>
     <t xml:space="preserve">8.18610000610352</t>
@@ -620,10 +620,10 @@
     <t xml:space="preserve">8.3779993057251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57925701141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64946269989014</t>
+    <t xml:space="preserve">8.57925796508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64946460723877</t>
   </si>
   <si>
     <t xml:space="preserve">8.72435092926025</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">8.67286682128906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74307250976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71031093597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.154953956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96773529052734</t>
+    <t xml:space="preserve">8.74307346343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71031188964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15495300292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96773433685303</t>
   </si>
   <si>
     <t xml:space="preserve">9.14091110229492</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">9.26728248596191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33749008178711</t>
+    <t xml:space="preserve">9.33749103546143</t>
   </si>
   <si>
     <t xml:space="preserve">9.40769672393799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37961578369141</t>
+    <t xml:space="preserve">9.37961483001709</t>
   </si>
   <si>
     <t xml:space="preserve">9.29536533355713</t>
@@ -668,46 +668,46 @@
     <t xml:space="preserve">9.44514179229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48258304595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4357795715332</t>
+    <t xml:space="preserve">9.48258495330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43577861785889</t>
   </si>
   <si>
     <t xml:space="preserve">9.35621070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11282825469971</t>
+    <t xml:space="preserve">9.11282920837402</t>
   </si>
   <si>
     <t xml:space="preserve">9.10814762115479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15963268280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4638614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81021308898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95999050140381</t>
+    <t xml:space="preserve">9.15963363647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46386241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81021404266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95998954772949</t>
   </si>
   <si>
     <t xml:space="preserve">9.82893657684326</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91318702697754</t>
+    <t xml:space="preserve">9.91318511962891</t>
   </si>
   <si>
     <t xml:space="preserve">9.64171886444092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70724487304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71660804748535</t>
+    <t xml:space="preserve">9.70724391937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71660709381104</t>
   </si>
   <si>
     <t xml:space="preserve">9.66044044494629</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">9.79149341583252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0255155563354</t>
+    <t xml:space="preserve">10.0255165100098</t>
   </si>
   <si>
     <t xml:space="preserve">10.0067939758301</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">10.1846504211426</t>
   </si>
   <si>
-    <t xml:space="preserve">10.240816116333</t>
+    <t xml:space="preserve">10.2408151626587</t>
   </si>
   <si>
     <t xml:space="preserve">10.2595376968384</t>
   </si>
   <si>
-    <t xml:space="preserve">10.428032875061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4748382568359</t>
+    <t xml:space="preserve">10.4280338287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4748363494873</t>
   </si>
   <si>
     <t xml:space="preserve">10.3625068664551</t>
@@ -743,19 +743,19 @@
     <t xml:space="preserve">10.3344259262085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.577808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5122833251953</t>
+    <t xml:space="preserve">10.5778074264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5122804641724</t>
   </si>
   <si>
     <t xml:space="preserve">10.5029220581055</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8118314743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8867168426514</t>
+    <t xml:space="preserve">10.8118305206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.88671875</t>
   </si>
   <si>
     <t xml:space="preserve">10.718222618103</t>
@@ -764,16 +764,16 @@
     <t xml:space="preserve">10.6526956558228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6433334350586</t>
+    <t xml:space="preserve">10.6433343887329</t>
   </si>
   <si>
     <t xml:space="preserve">10.6246128082275</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7088603973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8960800170898</t>
+    <t xml:space="preserve">10.7088594436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8960790634155</t>
   </si>
   <si>
     <t xml:space="preserve">10.8399133682251</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">10.9990482330322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1301021575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0926580429077</t>
+    <t xml:space="preserve">11.1301012039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.092658996582</t>
   </si>
   <si>
     <t xml:space="preserve">11.2517919540405</t>
@@ -797,31 +797,31 @@
     <t xml:space="preserve">10.9616041183472</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2049875259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1675462722778</t>
+    <t xml:space="preserve">11.2049894332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1675453186035</t>
   </si>
   <si>
     <t xml:space="preserve">11.1488227844238</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1862659454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2798748016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4296503067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.410927772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4577331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5801248550415</t>
+    <t xml:space="preserve">11.1862668991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2798757553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4296493530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4109258651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4577341079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5801229476929</t>
   </si>
   <si>
     <t xml:space="preserve">11.8249073028564</t>
@@ -830,28 +830,28 @@
     <t xml:space="preserve">11.862566947937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9472980499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9190540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9284696578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9378843307495</t>
+    <t xml:space="preserve">11.9472970962524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9190530776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9284687042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9378833770752</t>
   </si>
   <si>
     <t xml:space="preserve">11.9661273956299</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0602750778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0979347229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0226163864136</t>
+    <t xml:space="preserve">12.0602760314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0979337692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0226173400879</t>
   </si>
   <si>
     <t xml:space="preserve">12.2109117507935</t>
@@ -866,55 +866,55 @@
     <t xml:space="preserve">11.9096393585205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1450071334839</t>
+    <t xml:space="preserve">12.1450080871582</t>
   </si>
   <si>
     <t xml:space="preserve">11.4859762191772</t>
   </si>
   <si>
-    <t xml:space="preserve">11.297682762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6931009292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7307586669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7684183120728</t>
+    <t xml:space="preserve">11.2976808547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6930999755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7307605743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7684192657471</t>
   </si>
   <si>
     <t xml:space="preserve">11.7590036392212</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6271982192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5707092285156</t>
+    <t xml:space="preserve">11.627197265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5707082748413</t>
   </si>
   <si>
     <t xml:space="preserve">11.5236358642578</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4671459197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3730010986328</t>
+    <t xml:space="preserve">11.4671468734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3729991912842</t>
   </si>
   <si>
     <t xml:space="preserve">11.0811424255371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834342956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6951370239258</t>
+    <t xml:space="preserve">10.88343334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6951379776001</t>
   </si>
   <si>
     <t xml:space="preserve">10.5633335113525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6104049682617</t>
+    <t xml:space="preserve">10.610405921936</t>
   </si>
   <si>
     <t xml:space="preserve">10.7422122955322</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">10.9022626876831</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9493350982666</t>
+    <t xml:space="preserve">10.9493370056152</t>
   </si>
   <si>
     <t xml:space="preserve">11.1376314163208</t>
@@ -935,40 +935,40 @@
     <t xml:space="preserve">11.3541707992554</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3824148178101</t>
+    <t xml:space="preserve">11.3824129104614</t>
   </si>
   <si>
     <t xml:space="preserve">11.3447551727295</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4106578826904</t>
+    <t xml:space="preserve">11.4106597900391</t>
   </si>
   <si>
     <t xml:space="preserve">11.2694387435913</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5048055648804</t>
+    <t xml:space="preserve">11.5048065185547</t>
   </si>
   <si>
     <t xml:space="preserve">11.4294881820679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3353395462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2788524627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2506065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1093873977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0340700149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9210920333862</t>
+    <t xml:space="preserve">11.3353404998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2788515090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2506074905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1093864440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.034068107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9210929870605</t>
   </si>
   <si>
     <t xml:space="preserve">10.6668949127197</t>
@@ -980,10 +980,10 @@
     <t xml:space="preserve">10.78928565979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1941204071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1658744812012</t>
+    <t xml:space="preserve">11.1941194534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1658754348755</t>
   </si>
   <si>
     <t xml:space="preserve">11.0717277526855</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">11.2411918640137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0623140335083</t>
+    <t xml:space="preserve">11.062313079834</t>
   </si>
   <si>
     <t xml:space="preserve">11.0905561447144</t>
@@ -1013,34 +1013,34 @@
     <t xml:space="preserve">11.4389019012451</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7213430404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8154916763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9849576950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0132026672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9567127227783</t>
+    <t xml:space="preserve">11.7213449478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8154926300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.984956741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.013201713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9567136764526</t>
   </si>
   <si>
     <t xml:space="preserve">12.0508613586426</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0414457321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0791034698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9755420684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.834321975708</t>
+    <t xml:space="preserve">12.0414447784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0791053771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9755430221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8343210220337</t>
   </si>
   <si>
     <t xml:space="preserve">12.2203245162964</t>
@@ -1058,13 +1058,13 @@
     <t xml:space="preserve">12.5215978622437</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6439895629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7852077484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8134527206421</t>
+    <t xml:space="preserve">12.643988609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7852087020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8134536743164</t>
   </si>
   <si>
     <t xml:space="preserve">12.8322830200195</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">12.8040399551392</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1920804977417</t>
+    <t xml:space="preserve">12.1920795440674</t>
   </si>
   <si>
     <t xml:space="preserve">11.7872486114502</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">11.8531503677368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0320310592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1732521057129</t>
+    <t xml:space="preserve">12.0320301055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1732530593872</t>
   </si>
   <si>
     <t xml:space="preserve">12.2768135070801</t>
@@ -1094,16 +1094,16 @@
     <t xml:space="preserve">11.9002246856689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4483184814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5612926483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4012422561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6742725372314</t>
+    <t xml:space="preserve">11.448317527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5612936019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4012432098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6742706298828</t>
   </si>
   <si>
     <t xml:space="preserve">11.7778329849243</t>
@@ -1112,40 +1112,40 @@
     <t xml:space="preserve">12.0885200500488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0696887969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2014970779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.135594367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3615474700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3333024978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1638374328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7401752471924</t>
+    <t xml:space="preserve">12.0696907043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2014961242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1355934143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3615484237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3333044052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1638383865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7401742935181</t>
   </si>
   <si>
     <t xml:space="preserve">12.1261777877808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5404262542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5498418807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5027675628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6345729827881</t>
+    <t xml:space="preserve">12.5404272079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.549840927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5027666091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6345739364624</t>
   </si>
   <si>
     <t xml:space="preserve">13.1335535049438</t>
@@ -1160,22 +1160,22 @@
     <t xml:space="preserve">12.9546756744385</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4254102706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4630718231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5383882522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5572175979614</t>
+    <t xml:space="preserve">13.4254121780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4630699157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.538387298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5572185516357</t>
   </si>
   <si>
     <t xml:space="preserve">13.6042909622192</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5101432800293</t>
+    <t xml:space="preserve">13.5101442337036</t>
   </si>
   <si>
     <t xml:space="preserve">13.2559461593628</t>
@@ -1184,16 +1184,16 @@
     <t xml:space="preserve">13.4724855422974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3030195236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.973503112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.615743637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4086198806763</t>
+    <t xml:space="preserve">13.3030204772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9735040664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6157455444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4086208343506</t>
   </si>
   <si>
     <t xml:space="preserve">12.3803749084473</t>
@@ -1202,22 +1202,22 @@
     <t xml:space="preserve">12.4651079177856</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5121831893921</t>
+    <t xml:space="preserve">12.5121822357178</t>
   </si>
   <si>
     <t xml:space="preserve">12.822868347168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8793563842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.851113319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5969161987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.286229133606</t>
+    <t xml:space="preserve">12.8793573379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8511114120483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5969133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2862281799316</t>
   </si>
   <si>
     <t xml:space="preserve">12.2579851150513</t>
@@ -1235,19 +1235,19 @@
     <t xml:space="preserve">13.2653608322144</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4065828323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3312654495239</t>
+    <t xml:space="preserve">13.4065818786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3312644958496</t>
   </si>
   <si>
     <t xml:space="preserve">13.321849822998</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1617994308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3406782150269</t>
+    <t xml:space="preserve">13.1617984771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3406791687012</t>
   </si>
   <si>
     <t xml:space="preserve">13.2465324401855</t>
@@ -1262,34 +1262,34 @@
     <t xml:space="preserve">13.2936058044434</t>
   </si>
   <si>
-    <t xml:space="preserve">13.566632270813</t>
+    <t xml:space="preserve">13.5666332244873</t>
   </si>
   <si>
     <t xml:space="preserve">13.6419496536255</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3124361038208</t>
+    <t xml:space="preserve">13.3124351501465</t>
   </si>
   <si>
     <t xml:space="preserve">13.7925853729248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9997110366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1409320831299</t>
+    <t xml:space="preserve">13.9997100830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1409311294556</t>
   </si>
   <si>
     <t xml:space="preserve">14.3951292037964</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3009815216064</t>
+    <t xml:space="preserve">14.3009824752808</t>
   </si>
   <si>
     <t xml:space="preserve">14.5645952224731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6022529602051</t>
+    <t xml:space="preserve">14.6022539138794</t>
   </si>
   <si>
     <t xml:space="preserve">14.6869869232178</t>
@@ -1298,19 +1298,19 @@
     <t xml:space="preserve">14.9129400253296</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8564510345459</t>
+    <t xml:space="preserve">14.8564500808716</t>
   </si>
   <si>
     <t xml:space="preserve">15.1106481552124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9694271087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.997673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0353317260742</t>
+    <t xml:space="preserve">14.969428062439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9976720809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0353307723999</t>
   </si>
   <si>
     <t xml:space="preserve">14.903525352478</t>
@@ -1319,85 +1319,85 @@
     <t xml:space="preserve">14.8941087722778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7152309417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5928382873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.167140007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2706995010376</t>
+    <t xml:space="preserve">14.7152299880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5928392410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1671380996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2706985473633</t>
   </si>
   <si>
     <t xml:space="preserve">15.2424554824829</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2518730163574</t>
+    <t xml:space="preserve">15.2518720626831</t>
   </si>
   <si>
     <t xml:space="preserve">15.44016456604</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3930902481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5531425476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6567049026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4213342666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0165014266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3460168838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.818528175354</t>
+    <t xml:space="preserve">15.3930912017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5531415939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6567029953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4213333129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0165004730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3460178375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8185272216797</t>
   </si>
   <si>
     <t xml:space="preserve">14.6668348312378</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3444862365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6099491119385</t>
+    <t xml:space="preserve">14.3444871902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6099500656128</t>
   </si>
   <si>
     <t xml:space="preserve">14.7332000732422</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8754110336304</t>
+    <t xml:space="preserve">14.875412940979</t>
   </si>
   <si>
     <t xml:space="preserve">13.9273290634155</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4013710021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6194295883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6289110183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1882791519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4916648864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1174030303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4587116241455</t>
+    <t xml:space="preserve">14.4013719558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6194305419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6289119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1882801055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4916667938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1173992156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4587097167969</t>
   </si>
   <si>
     <t xml:space="preserve">16.1553249359131</t>
@@ -1406,16 +1406,16 @@
     <t xml:space="preserve">16.1648044586182</t>
   </si>
   <si>
-    <t xml:space="preserve">16.202730178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2122097015381</t>
+    <t xml:space="preserve">16.2027282714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2122077941895</t>
   </si>
   <si>
     <t xml:space="preserve">16.3259773254395</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1079196929932</t>
+    <t xml:space="preserve">16.1079177856445</t>
   </si>
   <si>
     <t xml:space="preserve">16.0699977874756</t>
@@ -1427,37 +1427,37 @@
     <t xml:space="preserve">16.7241744995117</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6672878265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5724811553955</t>
+    <t xml:space="preserve">16.6672859191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5724792480469</t>
   </si>
   <si>
     <t xml:space="preserve">16.3070182800293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596130371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6767692565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8379440307617</t>
+    <t xml:space="preserve">16.2596111297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6767711639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8379421234131</t>
   </si>
   <si>
     <t xml:space="preserve">16.885347366333</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0465240478516</t>
+    <t xml:space="preserve">17.0465202331543</t>
   </si>
   <si>
     <t xml:space="preserve">16.9232692718506</t>
   </si>
   <si>
-    <t xml:space="preserve">16.771577835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.373384475708</t>
+    <t xml:space="preserve">16.7715759277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3733825683594</t>
   </si>
   <si>
     <t xml:space="preserve">16.4492301940918</t>
@@ -1466,37 +1466,37 @@
     <t xml:space="preserve">16.2216892242432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4018230438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5535163879395</t>
+    <t xml:space="preserve">16.4018249511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5535182952881</t>
   </si>
   <si>
     <t xml:space="preserve">16.3639030456543</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5155963897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1034069061279</t>
+    <t xml:space="preserve">16.5155944824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1034107208252</t>
   </si>
   <si>
     <t xml:space="preserve">17.5395240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9472007751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4447154998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0799331665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1652603149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.715145111084</t>
+    <t xml:space="preserve">17.9472026824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4447135925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0799312591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1652584075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7151489257812</t>
   </si>
   <si>
     <t xml:space="preserve">18.1368141174316</t>
@@ -1505,16 +1505,16 @@
     <t xml:space="preserve">18.4117584228516</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2505874633789</t>
+    <t xml:space="preserve">18.2505855560303</t>
   </si>
   <si>
     <t xml:space="preserve">18.0704498291016</t>
   </si>
   <si>
-    <t xml:space="preserve">17.861873626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6343326568604</t>
+    <t xml:space="preserve">17.8618717193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.634334564209</t>
   </si>
   <si>
     <t xml:space="preserve">17.7860260009766</t>
@@ -1526,34 +1526,34 @@
     <t xml:space="preserve">18.2979888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.373836517334</t>
+    <t xml:space="preserve">18.3738346099854</t>
   </si>
   <si>
     <t xml:space="preserve">18.203182220459</t>
   </si>
   <si>
-    <t xml:space="preserve">18.032527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1083717346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2126617431641</t>
+    <t xml:space="preserve">18.0325241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1083755493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2126598358154</t>
   </si>
   <si>
     <t xml:space="preserve">18.0609683990479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9377174377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0040836334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.577449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3927974700928</t>
+    <t xml:space="preserve">17.9377193450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0040855407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5774478912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3927955627441</t>
   </si>
   <si>
     <t xml:space="preserve">17.8334293365479</t>
@@ -1562,40 +1562,40 @@
     <t xml:space="preserve">18.0135650634766</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7435894012451</t>
+    <t xml:space="preserve">18.7435874938965</t>
   </si>
   <si>
     <t xml:space="preserve">19.3408794403076</t>
   </si>
   <si>
-    <t xml:space="preserve">19.41672706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3788032531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.18918800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0564556121826</t>
+    <t xml:space="preserve">19.4167289733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3788051605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1891860961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0564575195312</t>
   </si>
   <si>
     <t xml:space="preserve">18.7246284484863</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4496803283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5255317687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7720317840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9616470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6867046356201</t>
+    <t xml:space="preserve">18.4496822357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5255298614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.772029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9616451263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6867027282715</t>
   </si>
   <si>
     <t xml:space="preserve">18.1462955474854</t>
@@ -1607,25 +1607,25 @@
     <t xml:space="preserve">18.0420074462891</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3025054931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5629978179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4537420272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5864772796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6718053817749</t>
+    <t xml:space="preserve">17.3025016784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5629997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.453742980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5864763259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6718015670776</t>
   </si>
   <si>
     <t xml:space="preserve">15.0081443786621</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4253005981445</t>
+    <t xml:space="preserve">15.4252986907959</t>
   </si>
   <si>
     <t xml:space="preserve">15.4632234573364</t>
@@ -1634,13 +1634,13 @@
     <t xml:space="preserve">15.8045320510864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7286853790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9512586593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0745086669922</t>
+    <t xml:space="preserve">15.7286863327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9512596130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0745096206665</t>
   </si>
   <si>
     <t xml:space="preserve">14.9986619949341</t>
@@ -1652,52 +1652,52 @@
     <t xml:space="preserve">15.0176248550415</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8469696044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6573543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7047576904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6763143539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6478729248047</t>
+    <t xml:space="preserve">14.8469686508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6573524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.704758644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6763153076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6478719711304</t>
   </si>
   <si>
     <t xml:space="preserve">14.932297706604</t>
   </si>
   <si>
-    <t xml:space="preserve">15.055549621582</t>
+    <t xml:space="preserve">15.0555477142334</t>
   </si>
   <si>
     <t xml:space="preserve">14.7900857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8135604858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7282333374023</t>
+    <t xml:space="preserve">13.8135595321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.728232383728</t>
   </si>
   <si>
     <t xml:space="preserve">13.1309413909912</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0835380554199</t>
+    <t xml:space="preserve">13.0835371017456</t>
   </si>
   <si>
     <t xml:space="preserve">13.386923789978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2636728286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3964033126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6523857116699</t>
+    <t xml:space="preserve">13.263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3964042663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6523866653442</t>
   </si>
   <si>
     <t xml:space="preserve">13.4912118911743</t>
@@ -1715,16 +1715,16 @@
     <t xml:space="preserve">14.4961795806885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2212352752686</t>
+    <t xml:space="preserve">14.2212362289429</t>
   </si>
   <si>
     <t xml:space="preserve">14.1643495559692</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3065624237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3350057601929</t>
+    <t xml:space="preserve">14.3065633773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3350067138672</t>
   </si>
   <si>
     <t xml:space="preserve">13.7945995330811</t>
@@ -1733,25 +1733,25 @@
     <t xml:space="preserve">13.7377128601074</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5955018997192</t>
+    <t xml:space="preserve">13.5955009460449</t>
   </si>
   <si>
     <t xml:space="preserve">13.7566757202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8988876342773</t>
+    <t xml:space="preserve">13.8988857269287</t>
   </si>
   <si>
     <t xml:space="preserve">13.9462928771973</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4203329086304</t>
+    <t xml:space="preserve">14.4203338623047</t>
   </si>
   <si>
     <t xml:space="preserve">13.7756366729736</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7232646942139</t>
+    <t xml:space="preserve">12.7232656478882</t>
   </si>
   <si>
     <t xml:space="preserve">13.3205575942993</t>
@@ -1769,31 +1769,31 @@
     <t xml:space="preserve">14.8374881744385</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2546453475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8848934173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0839900970459</t>
+    <t xml:space="preserve">15.2546463012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8848943710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0839910507202</t>
   </si>
   <si>
     <t xml:space="preserve">15.1787986755371</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1503572463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3115310668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3589372634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2925682067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1408758163452</t>
+    <t xml:space="preserve">15.1503562927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3115301132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3589363098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2925691604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1408748626709</t>
   </si>
   <si>
     <t xml:space="preserve">15.0271053314209</t>
@@ -1808,16 +1808,16 @@
     <t xml:space="preserve">14.8659315109253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9417772293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6149158477783</t>
+    <t xml:space="preserve">14.9417791366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6149168014526</t>
   </si>
   <si>
     <t xml:space="preserve">15.7097225189209</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0650300979614</t>
+    <t xml:space="preserve">15.0650291442871</t>
   </si>
   <si>
     <t xml:space="preserve">15.216721534729</t>
@@ -1832,16 +1832,16 @@
     <t xml:space="preserve">15.3968572616577</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7806043624878</t>
+    <t xml:space="preserve">14.7806053161621</t>
   </si>
   <si>
     <t xml:space="preserve">14.9038553237915</t>
   </si>
   <si>
-    <t xml:space="preserve">15.226203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1977605819702</t>
+    <t xml:space="preserve">15.2262029647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1977615356445</t>
   </si>
   <si>
     <t xml:space="preserve">15.4442625045776</t>
@@ -1865,22 +1865,22 @@
     <t xml:space="preserve">15.2641267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7855701446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6862487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8474235534668</t>
+    <t xml:space="preserve">15.7855710983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6862506866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8474254608154</t>
   </si>
   <si>
     <t xml:space="preserve">16.4966335296631</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1932468414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2311706542969</t>
+    <t xml:space="preserve">16.1932487487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2311687469482</t>
   </si>
   <si>
     <t xml:space="preserve">16.7526149749756</t>
@@ -1892,28 +1892,28 @@
     <t xml:space="preserve">16.8095016479492</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7336521148682</t>
+    <t xml:space="preserve">16.7336559295654</t>
   </si>
   <si>
     <t xml:space="preserve">16.8948287963867</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8663845062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2501335144043</t>
+    <t xml:space="preserve">16.8663864135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.250129699707</t>
   </si>
   <si>
     <t xml:space="preserve">15.8993425369263</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8898611068726</t>
+    <t xml:space="preserve">15.8898620605469</t>
   </si>
   <si>
     <t xml:space="preserve">15.9277820587158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8519372940063</t>
+    <t xml:space="preserve">15.8519344329834</t>
   </si>
   <si>
     <t xml:space="preserve">16.3544216156006</t>
@@ -1922,10 +1922,10 @@
     <t xml:space="preserve">16.2406482696533</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9183044433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5015983581543</t>
+    <t xml:space="preserve">15.9183053970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5016021728516</t>
   </si>
   <si>
     <t xml:space="preserve">17.6627731323242</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">17.2835426330566</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8239498138428</t>
+    <t xml:space="preserve">17.8239479064941</t>
   </si>
   <si>
     <t xml:space="preserve">18.6677417755127</t>
@@ -1949,28 +1949,28 @@
     <t xml:space="preserve">18.5743827819824</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8704280853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5962104797363</t>
+    <t xml:space="preserve">18.8704261779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.596212387085</t>
   </si>
   <si>
     <t xml:space="preserve">19.5007133483887</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9277267456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9468231201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9850254058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5934810638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.708080291748</t>
+    <t xml:space="preserve">18.9277248382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9468250274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9850234985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5934829711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7080783843994</t>
   </si>
   <si>
     <t xml:space="preserve">18.9659252166748</t>
@@ -1979,19 +1979,19 @@
     <t xml:space="preserve">19.0327739715576</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2333202362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3861179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0900726318359</t>
+    <t xml:space="preserve">19.2333221435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.386116027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0900707244873</t>
   </si>
   <si>
     <t xml:space="preserve">19.1951198577881</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1187229156494</t>
+    <t xml:space="preserve">19.1187210083008</t>
   </si>
   <si>
     <t xml:space="preserve">19.252420425415</t>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">19.9018077850342</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1501026153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2646980285645</t>
+    <t xml:space="preserve">20.1501007080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2646999359131</t>
   </si>
   <si>
     <t xml:space="preserve">20.5893936157227</t>
@@ -2012,67 +2012,67 @@
     <t xml:space="preserve">20.5511932373047</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7994899749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9591045379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8445091247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4816150665283</t>
+    <t xml:space="preserve">20.799488067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9591064453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8445072174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4816131591797</t>
   </si>
   <si>
     <t xml:space="preserve">19.3097171783447</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6344108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6726093292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0928039550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9400062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6535091400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5580139160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7299098968506</t>
+    <t xml:space="preserve">19.6344127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6726112365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0928020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9400043487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6535110473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.558012008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7299118041992</t>
   </si>
   <si>
     <t xml:space="preserve">20.3028984069824</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2838001251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2265014648438</t>
+    <t xml:space="preserve">20.2837982177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2264995574951</t>
   </si>
   <si>
     <t xml:space="preserve">20.7039909362793</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6848907470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4174957275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0355014801025</t>
+    <t xml:space="preserve">20.6848926544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4174976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0355033874512</t>
   </si>
   <si>
     <t xml:space="preserve">20.1310024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1882991790771</t>
+    <t xml:space="preserve">20.1883010864258</t>
   </si>
   <si>
     <t xml:space="preserve">21.2769794464111</t>
@@ -2087,46 +2087,46 @@
     <t xml:space="preserve">20.0164031982422</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5702953338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9904842376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1050834655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1623802185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2578792572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0286846160889</t>
+    <t xml:space="preserve">20.570291519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9904861450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1050815582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1623821258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2578811645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0286827087402</t>
   </si>
   <si>
     <t xml:space="preserve">21.2960796356201</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8499660491943</t>
+    <t xml:space="preserve">21.849967956543</t>
   </si>
   <si>
     <t xml:space="preserve">22.4802570343018</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5566539764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5184535980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0982627868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2510585784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9645652770996</t>
+    <t xml:space="preserve">22.5566520690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5184574127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0982608795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2510623931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9645671844482</t>
   </si>
   <si>
     <t xml:space="preserve">21.9454669952393</t>
@@ -2156,10 +2156,10 @@
     <t xml:space="preserve">20.474796295166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.455696105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1241836547852</t>
+    <t xml:space="preserve">20.4556941986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1241817474365</t>
   </si>
   <si>
     <t xml:space="preserve">20.7803897857666</t>
@@ -2174,67 +2174,67 @@
     <t xml:space="preserve">21.7353706359863</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5061740875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2196807861328</t>
+    <t xml:space="preserve">21.506175994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2196788787842</t>
   </si>
   <si>
     <t xml:space="preserve">21.3724765777588</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6016750335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.678071975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4870777130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5825748443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6466941833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.608491897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4938926696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8567867279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3792991638184</t>
+    <t xml:space="preserve">21.6016731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6780700683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4870758056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5825729370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.646692276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6084938049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4938945770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8567886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3792953491211</t>
   </si>
   <si>
     <t xml:space="preserve">20.8949851989746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9331874847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3219966888428</t>
+    <t xml:space="preserve">20.9331855773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3219985961914</t>
   </si>
   <si>
     <t xml:space="preserve">20.3410968780518</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8308696746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0218639373779</t>
+    <t xml:space="preserve">21.830867767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0218658447266</t>
   </si>
   <si>
     <t xml:space="preserve">22.5375556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6521530151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0150470733643</t>
+    <t xml:space="preserve">22.6521511077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.015043258667</t>
   </si>
   <si>
     <t xml:space="preserve">23.4543361663818</t>
@@ -2252,19 +2252,19 @@
     <t xml:space="preserve">24.084623336792</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7981300354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8745288848877</t>
+    <t xml:space="preserve">23.7981281280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8745307922363</t>
   </si>
   <si>
     <t xml:space="preserve">23.970027923584</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3711185455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8677082061768</t>
+    <t xml:space="preserve">24.3711204528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8677101135254</t>
   </si>
   <si>
     <t xml:space="preserve">25.0969047546387</t>
@@ -2273,94 +2273,94 @@
     <t xml:space="preserve">25.3642978668213</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3329181671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.982307434082</t>
+    <t xml:space="preserve">24.3329200744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9823055267334</t>
   </si>
   <si>
     <t xml:space="preserve">25.287899017334</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9250068664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0205059051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6194133758545</t>
+    <t xml:space="preserve">24.9250087738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6194114685059</t>
   </si>
   <si>
     <t xml:space="preserve">24.9441070556641</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8295097351074</t>
+    <t xml:space="preserve">24.8295078277588</t>
   </si>
   <si>
     <t xml:space="preserve">24.6385116577148</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4475173950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5430164337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3520183563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6576137542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6767139434814</t>
+    <t xml:space="preserve">24.4475154876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5430145263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3520164489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6576156616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6767120361328</t>
   </si>
   <si>
     <t xml:space="preserve">24.4857158660889</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5621166229248</t>
+    <t xml:space="preserve">24.5621147155762</t>
   </si>
   <si>
     <t xml:space="preserve">24.5812149047852</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6958103179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.306999206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3451976776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8486099243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0014057159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2115039825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7653884887695</t>
+    <t xml:space="preserve">24.6958141326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3070011138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3451995849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8486080169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0014038085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2115020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7653923034668</t>
   </si>
   <si>
     <t xml:space="preserve">25.6125926971436</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5552959442139</t>
+    <t xml:space="preserve">25.5552940368652</t>
   </si>
   <si>
     <t xml:space="preserve">25.1542015075684</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8226890563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7722110748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5239162445068</t>
+    <t xml:space="preserve">25.8226909637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7722091674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5239143371582</t>
   </si>
   <si>
     <t xml:space="preserve">24.9059066772461</t>
@@ -2372,67 +2372,67 @@
     <t xml:space="preserve">26.2237815856934</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2810821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.395679473877</t>
+    <t xml:space="preserve">26.2810802459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3956775665283</t>
   </si>
   <si>
     <t xml:space="preserve">27.1405620574951</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2169628143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.522554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6944541931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8281497955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1910419464111</t>
+    <t xml:space="preserve">27.2169647216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5225563049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.694450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8281517028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1910438537598</t>
   </si>
   <si>
     <t xml:space="preserve">28.783130645752</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2865428924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8854503631592</t>
+    <t xml:space="preserve">28.2865409851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8854484558105</t>
   </si>
   <si>
     <t xml:space="preserve">25.9754867553711</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2306022644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6003131866455</t>
+    <t xml:space="preserve">25.2306003570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6003170013428</t>
   </si>
   <si>
     <t xml:space="preserve">23.6071319580078</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4666156768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4352397918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8254089355469</t>
+    <t xml:space="preserve">24.4666175842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4352340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8254070281982</t>
   </si>
   <si>
     <t xml:space="preserve">19.3479175567627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5852909088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3233585357666</t>
+    <t xml:space="preserve">15.5852918624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.323356628418</t>
   </si>
   <si>
     <t xml:space="preserve">15.7285385131836</t>
@@ -2441,10 +2441,10 @@
     <t xml:space="preserve">16.1200790405273</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9031677246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.523904800415</t>
+    <t xml:space="preserve">16.9031658172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5239028930664</t>
   </si>
   <si>
     <t xml:space="preserve">17.7435512542725</t>
@@ -2453,10 +2453,10 @@
     <t xml:space="preserve">18.1350917816162</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8322296142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1446418762207</t>
+    <t xml:space="preserve">18.8322257995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1446399688721</t>
   </si>
   <si>
     <t xml:space="preserve">18.221040725708</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">17.8772449493408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3806571960449</t>
+    <t xml:space="preserve">17.3806591033936</t>
   </si>
   <si>
     <t xml:space="preserve">17.4093055725098</t>
@@ -2480,7 +2480,7 @@
     <t xml:space="preserve">17.6480503082275</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7844791412354</t>
+    <t xml:space="preserve">18.7844772338867</t>
   </si>
   <si>
     <t xml:space="preserve">18.4311351776123</t>
@@ -2495,49 +2495,49 @@
     <t xml:space="preserve">17.9536437988281</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8663368225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.271520614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8465538024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.006856918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2455997467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9877548217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9686546325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7681102752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6753406524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7640209197998</t>
+    <t xml:space="preserve">20.8663387298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2715187072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8465557098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0068531036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2456016540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.987756729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9686527252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7681083679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6753425598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7640190124512</t>
   </si>
   <si>
     <t xml:space="preserve">21.3820266723633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.337007522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.792667388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.019136428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4297752380371</t>
+    <t xml:space="preserve">22.3370094299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7926712036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0191345214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4297771453857</t>
   </si>
   <si>
     <t xml:space="preserve">21.8595161437988</t>
@@ -2549,10 +2549,10 @@
     <t xml:space="preserve">21.9932155609131</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6589736938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0341453552246</t>
+    <t xml:space="preserve">21.658971786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0341472625732</t>
   </si>
   <si>
     <t xml:space="preserve">23.1391906738281</t>
@@ -2567,19 +2567,19 @@
     <t xml:space="preserve">23.8267803192139</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5211849212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8458766937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8172283172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3588371276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6903495788574</t>
+    <t xml:space="preserve">23.521183013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8458786010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8172302246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3588390350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6903514862061</t>
   </si>
   <si>
     <t xml:space="preserve">22.6330528259277</t>
@@ -2597,16 +2597,16 @@
     <t xml:space="preserve">22.9386463165283</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3015403747559</t>
+    <t xml:space="preserve">23.3015384674072</t>
   </si>
   <si>
     <t xml:space="preserve">22.6808013916016</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7094497680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1487407684326</t>
+    <t xml:space="preserve">22.709451675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1487426757812</t>
   </si>
   <si>
     <t xml:space="preserve">23.4638862609863</t>
@@ -2615,10 +2615,10 @@
     <t xml:space="preserve">22.4229564666748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4611568450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6426029205322</t>
+    <t xml:space="preserve">22.4611549377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6426010131836</t>
   </si>
   <si>
     <t xml:space="preserve">22.7381000518799</t>
@@ -2630,16 +2630,16 @@
     <t xml:space="preserve">23.2442398071289</t>
   </si>
   <si>
-    <t xml:space="preserve">23.540283203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7408313751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8363285064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.71217918396</t>
+    <t xml:space="preserve">23.5402851104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7408294677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8363265991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7121810913086</t>
   </si>
   <si>
     <t xml:space="preserve">23.7599296569824</t>
@@ -2651,16 +2651,16 @@
     <t xml:space="preserve">24.3233680725098</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7340126037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2783489227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0682544708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0587024688721</t>
+    <t xml:space="preserve">24.7340106964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2783508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0682563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0587043762207</t>
   </si>
   <si>
     <t xml:space="preserve">24.7531108856201</t>
@@ -2672,43 +2672,43 @@
     <t xml:space="preserve">26.5580253601074</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5102787017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6467056274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2292423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5034561157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5894050598145</t>
+    <t xml:space="preserve">26.510274887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6467018127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2292404174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.503454208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5894031524658</t>
   </si>
   <si>
     <t xml:space="preserve">27.1596641540527</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5512065887451</t>
+    <t xml:space="preserve">27.5512046813965</t>
   </si>
   <si>
     <t xml:space="preserve">27.0164184570312</t>
   </si>
   <si>
-    <t xml:space="preserve">27.035514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3793106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2265129089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.054615020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2838096618652</t>
+    <t xml:space="preserve">27.0355129241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3793087005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2265110015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0546169281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2838115692139</t>
   </si>
   <si>
     <t xml:space="preserve">26.5675754547119</t>
@@ -2717,7 +2717,7 @@
     <t xml:space="preserve">27.0450668334961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.710823059082</t>
+    <t xml:space="preserve">26.7108211517334</t>
   </si>
   <si>
     <t xml:space="preserve">26.5007266998291</t>
@@ -2726,25 +2726,25 @@
     <t xml:space="preserve">26.4529762268066</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6630725860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5389270782471</t>
+    <t xml:space="preserve">26.6630744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5389251708984</t>
   </si>
   <si>
     <t xml:space="preserve">26.2619800567627</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4625244140625</t>
+    <t xml:space="preserve">26.4625263214111</t>
   </si>
   <si>
     <t xml:space="preserve">27.5989551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6726245880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7585735321045</t>
+    <t xml:space="preserve">26.6726226806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7585716247559</t>
   </si>
   <si>
     <t xml:space="preserve">27.3888607025146</t>
@@ -2756,10 +2756,10 @@
     <t xml:space="preserve">28.1814918518066</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3533897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5061893463135</t>
+    <t xml:space="preserve">28.3533935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5061874389648</t>
   </si>
   <si>
     <t xml:space="preserve">28.9932270050049</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">27.57985496521</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6562519073486</t>
+    <t xml:space="preserve">27.6562538146973</t>
   </si>
   <si>
     <t xml:space="preserve">27.4748077392578</t>
@@ -2783,28 +2783,28 @@
     <t xml:space="preserve">27.6849021911621</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3847713470459</t>
+    <t xml:space="preserve">29.3847694396973</t>
   </si>
   <si>
     <t xml:space="preserve">29.967306137085</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1746730804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4802684783936</t>
+    <t xml:space="preserve">29.1746711730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4802665710449</t>
   </si>
   <si>
     <t xml:space="preserve">29.8336124420166</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0246067047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1651248931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3274707794189</t>
+    <t xml:space="preserve">30.0246086120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1651229858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3274688720703</t>
   </si>
   <si>
     <t xml:space="preserve">29.8049602508545</t>
@@ -2813,22 +2813,22 @@
     <t xml:space="preserve">30.4734477996826</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9891376495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7503929138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5402965545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.922290802002</t>
+    <t xml:space="preserve">30.9891357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7503910064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5402984619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9222888946533</t>
   </si>
   <si>
     <t xml:space="preserve">30.7408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9318408966064</t>
+    <t xml:space="preserve">30.9318370819092</t>
   </si>
   <si>
     <t xml:space="preserve">30.7217407226562</t>
@@ -2843,52 +2843,52 @@
     <t xml:space="preserve">30.4829978942871</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5593948364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7258319854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2128734588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.903190612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9918689727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.899097442627</t>
+    <t xml:space="preserve">30.5593967437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7258338928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2128715515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9031887054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9918613433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8991012573242</t>
   </si>
   <si>
     <t xml:space="preserve">33.6535377502441</t>
   </si>
   <si>
-    <t xml:space="preserve">33.309741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4693565368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3288383483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.558032989502</t>
+    <t xml:space="preserve">33.3097457885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4693603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3288421630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5580368041992</t>
   </si>
   <si>
     <t xml:space="preserve">34.1310272216797</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4338874816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4461669921875</t>
+    <t xml:space="preserve">33.4338912963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4461708068848</t>
   </si>
   <si>
     <t xml:space="preserve">33.8158798217773</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9304809570312</t>
+    <t xml:space="preserve">33.930477142334</t>
   </si>
   <si>
     <t xml:space="preserve">32.6603546142578</t>
@@ -2900,28 +2900,28 @@
     <t xml:space="preserve">32.8513526916504</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5143737792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6098747253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9727668762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7367515563965</t>
+    <t xml:space="preserve">31.5143756866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6098728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9727687835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7367553710938</t>
   </si>
   <si>
     <t xml:space="preserve">32.0587158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2565326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8840923309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0177879333496</t>
+    <t xml:space="preserve">31.2565307617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.884090423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.017786026001</t>
   </si>
   <si>
     <t xml:space="preserve">31.1323852539062</t>
@@ -2930,19 +2930,19 @@
     <t xml:space="preserve">30.8745422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0846309661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6194267272949</t>
+    <t xml:space="preserve">31.0846347808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6194248199463</t>
   </si>
   <si>
     <t xml:space="preserve">32.0969161987305</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3615798950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1542091369629</t>
+    <t xml:space="preserve">31.3615779876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1542129516602</t>
   </si>
   <si>
     <t xml:space="preserve">31.9441204071045</t>
@@ -2951,55 +2951,55 @@
     <t xml:space="preserve">32.4216117858887</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6958198547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2115135192871</t>
+    <t xml:space="preserve">31.6958236694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2115097045898</t>
   </si>
   <si>
     <t xml:space="preserve">31.7435722351074</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2783584594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5075607299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4120559692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0491676330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5334739685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2087821960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3165626525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1637649536133</t>
+    <t xml:space="preserve">32.2783622741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5075531005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4120597839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0491638183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5334758758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2087802886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3165588378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.163761138916</t>
   </si>
   <si>
     <t xml:space="preserve">32.1064643859863</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3834114074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6221542358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.650806427002</t>
+    <t xml:space="preserve">32.3834075927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6221504211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6508026123047</t>
   </si>
   <si>
     <t xml:space="preserve">32.8036041259766</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5839500427246</t>
+    <t xml:space="preserve">32.5839614868164</t>
   </si>
   <si>
     <t xml:space="preserve">32.3547630310059</t>
@@ -3011,91 +3011,91 @@
     <t xml:space="preserve">32.0396194458008</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5648574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3261108398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9250202178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0423431396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7967796325684</t>
+    <t xml:space="preserve">32.5648536682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.326114654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9250164031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.042350769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7967834472656</t>
   </si>
   <si>
     <t xml:space="preserve">34.5989646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4843673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9427604675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8854522705078</t>
+    <t xml:space="preserve">34.4843711853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9427642822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8854598999023</t>
   </si>
   <si>
     <t xml:space="preserve">35.0000648498535</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8022422790527</t>
+    <t xml:space="preserve">35.80224609375</t>
   </si>
   <si>
     <t xml:space="preserve">35.5539474487305</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3342971801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2551727294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9018325805664</t>
+    <t xml:space="preserve">35.3343048095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2551765441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9018287658691</t>
   </si>
   <si>
     <t xml:space="preserve">33.3670387268066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3192939758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7817687988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8104209899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4598083496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7080993652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9768562316895</t>
+    <t xml:space="preserve">33.3192901611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7817707061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8104248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4598121643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7081031799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9768581390381</t>
   </si>
   <si>
     <t xml:space="preserve">29.4898147583008</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6876354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0027770996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3874988555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6453437805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4761753082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5211982727051</t>
+    <t xml:space="preserve">28.6876335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.002779006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3875007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6453456878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4761772155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5211944580078</t>
   </si>
   <si>
     <t xml:space="preserve">30.7312927246094</t>
@@ -3110,16 +3110,16 @@
     <t xml:space="preserve">29.5375652313232</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1487560272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6671733856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4065990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.769495010376</t>
+    <t xml:space="preserve">30.148754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.667179107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4065971374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7694931030273</t>
   </si>
   <si>
     <t xml:space="preserve">30.6644439697266</t>
@@ -3128,43 +3128,43 @@
     <t xml:space="preserve">30.3111019134521</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9413890838623</t>
+    <t xml:space="preserve">30.9413909912109</t>
   </si>
   <si>
     <t xml:space="preserve">31.2756328582764</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9604873657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5812282562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3424797058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5007362365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9373016357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8731842041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6344413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6248817443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1787757873535</t>
+    <t xml:space="preserve">30.960485458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5812244415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3424816131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5007400512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9372978210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8731803894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6344375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.624885559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1787796020508</t>
   </si>
   <si>
     <t xml:space="preserve">34.2169761657715</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9905090332031</t>
+    <t xml:space="preserve">34.9905052185059</t>
   </si>
   <si>
     <t xml:space="preserve">34.8281631469727</t>
@@ -3173,28 +3173,28 @@
     <t xml:space="preserve">34.302921295166</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1091918945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5484924316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8063354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2333450317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0928268432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5771369934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2688102722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9059238433838</t>
+    <t xml:space="preserve">33.1091957092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5484886169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8063316345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.233341217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.092830657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5771408081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2688179016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9059143066406</t>
   </si>
   <si>
     <t xml:space="preserve">31.8868217468262</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">33.1378440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7995071411133</t>
+    <t xml:space="preserve">34.7995109558105</t>
   </si>
   <si>
     <t xml:space="preserve">35.8851928710938</t>
@@ -3233,13 +3233,13 @@
     <t xml:space="preserve">37.1246032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0189170837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6818542480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2391090393066</t>
+    <t xml:space="preserve">37.018913269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6818580627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2391128540039</t>
   </si>
   <si>
     <t xml:space="preserve">37.7683258056641</t>
@@ -3254,10 +3254,10 @@
     <t xml:space="preserve">39.2479286193848</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6138114929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.642635345459</t>
+    <t xml:space="preserve">38.6138153076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6426391601562</t>
   </si>
   <si>
     <t xml:space="preserve">39.3440093994141</t>
@@ -3269,31 +3269,31 @@
     <t xml:space="preserve">38.7963638305664</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7195014953613</t>
+    <t xml:space="preserve">38.7194976806641</t>
   </si>
   <si>
     <t xml:space="preserve">38.6042060852051</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6130294799805</t>
+    <t xml:space="preserve">39.6130256652832</t>
   </si>
   <si>
     <t xml:space="preserve">39.6514587402344</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7475395202637</t>
+    <t xml:space="preserve">39.7475357055664</t>
   </si>
   <si>
     <t xml:space="preserve">40.4969482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0069427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8051872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9685134887695</t>
+    <t xml:space="preserve">40.0069465637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8051795959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9685173034668</t>
   </si>
   <si>
     <t xml:space="preserve">39.6034240722656</t>
@@ -3302,13 +3302,13 @@
     <t xml:space="preserve">39.7571487426758</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9973373413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0749855041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5769577026367</t>
+    <t xml:space="preserve">39.9973411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0749893188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5769538879395</t>
   </si>
   <si>
     <t xml:space="preserve">37.5665588378906</t>
@@ -3329,28 +3329,28 @@
     <t xml:space="preserve">38.4793014526367</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4496994018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1806793212891</t>
+    <t xml:space="preserve">39.4496955871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1806755065918</t>
   </si>
   <si>
     <t xml:space="preserve">38.8540115356445</t>
   </si>
   <si>
-    <t xml:space="preserve">39.430477142334</t>
+    <t xml:space="preserve">39.4304809570312</t>
   </si>
   <si>
     <t xml:space="preserve">38.7675399780273</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0453834533691</t>
+    <t xml:space="preserve">40.0453796386719</t>
   </si>
   <si>
     <t xml:space="preserve">40.6410636901855</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7275352478027</t>
+    <t xml:space="preserve">40.7275314331055</t>
   </si>
   <si>
     <t xml:space="preserve">40.3528289794922</t>
@@ -3359,16 +3359,16 @@
     <t xml:space="preserve">40.7083168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2567558288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.333610534668</t>
+    <t xml:space="preserve">40.2567520141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3336143493652</t>
   </si>
   <si>
     <t xml:space="preserve">40.266357421875</t>
   </si>
   <si>
-    <t xml:space="preserve">40.448902130127</t>
+    <t xml:space="preserve">40.4489059448242</t>
   </si>
   <si>
     <t xml:space="preserve">41.0157661437988</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">41.1406707763672</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3424301147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2271385192871</t>
+    <t xml:space="preserve">41.3424339294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2271423339844</t>
   </si>
   <si>
     <t xml:space="preserve">41.2367477416992</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">43.0814476013184</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2455749511719</t>
+    <t xml:space="preserve">42.2455673217773</t>
   </si>
   <si>
     <t xml:space="preserve">42.0341949462891</t>
@@ -3416,46 +3416,46 @@
     <t xml:space="preserve">42.6683120727539</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9853706359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3896865844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8988990783691</t>
+    <t xml:space="preserve">42.9853744506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3896903991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8989028930664</t>
   </si>
   <si>
     <t xml:space="preserve">42.0245895385742</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9765510559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5345916748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4577331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7187156677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0061645507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0165557861328</t>
+    <t xml:space="preserve">41.9765472412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.534595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4577293395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7187118530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.006160736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0165596008301</t>
   </si>
   <si>
     <t xml:space="preserve">40.8332214355469</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0638084411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0718383789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1679229736328</t>
+    <t xml:space="preserve">41.0638046264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0718421936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1679191589355</t>
   </si>
   <si>
     <t xml:space="preserve">44.3112487792969</t>
@@ -3464,16 +3464,16 @@
     <t xml:space="preserve">43.2159576416016</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9477310180664</t>
+    <t xml:space="preserve">41.9477272033691</t>
   </si>
   <si>
     <t xml:space="preserve">39.7859687805176</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2759628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5842018127441</t>
+    <t xml:space="preserve">40.2759666442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5842056274414</t>
   </si>
   <si>
     <t xml:space="preserve">39.1902847290039</t>
@@ -3485,19 +3485,19 @@
     <t xml:space="preserve">39.6802787780762</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1030311584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0077362060547</t>
+    <t xml:space="preserve">40.10302734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0077323913574</t>
   </si>
   <si>
     <t xml:space="preserve">39.0653800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9108695983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2087135314941</t>
+    <t xml:space="preserve">39.9108734130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2087097167969</t>
   </si>
   <si>
     <t xml:space="preserve">41.2463531494141</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">41.169490814209</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2263526916504</t>
+    <t xml:space="preserve">42.2263565063477</t>
   </si>
   <si>
     <t xml:space="preserve">42.9469375610352</t>
@@ -3524,58 +3524,58 @@
     <t xml:space="preserve">42.3800811767578</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3992958068848</t>
+    <t xml:space="preserve">42.3992919921875</t>
   </si>
   <si>
     <t xml:space="preserve">43.0045852661133</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9653625488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8596839904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7147789001465</t>
+    <t xml:space="preserve">43.9653663635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8596801757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7147750854492</t>
   </si>
   <si>
     <t xml:space="preserve">44.2632102966309</t>
   </si>
   <si>
-    <t xml:space="preserve">43.725170135498</t>
+    <t xml:space="preserve">43.7251739501953</t>
   </si>
   <si>
     <t xml:space="preserve">44.0037994384766</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2055625915527</t>
+    <t xml:space="preserve">44.2055587768555</t>
   </si>
   <si>
     <t xml:space="preserve">43.436939239502</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2551803588867</t>
+    <t xml:space="preserve">42.2551765441895</t>
   </si>
   <si>
     <t xml:space="preserve">42.8604698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8028182983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6794967651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6018447875977</t>
+    <t xml:space="preserve">42.8028221130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.679500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6018486022949</t>
   </si>
   <si>
     <t xml:space="preserve">40.5449867248535</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0830192565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4289054870605</t>
+    <t xml:space="preserve">41.0830230712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4289016723633</t>
   </si>
   <si>
     <t xml:space="preserve">41.4192962646484</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">40.1318511962891</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1606712341309</t>
+    <t xml:space="preserve">40.1606750488281</t>
   </si>
   <si>
     <t xml:space="preserve">41.2655715942383</t>
@@ -3596,7 +3596,7 @@
     <t xml:space="preserve">40.1414566040039</t>
   </si>
   <si>
-    <t xml:space="preserve">40.314395904541</t>
+    <t xml:space="preserve">40.3143997192383</t>
   </si>
   <si>
     <t xml:space="preserve">41.0926322937012</t>
@@ -3611,13 +3611,13 @@
     <t xml:space="preserve">42.3512573242188</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3704719543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5626258850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.533016204834</t>
+    <t xml:space="preserve">42.3704681396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5626220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5330200195312</t>
   </si>
   <si>
     <t xml:space="preserve">43.6579170227051</t>
@@ -3632,25 +3632,25 @@
     <t xml:space="preserve">45.3681106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5890922546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8108558654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8885078430176</t>
+    <t xml:space="preserve">45.5890884399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8108520507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8885040283203</t>
   </si>
   <si>
     <t xml:space="preserve">44.0518379211426</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5914497375488</t>
+    <t xml:space="preserve">42.5914535522461</t>
   </si>
   <si>
     <t xml:space="preserve">41.8708648681641</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0261650085449</t>
+    <t xml:space="preserve">40.0261611938477</t>
   </si>
   <si>
     <t xml:space="preserve">39.2671432495117</t>
@@ -3659,22 +3659,22 @@
     <t xml:space="preserve">38.9308700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3832321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1814613342285</t>
+    <t xml:space="preserve">38.383228302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1814651489258</t>
   </si>
   <si>
     <t xml:space="preserve">37.2014656066895</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7795104980469</t>
+    <t xml:space="preserve">35.7795066833496</t>
   </si>
   <si>
     <t xml:space="preserve">34.5208854675293</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0012741088867</t>
+    <t xml:space="preserve">35.001277923584</t>
   </si>
   <si>
     <t xml:space="preserve">35.0397071838379</t>
@@ -3683,7 +3683,7 @@
     <t xml:space="preserve">34.4632377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0581398010254</t>
+    <t xml:space="preserve">36.0581321716309</t>
   </si>
   <si>
     <t xml:space="preserve">36.7018585205078</t>
@@ -3698,22 +3698,22 @@
     <t xml:space="preserve">34.8859825134277</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6553916931152</t>
+    <t xml:space="preserve">34.6553955078125</t>
   </si>
   <si>
     <t xml:space="preserve">33.7138252258301</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1165657043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7706871032715</t>
+    <t xml:space="preserve">35.116569519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7706909179688</t>
   </si>
   <si>
     <t xml:space="preserve">33.9636306762695</t>
   </si>
   <si>
-    <t xml:space="preserve">33.377555847168</t>
+    <t xml:space="preserve">33.3775596618652</t>
   </si>
   <si>
     <t xml:space="preserve">34.7418632507324</t>
@@ -3722,10 +3722,10 @@
     <t xml:space="preserve">34.2710800170898</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2806930541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1461791992188</t>
+    <t xml:space="preserve">34.2806854248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.146183013916</t>
   </si>
   <si>
     <t xml:space="preserve">33.7714767456055</t>
@@ -3737,31 +3737,31 @@
     <t xml:space="preserve">34.5689239501953</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2510795593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.933235168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9420547485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4712677001953</t>
+    <t xml:space="preserve">35.2510757446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9332313537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9420509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4712715148926</t>
   </si>
   <si>
     <t xml:space="preserve">36.4520530700684</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1253890991211</t>
+    <t xml:space="preserve">36.1253852844238</t>
   </si>
   <si>
     <t xml:space="preserve">34.7802963256836</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5889282226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6450004577637</t>
+    <t xml:space="preserve">33.588924407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6449966430664</t>
   </si>
   <si>
     <t xml:space="preserve">33.7042236328125</t>
@@ -3779,16 +3779,16 @@
     <t xml:space="preserve">36.2695083618164</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3175430297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9812698364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5200996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0973472595215</t>
+    <t xml:space="preserve">36.3175468444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.981273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5200958251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.097354888916</t>
   </si>
   <si>
     <t xml:space="preserve">35.7602958679199</t>
@@ -3797,13 +3797,13 @@
     <t xml:space="preserve">36.2118606567383</t>
   </si>
   <si>
-    <t xml:space="preserve">38.508129119873</t>
+    <t xml:space="preserve">38.5081329345703</t>
   </si>
   <si>
     <t xml:space="preserve">39.0173416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9500885009766</t>
+    <t xml:space="preserve">38.9500846862793</t>
   </si>
   <si>
     <t xml:space="preserve">40.2375373840332</t>
@@ -3812,7 +3812,7 @@
     <t xml:space="preserve">41.2943954467773</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8908653259277</t>
+    <t xml:space="preserve">40.890869140625</t>
   </si>
   <si>
     <t xml:space="preserve">40.6891021728516</t>
@@ -3821,40 +3821,40 @@
     <t xml:space="preserve">39.8340072631836</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6330261230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4208679199219</t>
+    <t xml:space="preserve">38.6330299377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4208717346191</t>
   </si>
   <si>
     <t xml:space="preserve">39.219108581543</t>
   </si>
   <si>
-    <t xml:space="preserve">38.623420715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9796981811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.807544708252</t>
+    <t xml:space="preserve">38.6234169006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9797019958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8075485229492</t>
   </si>
   <si>
     <t xml:space="preserve">36.6442108154297</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3367614746094</t>
+    <t xml:space="preserve">36.3367652893066</t>
   </si>
   <si>
     <t xml:space="preserve">35.4528427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2502899169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.721076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1349983215332</t>
+    <t xml:space="preserve">36.2502861022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7210731506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1350021362305</t>
   </si>
   <si>
     <t xml:space="preserve">35.7218589782715</t>
@@ -3872,31 +3872,31 @@
     <t xml:space="preserve">32.9836387634277</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9740295410156</t>
+    <t xml:space="preserve">32.9740257263184</t>
   </si>
   <si>
     <t xml:space="preserve">31.0524616241455</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9067687988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.916374206543</t>
+    <t xml:space="preserve">32.9067726135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9163780212402</t>
   </si>
   <si>
     <t xml:space="preserve">32.9644203186035</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2734394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3414840698242</t>
+    <t xml:space="preserve">31.2734413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3414859771729</t>
   </si>
   <si>
     <t xml:space="preserve">30.6777591705322</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2105293273926</t>
+    <t xml:space="preserve">31.2105255126953</t>
   </si>
   <si>
     <t xml:space="preserve">31.0071048736572</t>
@@ -3905,10 +3905,10 @@
     <t xml:space="preserve">30.9489860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2492713928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.355827331543</t>
+    <t xml:space="preserve">31.2492733001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3558235168457</t>
   </si>
   <si>
     <t xml:space="preserve">31.6948623657227</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">30.0965557098389</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6099510192871</t>
+    <t xml:space="preserve">30.6099529266357</t>
   </si>
   <si>
     <t xml:space="preserve">30.3484115600586</t>
@@ -3932,13 +3932,13 @@
     <t xml:space="preserve">30.4646530151367</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7865829467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2948303222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.260627746582</t>
+    <t xml:space="preserve">29.7865810394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2948322296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2606258392334</t>
   </si>
   <si>
     <t xml:space="preserve">25.5438137054443</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">26.3090591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.398509979248</t>
+    <t xml:space="preserve">25.3985118865967</t>
   </si>
   <si>
     <t xml:space="preserve">25.4760036468506</t>
@@ -3956,10 +3956,10 @@
     <t xml:space="preserve">25.4663181304932</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5341262817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8828449249268</t>
+    <t xml:space="preserve">25.5341243743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8828430175781</t>
   </si>
   <si>
     <t xml:space="preserve">27.9364242553711</t>
@@ -3977,7 +3977,7 @@
     <t xml:space="preserve">28.2560863494873</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3335800170898</t>
+    <t xml:space="preserve">28.3335781097412</t>
   </si>
   <si>
     <t xml:space="preserve">29.4378604888916</t>
@@ -3986,13 +3986,13 @@
     <t xml:space="preserve">29.9900035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7358798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5883102416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2127990722656</t>
+    <t xml:space="preserve">30.7358779907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5883083343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.212797164917</t>
   </si>
   <si>
     <t xml:space="preserve">30.1740493774414</t>
@@ -4001,10 +4001,10 @@
     <t xml:space="preserve">30.3387241363525</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2173385620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7523746490479</t>
+    <t xml:space="preserve">28.2173366546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7523784637451</t>
   </si>
   <si>
     <t xml:space="preserve">28.3238925933838</t>
@@ -4016,13 +4016,13 @@
     <t xml:space="preserve">28.8469734191895</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6994018554688</t>
+    <t xml:space="preserve">29.6994037628174</t>
   </si>
   <si>
     <t xml:space="preserve">30.1837368011475</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6412830352783</t>
+    <t xml:space="preserve">29.6412811279297</t>
   </si>
   <si>
     <t xml:space="preserve">29.4766082763672</t>
@@ -4031,13 +4031,13 @@
     <t xml:space="preserve">30.358097076416</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3655166625977</t>
+    <t xml:space="preserve">31.365514755249</t>
   </si>
   <si>
     <t xml:space="preserve">31.2008399963379</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4236335754395</t>
+    <t xml:space="preserve">31.4236354827881</t>
   </si>
   <si>
     <t xml:space="preserve">29.970630645752</t>
@@ -4046,16 +4046,16 @@
     <t xml:space="preserve">30.8714923858643</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0942840576172</t>
+    <t xml:space="preserve">31.0942859649658</t>
   </si>
   <si>
     <t xml:space="preserve">29.4281749725342</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7381496429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9922733306885</t>
+    <t xml:space="preserve">29.7381477355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9922752380371</t>
   </si>
   <si>
     <t xml:space="preserve">29.4572353363037</t>
@@ -4070,10 +4070,10 @@
     <t xml:space="preserve">27.8879909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8104972839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4424018859863</t>
+    <t xml:space="preserve">27.8104953765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.442403793335</t>
   </si>
   <si>
     <t xml:space="preserve">26.8030815124512</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">24.1779861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8970718383789</t>
+    <t xml:space="preserve">23.8970737457275</t>
   </si>
   <si>
     <t xml:space="preserve">24.4201545715332</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">24.0908069610596</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0133152008057</t>
+    <t xml:space="preserve">24.013313293457</t>
   </si>
   <si>
     <t xml:space="preserve">24.1973609924316</t>
@@ -4154,19 +4154,19 @@
     <t xml:space="preserve">25.291955947876</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0572052001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5728721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7159023284912</t>
+    <t xml:space="preserve">26.0572071075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5728702545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7159004211426</t>
   </si>
   <si>
     <t xml:space="preserve">26.1928195953369</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9312801361084</t>
+    <t xml:space="preserve">25.9312782287598</t>
   </si>
   <si>
     <t xml:space="preserve">25.6309909820557</t>
@@ -4175,10 +4175,10 @@
     <t xml:space="preserve">25.3307037353516</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6235752105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8389549255371</t>
+    <t xml:space="preserve">24.6235733032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8389530181885</t>
   </si>
   <si>
     <t xml:space="preserve">22.9187183380127</t>
@@ -4190,7 +4190,7 @@
     <t xml:space="preserve">24.4395275115967</t>
   </si>
   <si>
-    <t xml:space="preserve">25.350076675415</t>
+    <t xml:space="preserve">25.3500785827637</t>
   </si>
   <si>
     <t xml:space="preserve">24.8366813659668</t>
@@ -4202,13 +4202,13 @@
     <t xml:space="preserve">25.3694515228271</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0594749450684</t>
+    <t xml:space="preserve">25.059476852417</t>
   </si>
   <si>
     <t xml:space="preserve">25.4275703430176</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3620319366455</t>
+    <t xml:space="preserve">24.3620338439941</t>
   </si>
   <si>
     <t xml:space="preserve">23.7517738342285</t>
@@ -4217,7 +4217,7 @@
     <t xml:space="preserve">23.906759262085</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3523464202881</t>
+    <t xml:space="preserve">24.3523483276367</t>
   </si>
   <si>
     <t xml:space="preserve">24.3039150238037</t>
@@ -4238,7 +4238,7 @@
     <t xml:space="preserve">27.2680416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1398429870605</t>
+    <t xml:space="preserve">28.1398448944092</t>
   </si>
   <si>
     <t xml:space="preserve">27.6748828887939</t>
@@ -4253,7 +4253,7 @@
     <t xml:space="preserve">26.764331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5221652984619</t>
+    <t xml:space="preserve">26.5221672058105</t>
   </si>
   <si>
     <t xml:space="preserve">26.3187465667725</t>
@@ -4262,13 +4262,13 @@
     <t xml:space="preserve">26.8321399688721</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8805751800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0065021514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1421165466309</t>
+    <t xml:space="preserve">26.8805732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0065002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1421146392822</t>
   </si>
   <si>
     <t xml:space="preserve">26.0087738037109</t>
@@ -4277,10 +4277,10 @@
     <t xml:space="preserve">26.7837085723877</t>
   </si>
   <si>
-    <t xml:space="preserve">27.645824432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9483814239502</t>
+    <t xml:space="preserve">27.6458225250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9483833312988</t>
   </si>
   <si>
     <t xml:space="preserve">26.1540718078613</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">26.6965274810791</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0936832427979</t>
+    <t xml:space="preserve">27.0936813354492</t>
   </si>
   <si>
     <t xml:space="preserve">27.1324291229248</t>
@@ -4307,25 +4307,25 @@
     <t xml:space="preserve">26.444673538208</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0959529876709</t>
+    <t xml:space="preserve">26.0959510803223</t>
   </si>
   <si>
     <t xml:space="preserve">26.0668926239014</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8925304412842</t>
+    <t xml:space="preserve">25.8925323486328</t>
   </si>
   <si>
     <t xml:space="preserve">26.4543590545654</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8344116210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9700241088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.628719329834</t>
+    <t xml:space="preserve">25.8344097137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9700260162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6287212371826</t>
   </si>
   <si>
     <t xml:space="preserve">26.8708896636963</t>
@@ -4334,25 +4334,25 @@
     <t xml:space="preserve">26.1443843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">26.250940322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9677543640137</t>
+    <t xml:space="preserve">26.2509384155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9677562713623</t>
   </si>
   <si>
     <t xml:space="preserve">25.9797115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.105640411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5996589660645</t>
+    <t xml:space="preserve">26.1056385040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5996608734131</t>
   </si>
   <si>
     <t xml:space="preserve">26.63840675354</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2412548065186</t>
+    <t xml:space="preserve">26.2412528991699</t>
   </si>
   <si>
     <t xml:space="preserve">25.6019306182861</t>
@@ -4361,7 +4361,7 @@
     <t xml:space="preserve">24.9044876098633</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0788478851318</t>
+    <t xml:space="preserve">25.0788497924805</t>
   </si>
   <si>
     <t xml:space="preserve">24.8851165771484</t>
@@ -4373,16 +4373,16 @@
     <t xml:space="preserve">24.9335498809814</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7398166656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4782752990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6070766448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9290084838867</t>
+    <t xml:space="preserve">24.7398147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4782733917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6070785522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9290065765381</t>
   </si>
   <si>
     <t xml:space="preserve">27.1227416992188</t>
@@ -4391,7 +4391,7 @@
     <t xml:space="preserve">25.7666053771973</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4834213256836</t>
+    <t xml:space="preserve">26.483419418335</t>
   </si>
   <si>
     <t xml:space="preserve">27.2777290344238</t>
@@ -4403,7 +4403,7 @@
     <t xml:space="preserve">26.2025051116943</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6190338134766</t>
+    <t xml:space="preserve">26.6190319061279</t>
   </si>
   <si>
     <t xml:space="preserve">26.5027942657471</t>
@@ -4418,37 +4418,37 @@
     <t xml:space="preserve">28.5466842651367</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4401340484619</t>
+    <t xml:space="preserve">28.4401321411133</t>
   </si>
   <si>
     <t xml:space="preserve">28.7694797515869</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2367115020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1107864379883</t>
+    <t xml:space="preserve">28.2367095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1107845306396</t>
   </si>
   <si>
     <t xml:space="preserve">29.0310211181641</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4304466247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8954086303711</t>
+    <t xml:space="preserve">28.4304447174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8954067230225</t>
   </si>
   <si>
     <t xml:space="preserve">29.1860084533691</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6606578826904</t>
+    <t xml:space="preserve">29.6606559753418</t>
   </si>
   <si>
     <t xml:space="preserve">30.6583862304688</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9393005371094</t>
+    <t xml:space="preserve">30.9392986297607</t>
   </si>
   <si>
     <t xml:space="preserve">30.8327445983887</t>
@@ -4457,7 +4457,7 @@
     <t xml:space="preserve">31.2589588165283</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4817523956299</t>
+    <t xml:space="preserve">31.4817543029785</t>
   </si>
   <si>
     <t xml:space="preserve">31.6173667907715</t>
@@ -4472,16 +4472,16 @@
     <t xml:space="preserve">31.6754875183105</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2783355712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9176578521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9854602813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7820453643799</t>
+    <t xml:space="preserve">31.2783336639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9176559448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9854621887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7820415496826</t>
   </si>
   <si>
     <t xml:space="preserve">32.3729286193848</t>
@@ -4496,16 +4496,16 @@
     <t xml:space="preserve">32.3341865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7313346862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2373123168945</t>
+    <t xml:space="preserve">32.7313423156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2373161315918</t>
   </si>
   <si>
     <t xml:space="preserve">32.0823287963867</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3780784606934</t>
+    <t xml:space="preserve">34.3780746459961</t>
   </si>
   <si>
     <t xml:space="preserve">33.7678146362305</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">34.8817825317383</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6105575561523</t>
+    <t xml:space="preserve">34.6105537414551</t>
   </si>
   <si>
     <t xml:space="preserve">33.8259315490723</t>
@@ -4538,10 +4538,10 @@
     <t xml:space="preserve">33.0413131713867</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8475799560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1478652954102</t>
+    <t xml:space="preserve">32.8475761413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1478691101074</t>
   </si>
   <si>
     <t xml:space="preserve">33.167407989502</t>
@@ -6237,6 +6237,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.4200000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3900003433228</t>
   </si>
 </sst>
 </file>
@@ -72017,7 +72020,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.6909722222</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>1000514</v>
@@ -72038,6 +72041,32 @@
         <v>2074</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6911574074</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>1068009</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>13.539999961853</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>13.2849998474121</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>13.4799995422363</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>13.3900003433228</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>2075</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AMP.MI.xlsx
+++ b/data/AMP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="2078">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="2079">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33520460128784</t>
+    <t xml:space="preserve">7.335205078125</t>
   </si>
   <si>
     <t xml:space="preserve">AMP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39109134674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31191921234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36780595779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15357160568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96262311935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21877336502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27931785583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16288566589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03248262405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08836936950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19548606872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9859094619751</t>
+    <t xml:space="preserve">7.3910927772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31191873550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36780500411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15357112884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96262359619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21877288818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27931833267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16288614273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03248167037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08836984634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1954870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98590993881226</t>
   </si>
   <si>
     <t xml:space="preserve">7.13494157791138</t>
@@ -86,79 +86,79 @@
     <t xml:space="preserve">7.34451961517334</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23740243911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35383415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14891481399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18151473999023</t>
+    <t xml:space="preserve">7.23740196228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35383462905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14891386032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18151521682739</t>
   </si>
   <si>
     <t xml:space="preserve">7.40972137451172</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28397512435913</t>
+    <t xml:space="preserve">7.28397560119629</t>
   </si>
   <si>
     <t xml:space="preserve">7.13959884643555</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05111122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84619092941284</t>
+    <t xml:space="preserve">7.05111169815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84619140625</t>
   </si>
   <si>
     <t xml:space="preserve">6.51086759567261</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45497989654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59004068374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33389234542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29197549819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42237901687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61798477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88344955444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71112966537476</t>
+    <t xml:space="preserve">6.45498037338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59004163742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33389091491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29197597503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4223804473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61798429489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8834490776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71113061904907</t>
   </si>
   <si>
     <t xml:space="preserve">6.8368763923645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70181560516357</t>
+    <t xml:space="preserve">6.70181608200073</t>
   </si>
   <si>
     <t xml:space="preserve">6.62729930877686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99522352218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89276361465454</t>
+    <t xml:space="preserve">6.99522542953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89276456832886</t>
   </si>
   <si>
     <t xml:space="preserve">6.80427551269531</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7996187210083</t>
+    <t xml:space="preserve">6.79961776733398</t>
   </si>
   <si>
     <t xml:space="preserve">6.84153366088867</t>
@@ -167,25 +167,25 @@
     <t xml:space="preserve">6.65990018844604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63195657730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79496145248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78564548492432</t>
+    <t xml:space="preserve">6.63195610046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79496192932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78564691543579</t>
   </si>
   <si>
     <t xml:space="preserve">6.86016321182251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00919580459595</t>
+    <t xml:space="preserve">7.00919532775879</t>
   </si>
   <si>
     <t xml:space="preserve">7.11165571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08371257781982</t>
+    <t xml:space="preserve">7.08371210098267</t>
   </si>
   <si>
     <t xml:space="preserve">7.20945835113525</t>
@@ -194,178 +194,178 @@
     <t xml:space="preserve">7.10699844360352</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04179668426514</t>
+    <t xml:space="preserve">7.04179620742798</t>
   </si>
   <si>
     <t xml:space="preserve">7.24205923080444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09768438339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17220067977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93467950820923</t>
+    <t xml:space="preserve">7.09768390655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17219972610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93467855453491</t>
   </si>
   <si>
     <t xml:space="preserve">6.91605043411255</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00453853607178</t>
+    <t xml:space="preserve">7.00453805923462</t>
   </si>
   <si>
     <t xml:space="preserve">7.27000331878662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3258900642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22808742523193</t>
+    <t xml:space="preserve">7.32589054107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22808790206909</t>
   </si>
   <si>
     <t xml:space="preserve">7.50286674499512</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41437911987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48423767089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57738351821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55409526824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7310733795166</t>
+    <t xml:space="preserve">7.41437864303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48423719406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57738304138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55409622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73107290267944</t>
   </si>
   <si>
     <t xml:space="preserve">7.60066938400269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64258480072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70313024520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73573064804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88476324081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88942050933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87079191207886</t>
+    <t xml:space="preserve">7.64258575439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70312929153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73573112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88476276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8894214630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87079000473022</t>
   </si>
   <si>
     <t xml:space="preserve">7.78695964813232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94530820846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8801064491272</t>
+    <t xml:space="preserve">7.94530725479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88010454177856</t>
   </si>
   <si>
     <t xml:space="preserve">8.08968353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01760482788086</t>
+    <t xml:space="preserve">8.01760292053223</t>
   </si>
   <si>
     <t xml:space="preserve">8.09717082977295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10653209686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05036926269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17205905914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21418380737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23758411407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22354412078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1580171585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07844924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0831298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14397621154785</t>
+    <t xml:space="preserve">8.10653305053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.050368309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21418190002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23758602142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22354507446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15801811218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07845115661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08313083648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14397525787354</t>
   </si>
   <si>
     <t xml:space="preserve">8.01292419433594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91463470458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82102537155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64316749572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62912607192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6525297164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55892038345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63848781585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9895224571228</t>
+    <t xml:space="preserve">7.91463375091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82102584838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64316892623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62912654876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65253019332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55891990661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63848876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98952102661133</t>
   </si>
   <si>
     <t xml:space="preserve">7.94739723205566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05972862243652</t>
+    <t xml:space="preserve">8.05972766876221</t>
   </si>
   <si>
     <t xml:space="preserve">7.67593240737915</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71337461471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72273588180542</t>
+    <t xml:space="preserve">7.71337556838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72273731231689</t>
   </si>
   <si>
     <t xml:space="preserve">7.87250995635986</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92867565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89123249053955</t>
+    <t xml:space="preserve">7.92867660522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89123058319092</t>
   </si>
   <si>
     <t xml:space="preserve">7.81166505813599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71805477142334</t>
+    <t xml:space="preserve">7.71805572509766</t>
   </si>
   <si>
     <t xml:space="preserve">7.88187074661255</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">7.96143913269043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91931438446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90995454788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0550479888916</t>
+    <t xml:space="preserve">7.91931390762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90995311737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05504703521729</t>
   </si>
   <si>
     <t xml:space="preserve">8.18141937255859</t>
@@ -392,31 +392,31 @@
     <t xml:space="preserve">8.19546031951904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19077968597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3077917098999</t>
+    <t xml:space="preserve">8.19078063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30779266357422</t>
   </si>
   <si>
     <t xml:space="preserve">8.36395835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34991550445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3311939239502</t>
+    <t xml:space="preserve">8.34991645812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33119487762451</t>
   </si>
   <si>
     <t xml:space="preserve">8.29375076293945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15333652496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28907108306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36863899230957</t>
+    <t xml:space="preserve">8.1533374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28906917572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36863803863525</t>
   </si>
   <si>
     <t xml:space="preserve">8.50905132293701</t>
@@ -425,16 +425,16 @@
     <t xml:space="preserve">8.60733985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5137300491333</t>
+    <t xml:space="preserve">8.51373291015625</t>
   </si>
   <si>
     <t xml:space="preserve">8.63542366027832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75711441040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65414524078369</t>
+    <t xml:space="preserve">8.75711345672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65414428710938</t>
   </si>
   <si>
     <t xml:space="preserve">8.78519725799561</t>
@@ -446,43 +446,43 @@
     <t xml:space="preserve">8.92093086242676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84604263305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81795978546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74775314331055</t>
+    <t xml:space="preserve">8.84604358673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81796169281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74775409698486</t>
   </si>
   <si>
     <t xml:space="preserve">8.75243473052979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82264137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7337121963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77115726470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76179599761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65882396697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59329795837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57457828521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56053733825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48564910888672</t>
+    <t xml:space="preserve">8.82264232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73371124267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77115535736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.761794090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6588249206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59329986572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57457733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56053638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4856481552124</t>
   </si>
   <si>
     <t xml:space="preserve">8.54181480407715</t>
@@ -491,46 +491,46 @@
     <t xml:space="preserve">8.53245258331299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66818523406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49969005584717</t>
+    <t xml:space="preserve">8.66818714141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49968910217285</t>
   </si>
   <si>
     <t xml:space="preserve">8.61670112609863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49501037597656</t>
+    <t xml:space="preserve">8.49500846862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.5558557510376</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61202049255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46692657470703</t>
+    <t xml:space="preserve">8.61202144622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46692562103271</t>
   </si>
   <si>
     <t xml:space="preserve">8.52777194976807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56521701812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69158935546875</t>
+    <t xml:space="preserve">8.56521606445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69158744812012</t>
   </si>
   <si>
     <t xml:space="preserve">9.08006572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24856185913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07070541381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01454067230225</t>
+    <t xml:space="preserve">9.24856281280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07070446014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01453876495361</t>
   </si>
   <si>
     <t xml:space="preserve">8.89284801483154</t>
@@ -545,88 +545,88 @@
     <t xml:space="preserve">8.50437068939209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42480278015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40140151977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39671897888184</t>
+    <t xml:space="preserve">8.42480182647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40140056610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39672183990479</t>
   </si>
   <si>
     <t xml:space="preserve">8.5839376449585</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34523391723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46224689483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3826789855957</t>
+    <t xml:space="preserve">8.34523582458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46224594116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38267993927002</t>
   </si>
   <si>
     <t xml:space="preserve">8.47160816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9864559173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09878730773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06134414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51841068267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16269874572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31247234344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4419093132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98484134674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95675754547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38735866546631</t>
+    <t xml:space="preserve">8.98645687103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09878635406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0613431930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51841163635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16269683837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31247329711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44190883636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98484086990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95675802230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38735961914062</t>
   </si>
   <si>
     <t xml:space="preserve">8.41076183319092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44820404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48096942901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37331867218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2329044342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18610000610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3779993057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57925796508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64946556091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72435188293457</t>
+    <t xml:space="preserve">8.44820499420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48096752166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37331771850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23290538787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18610095977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37799835205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57925701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64946365356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72435092926025</t>
   </si>
   <si>
     <t xml:space="preserve">8.67286586761475</t>
@@ -635,103 +635,103 @@
     <t xml:space="preserve">8.74307346343994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71031093597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15495204925537</t>
+    <t xml:space="preserve">8.7103099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15495300292969</t>
   </si>
   <si>
     <t xml:space="preserve">8.96773529052734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14091110229492</t>
+    <t xml:space="preserve">9.14091014862061</t>
   </si>
   <si>
     <t xml:space="preserve">9.26728343963623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33749103546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40769672393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37961387634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29536628723145</t>
+    <t xml:space="preserve">9.33749008178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4076976776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37961483001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29536533355713</t>
   </si>
   <si>
     <t xml:space="preserve">9.3608922958374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44514179229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48258399963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43578052520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3562126159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11282825469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10814666748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15963363647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4638614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81021595001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95999050140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82893562316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91318511962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64171886444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70724487304688</t>
+    <t xml:space="preserve">9.44514083862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48258495330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4357795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35621166229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11282920837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10814762115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15963268280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46386241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81021404266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95999145507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82893657684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91318416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6417179107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70724391937256</t>
   </si>
   <si>
     <t xml:space="preserve">9.71660709381104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66044139862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7914924621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0255155563354</t>
+    <t xml:space="preserve">9.66044044494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79149341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0255165100098</t>
   </si>
   <si>
     <t xml:space="preserve">10.0067939758301</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1846504211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2408170700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2595376968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4280338287354</t>
+    <t xml:space="preserve">10.1846494674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.240816116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2595386505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4280347824097</t>
   </si>
   <si>
     <t xml:space="preserve">10.4748373031616</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">10.3625068664551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3344259262085</t>
+    <t xml:space="preserve">10.3344249725342</t>
   </si>
   <si>
     <t xml:space="preserve">10.577808380127</t>
@@ -752,22 +752,22 @@
     <t xml:space="preserve">10.5029211044312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8118305206299</t>
+    <t xml:space="preserve">10.8118314743042</t>
   </si>
   <si>
     <t xml:space="preserve">10.8867177963257</t>
   </si>
   <si>
-    <t xml:space="preserve">10.718222618103</t>
+    <t xml:space="preserve">10.7182207107544</t>
   </si>
   <si>
     <t xml:space="preserve">10.6526956558228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6433343887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6246128082275</t>
+    <t xml:space="preserve">10.6433334350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6246137619019</t>
   </si>
   <si>
     <t xml:space="preserve">10.7088603973389</t>
@@ -785,31 +785,31 @@
     <t xml:space="preserve">10.9990472793579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1301012039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0926580429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2517938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9616050720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2049875259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1675443649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1488218307495</t>
+    <t xml:space="preserve">11.1301021575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.092658996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2517919540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9616041183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2049894332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1675462722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1488227844238</t>
   </si>
   <si>
     <t xml:space="preserve">11.1862668991089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2798748016357</t>
+    <t xml:space="preserve">11.2798757553101</t>
   </si>
   <si>
     <t xml:space="preserve">11.4296493530273</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">11.410927772522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4577322006226</t>
+    <t xml:space="preserve">11.4577312469482</t>
   </si>
   <si>
     <t xml:space="preserve">11.5801239013672</t>
@@ -827,16 +827,16 @@
     <t xml:space="preserve">11.8249073028564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8625650405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9472970962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9190549850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9284677505493</t>
+    <t xml:space="preserve">11.8625659942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9472980499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9190540313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9284696578979</t>
   </si>
   <si>
     <t xml:space="preserve">11.9378833770752</t>
@@ -848,37 +848,37 @@
     <t xml:space="preserve">12.0602741241455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0979347229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0226154327393</t>
+    <t xml:space="preserve">12.0979337692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0226173400879</t>
   </si>
   <si>
     <t xml:space="preserve">12.2109117507935</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1826658248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2391538619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9096384048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1450071334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4859752655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2976818084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6930999755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7307586669922</t>
+    <t xml:space="preserve">12.1826667785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2391548156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9096393585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1450080871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4859762191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.297682762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6931009292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7307605743408</t>
   </si>
   <si>
     <t xml:space="preserve">11.7684183120728</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">11.5236349105835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4671459197998</t>
+    <t xml:space="preserve">11.4671468734741</t>
   </si>
   <si>
     <t xml:space="preserve">11.3729991912842</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0811443328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.88343334198</t>
+    <t xml:space="preserve">11.0811424255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8834342956543</t>
   </si>
   <si>
     <t xml:space="preserve">10.6951379776001</t>
@@ -914,13 +914,13 @@
     <t xml:space="preserve">10.5633325576782</t>
   </si>
   <si>
-    <t xml:space="preserve">10.610405921936</t>
+    <t xml:space="preserve">10.6104068756104</t>
   </si>
   <si>
     <t xml:space="preserve">10.7422113418579</t>
   </si>
   <si>
-    <t xml:space="preserve">10.911678314209</t>
+    <t xml:space="preserve">10.9116773605347</t>
   </si>
   <si>
     <t xml:space="preserve">10.9022626876831</t>
@@ -929,100 +929,100 @@
     <t xml:space="preserve">10.9493360519409</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1376295089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3541707992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3824148178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3447551727295</t>
+    <t xml:space="preserve">11.1376314163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3541698455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3824138641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3447561264038</t>
   </si>
   <si>
     <t xml:space="preserve">11.4106578826904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2694368362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5048065185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4294881820679</t>
+    <t xml:space="preserve">11.2694387435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5048055648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4294872283936</t>
   </si>
   <si>
     <t xml:space="preserve">11.3353395462036</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2788524627686</t>
+    <t xml:space="preserve">11.2788505554199</t>
   </si>
   <si>
     <t xml:space="preserve">11.2506074905396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1093873977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.034068107605</t>
+    <t xml:space="preserve">11.1093883514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0340690612793</t>
   </si>
   <si>
     <t xml:space="preserve">10.9210939407349</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6668930053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8363599777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7892866134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1941194534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1658754348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0717277526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1282148361206</t>
+    <t xml:space="preserve">10.6668949127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8363609313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.78928565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1941204071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1658744812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0717296600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1282167434692</t>
   </si>
   <si>
     <t xml:space="preserve">11.3165121078491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3259239196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2411937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0623121261597</t>
+    <t xml:space="preserve">11.3259267807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2411918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.062313079834</t>
   </si>
   <si>
     <t xml:space="preserve">11.0905570983887</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1752901077271</t>
+    <t xml:space="preserve">11.1752910614014</t>
   </si>
   <si>
     <t xml:space="preserve">11.4389028549194</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7213459014893</t>
+    <t xml:space="preserve">11.7213449478149</t>
   </si>
   <si>
     <t xml:space="preserve">11.8154926300049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9849557876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.013201713562</t>
+    <t xml:space="preserve">11.984956741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0132007598877</t>
   </si>
   <si>
     <t xml:space="preserve">11.9567136764526</t>
@@ -1031,34 +1031,34 @@
     <t xml:space="preserve">12.0508604049683</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0414447784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0791044235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9755430221558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8343210220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2203254699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1544237136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1073484420776</t>
+    <t xml:space="preserve">12.0414457321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0791053771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9755420684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.834321975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2203245162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1544227600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.107349395752</t>
   </si>
   <si>
     <t xml:space="preserve">12.4839382171631</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5215978622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.643988609314</t>
+    <t xml:space="preserve">12.5215969085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6439895629883</t>
   </si>
   <si>
     <t xml:space="preserve">12.7852096557617</t>
@@ -1073,13 +1073,13 @@
     <t xml:space="preserve">12.8040399551392</t>
   </si>
   <si>
-    <t xml:space="preserve">12.192081451416</t>
+    <t xml:space="preserve">12.1920804977417</t>
   </si>
   <si>
     <t xml:space="preserve">11.7872476577759</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8531503677368</t>
+    <t xml:space="preserve">11.8531513214111</t>
   </si>
   <si>
     <t xml:space="preserve">12.0320310592651</t>
@@ -1091,16 +1091,16 @@
     <t xml:space="preserve">12.2768135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9002256393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4483165740967</t>
+    <t xml:space="preserve">11.9002237319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.448317527771</t>
   </si>
   <si>
     <t xml:space="preserve">11.5612945556641</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4012451171875</t>
+    <t xml:space="preserve">11.4012432098389</t>
   </si>
   <si>
     <t xml:space="preserve">11.6742706298828</t>
@@ -1118,88 +1118,88 @@
     <t xml:space="preserve">12.2014970779419</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1355934143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3615474700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3333015441895</t>
+    <t xml:space="preserve">12.135594367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3615484237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3333044052124</t>
   </si>
   <si>
     <t xml:space="preserve">12.1638374328613</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7401742935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1261777877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5404262542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5498418807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5027675628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6345729827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1335535049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1241388320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0864810943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9546756744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4254121780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4630708694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5383882522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5572166442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6042928695679</t>
+    <t xml:space="preserve">11.7401752471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1261787414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5404243469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.549840927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5027666091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6345748901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1335544586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1241397857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.086480140686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9546747207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4254112243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4630718231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5383892059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5572185516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6042900085449</t>
   </si>
   <si>
     <t xml:space="preserve">13.5101442337036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2559471130371</t>
+    <t xml:space="preserve">13.2559461593628</t>
   </si>
   <si>
     <t xml:space="preserve">13.4724855422974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3030204772949</t>
+    <t xml:space="preserve">13.3030195236206</t>
   </si>
   <si>
     <t xml:space="preserve">12.973503112793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6157445907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4086198806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3803758621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.46510887146</t>
+    <t xml:space="preserve">12.615743637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4086208343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3803768157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4651069641113</t>
   </si>
   <si>
     <t xml:space="preserve">12.5121822357178</t>
@@ -1208,28 +1208,28 @@
     <t xml:space="preserve">12.822868347168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.879358291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.851113319397</t>
+    <t xml:space="preserve">12.8793573379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8511123657227</t>
   </si>
   <si>
     <t xml:space="preserve">12.5969152450562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.286229133606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2579832077026</t>
+    <t xml:space="preserve">12.2862281799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2579851150513</t>
   </si>
   <si>
     <t xml:space="preserve">12.7287216186523</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0394077301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0958957672119</t>
+    <t xml:space="preserve">13.0394086837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0958948135376</t>
   </si>
   <si>
     <t xml:space="preserve">13.2653617858887</t>
@@ -1238,52 +1238,52 @@
     <t xml:space="preserve">13.4065818786621</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3312644958496</t>
+    <t xml:space="preserve">13.3312635421753</t>
   </si>
   <si>
     <t xml:space="preserve">13.3218488693237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1617975234985</t>
+    <t xml:space="preserve">13.1617984771729</t>
   </si>
   <si>
     <t xml:space="preserve">13.3406791687012</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2465314865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8887720108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8605270385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.293604850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5666313171387</t>
+    <t xml:space="preserve">13.2465333938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8887710571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8605279922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2936058044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.566632270813</t>
   </si>
   <si>
     <t xml:space="preserve">13.6419506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3124351501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7925863265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9997119903564</t>
+    <t xml:space="preserve">13.3124361038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7925853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9997110366821</t>
   </si>
   <si>
     <t xml:space="preserve">14.1409311294556</t>
   </si>
   <si>
-    <t xml:space="preserve">14.395131111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3009824752808</t>
+    <t xml:space="preserve">14.3951292037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3009815216064</t>
   </si>
   <si>
     <t xml:space="preserve">14.5645942687988</t>
@@ -1298,10 +1298,10 @@
     <t xml:space="preserve">14.9129400253296</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8564510345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1106491088867</t>
+    <t xml:space="preserve">14.8564500808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1106481552124</t>
   </si>
   <si>
     <t xml:space="preserve">14.969428062439</t>
@@ -1310,13 +1310,13 @@
     <t xml:space="preserve">14.997673034668</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0353317260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.903525352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8941097259521</t>
+    <t xml:space="preserve">15.0353326797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9035243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8941087722778</t>
   </si>
   <si>
     <t xml:space="preserve">14.7152299880981</t>
@@ -1325,10 +1325,10 @@
     <t xml:space="preserve">14.5928392410278</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1671380996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.270697593689</t>
+    <t xml:space="preserve">15.1671371459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2706985473633</t>
   </si>
   <si>
     <t xml:space="preserve">15.2424554824829</t>
@@ -1337,28 +1337,28 @@
     <t xml:space="preserve">15.2518711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4401655197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3930912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5531425476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6567029953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4213361740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0165004730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3460168838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8185262680054</t>
+    <t xml:space="preserve">15.44016456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3930892944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5531415939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.656702041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4213352203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0165014266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3460159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8185272216797</t>
   </si>
   <si>
     <t xml:space="preserve">14.6668338775635</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">14.3444862365723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6099500656128</t>
+    <t xml:space="preserve">14.6099491119385</t>
   </si>
   <si>
     <t xml:space="preserve">14.7332000732422</t>
@@ -1379,40 +1379,40 @@
     <t xml:space="preserve">13.9273290634155</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4013719558716</t>
+    <t xml:space="preserve">14.4013710021973</t>
   </si>
   <si>
     <t xml:space="preserve">14.6194305419922</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6289119720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1882810592651</t>
+    <t xml:space="preserve">14.6289110183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1882801055908</t>
   </si>
   <si>
     <t xml:space="preserve">15.4916658401489</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1173992156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4587097167969</t>
+    <t xml:space="preserve">16.1174011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4587078094482</t>
   </si>
   <si>
     <t xml:space="preserve">16.1553249359131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1648044586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2027282714844</t>
+    <t xml:space="preserve">16.1648025512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2027263641357</t>
   </si>
   <si>
     <t xml:space="preserve">16.2122077941895</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3259792327881</t>
+    <t xml:space="preserve">16.3259773254395</t>
   </si>
   <si>
     <t xml:space="preserve">16.1079196929932</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">16.5250759124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7241725921631</t>
+    <t xml:space="preserve">16.7241706848145</t>
   </si>
   <si>
     <t xml:space="preserve">16.6672878265381</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">16.3070182800293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596130371094</t>
+    <t xml:space="preserve">16.2596111297607</t>
   </si>
   <si>
     <t xml:space="preserve">16.6767692565918</t>
@@ -1445,13 +1445,13 @@
     <t xml:space="preserve">16.8379421234131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.885347366333</t>
+    <t xml:space="preserve">16.8853454589844</t>
   </si>
   <si>
     <t xml:space="preserve">17.0465221405029</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9232711791992</t>
+    <t xml:space="preserve">16.9232692718506</t>
   </si>
   <si>
     <t xml:space="preserve">16.771577835083</t>
@@ -1463,19 +1463,19 @@
     <t xml:space="preserve">16.4492301940918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2216911315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4018268585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5535182952881</t>
+    <t xml:space="preserve">16.2216892242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4018249511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5535202026367</t>
   </si>
   <si>
     <t xml:space="preserve">16.3639011383057</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5155944824219</t>
+    <t xml:space="preserve">16.5155963897705</t>
   </si>
   <si>
     <t xml:space="preserve">17.1034088134766</t>
@@ -1484,22 +1484,22 @@
     <t xml:space="preserve">17.5395259857178</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9472026824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4447135925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0799293518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1652565002441</t>
+    <t xml:space="preserve">17.9471988677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4447154998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0799331665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1652584075928</t>
   </si>
   <si>
     <t xml:space="preserve">18.7151470184326</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1368141174316</t>
+    <t xml:space="preserve">18.1368160247803</t>
   </si>
   <si>
     <t xml:space="preserve">18.4117584228516</t>
@@ -1511,19 +1511,19 @@
     <t xml:space="preserve">18.0704498291016</t>
   </si>
   <si>
-    <t xml:space="preserve">17.861873626709</t>
+    <t xml:space="preserve">17.8618717193604</t>
   </si>
   <si>
     <t xml:space="preserve">17.6343326568604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7860260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7575836181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2979907989502</t>
+    <t xml:space="preserve">17.7860240936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7575817108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2979888916016</t>
   </si>
   <si>
     <t xml:space="preserve">18.3738346099854</t>
@@ -1532,40 +1532,40 @@
     <t xml:space="preserve">18.203182220459</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0325241088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1083736419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2126598358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0609683990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9377193450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0040836334229</t>
+    <t xml:space="preserve">18.0325260162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1083755493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2126617431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0609703063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9377174377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0040817260742</t>
   </si>
   <si>
     <t xml:space="preserve">17.5774478912354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3927955627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8334312438965</t>
+    <t xml:space="preserve">18.3927974700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8334293365479</t>
   </si>
   <si>
     <t xml:space="preserve">18.0135631561279</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7435874938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3408794403076</t>
+    <t xml:space="preserve">18.7435894012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3408813476562</t>
   </si>
   <si>
     <t xml:space="preserve">19.41672706604</t>
@@ -1574,37 +1574,37 @@
     <t xml:space="preserve">19.3788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1891860961914</t>
+    <t xml:space="preserve">19.18918800354</t>
   </si>
   <si>
     <t xml:space="preserve">19.056453704834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7246265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4496822357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5255279541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.772029876709</t>
+    <t xml:space="preserve">18.7246284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4496803283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5255298614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7720336914062</t>
   </si>
   <si>
     <t xml:space="preserve">18.9616451263428</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6867008209229</t>
+    <t xml:space="preserve">18.6867046356201</t>
   </si>
   <si>
     <t xml:space="preserve">18.146297454834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5065689086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0420055389404</t>
+    <t xml:space="preserve">18.5065670013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0420093536377</t>
   </si>
   <si>
     <t xml:space="preserve">17.3025035858154</t>
@@ -1613,40 +1613,40 @@
     <t xml:space="preserve">16.5629997253418</t>
   </si>
   <si>
-    <t xml:space="preserve">15.453742980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5864753723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6718034744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0081443786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4252996444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4632225036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8045320510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7286863327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9512586593628</t>
+    <t xml:space="preserve">15.4537410736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5864763259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.671802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0081434249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4253005981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4632234573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8045330047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7286853790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9512596130371</t>
   </si>
   <si>
     <t xml:space="preserve">15.0745096206665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9986629486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9797029495239</t>
+    <t xml:space="preserve">14.9986619949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9797010421753</t>
   </si>
   <si>
     <t xml:space="preserve">15.0176248550415</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">14.8469696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6573534011841</t>
+    <t xml:space="preserve">14.6573543548584</t>
   </si>
   <si>
     <t xml:space="preserve">14.7047576904297</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">15.0555477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7900857925415</t>
+    <t xml:space="preserve">14.7900848388672</t>
   </si>
   <si>
     <t xml:space="preserve">13.8135604858398</t>
@@ -1682,13 +1682,13 @@
     <t xml:space="preserve">13.728232383728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1309404373169</t>
+    <t xml:space="preserve">13.1309423446655</t>
   </si>
   <si>
     <t xml:space="preserve">13.0835371017456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3869228363037</t>
+    <t xml:space="preserve">13.386923789978</t>
   </si>
   <si>
     <t xml:space="preserve">13.263671875</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">13.3964033126831</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6523857116699</t>
+    <t xml:space="preserve">13.6523866653442</t>
   </si>
   <si>
     <t xml:space="preserve">13.4912118911743</t>
@@ -1709,13 +1709,13 @@
     <t xml:space="preserve">13.8704452514648</t>
   </si>
   <si>
-    <t xml:space="preserve">14.012656211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4961805343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2212362289429</t>
+    <t xml:space="preserve">14.0126581192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4961795806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2212352752686</t>
   </si>
   <si>
     <t xml:space="preserve">14.1643495559692</t>
@@ -1724,10 +1724,10 @@
     <t xml:space="preserve">14.3065633773804</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3350057601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7945976257324</t>
+    <t xml:space="preserve">14.3350048065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7945995330811</t>
   </si>
   <si>
     <t xml:space="preserve">13.7377138137817</t>
@@ -1736,43 +1736,43 @@
     <t xml:space="preserve">13.5955009460449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7566747665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.898886680603</t>
+    <t xml:space="preserve">13.7566766738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8988876342773</t>
   </si>
   <si>
     <t xml:space="preserve">13.9462919235229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4203329086304</t>
+    <t xml:space="preserve">14.4203338623047</t>
   </si>
   <si>
     <t xml:space="preserve">13.7756376266479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7232656478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.320556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1878261566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7471942901611</t>
+    <t xml:space="preserve">12.7232666015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3205575942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1878252029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7471933364868</t>
   </si>
   <si>
     <t xml:space="preserve">14.0695428848267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8374891281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2546463012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8848943710327</t>
+    <t xml:space="preserve">14.8374881744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2546443939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8848934173584</t>
   </si>
   <si>
     <t xml:space="preserve">15.0839910507202</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">15.1503553390503</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3115291595459</t>
+    <t xml:space="preserve">15.3115301132202</t>
   </si>
   <si>
     <t xml:space="preserve">15.3589353561401</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">15.2925691604614</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1408748626709</t>
+    <t xml:space="preserve">15.1408767700195</t>
   </si>
   <si>
     <t xml:space="preserve">15.0271053314209</t>
@@ -1805,58 +1805,58 @@
     <t xml:space="preserve">14.8280086517334</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8659315109253</t>
+    <t xml:space="preserve">14.8659324645996</t>
   </si>
   <si>
     <t xml:space="preserve">14.9417791366577</t>
   </si>
   <si>
-    <t xml:space="preserve">15.614914894104</t>
+    <t xml:space="preserve">15.6149158477783</t>
   </si>
   <si>
     <t xml:space="preserve">15.7097244262695</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0650291442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2167224884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5485525131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4347820281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.396858215332</t>
+    <t xml:space="preserve">15.0650300979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.216721534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5485506057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4347801208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3968572616577</t>
   </si>
   <si>
     <t xml:space="preserve">14.7806043624878</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9038562774658</t>
+    <t xml:space="preserve">14.9038553237915</t>
   </si>
   <si>
     <t xml:space="preserve">15.2262020111084</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1977615356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.444263458252</t>
+    <t xml:space="preserve">15.1977605819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4442625045776</t>
   </si>
   <si>
     <t xml:space="preserve">15.3684148788452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5106287002563</t>
+    <t xml:space="preserve">15.510627746582</t>
   </si>
   <si>
     <t xml:space="preserve">15.7381677627563</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4302673339844</t>
+    <t xml:space="preserve">16.4302654266357</t>
   </si>
   <si>
     <t xml:space="preserve">15.9657077789307</t>
@@ -1865,19 +1865,19 @@
     <t xml:space="preserve">15.2641267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7855710983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6862506866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8474273681641</t>
+    <t xml:space="preserve">15.785572052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6862487792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8474254608154</t>
   </si>
   <si>
     <t xml:space="preserve">16.4966335296631</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1932468414307</t>
+    <t xml:space="preserve">16.1932487487793</t>
   </si>
   <si>
     <t xml:space="preserve">16.2311706542969</t>
@@ -1886,19 +1886,19 @@
     <t xml:space="preserve">16.7526168823242</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4207878112793</t>
+    <t xml:space="preserve">16.420783996582</t>
   </si>
   <si>
     <t xml:space="preserve">16.8095016479492</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7336559295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8948307037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8663864135742</t>
+    <t xml:space="preserve">16.7336540222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8948287963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8663845062256</t>
   </si>
   <si>
     <t xml:space="preserve">16.2501335144043</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">15.8993425369263</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8898620605469</t>
+    <t xml:space="preserve">15.8898601531982</t>
   </si>
   <si>
     <t xml:space="preserve">15.9277820587158</t>
@@ -1916,25 +1916,25 @@
     <t xml:space="preserve">15.851936340332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3544216156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.240650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9183053970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5016040802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6627731323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0894107818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3119850158691</t>
+    <t xml:space="preserve">16.354419708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2406482696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9183034896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5016002655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6627750396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.089412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3119831085205</t>
   </si>
   <si>
     <t xml:space="preserve">17.2835426330566</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">18.5743827819824</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8704261779785</t>
+    <t xml:space="preserve">18.8704299926758</t>
   </si>
   <si>
     <t xml:space="preserve">19.596212387085</t>
@@ -1958,22 +1958,22 @@
     <t xml:space="preserve">19.5007133483887</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9277248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9468250274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9850234985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5934829711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7080783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9659252166748</t>
+    <t xml:space="preserve">18.9277267456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9468231201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9850215911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5934810638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.708080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9659271240234</t>
   </si>
   <si>
     <t xml:space="preserve">19.0327739715576</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">19.2333221435547</t>
   </si>
   <si>
-    <t xml:space="preserve">19.386116027832</t>
+    <t xml:space="preserve">19.3861179351807</t>
   </si>
   <si>
     <t xml:space="preserve">19.0900707244873</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">19.1951198577881</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1187210083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.252420425415</t>
+    <t xml:space="preserve">19.1187229156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2524185180664</t>
   </si>
   <si>
     <t xml:space="preserve">19.9018077850342</t>
@@ -2003,10 +2003,10 @@
     <t xml:space="preserve">20.1501007080078</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2646999359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5893936157227</t>
+    <t xml:space="preserve">20.2646980285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.589391708374</t>
   </si>
   <si>
     <t xml:space="preserve">20.5511932373047</t>
@@ -2015,40 +2015,40 @@
     <t xml:space="preserve">20.799488067627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9591064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8445072174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4816131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3097171783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6344127655029</t>
+    <t xml:space="preserve">19.9591045379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8445091247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4816150665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3097190856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6344108581543</t>
   </si>
   <si>
     <t xml:space="preserve">19.6726112365723</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0928020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9400043487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6535110473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.558012008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7299118041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3028984069824</t>
+    <t xml:space="preserve">20.0928039550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9400062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6535091400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5580139160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.729907989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3029003143311</t>
   </si>
   <si>
     <t xml:space="preserve">20.2837982177734</t>
@@ -2057,10 +2057,10 @@
     <t xml:space="preserve">20.2264995574951</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7039909362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6848926544189</t>
+    <t xml:space="preserve">20.7039890289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6848907470703</t>
   </si>
   <si>
     <t xml:space="preserve">20.4174976348877</t>
@@ -2072,13 +2072,13 @@
     <t xml:space="preserve">20.1310024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1883010864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2769794464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1814804077148</t>
+    <t xml:space="preserve">20.1882991790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2769813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1814823150635</t>
   </si>
   <si>
     <t xml:space="preserve">20.436595916748</t>
@@ -2087,10 +2087,10 @@
     <t xml:space="preserve">20.0164031982422</t>
   </si>
   <si>
-    <t xml:space="preserve">20.570291519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9904861450195</t>
+    <t xml:space="preserve">20.5702953338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9904842376709</t>
   </si>
   <si>
     <t xml:space="preserve">21.1050815582275</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">21.1623821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2578811645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0286827087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2960796356201</t>
+    <t xml:space="preserve">21.2578792572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0286846160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2960758209229</t>
   </si>
   <si>
     <t xml:space="preserve">21.849967956543</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">22.4802570343018</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5566520690918</t>
+    <t xml:space="preserve">22.5566558837891</t>
   </si>
   <si>
     <t xml:space="preserve">22.5184574127197</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">22.0982608795166</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2510623931885</t>
+    <t xml:space="preserve">22.2510585784912</t>
   </si>
   <si>
     <t xml:space="preserve">21.9645671844482</t>
@@ -2135,10 +2135,10 @@
     <t xml:space="preserve">22.3083610534668</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5948543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7476501464844</t>
+    <t xml:space="preserve">22.5948524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7476482391357</t>
   </si>
   <si>
     <t xml:space="preserve">22.8049488067627</t>
@@ -2153,19 +2153,19 @@
     <t xml:space="preserve">21.3533782958984</t>
   </si>
   <si>
-    <t xml:space="preserve">20.474796295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4556941986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1241817474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7803897857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8758869171143</t>
+    <t xml:space="preserve">20.4747943878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.455696105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1241836547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.780387878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8758888244629</t>
   </si>
   <si>
     <t xml:space="preserve">21.0859832763672</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">21.2196788787842</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3724765777588</t>
+    <t xml:space="preserve">21.3724784851074</t>
   </si>
   <si>
     <t xml:space="preserve">21.6016731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6780700683594</t>
+    <t xml:space="preserve">21.678071975708</t>
   </si>
   <si>
     <t xml:space="preserve">21.4870758056641</t>
@@ -2204,10 +2204,10 @@
     <t xml:space="preserve">20.4938945770264</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8567886352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3792953491211</t>
+    <t xml:space="preserve">20.8567905426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3792972564697</t>
   </si>
   <si>
     <t xml:space="preserve">20.8949851989746</t>
@@ -2222,73 +2222,73 @@
     <t xml:space="preserve">20.3410968780518</t>
   </si>
   <si>
-    <t xml:space="preserve">21.830867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0218658447266</t>
+    <t xml:space="preserve">21.8308696746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0218639373779</t>
   </si>
   <si>
     <t xml:space="preserve">22.5375556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6521511077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.015043258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4543361663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7217311859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9127292633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5689334869385</t>
+    <t xml:space="preserve">22.6521492004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0150470733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4543380737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7217330932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.912727355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5689353942871</t>
   </si>
   <si>
     <t xml:space="preserve">24.084623336792</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7981281280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8745307922363</t>
+    <t xml:space="preserve">23.7981300354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">23.970027923584</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3711204528809</t>
+    <t xml:space="preserve">24.3711185455322</t>
   </si>
   <si>
     <t xml:space="preserve">24.8677101135254</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0969047546387</t>
+    <t xml:space="preserve">25.09690284729</t>
   </si>
   <si>
     <t xml:space="preserve">25.3642978668213</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3329200744629</t>
+    <t xml:space="preserve">24.3329181671143</t>
   </si>
   <si>
     <t xml:space="preserve">24.9823055267334</t>
   </si>
   <si>
-    <t xml:space="preserve">25.287899017334</t>
+    <t xml:space="preserve">25.2878971099854</t>
   </si>
   <si>
     <t xml:space="preserve">24.9250087738037</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6194114685059</t>
+    <t xml:space="preserve">25.0205097198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6194152832031</t>
   </si>
   <si>
     <t xml:space="preserve">24.9441070556641</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">24.5430145263672</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3520164489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6576156616211</t>
+    <t xml:space="preserve">24.3520183563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6576137542725</t>
   </si>
   <si>
     <t xml:space="preserve">24.6767120361328</t>
@@ -2318,13 +2318,13 @@
     <t xml:space="preserve">24.4857158660889</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5621147155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5812149047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6958141326904</t>
+    <t xml:space="preserve">24.5621166229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5812129974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6958122253418</t>
   </si>
   <si>
     <t xml:space="preserve">25.3070011138916</t>
@@ -2342,28 +2342,28 @@
     <t xml:space="preserve">25.2115020751953</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7653923034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6125926971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5552940368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1542015075684</t>
+    <t xml:space="preserve">25.7653903961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6125946044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5552959442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.154203414917</t>
   </si>
   <si>
     <t xml:space="preserve">25.8226909637451</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7722091674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5239143371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9059066772461</t>
+    <t xml:space="preserve">24.7722110748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5239162445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9059085845947</t>
   </si>
   <si>
     <t xml:space="preserve">25.6698932647705</t>
@@ -2375,13 +2375,13 @@
     <t xml:space="preserve">26.2810802459717</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3956775665283</t>
+    <t xml:space="preserve">26.3956756591797</t>
   </si>
   <si>
     <t xml:space="preserve">27.1405620574951</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2169647216797</t>
+    <t xml:space="preserve">27.2169628143311</t>
   </si>
   <si>
     <t xml:space="preserve">27.5225563049316</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">27.694450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8281517028809</t>
+    <t xml:space="preserve">27.8281497955322</t>
   </si>
   <si>
     <t xml:space="preserve">28.1910438537598</t>
@@ -2408,28 +2408,28 @@
     <t xml:space="preserve">25.9754867553711</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2306003570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6003170013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6071319580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4666175842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4352340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8254070281982</t>
+    <t xml:space="preserve">25.2306022644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6003150939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6071338653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4666156768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4352378845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8254089355469</t>
   </si>
   <si>
     <t xml:space="preserve">19.3479175567627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5852918624878</t>
+    <t xml:space="preserve">15.5852909088135</t>
   </si>
   <si>
     <t xml:space="preserve">17.323356628418</t>
@@ -2438,22 +2438,22 @@
     <t xml:space="preserve">15.7285385131836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1200790405273</t>
+    <t xml:space="preserve">16.120080947876</t>
   </si>
   <si>
     <t xml:space="preserve">16.9031658172607</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5239028930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7435512542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1350917816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8322257995605</t>
+    <t xml:space="preserve">17.523904800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7435493469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1350898742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8322277069092</t>
   </si>
   <si>
     <t xml:space="preserve">18.1446399688721</t>
@@ -2477,16 +2477,16 @@
     <t xml:space="preserve">16.8076667785645</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6480503082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7844772338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4311351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4454593658447</t>
+    <t xml:space="preserve">17.6480522155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7844791412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4311332702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4454612731934</t>
   </si>
   <si>
     <t xml:space="preserve">18.7653789520264</t>
@@ -2495,52 +2495,52 @@
     <t xml:space="preserve">17.9536437988281</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8663387298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2715187072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8465557098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0068531036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2456016540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.987756729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9686527252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7681083679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6753425598145</t>
+    <t xml:space="preserve">20.866340637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.271520614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8465538024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0068550109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2455978393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9877548217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9686546325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7681102752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6753406524658</t>
   </si>
   <si>
     <t xml:space="preserve">21.7640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3820266723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3370094299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7926712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0191345214844</t>
+    <t xml:space="preserve">21.3820285797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.337007522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7926692962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.019136428833</t>
   </si>
   <si>
     <t xml:space="preserve">21.4297771453857</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8595161437988</t>
+    <t xml:space="preserve">21.8595180511475</t>
   </si>
   <si>
     <t xml:space="preserve">20.9522857666016</t>
@@ -2552,13 +2552,13 @@
     <t xml:space="preserve">21.658971786499</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0341472625732</t>
+    <t xml:space="preserve">23.0341453552246</t>
   </si>
   <si>
     <t xml:space="preserve">23.1391906738281</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2797107696533</t>
+    <t xml:space="preserve">22.2797088623047</t>
   </si>
   <si>
     <t xml:space="preserve">23.5020866394043</t>
@@ -2567,19 +2567,19 @@
     <t xml:space="preserve">23.8267803192139</t>
   </si>
   <si>
-    <t xml:space="preserve">23.521183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8458786010742</t>
+    <t xml:space="preserve">23.5211849212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8458766937256</t>
   </si>
   <si>
     <t xml:space="preserve">23.8172302246094</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3588390350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6903514862061</t>
+    <t xml:space="preserve">23.3588371276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6903495788574</t>
   </si>
   <si>
     <t xml:space="preserve">22.6330528259277</t>
@@ -2588,55 +2588,55 @@
     <t xml:space="preserve">21.8881683349609</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0696125030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6999015808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9386463165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3015384674072</t>
+    <t xml:space="preserve">22.0696144104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6998996734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.938648223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3015365600586</t>
   </si>
   <si>
     <t xml:space="preserve">22.6808013916016</t>
   </si>
   <si>
-    <t xml:space="preserve">22.709451675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1487426757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4638862609863</t>
+    <t xml:space="preserve">22.7094535827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1487407684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.463888168335</t>
   </si>
   <si>
     <t xml:space="preserve">22.4229564666748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4611549377441</t>
+    <t xml:space="preserve">22.4611587524414</t>
   </si>
   <si>
     <t xml:space="preserve">22.6426010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7381000518799</t>
+    <t xml:space="preserve">22.7380981445312</t>
   </si>
   <si>
     <t xml:space="preserve">23.272891998291</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2442398071289</t>
+    <t xml:space="preserve">23.2442378997803</t>
   </si>
   <si>
     <t xml:space="preserve">23.5402851104736</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7408294677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8363265991211</t>
+    <t xml:space="preserve">23.7408313751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8363285064697</t>
   </si>
   <si>
     <t xml:space="preserve">23.7121810913086</t>
@@ -2645,13 +2645,13 @@
     <t xml:space="preserve">23.7599296569824</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1610202789307</t>
+    <t xml:space="preserve">24.1610221862793</t>
   </si>
   <si>
     <t xml:space="preserve">24.3233680725098</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7340106964111</t>
+    <t xml:space="preserve">24.7340087890625</t>
   </si>
   <si>
     <t xml:space="preserve">25.2783508300781</t>
@@ -2660,34 +2660,34 @@
     <t xml:space="preserve">25.0682563781738</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0587043762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7531108856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.135103225708</t>
+    <t xml:space="preserve">25.0587062835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7531127929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1351013183594</t>
   </si>
   <si>
     <t xml:space="preserve">26.5580253601074</t>
   </si>
   <si>
-    <t xml:space="preserve">26.510274887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6467018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2292404174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.503454208374</t>
+    <t xml:space="preserve">26.5102767944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6467037200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2292423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5034561157227</t>
   </si>
   <si>
     <t xml:space="preserve">27.5894031524658</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1596641540527</t>
+    <t xml:space="preserve">27.1596660614014</t>
   </si>
   <si>
     <t xml:space="preserve">27.5512046813965</t>
@@ -2699,10 +2699,10 @@
     <t xml:space="preserve">27.0355129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3793087005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2265110015869</t>
+    <t xml:space="preserve">27.3793106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2265129089355</t>
   </si>
   <si>
     <t xml:space="preserve">27.0546169281006</t>
@@ -2711,19 +2711,19 @@
     <t xml:space="preserve">27.2838115692139</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5675754547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0450668334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7108211517334</t>
+    <t xml:space="preserve">26.5675735473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0450630187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.710823059082</t>
   </si>
   <si>
     <t xml:space="preserve">26.5007266998291</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4529762268066</t>
+    <t xml:space="preserve">26.4529800415039</t>
   </si>
   <si>
     <t xml:space="preserve">26.6630744934082</t>
@@ -2735,25 +2735,25 @@
     <t xml:space="preserve">26.2619800567627</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4625263214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5989551544189</t>
+    <t xml:space="preserve">26.4625282287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5989513397217</t>
   </si>
   <si>
     <t xml:space="preserve">26.6726226806641</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7585716247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3888607025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4461574554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1814918518066</t>
+    <t xml:space="preserve">26.7585735321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.388858795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4461555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1814937591553</t>
   </si>
   <si>
     <t xml:space="preserve">28.3533935546875</t>
@@ -2762,16 +2762,16 @@
     <t xml:space="preserve">28.5061874389648</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9932270050049</t>
+    <t xml:space="preserve">28.9932250976562</t>
   </si>
   <si>
     <t xml:space="preserve">28.7926807403564</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6971836090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.57985496521</t>
+    <t xml:space="preserve">28.6971817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5798530578613</t>
   </si>
   <si>
     <t xml:space="preserve">27.6562538146973</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">27.4748077392578</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6849021911621</t>
+    <t xml:space="preserve">27.6849040985107</t>
   </si>
   <si>
     <t xml:space="preserve">29.3847694396973</t>
@@ -2792,40 +2792,40 @@
     <t xml:space="preserve">29.1746711730957</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4802665710449</t>
+    <t xml:space="preserve">29.4802684783936</t>
   </si>
   <si>
     <t xml:space="preserve">29.8336124420166</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0246086120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1651229858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3274688720703</t>
+    <t xml:space="preserve">30.0246067047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1651248931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3274707794189</t>
   </si>
   <si>
     <t xml:space="preserve">29.8049602508545</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4734477996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9891357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7503910064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5402984619141</t>
+    <t xml:space="preserve">30.473445892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9891376495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7503929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5402965545654</t>
   </si>
   <si>
     <t xml:space="preserve">30.9222888946533</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7408409118652</t>
+    <t xml:space="preserve">30.7408390045166</t>
   </si>
   <si>
     <t xml:space="preserve">30.9318370819092</t>
@@ -2834,10 +2834,10 @@
     <t xml:space="preserve">30.7217407226562</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6835460662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8172397613525</t>
+    <t xml:space="preserve">30.6835441589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8172435760498</t>
   </si>
   <si>
     <t xml:space="preserve">30.4829978942871</t>
@@ -2852,49 +2852,49 @@
     <t xml:space="preserve">29.2128715515137</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9031887054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9918613433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8991012573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6535377502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3097457885742</t>
+    <t xml:space="preserve">30.9031925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9918651580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.899097442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6535415649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.309741973877</t>
   </si>
   <si>
     <t xml:space="preserve">32.4693603515625</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3288421630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5580368041992</t>
+    <t xml:space="preserve">33.3288459777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5580406188965</t>
   </si>
   <si>
     <t xml:space="preserve">34.1310272216797</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4338912963867</t>
+    <t xml:space="preserve">33.4338874816895</t>
   </si>
   <si>
     <t xml:space="preserve">34.4461708068848</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8158798217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.930477142334</t>
+    <t xml:space="preserve">33.8158836364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9304809570312</t>
   </si>
   <si>
     <t xml:space="preserve">32.6603546142578</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6699028015137</t>
+    <t xml:space="preserve">32.6699066162109</t>
   </si>
   <si>
     <t xml:space="preserve">32.8513526916504</t>
@@ -2906,28 +2906,28 @@
     <t xml:space="preserve">31.6098728179932</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9727687835693</t>
+    <t xml:space="preserve">31.9727649688721</t>
   </si>
   <si>
     <t xml:space="preserve">32.7367553710938</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0587158203125</t>
+    <t xml:space="preserve">32.0587196350098</t>
   </si>
   <si>
     <t xml:space="preserve">31.2565307617188</t>
   </si>
   <si>
-    <t xml:space="preserve">30.884090423584</t>
+    <t xml:space="preserve">30.8840885162354</t>
   </si>
   <si>
     <t xml:space="preserve">31.017786026001</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1323852539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8745422363281</t>
+    <t xml:space="preserve">31.1323833465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8745403289795</t>
   </si>
   <si>
     <t xml:space="preserve">31.0846347808838</t>
@@ -2936,10 +2936,10 @@
     <t xml:space="preserve">31.6194248199463</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0969161987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3615779876709</t>
+    <t xml:space="preserve">32.0969123840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3615837097168</t>
   </si>
   <si>
     <t xml:space="preserve">32.1542129516602</t>
@@ -2951,22 +2951,22 @@
     <t xml:space="preserve">32.4216117858887</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6958236694336</t>
+    <t xml:space="preserve">31.695821762085</t>
   </si>
   <si>
     <t xml:space="preserve">32.2115097045898</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7435722351074</t>
+    <t xml:space="preserve">31.7435760498047</t>
   </si>
   <si>
     <t xml:space="preserve">32.2783622741699</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5075531005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4120597839355</t>
+    <t xml:space="preserve">32.5075569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4120559692383</t>
   </si>
   <si>
     <t xml:space="preserve">32.0491638183594</t>
@@ -2975,37 +2975,37 @@
     <t xml:space="preserve">31.5334758758545</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2087802886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3165588378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.163761138916</t>
+    <t xml:space="preserve">31.2087821960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3165626525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1637649536133</t>
   </si>
   <si>
     <t xml:space="preserve">32.1064643859863</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3834075927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6221504211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6508026123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8036041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5839614868164</t>
+    <t xml:space="preserve">32.3834037780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6221580505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.650806427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8036003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5839538574219</t>
   </si>
   <si>
     <t xml:space="preserve">32.3547630310059</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0682678222656</t>
+    <t xml:space="preserve">32.0682640075684</t>
   </si>
   <si>
     <t xml:space="preserve">32.0396194458008</t>
@@ -3014,22 +3014,22 @@
     <t xml:space="preserve">32.5648536682129</t>
   </si>
   <si>
-    <t xml:space="preserve">32.326114654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9250164031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.042350769043</t>
+    <t xml:space="preserve">32.3261108398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9250240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0423469543457</t>
   </si>
   <si>
     <t xml:space="preserve">33.7967834472656</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5989646911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4843711853027</t>
+    <t xml:space="preserve">34.5989608764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4843673706055</t>
   </si>
   <si>
     <t xml:space="preserve">34.9427642822266</t>
@@ -3038,37 +3038,37 @@
     <t xml:space="preserve">34.8854598999023</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0000648498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.80224609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5539474487305</t>
+    <t xml:space="preserve">35.0000610351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8022422790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5539512634277</t>
   </si>
   <si>
     <t xml:space="preserve">35.3343048095703</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2551765441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9018287658691</t>
+    <t xml:space="preserve">34.2551727294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9018249511719</t>
   </si>
   <si>
     <t xml:space="preserve">33.3670387268066</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3192901611328</t>
+    <t xml:space="preserve">33.3192863464355</t>
   </si>
   <si>
     <t xml:space="preserve">31.7817707061768</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8104248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4598121643066</t>
+    <t xml:space="preserve">31.8104209899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4598083496094</t>
   </si>
   <si>
     <t xml:space="preserve">32.7081031799316</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">30.3875007629395</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6453456878662</t>
+    <t xml:space="preserve">30.6453437805176</t>
   </si>
   <si>
     <t xml:space="preserve">31.4761772155762</t>
@@ -3098,31 +3098,31 @@
     <t xml:space="preserve">30.5211944580078</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7312927246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1228351593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5498447418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5375652313232</t>
+    <t xml:space="preserve">30.7312908172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1228332519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5498466491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5375671386719</t>
   </si>
   <si>
     <t xml:space="preserve">30.148754119873</t>
   </si>
   <si>
-    <t xml:space="preserve">31.667179107666</t>
-  </si>
-  <si>
-    